--- a/data/MFEA.MI.xlsx
+++ b/data/MFEA.MI.xlsx
@@ -27489,6 +27489,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1180">
+      <c r="A1180" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1180" t="n">
+        <v>951022</v>
+      </c>
+      <c r="C1180" t="n">
+        <v>2.5460000038147</v>
+      </c>
+      <c r="D1180" t="n">
+        <v>2.49600005149841</v>
+      </c>
+      <c r="E1180" t="n">
+        <v>2.50600004196167</v>
+      </c>
+      <c r="F1180" t="n">
+        <v>2.51200008392334</v>
+      </c>
+      <c r="G1180" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MFEA.MI.xlsx
+++ b/data/MFEA.MI.xlsx
@@ -27512,6 +27512,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1181">
+      <c r="A1181" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1181" t="n">
+        <v>1295594</v>
+      </c>
+      <c r="C1181" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="D1181" t="n">
+        <v>2.48799991607666</v>
+      </c>
+      <c r="E1181" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F1181" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G1181" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MFEA.MI.xlsx
+++ b/data/MFEA.MI.xlsx
@@ -27535,6 +27535,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1182">
+      <c r="A1182" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1182" t="n">
+        <v>1840561</v>
+      </c>
+      <c r="C1182" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="D1182" t="n">
+        <v>2.43400001525879</v>
+      </c>
+      <c r="E1182" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="F1182" t="n">
+        <v>2.43400001525879</v>
+      </c>
+      <c r="G1182" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MFEA.MI.xlsx
+++ b/data/MFEA.MI.xlsx
@@ -27558,6 +27558,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1183">
+      <c r="A1183" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1183" t="n">
+        <v>5299649</v>
+      </c>
+      <c r="C1183" t="n">
+        <v>2.55999994277954</v>
+      </c>
+      <c r="D1183" t="n">
+        <v>2.38199996948242</v>
+      </c>
+      <c r="E1183" t="n">
+        <v>2.48000001907349</v>
+      </c>
+      <c r="F1183" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="G1183" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MFEA.MI.xlsx
+++ b/data/MFEA.MI.xlsx
@@ -27399,16 +27399,16 @@
     </row>
     <row r="1176">
       <c r="A1176" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1176" t="n">
-        <v>1464354</v>
+        <v>1389414</v>
       </c>
       <c r="C1176" t="n">
-        <v>2.48600006103516</v>
+        <v>2.49000000953674</v>
       </c>
       <c r="D1176" t="n">
-        <v>2.4539999961853</v>
+        <v>2.46000003814697</v>
       </c>
       <c r="E1176" t="n">
         <v>2.48000001907349</v>
@@ -27422,22 +27422,22 @@
     </row>
     <row r="1177">
       <c r="A1177" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1177" t="n">
-        <v>1863001</v>
+        <v>1464354</v>
       </c>
       <c r="C1177" t="n">
-        <v>2.4760000705719</v>
+        <v>2.48600006103516</v>
       </c>
       <c r="D1177" t="n">
-        <v>2.43199992179871</v>
+        <v>2.4539999961853</v>
       </c>
       <c r="E1177" t="n">
-        <v>2.46000003814697</v>
+        <v>2.48000001907349</v>
       </c>
       <c r="F1177" t="n">
-        <v>2.45799994468689</v>
+        <v>2.47000002861023</v>
       </c>
       <c r="G1177" t="s">
         <v>7</v>
@@ -27445,22 +27445,22 @@
     </row>
     <row r="1178">
       <c r="A1178" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1178" t="n">
-        <v>1074279</v>
+        <v>1863001</v>
       </c>
       <c r="C1178" t="n">
-        <v>2.47399997711182</v>
+        <v>2.4760000705719</v>
       </c>
       <c r="D1178" t="n">
-        <v>2.45000004768372</v>
+        <v>2.43199992179871</v>
       </c>
       <c r="E1178" t="n">
-        <v>2.45000004768372</v>
+        <v>2.46000003814697</v>
       </c>
       <c r="F1178" t="n">
-        <v>2.46199989318848</v>
+        <v>2.45799994468689</v>
       </c>
       <c r="G1178" t="s">
         <v>7</v>
@@ -27468,22 +27468,22 @@
     </row>
     <row r="1179">
       <c r="A1179" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1179" t="n">
-        <v>1649594</v>
+        <v>1074279</v>
       </c>
       <c r="C1179" t="n">
-        <v>2.5220000743866</v>
+        <v>2.47399997711182</v>
       </c>
       <c r="D1179" t="n">
+        <v>2.45000004768372</v>
+      </c>
+      <c r="E1179" t="n">
+        <v>2.45000004768372</v>
+      </c>
+      <c r="F1179" t="n">
         <v>2.46199989318848</v>
-      </c>
-      <c r="E1179" t="n">
-        <v>2.46199989318848</v>
-      </c>
-      <c r="F1179" t="n">
-        <v>2.50600004196167</v>
       </c>
       <c r="G1179" t="s">
         <v>7</v>
@@ -27491,22 +27491,22 @@
     </row>
     <row r="1180">
       <c r="A1180" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1180" t="n">
-        <v>951022</v>
+        <v>1649594</v>
       </c>
       <c r="C1180" t="n">
-        <v>2.5460000038147</v>
+        <v>2.5220000743866</v>
       </c>
       <c r="D1180" t="n">
-        <v>2.49600005149841</v>
+        <v>2.46199989318848</v>
       </c>
       <c r="E1180" t="n">
+        <v>2.46199989318848</v>
+      </c>
+      <c r="F1180" t="n">
         <v>2.50600004196167</v>
-      </c>
-      <c r="F1180" t="n">
-        <v>2.51200008392334</v>
       </c>
       <c r="G1180" t="s">
         <v>7</v>
@@ -27514,22 +27514,22 @@
     </row>
     <row r="1181">
       <c r="A1181" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1181" t="n">
-        <v>1295594</v>
+        <v>951022</v>
       </c>
       <c r="C1181" t="n">
-        <v>2.51999998092651</v>
+        <v>2.5460000038147</v>
       </c>
       <c r="D1181" t="n">
-        <v>2.48799991607666</v>
+        <v>2.49600005149841</v>
       </c>
       <c r="E1181" t="n">
-        <v>2.5</v>
+        <v>2.50600004196167</v>
       </c>
       <c r="F1181" t="n">
-        <v>2.5</v>
+        <v>2.51200008392334</v>
       </c>
       <c r="G1181" t="s">
         <v>7</v>
@@ -27537,22 +27537,22 @@
     </row>
     <row r="1182">
       <c r="A1182" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1182" t="n">
-        <v>1840561</v>
+        <v>1295594</v>
       </c>
       <c r="C1182" t="n">
         <v>2.51999998092651</v>
       </c>
       <c r="D1182" t="n">
-        <v>2.43400001525879</v>
+        <v>2.48799991607666</v>
       </c>
       <c r="E1182" t="n">
-        <v>2.51999998092651</v>
+        <v>2.5</v>
       </c>
       <c r="F1182" t="n">
-        <v>2.43400001525879</v>
+        <v>2.5</v>
       </c>
       <c r="G1182" t="s">
         <v>7</v>
@@ -27560,24 +27560,47 @@
     </row>
     <row r="1183">
       <c r="A1183" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1183" t="n">
-        <v>5299649</v>
+        <v>1840561</v>
       </c>
       <c r="C1183" t="n">
-        <v>2.55999994277954</v>
+        <v>2.51999998092651</v>
       </c>
       <c r="D1183" t="n">
-        <v>2.38199996948242</v>
+        <v>2.43400001525879</v>
       </c>
       <c r="E1183" t="n">
-        <v>2.48000001907349</v>
+        <v>2.51999998092651</v>
       </c>
       <c r="F1183" t="n">
+        <v>2.43400001525879</v>
+      </c>
+      <c r="G1183" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1184" t="n">
+        <v>7335424</v>
+      </c>
+      <c r="C1184" t="n">
+        <v>2.39599990844727</v>
+      </c>
+      <c r="D1184" t="n">
+        <v>2.34599995613098</v>
+      </c>
+      <c r="E1184" t="n">
         <v>2.38000011444092</v>
       </c>
-      <c r="G1183" t="s">
+      <c r="F1184" t="n">
+        <v>2.36800003051758</v>
+      </c>
+      <c r="G1184" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MFEA.MI.xlsx
+++ b/data/MFEA.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.9375</v>
       </c>
       <c r="G2" t="n">
-        <v>2.42752814292908</v>
+        <v>2.42752838134766</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G3" t="n">
-        <v>2.25028014183044</v>
+        <v>2.25027990341187</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>3.71250009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>2.28881216049194</v>
+        <v>2.28881239891052</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G6" t="n">
-        <v>2.28727078437805</v>
+        <v>2.28727102279663</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.70749998092651</v>
       </c>
       <c r="G7" t="n">
-        <v>2.28572964668274</v>
+        <v>2.28572940826416</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G8" t="n">
-        <v>2.27494072914124</v>
+        <v>2.27494049072266</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G9" t="n">
-        <v>2.34892225265503</v>
+        <v>2.34892249107361</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>2.33659219741821</v>
+        <v>2.33659195899963</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G11" t="n">
-        <v>2.31501388549805</v>
+        <v>2.31501436233521</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G12" t="n">
-        <v>2.29035329818726</v>
+        <v>2.29035353660583</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G18" t="n">
-        <v>2.66951036453247</v>
+        <v>2.66951012611389</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G21" t="n">
-        <v>2.64793229103088</v>
+        <v>2.6479320526123</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>3.99499988555908</v>
       </c>
       <c r="G25" t="n">
-        <v>2.46297740936279</v>
+        <v>2.46297764778137</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G30" t="n">
-        <v>2.41365647315979</v>
+        <v>2.41365623474121</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>3.92750000953674</v>
       </c>
       <c r="G36" t="n">
-        <v>2.42136311531067</v>
+        <v>2.42136287689209</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.14249992370605</v>
       </c>
       <c r="G37" t="n">
-        <v>2.55391383171082</v>
+        <v>2.55391359329224</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.5</v>
       </c>
       <c r="G41" t="n">
-        <v>2.15780282020569</v>
+        <v>2.15780258178711</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.26749992370605</v>
       </c>
       <c r="G47" t="n">
-        <v>2.01446270942688</v>
+        <v>2.01446294784546</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G49" t="n">
-        <v>2.07149028778076</v>
+        <v>2.07149052619934</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.17750000953674</v>
       </c>
       <c r="G51" t="n">
-        <v>1.95897650718689</v>
+        <v>1.95897674560547</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G52" t="n">
-        <v>1.99442648887634</v>
+        <v>1.99442601203918</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.1175000667572</v>
       </c>
       <c r="G54" t="n">
-        <v>1.9219856262207</v>
+        <v>1.92198586463928</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3</v>
       </c>
       <c r="G57" t="n">
-        <v>1.84954512119293</v>
+        <v>1.84954524040222</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G60" t="n">
-        <v>1.79714155197144</v>
+        <v>1.79714143276215</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G61" t="n">
-        <v>1.80638909339905</v>
+        <v>1.80638921260834</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>2.96250009536743</v>
       </c>
       <c r="G62" t="n">
-        <v>1.82642602920532</v>
+        <v>1.82642579078674</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G64" t="n">
-        <v>1.8772885799408</v>
+        <v>1.87728834152222</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G68" t="n">
-        <v>1.66150832176208</v>
+        <v>1.66150796413422</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.92750000953674</v>
       </c>
       <c r="G70" t="n">
-        <v>1.80484795570374</v>
+        <v>1.80484771728516</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.88750004768372</v>
       </c>
       <c r="G72" t="n">
-        <v>1.78018724918365</v>
+        <v>1.78018736839294</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G75" t="n">
-        <v>1.66150832176208</v>
+        <v>1.66150796413422</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G76" t="n">
-        <v>1.63376498222351</v>
+        <v>1.63376486301422</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>1.64917778968811</v>
+        <v>1.6491779088974</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G78" t="n">
-        <v>1.74782013893127</v>
+        <v>1.74782001972198</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>2.66750001907349</v>
       </c>
       <c r="G79" t="n">
-        <v>1.64455389976501</v>
+        <v>1.6445540189743</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>2.68249988555908</v>
       </c>
       <c r="G80" t="n">
-        <v>1.65380167961121</v>
+        <v>1.65380156040192</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G81" t="n">
-        <v>1.62143456935883</v>
+        <v>1.62143468856812</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G82" t="n">
-        <v>1.63068246841431</v>
+        <v>1.63068234920502</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>2.58750009536743</v>
       </c>
       <c r="G85" t="n">
-        <v>1.59523272514343</v>
+        <v>1.59523284435272</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G86" t="n">
-        <v>1.58752632141113</v>
+        <v>1.58752644062042</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>2.64750003814697</v>
       </c>
       <c r="G88" t="n">
-        <v>1.6322238445282</v>
+        <v>1.63222372531891</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.65499997138977</v>
       </c>
       <c r="G89" t="n">
-        <v>1.636847615242</v>
+        <v>1.63684749603271</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G90" t="n">
-        <v>1.62143456935883</v>
+        <v>1.62143468856812</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>2.66750001907349</v>
       </c>
       <c r="G92" t="n">
-        <v>1.64455389976501</v>
+        <v>1.6445540189743</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G93" t="n">
-        <v>1.63068246841431</v>
+        <v>1.63068234920502</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G94" t="n">
-        <v>1.6399302482605</v>
+        <v>1.63993012905121</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G95" t="n">
-        <v>1.59985673427582</v>
+        <v>1.59985649585724</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.6324999332428</v>
       </c>
       <c r="G96" t="n">
-        <v>1.62297582626343</v>
+        <v>1.62297606468201</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G98" t="n">
-        <v>1.66459083557129</v>
+        <v>1.66459059715271</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>1.60602176189423</v>
+        <v>1.60602188110352</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G101" t="n">
-        <v>1.4549754858017</v>
+        <v>1.45497536659241</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G103" t="n">
-        <v>1.45867466926575</v>
+        <v>1.45867455005646</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G104" t="n">
-        <v>1.37482845783234</v>
+        <v>1.37482857704163</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G106" t="n">
-        <v>1.39085793495178</v>
+        <v>1.39085805416107</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>1.33475518226624</v>
+        <v>1.33475506305695</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.11899995803833</v>
       </c>
       <c r="G108" t="n">
-        <v>1.30639553070068</v>
+        <v>1.30639541149139</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.24900007247925</v>
       </c>
       <c r="G112" t="n">
-        <v>1.38654255867004</v>
+        <v>1.38654243946075</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.22300004959106</v>
       </c>
       <c r="G113" t="n">
-        <v>1.37051296234131</v>
+        <v>1.3705130815506</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G120" t="n">
-        <v>1.37236249446869</v>
+        <v>1.3723623752594</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G121" t="n">
-        <v>1.40565431118011</v>
+        <v>1.4056544303894</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.22099995613098</v>
       </c>
       <c r="G122" t="n">
-        <v>1.36927998065948</v>
+        <v>1.3692798614502</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.18300008773804</v>
       </c>
       <c r="G123" t="n">
-        <v>1.34585249423981</v>
+        <v>1.34585237503052</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G127" t="n">
-        <v>1.33043956756592</v>
+        <v>1.33043944835663</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G128" t="n">
-        <v>1.35325038433075</v>
+        <v>1.35325050354004</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>1.28543388843536</v>
+        <v>1.28543400764465</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G138" t="n">
-        <v>1.32304120063782</v>
+        <v>1.32304131984711</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G139" t="n">
-        <v>1.27002096176147</v>
+        <v>1.27002108097076</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>2.30900001525879</v>
       </c>
       <c r="G145" t="n">
-        <v>1.42353320121765</v>
+        <v>1.42353332042694</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G146" t="n">
-        <v>1.4025719165802</v>
+        <v>1.40257179737091</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G147" t="n">
-        <v>1.35325038433075</v>
+        <v>1.35325050354004</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G148" t="n">
-        <v>1.35633325576782</v>
+        <v>1.35633313655853</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.04699993133545</v>
       </c>
       <c r="G150" t="n">
-        <v>1.2620062828064</v>
+        <v>1.26200640201569</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G155" t="n">
-        <v>1.28235125541687</v>
+        <v>1.28235137462616</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G157" t="n">
-        <v>1.30392944812775</v>
+        <v>1.30392932891846</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G160" t="n">
-        <v>1.29098260402679</v>
+        <v>1.2909824848175</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G162" t="n">
-        <v>1.28235125541687</v>
+        <v>1.28235137462616</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G163" t="n">
-        <v>1.28235125541687</v>
+        <v>1.28235137462616</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G166" t="n">
-        <v>1.28543388843536</v>
+        <v>1.28543400764465</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.06900000572205</v>
       </c>
       <c r="G167" t="n">
-        <v>1.27556979656219</v>
+        <v>1.27556967735291</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G168" t="n">
-        <v>1.24782657623291</v>
+        <v>1.24782645702362</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>1.65199995040894</v>
       </c>
       <c r="G173" t="n">
-        <v>1.16406345367432</v>
+        <v>1.16406357288361</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>1.53900003433228</v>
       </c>
       <c r="G176" t="n">
-        <v>1.08443939685822</v>
+        <v>1.0844395160675</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G180" t="n">
-        <v>1.08514404296875</v>
+        <v>1.08514416217804</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>1.54700005054474</v>
       </c>
       <c r="G182" t="n">
-        <v>1.09007656574249</v>
+        <v>1.09007668495178</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G186" t="n">
-        <v>1.06752800941467</v>
+        <v>1.06752812862396</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>1.54200005531311</v>
       </c>
       <c r="G188" t="n">
-        <v>1.08655333518982</v>
+        <v>1.08655345439911</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>1.5110000371933</v>
       </c>
       <c r="G189" t="n">
-        <v>1.06470942497253</v>
+        <v>1.06470954418182</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G190" t="n">
-        <v>1.11473882198334</v>
+        <v>1.11473894119263</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>1.68900001049042</v>
       </c>
       <c r="G196" t="n">
-        <v>1.19013524055481</v>
+        <v>1.1901353597641</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>1.73800003528595</v>
       </c>
       <c r="G199" t="n">
-        <v>1.22466254234314</v>
+        <v>1.22466266155243</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>1.77300000190735</v>
       </c>
       <c r="G200" t="n">
-        <v>1.24932479858398</v>
+        <v>1.24932491779327</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G201" t="n">
-        <v>1.2577805519104</v>
+        <v>1.25778067111969</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>1.78199994564056</v>
       </c>
       <c r="G202" t="n">
-        <v>1.25566673278809</v>
+        <v>1.2556666135788</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>1.74699997901917</v>
       </c>
       <c r="G204" t="n">
-        <v>1.23100435733795</v>
+        <v>1.23100423812866</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>1.84399998188019</v>
       </c>
       <c r="G206" t="n">
-        <v>1.29935419559479</v>
+        <v>1.29935431480408</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>1.86800003051758</v>
       </c>
       <c r="G208" t="n">
-        <v>1.31626558303833</v>
+        <v>1.31626570224762</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G212" t="n">
-        <v>1.2937171459198</v>
+        <v>1.29371726512909</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>1.81099998950958</v>
       </c>
       <c r="G214" t="n">
-        <v>1.27610123157501</v>
+        <v>1.27610111236572</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G215" t="n">
-        <v>1.29301249980927</v>
+        <v>1.29301261901855</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G216" t="n">
-        <v>1.2859662771225</v>
+        <v>1.28596615791321</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>2.04699993133545</v>
       </c>
       <c r="G219" t="n">
-        <v>1.44239592552185</v>
+        <v>1.44239604473114</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G223" t="n">
-        <v>1.42618930339813</v>
+        <v>1.42618918418884</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G227" t="n">
-        <v>1.33035850524902</v>
+        <v>1.33035838603973</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G231" t="n">
-        <v>1.31908416748047</v>
+        <v>1.31908428668976</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G235" t="n">
-        <v>1.2577805519104</v>
+        <v>1.25778067111969</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G238" t="n">
-        <v>1.28455686569214</v>
+        <v>1.28455698490143</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G240" t="n">
-        <v>1.27891981601715</v>
+        <v>1.27891993522644</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>1.807000041008</v>
       </c>
       <c r="G243" t="n">
-        <v>1.27328288555145</v>
+        <v>1.27328276634216</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G250" t="n">
-        <v>1.3698183298111</v>
+        <v>1.36981821060181</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G251" t="n">
-        <v>1.38602495193481</v>
+        <v>1.38602483272552</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G252" t="n">
-        <v>1.35713469982147</v>
+        <v>1.35713481903076</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>1.98699998855591</v>
       </c>
       <c r="G256" t="n">
-        <v>1.40011775493622</v>
+        <v>1.40011763572693</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G258" t="n">
-        <v>1.39236652851105</v>
+        <v>1.39236664772034</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>1.942999958992</v>
       </c>
       <c r="G261" t="n">
-        <v>1.36911344528198</v>
+        <v>1.36911356449127</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.05699992179871</v>
       </c>
       <c r="G266" t="n">
-        <v>1.4494423866272</v>
+        <v>1.44944226741791</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G267" t="n">
-        <v>1.52765727043152</v>
+        <v>1.52765738964081</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G270" t="n">
-        <v>1.55161499977112</v>
+        <v>1.55161488056183</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.18300008773804</v>
       </c>
       <c r="G271" t="n">
-        <v>1.53822696208954</v>
+        <v>1.53822684288025</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G272" t="n">
-        <v>1.53329455852509</v>
+        <v>1.5332944393158</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>2.125</v>
       </c>
       <c r="G273" t="n">
-        <v>1.4973578453064</v>
+        <v>1.49735796451569</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G276" t="n">
-        <v>1.48819768428802</v>
+        <v>1.48819756507874</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>2.06699991226196</v>
       </c>
       <c r="G278" t="n">
-        <v>1.45648860931396</v>
+        <v>1.45648872852325</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G280" t="n">
-        <v>1.44450998306274</v>
+        <v>1.44450986385345</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.03699994087219</v>
       </c>
       <c r="G281" t="n">
-        <v>1.43534970283508</v>
+        <v>1.43534958362579</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G282" t="n">
-        <v>1.44450998306274</v>
+        <v>1.44450986385345</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G293" t="n">
-        <v>1.49101614952087</v>
+        <v>1.49101603031158</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G295" t="n">
-        <v>1.51074612140656</v>
+        <v>1.51074600219727</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>2.125</v>
       </c>
       <c r="G296" t="n">
-        <v>1.4973578453064</v>
+        <v>1.49735796451569</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>2.12299990653992</v>
       </c>
       <c r="G297" t="n">
-        <v>1.49594867229462</v>
+        <v>1.49594855308533</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G298" t="n">
-        <v>1.47551417350769</v>
+        <v>1.4755140542984</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G302" t="n">
-        <v>1.52202022075653</v>
+        <v>1.52202033996582</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G303" t="n">
-        <v>1.47974181175232</v>
+        <v>1.47974169254303</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>2.06699991226196</v>
       </c>
       <c r="G304" t="n">
-        <v>1.45648860931396</v>
+        <v>1.45648872852325</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>2.12299990653992</v>
       </c>
       <c r="G307" t="n">
-        <v>1.49594867229462</v>
+        <v>1.49594855308533</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G308" t="n">
-        <v>1.49383461475372</v>
+        <v>1.49383449554443</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.18300008773804</v>
       </c>
       <c r="G311" t="n">
-        <v>1.53822696208954</v>
+        <v>1.53822684288025</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G313" t="n">
-        <v>1.61855578422546</v>
+        <v>1.61855566501617</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G314" t="n">
-        <v>1.59600734710693</v>
+        <v>1.59600746631622</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G315" t="n">
-        <v>1.61855578422546</v>
+        <v>1.61855566501617</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G318" t="n">
-        <v>1.60305380821228</v>
+        <v>1.60305368900299</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.29299998283386</v>
       </c>
       <c r="G319" t="n">
-        <v>1.61573719978333</v>
+        <v>1.61573731899261</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G321" t="n">
-        <v>1.63758087158203</v>
+        <v>1.63758099079132</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G323" t="n">
-        <v>1.60234892368317</v>
+        <v>1.60234904289246</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G326" t="n">
-        <v>1.51074612140656</v>
+        <v>1.51074600219727</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.22099995613098</v>
       </c>
       <c r="G332" t="n">
-        <v>1.56500327587128</v>
+        <v>1.5650030374527</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G333" t="n">
-        <v>1.54456865787506</v>
+        <v>1.54456853866577</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G336" t="n">
-        <v>1.61855578422546</v>
+        <v>1.61855566501617</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G338" t="n">
-        <v>1.59671187400818</v>
+        <v>1.59671199321747</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>1.6453320980072</v>
+        <v>1.64533197879791</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G347" t="n">
-        <v>1.62912535667419</v>
+        <v>1.62912547588348</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G348" t="n">
-        <v>1.56147992610931</v>
+        <v>1.5614800453186</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G350" t="n">
-        <v>1.55161499977112</v>
+        <v>1.55161488056183</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.19400000572205</v>
       </c>
       <c r="G351" t="n">
-        <v>1.54597806930542</v>
+        <v>1.54597795009613</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>2.27099990844727</v>
       </c>
       <c r="G353" t="n">
-        <v>1.60023522377014</v>
+        <v>1.60023510456085</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2.26900005340576</v>
       </c>
       <c r="G354" t="n">
-        <v>1.59882593154907</v>
+        <v>1.59882581233978</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>2.36400008201599</v>
       </c>
       <c r="G355" t="n">
-        <v>1.66576659679413</v>
+        <v>1.66576671600342</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>2.83750009536743</v>
       </c>
       <c r="G357" t="n">
-        <v>1.99941301345825</v>
+        <v>1.99941325187683</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G359" t="n">
-        <v>1.86729335784912</v>
+        <v>1.86729323863983</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2.69749999046326</v>
       </c>
       <c r="G360" t="n">
-        <v>1.90076375007629</v>
+        <v>1.90076351165771</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>2.65750002861023</v>
       </c>
       <c r="G361" t="n">
-        <v>1.87257826328278</v>
+        <v>1.8725780248642</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G362" t="n">
-        <v>1.81444549560547</v>
+        <v>1.81444561481476</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>2.54250001907349</v>
       </c>
       <c r="G363" t="n">
-        <v>1.79154443740845</v>
+        <v>1.79154467582703</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G365" t="n">
-        <v>1.7933064699173</v>
+        <v>1.79330635070801</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G367" t="n">
-        <v>1.75736975669861</v>
+        <v>1.75736963748932</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G368" t="n">
-        <v>1.78625977039337</v>
+        <v>1.78626000881195</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G371" t="n">
-        <v>1.83206152915955</v>
+        <v>1.83206129074097</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G372" t="n">
-        <v>1.87786304950714</v>
+        <v>1.87786281108856</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G374" t="n">
-        <v>1.83910763263702</v>
+        <v>1.83910751342773</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G375" t="n">
-        <v>1.83910763263702</v>
+        <v>1.83910751342773</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G376" t="n">
-        <v>1.86377024650574</v>
+        <v>1.86377000808716</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G377" t="n">
-        <v>1.86377024650574</v>
+        <v>1.86377000808716</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>2.64249992370605</v>
       </c>
       <c r="G379" t="n">
-        <v>1.86200857162476</v>
+        <v>1.86200833320618</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>1.86377024650574</v>
+        <v>1.86377000808716</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>2.59750008583069</v>
       </c>
       <c r="G381" t="n">
-        <v>1.83029997348785</v>
+        <v>1.83029985427856</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>2.61249995231628</v>
       </c>
       <c r="G383" t="n">
-        <v>1.84086942672729</v>
+        <v>1.84086918830872</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.55749988555908</v>
       </c>
       <c r="G384" t="n">
-        <v>1.80211424827576</v>
+        <v>1.80211412906647</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.55250000953674</v>
       </c>
       <c r="G385" t="n">
-        <v>1.79859113693237</v>
+        <v>1.79859101772308</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G387" t="n">
-        <v>1.80601191520691</v>
+        <v>1.8060120344162</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>2.27699995040894</v>
       </c>
       <c r="G388" t="n">
-        <v>1.77867162227631</v>
+        <v>1.7786717414856</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G392" t="n">
-        <v>1.84741282463074</v>
+        <v>1.84741270542145</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G393" t="n">
-        <v>1.86069202423096</v>
+        <v>1.86069226264954</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G395" t="n">
-        <v>1.84506916999817</v>
+        <v>1.84506928920746</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G397" t="n">
-        <v>1.79429471492767</v>
+        <v>1.79429459571838</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G402" t="n">
-        <v>1.85444307327271</v>
+        <v>1.85444319248199</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.34299993515015</v>
       </c>
       <c r="G404" t="n">
-        <v>1.83022737503052</v>
+        <v>1.83022749423981</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G406" t="n">
-        <v>1.82944643497467</v>
+        <v>1.82944631576538</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.33899998664856</v>
       </c>
       <c r="G407" t="n">
-        <v>1.82710301876068</v>
+        <v>1.82710289955139</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G411" t="n">
-        <v>1.80601191520691</v>
+        <v>1.8060120344162</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>2.27699995040894</v>
       </c>
       <c r="G416" t="n">
-        <v>1.77867162227631</v>
+        <v>1.7786717414856</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G417" t="n">
-        <v>1.7794531583786</v>
+        <v>1.77945303916931</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>2.23699998855591</v>
       </c>
       <c r="G419" t="n">
-        <v>1.74742603302002</v>
+        <v>1.74742591381073</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2.11700010299683</v>
       </c>
       <c r="G426" t="n">
-        <v>1.65368831157684</v>
+        <v>1.65368843078613</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.11299991607666</v>
       </c>
       <c r="G427" t="n">
-        <v>1.65056359767914</v>
+        <v>1.65056347846985</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>1.97699999809265</v>
       </c>
       <c r="G433" t="n">
-        <v>1.54432761669159</v>
+        <v>1.54432773590088</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G436" t="n">
-        <v>1.45762050151825</v>
+        <v>1.45762038230896</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G437" t="n">
-        <v>1.44121634960175</v>
+        <v>1.44121623039246</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G441" t="n">
-        <v>1.48417925834656</v>
+        <v>1.48417937755585</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G442" t="n">
-        <v>1.48417925834656</v>
+        <v>1.48417937755585</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G445" t="n">
-        <v>1.48886620998383</v>
+        <v>1.48886632919312</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>1.85300004482269</v>
       </c>
       <c r="G447" t="n">
-        <v>1.44746553897858</v>
+        <v>1.44746541976929</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G451" t="n">
-        <v>1.40997040271759</v>
+        <v>1.4099702835083</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>1.69219994544983</v>
       </c>
       <c r="G455" t="n">
-        <v>1.32185697555542</v>
+        <v>1.32185685634613</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>1.69159996509552</v>
       </c>
       <c r="G457" t="n">
-        <v>1.3213883638382</v>
+        <v>1.32138824462891</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>1.94939994812012</v>
       </c>
       <c r="G463" t="n">
-        <v>1.52276790142059</v>
+        <v>1.52276802062988</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>1.93680000305176</v>
       </c>
       <c r="G464" t="n">
-        <v>1.51292562484741</v>
+        <v>1.51292550563812</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>1.92239999771118</v>
       </c>
       <c r="G465" t="n">
-        <v>1.50167715549469</v>
+        <v>1.5016770362854</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>2.02049994468689</v>
       </c>
       <c r="G467" t="n">
-        <v>1.57830739021301</v>
+        <v>1.5783075094223</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>1.97259998321533</v>
       </c>
       <c r="G468" t="n">
-        <v>1.54089069366455</v>
+        <v>1.54089057445526</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>2.15249991416931</v>
       </c>
       <c r="G473" t="n">
-        <v>1.68141889572144</v>
+        <v>1.68141901493073</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>2.29450011253357</v>
       </c>
       <c r="G474" t="n">
-        <v>1.79234206676483</v>
+        <v>1.79234182834625</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>2.25950002670288</v>
       </c>
       <c r="G475" t="n">
-        <v>1.76500177383423</v>
+        <v>1.76500165462494</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G477" t="n">
-        <v>1.75601840019226</v>
+        <v>1.75601851940155</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>2.22699999809265</v>
       </c>
       <c r="G478" t="n">
-        <v>1.73961436748505</v>
+        <v>1.73961448669434</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G480" t="n">
-        <v>1.74664485454559</v>
+        <v>1.74664497375488</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>2.31900000572205</v>
       </c>
       <c r="G482" t="n">
-        <v>1.81147992610931</v>
+        <v>1.8114800453186</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>2.33599996566772</v>
       </c>
       <c r="G484" t="n">
-        <v>1.82475936412811</v>
+        <v>1.8247594833374</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G485" t="n">
-        <v>1.86850380897522</v>
+        <v>1.86850357055664</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>2.33150005340576</v>
       </c>
       <c r="G488" t="n">
-        <v>1.82124447822571</v>
+        <v>1.82124435901642</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.34949994087219</v>
       </c>
       <c r="G489" t="n">
-        <v>1.83530497550964</v>
+        <v>1.83530509471893</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>2.39750003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>1.87280023097992</v>
+        <v>1.87279999256134</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.3989999294281</v>
       </c>
       <c r="G492" t="n">
-        <v>1.87397170066833</v>
+        <v>1.87397146224976</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G493" t="n">
-        <v>1.86225473880768</v>
+        <v>1.8622545003891</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G497" t="n">
-        <v>1.84194481372833</v>
+        <v>1.84194469451904</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.35899996757507</v>
       </c>
       <c r="G500" t="n">
-        <v>1.84272575378418</v>
+        <v>1.84272587299347</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G501" t="n">
-        <v>1.86069202423096</v>
+        <v>1.86069226264954</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G504" t="n">
-        <v>1.90443634986877</v>
+        <v>1.90443658828735</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.38750004768372</v>
       </c>
       <c r="G508" t="n">
-        <v>1.86498844623566</v>
+        <v>1.86498868465424</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>2.33949995040894</v>
       </c>
       <c r="G510" t="n">
-        <v>1.82749342918396</v>
+        <v>1.82749330997467</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G514" t="n">
-        <v>1.84819388389587</v>
+        <v>1.84819364547729</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>2.38700008392334</v>
       </c>
       <c r="G516" t="n">
-        <v>1.86459815502167</v>
+        <v>1.86459791660309</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G519" t="n">
-        <v>1.84506916999817</v>
+        <v>1.84506928920746</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G523" t="n">
-        <v>1.74352014064789</v>
+        <v>1.74352025985718</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>2.18650007247925</v>
       </c>
       <c r="G525" t="n">
-        <v>1.7079781293869</v>
+        <v>1.70797801017761</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>2.1324999332428</v>
       </c>
       <c r="G529" t="n">
-        <v>1.66579592227936</v>
+        <v>1.66579604148865</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G530" t="n">
-        <v>1.65603160858154</v>
+        <v>1.65603148937225</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G532" t="n">
-        <v>1.62478566169739</v>
+        <v>1.62478578090668</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>2.07750010490417</v>
       </c>
       <c r="G533" t="n">
-        <v>1.62283313274384</v>
+        <v>1.62283301353455</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>2.11150002479553</v>
       </c>
       <c r="G538" t="n">
-        <v>1.64939188957214</v>
+        <v>1.64939200878143</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.09249997138977</v>
       </c>
       <c r="G544" t="n">
-        <v>1.63455021381378</v>
+        <v>1.63455009460449</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.14299988746643</v>
       </c>
       <c r="G546" t="n">
-        <v>1.67399787902832</v>
+        <v>1.67399799823761</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>2.12949991226196</v>
       </c>
       <c r="G549" t="n">
-        <v>1.66345262527466</v>
+        <v>1.66345250606537</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.24300003051758</v>
       </c>
       <c r="G554" t="n">
-        <v>1.752112865448</v>
+        <v>1.75211298465729</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G555" t="n">
-        <v>1.74352014064789</v>
+        <v>1.74352025985718</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>2.24449992179871</v>
       </c>
       <c r="G556" t="n">
-        <v>1.75328457355499</v>
+        <v>1.7532844543457</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.30550003051758</v>
       </c>
       <c r="G557" t="n">
-        <v>1.80093443393707</v>
+        <v>1.80093455314636</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.42149996757507</v>
       </c>
       <c r="G559" t="n">
-        <v>1.89154732227325</v>
+        <v>1.89154756069183</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G568" t="n">
-        <v>1.99661159515381</v>
+        <v>1.99661183357239</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G569" t="n">
-        <v>1.92005944252014</v>
+        <v>1.92005920410156</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G570" t="n">
-        <v>1.92943322658539</v>
+        <v>1.9294331073761</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G575" t="n">
-        <v>2.04660511016846</v>
+        <v>2.04660534858704</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G585" t="n">
-        <v>2.19658541679382</v>
+        <v>2.1965856552124</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G586" t="n">
-        <v>2.2575147151947</v>
+        <v>2.25751495361328</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G588" t="n">
-        <v>2.31219530105591</v>
+        <v>2.31219506263733</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>3.05599999427795</v>
       </c>
       <c r="G593" t="n">
-        <v>2.3871853351593</v>
+        <v>2.38718557357788</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>3.04200005531311</v>
       </c>
       <c r="G598" t="n">
-        <v>2.37624931335449</v>
+        <v>2.37624955177307</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>3.06800007820129</v>
       </c>
       <c r="G602" t="n">
-        <v>2.39655900001526</v>
+        <v>2.39655923843384</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G603" t="n">
-        <v>2.4653000831604</v>
+        <v>2.46529984474182</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G604" t="n">
-        <v>2.4653000831604</v>
+        <v>2.46529984474182</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>3.17400002479553</v>
       </c>
       <c r="G605" t="n">
-        <v>2.47936081886292</v>
+        <v>2.47936058044434</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G609" t="n">
-        <v>2.54810166358948</v>
+        <v>2.54810190200806</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G610" t="n">
-        <v>2.46373772621155</v>
+        <v>2.46373796463013</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G612" t="n">
-        <v>2.41374444961548</v>
+        <v>2.4137442111969</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>3.09599995613098</v>
       </c>
       <c r="G614" t="n">
-        <v>2.41843104362488</v>
+        <v>2.41843128204346</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G615" t="n">
-        <v>2.42155575752258</v>
+        <v>2.421555519104</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>3.24200010299683</v>
       </c>
       <c r="G628" t="n">
-        <v>2.53247880935669</v>
+        <v>2.53247857093811</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>3.26399993896484</v>
       </c>
       <c r="G629" t="n">
-        <v>2.54966402053833</v>
+        <v>2.54966378211975</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G630" t="n">
-        <v>2.56216216087341</v>
+        <v>2.56216239929199</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G640" t="n">
-        <v>2.66151189804077</v>
+        <v>2.66151165962219</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G645" t="n">
-        <v>2.65814280509949</v>
+        <v>2.65814256668091</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G647" t="n">
-        <v>2.59413146972656</v>
+        <v>2.59413170814514</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>3.01399993896484</v>
       </c>
       <c r="G648" t="n">
-        <v>2.53854298591614</v>
+        <v>2.53854322433472</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G651" t="n">
-        <v>2.44926476478577</v>
+        <v>2.44926452636719</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G657" t="n">
-        <v>2.45600247383118</v>
+        <v>2.45600271224976</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G662" t="n">
-        <v>2.47116327285767</v>
+        <v>2.47116303443909</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G666" t="n">
-        <v>2.48800802230835</v>
+        <v>2.48800826072693</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>2.89800000190735</v>
       </c>
       <c r="G668" t="n">
-        <v>2.44084191322327</v>
+        <v>2.44084215164185</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G678" t="n">
-        <v>2.35661697387695</v>
+        <v>2.35661721229553</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>3.22399997711182</v>
       </c>
       <c r="G681" t="n">
-        <v>2.71541571617126</v>
+        <v>2.71541595458984</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G682" t="n">
-        <v>2.57223296165466</v>
+        <v>2.57223320007324</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G688" t="n">
-        <v>2.6109766960144</v>
+        <v>2.61097645759583</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G689" t="n">
-        <v>2.58570909500122</v>
+        <v>2.5857093334198</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G690" t="n">
-        <v>2.57560229301453</v>
+        <v>2.57560205459595</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G691" t="n">
-        <v>2.49306178092957</v>
+        <v>2.49306154251099</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>3.03200006484985</v>
       </c>
       <c r="G695" t="n">
-        <v>2.55370378494263</v>
+        <v>2.55370354652405</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>3.06800007820129</v>
       </c>
       <c r="G699" t="n">
-        <v>2.58402466773987</v>
+        <v>2.58402490615845</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G707" t="n">
-        <v>2.58570909500122</v>
+        <v>2.5857093334198</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G710" t="n">
-        <v>2.50990653038025</v>
+        <v>2.50990676879883</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>3.01399993896484</v>
       </c>
       <c r="G711" t="n">
-        <v>2.53854298591614</v>
+        <v>2.53854322433472</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G712" t="n">
-        <v>2.50990653038025</v>
+        <v>2.50990676879883</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>2.91400003433228</v>
       </c>
       <c r="G714" t="n">
-        <v>2.45431804656982</v>
+        <v>2.4543182849884</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G717" t="n">
-        <v>2.45600247383118</v>
+        <v>2.45600271224976</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G726" t="n">
-        <v>2.44926476478577</v>
+        <v>2.44926452636719</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>2.79200005531311</v>
       </c>
       <c r="G734" t="n">
-        <v>2.3515636920929</v>
+        <v>2.35156345367432</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G735" t="n">
-        <v>2.41389012336731</v>
+        <v>2.41388988494873</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>3.04200005531311</v>
       </c>
       <c r="G742" t="n">
-        <v>2.56212615966797</v>
+        <v>2.56212639808655</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G746" t="n">
-        <v>2.48295474052429</v>
+        <v>2.48295450210571</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>2.49306178092957</v>
+        <v>2.49306154251099</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>3.01399993896484</v>
       </c>
       <c r="G756" t="n">
-        <v>2.53854298591614</v>
+        <v>2.53854322433472</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G759" t="n">
-        <v>2.48295474052429</v>
+        <v>2.48295450210571</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>3.03399991989136</v>
       </c>
       <c r="G762" t="n">
-        <v>2.55538821220398</v>
+        <v>2.5553879737854</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>3.09599995613098</v>
       </c>
       <c r="G766" t="n">
-        <v>2.60760760307312</v>
+        <v>2.6076078414917</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G767" t="n">
-        <v>2.57728672027588</v>
+        <v>2.5772864818573</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G769" t="n">
-        <v>2.57560229301453</v>
+        <v>2.57560205459595</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G770" t="n">
-        <v>2.57223296165466</v>
+        <v>2.57223320007324</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G771" t="n">
-        <v>2.5890781879425</v>
+        <v>2.58907794952393</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G774" t="n">
-        <v>2.67835664749146</v>
+        <v>2.67835688591003</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>3.14199995994568</v>
       </c>
       <c r="G775" t="n">
-        <v>2.64635133743286</v>
+        <v>2.64635109901428</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G778" t="n">
-        <v>2.7171003818512</v>
+        <v>2.71710014343262</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>3.20600008964539</v>
       </c>
       <c r="G779" t="n">
-        <v>2.70025515556335</v>
+        <v>2.70025539398193</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>3.20600008964539</v>
       </c>
       <c r="G783" t="n">
-        <v>2.70025515556335</v>
+        <v>2.70025539398193</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G784" t="n">
-        <v>2.7171003818512</v>
+        <v>2.71710014343262</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G789" t="n">
-        <v>2.84680676460266</v>
+        <v>2.84680700302124</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>3.14199995994568</v>
       </c>
       <c r="G794" t="n">
-        <v>2.64635133743286</v>
+        <v>2.64635109901428</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>3.36800003051758</v>
       </c>
       <c r="G802" t="n">
-        <v>2.83669996261597</v>
+        <v>2.83669972419739</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G805" t="n">
-        <v>2.93776965141296</v>
+        <v>2.93776988983154</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>3.38800001144409</v>
       </c>
       <c r="G814" t="n">
-        <v>2.85354471206665</v>
+        <v>2.85354495048523</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G818" t="n">
-        <v>2.45600247383118</v>
+        <v>2.45600271224976</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>3.00600004196167</v>
       </c>
       <c r="G819" t="n">
-        <v>2.53180503845215</v>
+        <v>2.53180527687073</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G833" t="n">
-        <v>2.69183278083801</v>
+        <v>2.69183301925659</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G834" t="n">
-        <v>2.67835664749146</v>
+        <v>2.67835688591003</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G835" t="n">
-        <v>2.65814280509949</v>
+        <v>2.65814256668091</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G837" t="n">
-        <v>2.67835664749146</v>
+        <v>2.67835688591003</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>3.25</v>
       </c>
       <c r="G839" t="n">
-        <v>2.73731422424316</v>
+        <v>2.73731446266174</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>3.25</v>
       </c>
       <c r="G843" t="n">
-        <v>2.73731422424316</v>
+        <v>2.73731446266174</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>3.33599996566772</v>
       </c>
       <c r="G848" t="n">
-        <v>2.80974769592285</v>
+        <v>2.80974793434143</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G858" t="n">
-        <v>2.79795622825623</v>
+        <v>2.7979564666748</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G861" t="n">
-        <v>2.78784918785095</v>
+        <v>2.78784942626953</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G866" t="n">
-        <v>2.68677949905396</v>
+        <v>2.68677926063538</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G868" t="n">
-        <v>2.65814280509949</v>
+        <v>2.65814256668091</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -31208,6 +31208,32 @@
         <v>2.36199998855591</v>
       </c>
       <c r="H1186" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1187" t="n">
+        <v>2678458</v>
+      </c>
+      <c r="C1187" t="n">
+        <v>2.3840000629425</v>
+      </c>
+      <c r="D1187" t="n">
+        <v>2.31399989128113</v>
+      </c>
+      <c r="E1187" t="n">
+        <v>2.35999989509583</v>
+      </c>
+      <c r="F1187" t="n">
+        <v>2.31800007820129</v>
+      </c>
+      <c r="G1187" t="n">
+        <v>2.31800007820129</v>
+      </c>
+      <c r="H1187" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/MFEA.MI.xlsx
+++ b/data/MFEA.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.9375</v>
       </c>
       <c r="G2" t="n">
-        <v>2.42752838134766</v>
+        <v>2.42752814292908</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.70749998092651</v>
       </c>
       <c r="G7" t="n">
-        <v>2.28572940826416</v>
+        <v>2.28572964668274</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G8" t="n">
-        <v>2.27494049072266</v>
+        <v>2.27494072914124</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G11" t="n">
-        <v>2.31501436233521</v>
+        <v>2.31501412391663</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G18" t="n">
-        <v>2.66951012611389</v>
+        <v>2.66951036453247</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G20" t="n">
-        <v>2.61710619926453</v>
+        <v>2.61710643768311</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G21" t="n">
-        <v>2.6479320526123</v>
+        <v>2.64793229103088</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G22" t="n">
-        <v>2.59552836418152</v>
+        <v>2.5955286026001</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>3.98250007629395</v>
       </c>
       <c r="G27" t="n">
-        <v>2.45527124404907</v>
+        <v>2.45527148246765</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G29" t="n">
-        <v>2.47530794143677</v>
+        <v>2.47530770301819</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G31" t="n">
-        <v>2.4044086933136</v>
+        <v>2.40440893173218</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G46" t="n">
-        <v>2.02525210380554</v>
+        <v>2.02525186538696</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.26749992370605</v>
       </c>
       <c r="G47" t="n">
-        <v>2.01446294784546</v>
+        <v>2.01446270942688</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G48" t="n">
-        <v>2.03141736984253</v>
+        <v>2.03141713142395</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G50" t="n">
-        <v>2.02525210380554</v>
+        <v>2.02525186538696</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G52" t="n">
-        <v>1.99442601203918</v>
+        <v>1.99442625045776</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G53" t="n">
-        <v>1.97593080997467</v>
+        <v>1.97593069076538</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G59" t="n">
-        <v>1.79405891895294</v>
+        <v>1.79405903816223</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G60" t="n">
-        <v>1.79714143276215</v>
+        <v>1.79714131355286</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>2.96250009536743</v>
       </c>
       <c r="G62" t="n">
-        <v>1.82642579078674</v>
+        <v>1.82642602920532</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G63" t="n">
-        <v>1.81255447864532</v>
+        <v>1.81255435943604</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G64" t="n">
-        <v>1.87728834152222</v>
+        <v>1.87728846073151</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G67" t="n">
-        <v>1.69233381748199</v>
+        <v>1.69233405590057</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G68" t="n">
-        <v>1.66150796413422</v>
+        <v>1.66150808334351</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G69" t="n">
-        <v>1.65226030349731</v>
+        <v>1.6522604227066</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.92750000953674</v>
       </c>
       <c r="G70" t="n">
-        <v>1.80484771728516</v>
+        <v>1.80484783649445</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.86249995231628</v>
       </c>
       <c r="G71" t="n">
-        <v>1.76477432250977</v>
+        <v>1.76477420330048</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.88750004768372</v>
       </c>
       <c r="G72" t="n">
-        <v>1.78018736839294</v>
+        <v>1.78018724918365</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G73" t="n">
-        <v>1.74165499210358</v>
+        <v>1.74165511131287</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.75</v>
       </c>
       <c r="G74" t="n">
-        <v>1.69541645050049</v>
+        <v>1.6954163312912</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G75" t="n">
-        <v>1.66150796413422</v>
+        <v>1.66150808334351</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G76" t="n">
-        <v>1.63376486301422</v>
+        <v>1.63376498222351</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>1.6491779088974</v>
+        <v>1.64917767047882</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G78" t="n">
-        <v>1.74782001972198</v>
+        <v>1.74782013893127</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>2.66750001907349</v>
       </c>
       <c r="G79" t="n">
-        <v>1.6445540189743</v>
+        <v>1.64455389976501</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G81" t="n">
-        <v>1.62143468856812</v>
+        <v>1.62143456935883</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G82" t="n">
-        <v>1.63068234920502</v>
+        <v>1.63068246841431</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G83" t="n">
-        <v>1.60910415649414</v>
+        <v>1.60910427570343</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G84" t="n">
-        <v>1.56594812870026</v>
+        <v>1.56594824790955</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>2.58750009536743</v>
       </c>
       <c r="G85" t="n">
-        <v>1.59523284435272</v>
+        <v>1.59523260593414</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G86" t="n">
-        <v>1.58752644062042</v>
+        <v>1.58752632141113</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.65499997138977</v>
       </c>
       <c r="G89" t="n">
-        <v>1.63684749603271</v>
+        <v>1.636847615242</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G90" t="n">
-        <v>1.62143468856812</v>
+        <v>1.62143456935883</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>2.66750001907349</v>
       </c>
       <c r="G92" t="n">
-        <v>1.6445540189743</v>
+        <v>1.64455389976501</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G93" t="n">
-        <v>1.63068234920502</v>
+        <v>1.63068246841431</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G94" t="n">
-        <v>1.63993012905121</v>
+        <v>1.63993000984192</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G95" t="n">
-        <v>1.59985649585724</v>
+        <v>1.59985673427582</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.6324999332428</v>
       </c>
       <c r="G96" t="n">
-        <v>1.62297606468201</v>
+        <v>1.62297570705414</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G97" t="n">
-        <v>1.57827842235565</v>
+        <v>1.57827854156494</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G98" t="n">
-        <v>1.66459059715271</v>
+        <v>1.66459083557129</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>1.60602188110352</v>
+        <v>1.60602176189423</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.45300006866455</v>
       </c>
       <c r="G100" t="n">
-        <v>1.51231145858765</v>
+        <v>1.51231133937836</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G101" t="n">
-        <v>1.45497536659241</v>
+        <v>1.4549754858017</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G103" t="n">
-        <v>1.45867455005646</v>
+        <v>1.45867466926575</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.25699996948242</v>
       </c>
       <c r="G105" t="n">
-        <v>1.39147448539734</v>
+        <v>1.39147460460663</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G106" t="n">
-        <v>1.39085805416107</v>
+        <v>1.39085793495178</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>1.33475506305695</v>
+        <v>1.33475518226624</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G109" t="n">
-        <v>1.31934225559235</v>
+        <v>1.31934237480164</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G115" t="n">
-        <v>1.36558079719543</v>
+        <v>1.36558091640472</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G119" t="n">
-        <v>1.38099372386932</v>
+        <v>1.38099360466003</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G120" t="n">
-        <v>1.3723623752594</v>
+        <v>1.37236261367798</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G121" t="n">
-        <v>1.4056544303894</v>
+        <v>1.40565431118011</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.22099995613098</v>
       </c>
       <c r="G122" t="n">
-        <v>1.3692798614502</v>
+        <v>1.36927998065948</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.18300008773804</v>
       </c>
       <c r="G123" t="n">
-        <v>1.34585237503052</v>
+        <v>1.34585249423981</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G128" t="n">
-        <v>1.35325050354004</v>
+        <v>1.35325038433075</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>2.21399998664856</v>
       </c>
       <c r="G131" t="n">
-        <v>1.36496436595917</v>
+        <v>1.36496424674988</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>1.28543400764465</v>
+        <v>1.28543388843536</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G138" t="n">
-        <v>1.32304131984711</v>
+        <v>1.32304120063782</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G139" t="n">
-        <v>1.27002108097076</v>
+        <v>1.27002096176147</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>2.30900001525879</v>
       </c>
       <c r="G145" t="n">
-        <v>1.42353332042694</v>
+        <v>1.42353320121765</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G147" t="n">
-        <v>1.35325050354004</v>
+        <v>1.35325038433075</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G148" t="n">
-        <v>1.35633313655853</v>
+        <v>1.35633325576782</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>2.17300009727478</v>
       </c>
       <c r="G149" t="n">
-        <v>1.33968722820282</v>
+        <v>1.33968734741211</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.04699993133545</v>
       </c>
       <c r="G150" t="n">
-        <v>1.26200640201569</v>
+        <v>1.2620062828064</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G155" t="n">
-        <v>1.28235137462616</v>
+        <v>1.28235125541687</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.10899996757507</v>
       </c>
       <c r="G156" t="n">
-        <v>1.3002302646637</v>
+        <v>1.30023038387299</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G160" t="n">
-        <v>1.2909824848175</v>
+        <v>1.29098260402679</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G162" t="n">
-        <v>1.28235137462616</v>
+        <v>1.28235125541687</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G163" t="n">
-        <v>1.28235137462616</v>
+        <v>1.28235125541687</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G164" t="n">
-        <v>1.31625962257385</v>
+        <v>1.31625974178314</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G166" t="n">
-        <v>1.28543400764465</v>
+        <v>1.28543388843536</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>1.53900003433228</v>
       </c>
       <c r="G176" t="n">
-        <v>1.0844395160675</v>
+        <v>1.08443939685822</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>1.43900001049042</v>
       </c>
       <c r="G178" t="n">
-        <v>1.01397550106049</v>
+        <v>1.01397562026978</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G179" t="n">
-        <v>1.06400489807129</v>
+        <v>1.064004778862</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G180" t="n">
-        <v>1.08514416217804</v>
+        <v>1.08514392375946</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>1.54700005054474</v>
       </c>
       <c r="G182" t="n">
-        <v>1.09007668495178</v>
+        <v>1.09007656574249</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G186" t="n">
-        <v>1.06752812862396</v>
+        <v>1.06752800941467</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>1.5110000371933</v>
       </c>
       <c r="G189" t="n">
-        <v>1.06470954418182</v>
+        <v>1.06470942497253</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>1.63699996471405</v>
       </c>
       <c r="G191" t="n">
-        <v>1.15349411964417</v>
+        <v>1.15349400043488</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>1.15913116931915</v>
+        <v>1.15913128852844</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>1.62300002574921</v>
       </c>
       <c r="G194" t="n">
-        <v>1.14362919330597</v>
+        <v>1.14362907409668</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>1.68900001049042</v>
       </c>
       <c r="G196" t="n">
-        <v>1.1901353597641</v>
+        <v>1.19013524055481</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>1.64100003242493</v>
       </c>
       <c r="G197" t="n">
-        <v>1.15631258487701</v>
+        <v>1.1563127040863</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G201" t="n">
-        <v>1.25778067111969</v>
+        <v>1.25778043270111</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>1.78199994564056</v>
       </c>
       <c r="G202" t="n">
-        <v>1.2556666135788</v>
+        <v>1.25566673278809</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>1.74699997901917</v>
       </c>
       <c r="G204" t="n">
-        <v>1.23100423812866</v>
+        <v>1.23100435733795</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>1.83899998664856</v>
       </c>
       <c r="G207" t="n">
-        <v>1.2958310842514</v>
+        <v>1.29583096504211</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>1.81099998950958</v>
       </c>
       <c r="G214" t="n">
-        <v>1.27610111236572</v>
+        <v>1.27610123157501</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G216" t="n">
-        <v>1.28596615791321</v>
+        <v>1.2859662771225</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>2.04699993133545</v>
       </c>
       <c r="G219" t="n">
-        <v>1.44239604473114</v>
+        <v>1.44239592552185</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G221" t="n">
-        <v>1.41632437705994</v>
+        <v>1.41632425785065</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G223" t="n">
-        <v>1.42618918418884</v>
+        <v>1.42618930339813</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>1.98300004005432</v>
       </c>
       <c r="G225" t="n">
-        <v>1.39729917049408</v>
+        <v>1.39729928970337</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G231" t="n">
-        <v>1.31908428668976</v>
+        <v>1.31908416748047</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>1.75899994373322</v>
       </c>
       <c r="G234" t="n">
-        <v>1.23945999145508</v>
+        <v>1.23945987224579</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G235" t="n">
-        <v>1.25778067111969</v>
+        <v>1.25778043270111</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>1.76400005817413</v>
       </c>
       <c r="G236" t="n">
-        <v>1.24298334121704</v>
+        <v>1.24298322200775</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G238" t="n">
-        <v>1.28455698490143</v>
+        <v>1.28455686569214</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G240" t="n">
-        <v>1.27891993522644</v>
+        <v>1.27891981601715</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G244" t="n">
-        <v>1.29653573036194</v>
+        <v>1.29653584957123</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G250" t="n">
-        <v>1.36981821060181</v>
+        <v>1.3698183298111</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G251" t="n">
-        <v>1.38602483272552</v>
+        <v>1.38602495193481</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G252" t="n">
-        <v>1.35713481903076</v>
+        <v>1.35713469982147</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G253" t="n">
-        <v>1.32824456691742</v>
+        <v>1.32824444770813</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G255" t="n">
-        <v>1.4198477268219</v>
+        <v>1.41984760761261</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>1.98699998855591</v>
       </c>
       <c r="G256" t="n">
-        <v>1.40011763572693</v>
+        <v>1.40011775493622</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G258" t="n">
-        <v>1.39236664772034</v>
+        <v>1.39236652851105</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>1.96099996566772</v>
       </c>
       <c r="G260" t="n">
-        <v>1.38179707527161</v>
+        <v>1.38179695606232</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.00600004196167</v>
       </c>
       <c r="G262" t="n">
-        <v>1.41350591182709</v>
+        <v>1.4135057926178</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>1.97200000286102</v>
       </c>
       <c r="G263" t="n">
-        <v>1.3895480632782</v>
+        <v>1.38954818248749</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.05699992179871</v>
       </c>
       <c r="G266" t="n">
-        <v>1.44944226741791</v>
+        <v>1.4494423866272</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>2.20600008964539</v>
       </c>
       <c r="G269" t="n">
-        <v>1.55443370342255</v>
+        <v>1.55443358421326</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G270" t="n">
-        <v>1.55161488056183</v>
+        <v>1.55161511898041</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.18300008773804</v>
       </c>
       <c r="G271" t="n">
-        <v>1.53822684288025</v>
+        <v>1.53822708129883</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G272" t="n">
-        <v>1.5332944393158</v>
+        <v>1.53329455852509</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>2.125</v>
       </c>
       <c r="G273" t="n">
-        <v>1.49735796451569</v>
+        <v>1.4973578453064</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.10199999809265</v>
       </c>
       <c r="G275" t="n">
-        <v>1.48115110397339</v>
+        <v>1.48115122318268</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.03699994087219</v>
       </c>
       <c r="G281" t="n">
-        <v>1.43534958362579</v>
+        <v>1.43534970283508</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G285" t="n">
-        <v>1.46564912796021</v>
+        <v>1.46564900875092</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G288" t="n">
-        <v>1.43182647228241</v>
+        <v>1.4318265914917</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G293" t="n">
-        <v>1.49101603031158</v>
+        <v>1.49101614952087</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G295" t="n">
-        <v>1.51074600219727</v>
+        <v>1.51074612140656</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>2.125</v>
       </c>
       <c r="G296" t="n">
-        <v>1.49735796451569</v>
+        <v>1.4973578453064</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G298" t="n">
-        <v>1.4755140542984</v>
+        <v>1.47551417350769</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.11299991607666</v>
       </c>
       <c r="G299" t="n">
-        <v>1.48890197277069</v>
+        <v>1.48890209197998</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>2.12899994850159</v>
       </c>
       <c r="G301" t="n">
-        <v>1.50017631053925</v>
+        <v>1.50017642974854</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G302" t="n">
-        <v>1.52202033996582</v>
+        <v>1.52202022075653</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G303" t="n">
-        <v>1.47974169254303</v>
+        <v>1.47974193096161</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>2.12100005149841</v>
       </c>
       <c r="G306" t="n">
-        <v>1.49453926086426</v>
+        <v>1.49453938007355</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G308" t="n">
-        <v>1.49383449554443</v>
+        <v>1.49383461475372</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.18300008773804</v>
       </c>
       <c r="G311" t="n">
-        <v>1.53822684288025</v>
+        <v>1.53822708129883</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G313" t="n">
-        <v>1.61855566501617</v>
+        <v>1.61855578422546</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G315" t="n">
-        <v>1.61855566501617</v>
+        <v>1.61855578422546</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.29299998283386</v>
       </c>
       <c r="G319" t="n">
-        <v>1.61573731899261</v>
+        <v>1.61573719978333</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G320" t="n">
-        <v>1.62489748001099</v>
+        <v>1.62489759922028</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G321" t="n">
-        <v>1.63758099079132</v>
+        <v>1.63758087158203</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.27699995040894</v>
       </c>
       <c r="G322" t="n">
-        <v>1.60446298122406</v>
+        <v>1.60446286201477</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G323" t="n">
-        <v>1.60234904289246</v>
+        <v>1.60234892368317</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.2590000629425</v>
       </c>
       <c r="G324" t="n">
-        <v>1.59177947044373</v>
+        <v>1.59177958965302</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G326" t="n">
-        <v>1.51074600219727</v>
+        <v>1.51074612140656</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.12899994850159</v>
       </c>
       <c r="G329" t="n">
-        <v>1.50017631053925</v>
+        <v>1.50017642974854</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.22099995613098</v>
       </c>
       <c r="G332" t="n">
-        <v>1.5650030374527</v>
+        <v>1.56500315666199</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G333" t="n">
-        <v>1.54456853866577</v>
+        <v>1.54456865787506</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G335" t="n">
-        <v>1.5769819021225</v>
+        <v>1.57698202133179</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G336" t="n">
-        <v>1.61855566501617</v>
+        <v>1.61855578422546</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.28299999237061</v>
       </c>
       <c r="G337" t="n">
-        <v>1.60869073867798</v>
+        <v>1.60869085788727</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.43099999427795</v>
       </c>
       <c r="G339" t="n">
-        <v>1.71297752857208</v>
+        <v>1.71297740936279</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>1.64533197879791</v>
+        <v>1.6453320980072</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.33699989318848</v>
       </c>
       <c r="G345" t="n">
-        <v>1.64674127101898</v>
+        <v>1.64674139022827</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>2.33699989318848</v>
       </c>
       <c r="G346" t="n">
-        <v>1.64674127101898</v>
+        <v>1.64674139022827</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G347" t="n">
-        <v>1.62912547588348</v>
+        <v>1.62912535667419</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G348" t="n">
-        <v>1.5614800453186</v>
+        <v>1.56147992610931</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G349" t="n">
-        <v>1.5572521686554</v>
+        <v>1.55725228786469</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G350" t="n">
-        <v>1.55161488056183</v>
+        <v>1.55161511898041</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.19400000572205</v>
       </c>
       <c r="G351" t="n">
-        <v>1.54597795009613</v>
+        <v>1.54597806930542</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>2.27099990844727</v>
       </c>
       <c r="G353" t="n">
-        <v>1.60023510456085</v>
+        <v>1.60023522377014</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2.26900005340576</v>
       </c>
       <c r="G354" t="n">
-        <v>1.59882581233978</v>
+        <v>1.59882593154907</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>2.36400008201599</v>
       </c>
       <c r="G355" t="n">
-        <v>1.66576671600342</v>
+        <v>1.66576659679413</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>2.83750009536743</v>
       </c>
       <c r="G357" t="n">
-        <v>1.99941325187683</v>
+        <v>1.99941301345825</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G359" t="n">
-        <v>1.86729323863983</v>
+        <v>1.86729347705841</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2.69749999046326</v>
       </c>
       <c r="G360" t="n">
-        <v>1.90076351165771</v>
+        <v>1.90076375007629</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>2.65750002861023</v>
       </c>
       <c r="G361" t="n">
-        <v>1.8725780248642</v>
+        <v>1.87257826328278</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G362" t="n">
-        <v>1.81444561481476</v>
+        <v>1.81444549560547</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G365" t="n">
-        <v>1.79330635070801</v>
+        <v>1.79330623149872</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G368" t="n">
-        <v>1.78626000881195</v>
+        <v>1.78625988960266</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.5550000667572</v>
       </c>
       <c r="G370" t="n">
-        <v>1.80035269260406</v>
+        <v>1.80035281181335</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G371" t="n">
-        <v>1.83206129074097</v>
+        <v>1.83206140995026</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G372" t="n">
-        <v>1.87786281108856</v>
+        <v>1.87786293029785</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G373" t="n">
-        <v>1.88490927219391</v>
+        <v>1.88490915298462</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G374" t="n">
-        <v>1.83910751342773</v>
+        <v>1.8391078710556</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G375" t="n">
-        <v>1.83910751342773</v>
+        <v>1.8391078710556</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G376" t="n">
-        <v>1.86377000808716</v>
+        <v>1.86377024650574</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G377" t="n">
-        <v>1.86377000808716</v>
+        <v>1.86377024650574</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2.6324999332428</v>
       </c>
       <c r="G378" t="n">
-        <v>1.85496211051941</v>
+        <v>1.85496199131012</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>2.64249992370605</v>
       </c>
       <c r="G379" t="n">
-        <v>1.86200833320618</v>
+        <v>1.86200857162476</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>1.86377000808716</v>
+        <v>1.86377024650574</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>2.59750008583069</v>
       </c>
       <c r="G381" t="n">
-        <v>1.83029985427856</v>
+        <v>1.83029997348785</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>2.6324999332428</v>
       </c>
       <c r="G382" t="n">
-        <v>1.85496211051941</v>
+        <v>1.85496199131012</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>2.61249995231628</v>
       </c>
       <c r="G383" t="n">
-        <v>1.84086918830872</v>
+        <v>1.84086942672729</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.55749988555908</v>
       </c>
       <c r="G384" t="n">
-        <v>1.80211412906647</v>
+        <v>1.80211424827576</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.55250000953674</v>
       </c>
       <c r="G385" t="n">
-        <v>1.79859101772308</v>
+        <v>1.79859113693237</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G387" t="n">
-        <v>1.8060120344162</v>
+        <v>1.80601191520691</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>2.27699995040894</v>
       </c>
       <c r="G388" t="n">
-        <v>1.7786717414856</v>
+        <v>1.77867162227631</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G392" t="n">
-        <v>1.84741270542145</v>
+        <v>1.84741282463074</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G393" t="n">
-        <v>1.86069226264954</v>
+        <v>1.86069202423096</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G395" t="n">
-        <v>1.84506928920746</v>
+        <v>1.84506916999817</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G397" t="n">
-        <v>1.79429459571838</v>
+        <v>1.79429471492767</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G402" t="n">
-        <v>1.85444319248199</v>
+        <v>1.85444307327271</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.34299993515015</v>
       </c>
       <c r="G404" t="n">
-        <v>1.83022749423981</v>
+        <v>1.83022737503052</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G406" t="n">
-        <v>1.82944631576538</v>
+        <v>1.82944643497467</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.33899998664856</v>
       </c>
       <c r="G407" t="n">
-        <v>1.82710289955139</v>
+        <v>1.82710301876068</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G411" t="n">
-        <v>1.8060120344162</v>
+        <v>1.80601191520691</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>2.27699995040894</v>
       </c>
       <c r="G416" t="n">
-        <v>1.7786717414856</v>
+        <v>1.77867162227631</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G417" t="n">
-        <v>1.77945303916931</v>
+        <v>1.7794531583786</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>2.23699998855591</v>
       </c>
       <c r="G419" t="n">
-        <v>1.74742591381073</v>
+        <v>1.74742603302002</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2.11700010299683</v>
       </c>
       <c r="G426" t="n">
-        <v>1.65368843078613</v>
+        <v>1.65368831157684</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.11299991607666</v>
       </c>
       <c r="G427" t="n">
-        <v>1.65056347846985</v>
+        <v>1.65056359767914</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>1.97699999809265</v>
       </c>
       <c r="G433" t="n">
-        <v>1.54432773590088</v>
+        <v>1.54432761669159</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G436" t="n">
-        <v>1.45762038230896</v>
+        <v>1.45762050151825</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G437" t="n">
-        <v>1.44121623039246</v>
+        <v>1.44121634960175</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G441" t="n">
-        <v>1.48417937755585</v>
+        <v>1.48417925834656</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G442" t="n">
-        <v>1.48417937755585</v>
+        <v>1.48417925834656</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G445" t="n">
-        <v>1.48886632919312</v>
+        <v>1.48886620998383</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>1.85300004482269</v>
       </c>
       <c r="G447" t="n">
-        <v>1.44746541976929</v>
+        <v>1.44746553897858</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G451" t="n">
-        <v>1.4099702835083</v>
+        <v>1.40997040271759</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>1.69219994544983</v>
       </c>
       <c r="G455" t="n">
-        <v>1.32185685634613</v>
+        <v>1.32185697555542</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>1.69159996509552</v>
       </c>
       <c r="G457" t="n">
-        <v>1.32138824462891</v>
+        <v>1.3213883638382</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>1.94939994812012</v>
       </c>
       <c r="G463" t="n">
-        <v>1.52276802062988</v>
+        <v>1.52276790142059</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>1.93680000305176</v>
       </c>
       <c r="G464" t="n">
-        <v>1.51292550563812</v>
+        <v>1.51292562484741</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>1.92239999771118</v>
       </c>
       <c r="G465" t="n">
-        <v>1.5016770362854</v>
+        <v>1.50167715549469</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>2.02049994468689</v>
       </c>
       <c r="G467" t="n">
-        <v>1.5783075094223</v>
+        <v>1.57830739021301</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>1.97259998321533</v>
       </c>
       <c r="G468" t="n">
-        <v>1.54089057445526</v>
+        <v>1.54089069366455</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>2.15249991416931</v>
       </c>
       <c r="G473" t="n">
-        <v>1.68141901493073</v>
+        <v>1.68141889572144</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>2.29450011253357</v>
       </c>
       <c r="G474" t="n">
-        <v>1.79234182834625</v>
+        <v>1.79234206676483</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>2.25950002670288</v>
       </c>
       <c r="G475" t="n">
-        <v>1.76500165462494</v>
+        <v>1.76500177383423</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G477" t="n">
-        <v>1.75601851940155</v>
+        <v>1.75601840019226</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>2.22699999809265</v>
       </c>
       <c r="G478" t="n">
-        <v>1.73961448669434</v>
+        <v>1.73961436748505</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G480" t="n">
-        <v>1.74664497375488</v>
+        <v>1.74664485454559</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>2.31900000572205</v>
       </c>
       <c r="G482" t="n">
-        <v>1.8114800453186</v>
+        <v>1.81147992610931</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>2.33599996566772</v>
       </c>
       <c r="G484" t="n">
-        <v>1.8247594833374</v>
+        <v>1.82475936412811</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G485" t="n">
-        <v>1.86850357055664</v>
+        <v>1.86850380897522</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>2.33150005340576</v>
       </c>
       <c r="G488" t="n">
-        <v>1.82124435901642</v>
+        <v>1.82124447822571</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.34949994087219</v>
       </c>
       <c r="G489" t="n">
-        <v>1.83530509471893</v>
+        <v>1.83530497550964</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>2.39750003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>1.87279999256134</v>
+        <v>1.87280023097992</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.3989999294281</v>
       </c>
       <c r="G492" t="n">
-        <v>1.87397146224976</v>
+        <v>1.87397170066833</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G493" t="n">
-        <v>1.8622545003891</v>
+        <v>1.86225473880768</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G497" t="n">
-        <v>1.84194469451904</v>
+        <v>1.84194481372833</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.35899996757507</v>
       </c>
       <c r="G500" t="n">
-        <v>1.84272587299347</v>
+        <v>1.84272575378418</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G501" t="n">
-        <v>1.86069226264954</v>
+        <v>1.86069202423096</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G504" t="n">
-        <v>1.90443658828735</v>
+        <v>1.90443634986877</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.38750004768372</v>
       </c>
       <c r="G508" t="n">
-        <v>1.86498868465424</v>
+        <v>1.86498844623566</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>2.33949995040894</v>
       </c>
       <c r="G510" t="n">
-        <v>1.82749330997467</v>
+        <v>1.82749342918396</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G514" t="n">
-        <v>1.84819364547729</v>
+        <v>1.84819388389587</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>2.38700008392334</v>
       </c>
       <c r="G516" t="n">
-        <v>1.86459791660309</v>
+        <v>1.86459815502167</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G519" t="n">
-        <v>1.84506928920746</v>
+        <v>1.84506916999817</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G523" t="n">
-        <v>1.74352025985718</v>
+        <v>1.74352014064789</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>2.18650007247925</v>
       </c>
       <c r="G525" t="n">
-        <v>1.70797801017761</v>
+        <v>1.7079781293869</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>2.1324999332428</v>
       </c>
       <c r="G529" t="n">
-        <v>1.66579604148865</v>
+        <v>1.66579592227936</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G530" t="n">
-        <v>1.65603148937225</v>
+        <v>1.65603160858154</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G532" t="n">
-        <v>1.62478578090668</v>
+        <v>1.62478566169739</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>2.07750010490417</v>
       </c>
       <c r="G533" t="n">
-        <v>1.62283301353455</v>
+        <v>1.62283313274384</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>2.11150002479553</v>
       </c>
       <c r="G538" t="n">
-        <v>1.64939200878143</v>
+        <v>1.64939188957214</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.09249997138977</v>
       </c>
       <c r="G544" t="n">
-        <v>1.63455009460449</v>
+        <v>1.63455021381378</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.14299988746643</v>
       </c>
       <c r="G546" t="n">
-        <v>1.67399799823761</v>
+        <v>1.67399787902832</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>2.12949991226196</v>
       </c>
       <c r="G549" t="n">
-        <v>1.66345250606537</v>
+        <v>1.66345262527466</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.24300003051758</v>
       </c>
       <c r="G554" t="n">
-        <v>1.75211298465729</v>
+        <v>1.752112865448</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G555" t="n">
-        <v>1.74352025985718</v>
+        <v>1.74352014064789</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>2.24449992179871</v>
       </c>
       <c r="G556" t="n">
-        <v>1.7532844543457</v>
+        <v>1.75328457355499</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.30550003051758</v>
       </c>
       <c r="G557" t="n">
-        <v>1.80093455314636</v>
+        <v>1.80093443393707</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.42149996757507</v>
       </c>
       <c r="G559" t="n">
-        <v>1.89154756069183</v>
+        <v>1.89154732227325</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G568" t="n">
-        <v>1.99661183357239</v>
+        <v>1.99661159515381</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G569" t="n">
-        <v>1.92005920410156</v>
+        <v>1.92005944252014</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G570" t="n">
-        <v>1.9294331073761</v>
+        <v>1.92943322658539</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G575" t="n">
-        <v>2.04660534858704</v>
+        <v>2.04660511016846</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G585" t="n">
-        <v>2.1965856552124</v>
+        <v>2.19658541679382</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G586" t="n">
-        <v>2.25751495361328</v>
+        <v>2.2575147151947</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G588" t="n">
-        <v>2.31219506263733</v>
+        <v>2.31219530105591</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>3.05599999427795</v>
       </c>
       <c r="G593" t="n">
-        <v>2.38718557357788</v>
+        <v>2.3871853351593</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>3.04200005531311</v>
       </c>
       <c r="G598" t="n">
-        <v>2.37624955177307</v>
+        <v>2.37624931335449</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>3.06800007820129</v>
       </c>
       <c r="G602" t="n">
-        <v>2.39655923843384</v>
+        <v>2.39655900001526</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G603" t="n">
-        <v>2.46529984474182</v>
+        <v>2.4653000831604</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G604" t="n">
-        <v>2.46529984474182</v>
+        <v>2.4653000831604</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>3.17400002479553</v>
       </c>
       <c r="G605" t="n">
-        <v>2.47936058044434</v>
+        <v>2.47936081886292</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G609" t="n">
-        <v>2.54810190200806</v>
+        <v>2.54810166358948</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G610" t="n">
-        <v>2.46373796463013</v>
+        <v>2.46373772621155</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G612" t="n">
-        <v>2.4137442111969</v>
+        <v>2.41374444961548</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>3.09599995613098</v>
       </c>
       <c r="G614" t="n">
-        <v>2.41843128204346</v>
+        <v>2.41843104362488</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G615" t="n">
-        <v>2.421555519104</v>
+        <v>2.42155575752258</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>3.24200010299683</v>
       </c>
       <c r="G628" t="n">
-        <v>2.53247857093811</v>
+        <v>2.53247880935669</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>3.26399993896484</v>
       </c>
       <c r="G629" t="n">
-        <v>2.54966378211975</v>
+        <v>2.54966402053833</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G630" t="n">
-        <v>2.56216239929199</v>
+        <v>2.56216216087341</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G640" t="n">
-        <v>2.66151165962219</v>
+        <v>2.66151189804077</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G645" t="n">
-        <v>2.65814256668091</v>
+        <v>2.65814280509949</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G647" t="n">
-        <v>2.59413170814514</v>
+        <v>2.59413146972656</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>3.01399993896484</v>
       </c>
       <c r="G648" t="n">
-        <v>2.53854322433472</v>
+        <v>2.53854298591614</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G651" t="n">
-        <v>2.44926452636719</v>
+        <v>2.44926476478577</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G657" t="n">
-        <v>2.45600271224976</v>
+        <v>2.45600247383118</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G662" t="n">
-        <v>2.47116303443909</v>
+        <v>2.47116327285767</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G666" t="n">
-        <v>2.48800826072693</v>
+        <v>2.48800802230835</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>2.89800000190735</v>
       </c>
       <c r="G668" t="n">
-        <v>2.44084215164185</v>
+        <v>2.44084191322327</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G678" t="n">
-        <v>2.35661721229553</v>
+        <v>2.35661697387695</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>3.22399997711182</v>
       </c>
       <c r="G681" t="n">
-        <v>2.71541595458984</v>
+        <v>2.71541571617126</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G682" t="n">
-        <v>2.57223320007324</v>
+        <v>2.57223296165466</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G688" t="n">
-        <v>2.61097645759583</v>
+        <v>2.6109766960144</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G689" t="n">
-        <v>2.5857093334198</v>
+        <v>2.58570909500122</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G690" t="n">
-        <v>2.57560205459595</v>
+        <v>2.57560229301453</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G691" t="n">
-        <v>2.49306154251099</v>
+        <v>2.49306178092957</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>3.03200006484985</v>
       </c>
       <c r="G695" t="n">
-        <v>2.55370354652405</v>
+        <v>2.55370378494263</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>3.06800007820129</v>
       </c>
       <c r="G699" t="n">
-        <v>2.58402490615845</v>
+        <v>2.58402466773987</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G707" t="n">
-        <v>2.5857093334198</v>
+        <v>2.58570909500122</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G710" t="n">
-        <v>2.50990676879883</v>
+        <v>2.50990653038025</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>3.01399993896484</v>
       </c>
       <c r="G711" t="n">
-        <v>2.53854322433472</v>
+        <v>2.53854298591614</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G712" t="n">
-        <v>2.50990676879883</v>
+        <v>2.50990653038025</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>2.91400003433228</v>
       </c>
       <c r="G714" t="n">
-        <v>2.4543182849884</v>
+        <v>2.45431804656982</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G717" t="n">
-        <v>2.45600271224976</v>
+        <v>2.45600247383118</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G726" t="n">
-        <v>2.44926452636719</v>
+        <v>2.44926476478577</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>2.79200005531311</v>
       </c>
       <c r="G734" t="n">
-        <v>2.35156345367432</v>
+        <v>2.3515636920929</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G735" t="n">
-        <v>2.41388988494873</v>
+        <v>2.41389012336731</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>3.04200005531311</v>
       </c>
       <c r="G742" t="n">
-        <v>2.56212639808655</v>
+        <v>2.56212615966797</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G746" t="n">
-        <v>2.48295450210571</v>
+        <v>2.48295474052429</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>2.49306154251099</v>
+        <v>2.49306178092957</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>3.01399993896484</v>
       </c>
       <c r="G756" t="n">
-        <v>2.53854322433472</v>
+        <v>2.53854298591614</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G759" t="n">
-        <v>2.48295450210571</v>
+        <v>2.48295474052429</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>3.03399991989136</v>
       </c>
       <c r="G762" t="n">
-        <v>2.5553879737854</v>
+        <v>2.55538821220398</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>3.09599995613098</v>
       </c>
       <c r="G766" t="n">
-        <v>2.6076078414917</v>
+        <v>2.60760760307312</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G767" t="n">
-        <v>2.5772864818573</v>
+        <v>2.57728672027588</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G769" t="n">
-        <v>2.57560205459595</v>
+        <v>2.57560229301453</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G770" t="n">
-        <v>2.57223320007324</v>
+        <v>2.57223296165466</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G771" t="n">
-        <v>2.58907794952393</v>
+        <v>2.5890781879425</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G774" t="n">
-        <v>2.67835688591003</v>
+        <v>2.67835664749146</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>3.14199995994568</v>
       </c>
       <c r="G775" t="n">
-        <v>2.64635109901428</v>
+        <v>2.64635133743286</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G778" t="n">
-        <v>2.71710014343262</v>
+        <v>2.7171003818512</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>3.20600008964539</v>
       </c>
       <c r="G779" t="n">
-        <v>2.70025539398193</v>
+        <v>2.70025515556335</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>3.20600008964539</v>
       </c>
       <c r="G783" t="n">
-        <v>2.70025539398193</v>
+        <v>2.70025515556335</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G784" t="n">
-        <v>2.71710014343262</v>
+        <v>2.7171003818512</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G789" t="n">
-        <v>2.84680700302124</v>
+        <v>2.84680676460266</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>3.14199995994568</v>
       </c>
       <c r="G794" t="n">
-        <v>2.64635109901428</v>
+        <v>2.64635133743286</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>3.36800003051758</v>
       </c>
       <c r="G802" t="n">
-        <v>2.83669972419739</v>
+        <v>2.83669996261597</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G805" t="n">
-        <v>2.93776988983154</v>
+        <v>2.93776965141296</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>3.38800001144409</v>
       </c>
       <c r="G814" t="n">
-        <v>2.85354495048523</v>
+        <v>2.85354471206665</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G818" t="n">
-        <v>2.45600271224976</v>
+        <v>2.45600247383118</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>3.00600004196167</v>
       </c>
       <c r="G819" t="n">
-        <v>2.53180527687073</v>
+        <v>2.53180503845215</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G833" t="n">
-        <v>2.69183301925659</v>
+        <v>2.69183278083801</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G834" t="n">
-        <v>2.67835688591003</v>
+        <v>2.67835664749146</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G835" t="n">
-        <v>2.65814256668091</v>
+        <v>2.65814280509949</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G837" t="n">
-        <v>2.67835688591003</v>
+        <v>2.67835664749146</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>3.25</v>
       </c>
       <c r="G839" t="n">
-        <v>2.73731446266174</v>
+        <v>2.73731422424316</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>3.25</v>
       </c>
       <c r="G843" t="n">
-        <v>2.73731446266174</v>
+        <v>2.73731422424316</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>3.33599996566772</v>
       </c>
       <c r="G848" t="n">
-        <v>2.80974793434143</v>
+        <v>2.80974769592285</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G858" t="n">
-        <v>2.7979564666748</v>
+        <v>2.79795622825623</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G861" t="n">
-        <v>2.78784942626953</v>
+        <v>2.78784918785095</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G866" t="n">
-        <v>2.68677926063538</v>
+        <v>2.68677949905396</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G868" t="n">
-        <v>2.65814256668091</v>
+        <v>2.65814280509949</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -31234,6 +31234,32 @@
         <v>2.31800007820129</v>
       </c>
       <c r="H1187" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1188" t="n">
+        <v>3425491</v>
+      </c>
+      <c r="C1188" t="n">
+        <v>2.33599996566772</v>
+      </c>
+      <c r="D1188" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="E1188" t="n">
+        <v>2.32200002670288</v>
+      </c>
+      <c r="F1188" t="n">
+        <v>2.30999994277954</v>
+      </c>
+      <c r="G1188" t="n">
+        <v>2.30999994277954</v>
+      </c>
+      <c r="H1188" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/MFEA.MI.xlsx
+++ b/data/MFEA.MI.xlsx
@@ -447,7 +447,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G3" t="n">
-        <v>2.25027990341187</v>
+        <v>2.25028014183044</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>3.71250009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>2.28881239891052</v>
+        <v>2.28881216049194</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G6" t="n">
-        <v>2.28727102279663</v>
+        <v>2.28727078437805</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G9" t="n">
-        <v>2.34892249107361</v>
+        <v>2.34892225265503</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>2.33659195899963</v>
+        <v>2.33659219741821</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G11" t="n">
-        <v>2.31501412391663</v>
+        <v>2.31501388549805</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G12" t="n">
-        <v>2.29035353660583</v>
+        <v>2.29035329818726</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G20" t="n">
-        <v>2.61710643768311</v>
+        <v>2.61710619926453</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G22" t="n">
-        <v>2.5955286026001</v>
+        <v>2.59552836418152</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>3.99499988555908</v>
       </c>
       <c r="G25" t="n">
-        <v>2.46297764778137</v>
+        <v>2.46297740936279</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>3.98250007629395</v>
       </c>
       <c r="G27" t="n">
-        <v>2.45527148246765</v>
+        <v>2.45527124404907</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G29" t="n">
-        <v>2.47530770301819</v>
+        <v>2.47530794143677</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G30" t="n">
-        <v>2.41365623474121</v>
+        <v>2.41365647315979</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G31" t="n">
-        <v>2.40440893173218</v>
+        <v>2.4044086933136</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>3.92750000953674</v>
       </c>
       <c r="G36" t="n">
-        <v>2.42136287689209</v>
+        <v>2.42136311531067</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.14249992370605</v>
       </c>
       <c r="G37" t="n">
-        <v>2.55391359329224</v>
+        <v>2.55391383171082</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.5</v>
       </c>
       <c r="G41" t="n">
-        <v>2.15780258178711</v>
+        <v>2.15780282020569</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G46" t="n">
-        <v>2.02525186538696</v>
+        <v>2.02525210380554</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G48" t="n">
-        <v>2.03141713142395</v>
+        <v>2.03141736984253</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G49" t="n">
-        <v>2.07149052619934</v>
+        <v>2.07149028778076</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G50" t="n">
-        <v>2.02525186538696</v>
+        <v>2.02525210380554</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.17750000953674</v>
       </c>
       <c r="G51" t="n">
-        <v>1.95897674560547</v>
+        <v>1.95897650718689</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G52" t="n">
-        <v>1.99442625045776</v>
+        <v>1.99442648887634</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G53" t="n">
-        <v>1.97593069076538</v>
+        <v>1.97593080997467</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.1175000667572</v>
       </c>
       <c r="G54" t="n">
-        <v>1.92198586463928</v>
+        <v>1.9219856262207</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3</v>
       </c>
       <c r="G57" t="n">
-        <v>1.84954524040222</v>
+        <v>1.84954512119293</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G59" t="n">
-        <v>1.79405903816223</v>
+        <v>1.79405891895294</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G60" t="n">
-        <v>1.79714131355286</v>
+        <v>1.79714155197144</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G61" t="n">
-        <v>1.80638921260834</v>
+        <v>1.80638909339905</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G63" t="n">
-        <v>1.81255435943604</v>
+        <v>1.81255447864532</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G64" t="n">
-        <v>1.87728846073151</v>
+        <v>1.8772885799408</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G67" t="n">
-        <v>1.69233405590057</v>
+        <v>1.69233381748199</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G68" t="n">
-        <v>1.66150808334351</v>
+        <v>1.66150832176208</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G69" t="n">
-        <v>1.6522604227066</v>
+        <v>1.65226030349731</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.92750000953674</v>
       </c>
       <c r="G70" t="n">
-        <v>1.80484783649445</v>
+        <v>1.80484795570374</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.86249995231628</v>
       </c>
       <c r="G71" t="n">
-        <v>1.76477420330048</v>
+        <v>1.76477432250977</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G73" t="n">
-        <v>1.74165511131287</v>
+        <v>1.74165499210358</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.75</v>
       </c>
       <c r="G74" t="n">
-        <v>1.6954163312912</v>
+        <v>1.69541645050049</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G75" t="n">
-        <v>1.66150808334351</v>
+        <v>1.66150832176208</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>1.64917767047882</v>
+        <v>1.64917778968811</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>2.68249988555908</v>
       </c>
       <c r="G80" t="n">
-        <v>1.65380156040192</v>
+        <v>1.65380167961121</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G83" t="n">
-        <v>1.60910427570343</v>
+        <v>1.60910415649414</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G84" t="n">
-        <v>1.56594824790955</v>
+        <v>1.56594812870026</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>2.58750009536743</v>
       </c>
       <c r="G85" t="n">
-        <v>1.59523260593414</v>
+        <v>1.59523272514343</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>2.64750003814697</v>
       </c>
       <c r="G88" t="n">
-        <v>1.63222372531891</v>
+        <v>1.6322238445282</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G94" t="n">
-        <v>1.63993000984192</v>
+        <v>1.6399302482605</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.6324999332428</v>
       </c>
       <c r="G96" t="n">
-        <v>1.62297570705414</v>
+        <v>1.62297582626343</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G97" t="n">
-        <v>1.57827854156494</v>
+        <v>1.57827842235565</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.45300006866455</v>
       </c>
       <c r="G100" t="n">
-        <v>1.51231133937836</v>
+        <v>1.51231145858765</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G104" t="n">
-        <v>1.37482857704163</v>
+        <v>1.37482845783234</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.25699996948242</v>
       </c>
       <c r="G105" t="n">
-        <v>1.39147460460663</v>
+        <v>1.39147448539734</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.11899995803833</v>
       </c>
       <c r="G108" t="n">
-        <v>1.30639541149139</v>
+        <v>1.30639553070068</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G109" t="n">
-        <v>1.31934237480164</v>
+        <v>1.31934225559235</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.24900007247925</v>
       </c>
       <c r="G112" t="n">
-        <v>1.38654243946075</v>
+        <v>1.38654255867004</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.22300004959106</v>
       </c>
       <c r="G113" t="n">
-        <v>1.3705130815506</v>
+        <v>1.37051296234131</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G115" t="n">
-        <v>1.36558091640472</v>
+        <v>1.36558079719543</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G119" t="n">
-        <v>1.38099360466003</v>
+        <v>1.38099372386932</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G120" t="n">
-        <v>1.37236261367798</v>
+        <v>1.37236249446869</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G127" t="n">
-        <v>1.33043944835663</v>
+        <v>1.33043956756592</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>2.21399998664856</v>
       </c>
       <c r="G131" t="n">
-        <v>1.36496424674988</v>
+        <v>1.36496436595917</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G146" t="n">
-        <v>1.40257179737091</v>
+        <v>1.4025719165802</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>2.17300009727478</v>
       </c>
       <c r="G149" t="n">
-        <v>1.33968734741211</v>
+        <v>1.33968722820282</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.10899996757507</v>
       </c>
       <c r="G156" t="n">
-        <v>1.30023038387299</v>
+        <v>1.3002302646637</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G157" t="n">
-        <v>1.30392932891846</v>
+        <v>1.30392944812775</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G164" t="n">
-        <v>1.31625974178314</v>
+        <v>1.31625962257385</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.06900000572205</v>
       </c>
       <c r="G167" t="n">
-        <v>1.27556967735291</v>
+        <v>1.27556979656219</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G168" t="n">
-        <v>1.24782645702362</v>
+        <v>1.24782657623291</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>1.65199995040894</v>
       </c>
       <c r="G173" t="n">
-        <v>1.16406357288361</v>
+        <v>1.16406345367432</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>1.43900001049042</v>
       </c>
       <c r="G178" t="n">
-        <v>1.01397562026978</v>
+        <v>1.01397550106049</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G179" t="n">
-        <v>1.064004778862</v>
+        <v>1.06400489807129</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G180" t="n">
-        <v>1.08514392375946</v>
+        <v>1.08514404296875</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>1.54200005531311</v>
       </c>
       <c r="G188" t="n">
-        <v>1.08655345439911</v>
+        <v>1.08655333518982</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G190" t="n">
-        <v>1.11473894119263</v>
+        <v>1.11473882198334</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>1.63699996471405</v>
       </c>
       <c r="G191" t="n">
-        <v>1.15349400043488</v>
+        <v>1.15349411964417</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>1.15913128852844</v>
+        <v>1.15913116931915</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>1.62300002574921</v>
       </c>
       <c r="G194" t="n">
-        <v>1.14362907409668</v>
+        <v>1.14362919330597</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>1.64100003242493</v>
       </c>
       <c r="G197" t="n">
-        <v>1.1563127040863</v>
+        <v>1.15631258487701</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>1.73800003528595</v>
       </c>
       <c r="G199" t="n">
-        <v>1.22466266155243</v>
+        <v>1.22466254234314</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>1.77300000190735</v>
       </c>
       <c r="G200" t="n">
-        <v>1.24932491779327</v>
+        <v>1.24932479858398</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G201" t="n">
-        <v>1.25778043270111</v>
+        <v>1.2577805519104</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>1.84399998188019</v>
       </c>
       <c r="G206" t="n">
-        <v>1.29935431480408</v>
+        <v>1.29935419559479</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>1.83899998664856</v>
       </c>
       <c r="G207" t="n">
-        <v>1.29583096504211</v>
+        <v>1.2958310842514</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>1.86800003051758</v>
       </c>
       <c r="G208" t="n">
-        <v>1.31626570224762</v>
+        <v>1.31626558303833</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G212" t="n">
-        <v>1.29371726512909</v>
+        <v>1.2937171459198</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G215" t="n">
-        <v>1.29301261901855</v>
+        <v>1.29301249980927</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G221" t="n">
-        <v>1.41632425785065</v>
+        <v>1.41632437705994</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>1.98300004005432</v>
       </c>
       <c r="G225" t="n">
-        <v>1.39729928970337</v>
+        <v>1.39729917049408</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G227" t="n">
-        <v>1.33035838603973</v>
+        <v>1.33035850524902</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>1.75899994373322</v>
       </c>
       <c r="G234" t="n">
-        <v>1.23945987224579</v>
+        <v>1.23945999145508</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G235" t="n">
-        <v>1.25778043270111</v>
+        <v>1.2577805519104</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>1.76400005817413</v>
       </c>
       <c r="G236" t="n">
-        <v>1.24298322200775</v>
+        <v>1.24298334121704</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>1.807000041008</v>
       </c>
       <c r="G243" t="n">
-        <v>1.27328276634216</v>
+        <v>1.27328288555145</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G244" t="n">
-        <v>1.29653584957123</v>
+        <v>1.29653573036194</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G253" t="n">
-        <v>1.32824444770813</v>
+        <v>1.32824456691742</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G255" t="n">
-        <v>1.41984760761261</v>
+        <v>1.4198477268219</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>1.96099996566772</v>
       </c>
       <c r="G260" t="n">
-        <v>1.38179695606232</v>
+        <v>1.38179707527161</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>1.942999958992</v>
       </c>
       <c r="G261" t="n">
-        <v>1.36911356449127</v>
+        <v>1.36911344528198</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.00600004196167</v>
       </c>
       <c r="G262" t="n">
-        <v>1.4135057926178</v>
+        <v>1.41350591182709</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>1.97200000286102</v>
       </c>
       <c r="G263" t="n">
-        <v>1.38954818248749</v>
+        <v>1.3895480632782</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G267" t="n">
-        <v>1.52765738964081</v>
+        <v>1.52765727043152</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>2.20600008964539</v>
       </c>
       <c r="G269" t="n">
-        <v>1.55443358421326</v>
+        <v>1.55443370342255</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G270" t="n">
-        <v>1.55161511898041</v>
+        <v>1.55161499977112</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.18300008773804</v>
       </c>
       <c r="G271" t="n">
-        <v>1.53822708129883</v>
+        <v>1.53822696208954</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.10199999809265</v>
       </c>
       <c r="G275" t="n">
-        <v>1.48115122318268</v>
+        <v>1.48115110397339</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G276" t="n">
-        <v>1.48819756507874</v>
+        <v>1.48819768428802</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>2.06699991226196</v>
       </c>
       <c r="G278" t="n">
-        <v>1.45648872852325</v>
+        <v>1.45648860931396</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G280" t="n">
-        <v>1.44450986385345</v>
+        <v>1.44450998306274</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G282" t="n">
-        <v>1.44450986385345</v>
+        <v>1.44450998306274</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G285" t="n">
-        <v>1.46564900875092</v>
+        <v>1.46564912796021</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G288" t="n">
-        <v>1.4318265914917</v>
+        <v>1.43182647228241</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>2.12299990653992</v>
       </c>
       <c r="G297" t="n">
-        <v>1.49594855308533</v>
+        <v>1.49594867229462</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.11299991607666</v>
       </c>
       <c r="G299" t="n">
-        <v>1.48890209197998</v>
+        <v>1.48890197277069</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>2.12899994850159</v>
       </c>
       <c r="G301" t="n">
-        <v>1.50017642974854</v>
+        <v>1.50017631053925</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G303" t="n">
-        <v>1.47974193096161</v>
+        <v>1.47974181175232</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>2.06699991226196</v>
       </c>
       <c r="G304" t="n">
-        <v>1.45648872852325</v>
+        <v>1.45648860931396</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>2.12100005149841</v>
       </c>
       <c r="G306" t="n">
-        <v>1.49453938007355</v>
+        <v>1.49453926086426</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>2.12299990653992</v>
       </c>
       <c r="G307" t="n">
-        <v>1.49594855308533</v>
+        <v>1.49594867229462</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.18300008773804</v>
       </c>
       <c r="G311" t="n">
-        <v>1.53822708129883</v>
+        <v>1.53822696208954</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G314" t="n">
-        <v>1.59600746631622</v>
+        <v>1.59600734710693</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G318" t="n">
-        <v>1.60305368900299</v>
+        <v>1.60305380821228</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G320" t="n">
-        <v>1.62489759922028</v>
+        <v>1.62489748001099</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.27699995040894</v>
       </c>
       <c r="G322" t="n">
-        <v>1.60446286201477</v>
+        <v>1.60446298122406</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.2590000629425</v>
       </c>
       <c r="G324" t="n">
-        <v>1.59177958965302</v>
+        <v>1.59177947044373</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.12899994850159</v>
       </c>
       <c r="G329" t="n">
-        <v>1.50017642974854</v>
+        <v>1.50017631053925</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.22099995613098</v>
       </c>
       <c r="G332" t="n">
-        <v>1.56500315666199</v>
+        <v>1.56500327587128</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G335" t="n">
-        <v>1.57698202133179</v>
+        <v>1.5769819021225</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.28299999237061</v>
       </c>
       <c r="G337" t="n">
-        <v>1.60869085788727</v>
+        <v>1.60869073867798</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G338" t="n">
-        <v>1.59671199321747</v>
+        <v>1.59671187400818</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.43099999427795</v>
       </c>
       <c r="G339" t="n">
-        <v>1.71297740936279</v>
+        <v>1.71297752857208</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.33699989318848</v>
       </c>
       <c r="G345" t="n">
-        <v>1.64674139022827</v>
+        <v>1.64674127101898</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>2.33699989318848</v>
       </c>
       <c r="G346" t="n">
-        <v>1.64674139022827</v>
+        <v>1.64674127101898</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G349" t="n">
-        <v>1.55725228786469</v>
+        <v>1.5572521686554</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G350" t="n">
-        <v>1.55161511898041</v>
+        <v>1.55161499977112</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G359" t="n">
-        <v>1.86729347705841</v>
+        <v>1.86729335784912</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>2.54250001907349</v>
       </c>
       <c r="G363" t="n">
-        <v>1.79154467582703</v>
+        <v>1.79154443740845</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G365" t="n">
-        <v>1.79330623149872</v>
+        <v>1.7933064699173</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G367" t="n">
-        <v>1.75736963748932</v>
+        <v>1.75736975669861</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G368" t="n">
-        <v>1.78625988960266</v>
+        <v>1.78625977039337</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.5550000667572</v>
       </c>
       <c r="G370" t="n">
-        <v>1.80035281181335</v>
+        <v>1.80035269260406</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G371" t="n">
-        <v>1.83206140995026</v>
+        <v>1.83206152915955</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G372" t="n">
-        <v>1.87786293029785</v>
+        <v>1.87786304950714</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G373" t="n">
-        <v>1.88490915298462</v>
+        <v>1.88490927219391</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G374" t="n">
-        <v>1.8391078710556</v>
+        <v>1.83910763263702</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G375" t="n">
-        <v>1.8391078710556</v>
+        <v>1.83910763263702</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2.6324999332428</v>
       </c>
       <c r="G378" t="n">
-        <v>1.85496199131012</v>
+        <v>1.85496211051941</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>2.6324999332428</v>
       </c>
       <c r="G382" t="n">
-        <v>1.85496199131012</v>
+        <v>1.85496211051941</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -31260,6 +31260,32 @@
         <v>2.30999994277954</v>
       </c>
       <c r="H1188" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1189" t="n">
+        <v>1704203</v>
+      </c>
+      <c r="C1189" t="n">
+        <v>2.33599996566772</v>
+      </c>
+      <c r="D1189" t="n">
+        <v>2.28999996185303</v>
+      </c>
+      <c r="E1189" t="n">
+        <v>2.29200005531311</v>
+      </c>
+      <c r="F1189" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="G1189" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="H1189" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/MFEA.MI.xlsx
+++ b/data/MFEA.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.9375</v>
       </c>
       <c r="G2" t="n">
-        <v>2.42752814292908</v>
+        <v>2.4275279045105</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G3" t="n">
-        <v>2.25028014183044</v>
+        <v>2.25027990341187</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G6" t="n">
-        <v>2.28727078437805</v>
+        <v>2.28727102279663</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.70749998092651</v>
       </c>
       <c r="G7" t="n">
-        <v>2.28572964668274</v>
+        <v>2.28572940826416</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G8" t="n">
-        <v>2.27494072914124</v>
+        <v>2.27494049072266</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G11" t="n">
-        <v>2.31501388549805</v>
+        <v>2.31501412391663</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G13" t="n">
-        <v>2.29343605041504</v>
+        <v>2.29343628883362</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G15" t="n">
-        <v>2.32734441757202</v>
+        <v>2.3273446559906</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G17" t="n">
-        <v>2.69417071342468</v>
+        <v>2.69417095184326</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G18" t="n">
-        <v>2.66951036453247</v>
+        <v>2.66951012611389</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4.28249979019165</v>
       </c>
       <c r="G19" t="n">
-        <v>2.64022564888</v>
+        <v>2.64022588729858</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G20" t="n">
-        <v>2.61710619926453</v>
+        <v>2.61710643768311</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G22" t="n">
-        <v>2.59552836418152</v>
+        <v>2.5955286026001</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G23" t="n">
-        <v>2.49688625335693</v>
+        <v>2.49688649177551</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>3.99499988555908</v>
       </c>
       <c r="G25" t="n">
-        <v>2.46297740936279</v>
+        <v>2.46297764778137</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>3.94250011444092</v>
       </c>
       <c r="G26" t="n">
-        <v>2.43061065673828</v>
+        <v>2.43061089515686</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G31" t="n">
-        <v>2.4044086933136</v>
+        <v>2.40440893173218</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G32" t="n">
-        <v>2.25336265563965</v>
+        <v>2.25336241722107</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G33" t="n">
-        <v>2.21945428848267</v>
+        <v>2.21945405006409</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G34" t="n">
-        <v>2.29343605041504</v>
+        <v>2.29343628883362</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>3.92750000953674</v>
       </c>
       <c r="G36" t="n">
-        <v>2.42136311531067</v>
+        <v>2.42136287689209</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.14249992370605</v>
       </c>
       <c r="G37" t="n">
-        <v>2.55391383171082</v>
+        <v>2.55391359329224</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.73749995231628</v>
       </c>
       <c r="G40" t="n">
-        <v>2.30422496795654</v>
+        <v>2.30422520637512</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G43" t="n">
-        <v>2.03449964523315</v>
+        <v>2.03449988365173</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.26749992370605</v>
       </c>
       <c r="G47" t="n">
-        <v>2.01446270942688</v>
+        <v>2.01446294784546</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G49" t="n">
-        <v>2.07149028778076</v>
+        <v>2.07149076461792</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.17750000953674</v>
       </c>
       <c r="G51" t="n">
-        <v>1.95897650718689</v>
+        <v>1.95897674560547</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G52" t="n">
-        <v>1.99442648887634</v>
+        <v>1.99442601203918</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G53" t="n">
-        <v>1.97593080997467</v>
+        <v>1.97593057155609</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.1175000667572</v>
       </c>
       <c r="G54" t="n">
-        <v>1.9219856262207</v>
+        <v>1.92198586463928</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G56" t="n">
-        <v>1.85571038722992</v>
+        <v>1.85571026802063</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G58" t="n">
-        <v>1.82488453388214</v>
+        <v>1.82488465309143</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G59" t="n">
-        <v>1.79405891895294</v>
+        <v>1.79405903816223</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G60" t="n">
-        <v>1.79714155197144</v>
+        <v>1.79714131355286</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G61" t="n">
-        <v>1.80638909339905</v>
+        <v>1.80638897418976</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G63" t="n">
-        <v>1.81255447864532</v>
+        <v>1.81255424022675</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G64" t="n">
-        <v>1.8772885799408</v>
+        <v>1.87728846073151</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.89249992370605</v>
       </c>
       <c r="G65" t="n">
-        <v>1.78326988220215</v>
+        <v>1.78326976299286</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G66" t="n">
-        <v>1.71391177177429</v>
+        <v>1.713911652565</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G68" t="n">
-        <v>1.66150832176208</v>
+        <v>1.66150796413422</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G69" t="n">
-        <v>1.65226030349731</v>
+        <v>1.6522604227066</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.92750000953674</v>
       </c>
       <c r="G70" t="n">
-        <v>1.80484795570374</v>
+        <v>1.80484783649445</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.75</v>
       </c>
       <c r="G74" t="n">
-        <v>1.69541645050049</v>
+        <v>1.6954163312912</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G75" t="n">
-        <v>1.66150832176208</v>
+        <v>1.66150796413422</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>1.64917778968811</v>
+        <v>1.6491779088974</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G78" t="n">
-        <v>1.74782013893127</v>
+        <v>1.74782025814056</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>2.66750001907349</v>
       </c>
       <c r="G79" t="n">
-        <v>1.64455389976501</v>
+        <v>1.6445540189743</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>2.68249988555908</v>
       </c>
       <c r="G80" t="n">
-        <v>1.65380167961121</v>
+        <v>1.65380156040192</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G82" t="n">
-        <v>1.63068246841431</v>
+        <v>1.63068234920502</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G83" t="n">
-        <v>1.60910415649414</v>
+        <v>1.60910427570343</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G84" t="n">
-        <v>1.56594812870026</v>
+        <v>1.56594836711884</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>2.58750009536743</v>
       </c>
       <c r="G85" t="n">
-        <v>1.59523272514343</v>
+        <v>1.59523284435272</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>2.50250005722046</v>
       </c>
       <c r="G87" t="n">
-        <v>1.54282903671265</v>
+        <v>1.54282891750336</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.65499997138977</v>
       </c>
       <c r="G89" t="n">
-        <v>1.636847615242</v>
+        <v>1.63684749603271</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>1.6707558631897</v>
+        <v>1.67075574398041</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>2.66750001907349</v>
       </c>
       <c r="G92" t="n">
-        <v>1.64455389976501</v>
+        <v>1.6445540189743</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G93" t="n">
-        <v>1.63068246841431</v>
+        <v>1.63068234920502</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G94" t="n">
-        <v>1.6399302482605</v>
+        <v>1.63993012905121</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.6324999332428</v>
       </c>
       <c r="G96" t="n">
-        <v>1.62297582626343</v>
+        <v>1.62297594547272</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G97" t="n">
-        <v>1.57827842235565</v>
+        <v>1.57827866077423</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G98" t="n">
-        <v>1.66459083557129</v>
+        <v>1.66459047794342</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.45300006866455</v>
       </c>
       <c r="G100" t="n">
-        <v>1.51231145858765</v>
+        <v>1.51231169700623</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G104" t="n">
-        <v>1.37482845783234</v>
+        <v>1.37482857704163</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>1.33475518226624</v>
+        <v>1.33475506305695</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.11899995803833</v>
       </c>
       <c r="G108" t="n">
-        <v>1.30639553070068</v>
+        <v>1.30639541149139</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.24900007247925</v>
       </c>
       <c r="G112" t="n">
-        <v>1.38654255867004</v>
+        <v>1.38654243946075</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.22300004959106</v>
       </c>
       <c r="G113" t="n">
-        <v>1.37051296234131</v>
+        <v>1.3705130815506</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G114" t="n">
-        <v>1.35016798973083</v>
+        <v>1.35016810894012</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G118" t="n">
-        <v>1.34708535671234</v>
+        <v>1.34708547592163</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.22099995613098</v>
       </c>
       <c r="G122" t="n">
-        <v>1.36927998065948</v>
+        <v>1.3692798614502</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G124" t="n">
-        <v>1.27125406265259</v>
+        <v>1.27125418186188</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G127" t="n">
-        <v>1.33043956756592</v>
+        <v>1.33043944835663</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G128" t="n">
-        <v>1.35325038433075</v>
+        <v>1.35325062274933</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>2.02699995040894</v>
       </c>
       <c r="G133" t="n">
-        <v>1.24967610836029</v>
+        <v>1.249675989151</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>1.28543388843536</v>
+        <v>1.28543400764465</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G135" t="n">
-        <v>1.35016798973083</v>
+        <v>1.35016810894012</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.16199994087219</v>
       </c>
       <c r="G137" t="n">
-        <v>1.33290553092957</v>
+        <v>1.33290541172028</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G138" t="n">
-        <v>1.32304120063782</v>
+        <v>1.32304131984711</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G139" t="n">
-        <v>1.27002096176147</v>
+        <v>1.27002108097076</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.08400011062622</v>
       </c>
       <c r="G141" t="n">
-        <v>1.2848174571991</v>
+        <v>1.28481757640839</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>2.30900001525879</v>
       </c>
       <c r="G145" t="n">
-        <v>1.42353320121765</v>
+        <v>1.42353332042694</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G146" t="n">
-        <v>1.4025719165802</v>
+        <v>1.40257179737091</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G147" t="n">
-        <v>1.35325038433075</v>
+        <v>1.35325062274933</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G148" t="n">
-        <v>1.35633325576782</v>
+        <v>1.35633313655853</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>2.17300009727478</v>
       </c>
       <c r="G149" t="n">
-        <v>1.33968722820282</v>
+        <v>1.33968734741211</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.04699993133545</v>
       </c>
       <c r="G150" t="n">
-        <v>1.2620062828064</v>
+        <v>1.26200640201569</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.07100009918213</v>
       </c>
       <c r="G151" t="n">
-        <v>1.27680277824402</v>
+        <v>1.27680289745331</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>2.05299997329712</v>
       </c>
       <c r="G152" t="n">
-        <v>1.26570546627045</v>
+        <v>1.26570534706116</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>2.02099990844727</v>
       </c>
       <c r="G153" t="n">
-        <v>1.24597680568695</v>
+        <v>1.24597692489624</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G155" t="n">
-        <v>1.28235125541687</v>
+        <v>1.28235137462616</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>2.10199999809265</v>
       </c>
       <c r="G159" t="n">
-        <v>1.29591464996338</v>
+        <v>1.29591476917267</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.08899998664856</v>
       </c>
       <c r="G161" t="n">
-        <v>1.2878999710083</v>
+        <v>1.28790009021759</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G162" t="n">
-        <v>1.28235125541687</v>
+        <v>1.28235137462616</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G163" t="n">
-        <v>1.28235125541687</v>
+        <v>1.28235137462616</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G164" t="n">
-        <v>1.31625962257385</v>
+        <v>1.31625974178314</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G166" t="n">
-        <v>1.28543388843536</v>
+        <v>1.28543400764465</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.06900000572205</v>
       </c>
       <c r="G167" t="n">
-        <v>1.27556979656219</v>
+        <v>1.27556967735291</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G168" t="n">
-        <v>1.24782657623291</v>
+        <v>1.24782645702362</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G171" t="n">
-        <v>1.20140945911407</v>
+        <v>1.20140957832336</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>1.59099996089935</v>
       </c>
       <c r="G175" t="n">
-        <v>1.12108075618744</v>
+        <v>1.12108063697815</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>1.4889999628067</v>
       </c>
       <c r="G177" t="n">
-        <v>1.04920744895935</v>
+        <v>1.04920732975006</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>1.50899994373322</v>
       </c>
       <c r="G185" t="n">
-        <v>1.06330025196075</v>
+        <v>1.06330013275146</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>1.5110000371933</v>
       </c>
       <c r="G189" t="n">
-        <v>1.06470942497253</v>
+        <v>1.06470954418182</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G190" t="n">
-        <v>1.11473882198334</v>
+        <v>1.11473894119263</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>1.63699996471405</v>
       </c>
       <c r="G191" t="n">
-        <v>1.15349411964417</v>
+        <v>1.15349400043488</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>1.15913116931915</v>
+        <v>1.15913105010986</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>1.62300002574921</v>
       </c>
       <c r="G194" t="n">
-        <v>1.14362919330597</v>
+        <v>1.14362907409668</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>1.73800003528595</v>
       </c>
       <c r="G199" t="n">
-        <v>1.22466254234314</v>
+        <v>1.22466266155243</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>1.77300000190735</v>
       </c>
       <c r="G200" t="n">
-        <v>1.24932479858398</v>
+        <v>1.24932491779327</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G201" t="n">
-        <v>1.2577805519104</v>
+        <v>1.25778067111969</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>1.84399998188019</v>
       </c>
       <c r="G206" t="n">
-        <v>1.29935419559479</v>
+        <v>1.29935431480408</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>1.86800003051758</v>
       </c>
       <c r="G208" t="n">
-        <v>1.31626558303833</v>
+        <v>1.31626570224762</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G213" t="n">
-        <v>1.28737545013428</v>
+        <v>1.28737556934357</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G215" t="n">
-        <v>1.29301249980927</v>
+        <v>1.29301261901855</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G216" t="n">
-        <v>1.2859662771225</v>
+        <v>1.28596615791321</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>2.04699993133545</v>
       </c>
       <c r="G219" t="n">
-        <v>1.44239592552185</v>
+        <v>1.44239604473114</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>1.98300004005432</v>
       </c>
       <c r="G225" t="n">
-        <v>1.39729917049408</v>
+        <v>1.39729928970337</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G233" t="n">
-        <v>1.27539658546448</v>
+        <v>1.27539646625519</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G235" t="n">
-        <v>1.2577805519104</v>
+        <v>1.25778067111969</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>1.76400005817413</v>
       </c>
       <c r="G236" t="n">
-        <v>1.24298334121704</v>
+        <v>1.24298322200775</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>1.82099997997284</v>
       </c>
       <c r="G237" t="n">
-        <v>1.28314769268036</v>
+        <v>1.28314757347107</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G240" t="n">
-        <v>1.27891981601715</v>
+        <v>1.27891993522644</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G241" t="n">
-        <v>1.26482701301575</v>
+        <v>1.26482689380646</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>1.807000041008</v>
       </c>
       <c r="G243" t="n">
-        <v>1.27328288555145</v>
+        <v>1.27328276634216</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G244" t="n">
-        <v>1.29653573036194</v>
+        <v>1.29653584957123</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>1.94099998474121</v>
       </c>
       <c r="G249" t="n">
-        <v>1.3677042722702</v>
+        <v>1.36770439147949</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G250" t="n">
-        <v>1.3698183298111</v>
+        <v>1.36981821060181</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G252" t="n">
-        <v>1.35713469982147</v>
+        <v>1.35713481903076</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G253" t="n">
-        <v>1.32824456691742</v>
+        <v>1.32824444770813</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G255" t="n">
-        <v>1.4198477268219</v>
+        <v>1.41984760761261</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>1.98699998855591</v>
       </c>
       <c r="G256" t="n">
-        <v>1.40011775493622</v>
+        <v>1.40011763572693</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G258" t="n">
-        <v>1.39236652851105</v>
+        <v>1.39236664772034</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>1.942999958992</v>
       </c>
       <c r="G261" t="n">
-        <v>1.36911344528198</v>
+        <v>1.36911356449127</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>1.97200000286102</v>
       </c>
       <c r="G263" t="n">
-        <v>1.3895480632782</v>
+        <v>1.38954818248749</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G264" t="n">
-        <v>1.40223169326782</v>
+        <v>1.40223157405853</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.01300001144409</v>
       </c>
       <c r="G265" t="n">
-        <v>1.41843831539154</v>
+        <v>1.41843843460083</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G267" t="n">
-        <v>1.52765727043152</v>
+        <v>1.52765738964081</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G268" t="n">
-        <v>1.56077539920807</v>
+        <v>1.56077527999878</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G270" t="n">
-        <v>1.55161499977112</v>
+        <v>1.55161511898041</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.18300008773804</v>
       </c>
       <c r="G271" t="n">
-        <v>1.53822696208954</v>
+        <v>1.53822708129883</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.10199999809265</v>
       </c>
       <c r="G275" t="n">
-        <v>1.48115110397339</v>
+        <v>1.48115122318268</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G276" t="n">
-        <v>1.48819768428802</v>
+        <v>1.48819756507874</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>2.06699991226196</v>
       </c>
       <c r="G278" t="n">
-        <v>1.45648860931396</v>
+        <v>1.45648872852325</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G280" t="n">
-        <v>1.44450998306274</v>
+        <v>1.44450986385345</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.03699994087219</v>
       </c>
       <c r="G281" t="n">
-        <v>1.43534970283508</v>
+        <v>1.43534958362579</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G282" t="n">
-        <v>1.44450998306274</v>
+        <v>1.44450986385345</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>2.04299998283386</v>
       </c>
       <c r="G283" t="n">
-        <v>1.43957734107971</v>
+        <v>1.439577460289</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>2.05299997329712</v>
       </c>
       <c r="G286" t="n">
-        <v>1.44662392139435</v>
+        <v>1.44662380218506</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G288" t="n">
-        <v>1.43182647228241</v>
+        <v>1.4318265914917</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.14100003242493</v>
       </c>
       <c r="G291" t="n">
-        <v>1.50863206386566</v>
+        <v>1.50863218307495</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>2.12400007247925</v>
       </c>
       <c r="G292" t="n">
-        <v>1.49665331840515</v>
+        <v>1.49665343761444</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G293" t="n">
-        <v>1.49101614952087</v>
+        <v>1.49101603031158</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G294" t="n">
-        <v>1.46705842018127</v>
+        <v>1.46705853939056</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G295" t="n">
-        <v>1.51074612140656</v>
+        <v>1.51074600219727</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>2.12299990653992</v>
       </c>
       <c r="G297" t="n">
-        <v>1.49594867229462</v>
+        <v>1.49594855308533</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.11299991607666</v>
       </c>
       <c r="G299" t="n">
-        <v>1.48890197277069</v>
+        <v>1.48890221118927</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G300" t="n">
-        <v>1.51215517520905</v>
+        <v>1.51215529441833</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>2.12899994850159</v>
       </c>
       <c r="G301" t="n">
-        <v>1.50017631053925</v>
+        <v>1.50017642974854</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>2.06699991226196</v>
       </c>
       <c r="G304" t="n">
-        <v>1.45648860931396</v>
+        <v>1.45648872852325</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>2.12100005149841</v>
       </c>
       <c r="G306" t="n">
-        <v>1.49453926086426</v>
+        <v>1.49453938007355</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>2.12299990653992</v>
       </c>
       <c r="G307" t="n">
-        <v>1.49594867229462</v>
+        <v>1.49594855308533</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.1029999256134</v>
       </c>
       <c r="G309" t="n">
-        <v>1.48185575008392</v>
+        <v>1.48185586929321</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.18300008773804</v>
       </c>
       <c r="G311" t="n">
-        <v>1.53822696208954</v>
+        <v>1.53822708129883</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G313" t="n">
-        <v>1.61855578422546</v>
+        <v>1.61855566501617</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G315" t="n">
-        <v>1.61855578422546</v>
+        <v>1.61855566501617</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.29299998283386</v>
       </c>
       <c r="G319" t="n">
-        <v>1.61573719978333</v>
+        <v>1.61573731899261</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G321" t="n">
-        <v>1.63758087158203</v>
+        <v>1.63758099079132</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G323" t="n">
-        <v>1.60234892368317</v>
+        <v>1.60234904289246</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.2590000629425</v>
       </c>
       <c r="G324" t="n">
-        <v>1.59177947044373</v>
+        <v>1.59177935123444</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G326" t="n">
-        <v>1.51074612140656</v>
+        <v>1.51074600219727</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>2.12400007247925</v>
       </c>
       <c r="G328" t="n">
-        <v>1.49665331840515</v>
+        <v>1.49665343761444</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.12899994850159</v>
       </c>
       <c r="G329" t="n">
-        <v>1.50017631053925</v>
+        <v>1.50017642974854</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.19899988174438</v>
       </c>
       <c r="G330" t="n">
-        <v>1.54950106143951</v>
+        <v>1.5495011806488</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.25</v>
       </c>
       <c r="G331" t="n">
-        <v>1.58543789386749</v>
+        <v>1.58543765544891</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.22099995613098</v>
       </c>
       <c r="G332" t="n">
-        <v>1.56500327587128</v>
+        <v>1.56500315666199</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G333" t="n">
-        <v>1.54456865787506</v>
+        <v>1.54456877708435</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.25</v>
       </c>
       <c r="G334" t="n">
-        <v>1.58543789386749</v>
+        <v>1.58543765544891</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G335" t="n">
-        <v>1.5769819021225</v>
+        <v>1.57698202133179</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G336" t="n">
-        <v>1.61855578422546</v>
+        <v>1.61855566501617</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.40300011634827</v>
       </c>
       <c r="G340" t="n">
-        <v>1.6932475566864</v>
+        <v>1.69324779510498</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>1.6453320980072</v>
+        <v>1.64533221721649</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G344" t="n">
-        <v>1.66294801235199</v>
+        <v>1.6629478931427</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G348" t="n">
-        <v>1.56147992610931</v>
+        <v>1.56148016452789</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G350" t="n">
-        <v>1.55161499977112</v>
+        <v>1.55161511898041</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2.26900005340576</v>
       </c>
       <c r="G354" t="n">
-        <v>1.59882593154907</v>
+        <v>1.59882605075836</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>2.50250005722046</v>
       </c>
       <c r="G356" t="n">
-        <v>1.76335918903351</v>
+        <v>1.76335906982422</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>2.83750009536743</v>
       </c>
       <c r="G357" t="n">
-        <v>1.99941301345825</v>
+        <v>1.99941325187683</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>2.7574999332428</v>
       </c>
       <c r="G358" t="n">
-        <v>1.94304203987122</v>
+        <v>1.94304215908051</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G359" t="n">
-        <v>1.86729335784912</v>
+        <v>1.86729347705841</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2.69749999046326</v>
       </c>
       <c r="G360" t="n">
-        <v>1.90076375007629</v>
+        <v>1.900763630867</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>2.65750002861023</v>
       </c>
       <c r="G361" t="n">
-        <v>1.87257826328278</v>
+        <v>1.87257814407349</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>2.54250001907349</v>
       </c>
       <c r="G363" t="n">
-        <v>1.79154443740845</v>
+        <v>1.79154467582703</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G364" t="n">
-        <v>1.79682946205139</v>
+        <v>1.79682958126068</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G365" t="n">
-        <v>1.7933064699173</v>
+        <v>1.79330635070801</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2.50250005722046</v>
       </c>
       <c r="G366" t="n">
-        <v>1.76335918903351</v>
+        <v>1.76335906982422</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G368" t="n">
-        <v>1.78625977039337</v>
+        <v>1.78626012802124</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.5550000667572</v>
       </c>
       <c r="G370" t="n">
-        <v>1.80035269260406</v>
+        <v>1.80035281181335</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G371" t="n">
-        <v>1.83206152915955</v>
+        <v>1.83206129074097</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G372" t="n">
-        <v>1.87786304950714</v>
+        <v>1.87786293029785</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G373" t="n">
-        <v>1.88490927219391</v>
+        <v>1.8849093914032</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G374" t="n">
-        <v>1.83910763263702</v>
+        <v>1.83910775184631</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G375" t="n">
-        <v>1.83910763263702</v>
+        <v>1.83910775184631</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G376" t="n">
-        <v>1.86377024650574</v>
+        <v>1.86377012729645</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G377" t="n">
-        <v>1.86377024650574</v>
+        <v>1.86377012729645</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2.6324999332428</v>
       </c>
       <c r="G378" t="n">
-        <v>1.85496211051941</v>
+        <v>1.8549622297287</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>2.64249992370605</v>
       </c>
       <c r="G379" t="n">
-        <v>1.86200857162476</v>
+        <v>1.86200845241547</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>1.86377024650574</v>
+        <v>1.86377012729645</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>2.59750008583069</v>
       </c>
       <c r="G381" t="n">
-        <v>1.83029997348785</v>
+        <v>1.83029985427856</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>2.6324999332428</v>
       </c>
       <c r="G382" t="n">
-        <v>1.85496211051941</v>
+        <v>1.8549622297287</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.55749988555908</v>
       </c>
       <c r="G384" t="n">
-        <v>1.80211424827576</v>
+        <v>1.80211400985718</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.55250000953674</v>
       </c>
       <c r="G385" t="n">
-        <v>1.79859113693237</v>
+        <v>1.79859101772308</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>2.35700011253357</v>
       </c>
       <c r="G386" t="n">
-        <v>1.84116363525391</v>
+        <v>1.84116351604462</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>2.27699995040894</v>
       </c>
       <c r="G388" t="n">
-        <v>1.77867162227631</v>
+        <v>1.7786717414856</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G390" t="n">
-        <v>1.851318359375</v>
+        <v>1.85131824016571</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G393" t="n">
-        <v>1.86069202423096</v>
+        <v>1.86069214344025</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G394" t="n">
-        <v>1.81694805622101</v>
+        <v>1.81694793701172</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G395" t="n">
-        <v>1.84506916999817</v>
+        <v>1.84506940841675</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G396" t="n">
-        <v>1.81694805622101</v>
+        <v>1.81694793701172</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G397" t="n">
-        <v>1.79429471492767</v>
+        <v>1.79429459571838</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>2.3289999961853</v>
       </c>
       <c r="G399" t="n">
-        <v>1.819291472435</v>
+        <v>1.81929135322571</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>2.30800008773804</v>
       </c>
       <c r="G401" t="n">
-        <v>1.80288743972778</v>
+        <v>1.80288732051849</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G406" t="n">
-        <v>1.82944643497467</v>
+        <v>1.82944655418396</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.33899998664856</v>
       </c>
       <c r="G407" t="n">
-        <v>1.82710301876068</v>
+        <v>1.82710289955139</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G408" t="n">
-        <v>1.78257751464844</v>
+        <v>1.78257763385773</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.3289999961853</v>
       </c>
       <c r="G412" t="n">
-        <v>1.819291472435</v>
+        <v>1.81929135322571</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G413" t="n">
-        <v>1.82397830486298</v>
+        <v>1.82397842407227</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G415" t="n">
-        <v>1.79351353645325</v>
+        <v>1.79351365566254</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>2.27699995040894</v>
       </c>
       <c r="G416" t="n">
-        <v>1.77867162227631</v>
+        <v>1.7786717414856</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G417" t="n">
-        <v>1.7794531583786</v>
+        <v>1.77945303916931</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>2.26099991798401</v>
       </c>
       <c r="G418" t="n">
-        <v>1.76617324352264</v>
+        <v>1.76617348194122</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>2.23699998855591</v>
       </c>
       <c r="G419" t="n">
-        <v>1.74742603302002</v>
+        <v>1.74742591381073</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>2.2590000629425</v>
       </c>
       <c r="G421" t="n">
-        <v>1.76461124420166</v>
+        <v>1.76461112499237</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G422" t="n">
-        <v>1.73024070262909</v>
+        <v>1.7302405834198</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>2.14100003242493</v>
       </c>
       <c r="G424" t="n">
-        <v>1.67243576049805</v>
+        <v>1.67243587970734</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2.11700010299683</v>
       </c>
       <c r="G426" t="n">
-        <v>1.65368831157684</v>
+        <v>1.65368843078613</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>2.1010000705719</v>
       </c>
       <c r="G428" t="n">
-        <v>1.64118993282318</v>
+        <v>1.64119005203247</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>2.0789999961853</v>
       </c>
       <c r="G429" t="n">
-        <v>1.62400472164154</v>
+        <v>1.62400460243225</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>2.05299997329712</v>
       </c>
       <c r="G430" t="n">
-        <v>1.60369491577148</v>
+        <v>1.60369479656219</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>1.97699999809265</v>
       </c>
       <c r="G433" t="n">
-        <v>1.54432761669159</v>
+        <v>1.54432773590088</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G435" t="n">
-        <v>1.50136458873749</v>
+        <v>1.50136470794678</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G436" t="n">
-        <v>1.45762050151825</v>
+        <v>1.45762038230896</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G438" t="n">
-        <v>1.43887293338776</v>
+        <v>1.43887281417847</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G441" t="n">
-        <v>1.48417925834656</v>
+        <v>1.48417937755585</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G442" t="n">
-        <v>1.48417925834656</v>
+        <v>1.48417937755585</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G445" t="n">
-        <v>1.48886620998383</v>
+        <v>1.48886632919312</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>1.8309999704361</v>
       </c>
       <c r="G449" t="n">
-        <v>1.43028020858765</v>
+        <v>1.43028008937836</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G451" t="n">
-        <v>1.40997040271759</v>
+        <v>1.4099702835083</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G452" t="n">
-        <v>1.31232702732086</v>
+        <v>1.31232690811157</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>1.67340004444122</v>
       </c>
       <c r="G453" t="n">
-        <v>1.30717158317566</v>
+        <v>1.30717146396637</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G460" t="n">
-        <v>1.42715561389923</v>
+        <v>1.42715573310852</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>1.80599999427795</v>
       </c>
       <c r="G462" t="n">
-        <v>1.41075146198273</v>
+        <v>1.41075158119202</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>1.94939994812012</v>
       </c>
       <c r="G463" t="n">
-        <v>1.52276790142059</v>
+        <v>1.52276802062988</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>1.92239999771118</v>
       </c>
       <c r="G465" t="n">
-        <v>1.50167715549469</v>
+        <v>1.50167691707611</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>2.02049994468689</v>
       </c>
       <c r="G467" t="n">
-        <v>1.57830739021301</v>
+        <v>1.5783075094223</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.00850009918213</v>
       </c>
       <c r="G472" t="n">
-        <v>1.56893384456635</v>
+        <v>1.56893396377563</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>2.29450011253357</v>
       </c>
       <c r="G474" t="n">
-        <v>1.79234206676483</v>
+        <v>1.79234194755554</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>2.25950002670288</v>
       </c>
       <c r="G475" t="n">
-        <v>1.76500177383423</v>
+        <v>1.76500165462494</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>2.25650000572205</v>
       </c>
       <c r="G476" t="n">
-        <v>1.76265823841095</v>
+        <v>1.76265835762024</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G477" t="n">
-        <v>1.75601840019226</v>
+        <v>1.75601851940155</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>2.22699999809265</v>
       </c>
       <c r="G478" t="n">
-        <v>1.73961436748505</v>
+        <v>1.73961448669434</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G480" t="n">
-        <v>1.74664485454559</v>
+        <v>1.7466447353363</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>2.22300004959106</v>
       </c>
       <c r="G481" t="n">
-        <v>1.73648989200592</v>
+        <v>1.73649001121521</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>2.29749989509583</v>
       </c>
       <c r="G483" t="n">
-        <v>1.79468524456024</v>
+        <v>1.79468512535095</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G485" t="n">
-        <v>1.86850380897522</v>
+        <v>1.86850368976593</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.25</v>
       </c>
       <c r="G487" t="n">
-        <v>1.75758099555969</v>
+        <v>1.7575808763504</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G493" t="n">
-        <v>1.86225473880768</v>
+        <v>1.86225438117981</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.38100004196167</v>
       </c>
       <c r="G495" t="n">
-        <v>1.8599112033844</v>
+        <v>1.85991108417511</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.38899993896484</v>
       </c>
       <c r="G498" t="n">
-        <v>1.86616015434265</v>
+        <v>1.86616027355194</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.3289999961853</v>
       </c>
       <c r="G499" t="n">
-        <v>1.819291472435</v>
+        <v>1.81929135322571</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.35899996757507</v>
       </c>
       <c r="G500" t="n">
-        <v>1.84272575378418</v>
+        <v>1.84272587299347</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G501" t="n">
-        <v>1.86069202423096</v>
+        <v>1.86069214344025</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>2.4210000038147</v>
       </c>
       <c r="G503" t="n">
-        <v>1.89115715026855</v>
+        <v>1.89115703105927</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>2.40199995040894</v>
       </c>
       <c r="G505" t="n">
-        <v>1.87631523609161</v>
+        <v>1.87631499767303</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G507" t="n">
-        <v>1.851318359375</v>
+        <v>1.85131824016571</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.37949991226196</v>
       </c>
       <c r="G509" t="n">
-        <v>1.85873925685883</v>
+        <v>1.85873937606812</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>2.33949995040894</v>
       </c>
       <c r="G510" t="n">
-        <v>1.82749342918396</v>
+        <v>1.82749330997467</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>2.30800008773804</v>
       </c>
       <c r="G511" t="n">
-        <v>1.80288743972778</v>
+        <v>1.80288732051849</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G515" t="n">
-        <v>1.88256454467773</v>
+        <v>1.88256442546844</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>2.35949993133545</v>
       </c>
       <c r="G518" t="n">
-        <v>1.84311640262604</v>
+        <v>1.84311628341675</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G519" t="n">
-        <v>1.84506916999817</v>
+        <v>1.84506940841675</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G523" t="n">
-        <v>1.74352014064789</v>
+        <v>1.74352025985718</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>2.18650007247925</v>
       </c>
       <c r="G525" t="n">
-        <v>1.7079781293869</v>
+        <v>1.70797789096832</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G526" t="n">
-        <v>1.6310350894928</v>
+        <v>1.63103497028351</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>2.06399989128113</v>
       </c>
       <c r="G528" t="n">
-        <v>1.61228728294373</v>
+        <v>1.61228740215302</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>2.1324999332428</v>
       </c>
       <c r="G529" t="n">
-        <v>1.66579592227936</v>
+        <v>1.66579604148865</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G530" t="n">
-        <v>1.65603160858154</v>
+        <v>1.65603172779083</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G532" t="n">
-        <v>1.62478566169739</v>
+        <v>1.62478578090668</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>2.07750010490417</v>
       </c>
       <c r="G533" t="n">
-        <v>1.62283313274384</v>
+        <v>1.62283301353455</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>2.11150002479553</v>
       </c>
       <c r="G538" t="n">
-        <v>1.64939188957214</v>
+        <v>1.64939200878143</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>2.1010000705719</v>
       </c>
       <c r="G539" t="n">
-        <v>1.64118993282318</v>
+        <v>1.64119005203247</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.14299988746643</v>
       </c>
       <c r="G546" t="n">
-        <v>1.67399787902832</v>
+        <v>1.67399799823761</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G548" t="n">
-        <v>1.66852998733521</v>
+        <v>1.66853010654449</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>2.12949991226196</v>
       </c>
       <c r="G549" t="n">
-        <v>1.66345262527466</v>
+        <v>1.66345250606537</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G553" t="n">
-        <v>1.74976921081543</v>
+        <v>1.74976944923401</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G555" t="n">
-        <v>1.74352014064789</v>
+        <v>1.74352025985718</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.30550003051758</v>
       </c>
       <c r="G557" t="n">
-        <v>1.80093443393707</v>
+        <v>1.80093455314636</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.42149996757507</v>
       </c>
       <c r="G559" t="n">
-        <v>1.89154732227325</v>
+        <v>1.89154744148254</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G560" t="n">
-        <v>1.8786586523056</v>
+        <v>1.87865853309631</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G561" t="n">
-        <v>1.92630887031555</v>
+        <v>1.92630875110626</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G562" t="n">
-        <v>1.95130515098572</v>
+        <v>1.95130527019501</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G563" t="n">
-        <v>1.96536600589752</v>
+        <v>1.96536588668823</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G564" t="n">
-        <v>1.9216216802597</v>
+        <v>1.92162179946899</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G566" t="n">
-        <v>1.98411333560944</v>
+        <v>1.98411345481873</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G568" t="n">
-        <v>1.99661159515381</v>
+        <v>1.99661195278168</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G569" t="n">
-        <v>1.92005944252014</v>
+        <v>1.92005932331085</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G572" t="n">
-        <v>1.9216216802597</v>
+        <v>1.92162179946899</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.56800007820129</v>
       </c>
       <c r="G573" t="n">
-        <v>2.00598573684692</v>
+        <v>2.00598549842834</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G574" t="n">
-        <v>2.02785778045654</v>
+        <v>2.02785754203796</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>2.70600008964539</v>
       </c>
       <c r="G576" t="n">
-        <v>2.11378383636475</v>
+        <v>2.11378407478333</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G577" t="n">
-        <v>2.12784457206726</v>
+        <v>2.12784433364868</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G580" t="n">
-        <v>2.21064615249634</v>
+        <v>2.21064591407776</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>2.17940020561218</v>
+        <v>2.1793999671936</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G586" t="n">
-        <v>2.2575147151947</v>
+        <v>2.25751519203186</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G592" t="n">
-        <v>2.43874096870422</v>
+        <v>2.4387412071228</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>3.00399994850159</v>
       </c>
       <c r="G596" t="n">
-        <v>2.34656572341919</v>
+        <v>2.34656548500061</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>3.10800004005432</v>
       </c>
       <c r="G599" t="n">
-        <v>2.42780518531799</v>
+        <v>2.42780494689941</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>3.06800007820129</v>
       </c>
       <c r="G602" t="n">
-        <v>2.39655900001526</v>
+        <v>2.39655923843384</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>3.30399990081787</v>
       </c>
       <c r="G606" t="n">
-        <v>2.58090972900391</v>
+        <v>2.58090949058533</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>3.26799988746643</v>
       </c>
       <c r="G607" t="n">
-        <v>2.55278849601746</v>
+        <v>2.55278825759888</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G609" t="n">
-        <v>2.54810166358948</v>
+        <v>2.54810190200806</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G610" t="n">
-        <v>2.46373772621155</v>
+        <v>2.46373796463013</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G612" t="n">
-        <v>2.41374444961548</v>
+        <v>2.4137442111969</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>3.0220000743866</v>
       </c>
       <c r="G613" t="n">
-        <v>2.36062622070312</v>
+        <v>2.3606264591217</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G616" t="n">
-        <v>2.39343428611755</v>
+        <v>2.39343452453613</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>3.18799996376038</v>
       </c>
       <c r="G621" t="n">
-        <v>2.49029660224915</v>
+        <v>2.49029684066772</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G622" t="n">
-        <v>2.52310490608215</v>
+        <v>2.52310514450073</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G627" t="n">
-        <v>2.52310490608215</v>
+        <v>2.52310514450073</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>3.42199993133545</v>
       </c>
       <c r="G633" t="n">
-        <v>2.67308521270752</v>
+        <v>2.67308497428894</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>3.45199990272522</v>
       </c>
       <c r="G634" t="n">
-        <v>2.69651937484741</v>
+        <v>2.69651961326599</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G635" t="n">
-        <v>2.71058011054993</v>
+        <v>2.71058034896851</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>3.53600001335144</v>
       </c>
       <c r="G636" t="n">
-        <v>2.76213574409485</v>
+        <v>2.76213598251343</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -31286,6 +31286,32 @@
         <v>2.3199999332428</v>
       </c>
       <c r="H1189" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1190" t="n">
+        <v>2455565</v>
+      </c>
+      <c r="C1190" t="n">
+        <v>2.37800002098083</v>
+      </c>
+      <c r="D1190" t="n">
+        <v>2.30999994277954</v>
+      </c>
+      <c r="E1190" t="n">
+        <v>2.32200002670288</v>
+      </c>
+      <c r="F1190" t="n">
+        <v>2.33800005912781</v>
+      </c>
+      <c r="G1190" t="n">
+        <v>2.33800005912781</v>
+      </c>
+      <c r="H1190" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/MFEA.MI.xlsx
+++ b/data/MFEA.MI.xlsx
@@ -447,7 +447,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G3" t="n">
-        <v>2.25028038024902</v>
+        <v>2.25028014183044</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>3.71250009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>2.28881216049194</v>
+        <v>2.28881239891052</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G5" t="n">
-        <v>2.30884909629822</v>
+        <v>2.30884885787964</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.70749998092651</v>
       </c>
       <c r="G7" t="n">
-        <v>2.28572988510132</v>
+        <v>2.28572964668274</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G8" t="n">
-        <v>2.27494072914124</v>
+        <v>2.27494049072266</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G12" t="n">
-        <v>2.29035353660583</v>
+        <v>2.29035329818726</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G15" t="n">
-        <v>2.32734441757202</v>
+        <v>2.3273446559906</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6448495388031</v>
+        <v>2.64484977722168</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G17" t="n">
-        <v>2.69417071342468</v>
+        <v>2.69417095184326</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G18" t="n">
-        <v>2.66951012611389</v>
+        <v>2.66951036453247</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G20" t="n">
-        <v>2.61710619926453</v>
+        <v>2.61710643768311</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G21" t="n">
-        <v>2.64793252944946</v>
+        <v>2.64793229103088</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G22" t="n">
-        <v>2.5955286026001</v>
+        <v>2.59552836418152</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G23" t="n">
-        <v>2.49688601493835</v>
+        <v>2.49688625335693</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>3.98250007629395</v>
       </c>
       <c r="G27" t="n">
-        <v>2.45527148246765</v>
+        <v>2.45527124404907</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G28" t="n">
-        <v>2.47222542762756</v>
+        <v>2.47222566604614</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G31" t="n">
-        <v>2.40440893173218</v>
+        <v>2.4044086933136</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G35" t="n">
-        <v>2.48455595970154</v>
+        <v>2.48455572128296</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>3.92750000953674</v>
       </c>
       <c r="G36" t="n">
-        <v>2.42136311531067</v>
+        <v>2.42136287689209</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.73749995231628</v>
       </c>
       <c r="G40" t="n">
-        <v>2.30422472953796</v>
+        <v>2.30422496795654</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.26749992370605</v>
       </c>
       <c r="G47" t="n">
-        <v>2.01446294784546</v>
+        <v>2.01446318626404</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G49" t="n">
-        <v>2.07149076461792</v>
+        <v>2.07149052619934</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.17750000953674</v>
       </c>
       <c r="G51" t="n">
-        <v>1.95897674560547</v>
+        <v>1.95897650718689</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G55" t="n">
-        <v>1.82796740531921</v>
+        <v>1.82796728610992</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G56" t="n">
-        <v>1.8557106256485</v>
+        <v>1.85571014881134</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3</v>
       </c>
       <c r="G57" t="n">
-        <v>1.84954524040222</v>
+        <v>1.84954535961151</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G58" t="n">
-        <v>1.82488453388214</v>
+        <v>1.82488477230072</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G59" t="n">
-        <v>1.79405891895294</v>
+        <v>1.79405879974365</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G60" t="n">
-        <v>1.79714131355286</v>
+        <v>1.79714143276215</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G61" t="n">
-        <v>1.80638945102692</v>
+        <v>1.80638933181763</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G63" t="n">
-        <v>1.81255424022675</v>
+        <v>1.81255435943604</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G64" t="n">
-        <v>1.87728846073151</v>
+        <v>1.87728834152222</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.89249992370605</v>
       </c>
       <c r="G65" t="n">
-        <v>1.78326976299286</v>
+        <v>1.78326988220215</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G67" t="n">
-        <v>1.69233393669128</v>
+        <v>1.69233369827271</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G68" t="n">
-        <v>1.66150808334351</v>
+        <v>1.6615082025528</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.92750000953674</v>
       </c>
       <c r="G70" t="n">
-        <v>1.80484795570374</v>
+        <v>1.80484783649445</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.86249995231628</v>
       </c>
       <c r="G71" t="n">
-        <v>1.76477444171906</v>
+        <v>1.76477432250977</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.88750004768372</v>
       </c>
       <c r="G72" t="n">
-        <v>1.78018712997437</v>
+        <v>1.78018736839294</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G73" t="n">
-        <v>1.74165523052216</v>
+        <v>1.74165499210358</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.75</v>
       </c>
       <c r="G74" t="n">
-        <v>1.69541645050049</v>
+        <v>1.6954163312912</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G75" t="n">
-        <v>1.66150808334351</v>
+        <v>1.6615082025528</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G76" t="n">
-        <v>1.6337651014328</v>
+        <v>1.63376498222351</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>2.68249988555908</v>
       </c>
       <c r="G80" t="n">
-        <v>1.65380156040192</v>
+        <v>1.65380167961121</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G81" t="n">
-        <v>1.62143468856812</v>
+        <v>1.6214348077774</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G83" t="n">
-        <v>1.60910415649414</v>
+        <v>1.60910439491272</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G84" t="n">
-        <v>1.56594812870026</v>
+        <v>1.56594824790955</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>2.58750009536743</v>
       </c>
       <c r="G85" t="n">
-        <v>1.59523272514343</v>
+        <v>1.59523284435272</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G86" t="n">
-        <v>1.58752620220184</v>
+        <v>1.58752644062042</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>2.50250005722046</v>
       </c>
       <c r="G87" t="n">
-        <v>1.54282903671265</v>
+        <v>1.54282891750336</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.65499997138977</v>
       </c>
       <c r="G89" t="n">
-        <v>1.63684737682343</v>
+        <v>1.636847615242</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G90" t="n">
-        <v>1.62143468856812</v>
+        <v>1.6214348077774</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>1.6707558631897</v>
+        <v>1.67075574398041</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G94" t="n">
-        <v>1.63993012905121</v>
+        <v>1.6399302482605</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G97" t="n">
-        <v>1.57827854156494</v>
+        <v>1.57827842235565</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G98" t="n">
-        <v>1.66459059715271</v>
+        <v>1.66459083557129</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>1.60602188110352</v>
+        <v>1.60602176189423</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G104" t="n">
-        <v>1.37482857704163</v>
+        <v>1.37482845783234</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>1.33475506305695</v>
+        <v>1.33475518226624</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G109" t="n">
-        <v>1.31934237480164</v>
+        <v>1.31934225559235</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>2.18899989128113</v>
       </c>
       <c r="G111" t="n">
-        <v>1.34955132007599</v>
+        <v>1.34955143928528</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G114" t="n">
-        <v>1.35016787052155</v>
+        <v>1.35016798973083</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G115" t="n">
-        <v>1.36558079719543</v>
+        <v>1.36558091640472</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>2.28900003433228</v>
       </c>
       <c r="G116" t="n">
-        <v>1.41120290756226</v>
+        <v>1.41120302677155</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G117" t="n">
-        <v>1.41490209102631</v>
+        <v>1.4149022102356</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G118" t="n">
-        <v>1.34708535671234</v>
+        <v>1.34708547592163</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G119" t="n">
-        <v>1.38099384307861</v>
+        <v>1.38099372386932</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G120" t="n">
-        <v>1.37236261367798</v>
+        <v>1.37236249446869</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G121" t="n">
-        <v>1.4056544303894</v>
+        <v>1.40565431118011</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.22099995613098</v>
       </c>
       <c r="G122" t="n">
-        <v>1.36927998065948</v>
+        <v>1.3692798614502</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G124" t="n">
-        <v>1.27125406265259</v>
+        <v>1.27125418186188</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G125" t="n">
-        <v>1.23919534683228</v>
+        <v>1.23919522762299</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G126" t="n">
-        <v>1.29344868659973</v>
+        <v>1.29344856739044</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G127" t="n">
-        <v>1.33043956756592</v>
+        <v>1.33043944835663</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>2.02699995040894</v>
       </c>
       <c r="G133" t="n">
-        <v>1.249675989151</v>
+        <v>1.24967610836029</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G135" t="n">
-        <v>1.35016787052155</v>
+        <v>1.35016798973083</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G138" t="n">
-        <v>1.32304131984711</v>
+        <v>1.32304120063782</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.125</v>
       </c>
       <c r="G142" t="n">
-        <v>1.31009459495544</v>
+        <v>1.31009447574615</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>2.30900001525879</v>
       </c>
       <c r="G145" t="n">
-        <v>1.42353320121765</v>
+        <v>1.42353332042694</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G146" t="n">
-        <v>1.40257179737091</v>
+        <v>1.4025719165802</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G148" t="n">
-        <v>1.35633313655853</v>
+        <v>1.35633325576782</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>2.17300009727478</v>
       </c>
       <c r="G149" t="n">
-        <v>1.33968734741211</v>
+        <v>1.33968722820282</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G154" t="n">
-        <v>1.23611271381378</v>
+        <v>1.23611283302307</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.10899996757507</v>
       </c>
       <c r="G156" t="n">
-        <v>1.3002302646637</v>
+        <v>1.30023038387299</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>2.05100011825562</v>
       </c>
       <c r="G158" t="n">
-        <v>1.26447248458862</v>
+        <v>1.26447260379791</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G160" t="n">
-        <v>1.2909824848175</v>
+        <v>1.29098260402679</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G164" t="n">
-        <v>1.31625974178314</v>
+        <v>1.31625962257385</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.06900000572205</v>
       </c>
       <c r="G167" t="n">
-        <v>1.27556967735291</v>
+        <v>1.27556955814362</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G171" t="n">
-        <v>1.20140957832336</v>
+        <v>1.20140945911407</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1.68299996852875</v>
       </c>
       <c r="G172" t="n">
-        <v>1.18590748310089</v>
+        <v>1.1859073638916</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>1.65199995040894</v>
       </c>
       <c r="G173" t="n">
-        <v>1.16406345367432</v>
+        <v>1.16406357288361</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>1.57599997520447</v>
       </c>
       <c r="G181" t="n">
-        <v>1.11051106452942</v>
+        <v>1.11051094532013</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>1.557000041008</v>
       </c>
       <c r="G183" t="n">
-        <v>1.09712290763855</v>
+        <v>1.09712302684784</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>1.50899994373322</v>
       </c>
       <c r="G185" t="n">
-        <v>1.06330025196075</v>
+        <v>1.06330013275146</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G190" t="n">
-        <v>1.11473882198334</v>
+        <v>1.11473894119263</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>1.63699996471405</v>
       </c>
       <c r="G191" t="n">
-        <v>1.15349411964417</v>
+        <v>1.15349400043488</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G192" t="n">
-        <v>1.14715242385864</v>
+        <v>1.14715230464935</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>1.15913116931915</v>
+        <v>1.15913128852844</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G195" t="n">
-        <v>1.16265439987183</v>
+        <v>1.16265428066254</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>1.78699994087219</v>
       </c>
       <c r="G198" t="n">
-        <v>1.25918984413147</v>
+        <v>1.25918972492218</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>1.73800003528595</v>
       </c>
       <c r="G199" t="n">
-        <v>1.22466266155243</v>
+        <v>1.22466254234314</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>1.77300000190735</v>
       </c>
       <c r="G200" t="n">
-        <v>1.24932479858398</v>
+        <v>1.24932491779327</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G201" t="n">
-        <v>1.2577805519104</v>
+        <v>1.25778067111969</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>1.78199994564056</v>
       </c>
       <c r="G202" t="n">
-        <v>1.25566673278809</v>
+        <v>1.2556666135788</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G205" t="n">
-        <v>1.30499136447906</v>
+        <v>1.30499148368835</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>1.84399998188019</v>
       </c>
       <c r="G206" t="n">
-        <v>1.29935419559479</v>
+        <v>1.29935443401337</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>1.86800003051758</v>
       </c>
       <c r="G208" t="n">
-        <v>1.31626558303833</v>
+        <v>1.31626570224762</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>1.91100001335144</v>
       </c>
       <c r="G210" t="n">
-        <v>1.34656524658203</v>
+        <v>1.34656512737274</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G212" t="n">
-        <v>1.2937171459198</v>
+        <v>1.29371726512909</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G215" t="n">
-        <v>1.29301261901855</v>
+        <v>1.29301249980927</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>2.01900005340576</v>
       </c>
       <c r="G218" t="n">
-        <v>1.42266631126404</v>
+        <v>1.42266607284546</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>2.04699993133545</v>
       </c>
       <c r="G219" t="n">
-        <v>1.44239592552185</v>
+        <v>1.44239604473114</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.01900005340576</v>
       </c>
       <c r="G220" t="n">
-        <v>1.42266631126404</v>
+        <v>1.42266607284546</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>2.0090000629425</v>
       </c>
       <c r="G222" t="n">
-        <v>1.41561985015869</v>
+        <v>1.4156197309494</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G223" t="n">
-        <v>1.42618942260742</v>
+        <v>1.42618918418884</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G227" t="n">
-        <v>1.33035838603973</v>
+        <v>1.33035850524902</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G228" t="n">
-        <v>1.32472121715546</v>
+        <v>1.32472145557404</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G231" t="n">
-        <v>1.31908404827118</v>
+        <v>1.31908428668976</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>1.75899994373322</v>
       </c>
       <c r="G234" t="n">
-        <v>1.23945987224579</v>
+        <v>1.23945999145508</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G235" t="n">
-        <v>1.2577805519104</v>
+        <v>1.25778067111969</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>1.76400005817413</v>
       </c>
       <c r="G236" t="n">
-        <v>1.24298322200775</v>
+        <v>1.24298334121704</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G238" t="n">
-        <v>1.28455686569214</v>
+        <v>1.28455674648285</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G241" t="n">
-        <v>1.26482701301575</v>
+        <v>1.26482689380646</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>1.81900000572205</v>
       </c>
       <c r="G242" t="n">
-        <v>1.28173828125</v>
+        <v>1.28173840045929</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>1.807000041008</v>
       </c>
       <c r="G243" t="n">
-        <v>1.27328288555145</v>
+        <v>1.27328276634216</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G245" t="n">
-        <v>1.32331216335297</v>
+        <v>1.32331192493439</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G247" t="n">
-        <v>1.38109242916107</v>
+        <v>1.38109254837036</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>1.94099998474121</v>
       </c>
       <c r="G249" t="n">
-        <v>1.36770439147949</v>
+        <v>1.3677042722702</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G250" t="n">
-        <v>1.3698183298111</v>
+        <v>1.36981821060181</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G251" t="n">
-        <v>1.38602495193481</v>
+        <v>1.38602483272552</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G252" t="n">
-        <v>1.35713469982147</v>
+        <v>1.35713481903076</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G253" t="n">
-        <v>1.32824444770813</v>
+        <v>1.32824456691742</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>1.98699998855591</v>
       </c>
       <c r="G256" t="n">
-        <v>1.40011763572693</v>
+        <v>1.40011775493622</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G257" t="n">
-        <v>1.37052297592163</v>
+        <v>1.37052285671234</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G258" t="n">
-        <v>1.39236652851105</v>
+        <v>1.39236664772034</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>1.98800003528595</v>
       </c>
       <c r="G259" t="n">
-        <v>1.40082240104675</v>
+        <v>1.40082228183746</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>1.942999958992</v>
       </c>
       <c r="G261" t="n">
-        <v>1.36911344528198</v>
+        <v>1.36911356449127</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.00600004196167</v>
       </c>
       <c r="G262" t="n">
-        <v>1.41350591182709</v>
+        <v>1.4135057926178</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>1.97200000286102</v>
       </c>
       <c r="G263" t="n">
-        <v>1.3895480632782</v>
+        <v>1.38954818248749</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G264" t="n">
-        <v>1.40223157405853</v>
+        <v>1.40223169326782</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.01300001144409</v>
       </c>
       <c r="G265" t="n">
-        <v>1.41843843460083</v>
+        <v>1.41843819618225</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G270" t="n">
-        <v>1.55161511898041</v>
+        <v>1.55161488056183</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.18300008773804</v>
       </c>
       <c r="G271" t="n">
-        <v>1.53822708129883</v>
+        <v>1.53822696208954</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G274" t="n">
-        <v>1.48678827285767</v>
+        <v>1.48678815364838</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G277" t="n">
-        <v>1.47692322731018</v>
+        <v>1.47692334651947</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G280" t="n">
-        <v>1.44450986385345</v>
+        <v>1.44450998306274</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.03699994087219</v>
       </c>
       <c r="G281" t="n">
-        <v>1.43534958362579</v>
+        <v>1.43534970283508</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G282" t="n">
-        <v>1.44450986385345</v>
+        <v>1.44450998306274</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.07599997520447</v>
       </c>
       <c r="G284" t="n">
-        <v>1.46283054351807</v>
+        <v>1.46283066272736</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G285" t="n">
-        <v>1.46564900875092</v>
+        <v>1.46564912796021</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>2.05299997329712</v>
       </c>
       <c r="G286" t="n">
-        <v>1.44662380218506</v>
+        <v>1.44662392139435</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G288" t="n">
-        <v>1.4318265914917</v>
+        <v>1.43182647228241</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>2.09899997711182</v>
       </c>
       <c r="G289" t="n">
-        <v>1.47903716564178</v>
+        <v>1.47903728485107</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G293" t="n">
-        <v>1.49101614952087</v>
+        <v>1.49101603031158</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>2.12299990653992</v>
       </c>
       <c r="G297" t="n">
-        <v>1.49594867229462</v>
+        <v>1.49594855308533</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.11299991607666</v>
       </c>
       <c r="G299" t="n">
-        <v>1.48890209197998</v>
+        <v>1.48890197277069</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>2.12899994850159</v>
       </c>
       <c r="G301" t="n">
-        <v>1.50017642974854</v>
+        <v>1.50017631053925</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G302" t="n">
-        <v>1.52202022075653</v>
+        <v>1.52202033996582</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>2.12299990653992</v>
       </c>
       <c r="G307" t="n">
-        <v>1.49594867229462</v>
+        <v>1.49594855308533</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.18300008773804</v>
       </c>
       <c r="G311" t="n">
-        <v>1.53822708129883</v>
+        <v>1.53822696208954</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G312" t="n">
-        <v>1.58261930942535</v>
+        <v>1.58261919021606</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G313" t="n">
-        <v>1.61855578422546</v>
+        <v>1.61855566501617</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G315" t="n">
-        <v>1.61855578422546</v>
+        <v>1.61855566501617</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>2.27300000190735</v>
       </c>
       <c r="G316" t="n">
-        <v>1.60164439678192</v>
+        <v>1.60164451599121</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>2.27300000190735</v>
       </c>
       <c r="G317" t="n">
-        <v>1.60164439678192</v>
+        <v>1.60164451599121</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G318" t="n">
-        <v>1.60305380821228</v>
+        <v>1.60305368900299</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.29299998283386</v>
       </c>
       <c r="G319" t="n">
-        <v>1.61573719978333</v>
+        <v>1.61573731899261</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G321" t="n">
-        <v>1.63758087158203</v>
+        <v>1.63758099079132</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.27699995040894</v>
       </c>
       <c r="G322" t="n">
-        <v>1.60446286201477</v>
+        <v>1.60446298122406</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G323" t="n">
-        <v>1.60234892368317</v>
+        <v>1.60234916210175</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G327" t="n">
-        <v>1.47128617763519</v>
+        <v>1.47128629684448</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.12899994850159</v>
       </c>
       <c r="G329" t="n">
-        <v>1.50017642974854</v>
+        <v>1.50017631053925</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.25</v>
       </c>
       <c r="G331" t="n">
-        <v>1.58543789386749</v>
+        <v>1.5854377746582</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.22099995613098</v>
       </c>
       <c r="G332" t="n">
-        <v>1.56500327587128</v>
+        <v>1.5650030374527</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.25</v>
       </c>
       <c r="G334" t="n">
-        <v>1.58543789386749</v>
+        <v>1.5854377746582</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G336" t="n">
-        <v>1.61855578422546</v>
+        <v>1.61855566501617</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.28299999237061</v>
       </c>
       <c r="G337" t="n">
-        <v>1.60869073867798</v>
+        <v>1.60869085788727</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G338" t="n">
-        <v>1.59671187400818</v>
+        <v>1.59671199321747</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>1.6453320980072</v>
+        <v>1.64533221721649</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G343" t="n">
-        <v>1.61010015010834</v>
+        <v>1.61010026931763</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.33699989318848</v>
       </c>
       <c r="G345" t="n">
-        <v>1.64674139022827</v>
+        <v>1.64674115180969</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>2.33699989318848</v>
       </c>
       <c r="G346" t="n">
-        <v>1.64674139022827</v>
+        <v>1.64674115180969</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G347" t="n">
-        <v>1.62912547588348</v>
+        <v>1.62912535667419</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G348" t="n">
-        <v>1.5614800453186</v>
+        <v>1.56148016452789</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G350" t="n">
-        <v>1.55161511898041</v>
+        <v>1.55161488056183</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.19400000572205</v>
       </c>
       <c r="G351" t="n">
-        <v>1.54597806930542</v>
+        <v>1.54597795009613</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G352" t="n">
-        <v>1.56429862976074</v>
+        <v>1.56429851055145</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>2.27099990844727</v>
       </c>
       <c r="G353" t="n">
-        <v>1.60023522377014</v>
+        <v>1.60023510456085</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2.26900005340576</v>
       </c>
       <c r="G354" t="n">
-        <v>1.59882581233978</v>
+        <v>1.59882605075836</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>2.36400008201599</v>
       </c>
       <c r="G355" t="n">
-        <v>1.66576659679413</v>
+        <v>1.66576647758484</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>2.50250005722046</v>
       </c>
       <c r="G356" t="n">
-        <v>1.76335918903351</v>
+        <v>1.76335906982422</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>2.83750009536743</v>
       </c>
       <c r="G357" t="n">
-        <v>1.99941301345825</v>
+        <v>1.99941325187683</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>2.7574999332428</v>
       </c>
       <c r="G358" t="n">
-        <v>1.94304215908051</v>
+        <v>1.94304203987122</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G359" t="n">
-        <v>1.86729347705841</v>
+        <v>1.8672935962677</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2.69749999046326</v>
       </c>
       <c r="G360" t="n">
-        <v>1.90076386928558</v>
+        <v>1.90076375007629</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>2.65750002861023</v>
       </c>
       <c r="G361" t="n">
-        <v>1.87257814407349</v>
+        <v>1.87257826328278</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G364" t="n">
-        <v>1.79682958126068</v>
+        <v>1.79682946205139</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G365" t="n">
-        <v>1.7933064699173</v>
+        <v>1.79330635070801</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2.50250005722046</v>
       </c>
       <c r="G366" t="n">
-        <v>1.76335918903351</v>
+        <v>1.76335906982422</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G367" t="n">
-        <v>1.75736975669861</v>
+        <v>1.75736951828003</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G368" t="n">
-        <v>1.78625988960266</v>
+        <v>1.78625977039337</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G371" t="n">
-        <v>1.83206152915955</v>
+        <v>1.83206140995026</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G372" t="n">
-        <v>1.87786293029785</v>
+        <v>1.87786304950714</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G373" t="n">
-        <v>1.8849093914032</v>
+        <v>1.88490951061249</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G374" t="n">
-        <v>1.83910775184631</v>
+        <v>1.83910763263702</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G375" t="n">
-        <v>1.83910775184631</v>
+        <v>1.83910763263702</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G376" t="n">
-        <v>1.86377036571503</v>
+        <v>1.86377000808716</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G377" t="n">
-        <v>1.86377036571503</v>
+        <v>1.86377000808716</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2.6324999332428</v>
       </c>
       <c r="G378" t="n">
-        <v>1.85496199131012</v>
+        <v>1.85496234893799</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>2.64249992370605</v>
       </c>
       <c r="G379" t="n">
-        <v>1.86200845241547</v>
+        <v>1.86200857162476</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>1.86377036571503</v>
+        <v>1.86377000808716</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>2.6324999332428</v>
       </c>
       <c r="G382" t="n">
-        <v>1.85496199131012</v>
+        <v>1.85496234893799</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>2.35700011253357</v>
       </c>
       <c r="G386" t="n">
-        <v>1.8411637544632</v>
+        <v>1.84116363525391</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G387" t="n">
-        <v>1.80601191520691</v>
+        <v>1.8060120344162</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G390" t="n">
-        <v>1.85131847858429</v>
+        <v>1.851318359375</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>2.40700006484985</v>
       </c>
       <c r="G391" t="n">
-        <v>1.88022089004517</v>
+        <v>1.88022112846375</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G392" t="n">
-        <v>1.84741282463074</v>
+        <v>1.84741270542145</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G393" t="n">
-        <v>1.86069214344025</v>
+        <v>1.86069226264954</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G395" t="n">
-        <v>1.84506916999817</v>
+        <v>1.84506928920746</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G397" t="n">
-        <v>1.79429471492767</v>
+        <v>1.79429459571838</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>2.30800008773804</v>
       </c>
       <c r="G401" t="n">
-        <v>1.80288755893707</v>
+        <v>1.80288743972778</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G402" t="n">
-        <v>1.85444307327271</v>
+        <v>1.85444319248199</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.34299993515015</v>
       </c>
       <c r="G404" t="n">
-        <v>1.83022737503052</v>
+        <v>1.83022749423981</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G406" t="n">
-        <v>1.82944655418396</v>
+        <v>1.82944631576538</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G411" t="n">
-        <v>1.80601191520691</v>
+        <v>1.8060120344162</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>2.26099991798401</v>
       </c>
       <c r="G418" t="n">
-        <v>1.76617336273193</v>
+        <v>1.76617324352264</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>2.23699998855591</v>
       </c>
       <c r="G419" t="n">
-        <v>1.74742603302002</v>
+        <v>1.74742591381073</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>2.2590000629425</v>
       </c>
       <c r="G421" t="n">
-        <v>1.76461112499237</v>
+        <v>1.76461124420166</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G422" t="n">
-        <v>1.7302405834198</v>
+        <v>1.73024070262909</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>2.14100003242493</v>
       </c>
       <c r="G424" t="n">
-        <v>1.67243587970734</v>
+        <v>1.67243576049805</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2.11700010299683</v>
       </c>
       <c r="G426" t="n">
-        <v>1.65368831157684</v>
+        <v>1.65368843078613</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.11299991607666</v>
       </c>
       <c r="G427" t="n">
-        <v>1.65056359767914</v>
+        <v>1.65056347846985</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>1.97699999809265</v>
       </c>
       <c r="G433" t="n">
-        <v>1.54432761669159</v>
+        <v>1.54432773590088</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G435" t="n">
-        <v>1.50136470794678</v>
+        <v>1.50136458873749</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G436" t="n">
-        <v>1.45762050151825</v>
+        <v>1.45762038230896</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G437" t="n">
-        <v>1.44121634960175</v>
+        <v>1.44121623039246</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G438" t="n">
-        <v>1.43887281417847</v>
+        <v>1.43887293338776</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G445" t="n">
-        <v>1.48886620998383</v>
+        <v>1.48886632919312</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>1.85300004482269</v>
       </c>
       <c r="G447" t="n">
-        <v>1.44746553897858</v>
+        <v>1.44746541976929</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>1.84399998188019</v>
       </c>
       <c r="G448" t="n">
-        <v>1.44043505191803</v>
+        <v>1.44043517112732</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>1.8309999704361</v>
       </c>
       <c r="G449" t="n">
-        <v>1.43028008937836</v>
+        <v>1.43028020858765</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>1.69219994544983</v>
       </c>
       <c r="G455" t="n">
-        <v>1.32185697555542</v>
+        <v>1.32185685634613</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>1.69159996509552</v>
       </c>
       <c r="G457" t="n">
-        <v>1.3213883638382</v>
+        <v>1.32138824462891</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>1.93680000305176</v>
       </c>
       <c r="G464" t="n">
-        <v>1.51292562484741</v>
+        <v>1.51292550563812</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>2.02950000762939</v>
       </c>
       <c r="G466" t="n">
-        <v>1.58533799648285</v>
+        <v>1.58533787727356</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>1.97259998321533</v>
       </c>
       <c r="G468" t="n">
-        <v>1.54089069366455</v>
+        <v>1.54089057445526</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>2.15249991416931</v>
       </c>
       <c r="G473" t="n">
-        <v>1.68141889572144</v>
+        <v>1.68141901493073</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>2.29450011253357</v>
       </c>
       <c r="G474" t="n">
-        <v>1.79234194755554</v>
+        <v>1.79234182834625</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>2.25950002670288</v>
       </c>
       <c r="G475" t="n">
-        <v>1.76500177383423</v>
+        <v>1.76500165462494</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>2.25650000572205</v>
       </c>
       <c r="G476" t="n">
-        <v>1.76265835762024</v>
+        <v>1.76265823841095</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G477" t="n">
-        <v>1.75601840019226</v>
+        <v>1.75601851940155</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>2.22699999809265</v>
       </c>
       <c r="G478" t="n">
-        <v>1.73961436748505</v>
+        <v>1.73961448669434</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G480" t="n">
-        <v>1.74664485454559</v>
+        <v>1.74664497375488</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>2.22300004959106</v>
       </c>
       <c r="G481" t="n">
-        <v>1.73649001121521</v>
+        <v>1.73648989200592</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>2.31900000572205</v>
       </c>
       <c r="G482" t="n">
-        <v>1.81147992610931</v>
+        <v>1.8114800453186</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>2.29749989509583</v>
       </c>
       <c r="G483" t="n">
-        <v>1.79468536376953</v>
+        <v>1.79468524456024</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G485" t="n">
-        <v>1.86850368976593</v>
+        <v>1.86850357055664</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>2.32649993896484</v>
       </c>
       <c r="G486" t="n">
-        <v>1.81733870506287</v>
+        <v>1.81733858585358</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>2.33150005340576</v>
       </c>
       <c r="G488" t="n">
-        <v>1.82124447822571</v>
+        <v>1.82124435901642</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.34949994087219</v>
       </c>
       <c r="G489" t="n">
-        <v>1.83530497550964</v>
+        <v>1.83530509471893</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G490" t="n">
-        <v>1.82007241249084</v>
+        <v>1.82007253170013</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>2.39750003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>1.87280023097992</v>
+        <v>1.87279999256134</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.3989999294281</v>
       </c>
       <c r="G492" t="n">
-        <v>1.87397170066833</v>
+        <v>1.87397146224976</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G493" t="n">
-        <v>1.86225461959839</v>
+        <v>1.8622545003891</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.38100004196167</v>
       </c>
       <c r="G495" t="n">
-        <v>1.85991108417511</v>
+        <v>1.8599112033844</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G497" t="n">
-        <v>1.84194481372833</v>
+        <v>1.84194469451904</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.38899993896484</v>
       </c>
       <c r="G498" t="n">
-        <v>1.86616027355194</v>
+        <v>1.86616015434265</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G501" t="n">
-        <v>1.86069214344025</v>
+        <v>1.86069226264954</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>2.4210000038147</v>
       </c>
       <c r="G503" t="n">
-        <v>1.89115703105927</v>
+        <v>1.89115715026855</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G504" t="n">
-        <v>1.90443634986877</v>
+        <v>1.90443658828735</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G507" t="n">
-        <v>1.85131847858429</v>
+        <v>1.851318359375</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.38750004768372</v>
       </c>
       <c r="G508" t="n">
-        <v>1.86498844623566</v>
+        <v>1.86498868465424</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.37949991226196</v>
       </c>
       <c r="G509" t="n">
-        <v>1.85873913764954</v>
+        <v>1.85873925685883</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>2.33949995040894</v>
       </c>
       <c r="G510" t="n">
-        <v>1.82749342918396</v>
+        <v>1.82749330997467</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>2.30800008773804</v>
       </c>
       <c r="G511" t="n">
-        <v>1.80288755893707</v>
+        <v>1.80288743972778</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G514" t="n">
-        <v>1.84819388389587</v>
+        <v>1.84819364547729</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G515" t="n">
-        <v>1.88256442546844</v>
+        <v>1.88256454467773</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>2.38700008392334</v>
       </c>
       <c r="G516" t="n">
-        <v>1.86459815502167</v>
+        <v>1.86459791660309</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>2.35949993133545</v>
       </c>
       <c r="G518" t="n">
-        <v>1.84311628341675</v>
+        <v>1.84311640262604</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G519" t="n">
-        <v>1.84506916999817</v>
+        <v>1.84506928920746</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G521" t="n">
-        <v>1.83960139751434</v>
+        <v>1.83960127830505</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G523" t="n">
-        <v>1.74352014064789</v>
+        <v>1.74352025985718</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>2.18650007247925</v>
       </c>
       <c r="G525" t="n">
-        <v>1.7079781293869</v>
+        <v>1.70797801017761</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G526" t="n">
-        <v>1.63103497028351</v>
+        <v>1.6310350894928</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>2.06399989128113</v>
       </c>
       <c r="G528" t="n">
-        <v>1.61228740215302</v>
+        <v>1.61228728294373</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>2.1324999332428</v>
       </c>
       <c r="G529" t="n">
-        <v>1.66579592227936</v>
+        <v>1.66579604148865</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G530" t="n">
-        <v>1.65603172779083</v>
+        <v>1.65603148937225</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>2.11150002479553</v>
       </c>
       <c r="G538" t="n">
-        <v>1.64939188957214</v>
+        <v>1.64939200878143</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.09249997138977</v>
       </c>
       <c r="G544" t="n">
-        <v>1.63455021381378</v>
+        <v>1.63455009460449</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.14299988746643</v>
       </c>
       <c r="G546" t="n">
-        <v>1.67399787902832</v>
+        <v>1.67399799823761</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G548" t="n">
-        <v>1.66853010654449</v>
+        <v>1.66852998733521</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>2.12949991226196</v>
       </c>
       <c r="G549" t="n">
-        <v>1.66345262527466</v>
+        <v>1.66345250606537</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G553" t="n">
-        <v>1.74976933002472</v>
+        <v>1.74976921081543</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.24300003051758</v>
       </c>
       <c r="G554" t="n">
-        <v>1.75211274623871</v>
+        <v>1.75211298465729</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G555" t="n">
-        <v>1.74352014064789</v>
+        <v>1.74352025985718</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>2.24449992179871</v>
       </c>
       <c r="G556" t="n">
-        <v>1.75328457355499</v>
+        <v>1.7532844543457</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.30550003051758</v>
       </c>
       <c r="G557" t="n">
-        <v>1.80093443393707</v>
+        <v>1.80093455314636</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.42149996757507</v>
       </c>
       <c r="G559" t="n">
-        <v>1.89154744148254</v>
+        <v>1.89154756069183</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G560" t="n">
-        <v>1.87865853309631</v>
+        <v>1.8786586523056</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G561" t="n">
-        <v>1.92630875110626</v>
+        <v>1.92630887031555</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G563" t="n">
-        <v>1.96536612510681</v>
+        <v>1.96536600589752</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G564" t="n">
-        <v>1.92162179946899</v>
+        <v>1.9216216802597</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G566" t="n">
-        <v>1.98411345481873</v>
+        <v>1.98411333560944</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G568" t="n">
-        <v>1.9966117143631</v>
+        <v>1.99661183357239</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G569" t="n">
-        <v>1.92005956172943</v>
+        <v>1.92005920410156</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G570" t="n">
-        <v>1.92943322658539</v>
+        <v>1.9294331073761</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G572" t="n">
-        <v>1.92162179946899</v>
+        <v>1.9216216802597</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G575" t="n">
-        <v>2.04660511016846</v>
+        <v>2.04660534858704</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G580" t="n">
-        <v>2.21064591407776</v>
+        <v>2.21064615249634</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G585" t="n">
-        <v>2.19658541679382</v>
+        <v>2.1965856552124</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>3.05599999427795</v>
       </c>
       <c r="G593" t="n">
-        <v>2.3871853351593</v>
+        <v>2.38718557357788</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>3.00399994850159</v>
       </c>
       <c r="G596" t="n">
-        <v>2.34656548500061</v>
+        <v>2.34656572341919</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>3.04200005531311</v>
       </c>
       <c r="G598" t="n">
-        <v>2.37624931335449</v>
+        <v>2.37624955177307</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G603" t="n">
-        <v>2.4653000831604</v>
+        <v>2.46529984474182</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G604" t="n">
-        <v>2.4653000831604</v>
+        <v>2.46529984474182</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>3.17400002479553</v>
       </c>
       <c r="G605" t="n">
-        <v>2.47936081886292</v>
+        <v>2.47936058044434</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>3.26799988746643</v>
       </c>
       <c r="G607" t="n">
-        <v>2.55278825759888</v>
+        <v>2.55278849601746</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G609" t="n">
-        <v>2.54810166358948</v>
+        <v>2.54810190200806</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G610" t="n">
-        <v>2.46373772621155</v>
+        <v>2.46373796463013</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>3.24600005149841</v>
       </c>
       <c r="G611" t="n">
-        <v>2.53560304641724</v>
+        <v>2.53560328483582</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G612" t="n">
-        <v>2.41374444961548</v>
+        <v>2.4137442111969</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>3.0220000743866</v>
       </c>
       <c r="G613" t="n">
-        <v>2.3606264591217</v>
+        <v>2.36062622070312</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>3.09599995613098</v>
       </c>
       <c r="G614" t="n">
-        <v>2.41843104362488</v>
+        <v>2.41843128204346</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G615" t="n">
-        <v>2.42155575752258</v>
+        <v>2.421555519104</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>3.21799993515015</v>
       </c>
       <c r="G623" t="n">
-        <v>2.5137312412262</v>
+        <v>2.51373100280762</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>3.2720000743866</v>
       </c>
       <c r="G626" t="n">
-        <v>2.55591297149658</v>
+        <v>2.55591320991516</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>3.24200010299683</v>
       </c>
       <c r="G628" t="n">
-        <v>2.53247880935669</v>
+        <v>2.53247857093811</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>3.26399993896484</v>
       </c>
       <c r="G629" t="n">
-        <v>2.54966402053833</v>
+        <v>2.54966378211975</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G630" t="n">
-        <v>2.56216216087341</v>
+        <v>2.56216239929199</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G631" t="n">
-        <v>2.5777850151062</v>
+        <v>2.57778525352478</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>3.45199990272522</v>
       </c>
       <c r="G634" t="n">
-        <v>2.69651961326599</v>
+        <v>2.69651937484741</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>3.53600001335144</v>
       </c>
       <c r="G636" t="n">
-        <v>2.76213598251343</v>
+        <v>2.76213574409485</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>3.53200006484985</v>
       </c>
       <c r="G637" t="n">
-        <v>2.7590115070343</v>
+        <v>2.75901126861572</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G640" t="n">
-        <v>2.66151189804077</v>
+        <v>2.66151165962219</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G645" t="n">
-        <v>2.65814280509949</v>
+        <v>2.65814256668091</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G647" t="n">
-        <v>2.59413146972656</v>
+        <v>2.59413170814514</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>3.01399993896484</v>
       </c>
       <c r="G648" t="n">
-        <v>2.53854298591614</v>
+        <v>2.53854322433472</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G651" t="n">
-        <v>2.44926476478577</v>
+        <v>2.44926452636719</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G657" t="n">
-        <v>2.45600247383118</v>
+        <v>2.45600271224976</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G662" t="n">
-        <v>2.47116327285767</v>
+        <v>2.47116303443909</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G666" t="n">
-        <v>2.48800802230835</v>
+        <v>2.48800826072693</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>2.89800000190735</v>
       </c>
       <c r="G668" t="n">
-        <v>2.44084191322327</v>
+        <v>2.44084215164185</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G678" t="n">
-        <v>2.35661697387695</v>
+        <v>2.35661721229553</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>3.22399997711182</v>
       </c>
       <c r="G681" t="n">
-        <v>2.71541571617126</v>
+        <v>2.71541595458984</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G682" t="n">
-        <v>2.57223296165466</v>
+        <v>2.57223320007324</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G688" t="n">
-        <v>2.6109766960144</v>
+        <v>2.61097645759583</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G689" t="n">
-        <v>2.58570909500122</v>
+        <v>2.5857093334198</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G690" t="n">
-        <v>2.57560229301453</v>
+        <v>2.57560205459595</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G691" t="n">
-        <v>2.49306178092957</v>
+        <v>2.49306154251099</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>3.03200006484985</v>
       </c>
       <c r="G695" t="n">
-        <v>2.55370378494263</v>
+        <v>2.55370354652405</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>3.06800007820129</v>
       </c>
       <c r="G699" t="n">
-        <v>2.58402466773987</v>
+        <v>2.58402490615845</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G707" t="n">
-        <v>2.58570909500122</v>
+        <v>2.5857093334198</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G710" t="n">
-        <v>2.50990653038025</v>
+        <v>2.50990676879883</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>3.01399993896484</v>
       </c>
       <c r="G711" t="n">
-        <v>2.53854298591614</v>
+        <v>2.53854322433472</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G712" t="n">
-        <v>2.50990653038025</v>
+        <v>2.50990676879883</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>2.91400003433228</v>
       </c>
       <c r="G714" t="n">
-        <v>2.45431804656982</v>
+        <v>2.4543182849884</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G717" t="n">
-        <v>2.45600247383118</v>
+        <v>2.45600271224976</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G726" t="n">
-        <v>2.44926476478577</v>
+        <v>2.44926452636719</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>2.79200005531311</v>
       </c>
       <c r="G734" t="n">
-        <v>2.3515636920929</v>
+        <v>2.35156345367432</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G735" t="n">
-        <v>2.41389012336731</v>
+        <v>2.41388988494873</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>3.04200005531311</v>
       </c>
       <c r="G742" t="n">
-        <v>2.56212615966797</v>
+        <v>2.56212639808655</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G746" t="n">
-        <v>2.48295474052429</v>
+        <v>2.48295450210571</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>2.49306178092957</v>
+        <v>2.49306154251099</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>3.01399993896484</v>
       </c>
       <c r="G756" t="n">
-        <v>2.53854298591614</v>
+        <v>2.53854322433472</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G759" t="n">
-        <v>2.48295474052429</v>
+        <v>2.48295450210571</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>3.03399991989136</v>
       </c>
       <c r="G762" t="n">
-        <v>2.55538821220398</v>
+        <v>2.5553879737854</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>3.09599995613098</v>
       </c>
       <c r="G766" t="n">
-        <v>2.60760760307312</v>
+        <v>2.6076078414917</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G767" t="n">
-        <v>2.57728672027588</v>
+        <v>2.5772864818573</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G769" t="n">
-        <v>2.57560229301453</v>
+        <v>2.57560205459595</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G770" t="n">
-        <v>2.57223296165466</v>
+        <v>2.57223320007324</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G771" t="n">
-        <v>2.5890781879425</v>
+        <v>2.58907794952393</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G774" t="n">
-        <v>2.67835664749146</v>
+        <v>2.67835688591003</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>3.14199995994568</v>
       </c>
       <c r="G775" t="n">
-        <v>2.64635133743286</v>
+        <v>2.64635109901428</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G778" t="n">
-        <v>2.7171003818512</v>
+        <v>2.71710014343262</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>3.20600008964539</v>
       </c>
       <c r="G779" t="n">
-        <v>2.70025515556335</v>
+        <v>2.70025539398193</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>3.20600008964539</v>
       </c>
       <c r="G783" t="n">
-        <v>2.70025515556335</v>
+        <v>2.70025539398193</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G784" t="n">
-        <v>2.7171003818512</v>
+        <v>2.71710014343262</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G789" t="n">
-        <v>2.84680676460266</v>
+        <v>2.84680700302124</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>3.14199995994568</v>
       </c>
       <c r="G794" t="n">
-        <v>2.64635133743286</v>
+        <v>2.64635109901428</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>3.36800003051758</v>
       </c>
       <c r="G802" t="n">
-        <v>2.83669996261597</v>
+        <v>2.83669972419739</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G805" t="n">
-        <v>2.93776965141296</v>
+        <v>2.93776988983154</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>3.38800001144409</v>
       </c>
       <c r="G814" t="n">
-        <v>2.85354471206665</v>
+        <v>2.85354495048523</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G818" t="n">
-        <v>2.45600247383118</v>
+        <v>2.45600271224976</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>3.00600004196167</v>
       </c>
       <c r="G819" t="n">
-        <v>2.53180503845215</v>
+        <v>2.53180527687073</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G833" t="n">
-        <v>2.69183278083801</v>
+        <v>2.69183301925659</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G834" t="n">
-        <v>2.67835664749146</v>
+        <v>2.67835688591003</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G835" t="n">
-        <v>2.65814280509949</v>
+        <v>2.65814256668091</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G837" t="n">
-        <v>2.67835664749146</v>
+        <v>2.67835688591003</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>3.25</v>
       </c>
       <c r="G839" t="n">
-        <v>2.73731422424316</v>
+        <v>2.73731446266174</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>3.25</v>
       </c>
       <c r="G843" t="n">
-        <v>2.73731422424316</v>
+        <v>2.73731446266174</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>3.33599996566772</v>
       </c>
       <c r="G848" t="n">
-        <v>2.80974769592285</v>
+        <v>2.80974793434143</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G858" t="n">
-        <v>2.79795622825623</v>
+        <v>2.7979564666748</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G861" t="n">
-        <v>2.78784918785095</v>
+        <v>2.78784942626953</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G866" t="n">
-        <v>2.68677949905396</v>
+        <v>2.68677926063538</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G868" t="n">
-        <v>2.65814280509949</v>
+        <v>2.65814256668091</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -31364,6 +31364,32 @@
         <v>2.29999995231628</v>
       </c>
       <c r="H1192" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1193" t="n">
+        <v>3193879</v>
+      </c>
+      <c r="C1193" t="n">
+        <v>2.33599996566772</v>
+      </c>
+      <c r="D1193" t="n">
+        <v>2.26399993896484</v>
+      </c>
+      <c r="E1193" t="n">
+        <v>2.30399990081787</v>
+      </c>
+      <c r="F1193" t="n">
+        <v>2.2739999294281</v>
+      </c>
+      <c r="G1193" t="n">
+        <v>2.2739999294281</v>
+      </c>
+      <c r="H1193" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/MFEA.MI.xlsx
+++ b/data/MFEA.MI.xlsx
@@ -27873,8 +27873,31 @@
       <c r="E1196" t="n">
         <v>2.18799996376038</v>
       </c>
-      <c r="F1196"/>
+      <c r="F1196" t="n">
+        <v>2.16400003433228</v>
+      </c>
       <c r="G1196" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1197" t="n">
+        <v>3178477</v>
+      </c>
+      <c r="C1197" t="n">
+        <v>2.27800011634827</v>
+      </c>
+      <c r="D1197" t="n">
+        <v>2.16400003433228</v>
+      </c>
+      <c r="E1197" t="n">
+        <v>2.17199993133545</v>
+      </c>
+      <c r="F1197"/>
+      <c r="G1197" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MFEA.MI.xlsx
+++ b/data/MFEA.MI.xlsx
@@ -27896,8 +27896,31 @@
       <c r="E1197" t="n">
         <v>2.17199993133545</v>
       </c>
-      <c r="F1197"/>
+      <c r="F1197" t="n">
+        <v>2.25</v>
+      </c>
       <c r="G1197" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1198" t="n">
+        <v>3534185</v>
+      </c>
+      <c r="C1198" t="n">
+        <v>2.24799990653992</v>
+      </c>
+      <c r="D1198" t="n">
+        <v>2.15000009536743</v>
+      </c>
+      <c r="E1198" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="F1198"/>
+      <c r="G1198" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MFEA.MI.xlsx
+++ b/data/MFEA.MI.xlsx
@@ -27919,8 +27919,31 @@
       <c r="E1198" t="n">
         <v>2.24000000953674</v>
       </c>
-      <c r="F1198"/>
+      <c r="F1198" t="n">
+        <v>2.16799998283386</v>
+      </c>
       <c r="G1198" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1199" t="n">
+        <v>1781332</v>
+      </c>
+      <c r="C1199" t="n">
+        <v>2.1800000667572</v>
+      </c>
+      <c r="D1199" t="n">
+        <v>2.13199996948242</v>
+      </c>
+      <c r="E1199" t="n">
+        <v>2.15000009536743</v>
+      </c>
+      <c r="F1199"/>
+      <c r="G1199" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MFEA.MI.xlsx
+++ b/data/MFEA.MI.xlsx
@@ -27942,8 +27942,31 @@
       <c r="E1199" t="n">
         <v>2.15000009536743</v>
       </c>
-      <c r="F1199"/>
+      <c r="F1199" t="n">
+        <v>2.15599989891052</v>
+      </c>
       <c r="G1199" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1200" t="n">
+        <v>3922020</v>
+      </c>
+      <c r="C1200" t="n">
+        <v>2.1800000667572</v>
+      </c>
+      <c r="D1200" t="n">
+        <v>2.10999989509583</v>
+      </c>
+      <c r="E1200" t="n">
+        <v>2.16199994087219</v>
+      </c>
+      <c r="F1200"/>
+      <c r="G1200" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MFEA.MI.xlsx
+++ b/data/MFEA.MI.xlsx
@@ -27972,6 +27972,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1201">
+      <c r="A1201" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1201" t="n">
+        <v>4065405</v>
+      </c>
+      <c r="C1201" t="n">
+        <v>2.14800000190735</v>
+      </c>
+      <c r="D1201" t="n">
+        <v>2.07599997520447</v>
+      </c>
+      <c r="E1201" t="n">
+        <v>2.13199996948242</v>
+      </c>
+      <c r="F1201" t="n">
+        <v>2.08599996566772</v>
+      </c>
+      <c r="G1201" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MFEA.MI.xlsx
+++ b/data/MFEA.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.9375</v>
       </c>
       <c r="G2" t="n">
-        <v>2.42752814292908</v>
+        <v>2.4275279045105</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G3" t="n">
-        <v>2.25027990341187</v>
+        <v>2.25028014183044</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G5" t="n">
-        <v>2.30884909629822</v>
+        <v>2.30884861946106</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G6" t="n">
-        <v>2.28727102279663</v>
+        <v>2.28727078437805</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G9" t="n">
-        <v>2.34892225265503</v>
+        <v>2.34892249107361</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>2.33659195899963</v>
+        <v>2.33659219741821</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G12" t="n">
-        <v>2.29035353660583</v>
+        <v>2.29035329818726</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G13" t="n">
-        <v>2.29343605041504</v>
+        <v>2.29343628883362</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G14" t="n">
-        <v>2.23178458213806</v>
+        <v>2.23178434371948</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G15" t="n">
-        <v>2.3273446559906</v>
+        <v>2.32734441757202</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G17" t="n">
-        <v>2.6941704750061</v>
+        <v>2.69417095184326</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G18" t="n">
-        <v>2.66951012611389</v>
+        <v>2.66951036453247</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G22" t="n">
-        <v>2.5955286026001</v>
+        <v>2.59552836418152</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G24" t="n">
-        <v>2.42598676681519</v>
+        <v>2.42598652839661</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>3.99499988555908</v>
       </c>
       <c r="G25" t="n">
-        <v>2.46297740936279</v>
+        <v>2.46297764778137</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>3.98250007629395</v>
       </c>
       <c r="G27" t="n">
-        <v>2.45527148246765</v>
+        <v>2.45527124404907</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G29" t="n">
-        <v>2.47530794143677</v>
+        <v>2.47530817985535</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G30" t="n">
-        <v>2.41365671157837</v>
+        <v>2.41365623474121</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G31" t="n">
-        <v>2.40440893173218</v>
+        <v>2.4044086933136</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G33" t="n">
-        <v>2.21945428848267</v>
+        <v>2.21945405006409</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G34" t="n">
-        <v>2.29343605041504</v>
+        <v>2.29343628883362</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G35" t="n">
-        <v>2.48455572128296</v>
+        <v>2.48455595970154</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>3.92750000953674</v>
       </c>
       <c r="G36" t="n">
-        <v>2.42136287689209</v>
+        <v>2.42136311531067</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G42" t="n">
-        <v>2.00983905792236</v>
+        <v>2.00983929634094</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G48" t="n">
-        <v>2.03141689300537</v>
+        <v>2.03141713142395</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.17750000953674</v>
       </c>
       <c r="G51" t="n">
-        <v>1.95897674560547</v>
+        <v>1.95897686481476</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G52" t="n">
-        <v>1.99442613124847</v>
+        <v>1.99442625045776</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G53" t="n">
-        <v>1.97593092918396</v>
+        <v>1.97593069076538</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.1175000667572</v>
       </c>
       <c r="G54" t="n">
-        <v>1.92198586463928</v>
+        <v>1.92198574542999</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G55" t="n">
-        <v>1.82796692848206</v>
+        <v>1.82796716690063</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3</v>
       </c>
       <c r="G57" t="n">
-        <v>1.84954500198364</v>
+        <v>1.8495454788208</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G58" t="n">
-        <v>1.82488453388214</v>
+        <v>1.82488477230072</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G59" t="n">
-        <v>1.79405903816223</v>
+        <v>1.79405879974365</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G61" t="n">
-        <v>1.80638909339905</v>
+        <v>1.80638921260834</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G63" t="n">
-        <v>1.81255435943604</v>
+        <v>1.81255447864532</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G64" t="n">
-        <v>1.87728846073151</v>
+        <v>1.87728834152222</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G66" t="n">
-        <v>1.71391177177429</v>
+        <v>1.71391189098358</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G67" t="n">
-        <v>1.69233357906342</v>
+        <v>1.69233381748199</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G68" t="n">
-        <v>1.66150808334351</v>
+        <v>1.6615082025528</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G69" t="n">
-        <v>1.65226054191589</v>
+        <v>1.6522604227066</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.92750000953674</v>
       </c>
       <c r="G70" t="n">
-        <v>1.80484759807587</v>
+        <v>1.80484795570374</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.88750004768372</v>
       </c>
       <c r="G72" t="n">
-        <v>1.78018736839294</v>
+        <v>1.78018724918365</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.75</v>
       </c>
       <c r="G74" t="n">
-        <v>1.69541621208191</v>
+        <v>1.6954163312912</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G75" t="n">
-        <v>1.66150808334351</v>
+        <v>1.6615082025528</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G76" t="n">
-        <v>1.63376486301422</v>
+        <v>1.6337651014328</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G78" t="n">
-        <v>1.74782013893127</v>
+        <v>1.74782037734985</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>2.66750001907349</v>
       </c>
       <c r="G79" t="n">
-        <v>1.64455389976501</v>
+        <v>1.64455413818359</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>2.68249988555908</v>
       </c>
       <c r="G80" t="n">
-        <v>1.65380156040192</v>
+        <v>1.65380167961121</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G81" t="n">
-        <v>1.62143468856812</v>
+        <v>1.62143456935883</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G82" t="n">
-        <v>1.63068234920502</v>
+        <v>1.63068246841431</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G84" t="n">
-        <v>1.56594836711884</v>
+        <v>1.56594824790955</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>2.50250005722046</v>
       </c>
       <c r="G87" t="n">
-        <v>1.54282903671265</v>
+        <v>1.54282891750336</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>2.64750003814697</v>
       </c>
       <c r="G88" t="n">
-        <v>1.63222372531891</v>
+        <v>1.6322238445282</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.65499997138977</v>
       </c>
       <c r="G89" t="n">
-        <v>1.63684749603271</v>
+        <v>1.636847615242</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G90" t="n">
-        <v>1.62143468856812</v>
+        <v>1.62143456935883</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>1.67075598239899</v>
+        <v>1.6707558631897</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>2.66750001907349</v>
       </c>
       <c r="G92" t="n">
-        <v>1.64455389976501</v>
+        <v>1.64455413818359</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G93" t="n">
-        <v>1.63068234920502</v>
+        <v>1.63068246841431</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.6324999332428</v>
       </c>
       <c r="G96" t="n">
-        <v>1.62297594547272</v>
+        <v>1.62297582626343</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G97" t="n">
-        <v>1.57827842235565</v>
+        <v>1.57827854156494</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>1.60602164268494</v>
+        <v>1.60602176189423</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G106" t="n">
-        <v>1.39085793495178</v>
+        <v>1.39085805416107</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>1.33475506305695</v>
+        <v>1.33475518226624</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.14199995994568</v>
       </c>
       <c r="G110" t="n">
-        <v>1.32057535648346</v>
+        <v>1.32057523727417</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.24900007247925</v>
       </c>
       <c r="G112" t="n">
-        <v>1.38654243946075</v>
+        <v>1.38654255867004</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.22300004959106</v>
       </c>
       <c r="G113" t="n">
-        <v>1.3705130815506</v>
+        <v>1.37051296234131</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G115" t="n">
-        <v>1.36558079719543</v>
+        <v>1.36558091640472</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G117" t="n">
-        <v>1.41490209102631</v>
+        <v>1.4149022102356</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G118" t="n">
-        <v>1.34708523750305</v>
+        <v>1.34708547592163</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G120" t="n">
-        <v>1.37236249446869</v>
+        <v>1.37236261367798</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G121" t="n">
-        <v>1.40565431118011</v>
+        <v>1.4056544303894</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.22099995613098</v>
       </c>
       <c r="G122" t="n">
-        <v>1.36927998065948</v>
+        <v>1.3692798614502</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.18300008773804</v>
       </c>
       <c r="G123" t="n">
-        <v>1.34585225582123</v>
+        <v>1.34585249423981</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G126" t="n">
-        <v>1.29344868659973</v>
+        <v>1.29344856739044</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G127" t="n">
-        <v>1.33043956756592</v>
+        <v>1.33043944835663</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G128" t="n">
-        <v>1.35325050354004</v>
+        <v>1.35325062274933</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>1.28543400764465</v>
+        <v>1.28543388843536</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.08400011062622</v>
       </c>
       <c r="G141" t="n">
-        <v>1.2848174571991</v>
+        <v>1.28481733798981</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.125</v>
       </c>
       <c r="G142" t="n">
-        <v>1.31009459495544</v>
+        <v>1.31009435653687</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.19099998474121</v>
       </c>
       <c r="G143" t="n">
-        <v>1.35078454017639</v>
+        <v>1.3507844209671</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>2.30900001525879</v>
       </c>
       <c r="G145" t="n">
-        <v>1.42353308200836</v>
+        <v>1.42353343963623</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G147" t="n">
-        <v>1.35325050354004</v>
+        <v>1.35325062274933</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G148" t="n">
-        <v>1.35633301734924</v>
+        <v>1.35633325576782</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>2.05299997329712</v>
       </c>
       <c r="G152" t="n">
-        <v>1.26570534706116</v>
+        <v>1.26570546627045</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>2.05100011825562</v>
       </c>
       <c r="G158" t="n">
-        <v>1.26447248458862</v>
+        <v>1.26447236537933</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.08899998664856</v>
       </c>
       <c r="G161" t="n">
-        <v>1.2878999710083</v>
+        <v>1.28789985179901</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G164" t="n">
-        <v>1.31625974178314</v>
+        <v>1.31625962257385</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G166" t="n">
-        <v>1.28543400764465</v>
+        <v>1.28543388843536</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G168" t="n">
-        <v>1.24782645702362</v>
+        <v>1.24782633781433</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>1.99899995326996</v>
       </c>
       <c r="G169" t="n">
-        <v>1.23241353034973</v>
+        <v>1.23241364955902</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1.68299996852875</v>
       </c>
       <c r="G172" t="n">
-        <v>1.18590748310089</v>
+        <v>1.18590724468231</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>1.65199995040894</v>
       </c>
       <c r="G173" t="n">
-        <v>1.16406357288361</v>
+        <v>1.16406345367432</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G179" t="n">
-        <v>1.064004778862</v>
+        <v>1.06400489807129</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>1.54700005054474</v>
       </c>
       <c r="G182" t="n">
-        <v>1.09007668495178</v>
+        <v>1.09007656574249</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>1.557000041008</v>
       </c>
       <c r="G183" t="n">
-        <v>1.09712302684784</v>
+        <v>1.09712290763855</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G184" t="n">
-        <v>1.08796262741089</v>
+        <v>1.08796274662018</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G187" t="n">
-        <v>1.04850292205811</v>
+        <v>1.04850280284882</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>1.54200005531311</v>
       </c>
       <c r="G188" t="n">
-        <v>1.08655333518982</v>
+        <v>1.08655345439911</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>1.63699996471405</v>
       </c>
       <c r="G191" t="n">
-        <v>1.15349411964417</v>
+        <v>1.15349400043488</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>1.62300002574921</v>
       </c>
       <c r="G194" t="n">
-        <v>1.14362907409668</v>
+        <v>1.14362919330597</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G195" t="n">
-        <v>1.16265439987183</v>
+        <v>1.16265416145325</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>1.68900001049042</v>
       </c>
       <c r="G196" t="n">
-        <v>1.1901353597641</v>
+        <v>1.19013524055481</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>1.78699994087219</v>
       </c>
       <c r="G198" t="n">
-        <v>1.25918984413147</v>
+        <v>1.25918972492218</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>1.74699997901917</v>
       </c>
       <c r="G204" t="n">
-        <v>1.23100423812866</v>
+        <v>1.23100435733795</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>1.83899998664856</v>
       </c>
       <c r="G207" t="n">
-        <v>1.2958310842514</v>
+        <v>1.29583120346069</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>1.87100005149841</v>
       </c>
       <c r="G211" t="n">
-        <v>1.31837952136993</v>
+        <v>1.31837964057922</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G213" t="n">
-        <v>1.28737545013428</v>
+        <v>1.28737556934357</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>1.87100005149841</v>
       </c>
       <c r="G217" t="n">
-        <v>1.31837952136993</v>
+        <v>1.31837964057922</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>2.01900005340576</v>
       </c>
       <c r="G218" t="n">
-        <v>1.42266619205475</v>
+        <v>1.42266607284546</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>2.04699993133545</v>
       </c>
       <c r="G219" t="n">
-        <v>1.44239604473114</v>
+        <v>1.44239592552185</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.01900005340576</v>
       </c>
       <c r="G220" t="n">
-        <v>1.42266619205475</v>
+        <v>1.42266607284546</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>2.0090000629425</v>
       </c>
       <c r="G222" t="n">
-        <v>1.41561985015869</v>
+        <v>1.4156197309494</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G223" t="n">
-        <v>1.42618918418884</v>
+        <v>1.42618930339813</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>2.02099990844727</v>
       </c>
       <c r="G224" t="n">
-        <v>1.42407548427582</v>
+        <v>1.42407536506653</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>1.98300004005432</v>
       </c>
       <c r="G225" t="n">
-        <v>1.39729928970337</v>
+        <v>1.39729917049408</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>1.93099999427795</v>
       </c>
       <c r="G226" t="n">
-        <v>1.36065793037415</v>
+        <v>1.36065804958344</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G229" t="n">
-        <v>1.32965385913849</v>
+        <v>1.3296537399292</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G230" t="n">
-        <v>1.29442179203033</v>
+        <v>1.29442191123962</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G231" t="n">
-        <v>1.31908416748047</v>
+        <v>1.31908428668976</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>1.86300003528595</v>
       </c>
       <c r="G232" t="n">
-        <v>1.31274235248566</v>
+        <v>1.31274259090424</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G233" t="n">
-        <v>1.27539658546448</v>
+        <v>1.27539646625519</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>1.82099997997284</v>
       </c>
       <c r="G237" t="n">
-        <v>1.28314769268036</v>
+        <v>1.28314757347107</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G241" t="n">
-        <v>1.26482689380646</v>
+        <v>1.26482701301575</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>1.807000041008</v>
       </c>
       <c r="G243" t="n">
-        <v>1.27328276634216</v>
+        <v>1.27328264713287</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G246" t="n">
-        <v>1.36277174949646</v>
+        <v>1.36277186870575</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G247" t="n">
-        <v>1.38109242916107</v>
+        <v>1.38109254837036</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>1.94099998474121</v>
       </c>
       <c r="G249" t="n">
-        <v>1.3677042722702</v>
+        <v>1.36770439147949</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G252" t="n">
-        <v>1.35713469982147</v>
+        <v>1.35713481903076</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>1.95099997520447</v>
       </c>
       <c r="G254" t="n">
-        <v>1.37475061416626</v>
+        <v>1.37475073337555</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>1.98699998855591</v>
       </c>
       <c r="G256" t="n">
-        <v>1.40011763572693</v>
+        <v>1.40011775493622</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G257" t="n">
-        <v>1.37052297592163</v>
+        <v>1.37052285671234</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G258" t="n">
-        <v>1.39236664772034</v>
+        <v>1.39236676692963</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>1.96099996566772</v>
       </c>
       <c r="G260" t="n">
-        <v>1.38179695606232</v>
+        <v>1.3817971944809</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>1.942999958992</v>
       </c>
       <c r="G261" t="n">
-        <v>1.36911356449127</v>
+        <v>1.36911368370056</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>1.97200000286102</v>
       </c>
       <c r="G263" t="n">
-        <v>1.3895480632782</v>
+        <v>1.38954818248749</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G264" t="n">
-        <v>1.40223169326782</v>
+        <v>1.40223157405853</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.01300001144409</v>
       </c>
       <c r="G265" t="n">
-        <v>1.41843831539154</v>
+        <v>1.41843819618225</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G272" t="n">
-        <v>1.5332944393158</v>
+        <v>1.53329455852509</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>2.125</v>
       </c>
       <c r="G273" t="n">
-        <v>1.49735796451569</v>
+        <v>1.4973578453064</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G274" t="n">
-        <v>1.48678827285767</v>
+        <v>1.48678815364838</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.10199999809265</v>
       </c>
       <c r="G275" t="n">
-        <v>1.48115110397339</v>
+        <v>1.48115122318268</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>2.05299997329712</v>
       </c>
       <c r="G286" t="n">
-        <v>1.44662392139435</v>
+        <v>1.44662380218506</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.02099990844727</v>
       </c>
       <c r="G287" t="n">
-        <v>1.42407548427582</v>
+        <v>1.42407536506653</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G288" t="n">
-        <v>1.43182647228241</v>
+        <v>1.4318265914917</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G293" t="n">
-        <v>1.49101614952087</v>
+        <v>1.49101603031158</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G294" t="n">
-        <v>1.46705842018127</v>
+        <v>1.46705830097198</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>2.125</v>
       </c>
       <c r="G296" t="n">
-        <v>1.49735796451569</v>
+        <v>1.4973578453064</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>2.12299990653992</v>
       </c>
       <c r="G297" t="n">
-        <v>1.49594843387604</v>
+        <v>1.49594855308533</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.11299991607666</v>
       </c>
       <c r="G299" t="n">
-        <v>1.48890197277069</v>
+        <v>1.48890209197998</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G300" t="n">
-        <v>1.51215529441833</v>
+        <v>1.51215517520905</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G302" t="n">
-        <v>1.52202033996582</v>
+        <v>1.52202022075653</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>2.05599999427795</v>
       </c>
       <c r="G305" t="n">
-        <v>1.44873785972595</v>
+        <v>1.44873774051666</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>2.12299990653992</v>
       </c>
       <c r="G307" t="n">
-        <v>1.49594843387604</v>
+        <v>1.49594855308533</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G308" t="n">
-        <v>1.49383461475372</v>
+        <v>1.49383449554443</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.1029999256134</v>
       </c>
       <c r="G309" t="n">
-        <v>1.48185563087463</v>
+        <v>1.48185586929321</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G313" t="n">
-        <v>1.61855566501617</v>
+        <v>1.61855578422546</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G315" t="n">
-        <v>1.61855566501617</v>
+        <v>1.61855578422546</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>2.27300000190735</v>
       </c>
       <c r="G316" t="n">
-        <v>1.60164439678192</v>
+        <v>1.6016446352005</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>2.27300000190735</v>
       </c>
       <c r="G317" t="n">
-        <v>1.60164439678192</v>
+        <v>1.6016446352005</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G321" t="n">
-        <v>1.63758087158203</v>
+        <v>1.63758099079132</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.27699995040894</v>
       </c>
       <c r="G322" t="n">
-        <v>1.60446298122406</v>
+        <v>1.60446286201477</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.2590000629425</v>
       </c>
       <c r="G324" t="n">
-        <v>1.59177947044373</v>
+        <v>1.59177958965302</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G327" t="n">
-        <v>1.47128617763519</v>
+        <v>1.47128629684448</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.19899988174438</v>
       </c>
       <c r="G330" t="n">
-        <v>1.5495011806488</v>
+        <v>1.54950106143951</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.25</v>
       </c>
       <c r="G331" t="n">
-        <v>1.58543789386749</v>
+        <v>1.5854377746582</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.25</v>
       </c>
       <c r="G334" t="n">
-        <v>1.58543789386749</v>
+        <v>1.5854377746582</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G335" t="n">
-        <v>1.5769819021225</v>
+        <v>1.57698214054108</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G336" t="n">
-        <v>1.61855566501617</v>
+        <v>1.61855578422546</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.28299999237061</v>
       </c>
       <c r="G337" t="n">
-        <v>1.60869073867798</v>
+        <v>1.60869097709656</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.43099999427795</v>
       </c>
       <c r="G339" t="n">
-        <v>1.71297740936279</v>
+        <v>1.71297752857208</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.40300011634827</v>
       </c>
       <c r="G340" t="n">
-        <v>1.6932475566864</v>
+        <v>1.69324743747711</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G341" t="n">
-        <v>1.65942490100861</v>
+        <v>1.65942478179932</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G344" t="n">
-        <v>1.6629478931427</v>
+        <v>1.66294801235199</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.33699989318848</v>
       </c>
       <c r="G345" t="n">
-        <v>1.64674115180969</v>
+        <v>1.64674127101898</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>2.33699989318848</v>
       </c>
       <c r="G346" t="n">
-        <v>1.64674115180969</v>
+        <v>1.64674127101898</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G347" t="n">
-        <v>1.62912547588348</v>
+        <v>1.62912535667419</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G348" t="n">
-        <v>1.5614800453186</v>
+        <v>1.56148016452789</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G349" t="n">
-        <v>1.55725228786469</v>
+        <v>1.5572521686554</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.19400000572205</v>
       </c>
       <c r="G351" t="n">
-        <v>1.54597806930542</v>
+        <v>1.54597795009613</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G352" t="n">
-        <v>1.56429862976074</v>
+        <v>1.56429851055145</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2.26900005340576</v>
       </c>
       <c r="G354" t="n">
-        <v>1.59882581233978</v>
+        <v>1.59882605075836</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>2.36400008201599</v>
       </c>
       <c r="G355" t="n">
-        <v>1.66576671600342</v>
+        <v>1.66576659679413</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>2.83750009536743</v>
       </c>
       <c r="G357" t="n">
-        <v>1.99941301345825</v>
+        <v>1.99941325187683</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>2.7574999332428</v>
       </c>
       <c r="G358" t="n">
-        <v>1.94304203987122</v>
+        <v>1.94304192066193</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2.69749999046326</v>
       </c>
       <c r="G360" t="n">
-        <v>1.90076351165771</v>
+        <v>1.90076375007629</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>2.65750002861023</v>
       </c>
       <c r="G361" t="n">
-        <v>1.87257814407349</v>
+        <v>1.87257838249207</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G364" t="n">
-        <v>1.79682946205139</v>
+        <v>1.7968293428421</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G365" t="n">
-        <v>1.79330635070801</v>
+        <v>1.79330623149872</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G367" t="n">
-        <v>1.75736963748932</v>
+        <v>1.75736951828003</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G369" t="n">
-        <v>1.80739903450012</v>
+        <v>1.80739915370941</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.5550000667572</v>
       </c>
       <c r="G370" t="n">
-        <v>1.80035269260406</v>
+        <v>1.80035281181335</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G373" t="n">
-        <v>1.88490915298462</v>
+        <v>1.88490927219391</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G374" t="n">
-        <v>1.83910763263702</v>
+        <v>1.83910775184631</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G375" t="n">
-        <v>1.83910763263702</v>
+        <v>1.83910775184631</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G376" t="n">
-        <v>1.86377000808716</v>
+        <v>1.86377024650574</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G377" t="n">
-        <v>1.86377000808716</v>
+        <v>1.86377024650574</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>1.86377000808716</v>
+        <v>1.86377024650574</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>2.59750008583069</v>
       </c>
       <c r="G381" t="n">
-        <v>1.83029997348785</v>
+        <v>1.83029985427856</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>2.61249995231628</v>
       </c>
       <c r="G383" t="n">
-        <v>1.84086918830872</v>
+        <v>1.84086942672729</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.55749988555908</v>
       </c>
       <c r="G384" t="n">
-        <v>1.80211400985718</v>
+        <v>1.80211412906647</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.55250000953674</v>
       </c>
       <c r="G385" t="n">
-        <v>1.79859089851379</v>
+        <v>1.79859101772308</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>2.35700011253357</v>
       </c>
       <c r="G386" t="n">
-        <v>1.8411637544632</v>
+        <v>1.84116363525391</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G387" t="n">
-        <v>1.8060120344162</v>
+        <v>1.80601191520691</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G390" t="n">
-        <v>1.851318359375</v>
+        <v>1.85131824016571</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>2.40700006484985</v>
       </c>
       <c r="G391" t="n">
-        <v>1.88022112846375</v>
+        <v>1.88022089004517</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G394" t="n">
-        <v>1.81694805622101</v>
+        <v>1.81694793701172</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G396" t="n">
-        <v>1.81694805622101</v>
+        <v>1.81694793701172</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>2.3289999961853</v>
       </c>
       <c r="G399" t="n">
-        <v>1.819291472435</v>
+        <v>1.81929135322571</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>2.29900002479553</v>
       </c>
       <c r="G400" t="n">
-        <v>1.79585695266724</v>
+        <v>1.79585707187653</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.34299993515015</v>
       </c>
       <c r="G404" t="n">
-        <v>1.83022749423981</v>
+        <v>1.83022737503052</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G405" t="n">
-        <v>1.85912990570068</v>
+        <v>1.85913014411926</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G406" t="n">
-        <v>1.82944619655609</v>
+        <v>1.82944643497467</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.33899998664856</v>
       </c>
       <c r="G407" t="n">
-        <v>1.82710289955139</v>
+        <v>1.8271027803421</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G408" t="n">
-        <v>1.78257751464844</v>
+        <v>1.78257763385773</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>2.29900002479553</v>
       </c>
       <c r="G410" t="n">
-        <v>1.79585695266724</v>
+        <v>1.79585707187653</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G411" t="n">
-        <v>1.8060120344162</v>
+        <v>1.80601191520691</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.3289999961853</v>
       </c>
       <c r="G412" t="n">
-        <v>1.819291472435</v>
+        <v>1.81929135322571</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G413" t="n">
-        <v>1.82397830486298</v>
+        <v>1.82397842407227</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>2.23699998855591</v>
       </c>
       <c r="G419" t="n">
-        <v>1.74742591381073</v>
+        <v>1.74742603302002</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G422" t="n">
-        <v>1.73024070262909</v>
+        <v>1.7302405834198</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.11299991607666</v>
       </c>
       <c r="G427" t="n">
-        <v>1.65056347846985</v>
+        <v>1.65056359767914</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>2.0789999961853</v>
       </c>
       <c r="G429" t="n">
-        <v>1.62400472164154</v>
+        <v>1.62400460243225</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>2.05299997329712</v>
       </c>
       <c r="G430" t="n">
-        <v>1.60369491577148</v>
+        <v>1.60369479656219</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>1.99899995326996</v>
       </c>
       <c r="G434" t="n">
-        <v>1.56151282787323</v>
+        <v>1.56151294708252</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G438" t="n">
-        <v>1.43887293338776</v>
+        <v>1.43887281417847</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>1.85300004482269</v>
       </c>
       <c r="G447" t="n">
-        <v>1.44746541976929</v>
+        <v>1.44746553897858</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>0.366200000047684</v>
       </c>
       <c r="G450" t="n">
-        <v>0.286056041717529</v>
+        <v>0.286056071519852</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>1.69219994544983</v>
       </c>
       <c r="G455" t="n">
-        <v>1.32185685634613</v>
+        <v>1.32185697555542</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>1.69159996509552</v>
       </c>
       <c r="G457" t="n">
-        <v>1.32138824462891</v>
+        <v>1.3213883638382</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>1.84239995479584</v>
       </c>
       <c r="G459" t="n">
-        <v>1.43918514251709</v>
+        <v>1.43918526172638</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G460" t="n">
-        <v>1.42715561389923</v>
+        <v>1.42715573310852</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>1.93680000305176</v>
       </c>
       <c r="G464" t="n">
-        <v>1.51292550563812</v>
+        <v>1.51292562484741</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>2.02950000762939</v>
       </c>
       <c r="G466" t="n">
-        <v>1.58533799648285</v>
+        <v>1.58533787727356</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G469" t="n">
-        <v>1.58729076385498</v>
+        <v>1.58729088306427</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>2.03949999809265</v>
       </c>
       <c r="G470" t="n">
-        <v>1.59314930438995</v>
+        <v>1.59314942359924</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>2.15249991416931</v>
       </c>
       <c r="G473" t="n">
-        <v>1.68141901493073</v>
+        <v>1.68141889572144</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>2.22699999809265</v>
       </c>
       <c r="G478" t="n">
-        <v>1.73961448669434</v>
+        <v>1.73961460590363</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G480" t="n">
-        <v>1.74664485454559</v>
+        <v>1.7466447353363</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>2.31900000572205</v>
       </c>
       <c r="G482" t="n">
-        <v>1.8114800453186</v>
+        <v>1.81147992610931</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>2.29749989509583</v>
       </c>
       <c r="G483" t="n">
-        <v>1.79468524456024</v>
+        <v>1.79468512535095</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>2.33599996566772</v>
       </c>
       <c r="G484" t="n">
-        <v>1.8247594833374</v>
+        <v>1.82475936412811</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G485" t="n">
-        <v>1.86850345134735</v>
+        <v>1.86850368976593</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.25</v>
       </c>
       <c r="G487" t="n">
-        <v>1.75758099555969</v>
+        <v>1.7575808763504</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.34949994087219</v>
       </c>
       <c r="G489" t="n">
-        <v>1.83530509471893</v>
+        <v>1.83530485630035</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G494" t="n">
-        <v>1.85912990570068</v>
+        <v>1.85913014411926</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>2.375</v>
       </c>
       <c r="G496" t="n">
-        <v>1.85522401332855</v>
+        <v>1.85522425174713</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.3289999961853</v>
       </c>
       <c r="G499" t="n">
-        <v>1.819291472435</v>
+        <v>1.81929135322571</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>2.40199995040894</v>
       </c>
       <c r="G505" t="n">
-        <v>1.87631523609161</v>
+        <v>1.87631499767303</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G507" t="n">
-        <v>1.851318359375</v>
+        <v>1.85131824016571</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.38750004768372</v>
       </c>
       <c r="G508" t="n">
-        <v>1.86498880386353</v>
+        <v>1.86498856544495</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.37949991226196</v>
       </c>
       <c r="G509" t="n">
-        <v>1.85873925685883</v>
+        <v>1.8587394952774</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G514" t="n">
-        <v>1.84819376468658</v>
+        <v>1.84819400310516</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>2.34100008010864</v>
       </c>
       <c r="G517" t="n">
-        <v>1.82866525650024</v>
+        <v>1.82866537570953</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>2.35949993133545</v>
       </c>
       <c r="G518" t="n">
-        <v>1.84311640262604</v>
+        <v>1.84311628341675</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G523" t="n">
-        <v>1.74352037906647</v>
+        <v>1.74352025985718</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>2.1029999256134</v>
       </c>
       <c r="G534" t="n">
-        <v>1.64275205135345</v>
+        <v>1.64275217056274</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.10899996757507</v>
       </c>
       <c r="G535" t="n">
-        <v>1.64743912220001</v>
+        <v>1.64743900299072</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>2.11150002479553</v>
       </c>
       <c r="G538" t="n">
-        <v>1.64939188957214</v>
+        <v>1.64939200878143</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>2.10899996757507</v>
       </c>
       <c r="G540" t="n">
-        <v>1.64743912220001</v>
+        <v>1.64743900299072</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G551" t="n">
-        <v>1.67009222507477</v>
+        <v>1.67009234428406</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G553" t="n">
-        <v>1.74976933002472</v>
+        <v>1.74976944923401</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G555" t="n">
-        <v>1.74352037906647</v>
+        <v>1.74352025985718</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>2.24449992179871</v>
       </c>
       <c r="G556" t="n">
-        <v>1.75328433513641</v>
+        <v>1.75328457355499</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.30550003051758</v>
       </c>
       <c r="G557" t="n">
-        <v>1.80093455314636</v>
+        <v>1.80093443393707</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G560" t="n">
-        <v>1.8786586523056</v>
+        <v>1.87865841388702</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G562" t="n">
-        <v>1.95130503177643</v>
+        <v>1.95130527019501</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G570" t="n">
-        <v>1.9294331073761</v>
+        <v>1.92943334579468</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G574" t="n">
-        <v>2.02785778045654</v>
+        <v>2.02785754203796</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G575" t="n">
-        <v>2.04660534858704</v>
+        <v>2.04660511016846</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G577" t="n">
-        <v>2.12784457206726</v>
+        <v>2.12784433364868</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G585" t="n">
-        <v>2.1965856552124</v>
+        <v>2.19658541679382</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G588" t="n">
-        <v>2.31219506263733</v>
+        <v>2.31219530105591</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G592" t="n">
-        <v>2.43874073028564</v>
+        <v>2.43874096870422</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>3.17400002479553</v>
       </c>
       <c r="G605" t="n">
-        <v>2.47936058044434</v>
+        <v>2.47936081886292</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G608" t="n">
-        <v>2.5465395450592</v>
+        <v>2.54653930664062</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>3.09599995613098</v>
       </c>
       <c r="G614" t="n">
-        <v>2.41843128204346</v>
+        <v>2.41843104362488</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G618" t="n">
-        <v>2.44655251502991</v>
+        <v>2.44655227661133</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G622" t="n">
-        <v>2.52310490608215</v>
+        <v>2.52310514450073</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G627" t="n">
-        <v>2.52310490608215</v>
+        <v>2.52310514450073</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>3.24200010299683</v>
       </c>
       <c r="G628" t="n">
-        <v>2.53247880935669</v>
+        <v>2.53247857093811</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>3.26399993896484</v>
       </c>
       <c r="G629" t="n">
-        <v>2.54966378211975</v>
+        <v>2.54966402053833</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G632" t="n">
-        <v>2.76526045799255</v>
+        <v>2.76526021957397</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>3.53200006484985</v>
       </c>
       <c r="G637" t="n">
-        <v>2.75901126861572</v>
+        <v>2.7590115070343</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>3.44600009918213</v>
       </c>
       <c r="G638" t="n">
-        <v>2.69183278083801</v>
+        <v>2.69183301925659</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -31650,6 +31650,32 @@
         <v>2.08200001716614</v>
       </c>
       <c r="H1203" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1204" t="n">
+        <v>2652899</v>
+      </c>
+      <c r="C1204" t="n">
+        <v>2.1159999370575</v>
+      </c>
+      <c r="D1204" t="n">
+        <v>2.06800007820129</v>
+      </c>
+      <c r="E1204" t="n">
+        <v>2.0699999332428</v>
+      </c>
+      <c r="F1204" t="n">
+        <v>2.10400009155273</v>
+      </c>
+      <c r="G1204" t="n">
+        <v>2.10400009155273</v>
+      </c>
+      <c r="H1204" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/MFEA.MI.xlsx
+++ b/data/MFEA.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.9375</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4275279045105</v>
+        <v>2.42752814292908</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G3" t="n">
-        <v>2.25028014183044</v>
+        <v>2.25028038024902</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>3.71250009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>2.28881239891052</v>
+        <v>2.28881216049194</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G5" t="n">
-        <v>2.30884861946106</v>
+        <v>2.30884909629822</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G6" t="n">
-        <v>2.28727078437805</v>
+        <v>2.28727102279663</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G9" t="n">
-        <v>2.34892249107361</v>
+        <v>2.34892225265503</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G11" t="n">
-        <v>2.31501436233521</v>
+        <v>2.31501412391663</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G12" t="n">
-        <v>2.29035329818726</v>
+        <v>2.29035353660583</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G13" t="n">
-        <v>2.29343628883362</v>
+        <v>2.29343605041504</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6448495388031</v>
+        <v>2.64484977722168</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G17" t="n">
-        <v>2.69417095184326</v>
+        <v>2.69417071342468</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G18" t="n">
-        <v>2.66951036453247</v>
+        <v>2.66951012611389</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4.28249979019165</v>
       </c>
       <c r="G19" t="n">
-        <v>2.64022564888</v>
+        <v>2.64022541046143</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G20" t="n">
-        <v>2.61710643768311</v>
+        <v>2.61710619926453</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G24" t="n">
-        <v>2.42598652839661</v>
+        <v>2.42598676681519</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>3.98250007629395</v>
       </c>
       <c r="G27" t="n">
-        <v>2.45527124404907</v>
+        <v>2.45527148246765</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G29" t="n">
-        <v>2.47530817985535</v>
+        <v>2.47530794143677</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G30" t="n">
-        <v>2.41365623474121</v>
+        <v>2.41365647315979</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G34" t="n">
-        <v>2.29343628883362</v>
+        <v>2.29343605041504</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G35" t="n">
-        <v>2.48455595970154</v>
+        <v>2.48455572128296</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>3.92750000953674</v>
       </c>
       <c r="G36" t="n">
-        <v>2.42136311531067</v>
+        <v>2.42136287689209</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.14249992370605</v>
       </c>
       <c r="G37" t="n">
-        <v>2.55391359329224</v>
+        <v>2.55391383171082</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G38" t="n">
-        <v>2.58936309814453</v>
+        <v>2.58936333656311</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G39" t="n">
-        <v>2.58936309814453</v>
+        <v>2.58936333656311</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.73749995231628</v>
       </c>
       <c r="G40" t="n">
-        <v>2.30422496795654</v>
+        <v>2.30422472953796</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.5</v>
       </c>
       <c r="G41" t="n">
-        <v>2.15780258178711</v>
+        <v>2.15780282020569</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G42" t="n">
-        <v>2.00983929634094</v>
+        <v>2.00983905792236</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>3.3675000667572</v>
       </c>
       <c r="G44" t="n">
-        <v>2.07611465454102</v>
+        <v>2.07611441612244</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.17750000953674</v>
       </c>
       <c r="G51" t="n">
-        <v>1.95897686481476</v>
+        <v>1.95897674560547</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G52" t="n">
-        <v>1.99442625045776</v>
+        <v>1.99442613124847</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G53" t="n">
-        <v>1.97593069076538</v>
+        <v>1.97593057155609</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.1175000667572</v>
       </c>
       <c r="G54" t="n">
-        <v>1.92198574542999</v>
+        <v>1.92198586463928</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G56" t="n">
-        <v>1.85571038722992</v>
+        <v>1.8557106256485</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3</v>
       </c>
       <c r="G57" t="n">
-        <v>1.8495454788208</v>
+        <v>1.84954500198364</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G58" t="n">
-        <v>1.82488477230072</v>
+        <v>1.82488453388214</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G59" t="n">
-        <v>1.79405879974365</v>
+        <v>1.79405891895294</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G63" t="n">
-        <v>1.81255447864532</v>
+        <v>1.81255424022675</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G64" t="n">
-        <v>1.87728834152222</v>
+        <v>1.87728846073151</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.89249992370605</v>
       </c>
       <c r="G65" t="n">
-        <v>1.78326988220215</v>
+        <v>1.78326976299286</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G66" t="n">
-        <v>1.71391189098358</v>
+        <v>1.713911652565</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G68" t="n">
-        <v>1.6615082025528</v>
+        <v>1.66150808334351</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.92750000953674</v>
       </c>
       <c r="G70" t="n">
-        <v>1.80484795570374</v>
+        <v>1.80484783649445</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G75" t="n">
-        <v>1.6615082025528</v>
+        <v>1.66150808334351</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G78" t="n">
-        <v>1.74782037734985</v>
+        <v>1.74782049655914</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>2.66750001907349</v>
       </c>
       <c r="G79" t="n">
-        <v>1.64455413818359</v>
+        <v>1.6445540189743</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>2.68249988555908</v>
       </c>
       <c r="G80" t="n">
-        <v>1.65380167961121</v>
+        <v>1.65380156040192</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G81" t="n">
-        <v>1.62143456935883</v>
+        <v>1.62143468856812</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G83" t="n">
-        <v>1.60910427570343</v>
+        <v>1.60910439491272</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G84" t="n">
-        <v>1.56594824790955</v>
+        <v>1.56594812870026</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>2.58750009536743</v>
       </c>
       <c r="G85" t="n">
-        <v>1.59523284435272</v>
+        <v>1.59523272514343</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G86" t="n">
-        <v>1.58752632141113</v>
+        <v>1.58752620220184</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>2.50250005722046</v>
       </c>
       <c r="G87" t="n">
-        <v>1.54282891750336</v>
+        <v>1.54282903671265</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>2.64750003814697</v>
       </c>
       <c r="G88" t="n">
-        <v>1.6322238445282</v>
+        <v>1.63222372531891</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.65499997138977</v>
       </c>
       <c r="G89" t="n">
-        <v>1.636847615242</v>
+        <v>1.63684737682343</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G90" t="n">
-        <v>1.62143456935883</v>
+        <v>1.62143468856812</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>1.6707558631897</v>
+        <v>1.67075598239899</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>2.66750001907349</v>
       </c>
       <c r="G92" t="n">
-        <v>1.64455413818359</v>
+        <v>1.6445540189743</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G94" t="n">
-        <v>1.63993012905121</v>
+        <v>1.63993000984192</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G95" t="n">
-        <v>1.59985661506653</v>
+        <v>1.59985649585724</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.6324999332428</v>
       </c>
       <c r="G96" t="n">
-        <v>1.62297582626343</v>
+        <v>1.62297606468201</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.45300006866455</v>
       </c>
       <c r="G100" t="n">
-        <v>1.51231145858765</v>
+        <v>1.51231157779694</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G101" t="n">
-        <v>1.4549754858017</v>
+        <v>1.45497536659241</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G102" t="n">
-        <v>1.47716999053955</v>
+        <v>1.47717022895813</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G103" t="n">
-        <v>1.45867455005646</v>
+        <v>1.45867466926575</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.25699996948242</v>
       </c>
       <c r="G105" t="n">
-        <v>1.39147448539734</v>
+        <v>1.39147436618805</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>1.33475518226624</v>
+        <v>1.33475506305695</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G109" t="n">
-        <v>1.31934237480164</v>
+        <v>1.31934225559235</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.24900007247925</v>
       </c>
       <c r="G112" t="n">
-        <v>1.38654255867004</v>
+        <v>1.38654232025146</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.22300004959106</v>
       </c>
       <c r="G113" t="n">
-        <v>1.37051296234131</v>
+        <v>1.3705130815506</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G114" t="n">
-        <v>1.35016798973083</v>
+        <v>1.35016810894012</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G115" t="n">
-        <v>1.36558091640472</v>
+        <v>1.36558079719543</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>2.28900003433228</v>
       </c>
       <c r="G116" t="n">
-        <v>1.41120302677155</v>
+        <v>1.41120290756226</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G117" t="n">
-        <v>1.4149022102356</v>
+        <v>1.41490209102631</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G118" t="n">
-        <v>1.34708547592163</v>
+        <v>1.34708535671234</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G119" t="n">
-        <v>1.38099372386932</v>
+        <v>1.38099384307861</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.22099995613098</v>
       </c>
       <c r="G122" t="n">
-        <v>1.3692798614502</v>
+        <v>1.36927998065948</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G126" t="n">
-        <v>1.29344856739044</v>
+        <v>1.29344868659973</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G128" t="n">
-        <v>1.35325062274933</v>
+        <v>1.35325050354004</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.13700008392334</v>
       </c>
       <c r="G129" t="n">
-        <v>1.31749284267426</v>
+        <v>1.31749272346497</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G132" t="n">
-        <v>1.29468154907227</v>
+        <v>1.29468166828156</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>2.02699995040894</v>
       </c>
       <c r="G133" t="n">
-        <v>1.249675989151</v>
+        <v>1.24967610836029</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G135" t="n">
-        <v>1.35016798973083</v>
+        <v>1.35016810894012</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G139" t="n">
-        <v>1.27002108097076</v>
+        <v>1.27002096176147</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.08400011062622</v>
       </c>
       <c r="G141" t="n">
-        <v>1.28481733798981</v>
+        <v>1.2848174571991</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.125</v>
       </c>
       <c r="G142" t="n">
-        <v>1.31009435653687</v>
+        <v>1.31009459495544</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.19099998474121</v>
       </c>
       <c r="G143" t="n">
-        <v>1.3507844209671</v>
+        <v>1.35078454017639</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>2.30900001525879</v>
       </c>
       <c r="G145" t="n">
-        <v>1.42353343963623</v>
+        <v>1.42353320121765</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G146" t="n">
-        <v>1.4025719165802</v>
+        <v>1.40257179737091</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G147" t="n">
-        <v>1.35325062274933</v>
+        <v>1.35325050354004</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G148" t="n">
-        <v>1.35633325576782</v>
+        <v>1.35633313655853</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>2.05299997329712</v>
       </c>
       <c r="G152" t="n">
-        <v>1.26570546627045</v>
+        <v>1.26570534706116</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G157" t="n">
-        <v>1.30392932891846</v>
+        <v>1.30392944812775</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>2.05100011825562</v>
       </c>
       <c r="G158" t="n">
-        <v>1.26447236537933</v>
+        <v>1.26447248458862</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>2.10199999809265</v>
       </c>
       <c r="G159" t="n">
-        <v>1.29591464996338</v>
+        <v>1.29591476917267</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.08899998664856</v>
       </c>
       <c r="G161" t="n">
-        <v>1.28789985179901</v>
+        <v>1.2878999710083</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G168" t="n">
-        <v>1.24782633781433</v>
+        <v>1.24782645702362</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>1.84899997711182</v>
       </c>
       <c r="G170" t="n">
-        <v>1.30287754535675</v>
+        <v>1.30287742614746</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G171" t="n">
-        <v>1.20140945911407</v>
+        <v>1.20140957832336</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1.68299996852875</v>
       </c>
       <c r="G172" t="n">
-        <v>1.18590724468231</v>
+        <v>1.18590748310089</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>1.43900001049042</v>
       </c>
       <c r="G178" t="n">
-        <v>1.01397562026978</v>
+        <v>1.01397550106049</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G187" t="n">
-        <v>1.04850280284882</v>
+        <v>1.04850292205811</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>1.15913116931915</v>
+        <v>1.15913105010986</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G195" t="n">
-        <v>1.16265416145325</v>
+        <v>1.16265451908112</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>1.64100003242493</v>
       </c>
       <c r="G197" t="n">
-        <v>1.15631258487701</v>
+        <v>1.1563127040863</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>1.78699994087219</v>
       </c>
       <c r="G198" t="n">
-        <v>1.25918972492218</v>
+        <v>1.25918984413147</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>1.78199994564056</v>
       </c>
       <c r="G202" t="n">
-        <v>1.2556666135788</v>
+        <v>1.25566673278809</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G205" t="n">
-        <v>1.30499148368835</v>
+        <v>1.30499136447906</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>1.83899998664856</v>
       </c>
       <c r="G207" t="n">
-        <v>1.29583120346069</v>
+        <v>1.2958310842514</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G212" t="n">
-        <v>1.29371726512909</v>
+        <v>1.2937171459198</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>1.81099998950958</v>
       </c>
       <c r="G214" t="n">
-        <v>1.27610123157501</v>
+        <v>1.27610111236572</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>2.01900005340576</v>
       </c>
       <c r="G218" t="n">
-        <v>1.42266607284546</v>
+        <v>1.42266619205475</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>2.04699993133545</v>
       </c>
       <c r="G219" t="n">
-        <v>1.44239592552185</v>
+        <v>1.44239604473114</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.01900005340576</v>
       </c>
       <c r="G220" t="n">
-        <v>1.42266607284546</v>
+        <v>1.42266619205475</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>2.0090000629425</v>
       </c>
       <c r="G222" t="n">
-        <v>1.4156197309494</v>
+        <v>1.41561985015869</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>2.02099990844727</v>
       </c>
       <c r="G224" t="n">
-        <v>1.42407536506653</v>
+        <v>1.42407548427582</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>1.93099999427795</v>
       </c>
       <c r="G226" t="n">
-        <v>1.36065804958344</v>
+        <v>1.36065793037415</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G227" t="n">
-        <v>1.33035838603973</v>
+        <v>1.33035850524902</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G231" t="n">
-        <v>1.31908428668976</v>
+        <v>1.31908416748047</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G233" t="n">
-        <v>1.27539646625519</v>
+        <v>1.27539658546448</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>1.75899994373322</v>
       </c>
       <c r="G234" t="n">
-        <v>1.23945999145508</v>
+        <v>1.23945987224579</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G240" t="n">
-        <v>1.27891981601715</v>
+        <v>1.27891993522644</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G241" t="n">
-        <v>1.26482701301575</v>
+        <v>1.26482689380646</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>1.81900000572205</v>
       </c>
       <c r="G242" t="n">
-        <v>1.28173828125</v>
+        <v>1.28173840045929</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>1.807000041008</v>
       </c>
       <c r="G243" t="n">
-        <v>1.27328264713287</v>
+        <v>1.27328276634216</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G247" t="n">
-        <v>1.38109254837036</v>
+        <v>1.38109242916107</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G252" t="n">
-        <v>1.35713481903076</v>
+        <v>1.35713469982147</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G253" t="n">
-        <v>1.32824456691742</v>
+        <v>1.32824444770813</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>1.95099997520447</v>
       </c>
       <c r="G254" t="n">
-        <v>1.37475073337555</v>
+        <v>1.37475061416626</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>1.98699998855591</v>
       </c>
       <c r="G256" t="n">
-        <v>1.40011775493622</v>
+        <v>1.40011763572693</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G258" t="n">
-        <v>1.39236676692963</v>
+        <v>1.39236664772034</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>1.96099996566772</v>
       </c>
       <c r="G260" t="n">
-        <v>1.3817971944809</v>
+        <v>1.38179707527161</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>1.942999958992</v>
       </c>
       <c r="G261" t="n">
-        <v>1.36911368370056</v>
+        <v>1.36911356449127</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.00600004196167</v>
       </c>
       <c r="G262" t="n">
-        <v>1.4135057926178</v>
+        <v>1.41350591182709</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>1.97200000286102</v>
       </c>
       <c r="G263" t="n">
-        <v>1.38954818248749</v>
+        <v>1.3895480632782</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.01300001144409</v>
       </c>
       <c r="G265" t="n">
-        <v>1.41843819618225</v>
+        <v>1.41843843460083</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G268" t="n">
-        <v>1.56077539920807</v>
+        <v>1.56077527999878</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>2.20600008964539</v>
       </c>
       <c r="G269" t="n">
-        <v>1.55443370342255</v>
+        <v>1.55443382263184</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G270" t="n">
-        <v>1.55161499977112</v>
+        <v>1.55161511898041</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G272" t="n">
-        <v>1.53329455852509</v>
+        <v>1.5332944393158</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G274" t="n">
-        <v>1.48678815364838</v>
+        <v>1.48678827285767</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G276" t="n">
-        <v>1.48819756507874</v>
+        <v>1.48819744586945</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.07599997520447</v>
       </c>
       <c r="G284" t="n">
-        <v>1.46283054351807</v>
+        <v>1.46283066272736</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G285" t="n">
-        <v>1.46564912796021</v>
+        <v>1.46564900875092</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.02099990844727</v>
       </c>
       <c r="G287" t="n">
-        <v>1.42407536506653</v>
+        <v>1.42407548427582</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G294" t="n">
-        <v>1.46705830097198</v>
+        <v>1.46705853939056</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G295" t="n">
-        <v>1.51074612140656</v>
+        <v>1.51074600219727</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G300" t="n">
-        <v>1.51215517520905</v>
+        <v>1.51215529441833</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G302" t="n">
-        <v>1.52202022075653</v>
+        <v>1.52202033996582</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>2.12100005149841</v>
       </c>
       <c r="G306" t="n">
-        <v>1.49453938007355</v>
+        <v>1.49453926086426</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G308" t="n">
-        <v>1.49383449554443</v>
+        <v>1.49383473396301</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.1029999256134</v>
       </c>
       <c r="G309" t="n">
-        <v>1.48185586929321</v>
+        <v>1.48185575008392</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G313" t="n">
-        <v>1.61855578422546</v>
+        <v>1.61855566501617</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G315" t="n">
-        <v>1.61855578422546</v>
+        <v>1.61855566501617</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>2.27300000190735</v>
       </c>
       <c r="G316" t="n">
-        <v>1.6016446352005</v>
+        <v>1.60164427757263</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>2.27300000190735</v>
       </c>
       <c r="G317" t="n">
-        <v>1.6016446352005</v>
+        <v>1.60164427757263</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G320" t="n">
-        <v>1.62489759922028</v>
+        <v>1.62489748001099</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.27699995040894</v>
       </c>
       <c r="G322" t="n">
-        <v>1.60446286201477</v>
+        <v>1.60446298122406</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.2590000629425</v>
       </c>
       <c r="G324" t="n">
-        <v>1.59177958965302</v>
+        <v>1.59177947044373</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G326" t="n">
-        <v>1.51074612140656</v>
+        <v>1.51074600219727</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.22099995613098</v>
       </c>
       <c r="G332" t="n">
-        <v>1.5650030374527</v>
+        <v>1.56500315666199</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G335" t="n">
-        <v>1.57698214054108</v>
+        <v>1.5769819021225</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G336" t="n">
-        <v>1.61855578422546</v>
+        <v>1.61855566501617</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.28299999237061</v>
       </c>
       <c r="G337" t="n">
-        <v>1.60869097709656</v>
+        <v>1.60869073867798</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.43099999427795</v>
       </c>
       <c r="G339" t="n">
-        <v>1.71297752857208</v>
+        <v>1.71297740936279</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.40300011634827</v>
       </c>
       <c r="G340" t="n">
-        <v>1.69324743747711</v>
+        <v>1.69324767589569</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>1.6453320980072</v>
+        <v>1.64533221721649</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G343" t="n">
-        <v>1.61010015010834</v>
+        <v>1.61010026931763</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G344" t="n">
-        <v>1.66294801235199</v>
+        <v>1.6629478931427</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G347" t="n">
-        <v>1.62912535667419</v>
+        <v>1.62912547588348</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G349" t="n">
-        <v>1.5572521686554</v>
+        <v>1.55725228786469</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G350" t="n">
-        <v>1.55161499977112</v>
+        <v>1.55161511898041</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G352" t="n">
-        <v>1.56429851055145</v>
+        <v>1.56429862976074</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>2.7574999332428</v>
       </c>
       <c r="G358" t="n">
-        <v>1.94304192066193</v>
+        <v>1.94304215908051</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2.69749999046326</v>
       </c>
       <c r="G360" t="n">
-        <v>1.90076375007629</v>
+        <v>1.900763630867</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>2.65750002861023</v>
       </c>
       <c r="G361" t="n">
-        <v>1.87257838249207</v>
+        <v>1.87257814407349</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G362" t="n">
-        <v>1.81444549560547</v>
+        <v>1.81444537639618</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G364" t="n">
-        <v>1.7968293428421</v>
+        <v>1.79682946205139</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G365" t="n">
-        <v>1.79330623149872</v>
+        <v>1.79330635070801</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G367" t="n">
-        <v>1.75736951828003</v>
+        <v>1.75736963748932</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.5550000667572</v>
       </c>
       <c r="G370" t="n">
-        <v>1.80035281181335</v>
+        <v>1.80035269260406</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G371" t="n">
-        <v>1.83206140995026</v>
+        <v>1.83206129074097</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G372" t="n">
-        <v>1.87786293029785</v>
+        <v>1.87786269187927</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G373" t="n">
-        <v>1.88490927219391</v>
+        <v>1.8849093914032</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G376" t="n">
-        <v>1.86377024650574</v>
+        <v>1.86377012729645</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G377" t="n">
-        <v>1.86377024650574</v>
+        <v>1.86377012729645</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2.6324999332428</v>
       </c>
       <c r="G378" t="n">
-        <v>1.85496211051941</v>
+        <v>1.85496199131012</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>2.64249992370605</v>
       </c>
       <c r="G379" t="n">
-        <v>1.86200845241547</v>
+        <v>1.86200869083405</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>1.86377024650574</v>
+        <v>1.86377012729645</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>2.59750008583069</v>
       </c>
       <c r="G381" t="n">
-        <v>1.83029985427856</v>
+        <v>1.83029973506927</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>2.6324999332428</v>
       </c>
       <c r="G382" t="n">
-        <v>1.85496211051941</v>
+        <v>1.85496199131012</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.55250000953674</v>
       </c>
       <c r="G385" t="n">
-        <v>1.79859101772308</v>
+        <v>1.79859113693237</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>2.35700011253357</v>
       </c>
       <c r="G386" t="n">
-        <v>1.84116363525391</v>
+        <v>1.84116351604462</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>2.40700006484985</v>
       </c>
       <c r="G391" t="n">
-        <v>1.88022089004517</v>
+        <v>1.88022112846375</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G392" t="n">
-        <v>1.84741270542145</v>
+        <v>1.84741282463074</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G395" t="n">
-        <v>1.84506928920746</v>
+        <v>1.84506940841675</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>2.30800008773804</v>
       </c>
       <c r="G401" t="n">
-        <v>1.80288743972778</v>
+        <v>1.80288732051849</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G403" t="n">
-        <v>1.84350681304932</v>
+        <v>1.84350693225861</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G405" t="n">
-        <v>1.85913014411926</v>
+        <v>1.85913002490997</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G406" t="n">
-        <v>1.82944643497467</v>
+        <v>1.82944655418396</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.33899998664856</v>
       </c>
       <c r="G407" t="n">
-        <v>1.8271027803421</v>
+        <v>1.82710289955139</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>2.26099991798401</v>
       </c>
       <c r="G418" t="n">
-        <v>1.76617336273193</v>
+        <v>1.76617348194122</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>2.23699998855591</v>
       </c>
       <c r="G419" t="n">
-        <v>1.74742603302002</v>
+        <v>1.74742591381073</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>2.14100003242493</v>
       </c>
       <c r="G424" t="n">
-        <v>1.67243576049805</v>
+        <v>1.67243587970734</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>1.97699999809265</v>
       </c>
       <c r="G433" t="n">
-        <v>1.54432761669159</v>
+        <v>1.54432773590088</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G437" t="n">
-        <v>1.44121623039246</v>
+        <v>1.44121634960175</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G445" t="n">
-        <v>1.48886620998383</v>
+        <v>1.48886632919312</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>1.8309999704361</v>
       </c>
       <c r="G449" t="n">
-        <v>1.43028020858765</v>
+        <v>1.43028008937836</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>0.366200000047684</v>
       </c>
       <c r="G450" t="n">
-        <v>0.286056071519852</v>
+        <v>0.286056041717529</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G452" t="n">
-        <v>1.31232702732086</v>
+        <v>1.31232690811157</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>1.66719996929169</v>
       </c>
       <c r="G454" t="n">
-        <v>1.3023282289505</v>
+        <v>1.30232834815979</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>1.74259996414185</v>
       </c>
       <c r="G458" t="n">
-        <v>1.36122667789459</v>
+        <v>1.36122679710388</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>1.92239999771118</v>
       </c>
       <c r="G465" t="n">
-        <v>1.5016770362854</v>
+        <v>1.50167691707611</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>1.97259998321533</v>
       </c>
       <c r="G468" t="n">
-        <v>1.54089057445526</v>
+        <v>1.54089069366455</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>2.03949999809265</v>
       </c>
       <c r="G470" t="n">
-        <v>1.59314942359924</v>
+        <v>1.59314930438995</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.00850009918213</v>
       </c>
       <c r="G472" t="n">
-        <v>1.56893384456635</v>
+        <v>1.56893396377563</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>2.25650000572205</v>
       </c>
       <c r="G476" t="n">
-        <v>1.76265823841095</v>
+        <v>1.76265835762024</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>2.22699999809265</v>
       </c>
       <c r="G478" t="n">
-        <v>1.73961460590363</v>
+        <v>1.73961448669434</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>2.22300004959106</v>
       </c>
       <c r="G481" t="n">
-        <v>1.73648989200592</v>
+        <v>1.73649001121521</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.34949994087219</v>
       </c>
       <c r="G489" t="n">
-        <v>1.83530485630035</v>
+        <v>1.83530497550964</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>2.39750003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>1.87280011177063</v>
+        <v>1.87280023097992</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.3989999294281</v>
       </c>
       <c r="G492" t="n">
-        <v>1.87397158145905</v>
+        <v>1.87397170066833</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G493" t="n">
-        <v>1.86225461959839</v>
+        <v>1.86225438117981</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G494" t="n">
-        <v>1.85913014411926</v>
+        <v>1.85913002490997</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.38100004196167</v>
       </c>
       <c r="G495" t="n">
-        <v>1.8599112033844</v>
+        <v>1.85991108417511</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>2.375</v>
       </c>
       <c r="G496" t="n">
-        <v>1.85522425174713</v>
+        <v>1.85522413253784</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G502" t="n">
-        <v>1.89662492275238</v>
+        <v>1.89662504196167</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>2.4210000038147</v>
       </c>
       <c r="G503" t="n">
-        <v>1.89115715026855</v>
+        <v>1.89115703105927</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G504" t="n">
-        <v>1.90443646907806</v>
+        <v>1.90443634986877</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.38750004768372</v>
       </c>
       <c r="G508" t="n">
-        <v>1.86498856544495</v>
+        <v>1.86498844623566</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.37949991226196</v>
       </c>
       <c r="G509" t="n">
-        <v>1.8587394952774</v>
+        <v>1.85873937606812</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>2.33949995040894</v>
       </c>
       <c r="G510" t="n">
-        <v>1.82749342918396</v>
+        <v>1.82749330997467</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>2.30800008773804</v>
       </c>
       <c r="G511" t="n">
-        <v>1.80288743972778</v>
+        <v>1.80288732051849</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G514" t="n">
-        <v>1.84819400310516</v>
+        <v>1.84819388389587</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G515" t="n">
-        <v>1.88256430625916</v>
+        <v>1.88256442546844</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>2.38700008392334</v>
       </c>
       <c r="G516" t="n">
-        <v>1.86459803581238</v>
+        <v>1.86459815502167</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>2.34100008010864</v>
       </c>
       <c r="G517" t="n">
-        <v>1.82866537570953</v>
+        <v>1.82866525650024</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G519" t="n">
-        <v>1.84506928920746</v>
+        <v>1.84506940841675</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>2.18650007247925</v>
       </c>
       <c r="G525" t="n">
-        <v>1.70797801017761</v>
+        <v>1.70797789096832</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G530" t="n">
-        <v>1.65603160858154</v>
+        <v>1.65603172779083</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.10899996757507</v>
       </c>
       <c r="G535" t="n">
-        <v>1.64743900299072</v>
+        <v>1.64743912220001</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>2.10899996757507</v>
       </c>
       <c r="G540" t="n">
-        <v>1.64743900299072</v>
+        <v>1.64743912220001</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.10949993133545</v>
       </c>
       <c r="G541" t="n">
-        <v>1.64782965183258</v>
+        <v>1.64782953262329</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>2.12750005722046</v>
       </c>
       <c r="G545" t="n">
-        <v>1.66189050674438</v>
+        <v>1.6618903875351</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.10949993133545</v>
       </c>
       <c r="G547" t="n">
-        <v>1.64782965183258</v>
+        <v>1.64782953262329</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.30550003051758</v>
       </c>
       <c r="G557" t="n">
-        <v>1.80093443393707</v>
+        <v>1.80093455314636</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.42149996757507</v>
       </c>
       <c r="G559" t="n">
-        <v>1.89154756069183</v>
+        <v>1.89154744148254</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G560" t="n">
-        <v>1.87865841388702</v>
+        <v>1.87865853309631</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G561" t="n">
-        <v>1.92630863189697</v>
+        <v>1.92630875110626</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G565" t="n">
-        <v>1.97473990917206</v>
+        <v>1.97473978996277</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G567" t="n">
-        <v>1.97473990917206</v>
+        <v>1.97473978996277</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G568" t="n">
-        <v>1.99661183357239</v>
+        <v>1.99661195278168</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G570" t="n">
-        <v>1.92943334579468</v>
+        <v>1.92943322658539</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G571" t="n">
-        <v>1.93099534511566</v>
+        <v>1.93099522590637</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>2.71799993515015</v>
       </c>
       <c r="G579" t="n">
-        <v>2.1231575012207</v>
+        <v>2.12315773963928</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>2.17940020561218</v>
+        <v>2.1793999671936</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.76200008392334</v>
       </c>
       <c r="G584" t="n">
-        <v>2.15752840042114</v>
+        <v>2.15752816200256</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G586" t="n">
-        <v>2.25751495361328</v>
+        <v>2.25751519203186</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G592" t="n">
-        <v>2.43874096870422</v>
+        <v>2.4387412071228</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>3.11400008201599</v>
       </c>
       <c r="G595" t="n">
-        <v>2.43249201774597</v>
+        <v>2.43249177932739</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>3.00399994850159</v>
       </c>
       <c r="G596" t="n">
-        <v>2.34656572341919</v>
+        <v>2.34656548500061</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>3</v>
       </c>
       <c r="G597" t="n">
-        <v>2.34344100952148</v>
+        <v>2.34344124794006</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>3.10800004005432</v>
       </c>
       <c r="G599" t="n">
-        <v>2.42780518531799</v>
+        <v>2.42780494689941</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>3.05200004577637</v>
       </c>
       <c r="G601" t="n">
-        <v>2.3840606212616</v>
+        <v>2.38406085968018</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G603" t="n">
-        <v>2.46529984474182</v>
+        <v>2.4653000831604</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G604" t="n">
-        <v>2.46529984474182</v>
+        <v>2.4653000831604</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>3.30399990081787</v>
       </c>
       <c r="G606" t="n">
-        <v>2.58090972900391</v>
+        <v>2.58090949058533</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G609" t="n">
-        <v>2.54810166358948</v>
+        <v>2.54810190200806</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G618" t="n">
-        <v>2.44655227661133</v>
+        <v>2.44655251502991</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>3.18799996376038</v>
       </c>
       <c r="G621" t="n">
-        <v>2.49029660224915</v>
+        <v>2.49029684066772</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>3.24799990653992</v>
       </c>
       <c r="G625" t="n">
-        <v>2.53716540336609</v>
+        <v>2.53716564178467</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>3.24200010299683</v>
       </c>
       <c r="G628" t="n">
-        <v>2.53247857093811</v>
+        <v>2.53247880935669</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G632" t="n">
-        <v>2.76526021957397</v>
+        <v>2.76526045799255</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G635" t="n">
-        <v>2.71058011054993</v>
+        <v>2.71058034896851</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>3.53200006484985</v>
       </c>
       <c r="G637" t="n">
-        <v>2.7590115070343</v>
+        <v>2.75901126861572</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>3.44600009918213</v>
       </c>
       <c r="G638" t="n">
-        <v>2.69183301925659</v>
+        <v>2.69183278083801</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G640" t="n">
-        <v>2.66151165962219</v>
+        <v>2.66151189804077</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G645" t="n">
-        <v>2.65814256668091</v>
+        <v>2.65814280509949</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G647" t="n">
-        <v>2.59413170814514</v>
+        <v>2.59413146972656</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>3.01399993896484</v>
       </c>
       <c r="G648" t="n">
-        <v>2.53854322433472</v>
+        <v>2.53854298591614</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G651" t="n">
-        <v>2.44926452636719</v>
+        <v>2.44926476478577</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G657" t="n">
-        <v>2.45600271224976</v>
+        <v>2.45600247383118</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G662" t="n">
-        <v>2.47116303443909</v>
+        <v>2.47116327285767</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G666" t="n">
-        <v>2.48800826072693</v>
+        <v>2.48800802230835</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>2.89800000190735</v>
       </c>
       <c r="G668" t="n">
-        <v>2.44084215164185</v>
+        <v>2.44084191322327</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G678" t="n">
-        <v>2.35661721229553</v>
+        <v>2.35661697387695</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>3.22399997711182</v>
       </c>
       <c r="G681" t="n">
-        <v>2.71541595458984</v>
+        <v>2.71541571617126</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G682" t="n">
-        <v>2.57223320007324</v>
+        <v>2.57223296165466</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G688" t="n">
-        <v>2.61097645759583</v>
+        <v>2.6109766960144</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G689" t="n">
-        <v>2.5857093334198</v>
+        <v>2.58570909500122</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G690" t="n">
-        <v>2.57560205459595</v>
+        <v>2.57560229301453</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G691" t="n">
-        <v>2.49306154251099</v>
+        <v>2.49306178092957</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>3.03200006484985</v>
       </c>
       <c r="G695" t="n">
-        <v>2.55370354652405</v>
+        <v>2.55370378494263</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>3.06800007820129</v>
       </c>
       <c r="G699" t="n">
-        <v>2.58402490615845</v>
+        <v>2.58402466773987</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G707" t="n">
-        <v>2.5857093334198</v>
+        <v>2.58570909500122</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G710" t="n">
-        <v>2.50990676879883</v>
+        <v>2.50990653038025</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>3.01399993896484</v>
       </c>
       <c r="G711" t="n">
-        <v>2.53854322433472</v>
+        <v>2.53854298591614</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G712" t="n">
-        <v>2.50990676879883</v>
+        <v>2.50990653038025</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>2.91400003433228</v>
       </c>
       <c r="G714" t="n">
-        <v>2.4543182849884</v>
+        <v>2.45431804656982</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G717" t="n">
-        <v>2.45600271224976</v>
+        <v>2.45600247383118</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G726" t="n">
-        <v>2.44926452636719</v>
+        <v>2.44926476478577</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>2.79200005531311</v>
       </c>
       <c r="G734" t="n">
-        <v>2.35156345367432</v>
+        <v>2.3515636920929</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G735" t="n">
-        <v>2.41388988494873</v>
+        <v>2.41389012336731</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>3.04200005531311</v>
       </c>
       <c r="G742" t="n">
-        <v>2.56212639808655</v>
+        <v>2.56212615966797</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G746" t="n">
-        <v>2.48295450210571</v>
+        <v>2.48295474052429</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>2.49306154251099</v>
+        <v>2.49306178092957</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>3.01399993896484</v>
       </c>
       <c r="G756" t="n">
-        <v>2.53854322433472</v>
+        <v>2.53854298591614</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G759" t="n">
-        <v>2.48295450210571</v>
+        <v>2.48295474052429</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>3.03399991989136</v>
       </c>
       <c r="G762" t="n">
-        <v>2.5553879737854</v>
+        <v>2.55538821220398</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>3.09599995613098</v>
       </c>
       <c r="G766" t="n">
-        <v>2.6076078414917</v>
+        <v>2.60760760307312</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G767" t="n">
-        <v>2.5772864818573</v>
+        <v>2.57728672027588</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G769" t="n">
-        <v>2.57560205459595</v>
+        <v>2.57560229301453</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G770" t="n">
-        <v>2.57223320007324</v>
+        <v>2.57223296165466</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G771" t="n">
-        <v>2.58907794952393</v>
+        <v>2.5890781879425</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G774" t="n">
-        <v>2.67835688591003</v>
+        <v>2.67835664749146</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>3.14199995994568</v>
       </c>
       <c r="G775" t="n">
-        <v>2.64635109901428</v>
+        <v>2.64635133743286</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G778" t="n">
-        <v>2.71710014343262</v>
+        <v>2.7171003818512</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>3.20600008964539</v>
       </c>
       <c r="G779" t="n">
-        <v>2.70025539398193</v>
+        <v>2.70025515556335</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>3.20600008964539</v>
       </c>
       <c r="G783" t="n">
-        <v>2.70025539398193</v>
+        <v>2.70025515556335</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G784" t="n">
-        <v>2.71710014343262</v>
+        <v>2.7171003818512</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G789" t="n">
-        <v>2.84680700302124</v>
+        <v>2.84680676460266</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>3.14199995994568</v>
       </c>
       <c r="G794" t="n">
-        <v>2.64635109901428</v>
+        <v>2.64635133743286</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>3.36800003051758</v>
       </c>
       <c r="G802" t="n">
-        <v>2.83669972419739</v>
+        <v>2.83669996261597</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G805" t="n">
-        <v>2.93776988983154</v>
+        <v>2.93776965141296</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>3.38800001144409</v>
       </c>
       <c r="G814" t="n">
-        <v>2.85354495048523</v>
+        <v>2.85354471206665</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G818" t="n">
-        <v>2.45600271224976</v>
+        <v>2.45600247383118</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>3.00600004196167</v>
       </c>
       <c r="G819" t="n">
-        <v>2.53180527687073</v>
+        <v>2.53180503845215</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G833" t="n">
-        <v>2.69183301925659</v>
+        <v>2.69183278083801</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G834" t="n">
-        <v>2.67835688591003</v>
+        <v>2.67835664749146</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G835" t="n">
-        <v>2.65814256668091</v>
+        <v>2.65814280509949</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G837" t="n">
-        <v>2.67835688591003</v>
+        <v>2.67835664749146</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>3.25</v>
       </c>
       <c r="G839" t="n">
-        <v>2.73731446266174</v>
+        <v>2.73731422424316</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>3.25</v>
       </c>
       <c r="G843" t="n">
-        <v>2.73731446266174</v>
+        <v>2.73731422424316</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>3.33599996566772</v>
       </c>
       <c r="G848" t="n">
-        <v>2.80974793434143</v>
+        <v>2.80974769592285</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G858" t="n">
-        <v>2.7979564666748</v>
+        <v>2.79795622825623</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G861" t="n">
-        <v>2.78784942626953</v>
+        <v>2.78784918785095</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G866" t="n">
-        <v>2.68677926063538</v>
+        <v>2.68677949905396</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G868" t="n">
-        <v>2.65814256668091</v>
+        <v>2.65814280509949</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -31658,7 +31658,7 @@
         <v>46310.2916666667</v>
       </c>
       <c r="B1204" t="n">
-        <v>2652899</v>
+        <v>2670497</v>
       </c>
       <c r="C1204" t="n">
         <v>2.1159999370575</v>
@@ -31676,6 +31676,32 @@
         <v>2.10400009155273</v>
       </c>
       <c r="H1204" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1205" t="n">
+        <v>1727095</v>
+      </c>
+      <c r="C1205" t="n">
+        <v>2.15599989891052</v>
+      </c>
+      <c r="D1205" t="n">
+        <v>2.10400009155273</v>
+      </c>
+      <c r="E1205" t="n">
+        <v>2.11199998855591</v>
+      </c>
+      <c r="F1205" t="n">
+        <v>2.14400005340576</v>
+      </c>
+      <c r="G1205" t="n">
+        <v>2.14400005340576</v>
+      </c>
+      <c r="H1205" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/MFEA.MI.xlsx
+++ b/data/MFEA.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.9375</v>
       </c>
       <c r="G2" t="n">
-        <v>2.42752838134766</v>
+        <v>2.42752814292908</v>
       </c>
       <c r="H2" t="n">
         <v>437656</v>
@@ -514,7 +514,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G5" t="n">
-        <v>2.30884885787964</v>
+        <v>2.30884909629822</v>
       </c>
       <c r="H5" t="n">
         <v>278466</v>
@@ -543,7 +543,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G6" t="n">
-        <v>2.28727078437805</v>
+        <v>2.28727102279663</v>
       </c>
       <c r="H6" t="n">
         <v>214912</v>
@@ -601,7 +601,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G8" t="n">
-        <v>2.27494072914124</v>
+        <v>2.27494049072266</v>
       </c>
       <c r="H8" t="n">
         <v>174924</v>
@@ -630,7 +630,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G9" t="n">
-        <v>2.34892225265503</v>
+        <v>2.34892249107361</v>
       </c>
       <c r="H9" t="n">
         <v>257244</v>
@@ -746,7 +746,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G13" t="n">
-        <v>2.29343628883362</v>
+        <v>2.29343605041504</v>
       </c>
       <c r="H13" t="n">
         <v>85603</v>
@@ -891,7 +891,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G18" t="n">
-        <v>2.66951012611389</v>
+        <v>2.66951036453247</v>
       </c>
       <c r="H18" t="n">
         <v>629452</v>
@@ -920,7 +920,7 @@
         <v>4.28249979019165</v>
       </c>
       <c r="G19" t="n">
-        <v>2.64022564888</v>
+        <v>2.64022541046143</v>
       </c>
       <c r="H19" t="n">
         <v>318343</v>
@@ -949,7 +949,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G20" t="n">
-        <v>2.61710667610168</v>
+        <v>2.61710643768311</v>
       </c>
       <c r="H20" t="n">
         <v>162925</v>
@@ -978,7 +978,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G21" t="n">
-        <v>2.64793229103088</v>
+        <v>2.64793252944946</v>
       </c>
       <c r="H21" t="n">
         <v>296725</v>
@@ -1007,7 +1007,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G22" t="n">
-        <v>2.59552836418152</v>
+        <v>2.5955286026001</v>
       </c>
       <c r="H22" t="n">
         <v>210917</v>
@@ -1297,7 +1297,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G32" t="n">
-        <v>2.25336241722107</v>
+        <v>2.25336265563965</v>
       </c>
       <c r="H32" t="n">
         <v>156121</v>
@@ -1326,7 +1326,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G33" t="n">
-        <v>2.21945405006409</v>
+        <v>2.21945428848267</v>
       </c>
       <c r="H33" t="n">
         <v>419876</v>
@@ -1355,7 +1355,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G34" t="n">
-        <v>2.29343628883362</v>
+        <v>2.29343605041504</v>
       </c>
       <c r="H34" t="n">
         <v>612514</v>
@@ -1384,7 +1384,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G35" t="n">
-        <v>2.48455595970154</v>
+        <v>2.48455572128296</v>
       </c>
       <c r="H35" t="n">
         <v>267519</v>
@@ -1471,7 +1471,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G38" t="n">
-        <v>2.58936333656311</v>
+        <v>2.58936309814453</v>
       </c>
       <c r="H38" t="n">
         <v>208860</v>
@@ -1500,7 +1500,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G39" t="n">
-        <v>2.58936333656311</v>
+        <v>2.58936309814453</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -1558,7 +1558,7 @@
         <v>3.5</v>
       </c>
       <c r="G41" t="n">
-        <v>2.15780282020569</v>
+        <v>2.15780258178711</v>
       </c>
       <c r="H41" t="n">
         <v>1105386</v>
@@ -1616,7 +1616,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G43" t="n">
-        <v>2.03450012207031</v>
+        <v>2.03449964523315</v>
       </c>
       <c r="H43" t="n">
         <v>404535</v>
@@ -1645,7 +1645,7 @@
         <v>3.3675000667572</v>
       </c>
       <c r="G44" t="n">
-        <v>2.07611441612244</v>
+        <v>2.07611465454102</v>
       </c>
       <c r="H44" t="n">
         <v>214683</v>
@@ -1703,7 +1703,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G46" t="n">
-        <v>2.02525186538696</v>
+        <v>2.02525210380554</v>
       </c>
       <c r="H46" t="n">
         <v>426915</v>
@@ -1819,7 +1819,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G50" t="n">
-        <v>2.02525186538696</v>
+        <v>2.02525210380554</v>
       </c>
       <c r="H50" t="n">
         <v>165272</v>
@@ -1848,7 +1848,7 @@
         <v>3.17750000953674</v>
       </c>
       <c r="G51" t="n">
-        <v>1.95897686481476</v>
+        <v>1.95897650718689</v>
       </c>
       <c r="H51" t="n">
         <v>400267</v>
@@ -1877,7 +1877,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G52" t="n">
-        <v>1.99442601203918</v>
+        <v>1.99442625045776</v>
       </c>
       <c r="H52" t="n">
         <v>186459</v>
@@ -1906,7 +1906,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G53" t="n">
-        <v>1.97593092918396</v>
+        <v>1.97593069076538</v>
       </c>
       <c r="H53" t="n">
         <v>157204</v>
@@ -1935,7 +1935,7 @@
         <v>3.1175000667572</v>
       </c>
       <c r="G54" t="n">
-        <v>1.92198574542999</v>
+        <v>1.9219856262207</v>
       </c>
       <c r="H54" t="n">
         <v>195501</v>
@@ -1964,7 +1964,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G55" t="n">
-        <v>1.82796704769135</v>
+        <v>1.82796692848206</v>
       </c>
       <c r="H55" t="n">
         <v>452826</v>
@@ -2051,7 +2051,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G58" t="n">
-        <v>1.82488465309143</v>
+        <v>1.82488453388214</v>
       </c>
       <c r="H58" t="n">
         <v>168347</v>
@@ -2080,7 +2080,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G59" t="n">
-        <v>1.79405891895294</v>
+        <v>1.79405903816223</v>
       </c>
       <c r="H59" t="n">
         <v>174796</v>
@@ -2109,7 +2109,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G60" t="n">
-        <v>1.79714143276215</v>
+        <v>1.79714131355286</v>
       </c>
       <c r="H60" t="n">
         <v>140935</v>
@@ -2138,7 +2138,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G61" t="n">
-        <v>1.80638909339905</v>
+        <v>1.80638921260834</v>
       </c>
       <c r="H61" t="n">
         <v>175025</v>
@@ -2196,7 +2196,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G63" t="n">
-        <v>1.81255447864532</v>
+        <v>1.81255435943604</v>
       </c>
       <c r="H63" t="n">
         <v>134826</v>
@@ -2225,7 +2225,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G64" t="n">
-        <v>1.87728834152222</v>
+        <v>1.87728822231293</v>
       </c>
       <c r="H64" t="n">
         <v>324711</v>
@@ -2254,7 +2254,7 @@
         <v>2.89249992370605</v>
       </c>
       <c r="G65" t="n">
-        <v>1.78326988220215</v>
+        <v>1.78327000141144</v>
       </c>
       <c r="H65" t="n">
         <v>336035</v>
@@ -2283,7 +2283,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G66" t="n">
-        <v>1.71391201019287</v>
+        <v>1.713911652565</v>
       </c>
       <c r="H66" t="n">
         <v>344735</v>
@@ -2312,7 +2312,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G67" t="n">
-        <v>1.69233357906342</v>
+        <v>1.69233381748199</v>
       </c>
       <c r="H67" t="n">
         <v>293953</v>
@@ -2341,7 +2341,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G68" t="n">
-        <v>1.66150808334351</v>
+        <v>1.66150796413422</v>
       </c>
       <c r="H68" t="n">
         <v>213075</v>
@@ -2399,7 +2399,7 @@
         <v>2.92750000953674</v>
       </c>
       <c r="G70" t="n">
-        <v>1.80484771728516</v>
+        <v>1.80484783649445</v>
       </c>
       <c r="H70" t="n">
         <v>1271038</v>
@@ -2457,7 +2457,7 @@
         <v>2.88750004768372</v>
       </c>
       <c r="G72" t="n">
-        <v>1.78018736839294</v>
+        <v>1.78018724918365</v>
       </c>
       <c r="H72" t="n">
         <v>202748</v>
@@ -2515,7 +2515,7 @@
         <v>2.75</v>
       </c>
       <c r="G74" t="n">
-        <v>1.6954163312912</v>
+        <v>1.69541656970978</v>
       </c>
       <c r="H74" t="n">
         <v>168732</v>
@@ -2544,7 +2544,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G75" t="n">
-        <v>1.66150808334351</v>
+        <v>1.66150796413422</v>
       </c>
       <c r="H75" t="n">
         <v>331684</v>
@@ -2573,7 +2573,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G76" t="n">
-        <v>1.63376486301422</v>
+        <v>1.6337651014328</v>
       </c>
       <c r="H76" t="n">
         <v>246997</v>
@@ -2602,7 +2602,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>1.64917778968811</v>
+        <v>1.64917767047882</v>
       </c>
       <c r="H77" t="n">
         <v>209971</v>
@@ -2631,7 +2631,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G78" t="n">
-        <v>1.74782013893127</v>
+        <v>1.74782025814056</v>
       </c>
       <c r="H78" t="n">
         <v>522442</v>
@@ -2660,7 +2660,7 @@
         <v>2.66750001907349</v>
       </c>
       <c r="G79" t="n">
-        <v>1.64455413818359</v>
+        <v>1.64455389976501</v>
       </c>
       <c r="H79" t="n">
         <v>468659</v>
@@ -2689,7 +2689,7 @@
         <v>2.68249988555908</v>
       </c>
       <c r="G80" t="n">
-        <v>1.65380144119263</v>
+        <v>1.65380156040192</v>
       </c>
       <c r="H80" t="n">
         <v>289746</v>
@@ -2718,7 +2718,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G81" t="n">
-        <v>1.6214348077774</v>
+        <v>1.62143468856812</v>
       </c>
       <c r="H81" t="n">
         <v>237552</v>
@@ -2805,7 +2805,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G84" t="n">
-        <v>1.56594824790955</v>
+        <v>1.56594812870026</v>
       </c>
       <c r="H84" t="n">
         <v>392657</v>
@@ -2863,7 +2863,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G86" t="n">
-        <v>1.58752632141113</v>
+        <v>1.58752620220184</v>
       </c>
       <c r="H86" t="n">
         <v>329995</v>
@@ -2892,7 +2892,7 @@
         <v>2.50250005722046</v>
       </c>
       <c r="G87" t="n">
-        <v>1.54282891750336</v>
+        <v>1.54282903671265</v>
       </c>
       <c r="H87" t="n">
         <v>224920</v>
@@ -2921,7 +2921,7 @@
         <v>2.64750003814697</v>
       </c>
       <c r="G88" t="n">
-        <v>1.63222360610962</v>
+        <v>1.6322238445282</v>
       </c>
       <c r="H88" t="n">
         <v>842562</v>
@@ -2950,7 +2950,7 @@
         <v>2.65499997138977</v>
       </c>
       <c r="G89" t="n">
-        <v>1.63684749603271</v>
+        <v>1.636847615242</v>
       </c>
       <c r="H89" t="n">
         <v>285515</v>
@@ -2979,7 +2979,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G90" t="n">
-        <v>1.6214348077774</v>
+        <v>1.62143468856812</v>
       </c>
       <c r="H90" t="n">
         <v>381738</v>
@@ -3037,7 +3037,7 @@
         <v>2.66750001907349</v>
       </c>
       <c r="G92" t="n">
-        <v>1.64455413818359</v>
+        <v>1.64455389976501</v>
       </c>
       <c r="H92" t="n">
         <v>384701</v>
@@ -3095,7 +3095,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G94" t="n">
-        <v>1.63993000984192</v>
+        <v>1.63993012905121</v>
       </c>
       <c r="H94" t="n">
         <v>124415</v>
@@ -3153,7 +3153,7 @@
         <v>2.6324999332428</v>
       </c>
       <c r="G96" t="n">
-        <v>1.62297594547272</v>
+        <v>1.62297570705414</v>
       </c>
       <c r="H96" t="n">
         <v>316690</v>
@@ -3182,7 +3182,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G97" t="n">
-        <v>1.57827842235565</v>
+        <v>1.57827854156494</v>
       </c>
       <c r="H97" t="n">
         <v>975446</v>
@@ -3240,7 +3240,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>1.60602164268494</v>
+        <v>1.60602188110352</v>
       </c>
       <c r="H99" t="n">
         <v>524697</v>
@@ -3298,7 +3298,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G101" t="n">
-        <v>1.45497560501099</v>
+        <v>1.4549754858017</v>
       </c>
       <c r="H101" t="n">
         <v>241430</v>
@@ -3356,7 +3356,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G103" t="n">
-        <v>1.45867455005646</v>
+        <v>1.45867466926575</v>
       </c>
       <c r="H103" t="n">
         <v>277983</v>
@@ -3414,7 +3414,7 @@
         <v>2.25699996948242</v>
       </c>
       <c r="G105" t="n">
-        <v>1.39147436618805</v>
+        <v>1.39147448539734</v>
       </c>
       <c r="H105" t="n">
         <v>153134</v>
@@ -3443,7 +3443,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G106" t="n">
-        <v>1.39085805416107</v>
+        <v>1.39085793495178</v>
       </c>
       <c r="H106" t="n">
         <v>262719</v>
@@ -3472,7 +3472,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>1.33475506305695</v>
+        <v>1.33475518226624</v>
       </c>
       <c r="H107" t="n">
         <v>364496</v>
@@ -3617,7 +3617,7 @@
         <v>2.24900007247925</v>
       </c>
       <c r="G112" t="n">
-        <v>1.38654255867004</v>
+        <v>1.38654243946075</v>
       </c>
       <c r="H112" t="n">
         <v>617377</v>
@@ -3646,7 +3646,7 @@
         <v>2.22300004959106</v>
       </c>
       <c r="G113" t="n">
-        <v>1.37051296234131</v>
+        <v>1.3705130815506</v>
       </c>
       <c r="H113" t="n">
         <v>671913</v>
@@ -3675,7 +3675,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G114" t="n">
-        <v>1.35016798973083</v>
+        <v>1.35016810894012</v>
       </c>
       <c r="H114" t="n">
         <v>374071</v>
@@ -3704,7 +3704,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G115" t="n">
-        <v>1.36558091640472</v>
+        <v>1.36558079719543</v>
       </c>
       <c r="H115" t="n">
         <v>684447</v>
@@ -3733,7 +3733,7 @@
         <v>2.28900003433228</v>
       </c>
       <c r="G116" t="n">
-        <v>1.41120290756226</v>
+        <v>1.41120314598083</v>
       </c>
       <c r="H116" t="n">
         <v>1034023</v>
@@ -3907,7 +3907,7 @@
         <v>2.22099995613098</v>
       </c>
       <c r="G122" t="n">
-        <v>1.36927998065948</v>
+        <v>1.36928009986877</v>
       </c>
       <c r="H122" t="n">
         <v>2110801</v>
@@ -4023,7 +4023,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G126" t="n">
-        <v>1.29344868659973</v>
+        <v>1.29344856739044</v>
       </c>
       <c r="H126" t="n">
         <v>553530</v>
@@ -4052,7 +4052,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G127" t="n">
-        <v>1.33043944835663</v>
+        <v>1.33043956756592</v>
       </c>
       <c r="H127" t="n">
         <v>576146</v>
@@ -4081,7 +4081,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G128" t="n">
-        <v>1.35325062274933</v>
+        <v>1.35325050354004</v>
       </c>
       <c r="H128" t="n">
         <v>1234804</v>
@@ -4139,7 +4139,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G130" t="n">
-        <v>1.37791097164154</v>
+        <v>1.37791121006012</v>
       </c>
       <c r="H130" t="n">
         <v>658168</v>
@@ -4168,7 +4168,7 @@
         <v>2.21399998664856</v>
       </c>
       <c r="G131" t="n">
-        <v>1.36496424674988</v>
+        <v>1.36496436595917</v>
       </c>
       <c r="H131" t="n">
         <v>425795</v>
@@ -4197,7 +4197,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G132" t="n">
-        <v>1.29468166828156</v>
+        <v>1.29468154907227</v>
       </c>
       <c r="H132" t="n">
         <v>903030</v>
@@ -4226,7 +4226,7 @@
         <v>2.02699995040894</v>
       </c>
       <c r="G133" t="n">
-        <v>1.249675989151</v>
+        <v>1.24967610836029</v>
       </c>
       <c r="H133" t="n">
         <v>1799201</v>
@@ -4255,7 +4255,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>1.28543400764465</v>
+        <v>1.28543376922607</v>
       </c>
       <c r="H134" t="n">
         <v>1315577</v>
@@ -4284,7 +4284,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G135" t="n">
-        <v>1.35016798973083</v>
+        <v>1.35016810894012</v>
       </c>
       <c r="H135" t="n">
         <v>888081</v>
@@ -4313,7 +4313,7 @@
         <v>2.20099997520447</v>
       </c>
       <c r="G136" t="n">
-        <v>1.35694968700409</v>
+        <v>1.3569495677948</v>
       </c>
       <c r="H136" t="n">
         <v>597261</v>
@@ -4400,7 +4400,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G139" t="n">
-        <v>1.27002108097076</v>
+        <v>1.27002096176147</v>
       </c>
       <c r="H139" t="n">
         <v>1000781</v>
@@ -4603,7 +4603,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G146" t="n">
-        <v>1.4025719165802</v>
+        <v>1.40257179737091</v>
       </c>
       <c r="H146" t="n">
         <v>463835</v>
@@ -4632,7 +4632,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G147" t="n">
-        <v>1.35325062274933</v>
+        <v>1.35325050354004</v>
       </c>
       <c r="H147" t="n">
         <v>729575</v>
@@ -4661,7 +4661,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G148" t="n">
-        <v>1.35633301734924</v>
+        <v>1.35633325576782</v>
       </c>
       <c r="H148" t="n">
         <v>470520</v>
@@ -4719,7 +4719,7 @@
         <v>2.04699993133545</v>
       </c>
       <c r="G150" t="n">
-        <v>1.26200616359711</v>
+        <v>1.26200640201569</v>
       </c>
       <c r="H150" t="n">
         <v>1302379</v>
@@ -4748,7 +4748,7 @@
         <v>2.07100009918213</v>
       </c>
       <c r="G151" t="n">
-        <v>1.27680265903473</v>
+        <v>1.27680277824402</v>
       </c>
       <c r="H151" t="n">
         <v>802560</v>
@@ -4777,7 +4777,7 @@
         <v>2.05299997329712</v>
       </c>
       <c r="G152" t="n">
-        <v>1.26570546627045</v>
+        <v>1.26570534706116</v>
       </c>
       <c r="H152" t="n">
         <v>460461</v>
@@ -4806,7 +4806,7 @@
         <v>2.02099990844727</v>
       </c>
       <c r="G153" t="n">
-        <v>1.24597692489624</v>
+        <v>1.24597680568695</v>
       </c>
       <c r="H153" t="n">
         <v>550560</v>
@@ -4864,7 +4864,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G155" t="n">
-        <v>1.28235137462616</v>
+        <v>1.28235125541687</v>
       </c>
       <c r="H155" t="n">
         <v>897371</v>
@@ -4922,7 +4922,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G157" t="n">
-        <v>1.30392920970917</v>
+        <v>1.30392932891846</v>
       </c>
       <c r="H157" t="n">
         <v>621284</v>
@@ -5038,7 +5038,7 @@
         <v>2.08899998664856</v>
       </c>
       <c r="G161" t="n">
-        <v>1.2878999710083</v>
+        <v>1.28789985179901</v>
       </c>
       <c r="H161" t="n">
         <v>544349</v>
@@ -5067,7 +5067,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G162" t="n">
-        <v>1.28235137462616</v>
+        <v>1.28235125541687</v>
       </c>
       <c r="H162" t="n">
         <v>320464</v>
@@ -5096,7 +5096,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G163" t="n">
-        <v>1.28235137462616</v>
+        <v>1.28235125541687</v>
       </c>
       <c r="H163" t="n">
         <v>665085</v>
@@ -5125,7 +5125,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G164" t="n">
-        <v>1.31625962257385</v>
+        <v>1.31625974178314</v>
       </c>
       <c r="H164" t="n">
         <v>1321946</v>
@@ -5183,7 +5183,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G166" t="n">
-        <v>1.28543400764465</v>
+        <v>1.28543376922607</v>
       </c>
       <c r="H166" t="n">
         <v>925875</v>
@@ -5241,7 +5241,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G168" t="n">
-        <v>1.24782645702362</v>
+        <v>1.24782657623291</v>
       </c>
       <c r="H168" t="n">
         <v>1017897</v>
@@ -5270,7 +5270,7 @@
         <v>1.99899995326996</v>
       </c>
       <c r="G169" t="n">
-        <v>1.23241364955902</v>
+        <v>1.23241353034973</v>
       </c>
       <c r="H169" t="n">
         <v>2003498</v>
@@ -5299,7 +5299,7 @@
         <v>1.84899997711182</v>
       </c>
       <c r="G170" t="n">
-        <v>1.30287754535675</v>
+        <v>1.30287742614746</v>
       </c>
       <c r="H170" t="n">
         <v>1744533</v>
@@ -5357,7 +5357,7 @@
         <v>1.68299996852875</v>
       </c>
       <c r="G172" t="n">
-        <v>1.18590724468231</v>
+        <v>1.18590748310089</v>
       </c>
       <c r="H172" t="n">
         <v>1157709</v>
@@ -5386,7 +5386,7 @@
         <v>1.65199995040894</v>
       </c>
       <c r="G173" t="n">
-        <v>1.16406345367432</v>
+        <v>1.16406357288361</v>
       </c>
       <c r="H173" t="n">
         <v>1205156</v>
@@ -5415,7 +5415,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G174" t="n">
-        <v>1.14151513576508</v>
+        <v>1.14151525497437</v>
       </c>
       <c r="H174" t="n">
         <v>1315279</v>
@@ -5473,7 +5473,7 @@
         <v>1.53900003433228</v>
       </c>
       <c r="G176" t="n">
-        <v>1.08443939685822</v>
+        <v>1.0844395160675</v>
       </c>
       <c r="H176" t="n">
         <v>1625041</v>
@@ -5502,7 +5502,7 @@
         <v>1.4889999628067</v>
       </c>
       <c r="G177" t="n">
-        <v>1.04920732975006</v>
+        <v>1.04920744895935</v>
       </c>
       <c r="H177" t="n">
         <v>2864868</v>
@@ -5531,7 +5531,7 @@
         <v>1.43900001049042</v>
       </c>
       <c r="G178" t="n">
-        <v>1.01397562026978</v>
+        <v>1.01397550106049</v>
       </c>
       <c r="H178" t="n">
         <v>1366037</v>
@@ -5589,7 +5589,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G180" t="n">
-        <v>1.08514416217804</v>
+        <v>1.08514404296875</v>
       </c>
       <c r="H180" t="n">
         <v>1913773</v>
@@ -5705,7 +5705,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G184" t="n">
-        <v>1.08796274662018</v>
+        <v>1.08796262741089</v>
       </c>
       <c r="H184" t="n">
         <v>1603167</v>
@@ -5734,7 +5734,7 @@
         <v>1.50899994373322</v>
       </c>
       <c r="G185" t="n">
-        <v>1.06330037117004</v>
+        <v>1.06330013275146</v>
       </c>
       <c r="H185" t="n">
         <v>762123</v>
@@ -5763,7 +5763,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G186" t="n">
-        <v>1.06752812862396</v>
+        <v>1.06752800941467</v>
       </c>
       <c r="H186" t="n">
         <v>688465</v>
@@ -5792,7 +5792,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G187" t="n">
-        <v>1.04850280284882</v>
+        <v>1.04850292205811</v>
       </c>
       <c r="H187" t="n">
         <v>343484</v>
@@ -5821,7 +5821,7 @@
         <v>1.54200005531311</v>
       </c>
       <c r="G188" t="n">
-        <v>1.08655333518982</v>
+        <v>1.08655345439911</v>
       </c>
       <c r="H188" t="n">
         <v>1596742</v>
@@ -5850,7 +5850,7 @@
         <v>1.5110000371933</v>
       </c>
       <c r="G189" t="n">
-        <v>1.06470942497253</v>
+        <v>1.06470954418182</v>
       </c>
       <c r="H189" t="n">
         <v>1590572</v>
@@ -5879,7 +5879,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G190" t="n">
-        <v>1.11473882198334</v>
+        <v>1.11473894119263</v>
       </c>
       <c r="H190" t="n">
         <v>1164166</v>
@@ -5995,7 +5995,7 @@
         <v>1.62300002574921</v>
       </c>
       <c r="G194" t="n">
-        <v>1.14362919330597</v>
+        <v>1.14362895488739</v>
       </c>
       <c r="H194" t="n">
         <v>1339210</v>
@@ -6024,7 +6024,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G195" t="n">
-        <v>1.16265439987183</v>
+        <v>1.16265428066254</v>
       </c>
       <c r="H195" t="n">
         <v>1118932</v>
@@ -6053,7 +6053,7 @@
         <v>1.68900001049042</v>
       </c>
       <c r="G196" t="n">
-        <v>1.1901353597641</v>
+        <v>1.19013524055481</v>
       </c>
       <c r="H196" t="n">
         <v>693474</v>
@@ -6082,7 +6082,7 @@
         <v>1.64100003242493</v>
       </c>
       <c r="G197" t="n">
-        <v>1.15631258487701</v>
+        <v>1.1563127040863</v>
       </c>
       <c r="H197" t="n">
         <v>2056453</v>
@@ -6111,7 +6111,7 @@
         <v>1.78699994087219</v>
       </c>
       <c r="G198" t="n">
-        <v>1.25918972492218</v>
+        <v>1.25918984413147</v>
       </c>
       <c r="H198" t="n">
         <v>1728258</v>
@@ -6227,7 +6227,7 @@
         <v>1.78199994564056</v>
       </c>
       <c r="G202" t="n">
-        <v>1.2556666135788</v>
+        <v>1.25566673278809</v>
       </c>
       <c r="H202" t="n">
         <v>682872</v>
@@ -6256,7 +6256,7 @@
         <v>1.74600005149841</v>
       </c>
       <c r="G203" t="n">
-        <v>1.23029983043671</v>
+        <v>1.23029971122742</v>
       </c>
       <c r="H203" t="n">
         <v>753784</v>
@@ -6314,7 +6314,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G205" t="n">
-        <v>1.30499148368835</v>
+        <v>1.30499136447906</v>
       </c>
       <c r="H205" t="n">
         <v>1053905</v>
@@ -6372,7 +6372,7 @@
         <v>1.83899998664856</v>
       </c>
       <c r="G207" t="n">
-        <v>1.29583120346069</v>
+        <v>1.2958310842514</v>
       </c>
       <c r="H207" t="n">
         <v>359958</v>
@@ -6459,7 +6459,7 @@
         <v>1.91100001335144</v>
       </c>
       <c r="G210" t="n">
-        <v>1.34656512737274</v>
+        <v>1.34656524658203</v>
       </c>
       <c r="H210" t="n">
         <v>522665</v>
@@ -6517,7 +6517,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G212" t="n">
-        <v>1.29371726512909</v>
+        <v>1.2937171459198</v>
       </c>
       <c r="H212" t="n">
         <v>773982</v>
@@ -6575,7 +6575,7 @@
         <v>1.81099998950958</v>
       </c>
       <c r="G214" t="n">
-        <v>1.27610123157501</v>
+        <v>1.2761013507843</v>
       </c>
       <c r="H214" t="n">
         <v>308754</v>
@@ -6865,7 +6865,7 @@
         <v>2.02099990844727</v>
       </c>
       <c r="G224" t="n">
-        <v>1.42407536506653</v>
+        <v>1.42407548427582</v>
       </c>
       <c r="H224" t="n">
         <v>728660</v>
@@ -6894,7 +6894,7 @@
         <v>1.98300004005432</v>
       </c>
       <c r="G225" t="n">
-        <v>1.39729928970337</v>
+        <v>1.39729917049408</v>
       </c>
       <c r="H225" t="n">
         <v>1086938</v>
@@ -6923,7 +6923,7 @@
         <v>1.93099999427795</v>
       </c>
       <c r="G226" t="n">
-        <v>1.36065793037415</v>
+        <v>1.36065781116486</v>
       </c>
       <c r="H226" t="n">
         <v>764236</v>
@@ -7039,7 +7039,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G230" t="n">
-        <v>1.29442179203033</v>
+        <v>1.29442191123962</v>
       </c>
       <c r="H230" t="n">
         <v>689236</v>
@@ -7097,7 +7097,7 @@
         <v>1.86300003528595</v>
       </c>
       <c r="G232" t="n">
-        <v>1.31274247169495</v>
+        <v>1.31274235248566</v>
       </c>
       <c r="H232" t="n">
         <v>190892</v>
@@ -7126,7 +7126,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G233" t="n">
-        <v>1.27539646625519</v>
+        <v>1.27539658546448</v>
       </c>
       <c r="H233" t="n">
         <v>331881</v>
@@ -7416,7 +7416,7 @@
         <v>1.807000041008</v>
       </c>
       <c r="G243" t="n">
-        <v>1.27328264713287</v>
+        <v>1.27328276634216</v>
       </c>
       <c r="H243" t="n">
         <v>162393</v>
@@ -7503,7 +7503,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G246" t="n">
-        <v>1.36277174949646</v>
+        <v>1.36277186870575</v>
       </c>
       <c r="H246" t="n">
         <v>570217</v>
@@ -7532,7 +7532,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G247" t="n">
-        <v>1.38109254837036</v>
+        <v>1.38109242916107</v>
       </c>
       <c r="H247" t="n">
         <v>439371</v>
@@ -7561,7 +7561,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G248" t="n">
-        <v>1.37263667583466</v>
+        <v>1.37263679504395</v>
       </c>
       <c r="H248" t="n">
         <v>452614</v>
@@ -7619,7 +7619,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G250" t="n">
-        <v>1.36981821060181</v>
+        <v>1.3698183298111</v>
       </c>
       <c r="H250" t="n">
         <v>296376</v>
@@ -7648,7 +7648,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G251" t="n">
-        <v>1.38602483272552</v>
+        <v>1.38602495193481</v>
       </c>
       <c r="H251" t="n">
         <v>191879</v>
@@ -7706,7 +7706,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G253" t="n">
-        <v>1.32824456691742</v>
+        <v>1.32824444770813</v>
       </c>
       <c r="H253" t="n">
         <v>496653</v>
@@ -7735,7 +7735,7 @@
         <v>1.95099997520447</v>
       </c>
       <c r="G254" t="n">
-        <v>1.37475073337555</v>
+        <v>1.37475061416626</v>
       </c>
       <c r="H254" t="n">
         <v>410471</v>
@@ -7851,7 +7851,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G258" t="n">
-        <v>1.39236664772034</v>
+        <v>1.39236652851105</v>
       </c>
       <c r="H258" t="n">
         <v>262724</v>
@@ -7938,7 +7938,7 @@
         <v>1.942999958992</v>
       </c>
       <c r="G261" t="n">
-        <v>1.36911368370056</v>
+        <v>1.36911356449127</v>
       </c>
       <c r="H261" t="n">
         <v>657682</v>
@@ -7967,7 +7967,7 @@
         <v>2.00600004196167</v>
       </c>
       <c r="G262" t="n">
-        <v>1.41350591182709</v>
+        <v>1.4135057926178</v>
       </c>
       <c r="H262" t="n">
         <v>717038</v>
@@ -7996,7 +7996,7 @@
         <v>1.97200000286102</v>
       </c>
       <c r="G263" t="n">
-        <v>1.3895480632782</v>
+        <v>1.38954818248749</v>
       </c>
       <c r="H263" t="n">
         <v>310392</v>
@@ -8054,7 +8054,7 @@
         <v>2.01300001144409</v>
       </c>
       <c r="G265" t="n">
-        <v>1.41843819618225</v>
+        <v>1.41843831539154</v>
       </c>
       <c r="H265" t="n">
         <v>1394290</v>
@@ -8141,7 +8141,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G268" t="n">
-        <v>1.56077539920807</v>
+        <v>1.56077527999878</v>
       </c>
       <c r="H268" t="n">
         <v>856015</v>
@@ -8199,7 +8199,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G270" t="n">
-        <v>1.55161499977112</v>
+        <v>1.55161511898041</v>
       </c>
       <c r="H270" t="n">
         <v>421095</v>
@@ -8228,7 +8228,7 @@
         <v>2.18300008773804</v>
       </c>
       <c r="G271" t="n">
-        <v>1.53822696208954</v>
+        <v>1.53822708129883</v>
       </c>
       <c r="H271" t="n">
         <v>558105</v>
@@ -8257,7 +8257,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G272" t="n">
-        <v>1.5332944393158</v>
+        <v>1.53329455852509</v>
       </c>
       <c r="H272" t="n">
         <v>539558</v>
@@ -8373,7 +8373,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G276" t="n">
-        <v>1.48819768428802</v>
+        <v>1.48819756507874</v>
       </c>
       <c r="H276" t="n">
         <v>185994</v>
@@ -8431,7 +8431,7 @@
         <v>2.06699991226196</v>
       </c>
       <c r="G278" t="n">
-        <v>1.45648884773254</v>
+        <v>1.45648872852325</v>
       </c>
       <c r="H278" t="n">
         <v>289759</v>
@@ -8489,7 +8489,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G280" t="n">
-        <v>1.44450998306274</v>
+        <v>1.44450986385345</v>
       </c>
       <c r="H280" t="n">
         <v>636661</v>
@@ -8518,7 +8518,7 @@
         <v>2.03699994087219</v>
       </c>
       <c r="G281" t="n">
-        <v>1.43534958362579</v>
+        <v>1.43534970283508</v>
       </c>
       <c r="H281" t="n">
         <v>774489</v>
@@ -8547,7 +8547,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G282" t="n">
-        <v>1.44450998306274</v>
+        <v>1.44450986385345</v>
       </c>
       <c r="H282" t="n">
         <v>502402</v>
@@ -8692,7 +8692,7 @@
         <v>2.02099990844727</v>
       </c>
       <c r="G287" t="n">
-        <v>1.42407536506653</v>
+        <v>1.42407548427582</v>
       </c>
       <c r="H287" t="n">
         <v>575103</v>
@@ -8721,7 +8721,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G288" t="n">
-        <v>1.43182647228241</v>
+        <v>1.4318265914917</v>
       </c>
       <c r="H288" t="n">
         <v>514101</v>
@@ -8837,7 +8837,7 @@
         <v>2.12400007247925</v>
       </c>
       <c r="G292" t="n">
-        <v>1.49665343761444</v>
+        <v>1.49665331840515</v>
       </c>
       <c r="H292" t="n">
         <v>280648</v>
@@ -8924,7 +8924,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G295" t="n">
-        <v>1.51074600219727</v>
+        <v>1.51074612140656</v>
       </c>
       <c r="H295" t="n">
         <v>440171</v>
@@ -9011,7 +9011,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G298" t="n">
-        <v>1.4755140542984</v>
+        <v>1.47551417350769</v>
       </c>
       <c r="H298" t="n">
         <v>739456</v>
@@ -9040,7 +9040,7 @@
         <v>2.11299991607666</v>
       </c>
       <c r="G299" t="n">
-        <v>1.48890221118927</v>
+        <v>1.48890209197998</v>
       </c>
       <c r="H299" t="n">
         <v>234428</v>
@@ -9069,7 +9069,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G300" t="n">
-        <v>1.51215529441833</v>
+        <v>1.51215517520905</v>
       </c>
       <c r="H300" t="n">
         <v>616627</v>
@@ -9127,7 +9127,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G302" t="n">
-        <v>1.52202033996582</v>
+        <v>1.52202022075653</v>
       </c>
       <c r="H302" t="n">
         <v>208214</v>
@@ -9185,7 +9185,7 @@
         <v>2.06699991226196</v>
       </c>
       <c r="G304" t="n">
-        <v>1.45648884773254</v>
+        <v>1.45648872852325</v>
       </c>
       <c r="H304" t="n">
         <v>302700</v>
@@ -9214,7 +9214,7 @@
         <v>2.05599999427795</v>
       </c>
       <c r="G305" t="n">
-        <v>1.44873785972595</v>
+        <v>1.44873774051666</v>
       </c>
       <c r="H305" t="n">
         <v>446308</v>
@@ -9301,7 +9301,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G308" t="n">
-        <v>1.49383449554443</v>
+        <v>1.49383473396301</v>
       </c>
       <c r="H308" t="n">
         <v>190816</v>
@@ -9388,7 +9388,7 @@
         <v>2.18300008773804</v>
       </c>
       <c r="G311" t="n">
-        <v>1.53822696208954</v>
+        <v>1.53822708129883</v>
       </c>
       <c r="H311" t="n">
         <v>1223387</v>
@@ -9417,7 +9417,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G312" t="n">
-        <v>1.58261930942535</v>
+        <v>1.58261919021606</v>
       </c>
       <c r="H312" t="n">
         <v>1349589</v>
@@ -9446,7 +9446,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G313" t="n">
-        <v>1.61855566501617</v>
+        <v>1.61855578422546</v>
       </c>
       <c r="H313" t="n">
         <v>610651</v>
@@ -9504,7 +9504,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G315" t="n">
-        <v>1.61855566501617</v>
+        <v>1.61855578422546</v>
       </c>
       <c r="H315" t="n">
         <v>297781</v>
@@ -9620,7 +9620,7 @@
         <v>2.29299998283386</v>
       </c>
       <c r="G319" t="n">
-        <v>1.61573731899261</v>
+        <v>1.61573719978333</v>
       </c>
       <c r="H319" t="n">
         <v>855625</v>
@@ -9649,7 +9649,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G320" t="n">
-        <v>1.62489748001099</v>
+        <v>1.62489759922028</v>
       </c>
       <c r="H320" t="n">
         <v>946396</v>
@@ -9678,7 +9678,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G321" t="n">
-        <v>1.63758099079132</v>
+        <v>1.63758087158203</v>
       </c>
       <c r="H321" t="n">
         <v>897308</v>
@@ -9736,7 +9736,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G323" t="n">
-        <v>1.60234904289246</v>
+        <v>1.60234880447388</v>
       </c>
       <c r="H323" t="n">
         <v>324411</v>
@@ -9765,7 +9765,7 @@
         <v>2.2590000629425</v>
       </c>
       <c r="G324" t="n">
-        <v>1.59177958965302</v>
+        <v>1.59177947044373</v>
       </c>
       <c r="H324" t="n">
         <v>573058</v>
@@ -9794,7 +9794,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G325" t="n">
-        <v>1.57416355609894</v>
+        <v>1.57416367530823</v>
       </c>
       <c r="H325" t="n">
         <v>449454</v>
@@ -9823,7 +9823,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G326" t="n">
-        <v>1.51074600219727</v>
+        <v>1.51074612140656</v>
       </c>
       <c r="H326" t="n">
         <v>964268</v>
@@ -9852,7 +9852,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G327" t="n">
-        <v>1.47128629684448</v>
+        <v>1.47128617763519</v>
       </c>
       <c r="H327" t="n">
         <v>1679948</v>
@@ -9881,7 +9881,7 @@
         <v>2.12400007247925</v>
       </c>
       <c r="G328" t="n">
-        <v>1.49665343761444</v>
+        <v>1.49665331840515</v>
       </c>
       <c r="H328" t="n">
         <v>467462</v>
@@ -9997,7 +9997,7 @@
         <v>2.22099995613098</v>
       </c>
       <c r="G332" t="n">
-        <v>1.5650030374527</v>
+        <v>1.56500327587128</v>
       </c>
       <c r="H332" t="n">
         <v>221480</v>
@@ -10084,7 +10084,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G335" t="n">
-        <v>1.5769819021225</v>
+        <v>1.57698202133179</v>
       </c>
       <c r="H335" t="n">
         <v>717837</v>
@@ -10113,7 +10113,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G336" t="n">
-        <v>1.61855566501617</v>
+        <v>1.61855578422546</v>
       </c>
       <c r="H336" t="n">
         <v>709843</v>
@@ -10142,7 +10142,7 @@
         <v>2.28299999237061</v>
       </c>
       <c r="G337" t="n">
-        <v>1.60869073867798</v>
+        <v>1.60869085788727</v>
       </c>
       <c r="H337" t="n">
         <v>602165</v>
@@ -10171,7 +10171,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G338" t="n">
-        <v>1.59671187400818</v>
+        <v>1.59671199321747</v>
       </c>
       <c r="H338" t="n">
         <v>425896</v>
@@ -10258,7 +10258,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G341" t="n">
-        <v>1.65942490100861</v>
+        <v>1.6594250202179</v>
       </c>
       <c r="H341" t="n">
         <v>442544</v>
@@ -10316,7 +10316,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G343" t="n">
-        <v>1.61010015010834</v>
+        <v>1.61010003089905</v>
       </c>
       <c r="H343" t="n">
         <v>391481</v>
@@ -10374,7 +10374,7 @@
         <v>2.33699989318848</v>
       </c>
       <c r="G345" t="n">
-        <v>1.64674115180969</v>
+        <v>1.64674139022827</v>
       </c>
       <c r="H345" t="n">
         <v>1238842</v>
@@ -10403,7 +10403,7 @@
         <v>2.33699989318848</v>
       </c>
       <c r="G346" t="n">
-        <v>1.64674115180969</v>
+        <v>1.64674139022827</v>
       </c>
       <c r="H346" t="n">
         <v>580707</v>
@@ -10461,7 +10461,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G348" t="n">
-        <v>1.5614800453186</v>
+        <v>1.56147992610931</v>
       </c>
       <c r="H348" t="n">
         <v>2800039</v>
@@ -10519,7 +10519,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G350" t="n">
-        <v>1.55161499977112</v>
+        <v>1.55161511898041</v>
       </c>
       <c r="H350" t="n">
         <v>673952</v>
@@ -10548,7 +10548,7 @@
         <v>2.19400000572205</v>
       </c>
       <c r="G351" t="n">
-        <v>1.54597795009613</v>
+        <v>1.54597806930542</v>
       </c>
       <c r="H351" t="n">
         <v>432046</v>
@@ -10606,7 +10606,7 @@
         <v>2.27099990844727</v>
       </c>
       <c r="G353" t="n">
-        <v>1.60023498535156</v>
+        <v>1.60023522377014</v>
       </c>
       <c r="H353" t="n">
         <v>454310</v>
@@ -10664,7 +10664,7 @@
         <v>2.36400008201599</v>
       </c>
       <c r="G355" t="n">
-        <v>1.66576671600342</v>
+        <v>1.66576659679413</v>
       </c>
       <c r="H355" t="n">
         <v>862677</v>
@@ -10693,7 +10693,7 @@
         <v>2.50250005722046</v>
       </c>
       <c r="G356" t="n">
-        <v>1.76335906982422</v>
+        <v>1.76335918903351</v>
       </c>
       <c r="H356" t="n">
         <v>4862397</v>
@@ -10722,7 +10722,7 @@
         <v>2.83750009536743</v>
       </c>
       <c r="G357" t="n">
-        <v>1.99941325187683</v>
+        <v>1.99941301345825</v>
       </c>
       <c r="H357" t="n">
         <v>4829114</v>
@@ -10751,7 +10751,7 @@
         <v>2.7574999332428</v>
       </c>
       <c r="G358" t="n">
-        <v>1.94304215908051</v>
+        <v>1.94304203987122</v>
       </c>
       <c r="H358" t="n">
         <v>5360863</v>
@@ -10780,7 +10780,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G359" t="n">
-        <v>1.86729335784912</v>
+        <v>1.86729347705841</v>
       </c>
       <c r="H359" t="n">
         <v>1790824</v>
@@ -10809,7 +10809,7 @@
         <v>2.69749999046326</v>
       </c>
       <c r="G360" t="n">
-        <v>1.90076351165771</v>
+        <v>1.90076375007629</v>
       </c>
       <c r="H360" t="n">
         <v>2325561</v>
@@ -10838,7 +10838,7 @@
         <v>2.65750002861023</v>
       </c>
       <c r="G361" t="n">
-        <v>1.87257814407349</v>
+        <v>1.87257826328278</v>
       </c>
       <c r="H361" t="n">
         <v>670603</v>
@@ -10896,7 +10896,7 @@
         <v>2.54250001907349</v>
       </c>
       <c r="G363" t="n">
-        <v>1.79154455661774</v>
+        <v>1.79154443740845</v>
       </c>
       <c r="H363" t="n">
         <v>394519</v>
@@ -10925,7 +10925,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G364" t="n">
-        <v>1.7968293428421</v>
+        <v>1.79682946205139</v>
       </c>
       <c r="H364" t="n">
         <v>380123</v>
@@ -10983,7 +10983,7 @@
         <v>2.50250005722046</v>
       </c>
       <c r="G366" t="n">
-        <v>1.76335906982422</v>
+        <v>1.76335918903351</v>
       </c>
       <c r="H366" t="n">
         <v>920397</v>
@@ -11012,7 +11012,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G367" t="n">
-        <v>1.75736951828003</v>
+        <v>1.75736963748932</v>
       </c>
       <c r="H367" t="n">
         <v>543237</v>
@@ -11041,7 +11041,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G368" t="n">
-        <v>1.78626000881195</v>
+        <v>1.78625988960266</v>
       </c>
       <c r="H368" t="n">
         <v>410264</v>
@@ -11070,7 +11070,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G369" t="n">
-        <v>1.80739891529083</v>
+        <v>1.80739915370941</v>
       </c>
       <c r="H369" t="n">
         <v>372165</v>
@@ -11099,7 +11099,7 @@
         <v>2.5550000667572</v>
       </c>
       <c r="G370" t="n">
-        <v>1.80035269260406</v>
+        <v>1.80035281181335</v>
       </c>
       <c r="H370" t="n">
         <v>510079</v>
@@ -11157,7 +11157,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G372" t="n">
-        <v>1.87786293029785</v>
+        <v>1.87786269187927</v>
       </c>
       <c r="H372" t="n">
         <v>730632</v>
@@ -11186,7 +11186,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G373" t="n">
-        <v>1.88490927219391</v>
+        <v>1.8849093914032</v>
       </c>
       <c r="H373" t="n">
         <v>569369</v>
@@ -11273,7 +11273,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G376" t="n">
-        <v>1.86377000808716</v>
+        <v>1.86377024650574</v>
       </c>
       <c r="H376" t="n">
         <v>303450</v>
@@ -11302,7 +11302,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G377" t="n">
-        <v>1.86377000808716</v>
+        <v>1.86377024650574</v>
       </c>
       <c r="H377" t="n">
         <v>377689</v>
@@ -11360,7 +11360,7 @@
         <v>2.64249992370605</v>
       </c>
       <c r="G379" t="n">
-        <v>1.86200845241547</v>
+        <v>1.86200857162476</v>
       </c>
       <c r="H379" t="n">
         <v>662990</v>
@@ -11389,7 +11389,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>1.86377000808716</v>
+        <v>1.86377024650574</v>
       </c>
       <c r="H380" t="n">
         <v>668827</v>
@@ -11418,7 +11418,7 @@
         <v>2.59750008583069</v>
       </c>
       <c r="G381" t="n">
-        <v>1.83029985427856</v>
+        <v>1.83029997348785</v>
       </c>
       <c r="H381" t="n">
         <v>623499</v>
@@ -11476,7 +11476,7 @@
         <v>2.61249995231628</v>
       </c>
       <c r="G383" t="n">
-        <v>1.84086918830872</v>
+        <v>1.84086942672729</v>
       </c>
       <c r="H383" t="n">
         <v>982705</v>
@@ -11505,7 +11505,7 @@
         <v>2.55749988555908</v>
       </c>
       <c r="G384" t="n">
-        <v>1.80211424827576</v>
+        <v>1.80211412906647</v>
       </c>
       <c r="H384" t="n">
         <v>1307235</v>
@@ -11592,7 +11592,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G387" t="n">
-        <v>1.8060120344162</v>
+        <v>1.80601191520691</v>
       </c>
       <c r="H387" t="n">
         <v>2221253</v>
@@ -11679,7 +11679,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G390" t="n">
-        <v>1.851318359375</v>
+        <v>1.85131847858429</v>
       </c>
       <c r="H390" t="n">
         <v>717045</v>
@@ -11708,7 +11708,7 @@
         <v>2.40700006484985</v>
       </c>
       <c r="G391" t="n">
-        <v>1.88022112846375</v>
+        <v>1.88022089004517</v>
       </c>
       <c r="H391" t="n">
         <v>1427819</v>
@@ -11737,7 +11737,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G392" t="n">
-        <v>1.84741270542145</v>
+        <v>1.84741282463074</v>
       </c>
       <c r="H392" t="n">
         <v>573846</v>
@@ -11824,7 +11824,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G395" t="n">
-        <v>1.84506928920746</v>
+        <v>1.84506916999817</v>
       </c>
       <c r="H395" t="n">
         <v>768257</v>
@@ -11882,7 +11882,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G397" t="n">
-        <v>1.79429459571838</v>
+        <v>1.79429471492767</v>
       </c>
       <c r="H397" t="n">
         <v>625118</v>
@@ -11969,7 +11969,7 @@
         <v>2.29900002479553</v>
       </c>
       <c r="G400" t="n">
-        <v>1.79585695266724</v>
+        <v>1.79585707187653</v>
       </c>
       <c r="H400" t="n">
         <v>435929</v>
@@ -11998,7 +11998,7 @@
         <v>2.30800008773804</v>
       </c>
       <c r="G401" t="n">
-        <v>1.80288743972778</v>
+        <v>1.80288755893707</v>
       </c>
       <c r="H401" t="n">
         <v>290608</v>
@@ -12056,7 +12056,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G403" t="n">
-        <v>1.84350681304932</v>
+        <v>1.84350693225861</v>
       </c>
       <c r="H403" t="n">
         <v>508765</v>
@@ -12085,7 +12085,7 @@
         <v>2.34299993515015</v>
       </c>
       <c r="G404" t="n">
-        <v>1.83022749423981</v>
+        <v>1.83022737503052</v>
       </c>
       <c r="H404" t="n">
         <v>400051</v>
@@ -12114,7 +12114,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G405" t="n">
-        <v>1.85912990570068</v>
+        <v>1.85913002490997</v>
       </c>
       <c r="H405" t="n">
         <v>572167</v>
@@ -12143,7 +12143,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G406" t="n">
-        <v>1.82944619655609</v>
+        <v>1.82944655418396</v>
       </c>
       <c r="H406" t="n">
         <v>327031</v>
@@ -12259,7 +12259,7 @@
         <v>2.29900002479553</v>
       </c>
       <c r="G410" t="n">
-        <v>1.79585695266724</v>
+        <v>1.79585707187653</v>
       </c>
       <c r="H410" t="n">
         <v>244821</v>
@@ -12288,7 +12288,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G411" t="n">
-        <v>1.8060120344162</v>
+        <v>1.80601191520691</v>
       </c>
       <c r="H411" t="n">
         <v>489918</v>
@@ -12404,7 +12404,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G415" t="n">
-        <v>1.79351365566254</v>
+        <v>1.79351353645325</v>
       </c>
       <c r="H415" t="n">
         <v>274714</v>
@@ -12520,7 +12520,7 @@
         <v>2.23699998855591</v>
       </c>
       <c r="G419" t="n">
-        <v>1.74742591381073</v>
+        <v>1.74742603302002</v>
       </c>
       <c r="H419" t="n">
         <v>1089414</v>
@@ -12607,7 +12607,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G422" t="n">
-        <v>1.73024070262909</v>
+        <v>1.7302405834198</v>
       </c>
       <c r="H422" t="n">
         <v>493842</v>
@@ -12665,7 +12665,7 @@
         <v>2.14100003242493</v>
       </c>
       <c r="G424" t="n">
-        <v>1.67243576049805</v>
+        <v>1.67243587970734</v>
       </c>
       <c r="H424" t="n">
         <v>2417146</v>
@@ -12723,7 +12723,7 @@
         <v>2.11700010299683</v>
       </c>
       <c r="G426" t="n">
-        <v>1.65368843078613</v>
+        <v>1.65368831157684</v>
       </c>
       <c r="H426" t="n">
         <v>542238</v>
@@ -12752,7 +12752,7 @@
         <v>2.11299991607666</v>
       </c>
       <c r="G427" t="n">
-        <v>1.65056347846985</v>
+        <v>1.65056359767914</v>
       </c>
       <c r="H427" t="n">
         <v>344744</v>
@@ -12781,7 +12781,7 @@
         <v>2.1010000705719</v>
       </c>
       <c r="G428" t="n">
-        <v>1.64119005203247</v>
+        <v>1.64118993282318</v>
       </c>
       <c r="H428" t="n">
         <v>384515</v>
@@ -12955,7 +12955,7 @@
         <v>1.99899995326996</v>
       </c>
       <c r="G434" t="n">
-        <v>1.56151282787323</v>
+        <v>1.56151294708252</v>
       </c>
       <c r="H434" t="n">
         <v>852921</v>
@@ -13013,7 +13013,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G436" t="n">
-        <v>1.45762038230896</v>
+        <v>1.45762050151825</v>
       </c>
       <c r="H436" t="n">
         <v>630873</v>
@@ -13042,7 +13042,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G437" t="n">
-        <v>1.44121623039246</v>
+        <v>1.44121634960175</v>
       </c>
       <c r="H437" t="n">
         <v>430171</v>
@@ -13071,7 +13071,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G438" t="n">
-        <v>1.43887293338776</v>
+        <v>1.43887281417847</v>
       </c>
       <c r="H438" t="n">
         <v>297282</v>
@@ -13332,7 +13332,7 @@
         <v>1.85300004482269</v>
       </c>
       <c r="G447" t="n">
-        <v>1.44746541976929</v>
+        <v>1.44746553897858</v>
       </c>
       <c r="H447" t="n">
         <v>756122</v>
@@ -13361,7 +13361,7 @@
         <v>1.84399998188019</v>
       </c>
       <c r="G448" t="n">
-        <v>1.44043517112732</v>
+        <v>1.44043505191803</v>
       </c>
       <c r="H448" t="n">
         <v>564069</v>
@@ -13390,7 +13390,7 @@
         <v>1.8309999704361</v>
       </c>
       <c r="G449" t="n">
-        <v>1.43028020858765</v>
+        <v>1.43028008937836</v>
       </c>
       <c r="H449" t="n">
         <v>475160</v>
@@ -13506,7 +13506,7 @@
         <v>1.67340004444122</v>
       </c>
       <c r="G453" t="n">
-        <v>1.30717146396637</v>
+        <v>1.30717158317566</v>
       </c>
       <c r="H453" t="n">
         <v>770495</v>
@@ -13535,7 +13535,7 @@
         <v>1.66719996929169</v>
       </c>
       <c r="G454" t="n">
-        <v>1.3023282289505</v>
+        <v>1.30232834815979</v>
       </c>
       <c r="H454" t="n">
         <v>438827</v>
@@ -13564,7 +13564,7 @@
         <v>1.69219994544983</v>
       </c>
       <c r="G455" t="n">
-        <v>1.32185685634613</v>
+        <v>1.32185697555542</v>
       </c>
       <c r="H455" t="n">
         <v>907774</v>
@@ -13622,7 +13622,7 @@
         <v>1.69159996509552</v>
       </c>
       <c r="G457" t="n">
-        <v>1.32138824462891</v>
+        <v>1.3213883638382</v>
       </c>
       <c r="H457" t="n">
         <v>232730</v>
@@ -13651,7 +13651,7 @@
         <v>1.74259996414185</v>
       </c>
       <c r="G458" t="n">
-        <v>1.36122667789459</v>
+        <v>1.36122679710388</v>
       </c>
       <c r="H458" t="n">
         <v>372410</v>
@@ -13680,7 +13680,7 @@
         <v>1.84239995479584</v>
       </c>
       <c r="G459" t="n">
-        <v>1.43918514251709</v>
+        <v>1.43918526172638</v>
       </c>
       <c r="H459" t="n">
         <v>501526</v>
@@ -13767,7 +13767,7 @@
         <v>1.80599999427795</v>
       </c>
       <c r="G462" t="n">
-        <v>1.41075158119202</v>
+        <v>1.41075146198273</v>
       </c>
       <c r="H462" t="n">
         <v>246924</v>
@@ -13825,7 +13825,7 @@
         <v>1.93680000305176</v>
       </c>
       <c r="G464" t="n">
-        <v>1.51292550563812</v>
+        <v>1.51292562484741</v>
       </c>
       <c r="H464" t="n">
         <v>268931</v>
@@ -13941,7 +13941,7 @@
         <v>1.97259998321533</v>
       </c>
       <c r="G468" t="n">
-        <v>1.54089057445526</v>
+        <v>1.54089069366455</v>
       </c>
       <c r="H468" t="n">
         <v>448541</v>
@@ -13970,7 +13970,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G469" t="n">
-        <v>1.58729076385498</v>
+        <v>1.58729088306427</v>
       </c>
       <c r="H469" t="n">
         <v>310094</v>
@@ -14086,7 +14086,7 @@
         <v>2.15249991416931</v>
       </c>
       <c r="G473" t="n">
-        <v>1.68141901493073</v>
+        <v>1.68141889572144</v>
       </c>
       <c r="H473" t="n">
         <v>1172106</v>
@@ -14144,7 +14144,7 @@
         <v>2.25950002670288</v>
       </c>
       <c r="G475" t="n">
-        <v>1.76500165462494</v>
+        <v>1.76500177383423</v>
       </c>
       <c r="H475" t="n">
         <v>775246</v>
@@ -14173,7 +14173,7 @@
         <v>2.25650000572205</v>
       </c>
       <c r="G476" t="n">
-        <v>1.76265823841095</v>
+        <v>1.76265835762024</v>
       </c>
       <c r="H476" t="n">
         <v>463148</v>
@@ -14202,7 +14202,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G477" t="n">
-        <v>1.75601851940155</v>
+        <v>1.75601840019226</v>
       </c>
       <c r="H477" t="n">
         <v>381912</v>
@@ -14231,7 +14231,7 @@
         <v>2.22699999809265</v>
       </c>
       <c r="G478" t="n">
-        <v>1.73961448669434</v>
+        <v>1.73961436748505</v>
       </c>
       <c r="H478" t="n">
         <v>1434510</v>
@@ -14318,7 +14318,7 @@
         <v>2.22300004959106</v>
       </c>
       <c r="G481" t="n">
-        <v>1.73648989200592</v>
+        <v>1.73649001121521</v>
       </c>
       <c r="H481" t="n">
         <v>624711</v>
@@ -14347,7 +14347,7 @@
         <v>2.31900000572205</v>
       </c>
       <c r="G482" t="n">
-        <v>1.8114800453186</v>
+        <v>1.81147992610931</v>
       </c>
       <c r="H482" t="n">
         <v>1426253</v>
@@ -14376,7 +14376,7 @@
         <v>2.29749989509583</v>
       </c>
       <c r="G483" t="n">
-        <v>1.79468524456024</v>
+        <v>1.79468536376953</v>
       </c>
       <c r="H483" t="n">
         <v>1095196</v>
@@ -14434,7 +14434,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G485" t="n">
-        <v>1.86850345134735</v>
+        <v>1.86850368976593</v>
       </c>
       <c r="H485" t="n">
         <v>792725</v>
@@ -14463,7 +14463,7 @@
         <v>2.32649993896484</v>
       </c>
       <c r="G486" t="n">
-        <v>1.81733858585358</v>
+        <v>1.81733870506287</v>
       </c>
       <c r="H486" t="n">
         <v>753540</v>
@@ -14550,7 +14550,7 @@
         <v>2.34949994087219</v>
       </c>
       <c r="G489" t="n">
-        <v>1.83530509471893</v>
+        <v>1.83530497550964</v>
       </c>
       <c r="H489" t="n">
         <v>626584</v>
@@ -14579,7 +14579,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G490" t="n">
-        <v>1.82007253170013</v>
+        <v>1.82007241249084</v>
       </c>
       <c r="H490" t="n">
         <v>579196</v>
@@ -14608,7 +14608,7 @@
         <v>2.39750003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>1.87280011177063</v>
+        <v>1.87280023097992</v>
       </c>
       <c r="H491" t="n">
         <v>839004</v>
@@ -14637,7 +14637,7 @@
         <v>2.3989999294281</v>
       </c>
       <c r="G492" t="n">
-        <v>1.87397158145905</v>
+        <v>1.87397170066833</v>
       </c>
       <c r="H492" t="n">
         <v>458199</v>
@@ -14695,7 +14695,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G494" t="n">
-        <v>1.85912990570068</v>
+        <v>1.85913002490997</v>
       </c>
       <c r="H494" t="n">
         <v>254944</v>
@@ -14724,7 +14724,7 @@
         <v>2.38100004196167</v>
       </c>
       <c r="G495" t="n">
-        <v>1.8599112033844</v>
+        <v>1.85991108417511</v>
       </c>
       <c r="H495" t="n">
         <v>360476</v>
@@ -14753,7 +14753,7 @@
         <v>2.375</v>
       </c>
       <c r="G496" t="n">
-        <v>1.85522401332855</v>
+        <v>1.85522413253784</v>
       </c>
       <c r="H496" t="n">
         <v>380134</v>
@@ -14927,7 +14927,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G502" t="n">
-        <v>1.89662492275238</v>
+        <v>1.89662504196167</v>
       </c>
       <c r="H502" t="n">
         <v>886759</v>
@@ -14956,7 +14956,7 @@
         <v>2.4210000038147</v>
       </c>
       <c r="G503" t="n">
-        <v>1.89115715026855</v>
+        <v>1.89115703105927</v>
       </c>
       <c r="H503" t="n">
         <v>400870</v>
@@ -14985,7 +14985,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G504" t="n">
-        <v>1.90443646907806</v>
+        <v>1.90443634986877</v>
       </c>
       <c r="H504" t="n">
         <v>376866</v>
@@ -15072,7 +15072,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G507" t="n">
-        <v>1.851318359375</v>
+        <v>1.85131847858429</v>
       </c>
       <c r="H507" t="n">
         <v>420850</v>
@@ -15101,7 +15101,7 @@
         <v>2.38750004768372</v>
       </c>
       <c r="G508" t="n">
-        <v>1.86498880386353</v>
+        <v>1.86498844623566</v>
       </c>
       <c r="H508" t="n">
         <v>279164</v>
@@ -15130,7 +15130,7 @@
         <v>2.37949991226196</v>
       </c>
       <c r="G509" t="n">
-        <v>1.85873925685883</v>
+        <v>1.85873913764954</v>
       </c>
       <c r="H509" t="n">
         <v>517495</v>
@@ -15188,7 +15188,7 @@
         <v>2.30800008773804</v>
       </c>
       <c r="G511" t="n">
-        <v>1.80288743972778</v>
+        <v>1.80288755893707</v>
       </c>
       <c r="H511" t="n">
         <v>471638</v>
@@ -15275,7 +15275,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G514" t="n">
-        <v>1.84819376468658</v>
+        <v>1.84819388389587</v>
       </c>
       <c r="H514" t="n">
         <v>499423</v>
@@ -15304,7 +15304,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G515" t="n">
-        <v>1.88256430625916</v>
+        <v>1.88256442546844</v>
       </c>
       <c r="H515" t="n">
         <v>456876</v>
@@ -15333,7 +15333,7 @@
         <v>2.38700008392334</v>
       </c>
       <c r="G516" t="n">
-        <v>1.86459803581238</v>
+        <v>1.86459815502167</v>
       </c>
       <c r="H516" t="n">
         <v>378435</v>
@@ -15391,7 +15391,7 @@
         <v>2.35949993133545</v>
       </c>
       <c r="G518" t="n">
-        <v>1.84311640262604</v>
+        <v>1.84311628341675</v>
       </c>
       <c r="H518" t="n">
         <v>314732</v>
@@ -15420,7 +15420,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G519" t="n">
-        <v>1.84506928920746</v>
+        <v>1.84506916999817</v>
       </c>
       <c r="H519" t="n">
         <v>346938</v>
@@ -15478,7 +15478,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G521" t="n">
-        <v>1.83960127830505</v>
+        <v>1.83960139751434</v>
       </c>
       <c r="H521" t="n">
         <v>400601</v>
@@ -15536,7 +15536,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G523" t="n">
-        <v>1.74352037906647</v>
+        <v>1.74352014064789</v>
       </c>
       <c r="H523" t="n">
         <v>587511</v>
@@ -15594,7 +15594,7 @@
         <v>2.18650007247925</v>
       </c>
       <c r="G525" t="n">
-        <v>1.70797801017761</v>
+        <v>1.7079781293869</v>
       </c>
       <c r="H525" t="n">
         <v>339135</v>
@@ -15710,7 +15710,7 @@
         <v>2.1324999332428</v>
       </c>
       <c r="G529" t="n">
-        <v>1.66579604148865</v>
+        <v>1.66579592227936</v>
       </c>
       <c r="H529" t="n">
         <v>1224677</v>
@@ -15739,7 +15739,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G530" t="n">
-        <v>1.65603160858154</v>
+        <v>1.65603172779083</v>
       </c>
       <c r="H530" t="n">
         <v>1091564</v>
@@ -15855,7 +15855,7 @@
         <v>2.1029999256134</v>
       </c>
       <c r="G534" t="n">
-        <v>1.64275205135345</v>
+        <v>1.64275217056274</v>
       </c>
       <c r="H534" t="n">
         <v>489001</v>
@@ -16000,7 +16000,7 @@
         <v>2.1010000705719</v>
       </c>
       <c r="G539" t="n">
-        <v>1.64119005203247</v>
+        <v>1.64118993282318</v>
       </c>
       <c r="H539" t="n">
         <v>348613</v>
@@ -16058,7 +16058,7 @@
         <v>2.10949993133545</v>
       </c>
       <c r="G541" t="n">
-        <v>1.64782965183258</v>
+        <v>1.64782953262329</v>
       </c>
       <c r="H541" t="n">
         <v>509259</v>
@@ -16174,7 +16174,7 @@
         <v>2.12750005722046</v>
       </c>
       <c r="G545" t="n">
-        <v>1.66189050674438</v>
+        <v>1.6618903875351</v>
       </c>
       <c r="H545" t="n">
         <v>1419921</v>
@@ -16203,7 +16203,7 @@
         <v>2.14299988746643</v>
       </c>
       <c r="G546" t="n">
-        <v>1.67399799823761</v>
+        <v>1.67399787902832</v>
       </c>
       <c r="H546" t="n">
         <v>1450618</v>
@@ -16232,7 +16232,7 @@
         <v>2.10949993133545</v>
       </c>
       <c r="G547" t="n">
-        <v>1.64782965183258</v>
+        <v>1.64782953262329</v>
       </c>
       <c r="H547" t="n">
         <v>489388</v>
@@ -16290,7 +16290,7 @@
         <v>2.12949991226196</v>
       </c>
       <c r="G549" t="n">
-        <v>1.66345250606537</v>
+        <v>1.66345262527466</v>
       </c>
       <c r="H549" t="n">
         <v>838112</v>
@@ -16348,7 +16348,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G551" t="n">
-        <v>1.67009222507477</v>
+        <v>1.67009234428406</v>
       </c>
       <c r="H551" t="n">
         <v>1192328</v>
@@ -16435,7 +16435,7 @@
         <v>2.24300003051758</v>
       </c>
       <c r="G554" t="n">
-        <v>1.752112865448</v>
+        <v>1.75211274623871</v>
       </c>
       <c r="H554" t="n">
         <v>387019</v>
@@ -16464,7 +16464,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G555" t="n">
-        <v>1.74352037906647</v>
+        <v>1.74352014064789</v>
       </c>
       <c r="H555" t="n">
         <v>532106</v>
@@ -16493,7 +16493,7 @@
         <v>2.24449992179871</v>
       </c>
       <c r="G556" t="n">
-        <v>1.75328433513641</v>
+        <v>1.75328457355499</v>
       </c>
       <c r="H556" t="n">
         <v>397911</v>
@@ -16522,7 +16522,7 @@
         <v>2.30550003051758</v>
       </c>
       <c r="G557" t="n">
-        <v>1.80093455314636</v>
+        <v>1.80093443393707</v>
       </c>
       <c r="H557" t="n">
         <v>567946</v>
@@ -16580,7 +16580,7 @@
         <v>2.42149996757507</v>
       </c>
       <c r="G559" t="n">
-        <v>1.89154756069183</v>
+        <v>1.89154744148254</v>
       </c>
       <c r="H559" t="n">
         <v>1056336</v>
@@ -16609,7 +16609,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G560" t="n">
-        <v>1.8786586523056</v>
+        <v>1.87865853309631</v>
       </c>
       <c r="H560" t="n">
         <v>518625</v>
@@ -16638,7 +16638,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G561" t="n">
-        <v>1.92630863189697</v>
+        <v>1.92630875110626</v>
       </c>
       <c r="H561" t="n">
         <v>1119220</v>
@@ -16667,7 +16667,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G562" t="n">
-        <v>1.95130503177643</v>
+        <v>1.95130515098572</v>
       </c>
       <c r="H562" t="n">
         <v>455972</v>
@@ -16696,7 +16696,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G563" t="n">
-        <v>1.96536588668823</v>
+        <v>1.96536612510681</v>
       </c>
       <c r="H563" t="n">
         <v>1160065</v>
@@ -16754,7 +16754,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G565" t="n">
-        <v>1.97473990917206</v>
+        <v>1.97473978996277</v>
       </c>
       <c r="H565" t="n">
         <v>742112</v>
@@ -16812,7 +16812,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G567" t="n">
-        <v>1.97473990917206</v>
+        <v>1.97473978996277</v>
       </c>
       <c r="H567" t="n">
         <v>1363010</v>
@@ -16841,7 +16841,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G568" t="n">
-        <v>1.99661183357239</v>
+        <v>1.9966117143631</v>
       </c>
       <c r="H568" t="n">
         <v>1003381</v>
@@ -16870,7 +16870,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G569" t="n">
-        <v>1.92005932331085</v>
+        <v>1.92005956172943</v>
       </c>
       <c r="H569" t="n">
         <v>1136036</v>
@@ -16899,7 +16899,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G570" t="n">
-        <v>1.9294331073761</v>
+        <v>1.92943322658539</v>
       </c>
       <c r="H570" t="n">
         <v>765788</v>
@@ -16928,7 +16928,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G571" t="n">
-        <v>1.93099534511566</v>
+        <v>1.93099522590637</v>
       </c>
       <c r="H571" t="n">
         <v>439198</v>
@@ -16986,7 +16986,7 @@
         <v>2.56800007820129</v>
       </c>
       <c r="G573" t="n">
-        <v>2.00598549842834</v>
+        <v>2.00598573684692</v>
       </c>
       <c r="H573" t="n">
         <v>4035540</v>
@@ -17044,7 +17044,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G575" t="n">
-        <v>2.04660534858704</v>
+        <v>2.04660511016846</v>
       </c>
       <c r="H575" t="n">
         <v>671436</v>
@@ -17073,7 +17073,7 @@
         <v>2.70600008964539</v>
       </c>
       <c r="G576" t="n">
-        <v>2.11378407478333</v>
+        <v>2.11378383636475</v>
       </c>
       <c r="H576" t="n">
         <v>1342948</v>
@@ -17160,7 +17160,7 @@
         <v>2.71799993515015</v>
       </c>
       <c r="G579" t="n">
-        <v>2.1231575012207</v>
+        <v>2.12315773963928</v>
       </c>
       <c r="H579" t="n">
         <v>1054021</v>
@@ -17305,7 +17305,7 @@
         <v>2.76200008392334</v>
       </c>
       <c r="G584" t="n">
-        <v>2.15752840042114</v>
+        <v>2.15752816200256</v>
       </c>
       <c r="H584" t="n">
         <v>580443</v>
@@ -17334,7 +17334,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G585" t="n">
-        <v>2.1965856552124</v>
+        <v>2.19658541679382</v>
       </c>
       <c r="H585" t="n">
         <v>1518765</v>
@@ -17537,7 +17537,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G592" t="n">
-        <v>2.43874073028564</v>
+        <v>2.43874096870422</v>
       </c>
       <c r="H592" t="n">
         <v>965545</v>
@@ -17624,7 +17624,7 @@
         <v>3.11400008201599</v>
       </c>
       <c r="G595" t="n">
-        <v>2.43249201774597</v>
+        <v>2.43249177932739</v>
       </c>
       <c r="H595" t="n">
         <v>1799003</v>
@@ -17653,7 +17653,7 @@
         <v>3.00399994850159</v>
       </c>
       <c r="G596" t="n">
-        <v>2.34656572341919</v>
+        <v>2.34656548500061</v>
       </c>
       <c r="H596" t="n">
         <v>921949</v>
@@ -17682,7 +17682,7 @@
         <v>3</v>
       </c>
       <c r="G597" t="n">
-        <v>2.34344100952148</v>
+        <v>2.34344124794006</v>
       </c>
       <c r="H597" t="n">
         <v>1851145</v>
@@ -17798,7 +17798,7 @@
         <v>3.05200004577637</v>
       </c>
       <c r="G601" t="n">
-        <v>2.3840606212616</v>
+        <v>2.38406085968018</v>
       </c>
       <c r="H601" t="n">
         <v>913843</v>
@@ -17856,7 +17856,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G603" t="n">
-        <v>2.46529984474182</v>
+        <v>2.4653000831604</v>
       </c>
       <c r="H603" t="n">
         <v>1511750</v>
@@ -17885,7 +17885,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G604" t="n">
-        <v>2.46529984474182</v>
+        <v>2.4653000831604</v>
       </c>
       <c r="H604" t="n">
         <v>2000044</v>
@@ -17914,7 +17914,7 @@
         <v>3.17400002479553</v>
       </c>
       <c r="G605" t="n">
-        <v>2.47936058044434</v>
+        <v>2.47936081886292</v>
       </c>
       <c r="H605" t="n">
         <v>2744827</v>
@@ -18001,7 +18001,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G608" t="n">
-        <v>2.5465395450592</v>
+        <v>2.54653930664062</v>
       </c>
       <c r="H608" t="n">
         <v>795781</v>
@@ -18059,7 +18059,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G610" t="n">
-        <v>2.46373796463013</v>
+        <v>2.46373772621155</v>
       </c>
       <c r="H610" t="n">
         <v>1532299</v>
@@ -18088,7 +18088,7 @@
         <v>3.24600005149841</v>
       </c>
       <c r="G611" t="n">
-        <v>2.53560328483582</v>
+        <v>2.53560304641724</v>
       </c>
       <c r="H611" t="n">
         <v>978496</v>
@@ -18117,7 +18117,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G612" t="n">
-        <v>2.4137442111969</v>
+        <v>2.41374444961548</v>
       </c>
       <c r="H612" t="n">
         <v>1036670</v>
@@ -18175,7 +18175,7 @@
         <v>3.09599995613098</v>
       </c>
       <c r="G614" t="n">
-        <v>2.41843128204346</v>
+        <v>2.41843104362488</v>
       </c>
       <c r="H614" t="n">
         <v>539410</v>
@@ -18233,7 +18233,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G616" t="n">
-        <v>2.39343452453613</v>
+        <v>2.39343428611755</v>
       </c>
       <c r="H616" t="n">
         <v>397137</v>
@@ -18436,7 +18436,7 @@
         <v>3.21799993515015</v>
       </c>
       <c r="G623" t="n">
-        <v>2.51373100280762</v>
+        <v>2.5137312412262</v>
       </c>
       <c r="H623" t="n">
         <v>829894</v>
@@ -18494,7 +18494,7 @@
         <v>3.24799990653992</v>
       </c>
       <c r="G625" t="n">
-        <v>2.53716540336609</v>
+        <v>2.53716564178467</v>
       </c>
       <c r="H625" t="n">
         <v>505088</v>
@@ -18523,7 +18523,7 @@
         <v>3.2720000743866</v>
       </c>
       <c r="G626" t="n">
-        <v>2.55591320991516</v>
+        <v>2.55591297149658</v>
       </c>
       <c r="H626" t="n">
         <v>682877</v>
@@ -18610,7 +18610,7 @@
         <v>3.26399993896484</v>
       </c>
       <c r="G629" t="n">
-        <v>2.54966378211975</v>
+        <v>2.54966402053833</v>
       </c>
       <c r="H629" t="n">
         <v>1449732</v>
@@ -18668,7 +18668,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G631" t="n">
-        <v>2.57778525352478</v>
+        <v>2.5777850151062</v>
       </c>
       <c r="H631" t="n">
         <v>943074</v>
@@ -18726,7 +18726,7 @@
         <v>3.42199993133545</v>
       </c>
       <c r="G633" t="n">
-        <v>2.67308497428894</v>
+        <v>2.67308521270752</v>
       </c>
       <c r="H633" t="n">
         <v>1448985</v>
@@ -18842,7 +18842,7 @@
         <v>3.53200006484985</v>
       </c>
       <c r="G637" t="n">
-        <v>2.75901126861572</v>
+        <v>2.7590115070343</v>
       </c>
       <c r="H637" t="n">
         <v>1376981</v>
@@ -18929,7 +18929,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G640" t="n">
-        <v>2.66151165962219</v>
+        <v>2.66151189804077</v>
       </c>
       <c r="H640" t="n">
         <v>1142550</v>
@@ -19074,7 +19074,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G645" t="n">
-        <v>2.65814256668091</v>
+        <v>2.65814280509949</v>
       </c>
       <c r="H645" t="n">
         <v>687583</v>
@@ -19132,7 +19132,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G647" t="n">
-        <v>2.59413170814514</v>
+        <v>2.59413146972656</v>
       </c>
       <c r="H647" t="n">
         <v>573464</v>
@@ -19161,7 +19161,7 @@
         <v>3.01399993896484</v>
       </c>
       <c r="G648" t="n">
-        <v>2.53854322433472</v>
+        <v>2.53854298591614</v>
       </c>
       <c r="H648" t="n">
         <v>931043</v>
@@ -19248,7 +19248,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G651" t="n">
-        <v>2.44926452636719</v>
+        <v>2.44926476478577</v>
       </c>
       <c r="H651" t="n">
         <v>488032</v>
@@ -19422,7 +19422,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G657" t="n">
-        <v>2.45600271224976</v>
+        <v>2.45600247383118</v>
       </c>
       <c r="H657" t="n">
         <v>344477</v>
@@ -19567,7 +19567,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G662" t="n">
-        <v>2.47116303443909</v>
+        <v>2.47116327285767</v>
       </c>
       <c r="H662" t="n">
         <v>401363</v>
@@ -19683,7 +19683,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G666" t="n">
-        <v>2.48800826072693</v>
+        <v>2.48800802230835</v>
       </c>
       <c r="H666" t="n">
         <v>259923</v>
@@ -19741,7 +19741,7 @@
         <v>2.89800000190735</v>
       </c>
       <c r="G668" t="n">
-        <v>2.44084215164185</v>
+        <v>2.44084191322327</v>
       </c>
       <c r="H668" t="n">
         <v>360472</v>
@@ -20031,7 +20031,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G678" t="n">
-        <v>2.35661721229553</v>
+        <v>2.35661697387695</v>
       </c>
       <c r="H678" t="n">
         <v>240265</v>
@@ -20118,7 +20118,7 @@
         <v>3.22399997711182</v>
       </c>
       <c r="G681" t="n">
-        <v>2.71541595458984</v>
+        <v>2.71541571617126</v>
       </c>
       <c r="H681" t="n">
         <v>4686248</v>
@@ -20147,7 +20147,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G682" t="n">
-        <v>2.57223320007324</v>
+        <v>2.57223296165466</v>
       </c>
       <c r="H682" t="n">
         <v>2047557</v>
@@ -20321,7 +20321,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G688" t="n">
-        <v>2.61097645759583</v>
+        <v>2.6109766960144</v>
       </c>
       <c r="H688" t="n">
         <v>540996</v>
@@ -20350,7 +20350,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G689" t="n">
-        <v>2.5857093334198</v>
+        <v>2.58570909500122</v>
       </c>
       <c r="H689" t="n">
         <v>835995</v>
@@ -20379,7 +20379,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G690" t="n">
-        <v>2.57560205459595</v>
+        <v>2.57560229301453</v>
       </c>
       <c r="H690" t="n">
         <v>1181402</v>
@@ -20408,7 +20408,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G691" t="n">
-        <v>2.49306154251099</v>
+        <v>2.49306178092957</v>
       </c>
       <c r="H691" t="n">
         <v>554383</v>
@@ -20524,7 +20524,7 @@
         <v>3.03200006484985</v>
       </c>
       <c r="G695" t="n">
-        <v>2.55370354652405</v>
+        <v>2.55370378494263</v>
       </c>
       <c r="H695" t="n">
         <v>176181</v>
@@ -20640,7 +20640,7 @@
         <v>3.06800007820129</v>
       </c>
       <c r="G699" t="n">
-        <v>2.58402490615845</v>
+        <v>2.58402466773987</v>
       </c>
       <c r="H699" t="n">
         <v>565902</v>
@@ -20872,7 +20872,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G707" t="n">
-        <v>2.5857093334198</v>
+        <v>2.58570909500122</v>
       </c>
       <c r="H707" t="n">
         <v>503676</v>
@@ -20959,7 +20959,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G710" t="n">
-        <v>2.50990676879883</v>
+        <v>2.50990653038025</v>
       </c>
       <c r="H710" t="n">
         <v>1933202</v>
@@ -20988,7 +20988,7 @@
         <v>3.01399993896484</v>
       </c>
       <c r="G711" t="n">
-        <v>2.53854322433472</v>
+        <v>2.53854298591614</v>
       </c>
       <c r="H711" t="n">
         <v>357710</v>
@@ -21017,7 +21017,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G712" t="n">
-        <v>2.50990676879883</v>
+        <v>2.50990653038025</v>
       </c>
       <c r="H712" t="n">
         <v>660930</v>
@@ -21075,7 +21075,7 @@
         <v>2.91400003433228</v>
       </c>
       <c r="G714" t="n">
-        <v>2.4543182849884</v>
+        <v>2.45431804656982</v>
       </c>
       <c r="H714" t="n">
         <v>482372</v>
@@ -21162,7 +21162,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G717" t="n">
-        <v>2.45600271224976</v>
+        <v>2.45600247383118</v>
       </c>
       <c r="H717" t="n">
         <v>519899</v>
@@ -21423,7 +21423,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G726" t="n">
-        <v>2.44926452636719</v>
+        <v>2.44926476478577</v>
       </c>
       <c r="H726" t="n">
         <v>2315220</v>
@@ -21655,7 +21655,7 @@
         <v>2.79200005531311</v>
       </c>
       <c r="G734" t="n">
-        <v>2.35156345367432</v>
+        <v>2.3515636920929</v>
       </c>
       <c r="H734" t="n">
         <v>407635</v>
@@ -21684,7 +21684,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G735" t="n">
-        <v>2.41388988494873</v>
+        <v>2.41389012336731</v>
       </c>
       <c r="H735" t="n">
         <v>672584</v>
@@ -21887,7 +21887,7 @@
         <v>3.04200005531311</v>
       </c>
       <c r="G742" t="n">
-        <v>2.56212639808655</v>
+        <v>2.56212615966797</v>
       </c>
       <c r="H742" t="n">
         <v>920296</v>
@@ -22003,7 +22003,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G746" t="n">
-        <v>2.48295450210571</v>
+        <v>2.48295474052429</v>
       </c>
       <c r="H746" t="n">
         <v>959673</v>
@@ -22177,7 +22177,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>2.49306154251099</v>
+        <v>2.49306178092957</v>
       </c>
       <c r="H752" t="n">
         <v>229054</v>
@@ -22293,7 +22293,7 @@
         <v>3.01399993896484</v>
       </c>
       <c r="G756" t="n">
-        <v>2.53854322433472</v>
+        <v>2.53854298591614</v>
       </c>
       <c r="H756" t="n">
         <v>339559</v>
@@ -22380,7 +22380,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G759" t="n">
-        <v>2.48295450210571</v>
+        <v>2.48295474052429</v>
       </c>
       <c r="H759" t="n">
         <v>299028</v>
@@ -22467,7 +22467,7 @@
         <v>3.03399991989136</v>
       </c>
       <c r="G762" t="n">
-        <v>2.5553879737854</v>
+        <v>2.55538821220398</v>
       </c>
       <c r="H762" t="n">
         <v>577970</v>
@@ -22583,7 +22583,7 @@
         <v>3.09599995613098</v>
       </c>
       <c r="G766" t="n">
-        <v>2.6076078414917</v>
+        <v>2.60760760307312</v>
       </c>
       <c r="H766" t="n">
         <v>954705</v>
@@ -22612,7 +22612,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G767" t="n">
-        <v>2.5772864818573</v>
+        <v>2.57728672027588</v>
       </c>
       <c r="H767" t="n">
         <v>598686</v>
@@ -22670,7 +22670,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G769" t="n">
-        <v>2.57560205459595</v>
+        <v>2.57560229301453</v>
       </c>
       <c r="H769" t="n">
         <v>237570</v>
@@ -22699,7 +22699,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G770" t="n">
-        <v>2.57223320007324</v>
+        <v>2.57223296165466</v>
       </c>
       <c r="H770" t="n">
         <v>235087</v>
@@ -22728,7 +22728,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G771" t="n">
-        <v>2.58907794952393</v>
+        <v>2.5890781879425</v>
       </c>
       <c r="H771" t="n">
         <v>233031</v>
@@ -22815,7 +22815,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G774" t="n">
-        <v>2.67835688591003</v>
+        <v>2.67835664749146</v>
       </c>
       <c r="H774" t="n">
         <v>844822</v>
@@ -22844,7 +22844,7 @@
         <v>3.14199995994568</v>
       </c>
       <c r="G775" t="n">
-        <v>2.64635109901428</v>
+        <v>2.64635133743286</v>
       </c>
       <c r="H775" t="n">
         <v>1054352</v>
@@ -22931,7 +22931,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G778" t="n">
-        <v>2.71710014343262</v>
+        <v>2.7171003818512</v>
       </c>
       <c r="H778" t="n">
         <v>964874</v>
@@ -22960,7 +22960,7 @@
         <v>3.20600008964539</v>
       </c>
       <c r="G779" t="n">
-        <v>2.70025539398193</v>
+        <v>2.70025515556335</v>
       </c>
       <c r="H779" t="n">
         <v>409180</v>
@@ -23076,7 +23076,7 @@
         <v>3.20600008964539</v>
       </c>
       <c r="G783" t="n">
-        <v>2.70025539398193</v>
+        <v>2.70025515556335</v>
       </c>
       <c r="H783" t="n">
         <v>938332</v>
@@ -23105,7 +23105,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G784" t="n">
-        <v>2.71710014343262</v>
+        <v>2.7171003818512</v>
       </c>
       <c r="H784" t="n">
         <v>578855</v>
@@ -23250,7 +23250,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G789" t="n">
-        <v>2.84680700302124</v>
+        <v>2.84680676460266</v>
       </c>
       <c r="H789" t="n">
         <v>815915</v>
@@ -23395,7 +23395,7 @@
         <v>3.14199995994568</v>
       </c>
       <c r="G794" t="n">
-        <v>2.64635109901428</v>
+        <v>2.64635133743286</v>
       </c>
       <c r="H794" t="n">
         <v>768072</v>
@@ -23627,7 +23627,7 @@
         <v>3.36800003051758</v>
       </c>
       <c r="G802" t="n">
-        <v>2.83669972419739</v>
+        <v>2.83669996261597</v>
       </c>
       <c r="H802" t="n">
         <v>706988</v>
@@ -23714,7 +23714,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G805" t="n">
-        <v>2.93776988983154</v>
+        <v>2.93776965141296</v>
       </c>
       <c r="H805" t="n">
         <v>557350</v>
@@ -23975,7 +23975,7 @@
         <v>3.38800001144409</v>
       </c>
       <c r="G814" t="n">
-        <v>2.85354495048523</v>
+        <v>2.85354471206665</v>
       </c>
       <c r="H814" t="n">
         <v>347337</v>
@@ -24091,7 +24091,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G818" t="n">
-        <v>2.45600271224976</v>
+        <v>2.45600247383118</v>
       </c>
       <c r="H818" t="n">
         <v>1497205</v>
@@ -24120,7 +24120,7 @@
         <v>3.00600004196167</v>
       </c>
       <c r="G819" t="n">
-        <v>2.53180527687073</v>
+        <v>2.53180503845215</v>
       </c>
       <c r="H819" t="n">
         <v>790572</v>
@@ -24526,7 +24526,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G833" t="n">
-        <v>2.69183301925659</v>
+        <v>2.69183278083801</v>
       </c>
       <c r="H833" t="n">
         <v>488767</v>
@@ -24555,7 +24555,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G834" t="n">
-        <v>2.67835688591003</v>
+        <v>2.67835664749146</v>
       </c>
       <c r="H834" t="n">
         <v>708286</v>
@@ -24584,7 +24584,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G835" t="n">
-        <v>2.65814256668091</v>
+        <v>2.65814280509949</v>
       </c>
       <c r="H835" t="n">
         <v>524048</v>
@@ -24642,7 +24642,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G837" t="n">
-        <v>2.67835688591003</v>
+        <v>2.67835664749146</v>
       </c>
       <c r="H837" t="n">
         <v>361053</v>
@@ -24700,7 +24700,7 @@
         <v>3.25</v>
       </c>
       <c r="G839" t="n">
-        <v>2.73731446266174</v>
+        <v>2.73731422424316</v>
       </c>
       <c r="H839" t="n">
         <v>461413</v>
@@ -24816,7 +24816,7 @@
         <v>3.25</v>
       </c>
       <c r="G843" t="n">
-        <v>2.73731446266174</v>
+        <v>2.73731422424316</v>
       </c>
       <c r="H843" t="n">
         <v>565490</v>
@@ -24961,7 +24961,7 @@
         <v>3.33599996566772</v>
       </c>
       <c r="G848" t="n">
-        <v>2.80974793434143</v>
+        <v>2.80974769592285</v>
       </c>
       <c r="H848" t="n">
         <v>1117559</v>
@@ -25251,7 +25251,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G858" t="n">
-        <v>2.7979564666748</v>
+        <v>2.79795622825623</v>
       </c>
       <c r="H858" t="n">
         <v>402306</v>
@@ -25338,7 +25338,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G861" t="n">
-        <v>2.78784942626953</v>
+        <v>2.78784918785095</v>
       </c>
       <c r="H861" t="n">
         <v>436318</v>
@@ -25483,7 +25483,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G866" t="n">
-        <v>2.68677926063538</v>
+        <v>2.68677949905396</v>
       </c>
       <c r="H866" t="n">
         <v>1350411</v>
@@ -25541,7 +25541,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G868" t="n">
-        <v>2.65814256668091</v>
+        <v>2.65814280509949</v>
       </c>
       <c r="H868" t="n">
         <v>1567922</v>
@@ -35320,6 +35320,64 @@
         <v>1727825</v>
       </c>
       <c r="I1205" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1206" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1206" t="n">
+        <v>2.12400007247925</v>
+      </c>
+      <c r="D1206" t="n">
+        <v>2.1340000629425</v>
+      </c>
+      <c r="E1206" t="n">
+        <v>2.05399990081787</v>
+      </c>
+      <c r="F1206" t="n">
+        <v>2.08599996566772</v>
+      </c>
+      <c r="G1206" t="n">
+        <v>2.08599996566772</v>
+      </c>
+      <c r="H1206" t="n">
+        <v>2982134</v>
+      </c>
+      <c r="I1206" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1207" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1207" t="n">
+        <v>2.08800005912781</v>
+      </c>
+      <c r="D1207" t="n">
+        <v>2.10999989509583</v>
+      </c>
+      <c r="E1207" t="n">
+        <v>2.06399989128113</v>
+      </c>
+      <c r="F1207" t="n">
+        <v>2.09800004959106</v>
+      </c>
+      <c r="G1207" t="n">
+        <v>2.09800004959106</v>
+      </c>
+      <c r="H1207" t="n">
+        <v>1948882</v>
+      </c>
+      <c r="I1207" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MFEA.MI.xlsx
+++ b/data/MFEA.MI.xlsx
@@ -485,7 +485,7 @@
         <v>3.71250009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>2.28881239891052</v>
+        <v>2.28881216049194</v>
       </c>
       <c r="H4" t="n">
         <v>267411</v>
@@ -601,7 +601,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G8" t="n">
-        <v>2.27494049072266</v>
+        <v>2.27494072914124</v>
       </c>
       <c r="H8" t="n">
         <v>174924</v>
@@ -630,7 +630,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G9" t="n">
-        <v>2.34892249107361</v>
+        <v>2.34892225265503</v>
       </c>
       <c r="H9" t="n">
         <v>257244</v>
@@ -717,7 +717,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G12" t="n">
-        <v>2.29035353660583</v>
+        <v>2.29035329818726</v>
       </c>
       <c r="H12" t="n">
         <v>185082</v>
@@ -775,7 +775,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G14" t="n">
-        <v>2.23178434371948</v>
+        <v>2.2317841053009</v>
       </c>
       <c r="H14" t="n">
         <v>244637</v>
@@ -833,7 +833,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6448495388031</v>
+        <v>2.64484977722168</v>
       </c>
       <c r="H16" t="n">
         <v>857484</v>
@@ -862,7 +862,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G17" t="n">
-        <v>2.69417071342468</v>
+        <v>2.69417095184326</v>
       </c>
       <c r="H17" t="n">
         <v>431766</v>
@@ -891,7 +891,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G18" t="n">
-        <v>2.66951036453247</v>
+        <v>2.66951012611389</v>
       </c>
       <c r="H18" t="n">
         <v>629452</v>
@@ -949,7 +949,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G20" t="n">
-        <v>2.61710643768311</v>
+        <v>2.61710619926453</v>
       </c>
       <c r="H20" t="n">
         <v>162925</v>
@@ -978,7 +978,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G21" t="n">
-        <v>2.64793252944946</v>
+        <v>2.64793229103088</v>
       </c>
       <c r="H21" t="n">
         <v>296725</v>
@@ -1036,7 +1036,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G23" t="n">
-        <v>2.49688625335693</v>
+        <v>2.49688601493835</v>
       </c>
       <c r="H23" t="n">
         <v>230967</v>
@@ -1239,7 +1239,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G30" t="n">
-        <v>2.41365647315979</v>
+        <v>2.41365623474121</v>
       </c>
       <c r="H30" t="n">
         <v>227564</v>
@@ -1268,7 +1268,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G31" t="n">
-        <v>2.4044086933136</v>
+        <v>2.40440893173218</v>
       </c>
       <c r="H31" t="n">
         <v>128224</v>
@@ -1297,7 +1297,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G32" t="n">
-        <v>2.25336265563965</v>
+        <v>2.25336241722107</v>
       </c>
       <c r="H32" t="n">
         <v>156121</v>
@@ -1326,7 +1326,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G33" t="n">
-        <v>2.21945428848267</v>
+        <v>2.21945405006409</v>
       </c>
       <c r="H33" t="n">
         <v>419876</v>
@@ -1442,7 +1442,7 @@
         <v>4.14249992370605</v>
       </c>
       <c r="G37" t="n">
-        <v>2.55391359329224</v>
+        <v>2.55391383171082</v>
       </c>
       <c r="H37" t="n">
         <v>310291</v>
@@ -1558,7 +1558,7 @@
         <v>3.5</v>
       </c>
       <c r="G41" t="n">
-        <v>2.15780258178711</v>
+        <v>2.15780282020569</v>
       </c>
       <c r="H41" t="n">
         <v>1105386</v>
@@ -1587,7 +1587,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G42" t="n">
-        <v>2.00983929634094</v>
+        <v>2.00983905792236</v>
       </c>
       <c r="H42" t="n">
         <v>975360</v>
@@ -1616,7 +1616,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G43" t="n">
-        <v>2.03449964523315</v>
+        <v>2.03449988365173</v>
       </c>
       <c r="H43" t="n">
         <v>404535</v>
@@ -1645,7 +1645,7 @@
         <v>3.3675000667572</v>
       </c>
       <c r="G44" t="n">
-        <v>2.07611465454102</v>
+        <v>2.07611441612244</v>
       </c>
       <c r="H44" t="n">
         <v>214683</v>
@@ -1877,7 +1877,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G52" t="n">
-        <v>1.99442625045776</v>
+        <v>1.99442613124847</v>
       </c>
       <c r="H52" t="n">
         <v>186459</v>
@@ -1906,7 +1906,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G53" t="n">
-        <v>1.97593069076538</v>
+        <v>1.97593057155609</v>
       </c>
       <c r="H53" t="n">
         <v>157204</v>
@@ -1964,7 +1964,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G55" t="n">
-        <v>1.82796692848206</v>
+        <v>1.82796716690063</v>
       </c>
       <c r="H55" t="n">
         <v>452826</v>
@@ -2022,7 +2022,7 @@
         <v>3</v>
       </c>
       <c r="G57" t="n">
-        <v>1.84954524040222</v>
+        <v>1.84954500198364</v>
       </c>
       <c r="H57" t="n">
         <v>234992</v>
@@ -2051,7 +2051,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G58" t="n">
-        <v>1.82488453388214</v>
+        <v>1.82488465309143</v>
       </c>
       <c r="H58" t="n">
         <v>168347</v>
@@ -2080,7 +2080,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G59" t="n">
-        <v>1.79405903816223</v>
+        <v>1.79405891895294</v>
       </c>
       <c r="H59" t="n">
         <v>174796</v>
@@ -2196,7 +2196,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G63" t="n">
-        <v>1.81255435943604</v>
+        <v>1.81255424022675</v>
       </c>
       <c r="H63" t="n">
         <v>134826</v>
@@ -2225,7 +2225,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G64" t="n">
-        <v>1.87728822231293</v>
+        <v>1.87728846073151</v>
       </c>
       <c r="H64" t="n">
         <v>324711</v>
@@ -2341,7 +2341,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G68" t="n">
-        <v>1.66150796413422</v>
+        <v>1.66150808334351</v>
       </c>
       <c r="H68" t="n">
         <v>213075</v>
@@ -2486,7 +2486,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G73" t="n">
-        <v>1.74165523052216</v>
+        <v>1.74165499210358</v>
       </c>
       <c r="H73" t="n">
         <v>228203</v>
@@ -2515,7 +2515,7 @@
         <v>2.75</v>
       </c>
       <c r="G74" t="n">
-        <v>1.69541656970978</v>
+        <v>1.6954163312912</v>
       </c>
       <c r="H74" t="n">
         <v>168732</v>
@@ -2544,7 +2544,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G75" t="n">
-        <v>1.66150796413422</v>
+        <v>1.66150808334351</v>
       </c>
       <c r="H75" t="n">
         <v>331684</v>
@@ -2602,7 +2602,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>1.64917767047882</v>
+        <v>1.64917778968811</v>
       </c>
       <c r="H77" t="n">
         <v>209971</v>
@@ -2631,7 +2631,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G78" t="n">
-        <v>1.74782025814056</v>
+        <v>1.74782049655914</v>
       </c>
       <c r="H78" t="n">
         <v>522442</v>
@@ -2660,7 +2660,7 @@
         <v>2.66750001907349</v>
       </c>
       <c r="G79" t="n">
-        <v>1.64455389976501</v>
+        <v>1.6445540189743</v>
       </c>
       <c r="H79" t="n">
         <v>468659</v>
@@ -2747,7 +2747,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G82" t="n">
-        <v>1.63068234920502</v>
+        <v>1.63068222999573</v>
       </c>
       <c r="H82" t="n">
         <v>172630</v>
@@ -2776,7 +2776,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G83" t="n">
-        <v>1.60910427570343</v>
+        <v>1.60910439491272</v>
       </c>
       <c r="H83" t="n">
         <v>216063</v>
@@ -2834,7 +2834,7 @@
         <v>2.58750009536743</v>
       </c>
       <c r="G85" t="n">
-        <v>1.59523284435272</v>
+        <v>1.59523296356201</v>
       </c>
       <c r="H85" t="n">
         <v>241301</v>
@@ -2921,7 +2921,7 @@
         <v>2.64750003814697</v>
       </c>
       <c r="G88" t="n">
-        <v>1.6322238445282</v>
+        <v>1.63222372531891</v>
       </c>
       <c r="H88" t="n">
         <v>842562</v>
@@ -2950,7 +2950,7 @@
         <v>2.65499997138977</v>
       </c>
       <c r="G89" t="n">
-        <v>1.636847615242</v>
+        <v>1.63684737682343</v>
       </c>
       <c r="H89" t="n">
         <v>285515</v>
@@ -3037,7 +3037,7 @@
         <v>2.66750001907349</v>
       </c>
       <c r="G92" t="n">
-        <v>1.64455389976501</v>
+        <v>1.6445540189743</v>
       </c>
       <c r="H92" t="n">
         <v>384701</v>
@@ -3066,7 +3066,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G93" t="n">
-        <v>1.63068234920502</v>
+        <v>1.63068222999573</v>
       </c>
       <c r="H93" t="n">
         <v>293851</v>
@@ -3095,7 +3095,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G94" t="n">
-        <v>1.63993012905121</v>
+        <v>1.6399302482605</v>
       </c>
       <c r="H94" t="n">
         <v>124415</v>
@@ -3124,7 +3124,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G95" t="n">
-        <v>1.59985661506653</v>
+        <v>1.59985673427582</v>
       </c>
       <c r="H95" t="n">
         <v>255560</v>
@@ -3153,7 +3153,7 @@
         <v>2.6324999332428</v>
       </c>
       <c r="G96" t="n">
-        <v>1.62297570705414</v>
+        <v>1.62297582626343</v>
       </c>
       <c r="H96" t="n">
         <v>316690</v>
@@ -3240,7 +3240,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>1.60602188110352</v>
+        <v>1.60602176189423</v>
       </c>
       <c r="H99" t="n">
         <v>524697</v>
@@ -3269,7 +3269,7 @@
         <v>2.45300006866455</v>
       </c>
       <c r="G100" t="n">
-        <v>1.51231145858765</v>
+        <v>1.51231157779694</v>
       </c>
       <c r="H100" t="n">
         <v>588672</v>
@@ -3327,7 +3327,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G102" t="n">
-        <v>1.47716999053955</v>
+        <v>1.47717010974884</v>
       </c>
       <c r="H102" t="n">
         <v>189949</v>
@@ -3356,7 +3356,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G103" t="n">
-        <v>1.45867466926575</v>
+        <v>1.45867478847504</v>
       </c>
       <c r="H103" t="n">
         <v>277983</v>
@@ -3443,7 +3443,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G106" t="n">
-        <v>1.39085793495178</v>
+        <v>1.39085805416107</v>
       </c>
       <c r="H106" t="n">
         <v>262719</v>
@@ -3472,7 +3472,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>1.33475518226624</v>
+        <v>1.33475506305695</v>
       </c>
       <c r="H107" t="n">
         <v>364496</v>
@@ -3501,7 +3501,7 @@
         <v>2.11899995803833</v>
       </c>
       <c r="G108" t="n">
-        <v>1.30639541149139</v>
+        <v>1.3063952922821</v>
       </c>
       <c r="H108" t="n">
         <v>333946</v>
@@ -3530,7 +3530,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G109" t="n">
-        <v>1.31934237480164</v>
+        <v>1.31934213638306</v>
       </c>
       <c r="H109" t="n">
         <v>149597</v>
@@ -3588,7 +3588,7 @@
         <v>2.18899989128113</v>
       </c>
       <c r="G111" t="n">
-        <v>1.34955143928528</v>
+        <v>1.34955155849457</v>
       </c>
       <c r="H111" t="n">
         <v>386160</v>
@@ -3617,7 +3617,7 @@
         <v>2.24900007247925</v>
       </c>
       <c r="G112" t="n">
-        <v>1.38654243946075</v>
+        <v>1.38654232025146</v>
       </c>
       <c r="H112" t="n">
         <v>617377</v>
@@ -3675,7 +3675,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G114" t="n">
-        <v>1.35016810894012</v>
+        <v>1.35016798973083</v>
       </c>
       <c r="H114" t="n">
         <v>374071</v>
@@ -3791,7 +3791,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G118" t="n">
-        <v>1.34708535671234</v>
+        <v>1.34708547592163</v>
       </c>
       <c r="H118" t="n">
         <v>844960</v>
@@ -3820,7 +3820,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G119" t="n">
-        <v>1.38099372386932</v>
+        <v>1.38099384307861</v>
       </c>
       <c r="H119" t="n">
         <v>296846</v>
@@ -3878,7 +3878,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G121" t="n">
-        <v>1.40565431118011</v>
+        <v>1.4056544303894</v>
       </c>
       <c r="H121" t="n">
         <v>1163100</v>
@@ -3907,7 +3907,7 @@
         <v>2.22099995613098</v>
       </c>
       <c r="G122" t="n">
-        <v>1.36928009986877</v>
+        <v>1.3692798614502</v>
       </c>
       <c r="H122" t="n">
         <v>2110801</v>
@@ -3936,7 +3936,7 @@
         <v>2.18300008773804</v>
       </c>
       <c r="G123" t="n">
-        <v>1.34585237503052</v>
+        <v>1.34585249423981</v>
       </c>
       <c r="H123" t="n">
         <v>1057822</v>
@@ -4023,7 +4023,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G126" t="n">
-        <v>1.29344856739044</v>
+        <v>1.29344868659973</v>
       </c>
       <c r="H126" t="n">
         <v>553530</v>
@@ -4052,7 +4052,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G127" t="n">
-        <v>1.33043956756592</v>
+        <v>1.33043944835663</v>
       </c>
       <c r="H127" t="n">
         <v>576146</v>
@@ -4081,7 +4081,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G128" t="n">
-        <v>1.35325050354004</v>
+        <v>1.35325062274933</v>
       </c>
       <c r="H128" t="n">
         <v>1234804</v>
@@ -4110,7 +4110,7 @@
         <v>2.13700008392334</v>
       </c>
       <c r="G129" t="n">
-        <v>1.31749284267426</v>
+        <v>1.31749272346497</v>
       </c>
       <c r="H129" t="n">
         <v>756330</v>
@@ -4139,7 +4139,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G130" t="n">
-        <v>1.37791121006012</v>
+        <v>1.37791109085083</v>
       </c>
       <c r="H130" t="n">
         <v>658168</v>
@@ -4168,7 +4168,7 @@
         <v>2.21399998664856</v>
       </c>
       <c r="G131" t="n">
-        <v>1.36496436595917</v>
+        <v>1.36496424674988</v>
       </c>
       <c r="H131" t="n">
         <v>425795</v>
@@ -4226,7 +4226,7 @@
         <v>2.02699995040894</v>
       </c>
       <c r="G133" t="n">
-        <v>1.24967610836029</v>
+        <v>1.249675989151</v>
       </c>
       <c r="H133" t="n">
         <v>1799201</v>
@@ -4255,7 +4255,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>1.28543376922607</v>
+        <v>1.28543388843536</v>
       </c>
       <c r="H134" t="n">
         <v>1315577</v>
@@ -4284,7 +4284,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G135" t="n">
-        <v>1.35016810894012</v>
+        <v>1.35016798973083</v>
       </c>
       <c r="H135" t="n">
         <v>888081</v>
@@ -4313,7 +4313,7 @@
         <v>2.20099997520447</v>
       </c>
       <c r="G136" t="n">
-        <v>1.3569495677948</v>
+        <v>1.35694968700409</v>
       </c>
       <c r="H136" t="n">
         <v>597261</v>
@@ -4371,7 +4371,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G138" t="n">
-        <v>1.32304120063782</v>
+        <v>1.32304131984711</v>
       </c>
       <c r="H138" t="n">
         <v>662539</v>
@@ -4429,7 +4429,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G140" t="n">
-        <v>1.27926886081696</v>
+        <v>1.27926874160767</v>
       </c>
       <c r="H140" t="n">
         <v>489036</v>
@@ -4458,7 +4458,7 @@
         <v>2.08400011062622</v>
       </c>
       <c r="G141" t="n">
-        <v>1.2848174571991</v>
+        <v>1.28481757640839</v>
       </c>
       <c r="H141" t="n">
         <v>2061793</v>
@@ -4487,7 +4487,7 @@
         <v>2.125</v>
       </c>
       <c r="G142" t="n">
-        <v>1.31009447574615</v>
+        <v>1.31009459495544</v>
       </c>
       <c r="H142" t="n">
         <v>1089881</v>
@@ -4545,7 +4545,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G144" t="n">
-        <v>1.35386717319489</v>
+        <v>1.35386729240417</v>
       </c>
       <c r="H144" t="n">
         <v>698399</v>
@@ -4574,7 +4574,7 @@
         <v>2.30900001525879</v>
       </c>
       <c r="G145" t="n">
-        <v>1.42353320121765</v>
+        <v>1.42353332042694</v>
       </c>
       <c r="H145" t="n">
         <v>1061376</v>
@@ -4603,7 +4603,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G146" t="n">
-        <v>1.40257179737091</v>
+        <v>1.4025719165802</v>
       </c>
       <c r="H146" t="n">
         <v>463835</v>
@@ -4632,7 +4632,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G147" t="n">
-        <v>1.35325050354004</v>
+        <v>1.35325062274933</v>
       </c>
       <c r="H147" t="n">
         <v>729575</v>
@@ -4661,7 +4661,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G148" t="n">
-        <v>1.35633325576782</v>
+        <v>1.35633301734924</v>
       </c>
       <c r="H148" t="n">
         <v>470520</v>
@@ -4719,7 +4719,7 @@
         <v>2.04699993133545</v>
       </c>
       <c r="G150" t="n">
-        <v>1.26200640201569</v>
+        <v>1.2620062828064</v>
       </c>
       <c r="H150" t="n">
         <v>1302379</v>
@@ -4806,7 +4806,7 @@
         <v>2.02099990844727</v>
       </c>
       <c r="G153" t="n">
-        <v>1.24597680568695</v>
+        <v>1.24597692489624</v>
       </c>
       <c r="H153" t="n">
         <v>550560</v>
@@ -4864,7 +4864,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G155" t="n">
-        <v>1.28235125541687</v>
+        <v>1.28235137462616</v>
       </c>
       <c r="H155" t="n">
         <v>897371</v>
@@ -4922,7 +4922,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G157" t="n">
-        <v>1.30392932891846</v>
+        <v>1.30392944812775</v>
       </c>
       <c r="H157" t="n">
         <v>621284</v>
@@ -5038,7 +5038,7 @@
         <v>2.08899998664856</v>
       </c>
       <c r="G161" t="n">
-        <v>1.28789985179901</v>
+        <v>1.2878999710083</v>
       </c>
       <c r="H161" t="n">
         <v>544349</v>
@@ -5067,7 +5067,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G162" t="n">
-        <v>1.28235125541687</v>
+        <v>1.28235137462616</v>
       </c>
       <c r="H162" t="n">
         <v>320464</v>
@@ -5096,7 +5096,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G163" t="n">
-        <v>1.28235125541687</v>
+        <v>1.28235137462616</v>
       </c>
       <c r="H163" t="n">
         <v>665085</v>
@@ -5125,7 +5125,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G164" t="n">
-        <v>1.31625974178314</v>
+        <v>1.31625962257385</v>
       </c>
       <c r="H164" t="n">
         <v>1321946</v>
@@ -5183,7 +5183,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G166" t="n">
-        <v>1.28543376922607</v>
+        <v>1.28543388843536</v>
       </c>
       <c r="H166" t="n">
         <v>925875</v>
@@ -5241,7 +5241,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G168" t="n">
-        <v>1.24782657623291</v>
+        <v>1.24782633781433</v>
       </c>
       <c r="H168" t="n">
         <v>1017897</v>
@@ -5270,7 +5270,7 @@
         <v>1.99899995326996</v>
       </c>
       <c r="G169" t="n">
-        <v>1.23241353034973</v>
+        <v>1.23241364955902</v>
       </c>
       <c r="H169" t="n">
         <v>2003498</v>
@@ -5328,7 +5328,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G171" t="n">
-        <v>1.20140945911407</v>
+        <v>1.20140957832336</v>
       </c>
       <c r="H171" t="n">
         <v>1719560</v>
@@ -5386,7 +5386,7 @@
         <v>1.65199995040894</v>
       </c>
       <c r="G173" t="n">
-        <v>1.16406357288361</v>
+        <v>1.16406345367432</v>
       </c>
       <c r="H173" t="n">
         <v>1205156</v>
@@ -5705,7 +5705,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G184" t="n">
-        <v>1.08796262741089</v>
+        <v>1.08796274662018</v>
       </c>
       <c r="H184" t="n">
         <v>1603167</v>
@@ -5734,7 +5734,7 @@
         <v>1.50899994373322</v>
       </c>
       <c r="G185" t="n">
-        <v>1.06330013275146</v>
+        <v>1.06330025196075</v>
       </c>
       <c r="H185" t="n">
         <v>762123</v>
@@ -5966,7 +5966,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>1.15913116931915</v>
+        <v>1.15913105010986</v>
       </c>
       <c r="H193" t="n">
         <v>574328</v>
@@ -5995,7 +5995,7 @@
         <v>1.62300002574921</v>
       </c>
       <c r="G194" t="n">
-        <v>1.14362895488739</v>
+        <v>1.14362919330597</v>
       </c>
       <c r="H194" t="n">
         <v>1339210</v>
@@ -6024,7 +6024,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G195" t="n">
-        <v>1.16265428066254</v>
+        <v>1.16265451908112</v>
       </c>
       <c r="H195" t="n">
         <v>1118932</v>
@@ -6343,7 +6343,7 @@
         <v>1.84399998188019</v>
       </c>
       <c r="G206" t="n">
-        <v>1.29935419559479</v>
+        <v>1.29935431480408</v>
       </c>
       <c r="H206" t="n">
         <v>1182791</v>
@@ -6459,7 +6459,7 @@
         <v>1.91100001335144</v>
       </c>
       <c r="G210" t="n">
-        <v>1.34656524658203</v>
+        <v>1.34656512737274</v>
       </c>
       <c r="H210" t="n">
         <v>522665</v>
@@ -6546,7 +6546,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G213" t="n">
-        <v>1.28737545013428</v>
+        <v>1.28737556934357</v>
       </c>
       <c r="H213" t="n">
         <v>677501</v>
@@ -6575,7 +6575,7 @@
         <v>1.81099998950958</v>
       </c>
       <c r="G214" t="n">
-        <v>1.2761013507843</v>
+        <v>1.27610111236572</v>
       </c>
       <c r="H214" t="n">
         <v>308754</v>
@@ -6720,7 +6720,7 @@
         <v>2.04699993133545</v>
       </c>
       <c r="G219" t="n">
-        <v>1.44239592552185</v>
+        <v>1.44239604473114</v>
       </c>
       <c r="H219" t="n">
         <v>1110213</v>
@@ -6923,7 +6923,7 @@
         <v>1.93099999427795</v>
       </c>
       <c r="G226" t="n">
-        <v>1.36065781116486</v>
+        <v>1.36065793037415</v>
       </c>
       <c r="H226" t="n">
         <v>764236</v>
@@ -6952,7 +6952,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G227" t="n">
-        <v>1.33035838603973</v>
+        <v>1.33035850524902</v>
       </c>
       <c r="H227" t="n">
         <v>521176</v>
@@ -7097,7 +7097,7 @@
         <v>1.86300003528595</v>
       </c>
       <c r="G232" t="n">
-        <v>1.31274235248566</v>
+        <v>1.31274259090424</v>
       </c>
       <c r="H232" t="n">
         <v>190892</v>
@@ -7155,7 +7155,7 @@
         <v>1.75899994373322</v>
       </c>
       <c r="G234" t="n">
-        <v>1.23945999145508</v>
+        <v>1.23945987224579</v>
       </c>
       <c r="H234" t="n">
         <v>433004</v>
@@ -7329,7 +7329,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G240" t="n">
-        <v>1.27891981601715</v>
+        <v>1.27891993522644</v>
       </c>
       <c r="H240" t="n">
         <v>206556</v>
@@ -7358,7 +7358,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G241" t="n">
-        <v>1.26482701301575</v>
+        <v>1.26482689380646</v>
       </c>
       <c r="H241" t="n">
         <v>338837</v>
@@ -7387,7 +7387,7 @@
         <v>1.81900000572205</v>
       </c>
       <c r="G242" t="n">
-        <v>1.28173828125</v>
+        <v>1.28173840045929</v>
       </c>
       <c r="H242" t="n">
         <v>160229</v>
@@ -7590,7 +7590,7 @@
         <v>1.94099998474121</v>
       </c>
       <c r="G249" t="n">
-        <v>1.3677042722702</v>
+        <v>1.36770439147949</v>
       </c>
       <c r="H249" t="n">
         <v>394746</v>
@@ -7619,7 +7619,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G250" t="n">
-        <v>1.3698183298111</v>
+        <v>1.36981821060181</v>
       </c>
       <c r="H250" t="n">
         <v>296376</v>
@@ -7764,7 +7764,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G255" t="n">
-        <v>1.4198477268219</v>
+        <v>1.41984760761261</v>
       </c>
       <c r="H255" t="n">
         <v>809777</v>
@@ -7793,7 +7793,7 @@
         <v>1.98699998855591</v>
       </c>
       <c r="G256" t="n">
-        <v>1.40011775493622</v>
+        <v>1.40011763572693</v>
       </c>
       <c r="H256" t="n">
         <v>400869</v>
@@ -7851,7 +7851,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G258" t="n">
-        <v>1.39236652851105</v>
+        <v>1.39236664772034</v>
       </c>
       <c r="H258" t="n">
         <v>262724</v>
@@ -7967,7 +7967,7 @@
         <v>2.00600004196167</v>
       </c>
       <c r="G262" t="n">
-        <v>1.4135057926178</v>
+        <v>1.41350591182709</v>
       </c>
       <c r="H262" t="n">
         <v>717038</v>
@@ -7996,7 +7996,7 @@
         <v>1.97200000286102</v>
       </c>
       <c r="G263" t="n">
-        <v>1.38954818248749</v>
+        <v>1.3895480632782</v>
       </c>
       <c r="H263" t="n">
         <v>310392</v>
@@ -8054,7 +8054,7 @@
         <v>2.01300001144409</v>
       </c>
       <c r="G265" t="n">
-        <v>1.41843831539154</v>
+        <v>1.41843843460083</v>
       </c>
       <c r="H265" t="n">
         <v>1394290</v>
@@ -8170,7 +8170,7 @@
         <v>2.20600008964539</v>
       </c>
       <c r="G269" t="n">
-        <v>1.55443370342255</v>
+        <v>1.55443382263184</v>
       </c>
       <c r="H269" t="n">
         <v>461170</v>
@@ -8228,7 +8228,7 @@
         <v>2.18300008773804</v>
       </c>
       <c r="G271" t="n">
-        <v>1.53822708129883</v>
+        <v>1.53822696208954</v>
       </c>
       <c r="H271" t="n">
         <v>558105</v>
@@ -8257,7 +8257,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G272" t="n">
-        <v>1.53329455852509</v>
+        <v>1.5332944393158</v>
       </c>
       <c r="H272" t="n">
         <v>539558</v>
@@ -8286,7 +8286,7 @@
         <v>2.125</v>
       </c>
       <c r="G273" t="n">
-        <v>1.49735796451569</v>
+        <v>1.4973578453064</v>
       </c>
       <c r="H273" t="n">
         <v>544273</v>
@@ -8373,7 +8373,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G276" t="n">
-        <v>1.48819756507874</v>
+        <v>1.48819744586945</v>
       </c>
       <c r="H276" t="n">
         <v>185994</v>
@@ -8518,7 +8518,7 @@
         <v>2.03699994087219</v>
       </c>
       <c r="G281" t="n">
-        <v>1.43534970283508</v>
+        <v>1.43534958362579</v>
       </c>
       <c r="H281" t="n">
         <v>774489</v>
@@ -8605,7 +8605,7 @@
         <v>2.07599997520447</v>
       </c>
       <c r="G284" t="n">
-        <v>1.46283054351807</v>
+        <v>1.46283066272736</v>
       </c>
       <c r="H284" t="n">
         <v>725403</v>
@@ -8634,7 +8634,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G285" t="n">
-        <v>1.46564912796021</v>
+        <v>1.46564900875092</v>
       </c>
       <c r="H285" t="n">
         <v>331486</v>
@@ -8663,7 +8663,7 @@
         <v>2.05299997329712</v>
       </c>
       <c r="G286" t="n">
-        <v>1.44662392139435</v>
+        <v>1.44662380218506</v>
       </c>
       <c r="H286" t="n">
         <v>680373</v>
@@ -8808,7 +8808,7 @@
         <v>2.14100003242493</v>
       </c>
       <c r="G291" t="n">
-        <v>1.50863218307495</v>
+        <v>1.50863206386566</v>
       </c>
       <c r="H291" t="n">
         <v>308198</v>
@@ -8895,7 +8895,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G294" t="n">
-        <v>1.46705842018127</v>
+        <v>1.46705853939056</v>
       </c>
       <c r="H294" t="n">
         <v>796702</v>
@@ -8924,7 +8924,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G295" t="n">
-        <v>1.51074612140656</v>
+        <v>1.51074600219727</v>
       </c>
       <c r="H295" t="n">
         <v>440171</v>
@@ -8953,7 +8953,7 @@
         <v>2.125</v>
       </c>
       <c r="G296" t="n">
-        <v>1.49735796451569</v>
+        <v>1.4973578453064</v>
       </c>
       <c r="H296" t="n">
         <v>636274</v>
@@ -9011,7 +9011,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G298" t="n">
-        <v>1.47551417350769</v>
+        <v>1.4755140542984</v>
       </c>
       <c r="H298" t="n">
         <v>739456</v>
@@ -9069,7 +9069,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G300" t="n">
-        <v>1.51215517520905</v>
+        <v>1.51215529441833</v>
       </c>
       <c r="H300" t="n">
         <v>616627</v>
@@ -9127,7 +9127,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G302" t="n">
-        <v>1.52202022075653</v>
+        <v>1.52202033996582</v>
       </c>
       <c r="H302" t="n">
         <v>208214</v>
@@ -9243,7 +9243,7 @@
         <v>2.12100005149841</v>
       </c>
       <c r="G306" t="n">
-        <v>1.49453938007355</v>
+        <v>1.49453926086426</v>
       </c>
       <c r="H306" t="n">
         <v>349362</v>
@@ -9388,7 +9388,7 @@
         <v>2.18300008773804</v>
       </c>
       <c r="G311" t="n">
-        <v>1.53822708129883</v>
+        <v>1.53822696208954</v>
       </c>
       <c r="H311" t="n">
         <v>1223387</v>
@@ -9446,7 +9446,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G313" t="n">
-        <v>1.61855578422546</v>
+        <v>1.61855566501617</v>
       </c>
       <c r="H313" t="n">
         <v>610651</v>
@@ -9504,7 +9504,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G315" t="n">
-        <v>1.61855578422546</v>
+        <v>1.61855566501617</v>
       </c>
       <c r="H315" t="n">
         <v>297781</v>
@@ -9533,7 +9533,7 @@
         <v>2.27300000190735</v>
       </c>
       <c r="G316" t="n">
-        <v>1.60164451599121</v>
+        <v>1.60164427757263</v>
       </c>
       <c r="H316" t="n">
         <v>370098</v>
@@ -9562,7 +9562,7 @@
         <v>2.27300000190735</v>
       </c>
       <c r="G317" t="n">
-        <v>1.60164451599121</v>
+        <v>1.60164427757263</v>
       </c>
       <c r="H317" t="n">
         <v>460584</v>
@@ -9591,7 +9591,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G318" t="n">
-        <v>1.60305368900299</v>
+        <v>1.60305380821228</v>
       </c>
       <c r="H318" t="n">
         <v>434199</v>
@@ -9620,7 +9620,7 @@
         <v>2.29299998283386</v>
       </c>
       <c r="G319" t="n">
-        <v>1.61573719978333</v>
+        <v>1.61573731899261</v>
       </c>
       <c r="H319" t="n">
         <v>855625</v>
@@ -9649,7 +9649,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G320" t="n">
-        <v>1.62489759922028</v>
+        <v>1.62489748001099</v>
       </c>
       <c r="H320" t="n">
         <v>946396</v>
@@ -9678,7 +9678,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G321" t="n">
-        <v>1.63758087158203</v>
+        <v>1.63758099079132</v>
       </c>
       <c r="H321" t="n">
         <v>897308</v>
@@ -9736,7 +9736,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G323" t="n">
-        <v>1.60234880447388</v>
+        <v>1.60234904289246</v>
       </c>
       <c r="H323" t="n">
         <v>324411</v>
@@ -9794,7 +9794,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G325" t="n">
-        <v>1.57416367530823</v>
+        <v>1.57416355609894</v>
       </c>
       <c r="H325" t="n">
         <v>449454</v>
@@ -9823,7 +9823,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G326" t="n">
-        <v>1.51074612140656</v>
+        <v>1.51074600219727</v>
       </c>
       <c r="H326" t="n">
         <v>964268</v>
@@ -9852,7 +9852,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G327" t="n">
-        <v>1.47128617763519</v>
+        <v>1.47128629684448</v>
       </c>
       <c r="H327" t="n">
         <v>1679948</v>
@@ -9968,7 +9968,7 @@
         <v>2.25</v>
       </c>
       <c r="G331" t="n">
-        <v>1.58543789386749</v>
+        <v>1.5854377746582</v>
       </c>
       <c r="H331" t="n">
         <v>523276</v>
@@ -9997,7 +9997,7 @@
         <v>2.22099995613098</v>
       </c>
       <c r="G332" t="n">
-        <v>1.56500327587128</v>
+        <v>1.56500315666199</v>
       </c>
       <c r="H332" t="n">
         <v>221480</v>
@@ -10055,7 +10055,7 @@
         <v>2.25</v>
       </c>
       <c r="G334" t="n">
-        <v>1.58543789386749</v>
+        <v>1.5854377746582</v>
       </c>
       <c r="H334" t="n">
         <v>841797</v>
@@ -10084,7 +10084,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G335" t="n">
-        <v>1.57698202133179</v>
+        <v>1.5769819021225</v>
       </c>
       <c r="H335" t="n">
         <v>717837</v>
@@ -10113,7 +10113,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G336" t="n">
-        <v>1.61855578422546</v>
+        <v>1.61855566501617</v>
       </c>
       <c r="H336" t="n">
         <v>709843</v>
@@ -10142,7 +10142,7 @@
         <v>2.28299999237061</v>
       </c>
       <c r="G337" t="n">
-        <v>1.60869085788727</v>
+        <v>1.60869073867798</v>
       </c>
       <c r="H337" t="n">
         <v>602165</v>
@@ -10229,7 +10229,7 @@
         <v>2.40300011634827</v>
       </c>
       <c r="G340" t="n">
-        <v>1.6932475566864</v>
+        <v>1.69324767589569</v>
       </c>
       <c r="H340" t="n">
         <v>735566</v>
@@ -10258,7 +10258,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G341" t="n">
-        <v>1.6594250202179</v>
+        <v>1.65942478179932</v>
       </c>
       <c r="H341" t="n">
         <v>442544</v>
@@ -10287,7 +10287,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>1.6453320980072</v>
+        <v>1.64533221721649</v>
       </c>
       <c r="H342" t="n">
         <v>505221</v>
@@ -10316,7 +10316,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G343" t="n">
-        <v>1.61010003089905</v>
+        <v>1.61010026931763</v>
       </c>
       <c r="H343" t="n">
         <v>391481</v>
@@ -10345,7 +10345,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G344" t="n">
-        <v>1.66294801235199</v>
+        <v>1.6629478931427</v>
       </c>
       <c r="H344" t="n">
         <v>625059</v>
@@ -10374,7 +10374,7 @@
         <v>2.33699989318848</v>
       </c>
       <c r="G345" t="n">
-        <v>1.64674139022827</v>
+        <v>1.64674127101898</v>
       </c>
       <c r="H345" t="n">
         <v>1238842</v>
@@ -10403,7 +10403,7 @@
         <v>2.33699989318848</v>
       </c>
       <c r="G346" t="n">
-        <v>1.64674139022827</v>
+        <v>1.64674127101898</v>
       </c>
       <c r="H346" t="n">
         <v>580707</v>
@@ -10432,7 +10432,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G347" t="n">
-        <v>1.62912535667419</v>
+        <v>1.62912547588348</v>
       </c>
       <c r="H347" t="n">
         <v>376051</v>
@@ -10461,7 +10461,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G348" t="n">
-        <v>1.56147992610931</v>
+        <v>1.56148016452789</v>
       </c>
       <c r="H348" t="n">
         <v>2800039</v>
@@ -10548,7 +10548,7 @@
         <v>2.19400000572205</v>
       </c>
       <c r="G351" t="n">
-        <v>1.54597806930542</v>
+        <v>1.54597795009613</v>
       </c>
       <c r="H351" t="n">
         <v>432046</v>
@@ -10606,7 +10606,7 @@
         <v>2.27099990844727</v>
       </c>
       <c r="G353" t="n">
-        <v>1.60023522377014</v>
+        <v>1.60023510456085</v>
       </c>
       <c r="H353" t="n">
         <v>454310</v>
@@ -10635,7 +10635,7 @@
         <v>2.26900005340576</v>
       </c>
       <c r="G354" t="n">
-        <v>1.59882581233978</v>
+        <v>1.59882605075836</v>
       </c>
       <c r="H354" t="n">
         <v>579865</v>
@@ -10693,7 +10693,7 @@
         <v>2.50250005722046</v>
       </c>
       <c r="G356" t="n">
-        <v>1.76335918903351</v>
+        <v>1.76335906982422</v>
       </c>
       <c r="H356" t="n">
         <v>4862397</v>
@@ -10722,7 +10722,7 @@
         <v>2.83750009536743</v>
       </c>
       <c r="G357" t="n">
-        <v>1.99941301345825</v>
+        <v>1.99941325187683</v>
       </c>
       <c r="H357" t="n">
         <v>4829114</v>
@@ -10751,7 +10751,7 @@
         <v>2.7574999332428</v>
       </c>
       <c r="G358" t="n">
-        <v>1.94304203987122</v>
+        <v>1.94304215908051</v>
       </c>
       <c r="H358" t="n">
         <v>5360863</v>
@@ -10809,7 +10809,7 @@
         <v>2.69749999046326</v>
       </c>
       <c r="G360" t="n">
-        <v>1.90076375007629</v>
+        <v>1.900763630867</v>
       </c>
       <c r="H360" t="n">
         <v>2325561</v>
@@ -10838,7 +10838,7 @@
         <v>2.65750002861023</v>
       </c>
       <c r="G361" t="n">
-        <v>1.87257826328278</v>
+        <v>1.87257814407349</v>
       </c>
       <c r="H361" t="n">
         <v>670603</v>
@@ -10867,7 +10867,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G362" t="n">
-        <v>1.81444549560547</v>
+        <v>1.81444537639618</v>
       </c>
       <c r="H362" t="n">
         <v>1637436</v>
@@ -10896,7 +10896,7 @@
         <v>2.54250001907349</v>
       </c>
       <c r="G363" t="n">
-        <v>1.79154443740845</v>
+        <v>1.79154467582703</v>
       </c>
       <c r="H363" t="n">
         <v>394519</v>
@@ -10983,7 +10983,7 @@
         <v>2.50250005722046</v>
       </c>
       <c r="G366" t="n">
-        <v>1.76335918903351</v>
+        <v>1.76335906982422</v>
       </c>
       <c r="H366" t="n">
         <v>920397</v>
@@ -11099,7 +11099,7 @@
         <v>2.5550000667572</v>
       </c>
       <c r="G370" t="n">
-        <v>1.80035281181335</v>
+        <v>1.80035269260406</v>
       </c>
       <c r="H370" t="n">
         <v>510079</v>
@@ -11128,7 +11128,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G371" t="n">
-        <v>1.83206140995026</v>
+        <v>1.83206129074097</v>
       </c>
       <c r="H371" t="n">
         <v>521311</v>
@@ -11215,7 +11215,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G374" t="n">
-        <v>1.83910763263702</v>
+        <v>1.83910775184631</v>
       </c>
       <c r="H374" t="n">
         <v>564472</v>
@@ -11244,7 +11244,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G375" t="n">
-        <v>1.83910763263702</v>
+        <v>1.83910775184631</v>
       </c>
       <c r="H375" t="n">
         <v>442703</v>
@@ -11273,7 +11273,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G376" t="n">
-        <v>1.86377024650574</v>
+        <v>1.86377012729645</v>
       </c>
       <c r="H376" t="n">
         <v>303450</v>
@@ -11302,7 +11302,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G377" t="n">
-        <v>1.86377024650574</v>
+        <v>1.86377012729645</v>
       </c>
       <c r="H377" t="n">
         <v>377689</v>
@@ -11331,7 +11331,7 @@
         <v>2.6324999332428</v>
       </c>
       <c r="G378" t="n">
-        <v>1.85496211051941</v>
+        <v>1.85496199131012</v>
       </c>
       <c r="H378" t="n">
         <v>460839</v>
@@ -11360,7 +11360,7 @@
         <v>2.64249992370605</v>
       </c>
       <c r="G379" t="n">
-        <v>1.86200857162476</v>
+        <v>1.86200869083405</v>
       </c>
       <c r="H379" t="n">
         <v>662990</v>
@@ -11389,7 +11389,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>1.86377024650574</v>
+        <v>1.86377012729645</v>
       </c>
       <c r="H380" t="n">
         <v>668827</v>
@@ -11418,7 +11418,7 @@
         <v>2.59750008583069</v>
       </c>
       <c r="G381" t="n">
-        <v>1.83029997348785</v>
+        <v>1.83029973506927</v>
       </c>
       <c r="H381" t="n">
         <v>623499</v>
@@ -11447,7 +11447,7 @@
         <v>2.6324999332428</v>
       </c>
       <c r="G382" t="n">
-        <v>1.85496211051941</v>
+        <v>1.85496199131012</v>
       </c>
       <c r="H382" t="n">
         <v>848076</v>
@@ -11563,7 +11563,7 @@
         <v>2.35700011253357</v>
       </c>
       <c r="G386" t="n">
-        <v>1.8411637544632</v>
+        <v>1.84116351604462</v>
       </c>
       <c r="H386" t="n">
         <v>1675723</v>
@@ -11679,7 +11679,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G390" t="n">
-        <v>1.85131847858429</v>
+        <v>1.85131824016571</v>
       </c>
       <c r="H390" t="n">
         <v>717045</v>
@@ -11708,7 +11708,7 @@
         <v>2.40700006484985</v>
       </c>
       <c r="G391" t="n">
-        <v>1.88022089004517</v>
+        <v>1.88022112846375</v>
       </c>
       <c r="H391" t="n">
         <v>1427819</v>
@@ -11795,7 +11795,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G394" t="n">
-        <v>1.81694805622101</v>
+        <v>1.81694793701172</v>
       </c>
       <c r="H394" t="n">
         <v>634308</v>
@@ -11824,7 +11824,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G395" t="n">
-        <v>1.84506916999817</v>
+        <v>1.84506940841675</v>
       </c>
       <c r="H395" t="n">
         <v>768257</v>
@@ -11853,7 +11853,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G396" t="n">
-        <v>1.81694805622101</v>
+        <v>1.81694793701172</v>
       </c>
       <c r="H396" t="n">
         <v>564016</v>
@@ -11882,7 +11882,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G397" t="n">
-        <v>1.79429471492767</v>
+        <v>1.79429459571838</v>
       </c>
       <c r="H397" t="n">
         <v>625118</v>
@@ -11940,7 +11940,7 @@
         <v>2.3289999961853</v>
       </c>
       <c r="G399" t="n">
-        <v>1.819291472435</v>
+        <v>1.81929135322571</v>
       </c>
       <c r="H399" t="n">
         <v>717310</v>
@@ -11998,7 +11998,7 @@
         <v>2.30800008773804</v>
       </c>
       <c r="G401" t="n">
-        <v>1.80288755893707</v>
+        <v>1.80288732051849</v>
       </c>
       <c r="H401" t="n">
         <v>290608</v>
@@ -12201,7 +12201,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G408" t="n">
-        <v>1.78257751464844</v>
+        <v>1.78257763385773</v>
       </c>
       <c r="H408" t="n">
         <v>720575</v>
@@ -12317,7 +12317,7 @@
         <v>2.3289999961853</v>
       </c>
       <c r="G412" t="n">
-        <v>1.819291472435</v>
+        <v>1.81929135322571</v>
       </c>
       <c r="H412" t="n">
         <v>1092003</v>
@@ -12346,7 +12346,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G413" t="n">
-        <v>1.82397830486298</v>
+        <v>1.82397842407227</v>
       </c>
       <c r="H413" t="n">
         <v>525566</v>
@@ -12404,7 +12404,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G415" t="n">
-        <v>1.79351353645325</v>
+        <v>1.79351365566254</v>
       </c>
       <c r="H415" t="n">
         <v>274714</v>
@@ -12491,7 +12491,7 @@
         <v>2.26099991798401</v>
       </c>
       <c r="G418" t="n">
-        <v>1.76617336273193</v>
+        <v>1.76617348194122</v>
       </c>
       <c r="H418" t="n">
         <v>422740</v>
@@ -12520,7 +12520,7 @@
         <v>2.23699998855591</v>
       </c>
       <c r="G419" t="n">
-        <v>1.74742603302002</v>
+        <v>1.74742591381073</v>
       </c>
       <c r="H419" t="n">
         <v>1089414</v>
@@ -12723,7 +12723,7 @@
         <v>2.11700010299683</v>
       </c>
       <c r="G426" t="n">
-        <v>1.65368831157684</v>
+        <v>1.65368843078613</v>
       </c>
       <c r="H426" t="n">
         <v>542238</v>
@@ -12781,7 +12781,7 @@
         <v>2.1010000705719</v>
       </c>
       <c r="G428" t="n">
-        <v>1.64118993282318</v>
+        <v>1.64119005203247</v>
       </c>
       <c r="H428" t="n">
         <v>384515</v>
@@ -12810,7 +12810,7 @@
         <v>2.0789999961853</v>
       </c>
       <c r="G429" t="n">
-        <v>1.62400472164154</v>
+        <v>1.62400460243225</v>
       </c>
       <c r="H429" t="n">
         <v>242331</v>
@@ -12839,7 +12839,7 @@
         <v>2.05299997329712</v>
       </c>
       <c r="G430" t="n">
-        <v>1.60369491577148</v>
+        <v>1.60369479656219</v>
       </c>
       <c r="H430" t="n">
         <v>355572</v>
@@ -12926,7 +12926,7 @@
         <v>1.97699999809265</v>
       </c>
       <c r="G433" t="n">
-        <v>1.54432761669159</v>
+        <v>1.54432773590088</v>
       </c>
       <c r="H433" t="n">
         <v>335769</v>
@@ -13013,7 +13013,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G436" t="n">
-        <v>1.45762050151825</v>
+        <v>1.45762038230896</v>
       </c>
       <c r="H436" t="n">
         <v>630873</v>
@@ -13274,7 +13274,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G445" t="n">
-        <v>1.48886620998383</v>
+        <v>1.48886632919312</v>
       </c>
       <c r="H445" t="n">
         <v>825110</v>
@@ -13361,7 +13361,7 @@
         <v>1.84399998188019</v>
       </c>
       <c r="G448" t="n">
-        <v>1.44043505191803</v>
+        <v>1.44043517112732</v>
       </c>
       <c r="H448" t="n">
         <v>564069</v>
@@ -13477,7 +13477,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G452" t="n">
-        <v>1.31232702732086</v>
+        <v>1.31232690811157</v>
       </c>
       <c r="H452" t="n">
         <v>1384290</v>
@@ -13506,7 +13506,7 @@
         <v>1.67340004444122</v>
       </c>
       <c r="G453" t="n">
-        <v>1.30717158317566</v>
+        <v>1.30717146396637</v>
       </c>
       <c r="H453" t="n">
         <v>770495</v>
@@ -13709,7 +13709,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G460" t="n">
-        <v>1.42715561389923</v>
+        <v>1.42715573310852</v>
       </c>
       <c r="H460" t="n">
         <v>222767</v>
@@ -13767,7 +13767,7 @@
         <v>1.80599999427795</v>
       </c>
       <c r="G462" t="n">
-        <v>1.41075146198273</v>
+        <v>1.41075158119202</v>
       </c>
       <c r="H462" t="n">
         <v>246924</v>
@@ -13854,7 +13854,7 @@
         <v>1.92239999771118</v>
       </c>
       <c r="G465" t="n">
-        <v>1.5016770362854</v>
+        <v>1.50167691707611</v>
       </c>
       <c r="H465" t="n">
         <v>353065</v>
@@ -13883,7 +13883,7 @@
         <v>2.02950000762939</v>
       </c>
       <c r="G466" t="n">
-        <v>1.58533799648285</v>
+        <v>1.58533787727356</v>
       </c>
       <c r="H466" t="n">
         <v>617753</v>
@@ -14057,7 +14057,7 @@
         <v>2.00850009918213</v>
       </c>
       <c r="G472" t="n">
-        <v>1.56893384456635</v>
+        <v>1.56893396377563</v>
       </c>
       <c r="H472" t="n">
         <v>366405</v>
@@ -14144,7 +14144,7 @@
         <v>2.25950002670288</v>
       </c>
       <c r="G475" t="n">
-        <v>1.76500177383423</v>
+        <v>1.76500165462494</v>
       </c>
       <c r="H475" t="n">
         <v>775246</v>
@@ -14202,7 +14202,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G477" t="n">
-        <v>1.75601840019226</v>
+        <v>1.75601851940155</v>
       </c>
       <c r="H477" t="n">
         <v>381912</v>
@@ -14231,7 +14231,7 @@
         <v>2.22699999809265</v>
       </c>
       <c r="G478" t="n">
-        <v>1.73961436748505</v>
+        <v>1.73961448669434</v>
       </c>
       <c r="H478" t="n">
         <v>1434510</v>
@@ -14289,7 +14289,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G480" t="n">
-        <v>1.74664485454559</v>
+        <v>1.7466447353363</v>
       </c>
       <c r="H480" t="n">
         <v>1270704</v>
@@ -14376,7 +14376,7 @@
         <v>2.29749989509583</v>
       </c>
       <c r="G483" t="n">
-        <v>1.79468536376953</v>
+        <v>1.79468512535095</v>
       </c>
       <c r="H483" t="n">
         <v>1095196</v>
@@ -14405,7 +14405,7 @@
         <v>2.33599996566772</v>
       </c>
       <c r="G484" t="n">
-        <v>1.8247594833374</v>
+        <v>1.82475936412811</v>
       </c>
       <c r="H484" t="n">
         <v>451325</v>
@@ -14463,7 +14463,7 @@
         <v>2.32649993896484</v>
       </c>
       <c r="G486" t="n">
-        <v>1.81733870506287</v>
+        <v>1.81733858585358</v>
       </c>
       <c r="H486" t="n">
         <v>753540</v>
@@ -14492,7 +14492,7 @@
         <v>2.25</v>
       </c>
       <c r="G487" t="n">
-        <v>1.75758099555969</v>
+        <v>1.7575808763504</v>
       </c>
       <c r="H487" t="n">
         <v>1370262</v>
@@ -14579,7 +14579,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G490" t="n">
-        <v>1.82007241249084</v>
+        <v>1.82007253170013</v>
       </c>
       <c r="H490" t="n">
         <v>579196</v>
@@ -14666,7 +14666,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G493" t="n">
-        <v>1.86225461959839</v>
+        <v>1.86225438117981</v>
       </c>
       <c r="H493" t="n">
         <v>271589</v>
@@ -14840,7 +14840,7 @@
         <v>2.3289999961853</v>
       </c>
       <c r="G499" t="n">
-        <v>1.819291472435</v>
+        <v>1.81929135322571</v>
       </c>
       <c r="H499" t="n">
         <v>426104</v>
@@ -15014,7 +15014,7 @@
         <v>2.40199995040894</v>
       </c>
       <c r="G505" t="n">
-        <v>1.87631523609161</v>
+        <v>1.87631499767303</v>
       </c>
       <c r="H505" t="n">
         <v>719122</v>
@@ -15072,7 +15072,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G507" t="n">
-        <v>1.85131847858429</v>
+        <v>1.85131824016571</v>
       </c>
       <c r="H507" t="n">
         <v>420850</v>
@@ -15130,7 +15130,7 @@
         <v>2.37949991226196</v>
       </c>
       <c r="G509" t="n">
-        <v>1.85873913764954</v>
+        <v>1.85873937606812</v>
       </c>
       <c r="H509" t="n">
         <v>517495</v>
@@ -15159,7 +15159,7 @@
         <v>2.33949995040894</v>
       </c>
       <c r="G510" t="n">
-        <v>1.82749342918396</v>
+        <v>1.82749330997467</v>
       </c>
       <c r="H510" t="n">
         <v>387078</v>
@@ -15188,7 +15188,7 @@
         <v>2.30800008773804</v>
       </c>
       <c r="G511" t="n">
-        <v>1.80288755893707</v>
+        <v>1.80288732051849</v>
       </c>
       <c r="H511" t="n">
         <v>471638</v>
@@ -15420,7 +15420,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G519" t="n">
-        <v>1.84506916999817</v>
+        <v>1.84506940841675</v>
       </c>
       <c r="H519" t="n">
         <v>346938</v>
@@ -15478,7 +15478,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G521" t="n">
-        <v>1.83960139751434</v>
+        <v>1.83960127830505</v>
       </c>
       <c r="H521" t="n">
         <v>400601</v>
@@ -15536,7 +15536,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G523" t="n">
-        <v>1.74352014064789</v>
+        <v>1.74352025985718</v>
       </c>
       <c r="H523" t="n">
         <v>587511</v>
@@ -15594,7 +15594,7 @@
         <v>2.18650007247925</v>
       </c>
       <c r="G525" t="n">
-        <v>1.7079781293869</v>
+        <v>1.70797789096832</v>
       </c>
       <c r="H525" t="n">
         <v>339135</v>
@@ -15710,7 +15710,7 @@
         <v>2.1324999332428</v>
       </c>
       <c r="G529" t="n">
-        <v>1.66579592227936</v>
+        <v>1.66579604148865</v>
       </c>
       <c r="H529" t="n">
         <v>1224677</v>
@@ -15971,7 +15971,7 @@
         <v>2.11150002479553</v>
       </c>
       <c r="G538" t="n">
-        <v>1.64939188957214</v>
+        <v>1.64939200878143</v>
       </c>
       <c r="H538" t="n">
         <v>386864</v>
@@ -16000,7 +16000,7 @@
         <v>2.1010000705719</v>
       </c>
       <c r="G539" t="n">
-        <v>1.64118993282318</v>
+        <v>1.64119005203247</v>
       </c>
       <c r="H539" t="n">
         <v>348613</v>
@@ -16203,7 +16203,7 @@
         <v>2.14299988746643</v>
       </c>
       <c r="G546" t="n">
-        <v>1.67399787902832</v>
+        <v>1.67399799823761</v>
       </c>
       <c r="H546" t="n">
         <v>1450618</v>
@@ -16290,7 +16290,7 @@
         <v>2.12949991226196</v>
       </c>
       <c r="G549" t="n">
-        <v>1.66345262527466</v>
+        <v>1.66345250606537</v>
       </c>
       <c r="H549" t="n">
         <v>838112</v>
@@ -16406,7 +16406,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G553" t="n">
-        <v>1.74976933002472</v>
+        <v>1.74976944923401</v>
       </c>
       <c r="H553" t="n">
         <v>1944729</v>
@@ -16435,7 +16435,7 @@
         <v>2.24300003051758</v>
       </c>
       <c r="G554" t="n">
-        <v>1.75211274623871</v>
+        <v>1.752112865448</v>
       </c>
       <c r="H554" t="n">
         <v>387019</v>
@@ -16464,7 +16464,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G555" t="n">
-        <v>1.74352014064789</v>
+        <v>1.74352025985718</v>
       </c>
       <c r="H555" t="n">
         <v>532106</v>
@@ -16522,7 +16522,7 @@
         <v>2.30550003051758</v>
       </c>
       <c r="G557" t="n">
-        <v>1.80093443393707</v>
+        <v>1.80093455314636</v>
       </c>
       <c r="H557" t="n">
         <v>567946</v>
@@ -16667,7 +16667,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G562" t="n">
-        <v>1.95130515098572</v>
+        <v>1.95130527019501</v>
       </c>
       <c r="H562" t="n">
         <v>455972</v>
@@ -16696,7 +16696,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G563" t="n">
-        <v>1.96536612510681</v>
+        <v>1.96536588668823</v>
       </c>
       <c r="H563" t="n">
         <v>1160065</v>
@@ -16841,7 +16841,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G568" t="n">
-        <v>1.9966117143631</v>
+        <v>1.99661195278168</v>
       </c>
       <c r="H568" t="n">
         <v>1003381</v>
@@ -16870,7 +16870,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G569" t="n">
-        <v>1.92005956172943</v>
+        <v>1.92005932331085</v>
       </c>
       <c r="H569" t="n">
         <v>1136036</v>
@@ -16986,7 +16986,7 @@
         <v>2.56800007820129</v>
       </c>
       <c r="G573" t="n">
-        <v>2.00598573684692</v>
+        <v>2.00598549842834</v>
       </c>
       <c r="H573" t="n">
         <v>4035540</v>
@@ -17015,7 +17015,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G574" t="n">
-        <v>2.02785778045654</v>
+        <v>2.02785754203796</v>
       </c>
       <c r="H574" t="n">
         <v>1096883</v>
@@ -17073,7 +17073,7 @@
         <v>2.70600008964539</v>
       </c>
       <c r="G576" t="n">
-        <v>2.11378383636475</v>
+        <v>2.11378407478333</v>
       </c>
       <c r="H576" t="n">
         <v>1342948</v>
@@ -17102,7 +17102,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G577" t="n">
-        <v>2.12784457206726</v>
+        <v>2.12784433364868</v>
       </c>
       <c r="H577" t="n">
         <v>1427518</v>
@@ -17247,7 +17247,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>2.17940020561218</v>
+        <v>2.1793999671936</v>
       </c>
       <c r="H582" t="n">
         <v>543959</v>
@@ -17363,7 +17363,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G586" t="n">
-        <v>2.25751495361328</v>
+        <v>2.25751519203186</v>
       </c>
       <c r="H586" t="n">
         <v>1032388</v>
@@ -17421,7 +17421,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G588" t="n">
-        <v>2.31219506263733</v>
+        <v>2.31219530105591</v>
       </c>
       <c r="H588" t="n">
         <v>1282951</v>
@@ -17537,7 +17537,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G592" t="n">
-        <v>2.43874096870422</v>
+        <v>2.4387412071228</v>
       </c>
       <c r="H592" t="n">
         <v>965545</v>
@@ -17740,7 +17740,7 @@
         <v>3.10800004005432</v>
       </c>
       <c r="G599" t="n">
-        <v>2.42780518531799</v>
+        <v>2.42780494689941</v>
       </c>
       <c r="H599" t="n">
         <v>1169838</v>
@@ -17943,7 +17943,7 @@
         <v>3.30399990081787</v>
       </c>
       <c r="G606" t="n">
-        <v>2.58090972900391</v>
+        <v>2.58090949058533</v>
       </c>
       <c r="H606" t="n">
         <v>2221014</v>
@@ -18030,7 +18030,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G609" t="n">
-        <v>2.54810166358948</v>
+        <v>2.54810190200806</v>
       </c>
       <c r="H609" t="n">
         <v>548275</v>
@@ -18059,7 +18059,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G610" t="n">
-        <v>2.46373772621155</v>
+        <v>2.46373796463013</v>
       </c>
       <c r="H610" t="n">
         <v>1532299</v>
@@ -18088,7 +18088,7 @@
         <v>3.24600005149841</v>
       </c>
       <c r="G611" t="n">
-        <v>2.53560304641724</v>
+        <v>2.53560328483582</v>
       </c>
       <c r="H611" t="n">
         <v>978496</v>
@@ -18117,7 +18117,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G612" t="n">
-        <v>2.41374444961548</v>
+        <v>2.4137442111969</v>
       </c>
       <c r="H612" t="n">
         <v>1036670</v>
@@ -18233,7 +18233,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G616" t="n">
-        <v>2.39343428611755</v>
+        <v>2.39343452453613</v>
       </c>
       <c r="H616" t="n">
         <v>397137</v>
@@ -18378,7 +18378,7 @@
         <v>3.18799996376038</v>
       </c>
       <c r="G621" t="n">
-        <v>2.49029660224915</v>
+        <v>2.49029684066772</v>
       </c>
       <c r="H621" t="n">
         <v>691299</v>
@@ -18407,7 +18407,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G622" t="n">
-        <v>2.52310490608215</v>
+        <v>2.52310514450073</v>
       </c>
       <c r="H622" t="n">
         <v>1734037</v>
@@ -18436,7 +18436,7 @@
         <v>3.21799993515015</v>
       </c>
       <c r="G623" t="n">
-        <v>2.5137312412262</v>
+        <v>2.51373100280762</v>
       </c>
       <c r="H623" t="n">
         <v>829894</v>
@@ -18523,7 +18523,7 @@
         <v>3.2720000743866</v>
       </c>
       <c r="G626" t="n">
-        <v>2.55591297149658</v>
+        <v>2.55591320991516</v>
       </c>
       <c r="H626" t="n">
         <v>682877</v>
@@ -18552,7 +18552,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G627" t="n">
-        <v>2.52310490608215</v>
+        <v>2.52310514450073</v>
       </c>
       <c r="H627" t="n">
         <v>1052134</v>
@@ -18668,7 +18668,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G631" t="n">
-        <v>2.5777850151062</v>
+        <v>2.57778525352478</v>
       </c>
       <c r="H631" t="n">
         <v>943074</v>
@@ -18726,7 +18726,7 @@
         <v>3.42199993133545</v>
       </c>
       <c r="G633" t="n">
-        <v>2.67308521270752</v>
+        <v>2.67308497428894</v>
       </c>
       <c r="H633" t="n">
         <v>1448985</v>
@@ -18784,7 +18784,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G635" t="n">
-        <v>2.71058011054993</v>
+        <v>2.71058034896851</v>
       </c>
       <c r="H635" t="n">
         <v>867265</v>
@@ -18842,7 +18842,7 @@
         <v>3.53200006484985</v>
       </c>
       <c r="G637" t="n">
-        <v>2.7590115070343</v>
+        <v>2.75901126861572</v>
       </c>
       <c r="H637" t="n">
         <v>1376981</v>
@@ -35378,6 +35378,35 @@
         <v>1948882</v>
       </c>
       <c r="I1207" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1208" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1208" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="D1208" t="n">
+        <v>2.13199996948242</v>
+      </c>
+      <c r="E1208" t="n">
+        <v>2.07599997520447</v>
+      </c>
+      <c r="F1208" t="n">
+        <v>2.11199998855591</v>
+      </c>
+      <c r="G1208" t="n">
+        <v>2.11199998855591</v>
+      </c>
+      <c r="H1208" t="n">
+        <v>1578337</v>
+      </c>
+      <c r="I1208" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MFEA.MI.xlsx
+++ b/data/MFEA.MI.xlsx
@@ -514,7 +514,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G5" t="n">
-        <v>2.30884909629822</v>
+        <v>2.30884885787964</v>
       </c>
       <c r="H5" t="n">
         <v>278466</v>
@@ -630,7 +630,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G9" t="n">
-        <v>2.34892225265503</v>
+        <v>2.34892249107361</v>
       </c>
       <c r="H9" t="n">
         <v>257244</v>
@@ -659,7 +659,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>2.33659195899963</v>
+        <v>2.33659219741821</v>
       </c>
       <c r="H10" t="n">
         <v>166086</v>
@@ -688,7 +688,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G11" t="n">
-        <v>2.31501412391663</v>
+        <v>2.31501388549805</v>
       </c>
       <c r="H11" t="n">
         <v>127118</v>
@@ -775,7 +775,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G14" t="n">
-        <v>2.2317841053009</v>
+        <v>2.23178458213806</v>
       </c>
       <c r="H14" t="n">
         <v>244637</v>
@@ -833,7 +833,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G16" t="n">
-        <v>2.64484977722168</v>
+        <v>2.6448495388031</v>
       </c>
       <c r="H16" t="n">
         <v>857484</v>
@@ -862,7 +862,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G17" t="n">
-        <v>2.69417095184326</v>
+        <v>2.69417071342468</v>
       </c>
       <c r="H17" t="n">
         <v>431766</v>
@@ -891,7 +891,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G18" t="n">
-        <v>2.66951012611389</v>
+        <v>2.66951036453247</v>
       </c>
       <c r="H18" t="n">
         <v>629452</v>
@@ -920,7 +920,7 @@
         <v>4.28249979019165</v>
       </c>
       <c r="G19" t="n">
-        <v>2.64022541046143</v>
+        <v>2.64022588729858</v>
       </c>
       <c r="H19" t="n">
         <v>318343</v>
@@ -978,7 +978,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G21" t="n">
-        <v>2.64793229103088</v>
+        <v>2.6479320526123</v>
       </c>
       <c r="H21" t="n">
         <v>296725</v>
@@ -1036,7 +1036,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G23" t="n">
-        <v>2.49688601493835</v>
+        <v>2.49688625335693</v>
       </c>
       <c r="H23" t="n">
         <v>230967</v>
@@ -1065,7 +1065,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G24" t="n">
-        <v>2.42598676681519</v>
+        <v>2.42598700523376</v>
       </c>
       <c r="H24" t="n">
         <v>208426</v>
@@ -1094,7 +1094,7 @@
         <v>3.99499988555908</v>
       </c>
       <c r="G25" t="n">
-        <v>2.46297764778137</v>
+        <v>2.46297788619995</v>
       </c>
       <c r="H25" t="n">
         <v>109853</v>
@@ -1123,7 +1123,7 @@
         <v>3.94250011444092</v>
       </c>
       <c r="G26" t="n">
-        <v>2.43061065673828</v>
+        <v>2.43061089515686</v>
       </c>
       <c r="H26" t="n">
         <v>264886</v>
@@ -1181,7 +1181,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G28" t="n">
-        <v>2.47222566604614</v>
+        <v>2.47222542762756</v>
       </c>
       <c r="H28" t="n">
         <v>194221</v>
@@ -1442,7 +1442,7 @@
         <v>4.14249992370605</v>
       </c>
       <c r="G37" t="n">
-        <v>2.55391383171082</v>
+        <v>2.55391359329224</v>
       </c>
       <c r="H37" t="n">
         <v>310291</v>
@@ -1471,7 +1471,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G38" t="n">
-        <v>2.58936309814453</v>
+        <v>2.58936333656311</v>
       </c>
       <c r="H38" t="n">
         <v>208860</v>
@@ -1500,7 +1500,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G39" t="n">
-        <v>2.58936309814453</v>
+        <v>2.58936333656311</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -1529,7 +1529,7 @@
         <v>3.73749995231628</v>
       </c>
       <c r="G40" t="n">
-        <v>2.30422496795654</v>
+        <v>2.30422520637512</v>
       </c>
       <c r="H40" t="n">
         <v>2097188</v>
@@ -1558,7 +1558,7 @@
         <v>3.5</v>
       </c>
       <c r="G41" t="n">
-        <v>2.15780282020569</v>
+        <v>2.15780258178711</v>
       </c>
       <c r="H41" t="n">
         <v>1105386</v>
@@ -1703,7 +1703,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G46" t="n">
-        <v>2.02525210380554</v>
+        <v>2.02525186538696</v>
       </c>
       <c r="H46" t="n">
         <v>426915</v>
@@ -1732,7 +1732,7 @@
         <v>3.26749992370605</v>
       </c>
       <c r="G47" t="n">
-        <v>2.01446294784546</v>
+        <v>2.01446270942688</v>
       </c>
       <c r="H47" t="n">
         <v>127552</v>
@@ -1790,7 +1790,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G49" t="n">
-        <v>2.07149052619934</v>
+        <v>2.07149076461792</v>
       </c>
       <c r="H49" t="n">
         <v>101724</v>
@@ -1819,7 +1819,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G50" t="n">
-        <v>2.02525210380554</v>
+        <v>2.02525186538696</v>
       </c>
       <c r="H50" t="n">
         <v>165272</v>
@@ -1848,7 +1848,7 @@
         <v>3.17750000953674</v>
       </c>
       <c r="G51" t="n">
-        <v>1.95897650718689</v>
+        <v>1.95897674560547</v>
       </c>
       <c r="H51" t="n">
         <v>400267</v>
@@ -1877,7 +1877,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G52" t="n">
-        <v>1.99442613124847</v>
+        <v>1.99442625045776</v>
       </c>
       <c r="H52" t="n">
         <v>186459</v>
@@ -1906,7 +1906,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G53" t="n">
-        <v>1.97593057155609</v>
+        <v>1.97593080997467</v>
       </c>
       <c r="H53" t="n">
         <v>157204</v>
@@ -1935,7 +1935,7 @@
         <v>3.1175000667572</v>
       </c>
       <c r="G54" t="n">
-        <v>1.9219856262207</v>
+        <v>1.92198586463928</v>
       </c>
       <c r="H54" t="n">
         <v>195501</v>
@@ -1993,7 +1993,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G56" t="n">
-        <v>1.85571038722992</v>
+        <v>1.85571026802063</v>
       </c>
       <c r="H56" t="n">
         <v>119171</v>
@@ -2022,7 +2022,7 @@
         <v>3</v>
       </c>
       <c r="G57" t="n">
-        <v>1.84954500198364</v>
+        <v>1.84954535961151</v>
       </c>
       <c r="H57" t="n">
         <v>234992</v>
@@ -2080,7 +2080,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G59" t="n">
-        <v>1.79405891895294</v>
+        <v>1.79405903816223</v>
       </c>
       <c r="H59" t="n">
         <v>174796</v>
@@ -2109,7 +2109,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G60" t="n">
-        <v>1.79714131355286</v>
+        <v>1.79714155197144</v>
       </c>
       <c r="H60" t="n">
         <v>140935</v>
@@ -2196,7 +2196,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G63" t="n">
-        <v>1.81255424022675</v>
+        <v>1.81255447864532</v>
       </c>
       <c r="H63" t="n">
         <v>134826</v>
@@ -2225,7 +2225,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G64" t="n">
-        <v>1.87728846073151</v>
+        <v>1.87728869915009</v>
       </c>
       <c r="H64" t="n">
         <v>324711</v>
@@ -2254,7 +2254,7 @@
         <v>2.89249992370605</v>
       </c>
       <c r="G65" t="n">
-        <v>1.78327000141144</v>
+        <v>1.78326988220215</v>
       </c>
       <c r="H65" t="n">
         <v>336035</v>
@@ -2283,7 +2283,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G66" t="n">
-        <v>1.713911652565</v>
+        <v>1.71391189098358</v>
       </c>
       <c r="H66" t="n">
         <v>344735</v>
@@ -2312,7 +2312,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G67" t="n">
-        <v>1.69233381748199</v>
+        <v>1.69233393669128</v>
       </c>
       <c r="H67" t="n">
         <v>293953</v>
@@ -2428,7 +2428,7 @@
         <v>2.86249995231628</v>
       </c>
       <c r="G71" t="n">
-        <v>1.76477444171906</v>
+        <v>1.76477432250977</v>
       </c>
       <c r="H71" t="n">
         <v>710221</v>
@@ -2486,7 +2486,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G73" t="n">
-        <v>1.74165499210358</v>
+        <v>1.74165511131287</v>
       </c>
       <c r="H73" t="n">
         <v>228203</v>
@@ -2573,7 +2573,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G76" t="n">
-        <v>1.6337651014328</v>
+        <v>1.63376498222351</v>
       </c>
       <c r="H76" t="n">
         <v>246997</v>
@@ -2602,7 +2602,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>1.64917778968811</v>
+        <v>1.64917767047882</v>
       </c>
       <c r="H77" t="n">
         <v>209971</v>
@@ -2631,7 +2631,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G78" t="n">
-        <v>1.74782049655914</v>
+        <v>1.74782013893127</v>
       </c>
       <c r="H78" t="n">
         <v>522442</v>
@@ -2718,7 +2718,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G81" t="n">
-        <v>1.62143468856812</v>
+        <v>1.62143456935883</v>
       </c>
       <c r="H81" t="n">
         <v>237552</v>
@@ -2747,7 +2747,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G82" t="n">
-        <v>1.63068222999573</v>
+        <v>1.63068246841431</v>
       </c>
       <c r="H82" t="n">
         <v>172630</v>
@@ -2805,7 +2805,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G84" t="n">
-        <v>1.56594812870026</v>
+        <v>1.56594824790955</v>
       </c>
       <c r="H84" t="n">
         <v>392657</v>
@@ -2834,7 +2834,7 @@
         <v>2.58750009536743</v>
       </c>
       <c r="G85" t="n">
-        <v>1.59523296356201</v>
+        <v>1.59523260593414</v>
       </c>
       <c r="H85" t="n">
         <v>241301</v>
@@ -2863,7 +2863,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G86" t="n">
-        <v>1.58752620220184</v>
+        <v>1.58752632141113</v>
       </c>
       <c r="H86" t="n">
         <v>329995</v>
@@ -2950,7 +2950,7 @@
         <v>2.65499997138977</v>
       </c>
       <c r="G89" t="n">
-        <v>1.63684737682343</v>
+        <v>1.636847615242</v>
       </c>
       <c r="H89" t="n">
         <v>285515</v>
@@ -2979,7 +2979,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G90" t="n">
-        <v>1.62143468856812</v>
+        <v>1.62143456935883</v>
       </c>
       <c r="H90" t="n">
         <v>381738</v>
@@ -3008,7 +3008,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>1.67075598239899</v>
+        <v>1.6707558631897</v>
       </c>
       <c r="H91" t="n">
         <v>530043</v>
@@ -3066,7 +3066,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G93" t="n">
-        <v>1.63068222999573</v>
+        <v>1.63068246841431</v>
       </c>
       <c r="H93" t="n">
         <v>293851</v>
@@ -3095,7 +3095,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G94" t="n">
-        <v>1.6399302482605</v>
+        <v>1.63993000984192</v>
       </c>
       <c r="H94" t="n">
         <v>124415</v>
@@ -3153,7 +3153,7 @@
         <v>2.6324999332428</v>
       </c>
       <c r="G96" t="n">
-        <v>1.62297582626343</v>
+        <v>1.62297570705414</v>
       </c>
       <c r="H96" t="n">
         <v>316690</v>
@@ -3211,7 +3211,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G98" t="n">
-        <v>1.664590716362</v>
+        <v>1.66459095478058</v>
       </c>
       <c r="H98" t="n">
         <v>547180</v>
@@ -3269,7 +3269,7 @@
         <v>2.45300006866455</v>
       </c>
       <c r="G100" t="n">
-        <v>1.51231157779694</v>
+        <v>1.51231133937836</v>
       </c>
       <c r="H100" t="n">
         <v>588672</v>
@@ -3356,7 +3356,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G103" t="n">
-        <v>1.45867478847504</v>
+        <v>1.45867466926575</v>
       </c>
       <c r="H103" t="n">
         <v>277983</v>
@@ -3414,7 +3414,7 @@
         <v>2.25699996948242</v>
       </c>
       <c r="G105" t="n">
-        <v>1.39147448539734</v>
+        <v>1.39147460460663</v>
       </c>
       <c r="H105" t="n">
         <v>153134</v>
@@ -3472,7 +3472,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>1.33475506305695</v>
+        <v>1.33475518226624</v>
       </c>
       <c r="H107" t="n">
         <v>364496</v>
@@ -3501,7 +3501,7 @@
         <v>2.11899995803833</v>
       </c>
       <c r="G108" t="n">
-        <v>1.3063952922821</v>
+        <v>1.30639541149139</v>
       </c>
       <c r="H108" t="n">
         <v>333946</v>
@@ -3530,7 +3530,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G109" t="n">
-        <v>1.31934213638306</v>
+        <v>1.31934237480164</v>
       </c>
       <c r="H109" t="n">
         <v>149597</v>
@@ -3617,7 +3617,7 @@
         <v>2.24900007247925</v>
       </c>
       <c r="G112" t="n">
-        <v>1.38654232025146</v>
+        <v>1.38654243946075</v>
       </c>
       <c r="H112" t="n">
         <v>617377</v>
@@ -3704,7 +3704,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G115" t="n">
-        <v>1.36558079719543</v>
+        <v>1.36558091640472</v>
       </c>
       <c r="H115" t="n">
         <v>684447</v>
@@ -3733,7 +3733,7 @@
         <v>2.28900003433228</v>
       </c>
       <c r="G116" t="n">
-        <v>1.41120314598083</v>
+        <v>1.41120302677155</v>
       </c>
       <c r="H116" t="n">
         <v>1034023</v>
@@ -3791,7 +3791,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G118" t="n">
-        <v>1.34708547592163</v>
+        <v>1.34708535671234</v>
       </c>
       <c r="H118" t="n">
         <v>844960</v>
@@ -3820,7 +3820,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G119" t="n">
-        <v>1.38099384307861</v>
+        <v>1.38099360466003</v>
       </c>
       <c r="H119" t="n">
         <v>296846</v>
@@ -3878,7 +3878,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G121" t="n">
-        <v>1.4056544303894</v>
+        <v>1.40565419197083</v>
       </c>
       <c r="H121" t="n">
         <v>1163100</v>
@@ -4081,7 +4081,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G128" t="n">
-        <v>1.35325062274933</v>
+        <v>1.35325038433075</v>
       </c>
       <c r="H128" t="n">
         <v>1234804</v>
@@ -4139,7 +4139,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G130" t="n">
-        <v>1.37791109085083</v>
+        <v>1.37791097164154</v>
       </c>
       <c r="H130" t="n">
         <v>658168</v>
@@ -4197,7 +4197,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G132" t="n">
-        <v>1.29468154907227</v>
+        <v>1.29468166828156</v>
       </c>
       <c r="H132" t="n">
         <v>903030</v>
@@ -4226,7 +4226,7 @@
         <v>2.02699995040894</v>
       </c>
       <c r="G133" t="n">
-        <v>1.249675989151</v>
+        <v>1.24967610836029</v>
       </c>
       <c r="H133" t="n">
         <v>1799201</v>
@@ -4255,7 +4255,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>1.28543388843536</v>
+        <v>1.28543400764465</v>
       </c>
       <c r="H134" t="n">
         <v>1315577</v>
@@ -4313,7 +4313,7 @@
         <v>2.20099997520447</v>
       </c>
       <c r="G136" t="n">
-        <v>1.35694968700409</v>
+        <v>1.3569495677948</v>
       </c>
       <c r="H136" t="n">
         <v>597261</v>
@@ -4342,7 +4342,7 @@
         <v>2.16199994087219</v>
       </c>
       <c r="G137" t="n">
-        <v>1.33290553092957</v>
+        <v>1.33290541172028</v>
       </c>
       <c r="H137" t="n">
         <v>695720</v>
@@ -4371,7 +4371,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G138" t="n">
-        <v>1.32304131984711</v>
+        <v>1.32304120063782</v>
       </c>
       <c r="H138" t="n">
         <v>662539</v>
@@ -4400,7 +4400,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G139" t="n">
-        <v>1.27002096176147</v>
+        <v>1.27002108097076</v>
       </c>
       <c r="H139" t="n">
         <v>1000781</v>
@@ -4429,7 +4429,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G140" t="n">
-        <v>1.27926874160767</v>
+        <v>1.27926886081696</v>
       </c>
       <c r="H140" t="n">
         <v>489036</v>
@@ -4458,7 +4458,7 @@
         <v>2.08400011062622</v>
       </c>
       <c r="G141" t="n">
-        <v>1.28481757640839</v>
+        <v>1.2848174571991</v>
       </c>
       <c r="H141" t="n">
         <v>2061793</v>
@@ -4487,7 +4487,7 @@
         <v>2.125</v>
       </c>
       <c r="G142" t="n">
-        <v>1.31009459495544</v>
+        <v>1.31009447574615</v>
       </c>
       <c r="H142" t="n">
         <v>1089881</v>
@@ -4516,7 +4516,7 @@
         <v>2.19099998474121</v>
       </c>
       <c r="G143" t="n">
-        <v>1.35078454017639</v>
+        <v>1.3507844209671</v>
       </c>
       <c r="H143" t="n">
         <v>662529</v>
@@ -4545,7 +4545,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G144" t="n">
-        <v>1.35386729240417</v>
+        <v>1.35386717319489</v>
       </c>
       <c r="H144" t="n">
         <v>698399</v>
@@ -4603,7 +4603,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G146" t="n">
-        <v>1.4025719165802</v>
+        <v>1.40257179737091</v>
       </c>
       <c r="H146" t="n">
         <v>463835</v>
@@ -4632,7 +4632,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G147" t="n">
-        <v>1.35325062274933</v>
+        <v>1.35325038433075</v>
       </c>
       <c r="H147" t="n">
         <v>729575</v>
@@ -4661,7 +4661,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G148" t="n">
-        <v>1.35633301734924</v>
+        <v>1.35633325576782</v>
       </c>
       <c r="H148" t="n">
         <v>470520</v>
@@ -4777,7 +4777,7 @@
         <v>2.05299997329712</v>
       </c>
       <c r="G152" t="n">
-        <v>1.26570534706116</v>
+        <v>1.26570546627045</v>
       </c>
       <c r="H152" t="n">
         <v>460461</v>
@@ -4835,7 +4835,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G154" t="n">
-        <v>1.23611283302307</v>
+        <v>1.23611271381378</v>
       </c>
       <c r="H154" t="n">
         <v>622012</v>
@@ -4864,7 +4864,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G155" t="n">
-        <v>1.28235137462616</v>
+        <v>1.28235125541687</v>
       </c>
       <c r="H155" t="n">
         <v>897371</v>
@@ -4922,7 +4922,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G157" t="n">
-        <v>1.30392944812775</v>
+        <v>1.30392932891846</v>
       </c>
       <c r="H157" t="n">
         <v>621284</v>
@@ -4980,7 +4980,7 @@
         <v>2.10199999809265</v>
       </c>
       <c r="G159" t="n">
-        <v>1.29591464996338</v>
+        <v>1.29591476917267</v>
       </c>
       <c r="H159" t="n">
         <v>782752</v>
@@ -5067,7 +5067,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G162" t="n">
-        <v>1.28235137462616</v>
+        <v>1.28235125541687</v>
       </c>
       <c r="H162" t="n">
         <v>320464</v>
@@ -5096,7 +5096,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G163" t="n">
-        <v>1.28235137462616</v>
+        <v>1.28235125541687</v>
       </c>
       <c r="H163" t="n">
         <v>665085</v>
@@ -5125,7 +5125,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G164" t="n">
-        <v>1.31625962257385</v>
+        <v>1.31625974178314</v>
       </c>
       <c r="H164" t="n">
         <v>1321946</v>
@@ -5183,7 +5183,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G166" t="n">
-        <v>1.28543388843536</v>
+        <v>1.28543400764465</v>
       </c>
       <c r="H166" t="n">
         <v>925875</v>
@@ -5212,7 +5212,7 @@
         <v>2.06900000572205</v>
       </c>
       <c r="G167" t="n">
-        <v>1.27556967735291</v>
+        <v>1.27556955814362</v>
       </c>
       <c r="H167" t="n">
         <v>928824</v>
@@ -5241,7 +5241,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G168" t="n">
-        <v>1.24782633781433</v>
+        <v>1.24782645702362</v>
       </c>
       <c r="H168" t="n">
         <v>1017897</v>
@@ -5299,7 +5299,7 @@
         <v>1.84899997711182</v>
       </c>
       <c r="G170" t="n">
-        <v>1.30287742614746</v>
+        <v>1.30287754535675</v>
       </c>
       <c r="H170" t="n">
         <v>1744533</v>
@@ -5328,7 +5328,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G171" t="n">
-        <v>1.20140957832336</v>
+        <v>1.20140945911407</v>
       </c>
       <c r="H171" t="n">
         <v>1719560</v>
@@ -5386,7 +5386,7 @@
         <v>1.65199995040894</v>
       </c>
       <c r="G173" t="n">
-        <v>1.16406345367432</v>
+        <v>1.16406357288361</v>
       </c>
       <c r="H173" t="n">
         <v>1205156</v>
@@ -5444,7 +5444,7 @@
         <v>1.59099996089935</v>
       </c>
       <c r="G175" t="n">
-        <v>1.12108063697815</v>
+        <v>1.12108075618744</v>
       </c>
       <c r="H175" t="n">
         <v>1912525</v>
@@ -5473,7 +5473,7 @@
         <v>1.53900003433228</v>
       </c>
       <c r="G176" t="n">
-        <v>1.0844395160675</v>
+        <v>1.08443939685822</v>
       </c>
       <c r="H176" t="n">
         <v>1625041</v>
@@ -5531,7 +5531,7 @@
         <v>1.43900001049042</v>
       </c>
       <c r="G178" t="n">
-        <v>1.01397550106049</v>
+        <v>1.01397562026978</v>
       </c>
       <c r="H178" t="n">
         <v>1366037</v>
@@ -5560,7 +5560,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G179" t="n">
-        <v>1.06400489807129</v>
+        <v>1.064004778862</v>
       </c>
       <c r="H179" t="n">
         <v>1582704</v>
@@ -5589,7 +5589,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G180" t="n">
-        <v>1.08514404296875</v>
+        <v>1.08514392375946</v>
       </c>
       <c r="H180" t="n">
         <v>1913773</v>
@@ -5705,7 +5705,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G184" t="n">
-        <v>1.08796274662018</v>
+        <v>1.08796262741089</v>
       </c>
       <c r="H184" t="n">
         <v>1603167</v>
@@ -5850,7 +5850,7 @@
         <v>1.5110000371933</v>
       </c>
       <c r="G189" t="n">
-        <v>1.06470954418182</v>
+        <v>1.06470942497253</v>
       </c>
       <c r="H189" t="n">
         <v>1590572</v>
@@ -5966,7 +5966,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>1.15913105010986</v>
+        <v>1.15913128852844</v>
       </c>
       <c r="H193" t="n">
         <v>574328</v>
@@ -5995,7 +5995,7 @@
         <v>1.62300002574921</v>
       </c>
       <c r="G194" t="n">
-        <v>1.14362919330597</v>
+        <v>1.14362907409668</v>
       </c>
       <c r="H194" t="n">
         <v>1339210</v>
@@ -6024,7 +6024,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G195" t="n">
-        <v>1.16265451908112</v>
+        <v>1.16265439987183</v>
       </c>
       <c r="H195" t="n">
         <v>1118932</v>
@@ -6198,7 +6198,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G201" t="n">
-        <v>1.2577805519104</v>
+        <v>1.25778043270111</v>
       </c>
       <c r="H201" t="n">
         <v>515449</v>
@@ -6372,7 +6372,7 @@
         <v>1.83899998664856</v>
       </c>
       <c r="G207" t="n">
-        <v>1.2958310842514</v>
+        <v>1.29583096504211</v>
       </c>
       <c r="H207" t="n">
         <v>359958</v>
@@ -6517,7 +6517,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G212" t="n">
-        <v>1.2937171459198</v>
+        <v>1.29371726512909</v>
       </c>
       <c r="H212" t="n">
         <v>773982</v>
@@ -6546,7 +6546,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G213" t="n">
-        <v>1.28737556934357</v>
+        <v>1.28737545013428</v>
       </c>
       <c r="H213" t="n">
         <v>677501</v>
@@ -6575,7 +6575,7 @@
         <v>1.81099998950958</v>
       </c>
       <c r="G214" t="n">
-        <v>1.27610111236572</v>
+        <v>1.27610123157501</v>
       </c>
       <c r="H214" t="n">
         <v>308754</v>
@@ -6720,7 +6720,7 @@
         <v>2.04699993133545</v>
       </c>
       <c r="G219" t="n">
-        <v>1.44239604473114</v>
+        <v>1.44239592552185</v>
       </c>
       <c r="H219" t="n">
         <v>1110213</v>
@@ -6778,7 +6778,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G221" t="n">
-        <v>1.41632437705994</v>
+        <v>1.41632425785065</v>
       </c>
       <c r="H221" t="n">
         <v>434673</v>
@@ -6865,7 +6865,7 @@
         <v>2.02099990844727</v>
       </c>
       <c r="G224" t="n">
-        <v>1.42407548427582</v>
+        <v>1.42407536506653</v>
       </c>
       <c r="H224" t="n">
         <v>728660</v>
@@ -6894,7 +6894,7 @@
         <v>1.98300004005432</v>
       </c>
       <c r="G225" t="n">
-        <v>1.39729917049408</v>
+        <v>1.39729928970337</v>
       </c>
       <c r="H225" t="n">
         <v>1086938</v>
@@ -6952,7 +6952,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G227" t="n">
-        <v>1.33035850524902</v>
+        <v>1.33035838603973</v>
       </c>
       <c r="H227" t="n">
         <v>521176</v>
@@ -7097,7 +7097,7 @@
         <v>1.86300003528595</v>
       </c>
       <c r="G232" t="n">
-        <v>1.31274259090424</v>
+        <v>1.31274247169495</v>
       </c>
       <c r="H232" t="n">
         <v>190892</v>
@@ -7184,7 +7184,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G235" t="n">
-        <v>1.2577805519104</v>
+        <v>1.25778043270111</v>
       </c>
       <c r="H235" t="n">
         <v>235737</v>
@@ -7242,7 +7242,7 @@
         <v>1.82099997997284</v>
       </c>
       <c r="G237" t="n">
-        <v>1.28314757347107</v>
+        <v>1.28314769268036</v>
       </c>
       <c r="H237" t="n">
         <v>406192</v>
@@ -7329,7 +7329,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G240" t="n">
-        <v>1.27891993522644</v>
+        <v>1.27891981601715</v>
       </c>
       <c r="H240" t="n">
         <v>206556</v>
@@ -7358,7 +7358,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G241" t="n">
-        <v>1.26482689380646</v>
+        <v>1.26482701301575</v>
       </c>
       <c r="H241" t="n">
         <v>338837</v>
@@ -7387,7 +7387,7 @@
         <v>1.81900000572205</v>
       </c>
       <c r="G242" t="n">
-        <v>1.28173840045929</v>
+        <v>1.28173828125</v>
       </c>
       <c r="H242" t="n">
         <v>160229</v>
@@ -7590,7 +7590,7 @@
         <v>1.94099998474121</v>
       </c>
       <c r="G249" t="n">
-        <v>1.36770439147949</v>
+        <v>1.3677042722702</v>
       </c>
       <c r="H249" t="n">
         <v>394746</v>
@@ -7619,7 +7619,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G250" t="n">
-        <v>1.36981821060181</v>
+        <v>1.3698183298111</v>
       </c>
       <c r="H250" t="n">
         <v>296376</v>
@@ -7793,7 +7793,7 @@
         <v>1.98699998855591</v>
       </c>
       <c r="G256" t="n">
-        <v>1.40011763572693</v>
+        <v>1.40011775493622</v>
       </c>
       <c r="H256" t="n">
         <v>400869</v>
@@ -7822,7 +7822,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G257" t="n">
-        <v>1.37052285671234</v>
+        <v>1.37052297592163</v>
       </c>
       <c r="H257" t="n">
         <v>453008</v>
@@ -7851,7 +7851,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G258" t="n">
-        <v>1.39236664772034</v>
+        <v>1.39236652851105</v>
       </c>
       <c r="H258" t="n">
         <v>262724</v>
@@ -7909,7 +7909,7 @@
         <v>1.96099996566772</v>
       </c>
       <c r="G260" t="n">
-        <v>1.38179707527161</v>
+        <v>1.38179695606232</v>
       </c>
       <c r="H260" t="n">
         <v>487506</v>
@@ -7967,7 +7967,7 @@
         <v>2.00600004196167</v>
       </c>
       <c r="G262" t="n">
-        <v>1.41350591182709</v>
+        <v>1.4135057926178</v>
       </c>
       <c r="H262" t="n">
         <v>717038</v>
@@ -7996,7 +7996,7 @@
         <v>1.97200000286102</v>
       </c>
       <c r="G263" t="n">
-        <v>1.3895480632782</v>
+        <v>1.38954818248749</v>
       </c>
       <c r="H263" t="n">
         <v>310392</v>
@@ -8025,7 +8025,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G264" t="n">
-        <v>1.40223157405853</v>
+        <v>1.40223169326782</v>
       </c>
       <c r="H264" t="n">
         <v>511622</v>
@@ -8054,7 +8054,7 @@
         <v>2.01300001144409</v>
       </c>
       <c r="G265" t="n">
-        <v>1.41843843460083</v>
+        <v>1.41843831539154</v>
       </c>
       <c r="H265" t="n">
         <v>1394290</v>
@@ -8141,7 +8141,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G268" t="n">
-        <v>1.56077527999878</v>
+        <v>1.56077539920807</v>
       </c>
       <c r="H268" t="n">
         <v>856015</v>
@@ -8170,7 +8170,7 @@
         <v>2.20600008964539</v>
       </c>
       <c r="G269" t="n">
-        <v>1.55443382263184</v>
+        <v>1.55443358421326</v>
       </c>
       <c r="H269" t="n">
         <v>461170</v>
@@ -8228,7 +8228,7 @@
         <v>2.18300008773804</v>
       </c>
       <c r="G271" t="n">
-        <v>1.53822696208954</v>
+        <v>1.53822708129883</v>
       </c>
       <c r="H271" t="n">
         <v>558105</v>
@@ -8257,7 +8257,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G272" t="n">
-        <v>1.5332944393158</v>
+        <v>1.53329455852509</v>
       </c>
       <c r="H272" t="n">
         <v>539558</v>
@@ -8373,7 +8373,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G276" t="n">
-        <v>1.48819744586945</v>
+        <v>1.48819756507874</v>
       </c>
       <c r="H276" t="n">
         <v>185994</v>
@@ -8518,7 +8518,7 @@
         <v>2.03699994087219</v>
       </c>
       <c r="G281" t="n">
-        <v>1.43534958362579</v>
+        <v>1.43534970283508</v>
       </c>
       <c r="H281" t="n">
         <v>774489</v>
@@ -8576,7 +8576,7 @@
         <v>2.04299998283386</v>
       </c>
       <c r="G283" t="n">
-        <v>1.439577460289</v>
+        <v>1.43957734107971</v>
       </c>
       <c r="H283" t="n">
         <v>333599</v>
@@ -8605,7 +8605,7 @@
         <v>2.07599997520447</v>
       </c>
       <c r="G284" t="n">
-        <v>1.46283066272736</v>
+        <v>1.46283054351807</v>
       </c>
       <c r="H284" t="n">
         <v>725403</v>
@@ -8663,7 +8663,7 @@
         <v>2.05299997329712</v>
       </c>
       <c r="G286" t="n">
-        <v>1.44662380218506</v>
+        <v>1.44662392139435</v>
       </c>
       <c r="H286" t="n">
         <v>680373</v>
@@ -8692,7 +8692,7 @@
         <v>2.02099990844727</v>
       </c>
       <c r="G287" t="n">
-        <v>1.42407548427582</v>
+        <v>1.42407536506653</v>
       </c>
       <c r="H287" t="n">
         <v>575103</v>
@@ -8866,7 +8866,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G293" t="n">
-        <v>1.49101603031158</v>
+        <v>1.49101614952087</v>
       </c>
       <c r="H293" t="n">
         <v>500302</v>
@@ -8895,7 +8895,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G294" t="n">
-        <v>1.46705853939056</v>
+        <v>1.46705842018127</v>
       </c>
       <c r="H294" t="n">
         <v>796702</v>
@@ -8924,7 +8924,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G295" t="n">
-        <v>1.51074600219727</v>
+        <v>1.51074612140656</v>
       </c>
       <c r="H295" t="n">
         <v>440171</v>
@@ -9011,7 +9011,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G298" t="n">
-        <v>1.4755140542984</v>
+        <v>1.47551417350769</v>
       </c>
       <c r="H298" t="n">
         <v>739456</v>
@@ -9069,7 +9069,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G300" t="n">
-        <v>1.51215529441833</v>
+        <v>1.51215517520905</v>
       </c>
       <c r="H300" t="n">
         <v>616627</v>
@@ -9127,7 +9127,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G302" t="n">
-        <v>1.52202033996582</v>
+        <v>1.52202022075653</v>
       </c>
       <c r="H302" t="n">
         <v>208214</v>
@@ -9156,7 +9156,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G303" t="n">
-        <v>1.47974181175232</v>
+        <v>1.47974193096161</v>
       </c>
       <c r="H303" t="n">
         <v>495059</v>
@@ -9243,7 +9243,7 @@
         <v>2.12100005149841</v>
       </c>
       <c r="G306" t="n">
-        <v>1.49453926086426</v>
+        <v>1.49453938007355</v>
       </c>
       <c r="H306" t="n">
         <v>349362</v>
@@ -9301,7 +9301,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G308" t="n">
-        <v>1.49383473396301</v>
+        <v>1.49383461475372</v>
       </c>
       <c r="H308" t="n">
         <v>190816</v>
@@ -9388,7 +9388,7 @@
         <v>2.18300008773804</v>
       </c>
       <c r="G311" t="n">
-        <v>1.53822696208954</v>
+        <v>1.53822708129883</v>
       </c>
       <c r="H311" t="n">
         <v>1223387</v>
@@ -9446,7 +9446,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G313" t="n">
-        <v>1.61855566501617</v>
+        <v>1.61855578422546</v>
       </c>
       <c r="H313" t="n">
         <v>610651</v>
@@ -9504,7 +9504,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G315" t="n">
-        <v>1.61855566501617</v>
+        <v>1.61855578422546</v>
       </c>
       <c r="H315" t="n">
         <v>297781</v>
@@ -9533,7 +9533,7 @@
         <v>2.27300000190735</v>
       </c>
       <c r="G316" t="n">
-        <v>1.60164427757263</v>
+        <v>1.60164439678192</v>
       </c>
       <c r="H316" t="n">
         <v>370098</v>
@@ -9562,7 +9562,7 @@
         <v>2.27300000190735</v>
       </c>
       <c r="G317" t="n">
-        <v>1.60164427757263</v>
+        <v>1.60164439678192</v>
       </c>
       <c r="H317" t="n">
         <v>460584</v>
@@ -9591,7 +9591,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G318" t="n">
-        <v>1.60305380821228</v>
+        <v>1.60305368900299</v>
       </c>
       <c r="H318" t="n">
         <v>434199</v>
@@ -9620,7 +9620,7 @@
         <v>2.29299998283386</v>
       </c>
       <c r="G319" t="n">
-        <v>1.61573731899261</v>
+        <v>1.61573719978333</v>
       </c>
       <c r="H319" t="n">
         <v>855625</v>
@@ -9649,7 +9649,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G320" t="n">
-        <v>1.62489748001099</v>
+        <v>1.62489759922028</v>
       </c>
       <c r="H320" t="n">
         <v>946396</v>
@@ -9678,7 +9678,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G321" t="n">
-        <v>1.63758099079132</v>
+        <v>1.63758087158203</v>
       </c>
       <c r="H321" t="n">
         <v>897308</v>
@@ -9707,7 +9707,7 @@
         <v>2.27699995040894</v>
       </c>
       <c r="G322" t="n">
-        <v>1.60446298122406</v>
+        <v>1.60446286201477</v>
       </c>
       <c r="H322" t="n">
         <v>327351</v>
@@ -9736,7 +9736,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G323" t="n">
-        <v>1.60234904289246</v>
+        <v>1.60234892368317</v>
       </c>
       <c r="H323" t="n">
         <v>324411</v>
@@ -9765,7 +9765,7 @@
         <v>2.2590000629425</v>
       </c>
       <c r="G324" t="n">
-        <v>1.59177947044373</v>
+        <v>1.59177958965302</v>
       </c>
       <c r="H324" t="n">
         <v>573058</v>
@@ -9823,7 +9823,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G326" t="n">
-        <v>1.51074600219727</v>
+        <v>1.51074612140656</v>
       </c>
       <c r="H326" t="n">
         <v>964268</v>
@@ -9968,7 +9968,7 @@
         <v>2.25</v>
       </c>
       <c r="G331" t="n">
-        <v>1.5854377746582</v>
+        <v>1.58543789386749</v>
       </c>
       <c r="H331" t="n">
         <v>523276</v>
@@ -10055,7 +10055,7 @@
         <v>2.25</v>
       </c>
       <c r="G334" t="n">
-        <v>1.5854377746582</v>
+        <v>1.58543789386749</v>
       </c>
       <c r="H334" t="n">
         <v>841797</v>
@@ -10084,7 +10084,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G335" t="n">
-        <v>1.5769819021225</v>
+        <v>1.57698202133179</v>
       </c>
       <c r="H335" t="n">
         <v>717837</v>
@@ -10113,7 +10113,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G336" t="n">
-        <v>1.61855566501617</v>
+        <v>1.61855578422546</v>
       </c>
       <c r="H336" t="n">
         <v>709843</v>
@@ -10142,7 +10142,7 @@
         <v>2.28299999237061</v>
       </c>
       <c r="G337" t="n">
-        <v>1.60869073867798</v>
+        <v>1.60869085788727</v>
       </c>
       <c r="H337" t="n">
         <v>602165</v>
@@ -10229,7 +10229,7 @@
         <v>2.40300011634827</v>
       </c>
       <c r="G340" t="n">
-        <v>1.69324767589569</v>
+        <v>1.6932475566864</v>
       </c>
       <c r="H340" t="n">
         <v>735566</v>
@@ -10258,7 +10258,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G341" t="n">
-        <v>1.65942478179932</v>
+        <v>1.65942490100861</v>
       </c>
       <c r="H341" t="n">
         <v>442544</v>
@@ -10287,7 +10287,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>1.64533221721649</v>
+        <v>1.6453320980072</v>
       </c>
       <c r="H342" t="n">
         <v>505221</v>
@@ -10316,7 +10316,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G343" t="n">
-        <v>1.61010026931763</v>
+        <v>1.61010015010834</v>
       </c>
       <c r="H343" t="n">
         <v>391481</v>
@@ -10345,7 +10345,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G344" t="n">
-        <v>1.6629478931427</v>
+        <v>1.66294801235199</v>
       </c>
       <c r="H344" t="n">
         <v>625059</v>
@@ -10374,7 +10374,7 @@
         <v>2.33699989318848</v>
       </c>
       <c r="G345" t="n">
-        <v>1.64674127101898</v>
+        <v>1.64674139022827</v>
       </c>
       <c r="H345" t="n">
         <v>1238842</v>
@@ -10403,7 +10403,7 @@
         <v>2.33699989318848</v>
       </c>
       <c r="G346" t="n">
-        <v>1.64674127101898</v>
+        <v>1.64674139022827</v>
       </c>
       <c r="H346" t="n">
         <v>580707</v>
@@ -10432,7 +10432,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G347" t="n">
-        <v>1.62912547588348</v>
+        <v>1.62912535667419</v>
       </c>
       <c r="H347" t="n">
         <v>376051</v>
@@ -10461,7 +10461,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G348" t="n">
-        <v>1.56148016452789</v>
+        <v>1.56147992610931</v>
       </c>
       <c r="H348" t="n">
         <v>2800039</v>
@@ -10548,7 +10548,7 @@
         <v>2.19400000572205</v>
       </c>
       <c r="G351" t="n">
-        <v>1.54597795009613</v>
+        <v>1.54597806930542</v>
       </c>
       <c r="H351" t="n">
         <v>432046</v>
@@ -10606,7 +10606,7 @@
         <v>2.27099990844727</v>
       </c>
       <c r="G353" t="n">
-        <v>1.60023510456085</v>
+        <v>1.60023522377014</v>
       </c>
       <c r="H353" t="n">
         <v>454310</v>
@@ -10635,7 +10635,7 @@
         <v>2.26900005340576</v>
       </c>
       <c r="G354" t="n">
-        <v>1.59882605075836</v>
+        <v>1.59882593154907</v>
       </c>
       <c r="H354" t="n">
         <v>579865</v>
@@ -10693,7 +10693,7 @@
         <v>2.50250005722046</v>
       </c>
       <c r="G356" t="n">
-        <v>1.76335906982422</v>
+        <v>1.76335918903351</v>
       </c>
       <c r="H356" t="n">
         <v>4862397</v>
@@ -10722,7 +10722,7 @@
         <v>2.83750009536743</v>
       </c>
       <c r="G357" t="n">
-        <v>1.99941325187683</v>
+        <v>1.99941301345825</v>
       </c>
       <c r="H357" t="n">
         <v>4829114</v>
@@ -10751,7 +10751,7 @@
         <v>2.7574999332428</v>
       </c>
       <c r="G358" t="n">
-        <v>1.94304215908051</v>
+        <v>1.94304203987122</v>
       </c>
       <c r="H358" t="n">
         <v>5360863</v>
@@ -10809,7 +10809,7 @@
         <v>2.69749999046326</v>
       </c>
       <c r="G360" t="n">
-        <v>1.900763630867</v>
+        <v>1.90076375007629</v>
       </c>
       <c r="H360" t="n">
         <v>2325561</v>
@@ -10838,7 +10838,7 @@
         <v>2.65750002861023</v>
       </c>
       <c r="G361" t="n">
-        <v>1.87257814407349</v>
+        <v>1.87257826328278</v>
       </c>
       <c r="H361" t="n">
         <v>670603</v>
@@ -10867,7 +10867,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G362" t="n">
-        <v>1.81444537639618</v>
+        <v>1.81444549560547</v>
       </c>
       <c r="H362" t="n">
         <v>1637436</v>
@@ -10954,7 +10954,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G365" t="n">
-        <v>1.79330635070801</v>
+        <v>1.79330623149872</v>
       </c>
       <c r="H365" t="n">
         <v>341518</v>
@@ -10983,7 +10983,7 @@
         <v>2.50250005722046</v>
       </c>
       <c r="G366" t="n">
-        <v>1.76335906982422</v>
+        <v>1.76335918903351</v>
       </c>
       <c r="H366" t="n">
         <v>920397</v>
@@ -11099,7 +11099,7 @@
         <v>2.5550000667572</v>
       </c>
       <c r="G370" t="n">
-        <v>1.80035269260406</v>
+        <v>1.80035281181335</v>
       </c>
       <c r="H370" t="n">
         <v>510079</v>
@@ -11128,7 +11128,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G371" t="n">
-        <v>1.83206129074097</v>
+        <v>1.83206140995026</v>
       </c>
       <c r="H371" t="n">
         <v>521311</v>
@@ -11157,7 +11157,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G372" t="n">
-        <v>1.87786269187927</v>
+        <v>1.87786293029785</v>
       </c>
       <c r="H372" t="n">
         <v>730632</v>
@@ -11186,7 +11186,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G373" t="n">
-        <v>1.8849093914032</v>
+        <v>1.88490915298462</v>
       </c>
       <c r="H373" t="n">
         <v>569369</v>
@@ -11215,7 +11215,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G374" t="n">
-        <v>1.83910775184631</v>
+        <v>1.8391078710556</v>
       </c>
       <c r="H374" t="n">
         <v>564472</v>
@@ -11244,7 +11244,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G375" t="n">
-        <v>1.83910775184631</v>
+        <v>1.8391078710556</v>
       </c>
       <c r="H375" t="n">
         <v>442703</v>
@@ -11273,7 +11273,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G376" t="n">
-        <v>1.86377012729645</v>
+        <v>1.86377024650574</v>
       </c>
       <c r="H376" t="n">
         <v>303450</v>
@@ -11302,7 +11302,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G377" t="n">
-        <v>1.86377012729645</v>
+        <v>1.86377024650574</v>
       </c>
       <c r="H377" t="n">
         <v>377689</v>
@@ -11360,7 +11360,7 @@
         <v>2.64249992370605</v>
       </c>
       <c r="G379" t="n">
-        <v>1.86200869083405</v>
+        <v>1.86200857162476</v>
       </c>
       <c r="H379" t="n">
         <v>662990</v>
@@ -11389,7 +11389,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>1.86377012729645</v>
+        <v>1.86377024650574</v>
       </c>
       <c r="H380" t="n">
         <v>668827</v>
@@ -11418,7 +11418,7 @@
         <v>2.59750008583069</v>
       </c>
       <c r="G381" t="n">
-        <v>1.83029973506927</v>
+        <v>1.83029997348785</v>
       </c>
       <c r="H381" t="n">
         <v>623499</v>
@@ -11505,7 +11505,7 @@
         <v>2.55749988555908</v>
       </c>
       <c r="G384" t="n">
-        <v>1.80211412906647</v>
+        <v>1.80211424827576</v>
       </c>
       <c r="H384" t="n">
         <v>1307235</v>
@@ -11563,7 +11563,7 @@
         <v>2.35700011253357</v>
       </c>
       <c r="G386" t="n">
-        <v>1.84116351604462</v>
+        <v>1.84116363525391</v>
       </c>
       <c r="H386" t="n">
         <v>1675723</v>
@@ -11621,7 +11621,7 @@
         <v>2.27699995040894</v>
       </c>
       <c r="G388" t="n">
-        <v>1.7786717414856</v>
+        <v>1.77867162227631</v>
       </c>
       <c r="H388" t="n">
         <v>1448376</v>
@@ -11679,7 +11679,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G390" t="n">
-        <v>1.85131824016571</v>
+        <v>1.851318359375</v>
       </c>
       <c r="H390" t="n">
         <v>717045</v>
@@ -11766,7 +11766,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G393" t="n">
-        <v>1.86069214344025</v>
+        <v>1.86069202423096</v>
       </c>
       <c r="H393" t="n">
         <v>631226</v>
@@ -11795,7 +11795,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G394" t="n">
-        <v>1.81694793701172</v>
+        <v>1.81694805622101</v>
       </c>
       <c r="H394" t="n">
         <v>634308</v>
@@ -11824,7 +11824,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G395" t="n">
-        <v>1.84506940841675</v>
+        <v>1.84506916999817</v>
       </c>
       <c r="H395" t="n">
         <v>768257</v>
@@ -11853,7 +11853,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G396" t="n">
-        <v>1.81694793701172</v>
+        <v>1.81694805622101</v>
       </c>
       <c r="H396" t="n">
         <v>564016</v>
@@ -11882,7 +11882,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G397" t="n">
-        <v>1.79429459571838</v>
+        <v>1.79429471492767</v>
       </c>
       <c r="H397" t="n">
         <v>625118</v>
@@ -11940,7 +11940,7 @@
         <v>2.3289999961853</v>
       </c>
       <c r="G399" t="n">
-        <v>1.81929135322571</v>
+        <v>1.819291472435</v>
       </c>
       <c r="H399" t="n">
         <v>717310</v>
@@ -11998,7 +11998,7 @@
         <v>2.30800008773804</v>
       </c>
       <c r="G401" t="n">
-        <v>1.80288732051849</v>
+        <v>1.80288743972778</v>
       </c>
       <c r="H401" t="n">
         <v>290608</v>
@@ -12143,7 +12143,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G406" t="n">
-        <v>1.82944655418396</v>
+        <v>1.82944643497467</v>
       </c>
       <c r="H406" t="n">
         <v>327031</v>
@@ -12172,7 +12172,7 @@
         <v>2.33899998664856</v>
       </c>
       <c r="G407" t="n">
-        <v>1.82710289955139</v>
+        <v>1.82710301876068</v>
       </c>
       <c r="H407" t="n">
         <v>366090</v>
@@ -12201,7 +12201,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G408" t="n">
-        <v>1.78257763385773</v>
+        <v>1.78257751464844</v>
       </c>
       <c r="H408" t="n">
         <v>720575</v>
@@ -12317,7 +12317,7 @@
         <v>2.3289999961853</v>
       </c>
       <c r="G412" t="n">
-        <v>1.81929135322571</v>
+        <v>1.819291472435</v>
       </c>
       <c r="H412" t="n">
         <v>1092003</v>
@@ -12346,7 +12346,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G413" t="n">
-        <v>1.82397842407227</v>
+        <v>1.82397830486298</v>
       </c>
       <c r="H413" t="n">
         <v>525566</v>
@@ -12404,7 +12404,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G415" t="n">
-        <v>1.79351365566254</v>
+        <v>1.79351353645325</v>
       </c>
       <c r="H415" t="n">
         <v>274714</v>
@@ -12433,7 +12433,7 @@
         <v>2.27699995040894</v>
       </c>
       <c r="G416" t="n">
-        <v>1.7786717414856</v>
+        <v>1.77867162227631</v>
       </c>
       <c r="H416" t="n">
         <v>797388</v>
@@ -12462,7 +12462,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G417" t="n">
-        <v>1.77945303916931</v>
+        <v>1.7794531583786</v>
       </c>
       <c r="H417" t="n">
         <v>672807</v>
@@ -12491,7 +12491,7 @@
         <v>2.26099991798401</v>
       </c>
       <c r="G418" t="n">
-        <v>1.76617348194122</v>
+        <v>1.76617324352264</v>
       </c>
       <c r="H418" t="n">
         <v>422740</v>
@@ -12520,7 +12520,7 @@
         <v>2.23699998855591</v>
       </c>
       <c r="G419" t="n">
-        <v>1.74742591381073</v>
+        <v>1.74742603302002</v>
       </c>
       <c r="H419" t="n">
         <v>1089414</v>
@@ -12578,7 +12578,7 @@
         <v>2.2590000629425</v>
       </c>
       <c r="G421" t="n">
-        <v>1.76461112499237</v>
+        <v>1.76461124420166</v>
       </c>
       <c r="H421" t="n">
         <v>373347</v>
@@ -12607,7 +12607,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G422" t="n">
-        <v>1.7302405834198</v>
+        <v>1.73024070262909</v>
       </c>
       <c r="H422" t="n">
         <v>493842</v>
@@ -12665,7 +12665,7 @@
         <v>2.14100003242493</v>
       </c>
       <c r="G424" t="n">
-        <v>1.67243587970734</v>
+        <v>1.67243576049805</v>
       </c>
       <c r="H424" t="n">
         <v>2417146</v>
@@ -12723,7 +12723,7 @@
         <v>2.11700010299683</v>
       </c>
       <c r="G426" t="n">
-        <v>1.65368843078613</v>
+        <v>1.65368831157684</v>
       </c>
       <c r="H426" t="n">
         <v>542238</v>
@@ -12781,7 +12781,7 @@
         <v>2.1010000705719</v>
       </c>
       <c r="G428" t="n">
-        <v>1.64119005203247</v>
+        <v>1.64118993282318</v>
       </c>
       <c r="H428" t="n">
         <v>384515</v>
@@ -12810,7 +12810,7 @@
         <v>2.0789999961853</v>
       </c>
       <c r="G429" t="n">
-        <v>1.62400460243225</v>
+        <v>1.62400472164154</v>
       </c>
       <c r="H429" t="n">
         <v>242331</v>
@@ -12839,7 +12839,7 @@
         <v>2.05299997329712</v>
       </c>
       <c r="G430" t="n">
-        <v>1.60369479656219</v>
+        <v>1.60369491577148</v>
       </c>
       <c r="H430" t="n">
         <v>355572</v>
@@ -12926,7 +12926,7 @@
         <v>1.97699999809265</v>
       </c>
       <c r="G433" t="n">
-        <v>1.54432773590088</v>
+        <v>1.54432761669159</v>
       </c>
       <c r="H433" t="n">
         <v>335769</v>
@@ -12984,7 +12984,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G435" t="n">
-        <v>1.50136470794678</v>
+        <v>1.50136458873749</v>
       </c>
       <c r="H435" t="n">
         <v>423668</v>
@@ -13013,7 +13013,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G436" t="n">
-        <v>1.45762038230896</v>
+        <v>1.45762050151825</v>
       </c>
       <c r="H436" t="n">
         <v>630873</v>
@@ -13071,7 +13071,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G438" t="n">
-        <v>1.43887281417847</v>
+        <v>1.43887293338776</v>
       </c>
       <c r="H438" t="n">
         <v>297282</v>
@@ -13158,7 +13158,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G441" t="n">
-        <v>1.48417937755585</v>
+        <v>1.48417925834656</v>
       </c>
       <c r="H441" t="n">
         <v>558928</v>
@@ -13187,7 +13187,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G442" t="n">
-        <v>1.48417937755585</v>
+        <v>1.48417925834656</v>
       </c>
       <c r="H442" t="n">
         <v>264102</v>
@@ -13274,7 +13274,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G445" t="n">
-        <v>1.48886632919312</v>
+        <v>1.48886620998383</v>
       </c>
       <c r="H445" t="n">
         <v>825110</v>
@@ -13390,7 +13390,7 @@
         <v>1.8309999704361</v>
       </c>
       <c r="G449" t="n">
-        <v>1.43028008937836</v>
+        <v>1.43028020858765</v>
       </c>
       <c r="H449" t="n">
         <v>475160</v>
@@ -13448,7 +13448,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G451" t="n">
-        <v>1.4099702835083</v>
+        <v>1.40997040271759</v>
       </c>
       <c r="H451" t="n">
         <v>1406663</v>
@@ -13477,7 +13477,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G452" t="n">
-        <v>1.31232690811157</v>
+        <v>1.31232702732086</v>
       </c>
       <c r="H452" t="n">
         <v>1384290</v>
@@ -13506,7 +13506,7 @@
         <v>1.67340004444122</v>
       </c>
       <c r="G453" t="n">
-        <v>1.30717146396637</v>
+        <v>1.30717158317566</v>
       </c>
       <c r="H453" t="n">
         <v>770495</v>
@@ -13709,7 +13709,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G460" t="n">
-        <v>1.42715573310852</v>
+        <v>1.42715561389923</v>
       </c>
       <c r="H460" t="n">
         <v>222767</v>
@@ -13767,7 +13767,7 @@
         <v>1.80599999427795</v>
       </c>
       <c r="G462" t="n">
-        <v>1.41075158119202</v>
+        <v>1.41075146198273</v>
       </c>
       <c r="H462" t="n">
         <v>246924</v>
@@ -13796,7 +13796,7 @@
         <v>1.94939994812012</v>
       </c>
       <c r="G463" t="n">
-        <v>1.52276802062988</v>
+        <v>1.52276790142059</v>
       </c>
       <c r="H463" t="n">
         <v>916642</v>
@@ -13854,7 +13854,7 @@
         <v>1.92239999771118</v>
       </c>
       <c r="G465" t="n">
-        <v>1.50167691707611</v>
+        <v>1.50167715549469</v>
       </c>
       <c r="H465" t="n">
         <v>353065</v>
@@ -13912,7 +13912,7 @@
         <v>2.02049994468689</v>
       </c>
       <c r="G467" t="n">
-        <v>1.5783075094223</v>
+        <v>1.57830739021301</v>
       </c>
       <c r="H467" t="n">
         <v>756810</v>
@@ -14057,7 +14057,7 @@
         <v>2.00850009918213</v>
       </c>
       <c r="G472" t="n">
-        <v>1.56893396377563</v>
+        <v>1.56893384456635</v>
       </c>
       <c r="H472" t="n">
         <v>366405</v>
@@ -14115,7 +14115,7 @@
         <v>2.29450011253357</v>
       </c>
       <c r="G474" t="n">
-        <v>1.79234194755554</v>
+        <v>1.79234206676483</v>
       </c>
       <c r="H474" t="n">
         <v>1337287</v>
@@ -14144,7 +14144,7 @@
         <v>2.25950002670288</v>
       </c>
       <c r="G475" t="n">
-        <v>1.76500165462494</v>
+        <v>1.76500177383423</v>
       </c>
       <c r="H475" t="n">
         <v>775246</v>
@@ -14173,7 +14173,7 @@
         <v>2.25650000572205</v>
       </c>
       <c r="G476" t="n">
-        <v>1.76265835762024</v>
+        <v>1.76265823841095</v>
       </c>
       <c r="H476" t="n">
         <v>463148</v>
@@ -14202,7 +14202,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G477" t="n">
-        <v>1.75601851940155</v>
+        <v>1.75601840019226</v>
       </c>
       <c r="H477" t="n">
         <v>381912</v>
@@ -14231,7 +14231,7 @@
         <v>2.22699999809265</v>
       </c>
       <c r="G478" t="n">
-        <v>1.73961448669434</v>
+        <v>1.73961436748505</v>
       </c>
       <c r="H478" t="n">
         <v>1434510</v>
@@ -14289,7 +14289,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G480" t="n">
-        <v>1.7466447353363</v>
+        <v>1.74664485454559</v>
       </c>
       <c r="H480" t="n">
         <v>1270704</v>
@@ -14318,7 +14318,7 @@
         <v>2.22300004959106</v>
       </c>
       <c r="G481" t="n">
-        <v>1.73649001121521</v>
+        <v>1.73648989200592</v>
       </c>
       <c r="H481" t="n">
         <v>624711</v>
@@ -14376,7 +14376,7 @@
         <v>2.29749989509583</v>
       </c>
       <c r="G483" t="n">
-        <v>1.79468512535095</v>
+        <v>1.79468524456024</v>
       </c>
       <c r="H483" t="n">
         <v>1095196</v>
@@ -14434,7 +14434,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G485" t="n">
-        <v>1.86850368976593</v>
+        <v>1.86850380897522</v>
       </c>
       <c r="H485" t="n">
         <v>792725</v>
@@ -14492,7 +14492,7 @@
         <v>2.25</v>
       </c>
       <c r="G487" t="n">
-        <v>1.7575808763504</v>
+        <v>1.75758099555969</v>
       </c>
       <c r="H487" t="n">
         <v>1370262</v>
@@ -14666,7 +14666,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G493" t="n">
-        <v>1.86225438117981</v>
+        <v>1.86225473880768</v>
       </c>
       <c r="H493" t="n">
         <v>271589</v>
@@ -14724,7 +14724,7 @@
         <v>2.38100004196167</v>
       </c>
       <c r="G495" t="n">
-        <v>1.85991108417511</v>
+        <v>1.8599112033844</v>
       </c>
       <c r="H495" t="n">
         <v>360476</v>
@@ -14811,7 +14811,7 @@
         <v>2.38899993896484</v>
       </c>
       <c r="G498" t="n">
-        <v>1.86616027355194</v>
+        <v>1.86616015434265</v>
       </c>
       <c r="H498" t="n">
         <v>465046</v>
@@ -14840,7 +14840,7 @@
         <v>2.3289999961853</v>
       </c>
       <c r="G499" t="n">
-        <v>1.81929135322571</v>
+        <v>1.819291472435</v>
       </c>
       <c r="H499" t="n">
         <v>426104</v>
@@ -14869,7 +14869,7 @@
         <v>2.35899996757507</v>
       </c>
       <c r="G500" t="n">
-        <v>1.84272587299347</v>
+        <v>1.84272575378418</v>
       </c>
       <c r="H500" t="n">
         <v>444448</v>
@@ -14898,7 +14898,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G501" t="n">
-        <v>1.86069214344025</v>
+        <v>1.86069202423096</v>
       </c>
       <c r="H501" t="n">
         <v>431708</v>
@@ -14956,7 +14956,7 @@
         <v>2.4210000038147</v>
       </c>
       <c r="G503" t="n">
-        <v>1.89115703105927</v>
+        <v>1.89115715026855</v>
       </c>
       <c r="H503" t="n">
         <v>400870</v>
@@ -15014,7 +15014,7 @@
         <v>2.40199995040894</v>
       </c>
       <c r="G505" t="n">
-        <v>1.87631499767303</v>
+        <v>1.87631523609161</v>
       </c>
       <c r="H505" t="n">
         <v>719122</v>
@@ -15072,7 +15072,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G507" t="n">
-        <v>1.85131824016571</v>
+        <v>1.851318359375</v>
       </c>
       <c r="H507" t="n">
         <v>420850</v>
@@ -15130,7 +15130,7 @@
         <v>2.37949991226196</v>
       </c>
       <c r="G509" t="n">
-        <v>1.85873937606812</v>
+        <v>1.85873925685883</v>
       </c>
       <c r="H509" t="n">
         <v>517495</v>
@@ -15159,7 +15159,7 @@
         <v>2.33949995040894</v>
       </c>
       <c r="G510" t="n">
-        <v>1.82749330997467</v>
+        <v>1.82749342918396</v>
       </c>
       <c r="H510" t="n">
         <v>387078</v>
@@ -15188,7 +15188,7 @@
         <v>2.30800008773804</v>
       </c>
       <c r="G511" t="n">
-        <v>1.80288732051849</v>
+        <v>1.80288743972778</v>
       </c>
       <c r="H511" t="n">
         <v>471638</v>
@@ -15304,7 +15304,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G515" t="n">
-        <v>1.88256442546844</v>
+        <v>1.88256454467773</v>
       </c>
       <c r="H515" t="n">
         <v>456876</v>
@@ -15391,7 +15391,7 @@
         <v>2.35949993133545</v>
       </c>
       <c r="G518" t="n">
-        <v>1.84311628341675</v>
+        <v>1.84311640262604</v>
       </c>
       <c r="H518" t="n">
         <v>314732</v>
@@ -15420,7 +15420,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G519" t="n">
-        <v>1.84506940841675</v>
+        <v>1.84506916999817</v>
       </c>
       <c r="H519" t="n">
         <v>346938</v>
@@ -15536,7 +15536,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G523" t="n">
-        <v>1.74352025985718</v>
+        <v>1.74352014064789</v>
       </c>
       <c r="H523" t="n">
         <v>587511</v>
@@ -15594,7 +15594,7 @@
         <v>2.18650007247925</v>
       </c>
       <c r="G525" t="n">
-        <v>1.70797789096832</v>
+        <v>1.7079781293869</v>
       </c>
       <c r="H525" t="n">
         <v>339135</v>
@@ -15623,7 +15623,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G526" t="n">
-        <v>1.63103497028351</v>
+        <v>1.6310350894928</v>
       </c>
       <c r="H526" t="n">
         <v>2425155</v>
@@ -15681,7 +15681,7 @@
         <v>2.06399989128113</v>
       </c>
       <c r="G528" t="n">
-        <v>1.61228740215302</v>
+        <v>1.61228728294373</v>
       </c>
       <c r="H528" t="n">
         <v>854481</v>
@@ -15710,7 +15710,7 @@
         <v>2.1324999332428</v>
       </c>
       <c r="G529" t="n">
-        <v>1.66579604148865</v>
+        <v>1.66579592227936</v>
       </c>
       <c r="H529" t="n">
         <v>1224677</v>
@@ -15739,7 +15739,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G530" t="n">
-        <v>1.65603172779083</v>
+        <v>1.65603160858154</v>
       </c>
       <c r="H530" t="n">
         <v>1091564</v>
@@ -15797,7 +15797,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G532" t="n">
-        <v>1.62478578090668</v>
+        <v>1.62478566169739</v>
       </c>
       <c r="H532" t="n">
         <v>570995</v>
@@ -15826,7 +15826,7 @@
         <v>2.07750010490417</v>
       </c>
       <c r="G533" t="n">
-        <v>1.62283301353455</v>
+        <v>1.62283313274384</v>
       </c>
       <c r="H533" t="n">
         <v>369112</v>
@@ -15971,7 +15971,7 @@
         <v>2.11150002479553</v>
       </c>
       <c r="G538" t="n">
-        <v>1.64939200878143</v>
+        <v>1.64939188957214</v>
       </c>
       <c r="H538" t="n">
         <v>386864</v>
@@ -16000,7 +16000,7 @@
         <v>2.1010000705719</v>
       </c>
       <c r="G539" t="n">
-        <v>1.64119005203247</v>
+        <v>1.64118993282318</v>
       </c>
       <c r="H539" t="n">
         <v>348613</v>
@@ -16203,7 +16203,7 @@
         <v>2.14299988746643</v>
       </c>
       <c r="G546" t="n">
-        <v>1.67399799823761</v>
+        <v>1.67399787902832</v>
       </c>
       <c r="H546" t="n">
         <v>1450618</v>
@@ -16261,7 +16261,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G548" t="n">
-        <v>1.66853010654449</v>
+        <v>1.66852998733521</v>
       </c>
       <c r="H548" t="n">
         <v>589194</v>
@@ -16290,7 +16290,7 @@
         <v>2.12949991226196</v>
       </c>
       <c r="G549" t="n">
-        <v>1.66345250606537</v>
+        <v>1.66345262527466</v>
       </c>
       <c r="H549" t="n">
         <v>838112</v>
@@ -16406,7 +16406,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G553" t="n">
-        <v>1.74976944923401</v>
+        <v>1.74976921081543</v>
       </c>
       <c r="H553" t="n">
         <v>1944729</v>
@@ -16464,7 +16464,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G555" t="n">
-        <v>1.74352025985718</v>
+        <v>1.74352014064789</v>
       </c>
       <c r="H555" t="n">
         <v>532106</v>
@@ -16522,7 +16522,7 @@
         <v>2.30550003051758</v>
       </c>
       <c r="G557" t="n">
-        <v>1.80093455314636</v>
+        <v>1.80093443393707</v>
       </c>
       <c r="H557" t="n">
         <v>567946</v>
@@ -16580,7 +16580,7 @@
         <v>2.42149996757507</v>
       </c>
       <c r="G559" t="n">
-        <v>1.89154744148254</v>
+        <v>1.89154732227325</v>
       </c>
       <c r="H559" t="n">
         <v>1056336</v>
@@ -16609,7 +16609,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G560" t="n">
-        <v>1.87865853309631</v>
+        <v>1.8786586523056</v>
       </c>
       <c r="H560" t="n">
         <v>518625</v>
@@ -16638,7 +16638,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G561" t="n">
-        <v>1.92630875110626</v>
+        <v>1.92630887031555</v>
       </c>
       <c r="H561" t="n">
         <v>1119220</v>
@@ -16667,7 +16667,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G562" t="n">
-        <v>1.95130527019501</v>
+        <v>1.95130515098572</v>
       </c>
       <c r="H562" t="n">
         <v>455972</v>
@@ -16696,7 +16696,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G563" t="n">
-        <v>1.96536588668823</v>
+        <v>1.96536600589752</v>
       </c>
       <c r="H563" t="n">
         <v>1160065</v>
@@ -16725,7 +16725,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G564" t="n">
-        <v>1.92162179946899</v>
+        <v>1.9216216802597</v>
       </c>
       <c r="H564" t="n">
         <v>582073</v>
@@ -16783,7 +16783,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G566" t="n">
-        <v>1.98411345481873</v>
+        <v>1.98411333560944</v>
       </c>
       <c r="H566" t="n">
         <v>1037237</v>
@@ -16841,7 +16841,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G568" t="n">
-        <v>1.99661195278168</v>
+        <v>1.99661159515381</v>
       </c>
       <c r="H568" t="n">
         <v>1003381</v>
@@ -16870,7 +16870,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G569" t="n">
-        <v>1.92005932331085</v>
+        <v>1.92005944252014</v>
       </c>
       <c r="H569" t="n">
         <v>1136036</v>
@@ -16957,7 +16957,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G572" t="n">
-        <v>1.92162179946899</v>
+        <v>1.9216216802597</v>
       </c>
       <c r="H572" t="n">
         <v>224932</v>
@@ -16986,7 +16986,7 @@
         <v>2.56800007820129</v>
       </c>
       <c r="G573" t="n">
-        <v>2.00598549842834</v>
+        <v>2.00598573684692</v>
       </c>
       <c r="H573" t="n">
         <v>4035540</v>
@@ -17015,7 +17015,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G574" t="n">
-        <v>2.02785754203796</v>
+        <v>2.02785778045654</v>
       </c>
       <c r="H574" t="n">
         <v>1096883</v>
@@ -17073,7 +17073,7 @@
         <v>2.70600008964539</v>
       </c>
       <c r="G576" t="n">
-        <v>2.11378407478333</v>
+        <v>2.11378383636475</v>
       </c>
       <c r="H576" t="n">
         <v>1342948</v>
@@ -17102,7 +17102,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G577" t="n">
-        <v>2.12784433364868</v>
+        <v>2.12784457206726</v>
       </c>
       <c r="H577" t="n">
         <v>1427518</v>
@@ -17189,7 +17189,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G580" t="n">
-        <v>2.21064591407776</v>
+        <v>2.21064615249634</v>
       </c>
       <c r="H580" t="n">
         <v>2199411</v>
@@ -17247,7 +17247,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>2.1793999671936</v>
+        <v>2.17940020561218</v>
       </c>
       <c r="H582" t="n">
         <v>543959</v>
@@ -17363,7 +17363,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G586" t="n">
-        <v>2.25751519203186</v>
+        <v>2.2575147151947</v>
       </c>
       <c r="H586" t="n">
         <v>1032388</v>
@@ -17537,7 +17537,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G592" t="n">
-        <v>2.4387412071228</v>
+        <v>2.43874096870422</v>
       </c>
       <c r="H592" t="n">
         <v>965545</v>
@@ -17653,7 +17653,7 @@
         <v>3.00399994850159</v>
       </c>
       <c r="G596" t="n">
-        <v>2.34656548500061</v>
+        <v>2.34656572341919</v>
       </c>
       <c r="H596" t="n">
         <v>921949</v>
@@ -17740,7 +17740,7 @@
         <v>3.10800004005432</v>
       </c>
       <c r="G599" t="n">
-        <v>2.42780494689941</v>
+        <v>2.42780518531799</v>
       </c>
       <c r="H599" t="n">
         <v>1169838</v>
@@ -17827,7 +17827,7 @@
         <v>3.06800007820129</v>
       </c>
       <c r="G602" t="n">
-        <v>2.39655923843384</v>
+        <v>2.39655900001526</v>
       </c>
       <c r="H602" t="n">
         <v>1252196</v>
@@ -17943,7 +17943,7 @@
         <v>3.30399990081787</v>
       </c>
       <c r="G606" t="n">
-        <v>2.58090949058533</v>
+        <v>2.58090972900391</v>
       </c>
       <c r="H606" t="n">
         <v>2221014</v>
@@ -17972,7 +17972,7 @@
         <v>3.26799988746643</v>
       </c>
       <c r="G607" t="n">
-        <v>2.55278825759888</v>
+        <v>2.55278849601746</v>
       </c>
       <c r="H607" t="n">
         <v>1444083</v>
@@ -18030,7 +18030,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G609" t="n">
-        <v>2.54810190200806</v>
+        <v>2.54810166358948</v>
       </c>
       <c r="H609" t="n">
         <v>548275</v>
@@ -18059,7 +18059,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G610" t="n">
-        <v>2.46373796463013</v>
+        <v>2.46373772621155</v>
       </c>
       <c r="H610" t="n">
         <v>1532299</v>
@@ -18117,7 +18117,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G612" t="n">
-        <v>2.4137442111969</v>
+        <v>2.41374444961548</v>
       </c>
       <c r="H612" t="n">
         <v>1036670</v>
@@ -18146,7 +18146,7 @@
         <v>3.0220000743866</v>
       </c>
       <c r="G613" t="n">
-        <v>2.3606264591217</v>
+        <v>2.36062622070312</v>
       </c>
       <c r="H613" t="n">
         <v>1605438</v>
@@ -18233,7 +18233,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G616" t="n">
-        <v>2.39343452453613</v>
+        <v>2.39343428611755</v>
       </c>
       <c r="H616" t="n">
         <v>397137</v>
@@ -18378,7 +18378,7 @@
         <v>3.18799996376038</v>
       </c>
       <c r="G621" t="n">
-        <v>2.49029684066772</v>
+        <v>2.49029660224915</v>
       </c>
       <c r="H621" t="n">
         <v>691299</v>
@@ -18407,7 +18407,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G622" t="n">
-        <v>2.52310514450073</v>
+        <v>2.52310490608215</v>
       </c>
       <c r="H622" t="n">
         <v>1734037</v>
@@ -18552,7 +18552,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G627" t="n">
-        <v>2.52310514450073</v>
+        <v>2.52310490608215</v>
       </c>
       <c r="H627" t="n">
         <v>1052134</v>
@@ -18726,7 +18726,7 @@
         <v>3.42199993133545</v>
       </c>
       <c r="G633" t="n">
-        <v>2.67308497428894</v>
+        <v>2.67308521270752</v>
       </c>
       <c r="H633" t="n">
         <v>1448985</v>
@@ -18755,7 +18755,7 @@
         <v>3.45199990272522</v>
       </c>
       <c r="G634" t="n">
-        <v>2.69651961326599</v>
+        <v>2.69651937484741</v>
       </c>
       <c r="H634" t="n">
         <v>1023448</v>
@@ -18784,7 +18784,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G635" t="n">
-        <v>2.71058034896851</v>
+        <v>2.71058011054993</v>
       </c>
       <c r="H635" t="n">
         <v>867265</v>
@@ -18813,7 +18813,7 @@
         <v>3.53600001335144</v>
       </c>
       <c r="G636" t="n">
-        <v>2.76213598251343</v>
+        <v>2.76213574409485</v>
       </c>
       <c r="H636" t="n">
         <v>946938</v>
@@ -35407,6 +35407,35 @@
         <v>1578337</v>
       </c>
       <c r="I1208" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1209" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1209" t="n">
+        <v>2.11800003051758</v>
+      </c>
+      <c r="D1209" t="n">
+        <v>2.11800003051758</v>
+      </c>
+      <c r="E1209" t="n">
+        <v>2.08599996566772</v>
+      </c>
+      <c r="F1209" t="n">
+        <v>2.09200000762939</v>
+      </c>
+      <c r="G1209" t="n">
+        <v>2.09200000762939</v>
+      </c>
+      <c r="H1209" t="n">
+        <v>1359227</v>
+      </c>
+      <c r="I1209" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MFEA.MI.xlsx
+++ b/data/MFEA.MI.xlsx
@@ -456,7 +456,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G3" t="n">
-        <v>2.25028014183044</v>
+        <v>2.25028038024902</v>
       </c>
       <c r="H3" t="n">
         <v>367297</v>
@@ -601,7 +601,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G8" t="n">
-        <v>2.27494072914124</v>
+        <v>2.27494096755981</v>
       </c>
       <c r="H8" t="n">
         <v>174924</v>
@@ -659,7 +659,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>2.33659219741821</v>
+        <v>2.33659195899963</v>
       </c>
       <c r="H10" t="n">
         <v>166086</v>
@@ -688,7 +688,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G11" t="n">
-        <v>2.31501388549805</v>
+        <v>2.31501412391663</v>
       </c>
       <c r="H11" t="n">
         <v>127118</v>
@@ -775,7 +775,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G14" t="n">
-        <v>2.23178458213806</v>
+        <v>2.23178434371948</v>
       </c>
       <c r="H14" t="n">
         <v>244637</v>
@@ -833,7 +833,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6448495388031</v>
+        <v>2.64484977722168</v>
       </c>
       <c r="H16" t="n">
         <v>857484</v>
@@ -862,7 +862,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G17" t="n">
-        <v>2.69417071342468</v>
+        <v>2.69417095184326</v>
       </c>
       <c r="H17" t="n">
         <v>431766</v>
@@ -891,7 +891,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G18" t="n">
-        <v>2.66951036453247</v>
+        <v>2.66951012611389</v>
       </c>
       <c r="H18" t="n">
         <v>629452</v>
@@ -920,7 +920,7 @@
         <v>4.28249979019165</v>
       </c>
       <c r="G19" t="n">
-        <v>2.64022588729858</v>
+        <v>2.64022564888</v>
       </c>
       <c r="H19" t="n">
         <v>318343</v>
@@ -978,7 +978,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G21" t="n">
-        <v>2.6479320526123</v>
+        <v>2.64793229103088</v>
       </c>
       <c r="H21" t="n">
         <v>296725</v>
@@ -1036,7 +1036,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G23" t="n">
-        <v>2.49688625335693</v>
+        <v>2.49688601493835</v>
       </c>
       <c r="H23" t="n">
         <v>230967</v>
@@ -1065,7 +1065,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G24" t="n">
-        <v>2.42598700523376</v>
+        <v>2.42598676681519</v>
       </c>
       <c r="H24" t="n">
         <v>208426</v>
@@ -1094,7 +1094,7 @@
         <v>3.99499988555908</v>
       </c>
       <c r="G25" t="n">
-        <v>2.46297788619995</v>
+        <v>2.46297764778137</v>
       </c>
       <c r="H25" t="n">
         <v>109853</v>
@@ -1442,7 +1442,7 @@
         <v>4.14249992370605</v>
       </c>
       <c r="G37" t="n">
-        <v>2.55391359329224</v>
+        <v>2.55391383171082</v>
       </c>
       <c r="H37" t="n">
         <v>310291</v>
@@ -1471,7 +1471,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G38" t="n">
-        <v>2.58936333656311</v>
+        <v>2.58936309814453</v>
       </c>
       <c r="H38" t="n">
         <v>208860</v>
@@ -1500,7 +1500,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G39" t="n">
-        <v>2.58936333656311</v>
+        <v>2.58936309814453</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -1529,7 +1529,7 @@
         <v>3.73749995231628</v>
       </c>
       <c r="G40" t="n">
-        <v>2.30422520637512</v>
+        <v>2.30422496795654</v>
       </c>
       <c r="H40" t="n">
         <v>2097188</v>
@@ -1558,7 +1558,7 @@
         <v>3.5</v>
       </c>
       <c r="G41" t="n">
-        <v>2.15780258178711</v>
+        <v>2.15780282020569</v>
       </c>
       <c r="H41" t="n">
         <v>1105386</v>
@@ -1645,7 +1645,7 @@
         <v>3.3675000667572</v>
       </c>
       <c r="G44" t="n">
-        <v>2.07611441612244</v>
+        <v>2.07611465454102</v>
       </c>
       <c r="H44" t="n">
         <v>214683</v>
@@ -1703,7 +1703,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G46" t="n">
-        <v>2.02525186538696</v>
+        <v>2.02525210380554</v>
       </c>
       <c r="H46" t="n">
         <v>426915</v>
@@ -1732,7 +1732,7 @@
         <v>3.26749992370605</v>
       </c>
       <c r="G47" t="n">
-        <v>2.01446270942688</v>
+        <v>2.01446294784546</v>
       </c>
       <c r="H47" t="n">
         <v>127552</v>
@@ -1790,7 +1790,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G49" t="n">
-        <v>2.07149076461792</v>
+        <v>2.07149052619934</v>
       </c>
       <c r="H49" t="n">
         <v>101724</v>
@@ -1819,7 +1819,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G50" t="n">
-        <v>2.02525186538696</v>
+        <v>2.02525210380554</v>
       </c>
       <c r="H50" t="n">
         <v>165272</v>
@@ -1906,7 +1906,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G53" t="n">
-        <v>1.97593080997467</v>
+        <v>1.97593057155609</v>
       </c>
       <c r="H53" t="n">
         <v>157204</v>
@@ -1935,7 +1935,7 @@
         <v>3.1175000667572</v>
       </c>
       <c r="G54" t="n">
-        <v>1.92198586463928</v>
+        <v>1.9219856262207</v>
       </c>
       <c r="H54" t="n">
         <v>195501</v>
@@ -1964,7 +1964,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G55" t="n">
-        <v>1.82796716690063</v>
+        <v>1.82796704769135</v>
       </c>
       <c r="H55" t="n">
         <v>452826</v>
@@ -1993,7 +1993,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G56" t="n">
-        <v>1.85571026802063</v>
+        <v>1.85571038722992</v>
       </c>
       <c r="H56" t="n">
         <v>119171</v>
@@ -2022,7 +2022,7 @@
         <v>3</v>
       </c>
       <c r="G57" t="n">
-        <v>1.84954535961151</v>
+        <v>1.84954524040222</v>
       </c>
       <c r="H57" t="n">
         <v>234992</v>
@@ -2080,7 +2080,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G59" t="n">
-        <v>1.79405903816223</v>
+        <v>1.79405915737152</v>
       </c>
       <c r="H59" t="n">
         <v>174796</v>
@@ -2109,7 +2109,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G60" t="n">
-        <v>1.79714155197144</v>
+        <v>1.79714131355286</v>
       </c>
       <c r="H60" t="n">
         <v>140935</v>
@@ -2167,7 +2167,7 @@
         <v>2.96250009536743</v>
       </c>
       <c r="G62" t="n">
-        <v>1.82642602920532</v>
+        <v>1.82642579078674</v>
       </c>
       <c r="H62" t="n">
         <v>167649</v>
@@ -2225,7 +2225,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G64" t="n">
-        <v>1.87728869915009</v>
+        <v>1.87728846073151</v>
       </c>
       <c r="H64" t="n">
         <v>324711</v>
@@ -2254,7 +2254,7 @@
         <v>2.89249992370605</v>
       </c>
       <c r="G65" t="n">
-        <v>1.78326988220215</v>
+        <v>1.78326976299286</v>
       </c>
       <c r="H65" t="n">
         <v>336035</v>
@@ -2312,7 +2312,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G67" t="n">
-        <v>1.69233393669128</v>
+        <v>1.69233381748199</v>
       </c>
       <c r="H67" t="n">
         <v>293953</v>
@@ -2399,7 +2399,7 @@
         <v>2.92750000953674</v>
       </c>
       <c r="G70" t="n">
-        <v>1.80484783649445</v>
+        <v>1.80484795570374</v>
       </c>
       <c r="H70" t="n">
         <v>1271038</v>
@@ -2428,7 +2428,7 @@
         <v>2.86249995231628</v>
       </c>
       <c r="G71" t="n">
-        <v>1.76477432250977</v>
+        <v>1.76477444171906</v>
       </c>
       <c r="H71" t="n">
         <v>710221</v>
@@ -2486,7 +2486,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G73" t="n">
-        <v>1.74165511131287</v>
+        <v>1.74165499210358</v>
       </c>
       <c r="H73" t="n">
         <v>228203</v>
@@ -2515,7 +2515,7 @@
         <v>2.75</v>
       </c>
       <c r="G74" t="n">
-        <v>1.6954163312912</v>
+        <v>1.69541656970978</v>
       </c>
       <c r="H74" t="n">
         <v>168732</v>
@@ -2602,7 +2602,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>1.64917767047882</v>
+        <v>1.64917778968811</v>
       </c>
       <c r="H77" t="n">
         <v>209971</v>
@@ -2631,7 +2631,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G78" t="n">
-        <v>1.74782013893127</v>
+        <v>1.74782025814056</v>
       </c>
       <c r="H78" t="n">
         <v>522442</v>
@@ -2689,7 +2689,7 @@
         <v>2.68249988555908</v>
       </c>
       <c r="G80" t="n">
-        <v>1.65380156040192</v>
+        <v>1.65380144119263</v>
       </c>
       <c r="H80" t="n">
         <v>289746</v>
@@ -2718,7 +2718,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G81" t="n">
-        <v>1.62143456935883</v>
+        <v>1.62143468856812</v>
       </c>
       <c r="H81" t="n">
         <v>237552</v>
@@ -2747,7 +2747,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G82" t="n">
-        <v>1.63068246841431</v>
+        <v>1.63068222999573</v>
       </c>
       <c r="H82" t="n">
         <v>172630</v>
@@ -2834,7 +2834,7 @@
         <v>2.58750009536743</v>
       </c>
       <c r="G85" t="n">
-        <v>1.59523260593414</v>
+        <v>1.59523284435272</v>
       </c>
       <c r="H85" t="n">
         <v>241301</v>
@@ -2863,7 +2863,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G86" t="n">
-        <v>1.58752632141113</v>
+        <v>1.58752620220184</v>
       </c>
       <c r="H86" t="n">
         <v>329995</v>
@@ -2892,7 +2892,7 @@
         <v>2.50250005722046</v>
       </c>
       <c r="G87" t="n">
-        <v>1.54282903671265</v>
+        <v>1.54282891750336</v>
       </c>
       <c r="H87" t="n">
         <v>224920</v>
@@ -2921,7 +2921,7 @@
         <v>2.64750003814697</v>
       </c>
       <c r="G88" t="n">
-        <v>1.63222372531891</v>
+        <v>1.6322238445282</v>
       </c>
       <c r="H88" t="n">
         <v>842562</v>
@@ -2950,7 +2950,7 @@
         <v>2.65499997138977</v>
       </c>
       <c r="G89" t="n">
-        <v>1.636847615242</v>
+        <v>1.63684749603271</v>
       </c>
       <c r="H89" t="n">
         <v>285515</v>
@@ -2979,7 +2979,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G90" t="n">
-        <v>1.62143456935883</v>
+        <v>1.62143468856812</v>
       </c>
       <c r="H90" t="n">
         <v>381738</v>
@@ -3008,7 +3008,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>1.6707558631897</v>
+        <v>1.67075598239899</v>
       </c>
       <c r="H91" t="n">
         <v>530043</v>
@@ -3066,7 +3066,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G93" t="n">
-        <v>1.63068246841431</v>
+        <v>1.63068222999573</v>
       </c>
       <c r="H93" t="n">
         <v>293851</v>
@@ -3095,7 +3095,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G94" t="n">
-        <v>1.63993000984192</v>
+        <v>1.6399302482605</v>
       </c>
       <c r="H94" t="n">
         <v>124415</v>
@@ -3124,7 +3124,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G95" t="n">
-        <v>1.59985673427582</v>
+        <v>1.59985661506653</v>
       </c>
       <c r="H95" t="n">
         <v>255560</v>
@@ -3153,7 +3153,7 @@
         <v>2.6324999332428</v>
       </c>
       <c r="G96" t="n">
-        <v>1.62297570705414</v>
+        <v>1.62297582626343</v>
       </c>
       <c r="H96" t="n">
         <v>316690</v>
@@ -3211,7 +3211,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G98" t="n">
-        <v>1.66459095478058</v>
+        <v>1.664590716362</v>
       </c>
       <c r="H98" t="n">
         <v>547180</v>
@@ -3269,7 +3269,7 @@
         <v>2.45300006866455</v>
       </c>
       <c r="G100" t="n">
-        <v>1.51231133937836</v>
+        <v>1.51231157779694</v>
       </c>
       <c r="H100" t="n">
         <v>588672</v>
@@ -3414,7 +3414,7 @@
         <v>2.25699996948242</v>
       </c>
       <c r="G105" t="n">
-        <v>1.39147460460663</v>
+        <v>1.39147448539734</v>
       </c>
       <c r="H105" t="n">
         <v>153134</v>
@@ -3443,7 +3443,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G106" t="n">
-        <v>1.39085805416107</v>
+        <v>1.39085793495178</v>
       </c>
       <c r="H106" t="n">
         <v>262719</v>
@@ -3472,7 +3472,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>1.33475518226624</v>
+        <v>1.33475506305695</v>
       </c>
       <c r="H107" t="n">
         <v>364496</v>
@@ -3530,7 +3530,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G109" t="n">
-        <v>1.31934237480164</v>
+        <v>1.31934225559235</v>
       </c>
       <c r="H109" t="n">
         <v>149597</v>
@@ -3559,7 +3559,7 @@
         <v>2.14199995994568</v>
       </c>
       <c r="G110" t="n">
-        <v>1.32057523727417</v>
+        <v>1.32057511806488</v>
       </c>
       <c r="H110" t="n">
         <v>256397</v>
@@ -3617,7 +3617,7 @@
         <v>2.24900007247925</v>
       </c>
       <c r="G112" t="n">
-        <v>1.38654243946075</v>
+        <v>1.38654232025146</v>
       </c>
       <c r="H112" t="n">
         <v>617377</v>
@@ -3704,7 +3704,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G115" t="n">
-        <v>1.36558091640472</v>
+        <v>1.36558079719543</v>
       </c>
       <c r="H115" t="n">
         <v>684447</v>
@@ -3762,7 +3762,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G117" t="n">
-        <v>1.41490209102631</v>
+        <v>1.4149022102356</v>
       </c>
       <c r="H117" t="n">
         <v>647297</v>
@@ -3791,7 +3791,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G118" t="n">
-        <v>1.34708535671234</v>
+        <v>1.34708547592163</v>
       </c>
       <c r="H118" t="n">
         <v>844960</v>
@@ -3820,7 +3820,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G119" t="n">
-        <v>1.38099360466003</v>
+        <v>1.38099384307861</v>
       </c>
       <c r="H119" t="n">
         <v>296846</v>
@@ -3878,7 +3878,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G121" t="n">
-        <v>1.40565419197083</v>
+        <v>1.4056544303894</v>
       </c>
       <c r="H121" t="n">
         <v>1163100</v>
@@ -4052,7 +4052,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G127" t="n">
-        <v>1.33043944835663</v>
+        <v>1.33043932914734</v>
       </c>
       <c r="H127" t="n">
         <v>576146</v>
@@ -4081,7 +4081,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G128" t="n">
-        <v>1.35325038433075</v>
+        <v>1.35325062274933</v>
       </c>
       <c r="H128" t="n">
         <v>1234804</v>
@@ -4110,7 +4110,7 @@
         <v>2.13700008392334</v>
       </c>
       <c r="G129" t="n">
-        <v>1.31749272346497</v>
+        <v>1.31749284267426</v>
       </c>
       <c r="H129" t="n">
         <v>756330</v>
@@ -4139,7 +4139,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G130" t="n">
-        <v>1.37791097164154</v>
+        <v>1.37791109085083</v>
       </c>
       <c r="H130" t="n">
         <v>658168</v>
@@ -4168,7 +4168,7 @@
         <v>2.21399998664856</v>
       </c>
       <c r="G131" t="n">
-        <v>1.36496424674988</v>
+        <v>1.36496436595917</v>
       </c>
       <c r="H131" t="n">
         <v>425795</v>
@@ -4197,7 +4197,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G132" t="n">
-        <v>1.29468166828156</v>
+        <v>1.29468154907227</v>
       </c>
       <c r="H132" t="n">
         <v>903030</v>
@@ -4255,7 +4255,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>1.28543400764465</v>
+        <v>1.28543388843536</v>
       </c>
       <c r="H134" t="n">
         <v>1315577</v>
@@ -4313,7 +4313,7 @@
         <v>2.20099997520447</v>
       </c>
       <c r="G136" t="n">
-        <v>1.3569495677948</v>
+        <v>1.35694968700409</v>
       </c>
       <c r="H136" t="n">
         <v>597261</v>
@@ -4342,7 +4342,7 @@
         <v>2.16199994087219</v>
       </c>
       <c r="G137" t="n">
-        <v>1.33290541172028</v>
+        <v>1.33290553092957</v>
       </c>
       <c r="H137" t="n">
         <v>695720</v>
@@ -4371,7 +4371,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G138" t="n">
-        <v>1.32304120063782</v>
+        <v>1.32304131984711</v>
       </c>
       <c r="H138" t="n">
         <v>662539</v>
@@ -4400,7 +4400,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G139" t="n">
-        <v>1.27002108097076</v>
+        <v>1.27002096176147</v>
       </c>
       <c r="H139" t="n">
         <v>1000781</v>
@@ -4429,7 +4429,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G140" t="n">
-        <v>1.27926886081696</v>
+        <v>1.27926874160767</v>
       </c>
       <c r="H140" t="n">
         <v>489036</v>
@@ -4487,7 +4487,7 @@
         <v>2.125</v>
       </c>
       <c r="G142" t="n">
-        <v>1.31009447574615</v>
+        <v>1.31009459495544</v>
       </c>
       <c r="H142" t="n">
         <v>1089881</v>
@@ -4516,7 +4516,7 @@
         <v>2.19099998474121</v>
       </c>
       <c r="G143" t="n">
-        <v>1.3507844209671</v>
+        <v>1.35078454017639</v>
       </c>
       <c r="H143" t="n">
         <v>662529</v>
@@ -4545,7 +4545,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G144" t="n">
-        <v>1.35386717319489</v>
+        <v>1.35386729240417</v>
       </c>
       <c r="H144" t="n">
         <v>698399</v>
@@ -4603,7 +4603,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G146" t="n">
-        <v>1.40257179737091</v>
+        <v>1.4025719165802</v>
       </c>
       <c r="H146" t="n">
         <v>463835</v>
@@ -4632,7 +4632,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G147" t="n">
-        <v>1.35325038433075</v>
+        <v>1.35325062274933</v>
       </c>
       <c r="H147" t="n">
         <v>729575</v>
@@ -4661,7 +4661,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G148" t="n">
-        <v>1.35633325576782</v>
+        <v>1.35633301734924</v>
       </c>
       <c r="H148" t="n">
         <v>470520</v>
@@ -4777,7 +4777,7 @@
         <v>2.05299997329712</v>
       </c>
       <c r="G152" t="n">
-        <v>1.26570546627045</v>
+        <v>1.26570534706116</v>
       </c>
       <c r="H152" t="n">
         <v>460461</v>
@@ -4864,7 +4864,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G155" t="n">
-        <v>1.28235125541687</v>
+        <v>1.28235137462616</v>
       </c>
       <c r="H155" t="n">
         <v>897371</v>
@@ -4922,7 +4922,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G157" t="n">
-        <v>1.30392932891846</v>
+        <v>1.30392944812775</v>
       </c>
       <c r="H157" t="n">
         <v>621284</v>
@@ -5067,7 +5067,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G162" t="n">
-        <v>1.28235125541687</v>
+        <v>1.28235137462616</v>
       </c>
       <c r="H162" t="n">
         <v>320464</v>
@@ -5096,7 +5096,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G163" t="n">
-        <v>1.28235125541687</v>
+        <v>1.28235137462616</v>
       </c>
       <c r="H163" t="n">
         <v>665085</v>
@@ -5183,7 +5183,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G166" t="n">
-        <v>1.28543400764465</v>
+        <v>1.28543388843536</v>
       </c>
       <c r="H166" t="n">
         <v>925875</v>
@@ -5241,7 +5241,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G168" t="n">
-        <v>1.24782645702362</v>
+        <v>1.24782633781433</v>
       </c>
       <c r="H168" t="n">
         <v>1017897</v>
@@ -5299,7 +5299,7 @@
         <v>1.84899997711182</v>
       </c>
       <c r="G170" t="n">
-        <v>1.30287754535675</v>
+        <v>1.30287742614746</v>
       </c>
       <c r="H170" t="n">
         <v>1744533</v>
@@ -5328,7 +5328,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G171" t="n">
-        <v>1.20140945911407</v>
+        <v>1.20140957832336</v>
       </c>
       <c r="H171" t="n">
         <v>1719560</v>
@@ -5386,7 +5386,7 @@
         <v>1.65199995040894</v>
       </c>
       <c r="G173" t="n">
-        <v>1.16406357288361</v>
+        <v>1.16406345367432</v>
       </c>
       <c r="H173" t="n">
         <v>1205156</v>
@@ -5444,7 +5444,7 @@
         <v>1.59099996089935</v>
       </c>
       <c r="G175" t="n">
-        <v>1.12108075618744</v>
+        <v>1.12108063697815</v>
       </c>
       <c r="H175" t="n">
         <v>1912525</v>
@@ -5473,7 +5473,7 @@
         <v>1.53900003433228</v>
       </c>
       <c r="G176" t="n">
-        <v>1.08443939685822</v>
+        <v>1.0844395160675</v>
       </c>
       <c r="H176" t="n">
         <v>1625041</v>
@@ -5531,7 +5531,7 @@
         <v>1.43900001049042</v>
       </c>
       <c r="G178" t="n">
-        <v>1.01397562026978</v>
+        <v>1.01397550106049</v>
       </c>
       <c r="H178" t="n">
         <v>1366037</v>
@@ -5560,7 +5560,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G179" t="n">
-        <v>1.064004778862</v>
+        <v>1.06400489807129</v>
       </c>
       <c r="H179" t="n">
         <v>1582704</v>
@@ -5589,7 +5589,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G180" t="n">
-        <v>1.08514392375946</v>
+        <v>1.08514404296875</v>
       </c>
       <c r="H180" t="n">
         <v>1913773</v>
@@ -5705,7 +5705,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G184" t="n">
-        <v>1.08796262741089</v>
+        <v>1.08796274662018</v>
       </c>
       <c r="H184" t="n">
         <v>1603167</v>
@@ -5850,7 +5850,7 @@
         <v>1.5110000371933</v>
       </c>
       <c r="G189" t="n">
-        <v>1.06470942497253</v>
+        <v>1.06470954418182</v>
       </c>
       <c r="H189" t="n">
         <v>1590572</v>
@@ -5966,7 +5966,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>1.15913128852844</v>
+        <v>1.15913105010986</v>
       </c>
       <c r="H193" t="n">
         <v>574328</v>
@@ -5995,7 +5995,7 @@
         <v>1.62300002574921</v>
       </c>
       <c r="G194" t="n">
-        <v>1.14362907409668</v>
+        <v>1.14362919330597</v>
       </c>
       <c r="H194" t="n">
         <v>1339210</v>
@@ -6024,7 +6024,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G195" t="n">
-        <v>1.16265439987183</v>
+        <v>1.16265451908112</v>
       </c>
       <c r="H195" t="n">
         <v>1118932</v>
@@ -6198,7 +6198,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G201" t="n">
-        <v>1.25778043270111</v>
+        <v>1.2577805519104</v>
       </c>
       <c r="H201" t="n">
         <v>515449</v>
@@ -6372,7 +6372,7 @@
         <v>1.83899998664856</v>
       </c>
       <c r="G207" t="n">
-        <v>1.29583096504211</v>
+        <v>1.2958310842514</v>
       </c>
       <c r="H207" t="n">
         <v>359958</v>
@@ -6517,7 +6517,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G212" t="n">
-        <v>1.29371726512909</v>
+        <v>1.2937171459198</v>
       </c>
       <c r="H212" t="n">
         <v>773982</v>
@@ -6546,7 +6546,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G213" t="n">
-        <v>1.28737545013428</v>
+        <v>1.28737556934357</v>
       </c>
       <c r="H213" t="n">
         <v>677501</v>
@@ -6575,7 +6575,7 @@
         <v>1.81099998950958</v>
       </c>
       <c r="G214" t="n">
-        <v>1.27610123157501</v>
+        <v>1.27610111236572</v>
       </c>
       <c r="H214" t="n">
         <v>308754</v>
@@ -6720,7 +6720,7 @@
         <v>2.04699993133545</v>
       </c>
       <c r="G219" t="n">
-        <v>1.44239592552185</v>
+        <v>1.44239604473114</v>
       </c>
       <c r="H219" t="n">
         <v>1110213</v>
@@ -6778,7 +6778,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G221" t="n">
-        <v>1.41632425785065</v>
+        <v>1.41632437705994</v>
       </c>
       <c r="H221" t="n">
         <v>434673</v>
@@ -6865,7 +6865,7 @@
         <v>2.02099990844727</v>
       </c>
       <c r="G224" t="n">
-        <v>1.42407536506653</v>
+        <v>1.42407548427582</v>
       </c>
       <c r="H224" t="n">
         <v>728660</v>
@@ -6894,7 +6894,7 @@
         <v>1.98300004005432</v>
       </c>
       <c r="G225" t="n">
-        <v>1.39729928970337</v>
+        <v>1.39729917049408</v>
       </c>
       <c r="H225" t="n">
         <v>1086938</v>
@@ -6952,7 +6952,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G227" t="n">
-        <v>1.33035838603973</v>
+        <v>1.33035850524902</v>
       </c>
       <c r="H227" t="n">
         <v>521176</v>
@@ -7097,7 +7097,7 @@
         <v>1.86300003528595</v>
       </c>
       <c r="G232" t="n">
-        <v>1.31274247169495</v>
+        <v>1.31274259090424</v>
       </c>
       <c r="H232" t="n">
         <v>190892</v>
@@ -7184,7 +7184,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G235" t="n">
-        <v>1.25778043270111</v>
+        <v>1.2577805519104</v>
       </c>
       <c r="H235" t="n">
         <v>235737</v>
@@ -7242,7 +7242,7 @@
         <v>1.82099997997284</v>
       </c>
       <c r="G237" t="n">
-        <v>1.28314769268036</v>
+        <v>1.28314757347107</v>
       </c>
       <c r="H237" t="n">
         <v>406192</v>
@@ -7329,7 +7329,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G240" t="n">
-        <v>1.27891981601715</v>
+        <v>1.27891993522644</v>
       </c>
       <c r="H240" t="n">
         <v>206556</v>
@@ -7358,7 +7358,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G241" t="n">
-        <v>1.26482701301575</v>
+        <v>1.26482689380646</v>
       </c>
       <c r="H241" t="n">
         <v>338837</v>
@@ -7387,7 +7387,7 @@
         <v>1.81900000572205</v>
       </c>
       <c r="G242" t="n">
-        <v>1.28173828125</v>
+        <v>1.28173840045929</v>
       </c>
       <c r="H242" t="n">
         <v>160229</v>
@@ -7590,7 +7590,7 @@
         <v>1.94099998474121</v>
       </c>
       <c r="G249" t="n">
-        <v>1.3677042722702</v>
+        <v>1.36770439147949</v>
       </c>
       <c r="H249" t="n">
         <v>394746</v>
@@ -7619,7 +7619,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G250" t="n">
-        <v>1.3698183298111</v>
+        <v>1.36981821060181</v>
       </c>
       <c r="H250" t="n">
         <v>296376</v>
@@ -7793,7 +7793,7 @@
         <v>1.98699998855591</v>
       </c>
       <c r="G256" t="n">
-        <v>1.40011775493622</v>
+        <v>1.40011763572693</v>
       </c>
       <c r="H256" t="n">
         <v>400869</v>
@@ -7822,7 +7822,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G257" t="n">
-        <v>1.37052297592163</v>
+        <v>1.37052285671234</v>
       </c>
       <c r="H257" t="n">
         <v>453008</v>
@@ -7851,7 +7851,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G258" t="n">
-        <v>1.39236652851105</v>
+        <v>1.39236664772034</v>
       </c>
       <c r="H258" t="n">
         <v>262724</v>
@@ -7909,7 +7909,7 @@
         <v>1.96099996566772</v>
       </c>
       <c r="G260" t="n">
-        <v>1.38179695606232</v>
+        <v>1.38179707527161</v>
       </c>
       <c r="H260" t="n">
         <v>487506</v>
@@ -7967,7 +7967,7 @@
         <v>2.00600004196167</v>
       </c>
       <c r="G262" t="n">
-        <v>1.4135057926178</v>
+        <v>1.41350591182709</v>
       </c>
       <c r="H262" t="n">
         <v>717038</v>
@@ -7996,7 +7996,7 @@
         <v>1.97200000286102</v>
       </c>
       <c r="G263" t="n">
-        <v>1.38954818248749</v>
+        <v>1.3895480632782</v>
       </c>
       <c r="H263" t="n">
         <v>310392</v>
@@ -8025,7 +8025,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G264" t="n">
-        <v>1.40223169326782</v>
+        <v>1.40223157405853</v>
       </c>
       <c r="H264" t="n">
         <v>511622</v>
@@ -8054,7 +8054,7 @@
         <v>2.01300001144409</v>
       </c>
       <c r="G265" t="n">
-        <v>1.41843831539154</v>
+        <v>1.41843843460083</v>
       </c>
       <c r="H265" t="n">
         <v>1394290</v>
@@ -8141,7 +8141,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G268" t="n">
-        <v>1.56077539920807</v>
+        <v>1.56077527999878</v>
       </c>
       <c r="H268" t="n">
         <v>856015</v>
@@ -8170,7 +8170,7 @@
         <v>2.20600008964539</v>
       </c>
       <c r="G269" t="n">
-        <v>1.55443358421326</v>
+        <v>1.55443382263184</v>
       </c>
       <c r="H269" t="n">
         <v>461170</v>
@@ -8228,7 +8228,7 @@
         <v>2.18300008773804</v>
       </c>
       <c r="G271" t="n">
-        <v>1.53822708129883</v>
+        <v>1.53822696208954</v>
       </c>
       <c r="H271" t="n">
         <v>558105</v>
@@ -8257,7 +8257,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G272" t="n">
-        <v>1.53329455852509</v>
+        <v>1.5332944393158</v>
       </c>
       <c r="H272" t="n">
         <v>539558</v>
@@ -8373,7 +8373,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G276" t="n">
-        <v>1.48819756507874</v>
+        <v>1.48819744586945</v>
       </c>
       <c r="H276" t="n">
         <v>185994</v>
@@ -8518,7 +8518,7 @@
         <v>2.03699994087219</v>
       </c>
       <c r="G281" t="n">
-        <v>1.43534970283508</v>
+        <v>1.43534958362579</v>
       </c>
       <c r="H281" t="n">
         <v>774489</v>
@@ -8576,7 +8576,7 @@
         <v>2.04299998283386</v>
       </c>
       <c r="G283" t="n">
-        <v>1.43957734107971</v>
+        <v>1.439577460289</v>
       </c>
       <c r="H283" t="n">
         <v>333599</v>
@@ -8605,7 +8605,7 @@
         <v>2.07599997520447</v>
       </c>
       <c r="G284" t="n">
-        <v>1.46283054351807</v>
+        <v>1.46283066272736</v>
       </c>
       <c r="H284" t="n">
         <v>725403</v>
@@ -8663,7 +8663,7 @@
         <v>2.05299997329712</v>
       </c>
       <c r="G286" t="n">
-        <v>1.44662392139435</v>
+        <v>1.44662380218506</v>
       </c>
       <c r="H286" t="n">
         <v>680373</v>
@@ -8692,7 +8692,7 @@
         <v>2.02099990844727</v>
       </c>
       <c r="G287" t="n">
-        <v>1.42407536506653</v>
+        <v>1.42407548427582</v>
       </c>
       <c r="H287" t="n">
         <v>575103</v>
@@ -8866,7 +8866,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G293" t="n">
-        <v>1.49101614952087</v>
+        <v>1.49101603031158</v>
       </c>
       <c r="H293" t="n">
         <v>500302</v>
@@ -8895,7 +8895,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G294" t="n">
-        <v>1.46705842018127</v>
+        <v>1.46705853939056</v>
       </c>
       <c r="H294" t="n">
         <v>796702</v>
@@ -8924,7 +8924,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G295" t="n">
-        <v>1.51074612140656</v>
+        <v>1.51074600219727</v>
       </c>
       <c r="H295" t="n">
         <v>440171</v>
@@ -9011,7 +9011,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G298" t="n">
-        <v>1.47551417350769</v>
+        <v>1.4755140542984</v>
       </c>
       <c r="H298" t="n">
         <v>739456</v>
@@ -9069,7 +9069,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G300" t="n">
-        <v>1.51215517520905</v>
+        <v>1.51215529441833</v>
       </c>
       <c r="H300" t="n">
         <v>616627</v>
@@ -9127,7 +9127,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G302" t="n">
-        <v>1.52202022075653</v>
+        <v>1.52202033996582</v>
       </c>
       <c r="H302" t="n">
         <v>208214</v>
@@ -9156,7 +9156,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G303" t="n">
-        <v>1.47974193096161</v>
+        <v>1.47974181175232</v>
       </c>
       <c r="H303" t="n">
         <v>495059</v>
@@ -9243,7 +9243,7 @@
         <v>2.12100005149841</v>
       </c>
       <c r="G306" t="n">
-        <v>1.49453938007355</v>
+        <v>1.49453926086426</v>
       </c>
       <c r="H306" t="n">
         <v>349362</v>
@@ -9301,7 +9301,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G308" t="n">
-        <v>1.49383461475372</v>
+        <v>1.49383473396301</v>
       </c>
       <c r="H308" t="n">
         <v>190816</v>
@@ -9388,7 +9388,7 @@
         <v>2.18300008773804</v>
       </c>
       <c r="G311" t="n">
-        <v>1.53822708129883</v>
+        <v>1.53822696208954</v>
       </c>
       <c r="H311" t="n">
         <v>1223387</v>
@@ -9446,7 +9446,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G313" t="n">
-        <v>1.61855578422546</v>
+        <v>1.61855566501617</v>
       </c>
       <c r="H313" t="n">
         <v>610651</v>
@@ -9504,7 +9504,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G315" t="n">
-        <v>1.61855578422546</v>
+        <v>1.61855566501617</v>
       </c>
       <c r="H315" t="n">
         <v>297781</v>
@@ -9533,7 +9533,7 @@
         <v>2.27300000190735</v>
       </c>
       <c r="G316" t="n">
-        <v>1.60164439678192</v>
+        <v>1.60164427757263</v>
       </c>
       <c r="H316" t="n">
         <v>370098</v>
@@ -9562,7 +9562,7 @@
         <v>2.27300000190735</v>
       </c>
       <c r="G317" t="n">
-        <v>1.60164439678192</v>
+        <v>1.60164427757263</v>
       </c>
       <c r="H317" t="n">
         <v>460584</v>
@@ -9591,7 +9591,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G318" t="n">
-        <v>1.60305368900299</v>
+        <v>1.60305380821228</v>
       </c>
       <c r="H318" t="n">
         <v>434199</v>
@@ -9620,7 +9620,7 @@
         <v>2.29299998283386</v>
       </c>
       <c r="G319" t="n">
-        <v>1.61573719978333</v>
+        <v>1.61573731899261</v>
       </c>
       <c r="H319" t="n">
         <v>855625</v>
@@ -9649,7 +9649,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G320" t="n">
-        <v>1.62489759922028</v>
+        <v>1.62489748001099</v>
       </c>
       <c r="H320" t="n">
         <v>946396</v>
@@ -9678,7 +9678,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G321" t="n">
-        <v>1.63758087158203</v>
+        <v>1.63758099079132</v>
       </c>
       <c r="H321" t="n">
         <v>897308</v>
@@ -9707,7 +9707,7 @@
         <v>2.27699995040894</v>
       </c>
       <c r="G322" t="n">
-        <v>1.60446286201477</v>
+        <v>1.60446298122406</v>
       </c>
       <c r="H322" t="n">
         <v>327351</v>
@@ -9736,7 +9736,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G323" t="n">
-        <v>1.60234892368317</v>
+        <v>1.60234904289246</v>
       </c>
       <c r="H323" t="n">
         <v>324411</v>
@@ -9765,7 +9765,7 @@
         <v>2.2590000629425</v>
       </c>
       <c r="G324" t="n">
-        <v>1.59177958965302</v>
+        <v>1.59177947044373</v>
       </c>
       <c r="H324" t="n">
         <v>573058</v>
@@ -9823,7 +9823,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G326" t="n">
-        <v>1.51074612140656</v>
+        <v>1.51074600219727</v>
       </c>
       <c r="H326" t="n">
         <v>964268</v>
@@ -9968,7 +9968,7 @@
         <v>2.25</v>
       </c>
       <c r="G331" t="n">
-        <v>1.58543789386749</v>
+        <v>1.5854377746582</v>
       </c>
       <c r="H331" t="n">
         <v>523276</v>
@@ -10055,7 +10055,7 @@
         <v>2.25</v>
       </c>
       <c r="G334" t="n">
-        <v>1.58543789386749</v>
+        <v>1.5854377746582</v>
       </c>
       <c r="H334" t="n">
         <v>841797</v>
@@ -10084,7 +10084,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G335" t="n">
-        <v>1.57698202133179</v>
+        <v>1.5769819021225</v>
       </c>
       <c r="H335" t="n">
         <v>717837</v>
@@ -10113,7 +10113,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G336" t="n">
-        <v>1.61855578422546</v>
+        <v>1.61855566501617</v>
       </c>
       <c r="H336" t="n">
         <v>709843</v>
@@ -10142,7 +10142,7 @@
         <v>2.28299999237061</v>
       </c>
       <c r="G337" t="n">
-        <v>1.60869085788727</v>
+        <v>1.60869073867798</v>
       </c>
       <c r="H337" t="n">
         <v>602165</v>
@@ -10229,7 +10229,7 @@
         <v>2.40300011634827</v>
       </c>
       <c r="G340" t="n">
-        <v>1.6932475566864</v>
+        <v>1.69324767589569</v>
       </c>
       <c r="H340" t="n">
         <v>735566</v>
@@ -10258,7 +10258,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G341" t="n">
-        <v>1.65942490100861</v>
+        <v>1.65942478179932</v>
       </c>
       <c r="H341" t="n">
         <v>442544</v>
@@ -10287,7 +10287,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>1.6453320980072</v>
+        <v>1.64533221721649</v>
       </c>
       <c r="H342" t="n">
         <v>505221</v>
@@ -10316,7 +10316,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G343" t="n">
-        <v>1.61010015010834</v>
+        <v>1.61010026931763</v>
       </c>
       <c r="H343" t="n">
         <v>391481</v>
@@ -10345,7 +10345,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G344" t="n">
-        <v>1.66294801235199</v>
+        <v>1.6629478931427</v>
       </c>
       <c r="H344" t="n">
         <v>625059</v>
@@ -10374,7 +10374,7 @@
         <v>2.33699989318848</v>
       </c>
       <c r="G345" t="n">
-        <v>1.64674139022827</v>
+        <v>1.64674127101898</v>
       </c>
       <c r="H345" t="n">
         <v>1238842</v>
@@ -10403,7 +10403,7 @@
         <v>2.33699989318848</v>
       </c>
       <c r="G346" t="n">
-        <v>1.64674139022827</v>
+        <v>1.64674127101898</v>
       </c>
       <c r="H346" t="n">
         <v>580707</v>
@@ -10432,7 +10432,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G347" t="n">
-        <v>1.62912535667419</v>
+        <v>1.62912547588348</v>
       </c>
       <c r="H347" t="n">
         <v>376051</v>
@@ -10461,7 +10461,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G348" t="n">
-        <v>1.56147992610931</v>
+        <v>1.56148016452789</v>
       </c>
       <c r="H348" t="n">
         <v>2800039</v>
@@ -10548,7 +10548,7 @@
         <v>2.19400000572205</v>
       </c>
       <c r="G351" t="n">
-        <v>1.54597806930542</v>
+        <v>1.54597795009613</v>
       </c>
       <c r="H351" t="n">
         <v>432046</v>
@@ -10606,7 +10606,7 @@
         <v>2.27099990844727</v>
       </c>
       <c r="G353" t="n">
-        <v>1.60023522377014</v>
+        <v>1.60023510456085</v>
       </c>
       <c r="H353" t="n">
         <v>454310</v>
@@ -10635,7 +10635,7 @@
         <v>2.26900005340576</v>
       </c>
       <c r="G354" t="n">
-        <v>1.59882593154907</v>
+        <v>1.59882605075836</v>
       </c>
       <c r="H354" t="n">
         <v>579865</v>
@@ -10693,7 +10693,7 @@
         <v>2.50250005722046</v>
       </c>
       <c r="G356" t="n">
-        <v>1.76335918903351</v>
+        <v>1.76335906982422</v>
       </c>
       <c r="H356" t="n">
         <v>4862397</v>
@@ -10722,7 +10722,7 @@
         <v>2.83750009536743</v>
       </c>
       <c r="G357" t="n">
-        <v>1.99941301345825</v>
+        <v>1.99941325187683</v>
       </c>
       <c r="H357" t="n">
         <v>4829114</v>
@@ -10751,7 +10751,7 @@
         <v>2.7574999332428</v>
       </c>
       <c r="G358" t="n">
-        <v>1.94304203987122</v>
+        <v>1.94304215908051</v>
       </c>
       <c r="H358" t="n">
         <v>5360863</v>
@@ -10809,7 +10809,7 @@
         <v>2.69749999046326</v>
       </c>
       <c r="G360" t="n">
-        <v>1.90076375007629</v>
+        <v>1.900763630867</v>
       </c>
       <c r="H360" t="n">
         <v>2325561</v>
@@ -10838,7 +10838,7 @@
         <v>2.65750002861023</v>
       </c>
       <c r="G361" t="n">
-        <v>1.87257826328278</v>
+        <v>1.87257814407349</v>
       </c>
       <c r="H361" t="n">
         <v>670603</v>
@@ -10867,7 +10867,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G362" t="n">
-        <v>1.81444549560547</v>
+        <v>1.81444537639618</v>
       </c>
       <c r="H362" t="n">
         <v>1637436</v>
@@ -10954,7 +10954,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G365" t="n">
-        <v>1.79330623149872</v>
+        <v>1.79330635070801</v>
       </c>
       <c r="H365" t="n">
         <v>341518</v>
@@ -10983,7 +10983,7 @@
         <v>2.50250005722046</v>
       </c>
       <c r="G366" t="n">
-        <v>1.76335918903351</v>
+        <v>1.76335906982422</v>
       </c>
       <c r="H366" t="n">
         <v>920397</v>
@@ -11099,7 +11099,7 @@
         <v>2.5550000667572</v>
       </c>
       <c r="G370" t="n">
-        <v>1.80035281181335</v>
+        <v>1.80035269260406</v>
       </c>
       <c r="H370" t="n">
         <v>510079</v>
@@ -11128,7 +11128,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G371" t="n">
-        <v>1.83206140995026</v>
+        <v>1.83206129074097</v>
       </c>
       <c r="H371" t="n">
         <v>521311</v>
@@ -11157,7 +11157,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G372" t="n">
-        <v>1.87786293029785</v>
+        <v>1.87786269187927</v>
       </c>
       <c r="H372" t="n">
         <v>730632</v>
@@ -11186,7 +11186,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G373" t="n">
-        <v>1.88490915298462</v>
+        <v>1.8849093914032</v>
       </c>
       <c r="H373" t="n">
         <v>569369</v>
@@ -11215,7 +11215,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G374" t="n">
-        <v>1.8391078710556</v>
+        <v>1.83910775184631</v>
       </c>
       <c r="H374" t="n">
         <v>564472</v>
@@ -11244,7 +11244,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G375" t="n">
-        <v>1.8391078710556</v>
+        <v>1.83910775184631</v>
       </c>
       <c r="H375" t="n">
         <v>442703</v>
@@ -11273,7 +11273,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G376" t="n">
-        <v>1.86377024650574</v>
+        <v>1.86377012729645</v>
       </c>
       <c r="H376" t="n">
         <v>303450</v>
@@ -11302,7 +11302,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G377" t="n">
-        <v>1.86377024650574</v>
+        <v>1.86377012729645</v>
       </c>
       <c r="H377" t="n">
         <v>377689</v>
@@ -11360,7 +11360,7 @@
         <v>2.64249992370605</v>
       </c>
       <c r="G379" t="n">
-        <v>1.86200857162476</v>
+        <v>1.86200869083405</v>
       </c>
       <c r="H379" t="n">
         <v>662990</v>
@@ -11389,7 +11389,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>1.86377024650574</v>
+        <v>1.86377012729645</v>
       </c>
       <c r="H380" t="n">
         <v>668827</v>
@@ -11418,7 +11418,7 @@
         <v>2.59750008583069</v>
       </c>
       <c r="G381" t="n">
-        <v>1.83029997348785</v>
+        <v>1.83029973506927</v>
       </c>
       <c r="H381" t="n">
         <v>623499</v>
@@ -11505,7 +11505,7 @@
         <v>2.55749988555908</v>
       </c>
       <c r="G384" t="n">
-        <v>1.80211424827576</v>
+        <v>1.80211412906647</v>
       </c>
       <c r="H384" t="n">
         <v>1307235</v>
@@ -11563,7 +11563,7 @@
         <v>2.35700011253357</v>
       </c>
       <c r="G386" t="n">
-        <v>1.84116363525391</v>
+        <v>1.84116351604462</v>
       </c>
       <c r="H386" t="n">
         <v>1675723</v>
@@ -11621,7 +11621,7 @@
         <v>2.27699995040894</v>
       </c>
       <c r="G388" t="n">
-        <v>1.77867162227631</v>
+        <v>1.7786717414856</v>
       </c>
       <c r="H388" t="n">
         <v>1448376</v>
@@ -11679,7 +11679,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G390" t="n">
-        <v>1.851318359375</v>
+        <v>1.85131824016571</v>
       </c>
       <c r="H390" t="n">
         <v>717045</v>
@@ -11766,7 +11766,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G393" t="n">
-        <v>1.86069202423096</v>
+        <v>1.86069214344025</v>
       </c>
       <c r="H393" t="n">
         <v>631226</v>
@@ -11795,7 +11795,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G394" t="n">
-        <v>1.81694805622101</v>
+        <v>1.81694793701172</v>
       </c>
       <c r="H394" t="n">
         <v>634308</v>
@@ -11824,7 +11824,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G395" t="n">
-        <v>1.84506916999817</v>
+        <v>1.84506940841675</v>
       </c>
       <c r="H395" t="n">
         <v>768257</v>
@@ -11853,7 +11853,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G396" t="n">
-        <v>1.81694805622101</v>
+        <v>1.81694793701172</v>
       </c>
       <c r="H396" t="n">
         <v>564016</v>
@@ -11882,7 +11882,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G397" t="n">
-        <v>1.79429471492767</v>
+        <v>1.79429459571838</v>
       </c>
       <c r="H397" t="n">
         <v>625118</v>
@@ -11940,7 +11940,7 @@
         <v>2.3289999961853</v>
       </c>
       <c r="G399" t="n">
-        <v>1.819291472435</v>
+        <v>1.81929135322571</v>
       </c>
       <c r="H399" t="n">
         <v>717310</v>
@@ -11998,7 +11998,7 @@
         <v>2.30800008773804</v>
       </c>
       <c r="G401" t="n">
-        <v>1.80288743972778</v>
+        <v>1.80288732051849</v>
       </c>
       <c r="H401" t="n">
         <v>290608</v>
@@ -12143,7 +12143,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G406" t="n">
-        <v>1.82944643497467</v>
+        <v>1.82944655418396</v>
       </c>
       <c r="H406" t="n">
         <v>327031</v>
@@ -12172,7 +12172,7 @@
         <v>2.33899998664856</v>
       </c>
       <c r="G407" t="n">
-        <v>1.82710301876068</v>
+        <v>1.82710289955139</v>
       </c>
       <c r="H407" t="n">
         <v>366090</v>
@@ -12201,7 +12201,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G408" t="n">
-        <v>1.78257751464844</v>
+        <v>1.78257763385773</v>
       </c>
       <c r="H408" t="n">
         <v>720575</v>
@@ -12317,7 +12317,7 @@
         <v>2.3289999961853</v>
       </c>
       <c r="G412" t="n">
-        <v>1.819291472435</v>
+        <v>1.81929135322571</v>
       </c>
       <c r="H412" t="n">
         <v>1092003</v>
@@ -12346,7 +12346,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G413" t="n">
-        <v>1.82397830486298</v>
+        <v>1.82397842407227</v>
       </c>
       <c r="H413" t="n">
         <v>525566</v>
@@ -12404,7 +12404,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G415" t="n">
-        <v>1.79351353645325</v>
+        <v>1.79351365566254</v>
       </c>
       <c r="H415" t="n">
         <v>274714</v>
@@ -12433,7 +12433,7 @@
         <v>2.27699995040894</v>
       </c>
       <c r="G416" t="n">
-        <v>1.77867162227631</v>
+        <v>1.7786717414856</v>
       </c>
       <c r="H416" t="n">
         <v>797388</v>
@@ -12462,7 +12462,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G417" t="n">
-        <v>1.7794531583786</v>
+        <v>1.77945303916931</v>
       </c>
       <c r="H417" t="n">
         <v>672807</v>
@@ -12491,7 +12491,7 @@
         <v>2.26099991798401</v>
       </c>
       <c r="G418" t="n">
-        <v>1.76617324352264</v>
+        <v>1.76617348194122</v>
       </c>
       <c r="H418" t="n">
         <v>422740</v>
@@ -12520,7 +12520,7 @@
         <v>2.23699998855591</v>
       </c>
       <c r="G419" t="n">
-        <v>1.74742603302002</v>
+        <v>1.74742591381073</v>
       </c>
       <c r="H419" t="n">
         <v>1089414</v>
@@ -12578,7 +12578,7 @@
         <v>2.2590000629425</v>
       </c>
       <c r="G421" t="n">
-        <v>1.76461124420166</v>
+        <v>1.76461112499237</v>
       </c>
       <c r="H421" t="n">
         <v>373347</v>
@@ -12607,7 +12607,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G422" t="n">
-        <v>1.73024070262909</v>
+        <v>1.7302405834198</v>
       </c>
       <c r="H422" t="n">
         <v>493842</v>
@@ -12665,7 +12665,7 @@
         <v>2.14100003242493</v>
       </c>
       <c r="G424" t="n">
-        <v>1.67243576049805</v>
+        <v>1.67243587970734</v>
       </c>
       <c r="H424" t="n">
         <v>2417146</v>
@@ -12723,7 +12723,7 @@
         <v>2.11700010299683</v>
       </c>
       <c r="G426" t="n">
-        <v>1.65368831157684</v>
+        <v>1.65368843078613</v>
       </c>
       <c r="H426" t="n">
         <v>542238</v>
@@ -12781,7 +12781,7 @@
         <v>2.1010000705719</v>
       </c>
       <c r="G428" t="n">
-        <v>1.64118993282318</v>
+        <v>1.64119005203247</v>
       </c>
       <c r="H428" t="n">
         <v>384515</v>
@@ -12810,7 +12810,7 @@
         <v>2.0789999961853</v>
       </c>
       <c r="G429" t="n">
-        <v>1.62400472164154</v>
+        <v>1.62400460243225</v>
       </c>
       <c r="H429" t="n">
         <v>242331</v>
@@ -12839,7 +12839,7 @@
         <v>2.05299997329712</v>
       </c>
       <c r="G430" t="n">
-        <v>1.60369491577148</v>
+        <v>1.60369479656219</v>
       </c>
       <c r="H430" t="n">
         <v>355572</v>
@@ -12926,7 +12926,7 @@
         <v>1.97699999809265</v>
       </c>
       <c r="G433" t="n">
-        <v>1.54432761669159</v>
+        <v>1.54432773590088</v>
       </c>
       <c r="H433" t="n">
         <v>335769</v>
@@ -12984,7 +12984,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G435" t="n">
-        <v>1.50136458873749</v>
+        <v>1.50136470794678</v>
       </c>
       <c r="H435" t="n">
         <v>423668</v>
@@ -13013,7 +13013,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G436" t="n">
-        <v>1.45762050151825</v>
+        <v>1.45762038230896</v>
       </c>
       <c r="H436" t="n">
         <v>630873</v>
@@ -13071,7 +13071,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G438" t="n">
-        <v>1.43887293338776</v>
+        <v>1.43887281417847</v>
       </c>
       <c r="H438" t="n">
         <v>297282</v>
@@ -13158,7 +13158,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G441" t="n">
-        <v>1.48417925834656</v>
+        <v>1.48417937755585</v>
       </c>
       <c r="H441" t="n">
         <v>558928</v>
@@ -13187,7 +13187,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G442" t="n">
-        <v>1.48417925834656</v>
+        <v>1.48417937755585</v>
       </c>
       <c r="H442" t="n">
         <v>264102</v>
@@ -13274,7 +13274,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G445" t="n">
-        <v>1.48886620998383</v>
+        <v>1.48886632919312</v>
       </c>
       <c r="H445" t="n">
         <v>825110</v>
@@ -13390,7 +13390,7 @@
         <v>1.8309999704361</v>
       </c>
       <c r="G449" t="n">
-        <v>1.43028020858765</v>
+        <v>1.43028008937836</v>
       </c>
       <c r="H449" t="n">
         <v>475160</v>
@@ -13448,7 +13448,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G451" t="n">
-        <v>1.40997040271759</v>
+        <v>1.4099702835083</v>
       </c>
       <c r="H451" t="n">
         <v>1406663</v>
@@ -13477,7 +13477,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G452" t="n">
-        <v>1.31232702732086</v>
+        <v>1.31232690811157</v>
       </c>
       <c r="H452" t="n">
         <v>1384290</v>
@@ -13506,7 +13506,7 @@
         <v>1.67340004444122</v>
       </c>
       <c r="G453" t="n">
-        <v>1.30717158317566</v>
+        <v>1.30717146396637</v>
       </c>
       <c r="H453" t="n">
         <v>770495</v>
@@ -13709,7 +13709,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G460" t="n">
-        <v>1.42715561389923</v>
+        <v>1.42715573310852</v>
       </c>
       <c r="H460" t="n">
         <v>222767</v>
@@ -13767,7 +13767,7 @@
         <v>1.80599999427795</v>
       </c>
       <c r="G462" t="n">
-        <v>1.41075146198273</v>
+        <v>1.41075158119202</v>
       </c>
       <c r="H462" t="n">
         <v>246924</v>
@@ -13796,7 +13796,7 @@
         <v>1.94939994812012</v>
       </c>
       <c r="G463" t="n">
-        <v>1.52276790142059</v>
+        <v>1.52276802062988</v>
       </c>
       <c r="H463" t="n">
         <v>916642</v>
@@ -13854,7 +13854,7 @@
         <v>1.92239999771118</v>
       </c>
       <c r="G465" t="n">
-        <v>1.50167715549469</v>
+        <v>1.50167691707611</v>
       </c>
       <c r="H465" t="n">
         <v>353065</v>
@@ -13912,7 +13912,7 @@
         <v>2.02049994468689</v>
       </c>
       <c r="G467" t="n">
-        <v>1.57830739021301</v>
+        <v>1.5783075094223</v>
       </c>
       <c r="H467" t="n">
         <v>756810</v>
@@ -14057,7 +14057,7 @@
         <v>2.00850009918213</v>
       </c>
       <c r="G472" t="n">
-        <v>1.56893384456635</v>
+        <v>1.56893396377563</v>
       </c>
       <c r="H472" t="n">
         <v>366405</v>
@@ -14115,7 +14115,7 @@
         <v>2.29450011253357</v>
       </c>
       <c r="G474" t="n">
-        <v>1.79234206676483</v>
+        <v>1.79234194755554</v>
       </c>
       <c r="H474" t="n">
         <v>1337287</v>
@@ -14144,7 +14144,7 @@
         <v>2.25950002670288</v>
       </c>
       <c r="G475" t="n">
-        <v>1.76500177383423</v>
+        <v>1.76500165462494</v>
       </c>
       <c r="H475" t="n">
         <v>775246</v>
@@ -14173,7 +14173,7 @@
         <v>2.25650000572205</v>
       </c>
       <c r="G476" t="n">
-        <v>1.76265823841095</v>
+        <v>1.76265835762024</v>
       </c>
       <c r="H476" t="n">
         <v>463148</v>
@@ -14202,7 +14202,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G477" t="n">
-        <v>1.75601840019226</v>
+        <v>1.75601851940155</v>
       </c>
       <c r="H477" t="n">
         <v>381912</v>
@@ -14231,7 +14231,7 @@
         <v>2.22699999809265</v>
       </c>
       <c r="G478" t="n">
-        <v>1.73961436748505</v>
+        <v>1.73961448669434</v>
       </c>
       <c r="H478" t="n">
         <v>1434510</v>
@@ -14289,7 +14289,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G480" t="n">
-        <v>1.74664485454559</v>
+        <v>1.7466447353363</v>
       </c>
       <c r="H480" t="n">
         <v>1270704</v>
@@ -14318,7 +14318,7 @@
         <v>2.22300004959106</v>
       </c>
       <c r="G481" t="n">
-        <v>1.73648989200592</v>
+        <v>1.73649001121521</v>
       </c>
       <c r="H481" t="n">
         <v>624711</v>
@@ -14376,7 +14376,7 @@
         <v>2.29749989509583</v>
       </c>
       <c r="G483" t="n">
-        <v>1.79468524456024</v>
+        <v>1.79468512535095</v>
       </c>
       <c r="H483" t="n">
         <v>1095196</v>
@@ -14434,7 +14434,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G485" t="n">
-        <v>1.86850380897522</v>
+        <v>1.86850368976593</v>
       </c>
       <c r="H485" t="n">
         <v>792725</v>
@@ -14492,7 +14492,7 @@
         <v>2.25</v>
       </c>
       <c r="G487" t="n">
-        <v>1.75758099555969</v>
+        <v>1.7575808763504</v>
       </c>
       <c r="H487" t="n">
         <v>1370262</v>
@@ -14666,7 +14666,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G493" t="n">
-        <v>1.86225473880768</v>
+        <v>1.86225438117981</v>
       </c>
       <c r="H493" t="n">
         <v>271589</v>
@@ -14724,7 +14724,7 @@
         <v>2.38100004196167</v>
       </c>
       <c r="G495" t="n">
-        <v>1.8599112033844</v>
+        <v>1.85991108417511</v>
       </c>
       <c r="H495" t="n">
         <v>360476</v>
@@ -14811,7 +14811,7 @@
         <v>2.38899993896484</v>
       </c>
       <c r="G498" t="n">
-        <v>1.86616015434265</v>
+        <v>1.86616027355194</v>
       </c>
       <c r="H498" t="n">
         <v>465046</v>
@@ -14840,7 +14840,7 @@
         <v>2.3289999961853</v>
       </c>
       <c r="G499" t="n">
-        <v>1.819291472435</v>
+        <v>1.81929135322571</v>
       </c>
       <c r="H499" t="n">
         <v>426104</v>
@@ -14869,7 +14869,7 @@
         <v>2.35899996757507</v>
       </c>
       <c r="G500" t="n">
-        <v>1.84272575378418</v>
+        <v>1.84272587299347</v>
       </c>
       <c r="H500" t="n">
         <v>444448</v>
@@ -14898,7 +14898,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G501" t="n">
-        <v>1.86069202423096</v>
+        <v>1.86069214344025</v>
       </c>
       <c r="H501" t="n">
         <v>431708</v>
@@ -14956,7 +14956,7 @@
         <v>2.4210000038147</v>
       </c>
       <c r="G503" t="n">
-        <v>1.89115715026855</v>
+        <v>1.89115703105927</v>
       </c>
       <c r="H503" t="n">
         <v>400870</v>
@@ -15014,7 +15014,7 @@
         <v>2.40199995040894</v>
       </c>
       <c r="G505" t="n">
-        <v>1.87631523609161</v>
+        <v>1.87631499767303</v>
       </c>
       <c r="H505" t="n">
         <v>719122</v>
@@ -15072,7 +15072,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G507" t="n">
-        <v>1.851318359375</v>
+        <v>1.85131824016571</v>
       </c>
       <c r="H507" t="n">
         <v>420850</v>
@@ -15130,7 +15130,7 @@
         <v>2.37949991226196</v>
       </c>
       <c r="G509" t="n">
-        <v>1.85873925685883</v>
+        <v>1.85873937606812</v>
       </c>
       <c r="H509" t="n">
         <v>517495</v>
@@ -15159,7 +15159,7 @@
         <v>2.33949995040894</v>
       </c>
       <c r="G510" t="n">
-        <v>1.82749342918396</v>
+        <v>1.82749330997467</v>
       </c>
       <c r="H510" t="n">
         <v>387078</v>
@@ -15188,7 +15188,7 @@
         <v>2.30800008773804</v>
       </c>
       <c r="G511" t="n">
-        <v>1.80288743972778</v>
+        <v>1.80288732051849</v>
       </c>
       <c r="H511" t="n">
         <v>471638</v>
@@ -15304,7 +15304,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G515" t="n">
-        <v>1.88256454467773</v>
+        <v>1.88256442546844</v>
       </c>
       <c r="H515" t="n">
         <v>456876</v>
@@ -15391,7 +15391,7 @@
         <v>2.35949993133545</v>
       </c>
       <c r="G518" t="n">
-        <v>1.84311640262604</v>
+        <v>1.84311628341675</v>
       </c>
       <c r="H518" t="n">
         <v>314732</v>
@@ -15420,7 +15420,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G519" t="n">
-        <v>1.84506916999817</v>
+        <v>1.84506940841675</v>
       </c>
       <c r="H519" t="n">
         <v>346938</v>
@@ -15536,7 +15536,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G523" t="n">
-        <v>1.74352014064789</v>
+        <v>1.74352025985718</v>
       </c>
       <c r="H523" t="n">
         <v>587511</v>
@@ -15594,7 +15594,7 @@
         <v>2.18650007247925</v>
       </c>
       <c r="G525" t="n">
-        <v>1.7079781293869</v>
+        <v>1.70797789096832</v>
       </c>
       <c r="H525" t="n">
         <v>339135</v>
@@ -15623,7 +15623,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G526" t="n">
-        <v>1.6310350894928</v>
+        <v>1.63103497028351</v>
       </c>
       <c r="H526" t="n">
         <v>2425155</v>
@@ -15681,7 +15681,7 @@
         <v>2.06399989128113</v>
       </c>
       <c r="G528" t="n">
-        <v>1.61228728294373</v>
+        <v>1.61228740215302</v>
       </c>
       <c r="H528" t="n">
         <v>854481</v>
@@ -15710,7 +15710,7 @@
         <v>2.1324999332428</v>
       </c>
       <c r="G529" t="n">
-        <v>1.66579592227936</v>
+        <v>1.66579604148865</v>
       </c>
       <c r="H529" t="n">
         <v>1224677</v>
@@ -15739,7 +15739,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G530" t="n">
-        <v>1.65603160858154</v>
+        <v>1.65603172779083</v>
       </c>
       <c r="H530" t="n">
         <v>1091564</v>
@@ -15797,7 +15797,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G532" t="n">
-        <v>1.62478566169739</v>
+        <v>1.62478578090668</v>
       </c>
       <c r="H532" t="n">
         <v>570995</v>
@@ -15826,7 +15826,7 @@
         <v>2.07750010490417</v>
       </c>
       <c r="G533" t="n">
-        <v>1.62283313274384</v>
+        <v>1.62283301353455</v>
       </c>
       <c r="H533" t="n">
         <v>369112</v>
@@ -15971,7 +15971,7 @@
         <v>2.11150002479553</v>
       </c>
       <c r="G538" t="n">
-        <v>1.64939188957214</v>
+        <v>1.64939200878143</v>
       </c>
       <c r="H538" t="n">
         <v>386864</v>
@@ -16000,7 +16000,7 @@
         <v>2.1010000705719</v>
       </c>
       <c r="G539" t="n">
-        <v>1.64118993282318</v>
+        <v>1.64119005203247</v>
       </c>
       <c r="H539" t="n">
         <v>348613</v>
@@ -16203,7 +16203,7 @@
         <v>2.14299988746643</v>
       </c>
       <c r="G546" t="n">
-        <v>1.67399787902832</v>
+        <v>1.67399799823761</v>
       </c>
       <c r="H546" t="n">
         <v>1450618</v>
@@ -16261,7 +16261,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G548" t="n">
-        <v>1.66852998733521</v>
+        <v>1.66853010654449</v>
       </c>
       <c r="H548" t="n">
         <v>589194</v>
@@ -16290,7 +16290,7 @@
         <v>2.12949991226196</v>
       </c>
       <c r="G549" t="n">
-        <v>1.66345262527466</v>
+        <v>1.66345250606537</v>
       </c>
       <c r="H549" t="n">
         <v>838112</v>
@@ -16406,7 +16406,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G553" t="n">
-        <v>1.74976921081543</v>
+        <v>1.74976944923401</v>
       </c>
       <c r="H553" t="n">
         <v>1944729</v>
@@ -16464,7 +16464,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G555" t="n">
-        <v>1.74352014064789</v>
+        <v>1.74352025985718</v>
       </c>
       <c r="H555" t="n">
         <v>532106</v>
@@ -16522,7 +16522,7 @@
         <v>2.30550003051758</v>
       </c>
       <c r="G557" t="n">
-        <v>1.80093443393707</v>
+        <v>1.80093455314636</v>
       </c>
       <c r="H557" t="n">
         <v>567946</v>
@@ -16580,7 +16580,7 @@
         <v>2.42149996757507</v>
       </c>
       <c r="G559" t="n">
-        <v>1.89154732227325</v>
+        <v>1.89154744148254</v>
       </c>
       <c r="H559" t="n">
         <v>1056336</v>
@@ -16609,7 +16609,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G560" t="n">
-        <v>1.8786586523056</v>
+        <v>1.87865853309631</v>
       </c>
       <c r="H560" t="n">
         <v>518625</v>
@@ -16638,7 +16638,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G561" t="n">
-        <v>1.92630887031555</v>
+        <v>1.92630875110626</v>
       </c>
       <c r="H561" t="n">
         <v>1119220</v>
@@ -16667,7 +16667,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G562" t="n">
-        <v>1.95130515098572</v>
+        <v>1.95130527019501</v>
       </c>
       <c r="H562" t="n">
         <v>455972</v>
@@ -16696,7 +16696,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G563" t="n">
-        <v>1.96536600589752</v>
+        <v>1.96536588668823</v>
       </c>
       <c r="H563" t="n">
         <v>1160065</v>
@@ -16725,7 +16725,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G564" t="n">
-        <v>1.9216216802597</v>
+        <v>1.92162179946899</v>
       </c>
       <c r="H564" t="n">
         <v>582073</v>
@@ -16783,7 +16783,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G566" t="n">
-        <v>1.98411333560944</v>
+        <v>1.98411345481873</v>
       </c>
       <c r="H566" t="n">
         <v>1037237</v>
@@ -16841,7 +16841,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G568" t="n">
-        <v>1.99661159515381</v>
+        <v>1.99661195278168</v>
       </c>
       <c r="H568" t="n">
         <v>1003381</v>
@@ -16870,7 +16870,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G569" t="n">
-        <v>1.92005944252014</v>
+        <v>1.92005932331085</v>
       </c>
       <c r="H569" t="n">
         <v>1136036</v>
@@ -16957,7 +16957,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G572" t="n">
-        <v>1.9216216802597</v>
+        <v>1.92162179946899</v>
       </c>
       <c r="H572" t="n">
         <v>224932</v>
@@ -16986,7 +16986,7 @@
         <v>2.56800007820129</v>
       </c>
       <c r="G573" t="n">
-        <v>2.00598573684692</v>
+        <v>2.00598549842834</v>
       </c>
       <c r="H573" t="n">
         <v>4035540</v>
@@ -17015,7 +17015,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G574" t="n">
-        <v>2.02785778045654</v>
+        <v>2.02785754203796</v>
       </c>
       <c r="H574" t="n">
         <v>1096883</v>
@@ -17073,7 +17073,7 @@
         <v>2.70600008964539</v>
       </c>
       <c r="G576" t="n">
-        <v>2.11378383636475</v>
+        <v>2.11378407478333</v>
       </c>
       <c r="H576" t="n">
         <v>1342948</v>
@@ -17102,7 +17102,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G577" t="n">
-        <v>2.12784457206726</v>
+        <v>2.12784433364868</v>
       </c>
       <c r="H577" t="n">
         <v>1427518</v>
@@ -17189,7 +17189,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G580" t="n">
-        <v>2.21064615249634</v>
+        <v>2.21064591407776</v>
       </c>
       <c r="H580" t="n">
         <v>2199411</v>
@@ -17247,7 +17247,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>2.17940020561218</v>
+        <v>2.1793999671936</v>
       </c>
       <c r="H582" t="n">
         <v>543959</v>
@@ -17363,7 +17363,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G586" t="n">
-        <v>2.2575147151947</v>
+        <v>2.25751519203186</v>
       </c>
       <c r="H586" t="n">
         <v>1032388</v>
@@ -17537,7 +17537,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G592" t="n">
-        <v>2.43874096870422</v>
+        <v>2.4387412071228</v>
       </c>
       <c r="H592" t="n">
         <v>965545</v>
@@ -17653,7 +17653,7 @@
         <v>3.00399994850159</v>
       </c>
       <c r="G596" t="n">
-        <v>2.34656572341919</v>
+        <v>2.34656548500061</v>
       </c>
       <c r="H596" t="n">
         <v>921949</v>
@@ -17740,7 +17740,7 @@
         <v>3.10800004005432</v>
       </c>
       <c r="G599" t="n">
-        <v>2.42780518531799</v>
+        <v>2.42780494689941</v>
       </c>
       <c r="H599" t="n">
         <v>1169838</v>
@@ -17827,7 +17827,7 @@
         <v>3.06800007820129</v>
       </c>
       <c r="G602" t="n">
-        <v>2.39655900001526</v>
+        <v>2.39655923843384</v>
       </c>
       <c r="H602" t="n">
         <v>1252196</v>
@@ -17943,7 +17943,7 @@
         <v>3.30399990081787</v>
       </c>
       <c r="G606" t="n">
-        <v>2.58090972900391</v>
+        <v>2.58090949058533</v>
       </c>
       <c r="H606" t="n">
         <v>2221014</v>
@@ -17972,7 +17972,7 @@
         <v>3.26799988746643</v>
       </c>
       <c r="G607" t="n">
-        <v>2.55278849601746</v>
+        <v>2.55278825759888</v>
       </c>
       <c r="H607" t="n">
         <v>1444083</v>
@@ -18030,7 +18030,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G609" t="n">
-        <v>2.54810166358948</v>
+        <v>2.54810190200806</v>
       </c>
       <c r="H609" t="n">
         <v>548275</v>
@@ -18059,7 +18059,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G610" t="n">
-        <v>2.46373772621155</v>
+        <v>2.46373796463013</v>
       </c>
       <c r="H610" t="n">
         <v>1532299</v>
@@ -18117,7 +18117,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G612" t="n">
-        <v>2.41374444961548</v>
+        <v>2.4137442111969</v>
       </c>
       <c r="H612" t="n">
         <v>1036670</v>
@@ -18146,7 +18146,7 @@
         <v>3.0220000743866</v>
       </c>
       <c r="G613" t="n">
-        <v>2.36062622070312</v>
+        <v>2.3606264591217</v>
       </c>
       <c r="H613" t="n">
         <v>1605438</v>
@@ -18233,7 +18233,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G616" t="n">
-        <v>2.39343428611755</v>
+        <v>2.39343452453613</v>
       </c>
       <c r="H616" t="n">
         <v>397137</v>
@@ -18378,7 +18378,7 @@
         <v>3.18799996376038</v>
       </c>
       <c r="G621" t="n">
-        <v>2.49029660224915</v>
+        <v>2.49029684066772</v>
       </c>
       <c r="H621" t="n">
         <v>691299</v>
@@ -18407,7 +18407,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G622" t="n">
-        <v>2.52310490608215</v>
+        <v>2.52310514450073</v>
       </c>
       <c r="H622" t="n">
         <v>1734037</v>
@@ -18552,7 +18552,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G627" t="n">
-        <v>2.52310490608215</v>
+        <v>2.52310514450073</v>
       </c>
       <c r="H627" t="n">
         <v>1052134</v>
@@ -18726,7 +18726,7 @@
         <v>3.42199993133545</v>
       </c>
       <c r="G633" t="n">
-        <v>2.67308521270752</v>
+        <v>2.67308497428894</v>
       </c>
       <c r="H633" t="n">
         <v>1448985</v>
@@ -18755,7 +18755,7 @@
         <v>3.45199990272522</v>
       </c>
       <c r="G634" t="n">
-        <v>2.69651937484741</v>
+        <v>2.69651961326599</v>
       </c>
       <c r="H634" t="n">
         <v>1023448</v>
@@ -18784,7 +18784,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G635" t="n">
-        <v>2.71058011054993</v>
+        <v>2.71058034896851</v>
       </c>
       <c r="H635" t="n">
         <v>867265</v>
@@ -18813,7 +18813,7 @@
         <v>3.53600001335144</v>
       </c>
       <c r="G636" t="n">
-        <v>2.76213574409485</v>
+        <v>2.76213598251343</v>
       </c>
       <c r="H636" t="n">
         <v>946938</v>
@@ -35436,6 +35436,35 @@
         <v>1359227</v>
       </c>
       <c r="I1209" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1210" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1210" t="n">
+        <v>2.09800004959106</v>
+      </c>
+      <c r="D1210" t="n">
+        <v>2.10999989509583</v>
+      </c>
+      <c r="E1210" t="n">
+        <v>2.07599997520447</v>
+      </c>
+      <c r="F1210" t="n">
+        <v>2.08400011062622</v>
+      </c>
+      <c r="G1210" t="n">
+        <v>2.08400011062622</v>
+      </c>
+      <c r="H1210" t="n">
+        <v>1474425</v>
+      </c>
+      <c r="I1210" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MFEA.MI.xlsx
+++ b/data/MFEA.MI.xlsx
@@ -456,7 +456,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G3" t="n">
-        <v>2.25028038024902</v>
+        <v>2.25027990341187</v>
       </c>
       <c r="H3" t="n">
         <v>367297</v>
@@ -485,7 +485,7 @@
         <v>3.71250009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>2.28881216049194</v>
+        <v>2.28881239891052</v>
       </c>
       <c r="H4" t="n">
         <v>267411</v>
@@ -514,7 +514,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G5" t="n">
-        <v>2.30884885787964</v>
+        <v>2.30884909629822</v>
       </c>
       <c r="H5" t="n">
         <v>278466</v>
@@ -601,7 +601,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G8" t="n">
-        <v>2.27494096755981</v>
+        <v>2.27494072914124</v>
       </c>
       <c r="H8" t="n">
         <v>174924</v>
@@ -630,7 +630,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G9" t="n">
-        <v>2.34892249107361</v>
+        <v>2.34892225265503</v>
       </c>
       <c r="H9" t="n">
         <v>257244</v>
@@ -688,7 +688,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G11" t="n">
-        <v>2.31501412391663</v>
+        <v>2.31501436233521</v>
       </c>
       <c r="H11" t="n">
         <v>127118</v>
@@ -717,7 +717,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G12" t="n">
-        <v>2.29035329818726</v>
+        <v>2.29035353660583</v>
       </c>
       <c r="H12" t="n">
         <v>185082</v>
@@ -775,7 +775,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G14" t="n">
-        <v>2.23178434371948</v>
+        <v>2.23178458213806</v>
       </c>
       <c r="H14" t="n">
         <v>244637</v>
@@ -804,7 +804,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G15" t="n">
-        <v>2.32734441757202</v>
+        <v>2.3273446559906</v>
       </c>
       <c r="H15" t="n">
         <v>370744</v>
@@ -833,7 +833,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G16" t="n">
-        <v>2.64484977722168</v>
+        <v>2.6448495388031</v>
       </c>
       <c r="H16" t="n">
         <v>857484</v>
@@ -862,7 +862,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G17" t="n">
-        <v>2.69417095184326</v>
+        <v>2.6941704750061</v>
       </c>
       <c r="H17" t="n">
         <v>431766</v>
@@ -949,7 +949,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G20" t="n">
-        <v>2.61710619926453</v>
+        <v>2.61710643768311</v>
       </c>
       <c r="H20" t="n">
         <v>162925</v>
@@ -1094,7 +1094,7 @@
         <v>3.99499988555908</v>
       </c>
       <c r="G25" t="n">
-        <v>2.46297764778137</v>
+        <v>2.46297740936279</v>
       </c>
       <c r="H25" t="n">
         <v>109853</v>
@@ -1123,7 +1123,7 @@
         <v>3.94250011444092</v>
       </c>
       <c r="G26" t="n">
-        <v>2.43061089515686</v>
+        <v>2.43061065673828</v>
       </c>
       <c r="H26" t="n">
         <v>264886</v>
@@ -1181,7 +1181,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G28" t="n">
-        <v>2.47222542762756</v>
+        <v>2.47222566604614</v>
       </c>
       <c r="H28" t="n">
         <v>194221</v>
@@ -1239,7 +1239,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G30" t="n">
-        <v>2.41365623474121</v>
+        <v>2.41365671157837</v>
       </c>
       <c r="H30" t="n">
         <v>227564</v>
@@ -1326,7 +1326,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G33" t="n">
-        <v>2.21945405006409</v>
+        <v>2.21945428848267</v>
       </c>
       <c r="H33" t="n">
         <v>419876</v>
@@ -1442,7 +1442,7 @@
         <v>4.14249992370605</v>
       </c>
       <c r="G37" t="n">
-        <v>2.55391383171082</v>
+        <v>2.55391359329224</v>
       </c>
       <c r="H37" t="n">
         <v>310291</v>
@@ -1558,7 +1558,7 @@
         <v>3.5</v>
       </c>
       <c r="G41" t="n">
-        <v>2.15780282020569</v>
+        <v>2.15780258178711</v>
       </c>
       <c r="H41" t="n">
         <v>1105386</v>
@@ -1616,7 +1616,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G43" t="n">
-        <v>2.03449988365173</v>
+        <v>2.03449964523315</v>
       </c>
       <c r="H43" t="n">
         <v>404535</v>
@@ -1761,7 +1761,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G48" t="n">
-        <v>2.03141713142395</v>
+        <v>2.03141689300537</v>
       </c>
       <c r="H48" t="n">
         <v>198901</v>
@@ -1877,7 +1877,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G52" t="n">
-        <v>1.99442625045776</v>
+        <v>1.99442613124847</v>
       </c>
       <c r="H52" t="n">
         <v>186459</v>
@@ -1906,7 +1906,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G53" t="n">
-        <v>1.97593057155609</v>
+        <v>1.97593092918396</v>
       </c>
       <c r="H53" t="n">
         <v>157204</v>
@@ -1935,7 +1935,7 @@
         <v>3.1175000667572</v>
       </c>
       <c r="G54" t="n">
-        <v>1.9219856262207</v>
+        <v>1.92198586463928</v>
       </c>
       <c r="H54" t="n">
         <v>195501</v>
@@ -1964,7 +1964,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G55" t="n">
-        <v>1.82796704769135</v>
+        <v>1.82796692848206</v>
       </c>
       <c r="H55" t="n">
         <v>452826</v>
@@ -2022,7 +2022,7 @@
         <v>3</v>
       </c>
       <c r="G57" t="n">
-        <v>1.84954524040222</v>
+        <v>1.84954500198364</v>
       </c>
       <c r="H57" t="n">
         <v>234992</v>
@@ -2051,7 +2051,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G58" t="n">
-        <v>1.82488465309143</v>
+        <v>1.82488453388214</v>
       </c>
       <c r="H58" t="n">
         <v>168347</v>
@@ -2080,7 +2080,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G59" t="n">
-        <v>1.79405915737152</v>
+        <v>1.79405903816223</v>
       </c>
       <c r="H59" t="n">
         <v>174796</v>
@@ -2138,7 +2138,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G61" t="n">
-        <v>1.80638921260834</v>
+        <v>1.80638909339905</v>
       </c>
       <c r="H61" t="n">
         <v>175025</v>
@@ -2167,7 +2167,7 @@
         <v>2.96250009536743</v>
       </c>
       <c r="G62" t="n">
-        <v>1.82642579078674</v>
+        <v>1.82642602920532</v>
       </c>
       <c r="H62" t="n">
         <v>167649</v>
@@ -2196,7 +2196,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G63" t="n">
-        <v>1.81255447864532</v>
+        <v>1.81255435943604</v>
       </c>
       <c r="H63" t="n">
         <v>134826</v>
@@ -2254,7 +2254,7 @@
         <v>2.89249992370605</v>
       </c>
       <c r="G65" t="n">
-        <v>1.78326976299286</v>
+        <v>1.78326988220215</v>
       </c>
       <c r="H65" t="n">
         <v>336035</v>
@@ -2283,7 +2283,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G66" t="n">
-        <v>1.71391189098358</v>
+        <v>1.71391177177429</v>
       </c>
       <c r="H66" t="n">
         <v>344735</v>
@@ -2312,7 +2312,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G67" t="n">
-        <v>1.69233381748199</v>
+        <v>1.69233357906342</v>
       </c>
       <c r="H67" t="n">
         <v>293953</v>
@@ -2370,7 +2370,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G69" t="n">
-        <v>1.6522604227066</v>
+        <v>1.65226054191589</v>
       </c>
       <c r="H69" t="n">
         <v>531234</v>
@@ -2399,7 +2399,7 @@
         <v>2.92750000953674</v>
       </c>
       <c r="G70" t="n">
-        <v>1.80484795570374</v>
+        <v>1.80484759807587</v>
       </c>
       <c r="H70" t="n">
         <v>1271038</v>
@@ -2457,7 +2457,7 @@
         <v>2.88750004768372</v>
       </c>
       <c r="G72" t="n">
-        <v>1.78018724918365</v>
+        <v>1.78018736839294</v>
       </c>
       <c r="H72" t="n">
         <v>202748</v>
@@ -2486,7 +2486,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G73" t="n">
-        <v>1.74165499210358</v>
+        <v>1.74165523052216</v>
       </c>
       <c r="H73" t="n">
         <v>228203</v>
@@ -2515,7 +2515,7 @@
         <v>2.75</v>
       </c>
       <c r="G74" t="n">
-        <v>1.69541656970978</v>
+        <v>1.69541621208191</v>
       </c>
       <c r="H74" t="n">
         <v>168732</v>
@@ -2573,7 +2573,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G76" t="n">
-        <v>1.63376498222351</v>
+        <v>1.63376486301422</v>
       </c>
       <c r="H76" t="n">
         <v>246997</v>
@@ -2631,7 +2631,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G78" t="n">
-        <v>1.74782025814056</v>
+        <v>1.74782013893127</v>
       </c>
       <c r="H78" t="n">
         <v>522442</v>
@@ -2660,7 +2660,7 @@
         <v>2.66750001907349</v>
       </c>
       <c r="G79" t="n">
-        <v>1.6445540189743</v>
+        <v>1.64455389976501</v>
       </c>
       <c r="H79" t="n">
         <v>468659</v>
@@ -2689,7 +2689,7 @@
         <v>2.68249988555908</v>
       </c>
       <c r="G80" t="n">
-        <v>1.65380144119263</v>
+        <v>1.65380156040192</v>
       </c>
       <c r="H80" t="n">
         <v>289746</v>
@@ -2747,7 +2747,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G82" t="n">
-        <v>1.63068222999573</v>
+        <v>1.63068234920502</v>
       </c>
       <c r="H82" t="n">
         <v>172630</v>
@@ -2776,7 +2776,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G83" t="n">
-        <v>1.60910439491272</v>
+        <v>1.60910427570343</v>
       </c>
       <c r="H83" t="n">
         <v>216063</v>
@@ -2805,7 +2805,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G84" t="n">
-        <v>1.56594824790955</v>
+        <v>1.56594836711884</v>
       </c>
       <c r="H84" t="n">
         <v>392657</v>
@@ -2863,7 +2863,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G86" t="n">
-        <v>1.58752620220184</v>
+        <v>1.58752632141113</v>
       </c>
       <c r="H86" t="n">
         <v>329995</v>
@@ -2892,7 +2892,7 @@
         <v>2.50250005722046</v>
       </c>
       <c r="G87" t="n">
-        <v>1.54282891750336</v>
+        <v>1.54282903671265</v>
       </c>
       <c r="H87" t="n">
         <v>224920</v>
@@ -2921,7 +2921,7 @@
         <v>2.64750003814697</v>
       </c>
       <c r="G88" t="n">
-        <v>1.6322238445282</v>
+        <v>1.63222372531891</v>
       </c>
       <c r="H88" t="n">
         <v>842562</v>
@@ -3037,7 +3037,7 @@
         <v>2.66750001907349</v>
       </c>
       <c r="G92" t="n">
-        <v>1.6445540189743</v>
+        <v>1.64455389976501</v>
       </c>
       <c r="H92" t="n">
         <v>384701</v>
@@ -3066,7 +3066,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G93" t="n">
-        <v>1.63068222999573</v>
+        <v>1.63068234920502</v>
       </c>
       <c r="H93" t="n">
         <v>293851</v>
@@ -3095,7 +3095,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G94" t="n">
-        <v>1.6399302482605</v>
+        <v>1.63993012905121</v>
       </c>
       <c r="H94" t="n">
         <v>124415</v>
@@ -3153,7 +3153,7 @@
         <v>2.6324999332428</v>
       </c>
       <c r="G96" t="n">
-        <v>1.62297582626343</v>
+        <v>1.62297594547272</v>
       </c>
       <c r="H96" t="n">
         <v>316690</v>
@@ -3182,7 +3182,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G97" t="n">
-        <v>1.57827854156494</v>
+        <v>1.57827842235565</v>
       </c>
       <c r="H97" t="n">
         <v>975446</v>
@@ -3240,7 +3240,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>1.60602176189423</v>
+        <v>1.60602164268494</v>
       </c>
       <c r="H99" t="n">
         <v>524697</v>
@@ -3269,7 +3269,7 @@
         <v>2.45300006866455</v>
       </c>
       <c r="G100" t="n">
-        <v>1.51231157779694</v>
+        <v>1.51231145858765</v>
       </c>
       <c r="H100" t="n">
         <v>588672</v>
@@ -3327,7 +3327,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G102" t="n">
-        <v>1.47717010974884</v>
+        <v>1.47716999053955</v>
       </c>
       <c r="H102" t="n">
         <v>189949</v>
@@ -3356,7 +3356,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G103" t="n">
-        <v>1.45867466926575</v>
+        <v>1.45867455005646</v>
       </c>
       <c r="H103" t="n">
         <v>277983</v>
@@ -3530,7 +3530,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G109" t="n">
-        <v>1.31934225559235</v>
+        <v>1.31934237480164</v>
       </c>
       <c r="H109" t="n">
         <v>149597</v>
@@ -3559,7 +3559,7 @@
         <v>2.14199995994568</v>
       </c>
       <c r="G110" t="n">
-        <v>1.32057511806488</v>
+        <v>1.32057535648346</v>
       </c>
       <c r="H110" t="n">
         <v>256397</v>
@@ -3588,7 +3588,7 @@
         <v>2.18899989128113</v>
       </c>
       <c r="G111" t="n">
-        <v>1.34955155849457</v>
+        <v>1.34955143928528</v>
       </c>
       <c r="H111" t="n">
         <v>386160</v>
@@ -3617,7 +3617,7 @@
         <v>2.24900007247925</v>
       </c>
       <c r="G112" t="n">
-        <v>1.38654232025146</v>
+        <v>1.38654243946075</v>
       </c>
       <c r="H112" t="n">
         <v>617377</v>
@@ -3762,7 +3762,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G117" t="n">
-        <v>1.4149022102356</v>
+        <v>1.41490209102631</v>
       </c>
       <c r="H117" t="n">
         <v>647297</v>
@@ -3791,7 +3791,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G118" t="n">
-        <v>1.34708547592163</v>
+        <v>1.34708523750305</v>
       </c>
       <c r="H118" t="n">
         <v>844960</v>
@@ -3820,7 +3820,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G119" t="n">
-        <v>1.38099384307861</v>
+        <v>1.38099372386932</v>
       </c>
       <c r="H119" t="n">
         <v>296846</v>
@@ -3849,7 +3849,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G120" t="n">
-        <v>1.37236261367798</v>
+        <v>1.37236249446869</v>
       </c>
       <c r="H120" t="n">
         <v>898674</v>
@@ -3878,7 +3878,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G121" t="n">
-        <v>1.4056544303894</v>
+        <v>1.40565431118011</v>
       </c>
       <c r="H121" t="n">
         <v>1163100</v>
@@ -3907,7 +3907,7 @@
         <v>2.22099995613098</v>
       </c>
       <c r="G122" t="n">
-        <v>1.3692798614502</v>
+        <v>1.36927998065948</v>
       </c>
       <c r="H122" t="n">
         <v>2110801</v>
@@ -3936,7 +3936,7 @@
         <v>2.18300008773804</v>
       </c>
       <c r="G123" t="n">
-        <v>1.34585249423981</v>
+        <v>1.34585225582123</v>
       </c>
       <c r="H123" t="n">
         <v>1057822</v>
@@ -4052,7 +4052,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G127" t="n">
-        <v>1.33043932914734</v>
+        <v>1.33043956756592</v>
       </c>
       <c r="H127" t="n">
         <v>576146</v>
@@ -4081,7 +4081,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G128" t="n">
-        <v>1.35325062274933</v>
+        <v>1.35325050354004</v>
       </c>
       <c r="H128" t="n">
         <v>1234804</v>
@@ -4226,7 +4226,7 @@
         <v>2.02699995040894</v>
       </c>
       <c r="G133" t="n">
-        <v>1.24967610836029</v>
+        <v>1.249675989151</v>
       </c>
       <c r="H133" t="n">
         <v>1799201</v>
@@ -4255,7 +4255,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>1.28543388843536</v>
+        <v>1.28543400764465</v>
       </c>
       <c r="H134" t="n">
         <v>1315577</v>
@@ -4371,7 +4371,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G138" t="n">
-        <v>1.32304131984711</v>
+        <v>1.32304120063782</v>
       </c>
       <c r="H138" t="n">
         <v>662539</v>
@@ -4400,7 +4400,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G139" t="n">
-        <v>1.27002096176147</v>
+        <v>1.27002108097076</v>
       </c>
       <c r="H139" t="n">
         <v>1000781</v>
@@ -4545,7 +4545,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G144" t="n">
-        <v>1.35386729240417</v>
+        <v>1.35386717319489</v>
       </c>
       <c r="H144" t="n">
         <v>698399</v>
@@ -4574,7 +4574,7 @@
         <v>2.30900001525879</v>
       </c>
       <c r="G145" t="n">
-        <v>1.42353332042694</v>
+        <v>1.42353308200836</v>
       </c>
       <c r="H145" t="n">
         <v>1061376</v>
@@ -4632,7 +4632,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G147" t="n">
-        <v>1.35325062274933</v>
+        <v>1.35325050354004</v>
       </c>
       <c r="H147" t="n">
         <v>729575</v>
@@ -4835,7 +4835,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G154" t="n">
-        <v>1.23611271381378</v>
+        <v>1.23611283302307</v>
       </c>
       <c r="H154" t="n">
         <v>622012</v>
@@ -4922,7 +4922,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G157" t="n">
-        <v>1.30392944812775</v>
+        <v>1.30392932891846</v>
       </c>
       <c r="H157" t="n">
         <v>621284</v>
@@ -4980,7 +4980,7 @@
         <v>2.10199999809265</v>
       </c>
       <c r="G159" t="n">
-        <v>1.29591476917267</v>
+        <v>1.29591464996338</v>
       </c>
       <c r="H159" t="n">
         <v>782752</v>
@@ -5183,7 +5183,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G166" t="n">
-        <v>1.28543388843536</v>
+        <v>1.28543400764465</v>
       </c>
       <c r="H166" t="n">
         <v>925875</v>
@@ -5212,7 +5212,7 @@
         <v>2.06900000572205</v>
       </c>
       <c r="G167" t="n">
-        <v>1.27556955814362</v>
+        <v>1.27556967735291</v>
       </c>
       <c r="H167" t="n">
         <v>928824</v>
@@ -5241,7 +5241,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G168" t="n">
-        <v>1.24782633781433</v>
+        <v>1.24782645702362</v>
       </c>
       <c r="H168" t="n">
         <v>1017897</v>
@@ -5270,7 +5270,7 @@
         <v>1.99899995326996</v>
       </c>
       <c r="G169" t="n">
-        <v>1.23241364955902</v>
+        <v>1.23241353034973</v>
       </c>
       <c r="H169" t="n">
         <v>2003498</v>
@@ -5299,7 +5299,7 @@
         <v>1.84899997711182</v>
       </c>
       <c r="G170" t="n">
-        <v>1.30287742614746</v>
+        <v>1.30287754535675</v>
       </c>
       <c r="H170" t="n">
         <v>1744533</v>
@@ -5328,7 +5328,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G171" t="n">
-        <v>1.20140957832336</v>
+        <v>1.20140945911407</v>
       </c>
       <c r="H171" t="n">
         <v>1719560</v>
@@ -5386,7 +5386,7 @@
         <v>1.65199995040894</v>
       </c>
       <c r="G173" t="n">
-        <v>1.16406345367432</v>
+        <v>1.16406357288361</v>
       </c>
       <c r="H173" t="n">
         <v>1205156</v>
@@ -5531,7 +5531,7 @@
         <v>1.43900001049042</v>
       </c>
       <c r="G178" t="n">
-        <v>1.01397550106049</v>
+        <v>1.01397562026978</v>
       </c>
       <c r="H178" t="n">
         <v>1366037</v>
@@ -5560,7 +5560,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G179" t="n">
-        <v>1.06400489807129</v>
+        <v>1.064004778862</v>
       </c>
       <c r="H179" t="n">
         <v>1582704</v>
@@ -5647,7 +5647,7 @@
         <v>1.54700005054474</v>
       </c>
       <c r="G182" t="n">
-        <v>1.09007656574249</v>
+        <v>1.09007668495178</v>
       </c>
       <c r="H182" t="n">
         <v>808303</v>
@@ -5676,7 +5676,7 @@
         <v>1.557000041008</v>
       </c>
       <c r="G183" t="n">
-        <v>1.09712290763855</v>
+        <v>1.09712302684784</v>
       </c>
       <c r="H183" t="n">
         <v>1335356</v>
@@ -5705,7 +5705,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G184" t="n">
-        <v>1.08796274662018</v>
+        <v>1.08796262741089</v>
       </c>
       <c r="H184" t="n">
         <v>1603167</v>
@@ -5821,7 +5821,7 @@
         <v>1.54200005531311</v>
       </c>
       <c r="G188" t="n">
-        <v>1.08655345439911</v>
+        <v>1.08655333518982</v>
       </c>
       <c r="H188" t="n">
         <v>1596742</v>
@@ -5908,7 +5908,7 @@
         <v>1.63699996471405</v>
       </c>
       <c r="G191" t="n">
-        <v>1.15349400043488</v>
+        <v>1.15349411964417</v>
       </c>
       <c r="H191" t="n">
         <v>1020050</v>
@@ -5966,7 +5966,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>1.15913105010986</v>
+        <v>1.15913116931915</v>
       </c>
       <c r="H193" t="n">
         <v>574328</v>
@@ -5995,7 +5995,7 @@
         <v>1.62300002574921</v>
       </c>
       <c r="G194" t="n">
-        <v>1.14362919330597</v>
+        <v>1.14362907409668</v>
       </c>
       <c r="H194" t="n">
         <v>1339210</v>
@@ -6024,7 +6024,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G195" t="n">
-        <v>1.16265451908112</v>
+        <v>1.16265439987183</v>
       </c>
       <c r="H195" t="n">
         <v>1118932</v>
@@ -6053,7 +6053,7 @@
         <v>1.68900001049042</v>
       </c>
       <c r="G196" t="n">
-        <v>1.19013524055481</v>
+        <v>1.1901353597641</v>
       </c>
       <c r="H196" t="n">
         <v>693474</v>
@@ -6082,7 +6082,7 @@
         <v>1.64100003242493</v>
       </c>
       <c r="G197" t="n">
-        <v>1.1563127040863</v>
+        <v>1.15631258487701</v>
       </c>
       <c r="H197" t="n">
         <v>2056453</v>
@@ -6227,7 +6227,7 @@
         <v>1.78199994564056</v>
       </c>
       <c r="G202" t="n">
-        <v>1.25566673278809</v>
+        <v>1.2556666135788</v>
       </c>
       <c r="H202" t="n">
         <v>682872</v>
@@ -6285,7 +6285,7 @@
         <v>1.74699997901917</v>
       </c>
       <c r="G204" t="n">
-        <v>1.23100435733795</v>
+        <v>1.23100423812866</v>
       </c>
       <c r="H204" t="n">
         <v>658672</v>
@@ -6314,7 +6314,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G205" t="n">
-        <v>1.30499136447906</v>
+        <v>1.30499148368835</v>
       </c>
       <c r="H205" t="n">
         <v>1053905</v>
@@ -6488,7 +6488,7 @@
         <v>1.87100005149841</v>
       </c>
       <c r="G211" t="n">
-        <v>1.31837964057922</v>
+        <v>1.31837952136993</v>
       </c>
       <c r="H211" t="n">
         <v>796652</v>
@@ -6517,7 +6517,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G212" t="n">
-        <v>1.2937171459198</v>
+        <v>1.29371726512909</v>
       </c>
       <c r="H212" t="n">
         <v>773982</v>
@@ -6546,7 +6546,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G213" t="n">
-        <v>1.28737556934357</v>
+        <v>1.28737545013428</v>
       </c>
       <c r="H213" t="n">
         <v>677501</v>
@@ -6575,7 +6575,7 @@
         <v>1.81099998950958</v>
       </c>
       <c r="G214" t="n">
-        <v>1.27610111236572</v>
+        <v>1.27610123157501</v>
       </c>
       <c r="H214" t="n">
         <v>308754</v>
@@ -6662,7 +6662,7 @@
         <v>1.87100005149841</v>
       </c>
       <c r="G217" t="n">
-        <v>1.31837964057922</v>
+        <v>1.31837952136993</v>
       </c>
       <c r="H217" t="n">
         <v>596050</v>
@@ -6836,7 +6836,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G223" t="n">
-        <v>1.42618930339813</v>
+        <v>1.42618918418884</v>
       </c>
       <c r="H223" t="n">
         <v>405478</v>
@@ -6894,7 +6894,7 @@
         <v>1.98300004005432</v>
       </c>
       <c r="G225" t="n">
-        <v>1.39729917049408</v>
+        <v>1.39729928970337</v>
       </c>
       <c r="H225" t="n">
         <v>1086938</v>
@@ -6952,7 +6952,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G227" t="n">
-        <v>1.33035850524902</v>
+        <v>1.33035838603973</v>
       </c>
       <c r="H227" t="n">
         <v>521176</v>
@@ -7010,7 +7010,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G229" t="n">
-        <v>1.3296537399292</v>
+        <v>1.32965385913849</v>
       </c>
       <c r="H229" t="n">
         <v>305555</v>
@@ -7039,7 +7039,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G230" t="n">
-        <v>1.29442191123962</v>
+        <v>1.29442179203033</v>
       </c>
       <c r="H230" t="n">
         <v>689236</v>
@@ -7097,7 +7097,7 @@
         <v>1.86300003528595</v>
       </c>
       <c r="G232" t="n">
-        <v>1.31274259090424</v>
+        <v>1.31274235248566</v>
       </c>
       <c r="H232" t="n">
         <v>190892</v>
@@ -7155,7 +7155,7 @@
         <v>1.75899994373322</v>
       </c>
       <c r="G234" t="n">
-        <v>1.23945987224579</v>
+        <v>1.23945999145508</v>
       </c>
       <c r="H234" t="n">
         <v>433004</v>
@@ -7242,7 +7242,7 @@
         <v>1.82099997997284</v>
       </c>
       <c r="G237" t="n">
-        <v>1.28314757347107</v>
+        <v>1.28314769268036</v>
       </c>
       <c r="H237" t="n">
         <v>406192</v>
@@ -7329,7 +7329,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G240" t="n">
-        <v>1.27891993522644</v>
+        <v>1.27891981601715</v>
       </c>
       <c r="H240" t="n">
         <v>206556</v>
@@ -7387,7 +7387,7 @@
         <v>1.81900000572205</v>
       </c>
       <c r="G242" t="n">
-        <v>1.28173840045929</v>
+        <v>1.28173828125</v>
       </c>
       <c r="H242" t="n">
         <v>160229</v>
@@ -7503,7 +7503,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G246" t="n">
-        <v>1.36277186870575</v>
+        <v>1.36277174949646</v>
       </c>
       <c r="H246" t="n">
         <v>570217</v>
@@ -7590,7 +7590,7 @@
         <v>1.94099998474121</v>
       </c>
       <c r="G249" t="n">
-        <v>1.36770439147949</v>
+        <v>1.3677042722702</v>
       </c>
       <c r="H249" t="n">
         <v>394746</v>
@@ -7706,7 +7706,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G253" t="n">
-        <v>1.32824444770813</v>
+        <v>1.32824456691742</v>
       </c>
       <c r="H253" t="n">
         <v>496653</v>
@@ -7822,7 +7822,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G257" t="n">
-        <v>1.37052285671234</v>
+        <v>1.37052297592163</v>
       </c>
       <c r="H257" t="n">
         <v>453008</v>
@@ -7909,7 +7909,7 @@
         <v>1.96099996566772</v>
       </c>
       <c r="G260" t="n">
-        <v>1.38179707527161</v>
+        <v>1.38179695606232</v>
       </c>
       <c r="H260" t="n">
         <v>487506</v>
@@ -7967,7 +7967,7 @@
         <v>2.00600004196167</v>
       </c>
       <c r="G262" t="n">
-        <v>1.41350591182709</v>
+        <v>1.4135057926178</v>
       </c>
       <c r="H262" t="n">
         <v>717038</v>
@@ -8025,7 +8025,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G264" t="n">
-        <v>1.40223157405853</v>
+        <v>1.40223169326782</v>
       </c>
       <c r="H264" t="n">
         <v>511622</v>
@@ -8054,7 +8054,7 @@
         <v>2.01300001144409</v>
       </c>
       <c r="G265" t="n">
-        <v>1.41843843460083</v>
+        <v>1.41843831539154</v>
       </c>
       <c r="H265" t="n">
         <v>1394290</v>
@@ -8141,7 +8141,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G268" t="n">
-        <v>1.56077527999878</v>
+        <v>1.56077539920807</v>
       </c>
       <c r="H268" t="n">
         <v>856015</v>
@@ -8170,7 +8170,7 @@
         <v>2.20600008964539</v>
       </c>
       <c r="G269" t="n">
-        <v>1.55443382263184</v>
+        <v>1.55443370342255</v>
       </c>
       <c r="H269" t="n">
         <v>461170</v>
@@ -8199,7 +8199,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G270" t="n">
-        <v>1.55161511898041</v>
+        <v>1.55161499977112</v>
       </c>
       <c r="H270" t="n">
         <v>421095</v>
@@ -8286,7 +8286,7 @@
         <v>2.125</v>
       </c>
       <c r="G273" t="n">
-        <v>1.4973578453064</v>
+        <v>1.49735796451569</v>
       </c>
       <c r="H273" t="n">
         <v>544273</v>
@@ -8344,7 +8344,7 @@
         <v>2.10199999809265</v>
       </c>
       <c r="G275" t="n">
-        <v>1.48115122318268</v>
+        <v>1.48115110397339</v>
       </c>
       <c r="H275" t="n">
         <v>214268</v>
@@ -8373,7 +8373,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G276" t="n">
-        <v>1.48819744586945</v>
+        <v>1.48819756507874</v>
       </c>
       <c r="H276" t="n">
         <v>185994</v>
@@ -8605,7 +8605,7 @@
         <v>2.07599997520447</v>
       </c>
       <c r="G284" t="n">
-        <v>1.46283066272736</v>
+        <v>1.46283054351807</v>
       </c>
       <c r="H284" t="n">
         <v>725403</v>
@@ -8634,7 +8634,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G285" t="n">
-        <v>1.46564900875092</v>
+        <v>1.46564912796021</v>
       </c>
       <c r="H285" t="n">
         <v>331486</v>
@@ -8663,7 +8663,7 @@
         <v>2.05299997329712</v>
       </c>
       <c r="G286" t="n">
-        <v>1.44662380218506</v>
+        <v>1.44662392139435</v>
       </c>
       <c r="H286" t="n">
         <v>680373</v>
@@ -8721,7 +8721,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G288" t="n">
-        <v>1.4318265914917</v>
+        <v>1.43182647228241</v>
       </c>
       <c r="H288" t="n">
         <v>514101</v>
@@ -8866,7 +8866,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G293" t="n">
-        <v>1.49101603031158</v>
+        <v>1.49101614952087</v>
       </c>
       <c r="H293" t="n">
         <v>500302</v>
@@ -8895,7 +8895,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G294" t="n">
-        <v>1.46705853939056</v>
+        <v>1.46705842018127</v>
       </c>
       <c r="H294" t="n">
         <v>796702</v>
@@ -8924,7 +8924,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G295" t="n">
-        <v>1.51074600219727</v>
+        <v>1.51074612140656</v>
       </c>
       <c r="H295" t="n">
         <v>440171</v>
@@ -8953,7 +8953,7 @@
         <v>2.125</v>
       </c>
       <c r="G296" t="n">
-        <v>1.4973578453064</v>
+        <v>1.49735796451569</v>
       </c>
       <c r="H296" t="n">
         <v>636274</v>
@@ -8982,7 +8982,7 @@
         <v>2.12299990653992</v>
       </c>
       <c r="G297" t="n">
-        <v>1.49594855308533</v>
+        <v>1.49594843387604</v>
       </c>
       <c r="H297" t="n">
         <v>507637</v>
@@ -9040,7 +9040,7 @@
         <v>2.11299991607666</v>
       </c>
       <c r="G299" t="n">
-        <v>1.48890209197998</v>
+        <v>1.48890197277069</v>
       </c>
       <c r="H299" t="n">
         <v>234428</v>
@@ -9214,7 +9214,7 @@
         <v>2.05599999427795</v>
       </c>
       <c r="G305" t="n">
-        <v>1.44873774051666</v>
+        <v>1.44873785972595</v>
       </c>
       <c r="H305" t="n">
         <v>446308</v>
@@ -9243,7 +9243,7 @@
         <v>2.12100005149841</v>
       </c>
       <c r="G306" t="n">
-        <v>1.49453926086426</v>
+        <v>1.49453938007355</v>
       </c>
       <c r="H306" t="n">
         <v>349362</v>
@@ -9272,7 +9272,7 @@
         <v>2.12299990653992</v>
       </c>
       <c r="G307" t="n">
-        <v>1.49594855308533</v>
+        <v>1.49594843387604</v>
       </c>
       <c r="H307" t="n">
         <v>183000</v>
@@ -9301,7 +9301,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G308" t="n">
-        <v>1.49383473396301</v>
+        <v>1.49383461475372</v>
       </c>
       <c r="H308" t="n">
         <v>190816</v>
@@ -9330,7 +9330,7 @@
         <v>2.1029999256134</v>
       </c>
       <c r="G309" t="n">
-        <v>1.48185575008392</v>
+        <v>1.48185563087463</v>
       </c>
       <c r="H309" t="n">
         <v>262297</v>
@@ -9533,7 +9533,7 @@
         <v>2.27300000190735</v>
       </c>
       <c r="G316" t="n">
-        <v>1.60164427757263</v>
+        <v>1.60164439678192</v>
       </c>
       <c r="H316" t="n">
         <v>370098</v>
@@ -9562,7 +9562,7 @@
         <v>2.27300000190735</v>
       </c>
       <c r="G317" t="n">
-        <v>1.60164427757263</v>
+        <v>1.60164439678192</v>
       </c>
       <c r="H317" t="n">
         <v>460584</v>
@@ -9649,7 +9649,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G320" t="n">
-        <v>1.62489748001099</v>
+        <v>1.62489759922028</v>
       </c>
       <c r="H320" t="n">
         <v>946396</v>
@@ -9678,7 +9678,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G321" t="n">
-        <v>1.63758099079132</v>
+        <v>1.63758087158203</v>
       </c>
       <c r="H321" t="n">
         <v>897308</v>
@@ -9823,7 +9823,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G326" t="n">
-        <v>1.51074600219727</v>
+        <v>1.51074612140656</v>
       </c>
       <c r="H326" t="n">
         <v>964268</v>
@@ -9852,7 +9852,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G327" t="n">
-        <v>1.47128629684448</v>
+        <v>1.47128617763519</v>
       </c>
       <c r="H327" t="n">
         <v>1679948</v>
@@ -9939,7 +9939,7 @@
         <v>2.19899988174438</v>
       </c>
       <c r="G330" t="n">
-        <v>1.54950106143951</v>
+        <v>1.5495011806488</v>
       </c>
       <c r="H330" t="n">
         <v>398017</v>
@@ -9968,7 +9968,7 @@
         <v>2.25</v>
       </c>
       <c r="G331" t="n">
-        <v>1.5854377746582</v>
+        <v>1.58543789386749</v>
       </c>
       <c r="H331" t="n">
         <v>523276</v>
@@ -9997,7 +9997,7 @@
         <v>2.22099995613098</v>
       </c>
       <c r="G332" t="n">
-        <v>1.56500315666199</v>
+        <v>1.5650030374527</v>
       </c>
       <c r="H332" t="n">
         <v>221480</v>
@@ -10055,7 +10055,7 @@
         <v>2.25</v>
       </c>
       <c r="G334" t="n">
-        <v>1.5854377746582</v>
+        <v>1.58543789386749</v>
       </c>
       <c r="H334" t="n">
         <v>841797</v>
@@ -10229,7 +10229,7 @@
         <v>2.40300011634827</v>
       </c>
       <c r="G340" t="n">
-        <v>1.69324767589569</v>
+        <v>1.6932475566864</v>
       </c>
       <c r="H340" t="n">
         <v>735566</v>
@@ -10258,7 +10258,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G341" t="n">
-        <v>1.65942478179932</v>
+        <v>1.65942490100861</v>
       </c>
       <c r="H341" t="n">
         <v>442544</v>
@@ -10287,7 +10287,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>1.64533221721649</v>
+        <v>1.6453320980072</v>
       </c>
       <c r="H342" t="n">
         <v>505221</v>
@@ -10316,7 +10316,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G343" t="n">
-        <v>1.61010026931763</v>
+        <v>1.61010015010834</v>
       </c>
       <c r="H343" t="n">
         <v>391481</v>
@@ -10374,7 +10374,7 @@
         <v>2.33699989318848</v>
       </c>
       <c r="G345" t="n">
-        <v>1.64674127101898</v>
+        <v>1.64674115180969</v>
       </c>
       <c r="H345" t="n">
         <v>1238842</v>
@@ -10403,7 +10403,7 @@
         <v>2.33699989318848</v>
       </c>
       <c r="G346" t="n">
-        <v>1.64674127101898</v>
+        <v>1.64674115180969</v>
       </c>
       <c r="H346" t="n">
         <v>580707</v>
@@ -10461,7 +10461,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G348" t="n">
-        <v>1.56148016452789</v>
+        <v>1.5614800453186</v>
       </c>
       <c r="H348" t="n">
         <v>2800039</v>
@@ -10519,7 +10519,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G350" t="n">
-        <v>1.55161511898041</v>
+        <v>1.55161499977112</v>
       </c>
       <c r="H350" t="n">
         <v>673952</v>
@@ -10548,7 +10548,7 @@
         <v>2.19400000572205</v>
       </c>
       <c r="G351" t="n">
-        <v>1.54597795009613</v>
+        <v>1.54597806930542</v>
       </c>
       <c r="H351" t="n">
         <v>432046</v>
@@ -10635,7 +10635,7 @@
         <v>2.26900005340576</v>
       </c>
       <c r="G354" t="n">
-        <v>1.59882605075836</v>
+        <v>1.59882581233978</v>
       </c>
       <c r="H354" t="n">
         <v>579865</v>
@@ -10664,7 +10664,7 @@
         <v>2.36400008201599</v>
       </c>
       <c r="G355" t="n">
-        <v>1.66576659679413</v>
+        <v>1.66576671600342</v>
       </c>
       <c r="H355" t="n">
         <v>862677</v>
@@ -10722,7 +10722,7 @@
         <v>2.83750009536743</v>
       </c>
       <c r="G357" t="n">
-        <v>1.99941325187683</v>
+        <v>1.99941301345825</v>
       </c>
       <c r="H357" t="n">
         <v>4829114</v>
@@ -10751,7 +10751,7 @@
         <v>2.7574999332428</v>
       </c>
       <c r="G358" t="n">
-        <v>1.94304215908051</v>
+        <v>1.94304203987122</v>
       </c>
       <c r="H358" t="n">
         <v>5360863</v>
@@ -10809,7 +10809,7 @@
         <v>2.69749999046326</v>
       </c>
       <c r="G360" t="n">
-        <v>1.900763630867</v>
+        <v>1.90076351165771</v>
       </c>
       <c r="H360" t="n">
         <v>2325561</v>
@@ -10867,7 +10867,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G362" t="n">
-        <v>1.81444537639618</v>
+        <v>1.81444549560547</v>
       </c>
       <c r="H362" t="n">
         <v>1637436</v>
@@ -11070,7 +11070,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G369" t="n">
-        <v>1.80739915370941</v>
+        <v>1.80739903450012</v>
       </c>
       <c r="H369" t="n">
         <v>372165</v>
@@ -11128,7 +11128,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G371" t="n">
-        <v>1.83206129074097</v>
+        <v>1.83206140995026</v>
       </c>
       <c r="H371" t="n">
         <v>521311</v>
@@ -11157,7 +11157,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G372" t="n">
-        <v>1.87786269187927</v>
+        <v>1.87786293029785</v>
       </c>
       <c r="H372" t="n">
         <v>730632</v>
@@ -11186,7 +11186,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G373" t="n">
-        <v>1.8849093914032</v>
+        <v>1.88490915298462</v>
       </c>
       <c r="H373" t="n">
         <v>569369</v>
@@ -11215,7 +11215,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G374" t="n">
-        <v>1.83910775184631</v>
+        <v>1.83910763263702</v>
       </c>
       <c r="H374" t="n">
         <v>564472</v>
@@ -11244,7 +11244,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G375" t="n">
-        <v>1.83910775184631</v>
+        <v>1.83910763263702</v>
       </c>
       <c r="H375" t="n">
         <v>442703</v>
@@ -11273,7 +11273,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G376" t="n">
-        <v>1.86377012729645</v>
+        <v>1.86377000808716</v>
       </c>
       <c r="H376" t="n">
         <v>303450</v>
@@ -11302,7 +11302,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G377" t="n">
-        <v>1.86377012729645</v>
+        <v>1.86377000808716</v>
       </c>
       <c r="H377" t="n">
         <v>377689</v>
@@ -11331,7 +11331,7 @@
         <v>2.6324999332428</v>
       </c>
       <c r="G378" t="n">
-        <v>1.85496199131012</v>
+        <v>1.85496211051941</v>
       </c>
       <c r="H378" t="n">
         <v>460839</v>
@@ -11360,7 +11360,7 @@
         <v>2.64249992370605</v>
       </c>
       <c r="G379" t="n">
-        <v>1.86200869083405</v>
+        <v>1.86200845241547</v>
       </c>
       <c r="H379" t="n">
         <v>662990</v>
@@ -11389,7 +11389,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>1.86377012729645</v>
+        <v>1.86377000808716</v>
       </c>
       <c r="H380" t="n">
         <v>668827</v>
@@ -11418,7 +11418,7 @@
         <v>2.59750008583069</v>
       </c>
       <c r="G381" t="n">
-        <v>1.83029973506927</v>
+        <v>1.83029997348785</v>
       </c>
       <c r="H381" t="n">
         <v>623499</v>
@@ -11447,7 +11447,7 @@
         <v>2.6324999332428</v>
       </c>
       <c r="G382" t="n">
-        <v>1.85496199131012</v>
+        <v>1.85496211051941</v>
       </c>
       <c r="H382" t="n">
         <v>848076</v>
@@ -11476,7 +11476,7 @@
         <v>2.61249995231628</v>
       </c>
       <c r="G383" t="n">
-        <v>1.84086942672729</v>
+        <v>1.84086918830872</v>
       </c>
       <c r="H383" t="n">
         <v>982705</v>
@@ -11505,7 +11505,7 @@
         <v>2.55749988555908</v>
       </c>
       <c r="G384" t="n">
-        <v>1.80211412906647</v>
+        <v>1.80211400985718</v>
       </c>
       <c r="H384" t="n">
         <v>1307235</v>
@@ -11534,7 +11534,7 @@
         <v>2.55250000953674</v>
       </c>
       <c r="G385" t="n">
-        <v>1.79859113693237</v>
+        <v>1.79859089851379</v>
       </c>
       <c r="H385" t="n">
         <v>1784366</v>
@@ -11563,7 +11563,7 @@
         <v>2.35700011253357</v>
       </c>
       <c r="G386" t="n">
-        <v>1.84116351604462</v>
+        <v>1.8411637544632</v>
       </c>
       <c r="H386" t="n">
         <v>1675723</v>
@@ -11592,7 +11592,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G387" t="n">
-        <v>1.80601191520691</v>
+        <v>1.8060120344162</v>
       </c>
       <c r="H387" t="n">
         <v>2221253</v>
@@ -11679,7 +11679,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G390" t="n">
-        <v>1.85131824016571</v>
+        <v>1.851318359375</v>
       </c>
       <c r="H390" t="n">
         <v>717045</v>
@@ -11737,7 +11737,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G392" t="n">
-        <v>1.84741282463074</v>
+        <v>1.84741270542145</v>
       </c>
       <c r="H392" t="n">
         <v>573846</v>
@@ -11795,7 +11795,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G394" t="n">
-        <v>1.81694793701172</v>
+        <v>1.81694805622101</v>
       </c>
       <c r="H394" t="n">
         <v>634308</v>
@@ -11824,7 +11824,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G395" t="n">
-        <v>1.84506940841675</v>
+        <v>1.84506928920746</v>
       </c>
       <c r="H395" t="n">
         <v>768257</v>
@@ -11853,7 +11853,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G396" t="n">
-        <v>1.81694793701172</v>
+        <v>1.81694805622101</v>
       </c>
       <c r="H396" t="n">
         <v>564016</v>
@@ -11940,7 +11940,7 @@
         <v>2.3289999961853</v>
       </c>
       <c r="G399" t="n">
-        <v>1.81929135322571</v>
+        <v>1.819291472435</v>
       </c>
       <c r="H399" t="n">
         <v>717310</v>
@@ -11969,7 +11969,7 @@
         <v>2.29900002479553</v>
       </c>
       <c r="G400" t="n">
-        <v>1.79585707187653</v>
+        <v>1.79585695266724</v>
       </c>
       <c r="H400" t="n">
         <v>435929</v>
@@ -11998,7 +11998,7 @@
         <v>2.30800008773804</v>
       </c>
       <c r="G401" t="n">
-        <v>1.80288732051849</v>
+        <v>1.80288743972778</v>
       </c>
       <c r="H401" t="n">
         <v>290608</v>
@@ -12056,7 +12056,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G403" t="n">
-        <v>1.84350693225861</v>
+        <v>1.84350681304932</v>
       </c>
       <c r="H403" t="n">
         <v>508765</v>
@@ -12085,7 +12085,7 @@
         <v>2.34299993515015</v>
       </c>
       <c r="G404" t="n">
-        <v>1.83022737503052</v>
+        <v>1.83022749423981</v>
       </c>
       <c r="H404" t="n">
         <v>400051</v>
@@ -12114,7 +12114,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G405" t="n">
-        <v>1.85913002490997</v>
+        <v>1.85912990570068</v>
       </c>
       <c r="H405" t="n">
         <v>572167</v>
@@ -12143,7 +12143,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G406" t="n">
-        <v>1.82944655418396</v>
+        <v>1.82944619655609</v>
       </c>
       <c r="H406" t="n">
         <v>327031</v>
@@ -12201,7 +12201,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G408" t="n">
-        <v>1.78257763385773</v>
+        <v>1.78257751464844</v>
       </c>
       <c r="H408" t="n">
         <v>720575</v>
@@ -12259,7 +12259,7 @@
         <v>2.29900002479553</v>
       </c>
       <c r="G410" t="n">
-        <v>1.79585707187653</v>
+        <v>1.79585695266724</v>
       </c>
       <c r="H410" t="n">
         <v>244821</v>
@@ -12288,7 +12288,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G411" t="n">
-        <v>1.80601191520691</v>
+        <v>1.8060120344162</v>
       </c>
       <c r="H411" t="n">
         <v>489918</v>
@@ -12317,7 +12317,7 @@
         <v>2.3289999961853</v>
       </c>
       <c r="G412" t="n">
-        <v>1.81929135322571</v>
+        <v>1.819291472435</v>
       </c>
       <c r="H412" t="n">
         <v>1092003</v>
@@ -12346,7 +12346,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G413" t="n">
-        <v>1.82397842407227</v>
+        <v>1.82397830486298</v>
       </c>
       <c r="H413" t="n">
         <v>525566</v>
@@ -12491,7 +12491,7 @@
         <v>2.26099991798401</v>
       </c>
       <c r="G418" t="n">
-        <v>1.76617348194122</v>
+        <v>1.76617336273193</v>
       </c>
       <c r="H418" t="n">
         <v>422740</v>
@@ -12607,7 +12607,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G422" t="n">
-        <v>1.7302405834198</v>
+        <v>1.73024070262909</v>
       </c>
       <c r="H422" t="n">
         <v>493842</v>
@@ -12665,7 +12665,7 @@
         <v>2.14100003242493</v>
       </c>
       <c r="G424" t="n">
-        <v>1.67243587970734</v>
+        <v>1.67243576049805</v>
       </c>
       <c r="H424" t="n">
         <v>2417146</v>
@@ -12752,7 +12752,7 @@
         <v>2.11299991607666</v>
       </c>
       <c r="G427" t="n">
-        <v>1.65056359767914</v>
+        <v>1.65056347846985</v>
       </c>
       <c r="H427" t="n">
         <v>344744</v>
@@ -12810,7 +12810,7 @@
         <v>2.0789999961853</v>
       </c>
       <c r="G429" t="n">
-        <v>1.62400460243225</v>
+        <v>1.62400472164154</v>
       </c>
       <c r="H429" t="n">
         <v>242331</v>
@@ -12839,7 +12839,7 @@
         <v>2.05299997329712</v>
       </c>
       <c r="G430" t="n">
-        <v>1.60369479656219</v>
+        <v>1.60369491577148</v>
       </c>
       <c r="H430" t="n">
         <v>355572</v>
@@ -12926,7 +12926,7 @@
         <v>1.97699999809265</v>
       </c>
       <c r="G433" t="n">
-        <v>1.54432773590088</v>
+        <v>1.54432761669159</v>
       </c>
       <c r="H433" t="n">
         <v>335769</v>
@@ -12955,7 +12955,7 @@
         <v>1.99899995326996</v>
       </c>
       <c r="G434" t="n">
-        <v>1.56151294708252</v>
+        <v>1.56151282787323</v>
       </c>
       <c r="H434" t="n">
         <v>852921</v>
@@ -13042,7 +13042,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G437" t="n">
-        <v>1.44121634960175</v>
+        <v>1.44121623039246</v>
       </c>
       <c r="H437" t="n">
         <v>430171</v>
@@ -13071,7 +13071,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G438" t="n">
-        <v>1.43887281417847</v>
+        <v>1.43887293338776</v>
       </c>
       <c r="H438" t="n">
         <v>297282</v>
@@ -13274,7 +13274,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G445" t="n">
-        <v>1.48886632919312</v>
+        <v>1.48886620998383</v>
       </c>
       <c r="H445" t="n">
         <v>825110</v>
@@ -13332,7 +13332,7 @@
         <v>1.85300004482269</v>
       </c>
       <c r="G447" t="n">
-        <v>1.44746553897858</v>
+        <v>1.44746541976929</v>
       </c>
       <c r="H447" t="n">
         <v>756122</v>
@@ -13390,7 +13390,7 @@
         <v>1.8309999704361</v>
       </c>
       <c r="G449" t="n">
-        <v>1.43028008937836</v>
+        <v>1.43028020858765</v>
       </c>
       <c r="H449" t="n">
         <v>475160</v>
@@ -13477,7 +13477,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G452" t="n">
-        <v>1.31232690811157</v>
+        <v>1.31232702732086</v>
       </c>
       <c r="H452" t="n">
         <v>1384290</v>
@@ -13535,7 +13535,7 @@
         <v>1.66719996929169</v>
       </c>
       <c r="G454" t="n">
-        <v>1.30232834815979</v>
+        <v>1.3023282289505</v>
       </c>
       <c r="H454" t="n">
         <v>438827</v>
@@ -13564,7 +13564,7 @@
         <v>1.69219994544983</v>
       </c>
       <c r="G455" t="n">
-        <v>1.32185697555542</v>
+        <v>1.32185685634613</v>
       </c>
       <c r="H455" t="n">
         <v>907774</v>
@@ -13622,7 +13622,7 @@
         <v>1.69159996509552</v>
       </c>
       <c r="G457" t="n">
-        <v>1.3213883638382</v>
+        <v>1.32138824462891</v>
       </c>
       <c r="H457" t="n">
         <v>232730</v>
@@ -13651,7 +13651,7 @@
         <v>1.74259996414185</v>
       </c>
       <c r="G458" t="n">
-        <v>1.36122679710388</v>
+        <v>1.36122667789459</v>
       </c>
       <c r="H458" t="n">
         <v>372410</v>
@@ -13680,7 +13680,7 @@
         <v>1.84239995479584</v>
       </c>
       <c r="G459" t="n">
-        <v>1.43918526172638</v>
+        <v>1.43918514251709</v>
       </c>
       <c r="H459" t="n">
         <v>501526</v>
@@ -13709,7 +13709,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G460" t="n">
-        <v>1.42715573310852</v>
+        <v>1.42715561389923</v>
       </c>
       <c r="H460" t="n">
         <v>222767</v>
@@ -13825,7 +13825,7 @@
         <v>1.93680000305176</v>
       </c>
       <c r="G464" t="n">
-        <v>1.51292562484741</v>
+        <v>1.51292550563812</v>
       </c>
       <c r="H464" t="n">
         <v>268931</v>
@@ -13854,7 +13854,7 @@
         <v>1.92239999771118</v>
       </c>
       <c r="G465" t="n">
-        <v>1.50167691707611</v>
+        <v>1.5016770362854</v>
       </c>
       <c r="H465" t="n">
         <v>353065</v>
@@ -13883,7 +13883,7 @@
         <v>2.02950000762939</v>
       </c>
       <c r="G466" t="n">
-        <v>1.58533787727356</v>
+        <v>1.58533799648285</v>
       </c>
       <c r="H466" t="n">
         <v>617753</v>
@@ -13941,7 +13941,7 @@
         <v>1.97259998321533</v>
       </c>
       <c r="G468" t="n">
-        <v>1.54089069366455</v>
+        <v>1.54089057445526</v>
       </c>
       <c r="H468" t="n">
         <v>448541</v>
@@ -13970,7 +13970,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G469" t="n">
-        <v>1.58729088306427</v>
+        <v>1.58729076385498</v>
       </c>
       <c r="H469" t="n">
         <v>310094</v>
@@ -14057,7 +14057,7 @@
         <v>2.00850009918213</v>
       </c>
       <c r="G472" t="n">
-        <v>1.56893396377563</v>
+        <v>1.56893384456635</v>
       </c>
       <c r="H472" t="n">
         <v>366405</v>
@@ -14086,7 +14086,7 @@
         <v>2.15249991416931</v>
       </c>
       <c r="G473" t="n">
-        <v>1.68141889572144</v>
+        <v>1.68141901493073</v>
       </c>
       <c r="H473" t="n">
         <v>1172106</v>
@@ -14173,7 +14173,7 @@
         <v>2.25650000572205</v>
       </c>
       <c r="G476" t="n">
-        <v>1.76265835762024</v>
+        <v>1.76265823841095</v>
       </c>
       <c r="H476" t="n">
         <v>463148</v>
@@ -14289,7 +14289,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G480" t="n">
-        <v>1.7466447353363</v>
+        <v>1.74664485454559</v>
       </c>
       <c r="H480" t="n">
         <v>1270704</v>
@@ -14318,7 +14318,7 @@
         <v>2.22300004959106</v>
       </c>
       <c r="G481" t="n">
-        <v>1.73649001121521</v>
+        <v>1.73648989200592</v>
       </c>
       <c r="H481" t="n">
         <v>624711</v>
@@ -14347,7 +14347,7 @@
         <v>2.31900000572205</v>
       </c>
       <c r="G482" t="n">
-        <v>1.81147992610931</v>
+        <v>1.8114800453186</v>
       </c>
       <c r="H482" t="n">
         <v>1426253</v>
@@ -14376,7 +14376,7 @@
         <v>2.29749989509583</v>
       </c>
       <c r="G483" t="n">
-        <v>1.79468512535095</v>
+        <v>1.79468524456024</v>
       </c>
       <c r="H483" t="n">
         <v>1095196</v>
@@ -14405,7 +14405,7 @@
         <v>2.33599996566772</v>
       </c>
       <c r="G484" t="n">
-        <v>1.82475936412811</v>
+        <v>1.8247594833374</v>
       </c>
       <c r="H484" t="n">
         <v>451325</v>
@@ -14434,7 +14434,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G485" t="n">
-        <v>1.86850368976593</v>
+        <v>1.86850345134735</v>
       </c>
       <c r="H485" t="n">
         <v>792725</v>
@@ -14492,7 +14492,7 @@
         <v>2.25</v>
       </c>
       <c r="G487" t="n">
-        <v>1.7575808763504</v>
+        <v>1.75758099555969</v>
       </c>
       <c r="H487" t="n">
         <v>1370262</v>
@@ -14550,7 +14550,7 @@
         <v>2.34949994087219</v>
       </c>
       <c r="G489" t="n">
-        <v>1.83530497550964</v>
+        <v>1.83530509471893</v>
       </c>
       <c r="H489" t="n">
         <v>626584</v>
@@ -14608,7 +14608,7 @@
         <v>2.39750003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>1.87280023097992</v>
+        <v>1.87280011177063</v>
       </c>
       <c r="H491" t="n">
         <v>839004</v>
@@ -14637,7 +14637,7 @@
         <v>2.3989999294281</v>
       </c>
       <c r="G492" t="n">
-        <v>1.87397170066833</v>
+        <v>1.87397158145905</v>
       </c>
       <c r="H492" t="n">
         <v>458199</v>
@@ -14666,7 +14666,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G493" t="n">
-        <v>1.86225438117981</v>
+        <v>1.86225461959839</v>
       </c>
       <c r="H493" t="n">
         <v>271589</v>
@@ -14695,7 +14695,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G494" t="n">
-        <v>1.85913002490997</v>
+        <v>1.85912990570068</v>
       </c>
       <c r="H494" t="n">
         <v>254944</v>
@@ -14724,7 +14724,7 @@
         <v>2.38100004196167</v>
       </c>
       <c r="G495" t="n">
-        <v>1.85991108417511</v>
+        <v>1.8599112033844</v>
       </c>
       <c r="H495" t="n">
         <v>360476</v>
@@ -14753,7 +14753,7 @@
         <v>2.375</v>
       </c>
       <c r="G496" t="n">
-        <v>1.85522413253784</v>
+        <v>1.85522401332855</v>
       </c>
       <c r="H496" t="n">
         <v>380134</v>
@@ -14840,7 +14840,7 @@
         <v>2.3289999961853</v>
       </c>
       <c r="G499" t="n">
-        <v>1.81929135322571</v>
+        <v>1.819291472435</v>
       </c>
       <c r="H499" t="n">
         <v>426104</v>
@@ -14927,7 +14927,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G502" t="n">
-        <v>1.89662504196167</v>
+        <v>1.89662492275238</v>
       </c>
       <c r="H502" t="n">
         <v>886759</v>
@@ -14956,7 +14956,7 @@
         <v>2.4210000038147</v>
       </c>
       <c r="G503" t="n">
-        <v>1.89115703105927</v>
+        <v>1.89115715026855</v>
       </c>
       <c r="H503" t="n">
         <v>400870</v>
@@ -14985,7 +14985,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G504" t="n">
-        <v>1.90443634986877</v>
+        <v>1.90443646907806</v>
       </c>
       <c r="H504" t="n">
         <v>376866</v>
@@ -15014,7 +15014,7 @@
         <v>2.40199995040894</v>
       </c>
       <c r="G505" t="n">
-        <v>1.87631499767303</v>
+        <v>1.87631523609161</v>
       </c>
       <c r="H505" t="n">
         <v>719122</v>
@@ -15072,7 +15072,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G507" t="n">
-        <v>1.85131824016571</v>
+        <v>1.851318359375</v>
       </c>
       <c r="H507" t="n">
         <v>420850</v>
@@ -15101,7 +15101,7 @@
         <v>2.38750004768372</v>
       </c>
       <c r="G508" t="n">
-        <v>1.86498844623566</v>
+        <v>1.86498880386353</v>
       </c>
       <c r="H508" t="n">
         <v>279164</v>
@@ -15130,7 +15130,7 @@
         <v>2.37949991226196</v>
       </c>
       <c r="G509" t="n">
-        <v>1.85873937606812</v>
+        <v>1.85873925685883</v>
       </c>
       <c r="H509" t="n">
         <v>517495</v>
@@ -15159,7 +15159,7 @@
         <v>2.33949995040894</v>
       </c>
       <c r="G510" t="n">
-        <v>1.82749330997467</v>
+        <v>1.82749342918396</v>
       </c>
       <c r="H510" t="n">
         <v>387078</v>
@@ -15188,7 +15188,7 @@
         <v>2.30800008773804</v>
       </c>
       <c r="G511" t="n">
-        <v>1.80288732051849</v>
+        <v>1.80288743972778</v>
       </c>
       <c r="H511" t="n">
         <v>471638</v>
@@ -15275,7 +15275,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G514" t="n">
-        <v>1.84819388389587</v>
+        <v>1.84819376468658</v>
       </c>
       <c r="H514" t="n">
         <v>499423</v>
@@ -15304,7 +15304,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G515" t="n">
-        <v>1.88256442546844</v>
+        <v>1.88256430625916</v>
       </c>
       <c r="H515" t="n">
         <v>456876</v>
@@ -15333,7 +15333,7 @@
         <v>2.38700008392334</v>
       </c>
       <c r="G516" t="n">
-        <v>1.86459815502167</v>
+        <v>1.86459803581238</v>
       </c>
       <c r="H516" t="n">
         <v>378435</v>
@@ -15391,7 +15391,7 @@
         <v>2.35949993133545</v>
       </c>
       <c r="G518" t="n">
-        <v>1.84311628341675</v>
+        <v>1.84311640262604</v>
       </c>
       <c r="H518" t="n">
         <v>314732</v>
@@ -15420,7 +15420,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G519" t="n">
-        <v>1.84506940841675</v>
+        <v>1.84506928920746</v>
       </c>
       <c r="H519" t="n">
         <v>346938</v>
@@ -15536,7 +15536,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G523" t="n">
-        <v>1.74352025985718</v>
+        <v>1.74352037906647</v>
       </c>
       <c r="H523" t="n">
         <v>587511</v>
@@ -15594,7 +15594,7 @@
         <v>2.18650007247925</v>
       </c>
       <c r="G525" t="n">
-        <v>1.70797789096832</v>
+        <v>1.70797801017761</v>
       </c>
       <c r="H525" t="n">
         <v>339135</v>
@@ -15739,7 +15739,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G530" t="n">
-        <v>1.65603172779083</v>
+        <v>1.65603160858154</v>
       </c>
       <c r="H530" t="n">
         <v>1091564</v>
@@ -15855,7 +15855,7 @@
         <v>2.1029999256134</v>
       </c>
       <c r="G534" t="n">
-        <v>1.64275217056274</v>
+        <v>1.64275205135345</v>
       </c>
       <c r="H534" t="n">
         <v>489001</v>
@@ -15971,7 +15971,7 @@
         <v>2.11150002479553</v>
       </c>
       <c r="G538" t="n">
-        <v>1.64939200878143</v>
+        <v>1.64939188957214</v>
       </c>
       <c r="H538" t="n">
         <v>386864</v>
@@ -16058,7 +16058,7 @@
         <v>2.10949993133545</v>
       </c>
       <c r="G541" t="n">
-        <v>1.64782953262329</v>
+        <v>1.64782965183258</v>
       </c>
       <c r="H541" t="n">
         <v>509259</v>
@@ -16174,7 +16174,7 @@
         <v>2.12750005722046</v>
       </c>
       <c r="G545" t="n">
-        <v>1.6618903875351</v>
+        <v>1.66189050674438</v>
       </c>
       <c r="H545" t="n">
         <v>1419921</v>
@@ -16232,7 +16232,7 @@
         <v>2.10949993133545</v>
       </c>
       <c r="G547" t="n">
-        <v>1.64782953262329</v>
+        <v>1.64782965183258</v>
       </c>
       <c r="H547" t="n">
         <v>489388</v>
@@ -16348,7 +16348,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G551" t="n">
-        <v>1.67009234428406</v>
+        <v>1.67009222507477</v>
       </c>
       <c r="H551" t="n">
         <v>1192328</v>
@@ -16406,7 +16406,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G553" t="n">
-        <v>1.74976944923401</v>
+        <v>1.74976933002472</v>
       </c>
       <c r="H553" t="n">
         <v>1944729</v>
@@ -16464,7 +16464,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G555" t="n">
-        <v>1.74352025985718</v>
+        <v>1.74352037906647</v>
       </c>
       <c r="H555" t="n">
         <v>532106</v>
@@ -16493,7 +16493,7 @@
         <v>2.24449992179871</v>
       </c>
       <c r="G556" t="n">
-        <v>1.75328457355499</v>
+        <v>1.75328433513641</v>
       </c>
       <c r="H556" t="n">
         <v>397911</v>
@@ -16580,7 +16580,7 @@
         <v>2.42149996757507</v>
       </c>
       <c r="G559" t="n">
-        <v>1.89154744148254</v>
+        <v>1.89154756069183</v>
       </c>
       <c r="H559" t="n">
         <v>1056336</v>
@@ -16609,7 +16609,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G560" t="n">
-        <v>1.87865853309631</v>
+        <v>1.8786586523056</v>
       </c>
       <c r="H560" t="n">
         <v>518625</v>
@@ -16638,7 +16638,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G561" t="n">
-        <v>1.92630875110626</v>
+        <v>1.92630863189697</v>
       </c>
       <c r="H561" t="n">
         <v>1119220</v>
@@ -16667,7 +16667,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G562" t="n">
-        <v>1.95130527019501</v>
+        <v>1.95130503177643</v>
       </c>
       <c r="H562" t="n">
         <v>455972</v>
@@ -16754,7 +16754,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G565" t="n">
-        <v>1.97473978996277</v>
+        <v>1.97473990917206</v>
       </c>
       <c r="H565" t="n">
         <v>742112</v>
@@ -16812,7 +16812,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G567" t="n">
-        <v>1.97473978996277</v>
+        <v>1.97473990917206</v>
       </c>
       <c r="H567" t="n">
         <v>1363010</v>
@@ -16841,7 +16841,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G568" t="n">
-        <v>1.99661195278168</v>
+        <v>1.99661183357239</v>
       </c>
       <c r="H568" t="n">
         <v>1003381</v>
@@ -16899,7 +16899,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G570" t="n">
-        <v>1.92943322658539</v>
+        <v>1.9294331073761</v>
       </c>
       <c r="H570" t="n">
         <v>765788</v>
@@ -16928,7 +16928,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G571" t="n">
-        <v>1.93099522590637</v>
+        <v>1.93099534511566</v>
       </c>
       <c r="H571" t="n">
         <v>439198</v>
@@ -17015,7 +17015,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G574" t="n">
-        <v>2.02785754203796</v>
+        <v>2.02785778045654</v>
       </c>
       <c r="H574" t="n">
         <v>1096883</v>
@@ -17044,7 +17044,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G575" t="n">
-        <v>2.04660511016846</v>
+        <v>2.04660534858704</v>
       </c>
       <c r="H575" t="n">
         <v>671436</v>
@@ -17102,7 +17102,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G577" t="n">
-        <v>2.12784433364868</v>
+        <v>2.12784457206726</v>
       </c>
       <c r="H577" t="n">
         <v>1427518</v>
@@ -17160,7 +17160,7 @@
         <v>2.71799993515015</v>
       </c>
       <c r="G579" t="n">
-        <v>2.12315773963928</v>
+        <v>2.1231575012207</v>
       </c>
       <c r="H579" t="n">
         <v>1054021</v>
@@ -17247,7 +17247,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>2.1793999671936</v>
+        <v>2.17940020561218</v>
       </c>
       <c r="H582" t="n">
         <v>543959</v>
@@ -17305,7 +17305,7 @@
         <v>2.76200008392334</v>
       </c>
       <c r="G584" t="n">
-        <v>2.15752816200256</v>
+        <v>2.15752840042114</v>
       </c>
       <c r="H584" t="n">
         <v>580443</v>
@@ -17334,7 +17334,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G585" t="n">
-        <v>2.19658541679382</v>
+        <v>2.1965856552124</v>
       </c>
       <c r="H585" t="n">
         <v>1518765</v>
@@ -17363,7 +17363,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G586" t="n">
-        <v>2.25751519203186</v>
+        <v>2.25751495361328</v>
       </c>
       <c r="H586" t="n">
         <v>1032388</v>
@@ -17421,7 +17421,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G588" t="n">
-        <v>2.31219530105591</v>
+        <v>2.31219506263733</v>
       </c>
       <c r="H588" t="n">
         <v>1282951</v>
@@ -17537,7 +17537,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G592" t="n">
-        <v>2.4387412071228</v>
+        <v>2.43874073028564</v>
       </c>
       <c r="H592" t="n">
         <v>965545</v>
@@ -17624,7 +17624,7 @@
         <v>3.11400008201599</v>
       </c>
       <c r="G595" t="n">
-        <v>2.43249177932739</v>
+        <v>2.43249201774597</v>
       </c>
       <c r="H595" t="n">
         <v>1799003</v>
@@ -17653,7 +17653,7 @@
         <v>3.00399994850159</v>
       </c>
       <c r="G596" t="n">
-        <v>2.34656548500061</v>
+        <v>2.34656572341919</v>
       </c>
       <c r="H596" t="n">
         <v>921949</v>
@@ -17682,7 +17682,7 @@
         <v>3</v>
       </c>
       <c r="G597" t="n">
-        <v>2.34344124794006</v>
+        <v>2.34344100952148</v>
       </c>
       <c r="H597" t="n">
         <v>1851145</v>
@@ -17740,7 +17740,7 @@
         <v>3.10800004005432</v>
       </c>
       <c r="G599" t="n">
-        <v>2.42780494689941</v>
+        <v>2.42780518531799</v>
       </c>
       <c r="H599" t="n">
         <v>1169838</v>
@@ -17798,7 +17798,7 @@
         <v>3.05200004577637</v>
       </c>
       <c r="G601" t="n">
-        <v>2.38406085968018</v>
+        <v>2.3840606212616</v>
       </c>
       <c r="H601" t="n">
         <v>913843</v>
@@ -17856,7 +17856,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G603" t="n">
-        <v>2.4653000831604</v>
+        <v>2.46529984474182</v>
       </c>
       <c r="H603" t="n">
         <v>1511750</v>
@@ -17885,7 +17885,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G604" t="n">
-        <v>2.4653000831604</v>
+        <v>2.46529984474182</v>
       </c>
       <c r="H604" t="n">
         <v>2000044</v>
@@ -17914,7 +17914,7 @@
         <v>3.17400002479553</v>
       </c>
       <c r="G605" t="n">
-        <v>2.47936081886292</v>
+        <v>2.47936058044434</v>
       </c>
       <c r="H605" t="n">
         <v>2744827</v>
@@ -17943,7 +17943,7 @@
         <v>3.30399990081787</v>
       </c>
       <c r="G606" t="n">
-        <v>2.58090949058533</v>
+        <v>2.58090972900391</v>
       </c>
       <c r="H606" t="n">
         <v>2221014</v>
@@ -18001,7 +18001,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G608" t="n">
-        <v>2.54653930664062</v>
+        <v>2.5465395450592</v>
       </c>
       <c r="H608" t="n">
         <v>795781</v>
@@ -18030,7 +18030,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G609" t="n">
-        <v>2.54810190200806</v>
+        <v>2.54810166358948</v>
       </c>
       <c r="H609" t="n">
         <v>548275</v>
@@ -18175,7 +18175,7 @@
         <v>3.09599995613098</v>
       </c>
       <c r="G614" t="n">
-        <v>2.41843104362488</v>
+        <v>2.41843128204346</v>
       </c>
       <c r="H614" t="n">
         <v>539410</v>
@@ -18378,7 +18378,7 @@
         <v>3.18799996376038</v>
       </c>
       <c r="G621" t="n">
-        <v>2.49029684066772</v>
+        <v>2.49029660224915</v>
       </c>
       <c r="H621" t="n">
         <v>691299</v>
@@ -18407,7 +18407,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G622" t="n">
-        <v>2.52310514450073</v>
+        <v>2.52310490608215</v>
       </c>
       <c r="H622" t="n">
         <v>1734037</v>
@@ -18494,7 +18494,7 @@
         <v>3.24799990653992</v>
       </c>
       <c r="G625" t="n">
-        <v>2.53716564178467</v>
+        <v>2.53716540336609</v>
       </c>
       <c r="H625" t="n">
         <v>505088</v>
@@ -18552,7 +18552,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G627" t="n">
-        <v>2.52310514450073</v>
+        <v>2.52310490608215</v>
       </c>
       <c r="H627" t="n">
         <v>1052134</v>
@@ -18610,7 +18610,7 @@
         <v>3.26399993896484</v>
       </c>
       <c r="G629" t="n">
-        <v>2.54966402053833</v>
+        <v>2.54966378211975</v>
       </c>
       <c r="H629" t="n">
         <v>1449732</v>
@@ -18784,7 +18784,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G635" t="n">
-        <v>2.71058034896851</v>
+        <v>2.71058011054993</v>
       </c>
       <c r="H635" t="n">
         <v>867265</v>
@@ -18929,7 +18929,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G640" t="n">
-        <v>2.66151189804077</v>
+        <v>2.66151165962219</v>
       </c>
       <c r="H640" t="n">
         <v>1142550</v>
@@ -19074,7 +19074,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G645" t="n">
-        <v>2.65814280509949</v>
+        <v>2.65814256668091</v>
       </c>
       <c r="H645" t="n">
         <v>687583</v>
@@ -19132,7 +19132,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G647" t="n">
-        <v>2.59413146972656</v>
+        <v>2.59413170814514</v>
       </c>
       <c r="H647" t="n">
         <v>573464</v>
@@ -19161,7 +19161,7 @@
         <v>3.01399993896484</v>
       </c>
       <c r="G648" t="n">
-        <v>2.53854298591614</v>
+        <v>2.53854322433472</v>
       </c>
       <c r="H648" t="n">
         <v>931043</v>
@@ -19248,7 +19248,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G651" t="n">
-        <v>2.44926476478577</v>
+        <v>2.44926452636719</v>
       </c>
       <c r="H651" t="n">
         <v>488032</v>
@@ -19422,7 +19422,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G657" t="n">
-        <v>2.45600247383118</v>
+        <v>2.45600271224976</v>
       </c>
       <c r="H657" t="n">
         <v>344477</v>
@@ -19567,7 +19567,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G662" t="n">
-        <v>2.47116327285767</v>
+        <v>2.47116303443909</v>
       </c>
       <c r="H662" t="n">
         <v>401363</v>
@@ -19683,7 +19683,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G666" t="n">
-        <v>2.48800802230835</v>
+        <v>2.48800826072693</v>
       </c>
       <c r="H666" t="n">
         <v>259923</v>
@@ -19741,7 +19741,7 @@
         <v>2.89800000190735</v>
       </c>
       <c r="G668" t="n">
-        <v>2.44084191322327</v>
+        <v>2.44084215164185</v>
       </c>
       <c r="H668" t="n">
         <v>360472</v>
@@ -20031,7 +20031,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G678" t="n">
-        <v>2.35661697387695</v>
+        <v>2.35661721229553</v>
       </c>
       <c r="H678" t="n">
         <v>240265</v>
@@ -20118,7 +20118,7 @@
         <v>3.22399997711182</v>
       </c>
       <c r="G681" t="n">
-        <v>2.71541571617126</v>
+        <v>2.71541595458984</v>
       </c>
       <c r="H681" t="n">
         <v>4686248</v>
@@ -20147,7 +20147,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G682" t="n">
-        <v>2.57223296165466</v>
+        <v>2.57223320007324</v>
       </c>
       <c r="H682" t="n">
         <v>2047557</v>
@@ -20321,7 +20321,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G688" t="n">
-        <v>2.6109766960144</v>
+        <v>2.61097645759583</v>
       </c>
       <c r="H688" t="n">
         <v>540996</v>
@@ -20350,7 +20350,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G689" t="n">
-        <v>2.58570909500122</v>
+        <v>2.5857093334198</v>
       </c>
       <c r="H689" t="n">
         <v>835995</v>
@@ -20379,7 +20379,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G690" t="n">
-        <v>2.57560229301453</v>
+        <v>2.57560205459595</v>
       </c>
       <c r="H690" t="n">
         <v>1181402</v>
@@ -20408,7 +20408,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G691" t="n">
-        <v>2.49306178092957</v>
+        <v>2.49306154251099</v>
       </c>
       <c r="H691" t="n">
         <v>554383</v>
@@ -20524,7 +20524,7 @@
         <v>3.03200006484985</v>
       </c>
       <c r="G695" t="n">
-        <v>2.55370378494263</v>
+        <v>2.55370354652405</v>
       </c>
       <c r="H695" t="n">
         <v>176181</v>
@@ -20640,7 +20640,7 @@
         <v>3.06800007820129</v>
       </c>
       <c r="G699" t="n">
-        <v>2.58402466773987</v>
+        <v>2.58402490615845</v>
       </c>
       <c r="H699" t="n">
         <v>565902</v>
@@ -20872,7 +20872,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G707" t="n">
-        <v>2.58570909500122</v>
+        <v>2.5857093334198</v>
       </c>
       <c r="H707" t="n">
         <v>503676</v>
@@ -20959,7 +20959,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G710" t="n">
-        <v>2.50990653038025</v>
+        <v>2.50990676879883</v>
       </c>
       <c r="H710" t="n">
         <v>1933202</v>
@@ -20988,7 +20988,7 @@
         <v>3.01399993896484</v>
       </c>
       <c r="G711" t="n">
-        <v>2.53854298591614</v>
+        <v>2.53854322433472</v>
       </c>
       <c r="H711" t="n">
         <v>357710</v>
@@ -21017,7 +21017,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G712" t="n">
-        <v>2.50990653038025</v>
+        <v>2.50990676879883</v>
       </c>
       <c r="H712" t="n">
         <v>660930</v>
@@ -21075,7 +21075,7 @@
         <v>2.91400003433228</v>
       </c>
       <c r="G714" t="n">
-        <v>2.45431804656982</v>
+        <v>2.4543182849884</v>
       </c>
       <c r="H714" t="n">
         <v>482372</v>
@@ -21162,7 +21162,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G717" t="n">
-        <v>2.45600247383118</v>
+        <v>2.45600271224976</v>
       </c>
       <c r="H717" t="n">
         <v>519899</v>
@@ -21423,7 +21423,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G726" t="n">
-        <v>2.44926476478577</v>
+        <v>2.44926452636719</v>
       </c>
       <c r="H726" t="n">
         <v>2315220</v>
@@ -21655,7 +21655,7 @@
         <v>2.79200005531311</v>
       </c>
       <c r="G734" t="n">
-        <v>2.3515636920929</v>
+        <v>2.35156345367432</v>
       </c>
       <c r="H734" t="n">
         <v>407635</v>
@@ -21684,7 +21684,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G735" t="n">
-        <v>2.41389012336731</v>
+        <v>2.41388988494873</v>
       </c>
       <c r="H735" t="n">
         <v>672584</v>
@@ -21887,7 +21887,7 @@
         <v>3.04200005531311</v>
       </c>
       <c r="G742" t="n">
-        <v>2.56212615966797</v>
+        <v>2.56212639808655</v>
       </c>
       <c r="H742" t="n">
         <v>920296</v>
@@ -22003,7 +22003,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G746" t="n">
-        <v>2.48295474052429</v>
+        <v>2.48295450210571</v>
       </c>
       <c r="H746" t="n">
         <v>959673</v>
@@ -22177,7 +22177,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>2.49306178092957</v>
+        <v>2.49306154251099</v>
       </c>
       <c r="H752" t="n">
         <v>229054</v>
@@ -22293,7 +22293,7 @@
         <v>3.01399993896484</v>
       </c>
       <c r="G756" t="n">
-        <v>2.53854298591614</v>
+        <v>2.53854322433472</v>
       </c>
       <c r="H756" t="n">
         <v>339559</v>
@@ -22380,7 +22380,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G759" t="n">
-        <v>2.48295474052429</v>
+        <v>2.48295450210571</v>
       </c>
       <c r="H759" t="n">
         <v>299028</v>
@@ -22467,7 +22467,7 @@
         <v>3.03399991989136</v>
       </c>
       <c r="G762" t="n">
-        <v>2.55538821220398</v>
+        <v>2.5553879737854</v>
       </c>
       <c r="H762" t="n">
         <v>577970</v>
@@ -22583,7 +22583,7 @@
         <v>3.09599995613098</v>
       </c>
       <c r="G766" t="n">
-        <v>2.60760760307312</v>
+        <v>2.6076078414917</v>
       </c>
       <c r="H766" t="n">
         <v>954705</v>
@@ -22612,7 +22612,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G767" t="n">
-        <v>2.57728672027588</v>
+        <v>2.5772864818573</v>
       </c>
       <c r="H767" t="n">
         <v>598686</v>
@@ -22670,7 +22670,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G769" t="n">
-        <v>2.57560229301453</v>
+        <v>2.57560205459595</v>
       </c>
       <c r="H769" t="n">
         <v>237570</v>
@@ -22699,7 +22699,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G770" t="n">
-        <v>2.57223296165466</v>
+        <v>2.57223320007324</v>
       </c>
       <c r="H770" t="n">
         <v>235087</v>
@@ -22728,7 +22728,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G771" t="n">
-        <v>2.5890781879425</v>
+        <v>2.58907794952393</v>
       </c>
       <c r="H771" t="n">
         <v>233031</v>
@@ -22815,7 +22815,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G774" t="n">
-        <v>2.67835664749146</v>
+        <v>2.67835688591003</v>
       </c>
       <c r="H774" t="n">
         <v>844822</v>
@@ -22844,7 +22844,7 @@
         <v>3.14199995994568</v>
       </c>
       <c r="G775" t="n">
-        <v>2.64635133743286</v>
+        <v>2.64635109901428</v>
       </c>
       <c r="H775" t="n">
         <v>1054352</v>
@@ -22931,7 +22931,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G778" t="n">
-        <v>2.7171003818512</v>
+        <v>2.71710014343262</v>
       </c>
       <c r="H778" t="n">
         <v>964874</v>
@@ -22960,7 +22960,7 @@
         <v>3.20600008964539</v>
       </c>
       <c r="G779" t="n">
-        <v>2.70025515556335</v>
+        <v>2.70025539398193</v>
       </c>
       <c r="H779" t="n">
         <v>409180</v>
@@ -23076,7 +23076,7 @@
         <v>3.20600008964539</v>
       </c>
       <c r="G783" t="n">
-        <v>2.70025515556335</v>
+        <v>2.70025539398193</v>
       </c>
       <c r="H783" t="n">
         <v>938332</v>
@@ -23105,7 +23105,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G784" t="n">
-        <v>2.7171003818512</v>
+        <v>2.71710014343262</v>
       </c>
       <c r="H784" t="n">
         <v>578855</v>
@@ -23250,7 +23250,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G789" t="n">
-        <v>2.84680676460266</v>
+        <v>2.84680700302124</v>
       </c>
       <c r="H789" t="n">
         <v>815915</v>
@@ -23395,7 +23395,7 @@
         <v>3.14199995994568</v>
       </c>
       <c r="G794" t="n">
-        <v>2.64635133743286</v>
+        <v>2.64635109901428</v>
       </c>
       <c r="H794" t="n">
         <v>768072</v>
@@ -23627,7 +23627,7 @@
         <v>3.36800003051758</v>
       </c>
       <c r="G802" t="n">
-        <v>2.83669996261597</v>
+        <v>2.83669972419739</v>
       </c>
       <c r="H802" t="n">
         <v>706988</v>
@@ -23714,7 +23714,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G805" t="n">
-        <v>2.93776965141296</v>
+        <v>2.93776988983154</v>
       </c>
       <c r="H805" t="n">
         <v>557350</v>
@@ -23975,7 +23975,7 @@
         <v>3.38800001144409</v>
       </c>
       <c r="G814" t="n">
-        <v>2.85354471206665</v>
+        <v>2.85354495048523</v>
       </c>
       <c r="H814" t="n">
         <v>347337</v>
@@ -24091,7 +24091,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G818" t="n">
-        <v>2.45600247383118</v>
+        <v>2.45600271224976</v>
       </c>
       <c r="H818" t="n">
         <v>1497205</v>
@@ -24120,7 +24120,7 @@
         <v>3.00600004196167</v>
       </c>
       <c r="G819" t="n">
-        <v>2.53180503845215</v>
+        <v>2.53180527687073</v>
       </c>
       <c r="H819" t="n">
         <v>790572</v>
@@ -24526,7 +24526,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G833" t="n">
-        <v>2.69183278083801</v>
+        <v>2.69183301925659</v>
       </c>
       <c r="H833" t="n">
         <v>488767</v>
@@ -24555,7 +24555,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G834" t="n">
-        <v>2.67835664749146</v>
+        <v>2.67835688591003</v>
       </c>
       <c r="H834" t="n">
         <v>708286</v>
@@ -24584,7 +24584,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G835" t="n">
-        <v>2.65814280509949</v>
+        <v>2.65814256668091</v>
       </c>
       <c r="H835" t="n">
         <v>524048</v>
@@ -24642,7 +24642,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G837" t="n">
-        <v>2.67835664749146</v>
+        <v>2.67835688591003</v>
       </c>
       <c r="H837" t="n">
         <v>361053</v>
@@ -24700,7 +24700,7 @@
         <v>3.25</v>
       </c>
       <c r="G839" t="n">
-        <v>2.73731422424316</v>
+        <v>2.73731446266174</v>
       </c>
       <c r="H839" t="n">
         <v>461413</v>
@@ -24816,7 +24816,7 @@
         <v>3.25</v>
       </c>
       <c r="G843" t="n">
-        <v>2.73731422424316</v>
+        <v>2.73731446266174</v>
       </c>
       <c r="H843" t="n">
         <v>565490</v>
@@ -24961,7 +24961,7 @@
         <v>3.33599996566772</v>
       </c>
       <c r="G848" t="n">
-        <v>2.80974769592285</v>
+        <v>2.80974793434143</v>
       </c>
       <c r="H848" t="n">
         <v>1117559</v>
@@ -25251,7 +25251,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G858" t="n">
-        <v>2.79795622825623</v>
+        <v>2.7979564666748</v>
       </c>
       <c r="H858" t="n">
         <v>402306</v>
@@ -25338,7 +25338,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G861" t="n">
-        <v>2.78784918785095</v>
+        <v>2.78784942626953</v>
       </c>
       <c r="H861" t="n">
         <v>436318</v>
@@ -25483,7 +25483,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G866" t="n">
-        <v>2.68677949905396</v>
+        <v>2.68677926063538</v>
       </c>
       <c r="H866" t="n">
         <v>1350411</v>
@@ -25541,7 +25541,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G868" t="n">
-        <v>2.65814280509949</v>
+        <v>2.65814256668091</v>
       </c>
       <c r="H868" t="n">
         <v>1567922</v>
@@ -35465,6 +35465,35 @@
         <v>1474425</v>
       </c>
       <c r="I1210" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1211" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1211" t="n">
+        <v>2.08400011062622</v>
+      </c>
+      <c r="D1211" t="n">
+        <v>2.10800004005432</v>
+      </c>
+      <c r="E1211" t="n">
+        <v>2.08200001716614</v>
+      </c>
+      <c r="F1211" t="n">
+        <v>2.08200001716614</v>
+      </c>
+      <c r="G1211" t="n">
+        <v>2.08200001716614</v>
+      </c>
+      <c r="H1211" t="n">
+        <v>1362738</v>
+      </c>
+      <c r="I1211" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MFEA.MI.xlsx
+++ b/data/MFEA.MI.xlsx
@@ -456,7 +456,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G3" t="n">
-        <v>2.25027990341187</v>
+        <v>2.25028014183044</v>
       </c>
       <c r="H3" t="n">
         <v>367297</v>
@@ -485,7 +485,7 @@
         <v>3.71250009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>2.28881239891052</v>
+        <v>2.28881216049194</v>
       </c>
       <c r="H4" t="n">
         <v>267411</v>
@@ -514,7 +514,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G5" t="n">
-        <v>2.30884909629822</v>
+        <v>2.30884885787964</v>
       </c>
       <c r="H5" t="n">
         <v>278466</v>
@@ -543,7 +543,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G6" t="n">
-        <v>2.28727102279663</v>
+        <v>2.28727078437805</v>
       </c>
       <c r="H6" t="n">
         <v>214912</v>
@@ -659,7 +659,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>2.33659195899963</v>
+        <v>2.33659219741821</v>
       </c>
       <c r="H10" t="n">
         <v>166086</v>
@@ -746,7 +746,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G13" t="n">
-        <v>2.29343605041504</v>
+        <v>2.29343628883362</v>
       </c>
       <c r="H13" t="n">
         <v>85603</v>
@@ -775,7 +775,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G14" t="n">
-        <v>2.23178458213806</v>
+        <v>2.23178434371948</v>
       </c>
       <c r="H14" t="n">
         <v>244637</v>
@@ -804,7 +804,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G15" t="n">
-        <v>2.3273446559906</v>
+        <v>2.32734441757202</v>
       </c>
       <c r="H15" t="n">
         <v>370744</v>
@@ -862,7 +862,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G17" t="n">
-        <v>2.6941704750061</v>
+        <v>2.69417095184326</v>
       </c>
       <c r="H17" t="n">
         <v>431766</v>
@@ -891,7 +891,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G18" t="n">
-        <v>2.66951012611389</v>
+        <v>2.66951036453247</v>
       </c>
       <c r="H18" t="n">
         <v>629452</v>
@@ -949,7 +949,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G20" t="n">
-        <v>2.61710643768311</v>
+        <v>2.61710619926453</v>
       </c>
       <c r="H20" t="n">
         <v>162925</v>
@@ -1065,7 +1065,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G24" t="n">
-        <v>2.42598676681519</v>
+        <v>2.42598652839661</v>
       </c>
       <c r="H24" t="n">
         <v>208426</v>
@@ -1094,7 +1094,7 @@
         <v>3.99499988555908</v>
       </c>
       <c r="G25" t="n">
-        <v>2.46297740936279</v>
+        <v>2.46297764778137</v>
       </c>
       <c r="H25" t="n">
         <v>109853</v>
@@ -1123,7 +1123,7 @@
         <v>3.94250011444092</v>
       </c>
       <c r="G26" t="n">
-        <v>2.43061065673828</v>
+        <v>2.43061089515686</v>
       </c>
       <c r="H26" t="n">
         <v>264886</v>
@@ -1152,7 +1152,7 @@
         <v>3.98250007629395</v>
       </c>
       <c r="G27" t="n">
-        <v>2.45527148246765</v>
+        <v>2.45527124404907</v>
       </c>
       <c r="H27" t="n">
         <v>73167</v>
@@ -1239,7 +1239,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G30" t="n">
-        <v>2.41365671157837</v>
+        <v>2.41365647315979</v>
       </c>
       <c r="H30" t="n">
         <v>227564</v>
@@ -1268,7 +1268,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G31" t="n">
-        <v>2.40440893173218</v>
+        <v>2.4044086933136</v>
       </c>
       <c r="H31" t="n">
         <v>128224</v>
@@ -1297,7 +1297,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G32" t="n">
-        <v>2.25336241722107</v>
+        <v>2.25336265563965</v>
       </c>
       <c r="H32" t="n">
         <v>156121</v>
@@ -1326,7 +1326,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G33" t="n">
-        <v>2.21945428848267</v>
+        <v>2.21945405006409</v>
       </c>
       <c r="H33" t="n">
         <v>419876</v>
@@ -1355,7 +1355,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G34" t="n">
-        <v>2.29343605041504</v>
+        <v>2.29343628883362</v>
       </c>
       <c r="H34" t="n">
         <v>612514</v>
@@ -1442,7 +1442,7 @@
         <v>4.14249992370605</v>
       </c>
       <c r="G37" t="n">
-        <v>2.55391359329224</v>
+        <v>2.55391383171082</v>
       </c>
       <c r="H37" t="n">
         <v>310291</v>
@@ -1471,7 +1471,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G38" t="n">
-        <v>2.58936309814453</v>
+        <v>2.58936333656311</v>
       </c>
       <c r="H38" t="n">
         <v>208860</v>
@@ -1500,7 +1500,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G39" t="n">
-        <v>2.58936309814453</v>
+        <v>2.58936333656311</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -1558,7 +1558,7 @@
         <v>3.5</v>
       </c>
       <c r="G41" t="n">
-        <v>2.15780258178711</v>
+        <v>2.15780282020569</v>
       </c>
       <c r="H41" t="n">
         <v>1105386</v>
@@ -1732,7 +1732,7 @@
         <v>3.26749992370605</v>
       </c>
       <c r="G47" t="n">
-        <v>2.01446294784546</v>
+        <v>2.01446318626404</v>
       </c>
       <c r="H47" t="n">
         <v>127552</v>
@@ -1761,7 +1761,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G48" t="n">
-        <v>2.03141689300537</v>
+        <v>2.03141713142395</v>
       </c>
       <c r="H48" t="n">
         <v>198901</v>
@@ -1877,7 +1877,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G52" t="n">
-        <v>1.99442613124847</v>
+        <v>1.99442625045776</v>
       </c>
       <c r="H52" t="n">
         <v>186459</v>
@@ -1906,7 +1906,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G53" t="n">
-        <v>1.97593092918396</v>
+        <v>1.97593080997467</v>
       </c>
       <c r="H53" t="n">
         <v>157204</v>
@@ -1964,7 +1964,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G55" t="n">
-        <v>1.82796692848206</v>
+        <v>1.82796716690063</v>
       </c>
       <c r="H55" t="n">
         <v>452826</v>
@@ -2022,7 +2022,7 @@
         <v>3</v>
       </c>
       <c r="G57" t="n">
-        <v>1.84954500198364</v>
+        <v>1.84954524040222</v>
       </c>
       <c r="H57" t="n">
         <v>234992</v>
@@ -2051,7 +2051,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G58" t="n">
-        <v>1.82488453388214</v>
+        <v>1.82488465309143</v>
       </c>
       <c r="H58" t="n">
         <v>168347</v>
@@ -2080,7 +2080,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G59" t="n">
-        <v>1.79405903816223</v>
+        <v>1.79405879974365</v>
       </c>
       <c r="H59" t="n">
         <v>174796</v>
@@ -2109,7 +2109,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G60" t="n">
-        <v>1.79714131355286</v>
+        <v>1.79714143276215</v>
       </c>
       <c r="H60" t="n">
         <v>140935</v>
@@ -2138,7 +2138,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G61" t="n">
-        <v>1.80638909339905</v>
+        <v>1.80638933181763</v>
       </c>
       <c r="H61" t="n">
         <v>175025</v>
@@ -2167,7 +2167,7 @@
         <v>2.96250009536743</v>
       </c>
       <c r="G62" t="n">
-        <v>1.82642602920532</v>
+        <v>1.82642614841461</v>
       </c>
       <c r="H62" t="n">
         <v>167649</v>
@@ -2196,7 +2196,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G63" t="n">
-        <v>1.81255435943604</v>
+        <v>1.81255447864532</v>
       </c>
       <c r="H63" t="n">
         <v>134826</v>
@@ -2254,7 +2254,7 @@
         <v>2.89249992370605</v>
       </c>
       <c r="G65" t="n">
-        <v>1.78326988220215</v>
+        <v>1.78326976299286</v>
       </c>
       <c r="H65" t="n">
         <v>336035</v>
@@ -2312,7 +2312,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G67" t="n">
-        <v>1.69233357906342</v>
+        <v>1.69233381748199</v>
       </c>
       <c r="H67" t="n">
         <v>293953</v>
@@ -2341,7 +2341,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G68" t="n">
-        <v>1.66150808334351</v>
+        <v>1.6615082025528</v>
       </c>
       <c r="H68" t="n">
         <v>213075</v>
@@ -2399,7 +2399,7 @@
         <v>2.92750000953674</v>
       </c>
       <c r="G70" t="n">
-        <v>1.80484759807587</v>
+        <v>1.80484795570374</v>
       </c>
       <c r="H70" t="n">
         <v>1271038</v>
@@ -2457,7 +2457,7 @@
         <v>2.88750004768372</v>
       </c>
       <c r="G72" t="n">
-        <v>1.78018736839294</v>
+        <v>1.78018724918365</v>
       </c>
       <c r="H72" t="n">
         <v>202748</v>
@@ -2486,7 +2486,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G73" t="n">
-        <v>1.74165523052216</v>
+        <v>1.74165511131287</v>
       </c>
       <c r="H73" t="n">
         <v>228203</v>
@@ -2515,7 +2515,7 @@
         <v>2.75</v>
       </c>
       <c r="G74" t="n">
-        <v>1.69541621208191</v>
+        <v>1.69541645050049</v>
       </c>
       <c r="H74" t="n">
         <v>168732</v>
@@ -2544,7 +2544,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G75" t="n">
-        <v>1.66150808334351</v>
+        <v>1.6615082025528</v>
       </c>
       <c r="H75" t="n">
         <v>331684</v>
@@ -2573,7 +2573,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G76" t="n">
-        <v>1.63376486301422</v>
+        <v>1.6337651014328</v>
       </c>
       <c r="H76" t="n">
         <v>246997</v>
@@ -2631,7 +2631,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G78" t="n">
-        <v>1.74782013893127</v>
+        <v>1.74782037734985</v>
       </c>
       <c r="H78" t="n">
         <v>522442</v>
@@ -2660,7 +2660,7 @@
         <v>2.66750001907349</v>
       </c>
       <c r="G79" t="n">
-        <v>1.64455389976501</v>
+        <v>1.6445540189743</v>
       </c>
       <c r="H79" t="n">
         <v>468659</v>
@@ -2834,7 +2834,7 @@
         <v>2.58750009536743</v>
       </c>
       <c r="G85" t="n">
-        <v>1.59523284435272</v>
+        <v>1.59523272514343</v>
       </c>
       <c r="H85" t="n">
         <v>241301</v>
@@ -2892,7 +2892,7 @@
         <v>2.50250005722046</v>
       </c>
       <c r="G87" t="n">
-        <v>1.54282903671265</v>
+        <v>1.54282891750336</v>
       </c>
       <c r="H87" t="n">
         <v>224920</v>
@@ -2921,7 +2921,7 @@
         <v>2.64750003814697</v>
       </c>
       <c r="G88" t="n">
-        <v>1.63222372531891</v>
+        <v>1.6322238445282</v>
       </c>
       <c r="H88" t="n">
         <v>842562</v>
@@ -3008,7 +3008,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>1.67075598239899</v>
+        <v>1.6707558631897</v>
       </c>
       <c r="H91" t="n">
         <v>530043</v>
@@ -3037,7 +3037,7 @@
         <v>2.66750001907349</v>
       </c>
       <c r="G92" t="n">
-        <v>1.64455389976501</v>
+        <v>1.6445540189743</v>
       </c>
       <c r="H92" t="n">
         <v>384701</v>
@@ -3095,7 +3095,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G94" t="n">
-        <v>1.63993012905121</v>
+        <v>1.6399302482605</v>
       </c>
       <c r="H94" t="n">
         <v>124415</v>
@@ -3153,7 +3153,7 @@
         <v>2.6324999332428</v>
       </c>
       <c r="G96" t="n">
-        <v>1.62297594547272</v>
+        <v>1.62297582626343</v>
       </c>
       <c r="H96" t="n">
         <v>316690</v>
@@ -3182,7 +3182,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G97" t="n">
-        <v>1.57827842235565</v>
+        <v>1.57827854156494</v>
       </c>
       <c r="H97" t="n">
         <v>975446</v>
@@ -3240,7 +3240,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>1.60602164268494</v>
+        <v>1.60602176189423</v>
       </c>
       <c r="H99" t="n">
         <v>524697</v>
@@ -3269,7 +3269,7 @@
         <v>2.45300006866455</v>
       </c>
       <c r="G100" t="n">
-        <v>1.51231145858765</v>
+        <v>1.51231157779694</v>
       </c>
       <c r="H100" t="n">
         <v>588672</v>
@@ -3298,7 +3298,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G101" t="n">
-        <v>1.4549754858017</v>
+        <v>1.45497560501099</v>
       </c>
       <c r="H101" t="n">
         <v>241430</v>
@@ -3327,7 +3327,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G102" t="n">
-        <v>1.47716999053955</v>
+        <v>1.47717010974884</v>
       </c>
       <c r="H102" t="n">
         <v>189949</v>
@@ -3356,7 +3356,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G103" t="n">
-        <v>1.45867455005646</v>
+        <v>1.45867466926575</v>
       </c>
       <c r="H103" t="n">
         <v>277983</v>
@@ -3414,7 +3414,7 @@
         <v>2.25699996948242</v>
       </c>
       <c r="G105" t="n">
-        <v>1.39147448539734</v>
+        <v>1.39147460460663</v>
       </c>
       <c r="H105" t="n">
         <v>153134</v>
@@ -3443,7 +3443,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G106" t="n">
-        <v>1.39085793495178</v>
+        <v>1.39085781574249</v>
       </c>
       <c r="H106" t="n">
         <v>262719</v>
@@ -3472,7 +3472,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>1.33475506305695</v>
+        <v>1.33475518226624</v>
       </c>
       <c r="H107" t="n">
         <v>364496</v>
@@ -3559,7 +3559,7 @@
         <v>2.14199995994568</v>
       </c>
       <c r="G110" t="n">
-        <v>1.32057535648346</v>
+        <v>1.32057523727417</v>
       </c>
       <c r="H110" t="n">
         <v>256397</v>
@@ -3588,7 +3588,7 @@
         <v>2.18899989128113</v>
       </c>
       <c r="G111" t="n">
-        <v>1.34955143928528</v>
+        <v>1.34955132007599</v>
       </c>
       <c r="H111" t="n">
         <v>386160</v>
@@ -3617,7 +3617,7 @@
         <v>2.24900007247925</v>
       </c>
       <c r="G112" t="n">
-        <v>1.38654243946075</v>
+        <v>1.38654232025146</v>
       </c>
       <c r="H112" t="n">
         <v>617377</v>
@@ -3704,7 +3704,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G115" t="n">
-        <v>1.36558079719543</v>
+        <v>1.36558091640472</v>
       </c>
       <c r="H115" t="n">
         <v>684447</v>
@@ -3791,7 +3791,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G118" t="n">
-        <v>1.34708523750305</v>
+        <v>1.34708547592163</v>
       </c>
       <c r="H118" t="n">
         <v>844960</v>
@@ -3878,7 +3878,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G121" t="n">
-        <v>1.40565431118011</v>
+        <v>1.4056544303894</v>
       </c>
       <c r="H121" t="n">
         <v>1163100</v>
@@ -3907,7 +3907,7 @@
         <v>2.22099995613098</v>
       </c>
       <c r="G122" t="n">
-        <v>1.36927998065948</v>
+        <v>1.3692798614502</v>
       </c>
       <c r="H122" t="n">
         <v>2110801</v>
@@ -3936,7 +3936,7 @@
         <v>2.18300008773804</v>
       </c>
       <c r="G123" t="n">
-        <v>1.34585225582123</v>
+        <v>1.34585249423981</v>
       </c>
       <c r="H123" t="n">
         <v>1057822</v>
@@ -3965,7 +3965,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G124" t="n">
-        <v>1.27125406265259</v>
+        <v>1.27125418186188</v>
       </c>
       <c r="H124" t="n">
         <v>589312</v>
@@ -3994,7 +3994,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G125" t="n">
-        <v>1.23919522762299</v>
+        <v>1.23919534683228</v>
       </c>
       <c r="H125" t="n">
         <v>572938</v>
@@ -4052,7 +4052,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G127" t="n">
-        <v>1.33043956756592</v>
+        <v>1.33043944835663</v>
       </c>
       <c r="H127" t="n">
         <v>576146</v>
@@ -4081,7 +4081,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G128" t="n">
-        <v>1.35325050354004</v>
+        <v>1.35325062274933</v>
       </c>
       <c r="H128" t="n">
         <v>1234804</v>
@@ -4168,7 +4168,7 @@
         <v>2.21399998664856</v>
       </c>
       <c r="G131" t="n">
-        <v>1.36496436595917</v>
+        <v>1.36496424674988</v>
       </c>
       <c r="H131" t="n">
         <v>425795</v>
@@ -4197,7 +4197,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G132" t="n">
-        <v>1.29468154907227</v>
+        <v>1.29468166828156</v>
       </c>
       <c r="H132" t="n">
         <v>903030</v>
@@ -4226,7 +4226,7 @@
         <v>2.02699995040894</v>
       </c>
       <c r="G133" t="n">
-        <v>1.249675989151</v>
+        <v>1.24967610836029</v>
       </c>
       <c r="H133" t="n">
         <v>1799201</v>
@@ -4255,7 +4255,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>1.28543400764465</v>
+        <v>1.28543388843536</v>
       </c>
       <c r="H134" t="n">
         <v>1315577</v>
@@ -4371,7 +4371,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G138" t="n">
-        <v>1.32304120063782</v>
+        <v>1.32304131984711</v>
       </c>
       <c r="H138" t="n">
         <v>662539</v>
@@ -4458,7 +4458,7 @@
         <v>2.08400011062622</v>
       </c>
       <c r="G141" t="n">
-        <v>1.2848174571991</v>
+        <v>1.28481733798981</v>
       </c>
       <c r="H141" t="n">
         <v>2061793</v>
@@ -4487,7 +4487,7 @@
         <v>2.125</v>
       </c>
       <c r="G142" t="n">
-        <v>1.31009459495544</v>
+        <v>1.31009447574615</v>
       </c>
       <c r="H142" t="n">
         <v>1089881</v>
@@ -4516,7 +4516,7 @@
         <v>2.19099998474121</v>
       </c>
       <c r="G143" t="n">
-        <v>1.35078454017639</v>
+        <v>1.3507844209671</v>
       </c>
       <c r="H143" t="n">
         <v>662529</v>
@@ -4545,7 +4545,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G144" t="n">
-        <v>1.35386717319489</v>
+        <v>1.35386729240417</v>
       </c>
       <c r="H144" t="n">
         <v>698399</v>
@@ -4574,7 +4574,7 @@
         <v>2.30900001525879</v>
       </c>
       <c r="G145" t="n">
-        <v>1.42353308200836</v>
+        <v>1.42353343963623</v>
       </c>
       <c r="H145" t="n">
         <v>1061376</v>
@@ -4603,7 +4603,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G146" t="n">
-        <v>1.4025719165802</v>
+        <v>1.40257179737091</v>
       </c>
       <c r="H146" t="n">
         <v>463835</v>
@@ -4632,7 +4632,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G147" t="n">
-        <v>1.35325050354004</v>
+        <v>1.35325062274933</v>
       </c>
       <c r="H147" t="n">
         <v>729575</v>
@@ -4661,7 +4661,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G148" t="n">
-        <v>1.35633301734924</v>
+        <v>1.35633325576782</v>
       </c>
       <c r="H148" t="n">
         <v>470520</v>
@@ -4719,7 +4719,7 @@
         <v>2.04699993133545</v>
       </c>
       <c r="G150" t="n">
-        <v>1.2620062828064</v>
+        <v>1.26200640201569</v>
       </c>
       <c r="H150" t="n">
         <v>1302379</v>
@@ -4806,7 +4806,7 @@
         <v>2.02099990844727</v>
       </c>
       <c r="G153" t="n">
-        <v>1.24597692489624</v>
+        <v>1.24597680568695</v>
       </c>
       <c r="H153" t="n">
         <v>550560</v>
@@ -4864,7 +4864,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G155" t="n">
-        <v>1.28235137462616</v>
+        <v>1.28235125541687</v>
       </c>
       <c r="H155" t="n">
         <v>897371</v>
@@ -5067,7 +5067,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G162" t="n">
-        <v>1.28235137462616</v>
+        <v>1.28235125541687</v>
       </c>
       <c r="H162" t="n">
         <v>320464</v>
@@ -5096,7 +5096,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G163" t="n">
-        <v>1.28235137462616</v>
+        <v>1.28235125541687</v>
       </c>
       <c r="H163" t="n">
         <v>665085</v>
@@ -5183,7 +5183,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G166" t="n">
-        <v>1.28543400764465</v>
+        <v>1.28543388843536</v>
       </c>
       <c r="H166" t="n">
         <v>925875</v>
@@ -5270,7 +5270,7 @@
         <v>1.99899995326996</v>
       </c>
       <c r="G169" t="n">
-        <v>1.23241353034973</v>
+        <v>1.23241364955902</v>
       </c>
       <c r="H169" t="n">
         <v>2003498</v>
@@ -5328,7 +5328,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G171" t="n">
-        <v>1.20140945911407</v>
+        <v>1.20140957832336</v>
       </c>
       <c r="H171" t="n">
         <v>1719560</v>
@@ -5357,7 +5357,7 @@
         <v>1.68299996852875</v>
       </c>
       <c r="G172" t="n">
-        <v>1.18590748310089</v>
+        <v>1.1859073638916</v>
       </c>
       <c r="H172" t="n">
         <v>1157709</v>
@@ -5386,7 +5386,7 @@
         <v>1.65199995040894</v>
       </c>
       <c r="G173" t="n">
-        <v>1.16406357288361</v>
+        <v>1.16406345367432</v>
       </c>
       <c r="H173" t="n">
         <v>1205156</v>
@@ -5473,7 +5473,7 @@
         <v>1.53900003433228</v>
       </c>
       <c r="G176" t="n">
-        <v>1.0844395160675</v>
+        <v>1.08443939685822</v>
       </c>
       <c r="H176" t="n">
         <v>1625041</v>
@@ -5560,7 +5560,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G179" t="n">
-        <v>1.064004778862</v>
+        <v>1.06400489807129</v>
       </c>
       <c r="H179" t="n">
         <v>1582704</v>
@@ -5647,7 +5647,7 @@
         <v>1.54700005054474</v>
       </c>
       <c r="G182" t="n">
-        <v>1.09007668495178</v>
+        <v>1.09007656574249</v>
       </c>
       <c r="H182" t="n">
         <v>808303</v>
@@ -5676,7 +5676,7 @@
         <v>1.557000041008</v>
       </c>
       <c r="G183" t="n">
-        <v>1.09712302684784</v>
+        <v>1.09712290763855</v>
       </c>
       <c r="H183" t="n">
         <v>1335356</v>
@@ -5734,7 +5734,7 @@
         <v>1.50899994373322</v>
       </c>
       <c r="G185" t="n">
-        <v>1.06330025196075</v>
+        <v>1.06330013275146</v>
       </c>
       <c r="H185" t="n">
         <v>762123</v>
@@ -5908,7 +5908,7 @@
         <v>1.63699996471405</v>
       </c>
       <c r="G191" t="n">
-        <v>1.15349411964417</v>
+        <v>1.15349400043488</v>
       </c>
       <c r="H191" t="n">
         <v>1020050</v>
@@ -5937,7 +5937,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G192" t="n">
-        <v>1.14715230464935</v>
+        <v>1.14715242385864</v>
       </c>
       <c r="H192" t="n">
         <v>1257403</v>
@@ -6024,7 +6024,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G195" t="n">
-        <v>1.16265439987183</v>
+        <v>1.16265428066254</v>
       </c>
       <c r="H195" t="n">
         <v>1118932</v>
@@ -6053,7 +6053,7 @@
         <v>1.68900001049042</v>
       </c>
       <c r="G196" t="n">
-        <v>1.1901353597641</v>
+        <v>1.19013524055481</v>
       </c>
       <c r="H196" t="n">
         <v>693474</v>
@@ -6198,7 +6198,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G201" t="n">
-        <v>1.2577805519104</v>
+        <v>1.25778067111969</v>
       </c>
       <c r="H201" t="n">
         <v>515449</v>
@@ -6285,7 +6285,7 @@
         <v>1.74699997901917</v>
       </c>
       <c r="G204" t="n">
-        <v>1.23100423812866</v>
+        <v>1.23100435733795</v>
       </c>
       <c r="H204" t="n">
         <v>658672</v>
@@ -6314,7 +6314,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G205" t="n">
-        <v>1.30499148368835</v>
+        <v>1.30499136447906</v>
       </c>
       <c r="H205" t="n">
         <v>1053905</v>
@@ -6488,7 +6488,7 @@
         <v>1.87100005149841</v>
       </c>
       <c r="G211" t="n">
-        <v>1.31837952136993</v>
+        <v>1.31837964057922</v>
       </c>
       <c r="H211" t="n">
         <v>796652</v>
@@ -6546,7 +6546,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G213" t="n">
-        <v>1.28737545013428</v>
+        <v>1.28737556934357</v>
       </c>
       <c r="H213" t="n">
         <v>677501</v>
@@ -6633,7 +6633,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G216" t="n">
-        <v>1.2859662771225</v>
+        <v>1.28596615791321</v>
       </c>
       <c r="H216" t="n">
         <v>274038</v>
@@ -6662,7 +6662,7 @@
         <v>1.87100005149841</v>
       </c>
       <c r="G217" t="n">
-        <v>1.31837952136993</v>
+        <v>1.31837964057922</v>
       </c>
       <c r="H217" t="n">
         <v>596050</v>
@@ -6691,7 +6691,7 @@
         <v>2.01900005340576</v>
       </c>
       <c r="G218" t="n">
-        <v>1.42266619205475</v>
+        <v>1.42266607284546</v>
       </c>
       <c r="H218" t="n">
         <v>2210201</v>
@@ -6749,7 +6749,7 @@
         <v>2.01900005340576</v>
       </c>
       <c r="G220" t="n">
-        <v>1.42266619205475</v>
+        <v>1.42266607284546</v>
       </c>
       <c r="H220" t="n">
         <v>731881</v>
@@ -6807,7 +6807,7 @@
         <v>2.0090000629425</v>
       </c>
       <c r="G222" t="n">
-        <v>1.41561985015869</v>
+        <v>1.4156197309494</v>
       </c>
       <c r="H222" t="n">
         <v>1297053</v>
@@ -6836,7 +6836,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G223" t="n">
-        <v>1.42618918418884</v>
+        <v>1.42618930339813</v>
       </c>
       <c r="H223" t="n">
         <v>405478</v>
@@ -6865,7 +6865,7 @@
         <v>2.02099990844727</v>
       </c>
       <c r="G224" t="n">
-        <v>1.42407548427582</v>
+        <v>1.42407536506653</v>
       </c>
       <c r="H224" t="n">
         <v>728660</v>
@@ -6894,7 +6894,7 @@
         <v>1.98300004005432</v>
       </c>
       <c r="G225" t="n">
-        <v>1.39729928970337</v>
+        <v>1.39729917049408</v>
       </c>
       <c r="H225" t="n">
         <v>1086938</v>
@@ -7010,7 +7010,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G229" t="n">
-        <v>1.32965385913849</v>
+        <v>1.3296537399292</v>
       </c>
       <c r="H229" t="n">
         <v>305555</v>
@@ -7039,7 +7039,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G230" t="n">
-        <v>1.29442179203033</v>
+        <v>1.29442191123962</v>
       </c>
       <c r="H230" t="n">
         <v>689236</v>
@@ -7097,7 +7097,7 @@
         <v>1.86300003528595</v>
       </c>
       <c r="G232" t="n">
-        <v>1.31274235248566</v>
+        <v>1.31274247169495</v>
       </c>
       <c r="H232" t="n">
         <v>190892</v>
@@ -7126,7 +7126,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G233" t="n">
-        <v>1.27539658546448</v>
+        <v>1.27539646625519</v>
       </c>
       <c r="H233" t="n">
         <v>331881</v>
@@ -7184,7 +7184,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G235" t="n">
-        <v>1.2577805519104</v>
+        <v>1.25778067111969</v>
       </c>
       <c r="H235" t="n">
         <v>235737</v>
@@ -7242,7 +7242,7 @@
         <v>1.82099997997284</v>
       </c>
       <c r="G237" t="n">
-        <v>1.28314769268036</v>
+        <v>1.28314757347107</v>
       </c>
       <c r="H237" t="n">
         <v>406192</v>
@@ -7503,7 +7503,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G246" t="n">
-        <v>1.36277174949646</v>
+        <v>1.36277186870575</v>
       </c>
       <c r="H246" t="n">
         <v>570217</v>
@@ -7590,7 +7590,7 @@
         <v>1.94099998474121</v>
       </c>
       <c r="G249" t="n">
-        <v>1.3677042722702</v>
+        <v>1.36770439147949</v>
       </c>
       <c r="H249" t="n">
         <v>394746</v>
@@ -7677,7 +7677,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G252" t="n">
-        <v>1.35713469982147</v>
+        <v>1.35713481903076</v>
       </c>
       <c r="H252" t="n">
         <v>504498</v>
@@ -7706,7 +7706,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G253" t="n">
-        <v>1.32824456691742</v>
+        <v>1.32824444770813</v>
       </c>
       <c r="H253" t="n">
         <v>496653</v>
@@ -7822,7 +7822,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G257" t="n">
-        <v>1.37052297592163</v>
+        <v>1.37052285671234</v>
       </c>
       <c r="H257" t="n">
         <v>453008</v>
@@ -7880,7 +7880,7 @@
         <v>1.98800003528595</v>
       </c>
       <c r="G259" t="n">
-        <v>1.40082240104675</v>
+        <v>1.40082228183746</v>
       </c>
       <c r="H259" t="n">
         <v>688541</v>
@@ -7909,7 +7909,7 @@
         <v>1.96099996566772</v>
       </c>
       <c r="G260" t="n">
-        <v>1.38179695606232</v>
+        <v>1.3817971944809</v>
       </c>
       <c r="H260" t="n">
         <v>487506</v>
@@ -7996,7 +7996,7 @@
         <v>1.97200000286102</v>
       </c>
       <c r="G263" t="n">
-        <v>1.3895480632782</v>
+        <v>1.38954818248749</v>
       </c>
       <c r="H263" t="n">
         <v>310392</v>
@@ -8025,7 +8025,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G264" t="n">
-        <v>1.40223169326782</v>
+        <v>1.40223157405853</v>
       </c>
       <c r="H264" t="n">
         <v>511622</v>
@@ -8141,7 +8141,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G268" t="n">
-        <v>1.56077539920807</v>
+        <v>1.56077527999878</v>
       </c>
       <c r="H268" t="n">
         <v>856015</v>
@@ -8228,7 +8228,7 @@
         <v>2.18300008773804</v>
       </c>
       <c r="G271" t="n">
-        <v>1.53822696208954</v>
+        <v>1.53822708129883</v>
       </c>
       <c r="H271" t="n">
         <v>558105</v>
@@ -8257,7 +8257,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G272" t="n">
-        <v>1.5332944393158</v>
+        <v>1.53329455852509</v>
       </c>
       <c r="H272" t="n">
         <v>539558</v>
@@ -8286,7 +8286,7 @@
         <v>2.125</v>
       </c>
       <c r="G273" t="n">
-        <v>1.49735796451569</v>
+        <v>1.4973578453064</v>
       </c>
       <c r="H273" t="n">
         <v>544273</v>
@@ -8315,7 +8315,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G274" t="n">
-        <v>1.48678827285767</v>
+        <v>1.48678815364838</v>
       </c>
       <c r="H274" t="n">
         <v>214455</v>
@@ -8344,7 +8344,7 @@
         <v>2.10199999809265</v>
       </c>
       <c r="G275" t="n">
-        <v>1.48115110397339</v>
+        <v>1.48115122318268</v>
       </c>
       <c r="H275" t="n">
         <v>214268</v>
@@ -8663,7 +8663,7 @@
         <v>2.05299997329712</v>
       </c>
       <c r="G286" t="n">
-        <v>1.44662392139435</v>
+        <v>1.44662380218506</v>
       </c>
       <c r="H286" t="n">
         <v>680373</v>
@@ -8692,7 +8692,7 @@
         <v>2.02099990844727</v>
       </c>
       <c r="G287" t="n">
-        <v>1.42407548427582</v>
+        <v>1.42407536506653</v>
       </c>
       <c r="H287" t="n">
         <v>575103</v>
@@ -8721,7 +8721,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G288" t="n">
-        <v>1.43182647228241</v>
+        <v>1.4318265914917</v>
       </c>
       <c r="H288" t="n">
         <v>514101</v>
@@ -8866,7 +8866,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G293" t="n">
-        <v>1.49101614952087</v>
+        <v>1.49101603031158</v>
       </c>
       <c r="H293" t="n">
         <v>500302</v>
@@ -8924,7 +8924,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G295" t="n">
-        <v>1.51074612140656</v>
+        <v>1.51074600219727</v>
       </c>
       <c r="H295" t="n">
         <v>440171</v>
@@ -8953,7 +8953,7 @@
         <v>2.125</v>
       </c>
       <c r="G296" t="n">
-        <v>1.49735796451569</v>
+        <v>1.4973578453064</v>
       </c>
       <c r="H296" t="n">
         <v>636274</v>
@@ -8982,7 +8982,7 @@
         <v>2.12299990653992</v>
       </c>
       <c r="G297" t="n">
-        <v>1.49594843387604</v>
+        <v>1.49594855308533</v>
       </c>
       <c r="H297" t="n">
         <v>507637</v>
@@ -9040,7 +9040,7 @@
         <v>2.11299991607666</v>
       </c>
       <c r="G299" t="n">
-        <v>1.48890197277069</v>
+        <v>1.48890209197998</v>
       </c>
       <c r="H299" t="n">
         <v>234428</v>
@@ -9069,7 +9069,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G300" t="n">
-        <v>1.51215529441833</v>
+        <v>1.51215517520905</v>
       </c>
       <c r="H300" t="n">
         <v>616627</v>
@@ -9127,7 +9127,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G302" t="n">
-        <v>1.52202033996582</v>
+        <v>1.52202022075653</v>
       </c>
       <c r="H302" t="n">
         <v>208214</v>
@@ -9214,7 +9214,7 @@
         <v>2.05599999427795</v>
       </c>
       <c r="G305" t="n">
-        <v>1.44873785972595</v>
+        <v>1.44873774051666</v>
       </c>
       <c r="H305" t="n">
         <v>446308</v>
@@ -9272,7 +9272,7 @@
         <v>2.12299990653992</v>
       </c>
       <c r="G307" t="n">
-        <v>1.49594843387604</v>
+        <v>1.49594855308533</v>
       </c>
       <c r="H307" t="n">
         <v>183000</v>
@@ -9330,7 +9330,7 @@
         <v>2.1029999256134</v>
       </c>
       <c r="G309" t="n">
-        <v>1.48185563087463</v>
+        <v>1.48185586929321</v>
       </c>
       <c r="H309" t="n">
         <v>262297</v>
@@ -9388,7 +9388,7 @@
         <v>2.18300008773804</v>
       </c>
       <c r="G311" t="n">
-        <v>1.53822696208954</v>
+        <v>1.53822708129883</v>
       </c>
       <c r="H311" t="n">
         <v>1223387</v>
@@ -9475,7 +9475,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G314" t="n">
-        <v>1.59600746631622</v>
+        <v>1.59600734710693</v>
       </c>
       <c r="H314" t="n">
         <v>377668</v>
@@ -9533,7 +9533,7 @@
         <v>2.27300000190735</v>
       </c>
       <c r="G316" t="n">
-        <v>1.60164439678192</v>
+        <v>1.60164451599121</v>
       </c>
       <c r="H316" t="n">
         <v>370098</v>
@@ -9562,7 +9562,7 @@
         <v>2.27300000190735</v>
       </c>
       <c r="G317" t="n">
-        <v>1.60164439678192</v>
+        <v>1.60164451599121</v>
       </c>
       <c r="H317" t="n">
         <v>460584</v>
@@ -9649,7 +9649,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G320" t="n">
-        <v>1.62489759922028</v>
+        <v>1.62489748001099</v>
       </c>
       <c r="H320" t="n">
         <v>946396</v>
@@ -9678,7 +9678,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G321" t="n">
-        <v>1.63758087158203</v>
+        <v>1.63758099079132</v>
       </c>
       <c r="H321" t="n">
         <v>897308</v>
@@ -9707,7 +9707,7 @@
         <v>2.27699995040894</v>
       </c>
       <c r="G322" t="n">
-        <v>1.60446298122406</v>
+        <v>1.60446286201477</v>
       </c>
       <c r="H322" t="n">
         <v>327351</v>
@@ -9823,7 +9823,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G326" t="n">
-        <v>1.51074612140656</v>
+        <v>1.51074600219727</v>
       </c>
       <c r="H326" t="n">
         <v>964268</v>
@@ -9852,7 +9852,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G327" t="n">
-        <v>1.47128617763519</v>
+        <v>1.47128629684448</v>
       </c>
       <c r="H327" t="n">
         <v>1679948</v>
@@ -9939,7 +9939,7 @@
         <v>2.19899988174438</v>
       </c>
       <c r="G330" t="n">
-        <v>1.5495011806488</v>
+        <v>1.54950106143951</v>
       </c>
       <c r="H330" t="n">
         <v>398017</v>
@@ -9968,7 +9968,7 @@
         <v>2.25</v>
       </c>
       <c r="G331" t="n">
-        <v>1.58543789386749</v>
+        <v>1.58543765544891</v>
       </c>
       <c r="H331" t="n">
         <v>523276</v>
@@ -9997,7 +9997,7 @@
         <v>2.22099995613098</v>
       </c>
       <c r="G332" t="n">
-        <v>1.5650030374527</v>
+        <v>1.56500315666199</v>
       </c>
       <c r="H332" t="n">
         <v>221480</v>
@@ -10055,7 +10055,7 @@
         <v>2.25</v>
       </c>
       <c r="G334" t="n">
-        <v>1.58543789386749</v>
+        <v>1.58543765544891</v>
       </c>
       <c r="H334" t="n">
         <v>841797</v>
@@ -10084,7 +10084,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G335" t="n">
-        <v>1.5769819021225</v>
+        <v>1.57698214054108</v>
       </c>
       <c r="H335" t="n">
         <v>717837</v>
@@ -10142,7 +10142,7 @@
         <v>2.28299999237061</v>
       </c>
       <c r="G337" t="n">
-        <v>1.60869073867798</v>
+        <v>1.60869085788727</v>
       </c>
       <c r="H337" t="n">
         <v>602165</v>
@@ -10200,7 +10200,7 @@
         <v>2.43099999427795</v>
       </c>
       <c r="G339" t="n">
-        <v>1.71297740936279</v>
+        <v>1.71297752857208</v>
       </c>
       <c r="H339" t="n">
         <v>1632236</v>
@@ -10287,7 +10287,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>1.6453320980072</v>
+        <v>1.64533221721649</v>
       </c>
       <c r="H342" t="n">
         <v>505221</v>
@@ -10345,7 +10345,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G344" t="n">
-        <v>1.6629478931427</v>
+        <v>1.66294801235199</v>
       </c>
       <c r="H344" t="n">
         <v>625059</v>
@@ -10374,7 +10374,7 @@
         <v>2.33699989318848</v>
       </c>
       <c r="G345" t="n">
-        <v>1.64674115180969</v>
+        <v>1.64674127101898</v>
       </c>
       <c r="H345" t="n">
         <v>1238842</v>
@@ -10403,7 +10403,7 @@
         <v>2.33699989318848</v>
       </c>
       <c r="G346" t="n">
-        <v>1.64674115180969</v>
+        <v>1.64674127101898</v>
       </c>
       <c r="H346" t="n">
         <v>580707</v>
@@ -10432,7 +10432,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G347" t="n">
-        <v>1.62912547588348</v>
+        <v>1.62912535667419</v>
       </c>
       <c r="H347" t="n">
         <v>376051</v>
@@ -10461,7 +10461,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G348" t="n">
-        <v>1.5614800453186</v>
+        <v>1.56148016452789</v>
       </c>
       <c r="H348" t="n">
         <v>2800039</v>
@@ -10490,7 +10490,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G349" t="n">
-        <v>1.55725228786469</v>
+        <v>1.5572521686554</v>
       </c>
       <c r="H349" t="n">
         <v>599427</v>
@@ -10577,7 +10577,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G352" t="n">
-        <v>1.56429862976074</v>
+        <v>1.56429851055145</v>
       </c>
       <c r="H352" t="n">
         <v>413799</v>
@@ -10635,7 +10635,7 @@
         <v>2.26900005340576</v>
       </c>
       <c r="G354" t="n">
-        <v>1.59882581233978</v>
+        <v>1.59882605075836</v>
       </c>
       <c r="H354" t="n">
         <v>579865</v>
@@ -10664,7 +10664,7 @@
         <v>2.36400008201599</v>
       </c>
       <c r="G355" t="n">
-        <v>1.66576671600342</v>
+        <v>1.66576659679413</v>
       </c>
       <c r="H355" t="n">
         <v>862677</v>
@@ -10722,7 +10722,7 @@
         <v>2.83750009536743</v>
       </c>
       <c r="G357" t="n">
-        <v>1.99941301345825</v>
+        <v>1.99941325187683</v>
       </c>
       <c r="H357" t="n">
         <v>4829114</v>
@@ -10751,7 +10751,7 @@
         <v>2.7574999332428</v>
       </c>
       <c r="G358" t="n">
-        <v>1.94304203987122</v>
+        <v>1.94304192066193</v>
       </c>
       <c r="H358" t="n">
         <v>5360863</v>
@@ -10780,7 +10780,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G359" t="n">
-        <v>1.86729347705841</v>
+        <v>1.8672935962677</v>
       </c>
       <c r="H359" t="n">
         <v>1790824</v>
@@ -10809,7 +10809,7 @@
         <v>2.69749999046326</v>
       </c>
       <c r="G360" t="n">
-        <v>1.90076351165771</v>
+        <v>1.90076386928558</v>
       </c>
       <c r="H360" t="n">
         <v>2325561</v>
@@ -10925,7 +10925,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G364" t="n">
-        <v>1.79682946205139</v>
+        <v>1.7968293428421</v>
       </c>
       <c r="H364" t="n">
         <v>380123</v>
@@ -10954,7 +10954,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G365" t="n">
-        <v>1.79330635070801</v>
+        <v>1.79330611228943</v>
       </c>
       <c r="H365" t="n">
         <v>341518</v>
@@ -11070,7 +11070,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G369" t="n">
-        <v>1.80739903450012</v>
+        <v>1.80739915370941</v>
       </c>
       <c r="H369" t="n">
         <v>372165</v>
@@ -11099,7 +11099,7 @@
         <v>2.5550000667572</v>
       </c>
       <c r="G370" t="n">
-        <v>1.80035269260406</v>
+        <v>1.80035281181335</v>
       </c>
       <c r="H370" t="n">
         <v>510079</v>
@@ -11128,7 +11128,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G371" t="n">
-        <v>1.83206140995026</v>
+        <v>1.83206129074097</v>
       </c>
       <c r="H371" t="n">
         <v>521311</v>
@@ -11186,7 +11186,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G373" t="n">
-        <v>1.88490915298462</v>
+        <v>1.8849093914032</v>
       </c>
       <c r="H373" t="n">
         <v>569369</v>
@@ -11215,7 +11215,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G374" t="n">
-        <v>1.83910763263702</v>
+        <v>1.83910775184631</v>
       </c>
       <c r="H374" t="n">
         <v>564472</v>
@@ -11244,7 +11244,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G375" t="n">
-        <v>1.83910763263702</v>
+        <v>1.83910775184631</v>
       </c>
       <c r="H375" t="n">
         <v>442703</v>
@@ -11273,7 +11273,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G376" t="n">
-        <v>1.86377000808716</v>
+        <v>1.86377012729645</v>
       </c>
       <c r="H376" t="n">
         <v>303450</v>
@@ -11302,7 +11302,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G377" t="n">
-        <v>1.86377000808716</v>
+        <v>1.86377012729645</v>
       </c>
       <c r="H377" t="n">
         <v>377689</v>
@@ -11331,7 +11331,7 @@
         <v>2.6324999332428</v>
       </c>
       <c r="G378" t="n">
-        <v>1.85496211051941</v>
+        <v>1.8549622297287</v>
       </c>
       <c r="H378" t="n">
         <v>460839</v>
@@ -11389,7 +11389,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>1.86377000808716</v>
+        <v>1.86377012729645</v>
       </c>
       <c r="H380" t="n">
         <v>668827</v>
@@ -11418,7 +11418,7 @@
         <v>2.59750008583069</v>
       </c>
       <c r="G381" t="n">
-        <v>1.83029997348785</v>
+        <v>1.83029985427856</v>
       </c>
       <c r="H381" t="n">
         <v>623499</v>
@@ -11447,7 +11447,7 @@
         <v>2.6324999332428</v>
       </c>
       <c r="G382" t="n">
-        <v>1.85496211051941</v>
+        <v>1.8549622297287</v>
       </c>
       <c r="H382" t="n">
         <v>848076</v>
@@ -11476,7 +11476,7 @@
         <v>2.61249995231628</v>
       </c>
       <c r="G383" t="n">
-        <v>1.84086918830872</v>
+        <v>1.84086942672729</v>
       </c>
       <c r="H383" t="n">
         <v>982705</v>
@@ -11534,7 +11534,7 @@
         <v>2.55250000953674</v>
       </c>
       <c r="G385" t="n">
-        <v>1.79859089851379</v>
+        <v>1.79859101772308</v>
       </c>
       <c r="H385" t="n">
         <v>1784366</v>
@@ -11563,7 +11563,7 @@
         <v>2.35700011253357</v>
       </c>
       <c r="G386" t="n">
-        <v>1.8411637544632</v>
+        <v>1.84116351604462</v>
       </c>
       <c r="H386" t="n">
         <v>1675723</v>
@@ -11592,7 +11592,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G387" t="n">
-        <v>1.8060120344162</v>
+        <v>1.80601191520691</v>
       </c>
       <c r="H387" t="n">
         <v>2221253</v>
@@ -11679,7 +11679,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G390" t="n">
-        <v>1.851318359375</v>
+        <v>1.85131824016571</v>
       </c>
       <c r="H390" t="n">
         <v>717045</v>
@@ -11737,7 +11737,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G392" t="n">
-        <v>1.84741270542145</v>
+        <v>1.84741282463074</v>
       </c>
       <c r="H392" t="n">
         <v>573846</v>
@@ -11795,7 +11795,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G394" t="n">
-        <v>1.81694805622101</v>
+        <v>1.81694793701172</v>
       </c>
       <c r="H394" t="n">
         <v>634308</v>
@@ -11824,7 +11824,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G395" t="n">
-        <v>1.84506928920746</v>
+        <v>1.84506940841675</v>
       </c>
       <c r="H395" t="n">
         <v>768257</v>
@@ -11853,7 +11853,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G396" t="n">
-        <v>1.81694805622101</v>
+        <v>1.81694793701172</v>
       </c>
       <c r="H396" t="n">
         <v>564016</v>
@@ -11940,7 +11940,7 @@
         <v>2.3289999961853</v>
       </c>
       <c r="G399" t="n">
-        <v>1.819291472435</v>
+        <v>1.81929135322571</v>
       </c>
       <c r="H399" t="n">
         <v>717310</v>
@@ -11969,7 +11969,7 @@
         <v>2.29900002479553</v>
       </c>
       <c r="G400" t="n">
-        <v>1.79585695266724</v>
+        <v>1.79585707187653</v>
       </c>
       <c r="H400" t="n">
         <v>435929</v>
@@ -11998,7 +11998,7 @@
         <v>2.30800008773804</v>
       </c>
       <c r="G401" t="n">
-        <v>1.80288743972778</v>
+        <v>1.80288732051849</v>
       </c>
       <c r="H401" t="n">
         <v>290608</v>
@@ -12056,7 +12056,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G403" t="n">
-        <v>1.84350681304932</v>
+        <v>1.84350693225861</v>
       </c>
       <c r="H403" t="n">
         <v>508765</v>
@@ -12085,7 +12085,7 @@
         <v>2.34299993515015</v>
       </c>
       <c r="G404" t="n">
-        <v>1.83022749423981</v>
+        <v>1.83022737503052</v>
       </c>
       <c r="H404" t="n">
         <v>400051</v>
@@ -12114,7 +12114,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G405" t="n">
-        <v>1.85912990570068</v>
+        <v>1.85913002490997</v>
       </c>
       <c r="H405" t="n">
         <v>572167</v>
@@ -12143,7 +12143,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G406" t="n">
-        <v>1.82944619655609</v>
+        <v>1.82944655418396</v>
       </c>
       <c r="H406" t="n">
         <v>327031</v>
@@ -12201,7 +12201,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G408" t="n">
-        <v>1.78257751464844</v>
+        <v>1.78257763385773</v>
       </c>
       <c r="H408" t="n">
         <v>720575</v>
@@ -12259,7 +12259,7 @@
         <v>2.29900002479553</v>
       </c>
       <c r="G410" t="n">
-        <v>1.79585695266724</v>
+        <v>1.79585707187653</v>
       </c>
       <c r="H410" t="n">
         <v>244821</v>
@@ -12288,7 +12288,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G411" t="n">
-        <v>1.8060120344162</v>
+        <v>1.80601191520691</v>
       </c>
       <c r="H411" t="n">
         <v>489918</v>
@@ -12317,7 +12317,7 @@
         <v>2.3289999961853</v>
       </c>
       <c r="G412" t="n">
-        <v>1.819291472435</v>
+        <v>1.81929135322571</v>
       </c>
       <c r="H412" t="n">
         <v>1092003</v>
@@ -12346,7 +12346,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G413" t="n">
-        <v>1.82397830486298</v>
+        <v>1.82397842407227</v>
       </c>
       <c r="H413" t="n">
         <v>525566</v>
@@ -12491,7 +12491,7 @@
         <v>2.26099991798401</v>
       </c>
       <c r="G418" t="n">
-        <v>1.76617336273193</v>
+        <v>1.76617348194122</v>
       </c>
       <c r="H418" t="n">
         <v>422740</v>
@@ -12607,7 +12607,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G422" t="n">
-        <v>1.73024070262909</v>
+        <v>1.7302405834198</v>
       </c>
       <c r="H422" t="n">
         <v>493842</v>
@@ -12665,7 +12665,7 @@
         <v>2.14100003242493</v>
       </c>
       <c r="G424" t="n">
-        <v>1.67243576049805</v>
+        <v>1.67243587970734</v>
       </c>
       <c r="H424" t="n">
         <v>2417146</v>
@@ -12752,7 +12752,7 @@
         <v>2.11299991607666</v>
       </c>
       <c r="G427" t="n">
-        <v>1.65056347846985</v>
+        <v>1.65056359767914</v>
       </c>
       <c r="H427" t="n">
         <v>344744</v>
@@ -12810,7 +12810,7 @@
         <v>2.0789999961853</v>
       </c>
       <c r="G429" t="n">
-        <v>1.62400472164154</v>
+        <v>1.62400460243225</v>
       </c>
       <c r="H429" t="n">
         <v>242331</v>
@@ -12839,7 +12839,7 @@
         <v>2.05299997329712</v>
       </c>
       <c r="G430" t="n">
-        <v>1.60369491577148</v>
+        <v>1.60369479656219</v>
       </c>
       <c r="H430" t="n">
         <v>355572</v>
@@ -12926,7 +12926,7 @@
         <v>1.97699999809265</v>
       </c>
       <c r="G433" t="n">
-        <v>1.54432761669159</v>
+        <v>1.54432773590088</v>
       </c>
       <c r="H433" t="n">
         <v>335769</v>
@@ -12955,7 +12955,7 @@
         <v>1.99899995326996</v>
       </c>
       <c r="G434" t="n">
-        <v>1.56151282787323</v>
+        <v>1.56151294708252</v>
       </c>
       <c r="H434" t="n">
         <v>852921</v>
@@ -13042,7 +13042,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G437" t="n">
-        <v>1.44121623039246</v>
+        <v>1.44121634960175</v>
       </c>
       <c r="H437" t="n">
         <v>430171</v>
@@ -13071,7 +13071,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G438" t="n">
-        <v>1.43887293338776</v>
+        <v>1.43887281417847</v>
       </c>
       <c r="H438" t="n">
         <v>297282</v>
@@ -13274,7 +13274,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G445" t="n">
-        <v>1.48886620998383</v>
+        <v>1.48886632919312</v>
       </c>
       <c r="H445" t="n">
         <v>825110</v>
@@ -13332,7 +13332,7 @@
         <v>1.85300004482269</v>
       </c>
       <c r="G447" t="n">
-        <v>1.44746541976929</v>
+        <v>1.44746553897858</v>
       </c>
       <c r="H447" t="n">
         <v>756122</v>
@@ -13390,7 +13390,7 @@
         <v>1.8309999704361</v>
       </c>
       <c r="G449" t="n">
-        <v>1.43028020858765</v>
+        <v>1.43028008937836</v>
       </c>
       <c r="H449" t="n">
         <v>475160</v>
@@ -13477,7 +13477,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G452" t="n">
-        <v>1.31232702732086</v>
+        <v>1.31232690811157</v>
       </c>
       <c r="H452" t="n">
         <v>1384290</v>
@@ -13535,7 +13535,7 @@
         <v>1.66719996929169</v>
       </c>
       <c r="G454" t="n">
-        <v>1.3023282289505</v>
+        <v>1.30232834815979</v>
       </c>
       <c r="H454" t="n">
         <v>438827</v>
@@ -13564,7 +13564,7 @@
         <v>1.69219994544983</v>
       </c>
       <c r="G455" t="n">
-        <v>1.32185685634613</v>
+        <v>1.32185697555542</v>
       </c>
       <c r="H455" t="n">
         <v>907774</v>
@@ -13622,7 +13622,7 @@
         <v>1.69159996509552</v>
       </c>
       <c r="G457" t="n">
-        <v>1.32138824462891</v>
+        <v>1.3213883638382</v>
       </c>
       <c r="H457" t="n">
         <v>232730</v>
@@ -13651,7 +13651,7 @@
         <v>1.74259996414185</v>
       </c>
       <c r="G458" t="n">
-        <v>1.36122667789459</v>
+        <v>1.36122679710388</v>
       </c>
       <c r="H458" t="n">
         <v>372410</v>
@@ -13680,7 +13680,7 @@
         <v>1.84239995479584</v>
       </c>
       <c r="G459" t="n">
-        <v>1.43918514251709</v>
+        <v>1.43918526172638</v>
       </c>
       <c r="H459" t="n">
         <v>501526</v>
@@ -13709,7 +13709,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G460" t="n">
-        <v>1.42715561389923</v>
+        <v>1.42715573310852</v>
       </c>
       <c r="H460" t="n">
         <v>222767</v>
@@ -13825,7 +13825,7 @@
         <v>1.93680000305176</v>
       </c>
       <c r="G464" t="n">
-        <v>1.51292550563812</v>
+        <v>1.51292562484741</v>
       </c>
       <c r="H464" t="n">
         <v>268931</v>
@@ -13854,7 +13854,7 @@
         <v>1.92239999771118</v>
       </c>
       <c r="G465" t="n">
-        <v>1.5016770362854</v>
+        <v>1.50167691707611</v>
       </c>
       <c r="H465" t="n">
         <v>353065</v>
@@ -13883,7 +13883,7 @@
         <v>2.02950000762939</v>
       </c>
       <c r="G466" t="n">
-        <v>1.58533799648285</v>
+        <v>1.58533787727356</v>
       </c>
       <c r="H466" t="n">
         <v>617753</v>
@@ -13941,7 +13941,7 @@
         <v>1.97259998321533</v>
       </c>
       <c r="G468" t="n">
-        <v>1.54089057445526</v>
+        <v>1.54089069366455</v>
       </c>
       <c r="H468" t="n">
         <v>448541</v>
@@ -13970,7 +13970,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G469" t="n">
-        <v>1.58729076385498</v>
+        <v>1.58729088306427</v>
       </c>
       <c r="H469" t="n">
         <v>310094</v>
@@ -14057,7 +14057,7 @@
         <v>2.00850009918213</v>
       </c>
       <c r="G472" t="n">
-        <v>1.56893384456635</v>
+        <v>1.56893396377563</v>
       </c>
       <c r="H472" t="n">
         <v>366405</v>
@@ -14086,7 +14086,7 @@
         <v>2.15249991416931</v>
       </c>
       <c r="G473" t="n">
-        <v>1.68141901493073</v>
+        <v>1.68141889572144</v>
       </c>
       <c r="H473" t="n">
         <v>1172106</v>
@@ -14173,7 +14173,7 @@
         <v>2.25650000572205</v>
       </c>
       <c r="G476" t="n">
-        <v>1.76265823841095</v>
+        <v>1.76265835762024</v>
       </c>
       <c r="H476" t="n">
         <v>463148</v>
@@ -14289,7 +14289,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G480" t="n">
-        <v>1.74664485454559</v>
+        <v>1.7466447353363</v>
       </c>
       <c r="H480" t="n">
         <v>1270704</v>
@@ -14318,7 +14318,7 @@
         <v>2.22300004959106</v>
       </c>
       <c r="G481" t="n">
-        <v>1.73648989200592</v>
+        <v>1.73649001121521</v>
       </c>
       <c r="H481" t="n">
         <v>624711</v>
@@ -14347,7 +14347,7 @@
         <v>2.31900000572205</v>
       </c>
       <c r="G482" t="n">
-        <v>1.8114800453186</v>
+        <v>1.81147992610931</v>
       </c>
       <c r="H482" t="n">
         <v>1426253</v>
@@ -14376,7 +14376,7 @@
         <v>2.29749989509583</v>
       </c>
       <c r="G483" t="n">
-        <v>1.79468524456024</v>
+        <v>1.79468512535095</v>
       </c>
       <c r="H483" t="n">
         <v>1095196</v>
@@ -14405,7 +14405,7 @@
         <v>2.33599996566772</v>
       </c>
       <c r="G484" t="n">
-        <v>1.8247594833374</v>
+        <v>1.82475936412811</v>
       </c>
       <c r="H484" t="n">
         <v>451325</v>
@@ -14434,7 +14434,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G485" t="n">
-        <v>1.86850345134735</v>
+        <v>1.86850368976593</v>
       </c>
       <c r="H485" t="n">
         <v>792725</v>
@@ -14492,7 +14492,7 @@
         <v>2.25</v>
       </c>
       <c r="G487" t="n">
-        <v>1.75758099555969</v>
+        <v>1.7575808763504</v>
       </c>
       <c r="H487" t="n">
         <v>1370262</v>
@@ -14550,7 +14550,7 @@
         <v>2.34949994087219</v>
       </c>
       <c r="G489" t="n">
-        <v>1.83530509471893</v>
+        <v>1.83530497550964</v>
       </c>
       <c r="H489" t="n">
         <v>626584</v>
@@ -14608,7 +14608,7 @@
         <v>2.39750003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>1.87280011177063</v>
+        <v>1.87280023097992</v>
       </c>
       <c r="H491" t="n">
         <v>839004</v>
@@ -14637,7 +14637,7 @@
         <v>2.3989999294281</v>
       </c>
       <c r="G492" t="n">
-        <v>1.87397158145905</v>
+        <v>1.87397170066833</v>
       </c>
       <c r="H492" t="n">
         <v>458199</v>
@@ -14666,7 +14666,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G493" t="n">
-        <v>1.86225461959839</v>
+        <v>1.86225438117981</v>
       </c>
       <c r="H493" t="n">
         <v>271589</v>
@@ -14695,7 +14695,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G494" t="n">
-        <v>1.85912990570068</v>
+        <v>1.85913002490997</v>
       </c>
       <c r="H494" t="n">
         <v>254944</v>
@@ -14724,7 +14724,7 @@
         <v>2.38100004196167</v>
       </c>
       <c r="G495" t="n">
-        <v>1.8599112033844</v>
+        <v>1.85991108417511</v>
       </c>
       <c r="H495" t="n">
         <v>360476</v>
@@ -14753,7 +14753,7 @@
         <v>2.375</v>
       </c>
       <c r="G496" t="n">
-        <v>1.85522401332855</v>
+        <v>1.85522413253784</v>
       </c>
       <c r="H496" t="n">
         <v>380134</v>
@@ -14840,7 +14840,7 @@
         <v>2.3289999961853</v>
       </c>
       <c r="G499" t="n">
-        <v>1.819291472435</v>
+        <v>1.81929135322571</v>
       </c>
       <c r="H499" t="n">
         <v>426104</v>
@@ -14927,7 +14927,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G502" t="n">
-        <v>1.89662492275238</v>
+        <v>1.89662504196167</v>
       </c>
       <c r="H502" t="n">
         <v>886759</v>
@@ -14956,7 +14956,7 @@
         <v>2.4210000038147</v>
       </c>
       <c r="G503" t="n">
-        <v>1.89115715026855</v>
+        <v>1.89115703105927</v>
       </c>
       <c r="H503" t="n">
         <v>400870</v>
@@ -14985,7 +14985,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G504" t="n">
-        <v>1.90443646907806</v>
+        <v>1.90443634986877</v>
       </c>
       <c r="H504" t="n">
         <v>376866</v>
@@ -15014,7 +15014,7 @@
         <v>2.40199995040894</v>
       </c>
       <c r="G505" t="n">
-        <v>1.87631523609161</v>
+        <v>1.87631499767303</v>
       </c>
       <c r="H505" t="n">
         <v>719122</v>
@@ -15072,7 +15072,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G507" t="n">
-        <v>1.851318359375</v>
+        <v>1.85131824016571</v>
       </c>
       <c r="H507" t="n">
         <v>420850</v>
@@ -15101,7 +15101,7 @@
         <v>2.38750004768372</v>
       </c>
       <c r="G508" t="n">
-        <v>1.86498880386353</v>
+        <v>1.86498844623566</v>
       </c>
       <c r="H508" t="n">
         <v>279164</v>
@@ -15130,7 +15130,7 @@
         <v>2.37949991226196</v>
       </c>
       <c r="G509" t="n">
-        <v>1.85873925685883</v>
+        <v>1.85873937606812</v>
       </c>
       <c r="H509" t="n">
         <v>517495</v>
@@ -15159,7 +15159,7 @@
         <v>2.33949995040894</v>
       </c>
       <c r="G510" t="n">
-        <v>1.82749342918396</v>
+        <v>1.82749330997467</v>
       </c>
       <c r="H510" t="n">
         <v>387078</v>
@@ -15188,7 +15188,7 @@
         <v>2.30800008773804</v>
       </c>
       <c r="G511" t="n">
-        <v>1.80288743972778</v>
+        <v>1.80288732051849</v>
       </c>
       <c r="H511" t="n">
         <v>471638</v>
@@ -15275,7 +15275,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G514" t="n">
-        <v>1.84819376468658</v>
+        <v>1.84819388389587</v>
       </c>
       <c r="H514" t="n">
         <v>499423</v>
@@ -15304,7 +15304,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G515" t="n">
-        <v>1.88256430625916</v>
+        <v>1.88256442546844</v>
       </c>
       <c r="H515" t="n">
         <v>456876</v>
@@ -15333,7 +15333,7 @@
         <v>2.38700008392334</v>
       </c>
       <c r="G516" t="n">
-        <v>1.86459803581238</v>
+        <v>1.86459815502167</v>
       </c>
       <c r="H516" t="n">
         <v>378435</v>
@@ -15391,7 +15391,7 @@
         <v>2.35949993133545</v>
       </c>
       <c r="G518" t="n">
-        <v>1.84311640262604</v>
+        <v>1.84311628341675</v>
       </c>
       <c r="H518" t="n">
         <v>314732</v>
@@ -15420,7 +15420,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G519" t="n">
-        <v>1.84506928920746</v>
+        <v>1.84506940841675</v>
       </c>
       <c r="H519" t="n">
         <v>346938</v>
@@ -15536,7 +15536,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G523" t="n">
-        <v>1.74352037906647</v>
+        <v>1.74352025985718</v>
       </c>
       <c r="H523" t="n">
         <v>587511</v>
@@ -15594,7 +15594,7 @@
         <v>2.18650007247925</v>
       </c>
       <c r="G525" t="n">
-        <v>1.70797801017761</v>
+        <v>1.70797789096832</v>
       </c>
       <c r="H525" t="n">
         <v>339135</v>
@@ -15739,7 +15739,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G530" t="n">
-        <v>1.65603160858154</v>
+        <v>1.65603172779083</v>
       </c>
       <c r="H530" t="n">
         <v>1091564</v>
@@ -15855,7 +15855,7 @@
         <v>2.1029999256134</v>
       </c>
       <c r="G534" t="n">
-        <v>1.64275205135345</v>
+        <v>1.64275217056274</v>
       </c>
       <c r="H534" t="n">
         <v>489001</v>
@@ -15971,7 +15971,7 @@
         <v>2.11150002479553</v>
       </c>
       <c r="G538" t="n">
-        <v>1.64939188957214</v>
+        <v>1.64939200878143</v>
       </c>
       <c r="H538" t="n">
         <v>386864</v>
@@ -16058,7 +16058,7 @@
         <v>2.10949993133545</v>
       </c>
       <c r="G541" t="n">
-        <v>1.64782965183258</v>
+        <v>1.64782953262329</v>
       </c>
       <c r="H541" t="n">
         <v>509259</v>
@@ -16174,7 +16174,7 @@
         <v>2.12750005722046</v>
       </c>
       <c r="G545" t="n">
-        <v>1.66189050674438</v>
+        <v>1.6618903875351</v>
       </c>
       <c r="H545" t="n">
         <v>1419921</v>
@@ -16232,7 +16232,7 @@
         <v>2.10949993133545</v>
       </c>
       <c r="G547" t="n">
-        <v>1.64782965183258</v>
+        <v>1.64782953262329</v>
       </c>
       <c r="H547" t="n">
         <v>489388</v>
@@ -16348,7 +16348,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G551" t="n">
-        <v>1.67009222507477</v>
+        <v>1.67009234428406</v>
       </c>
       <c r="H551" t="n">
         <v>1192328</v>
@@ -16406,7 +16406,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G553" t="n">
-        <v>1.74976933002472</v>
+        <v>1.74976944923401</v>
       </c>
       <c r="H553" t="n">
         <v>1944729</v>
@@ -16464,7 +16464,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G555" t="n">
-        <v>1.74352037906647</v>
+        <v>1.74352025985718</v>
       </c>
       <c r="H555" t="n">
         <v>532106</v>
@@ -16493,7 +16493,7 @@
         <v>2.24449992179871</v>
       </c>
       <c r="G556" t="n">
-        <v>1.75328433513641</v>
+        <v>1.75328457355499</v>
       </c>
       <c r="H556" t="n">
         <v>397911</v>
@@ -16580,7 +16580,7 @@
         <v>2.42149996757507</v>
       </c>
       <c r="G559" t="n">
-        <v>1.89154756069183</v>
+        <v>1.89154744148254</v>
       </c>
       <c r="H559" t="n">
         <v>1056336</v>
@@ -16609,7 +16609,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G560" t="n">
-        <v>1.8786586523056</v>
+        <v>1.87865853309631</v>
       </c>
       <c r="H560" t="n">
         <v>518625</v>
@@ -16638,7 +16638,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G561" t="n">
-        <v>1.92630863189697</v>
+        <v>1.92630875110626</v>
       </c>
       <c r="H561" t="n">
         <v>1119220</v>
@@ -16667,7 +16667,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G562" t="n">
-        <v>1.95130503177643</v>
+        <v>1.95130527019501</v>
       </c>
       <c r="H562" t="n">
         <v>455972</v>
@@ -16754,7 +16754,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G565" t="n">
-        <v>1.97473990917206</v>
+        <v>1.97473978996277</v>
       </c>
       <c r="H565" t="n">
         <v>742112</v>
@@ -16812,7 +16812,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G567" t="n">
-        <v>1.97473990917206</v>
+        <v>1.97473978996277</v>
       </c>
       <c r="H567" t="n">
         <v>1363010</v>
@@ -16841,7 +16841,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G568" t="n">
-        <v>1.99661183357239</v>
+        <v>1.99661195278168</v>
       </c>
       <c r="H568" t="n">
         <v>1003381</v>
@@ -16899,7 +16899,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G570" t="n">
-        <v>1.9294331073761</v>
+        <v>1.92943322658539</v>
       </c>
       <c r="H570" t="n">
         <v>765788</v>
@@ -16928,7 +16928,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G571" t="n">
-        <v>1.93099534511566</v>
+        <v>1.93099522590637</v>
       </c>
       <c r="H571" t="n">
         <v>439198</v>
@@ -17015,7 +17015,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G574" t="n">
-        <v>2.02785778045654</v>
+        <v>2.02785754203796</v>
       </c>
       <c r="H574" t="n">
         <v>1096883</v>
@@ -17044,7 +17044,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G575" t="n">
-        <v>2.04660534858704</v>
+        <v>2.04660511016846</v>
       </c>
       <c r="H575" t="n">
         <v>671436</v>
@@ -17102,7 +17102,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G577" t="n">
-        <v>2.12784457206726</v>
+        <v>2.12784433364868</v>
       </c>
       <c r="H577" t="n">
         <v>1427518</v>
@@ -17160,7 +17160,7 @@
         <v>2.71799993515015</v>
       </c>
       <c r="G579" t="n">
-        <v>2.1231575012207</v>
+        <v>2.12315773963928</v>
       </c>
       <c r="H579" t="n">
         <v>1054021</v>
@@ -17247,7 +17247,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>2.17940020561218</v>
+        <v>2.1793999671936</v>
       </c>
       <c r="H582" t="n">
         <v>543959</v>
@@ -17305,7 +17305,7 @@
         <v>2.76200008392334</v>
       </c>
       <c r="G584" t="n">
-        <v>2.15752840042114</v>
+        <v>2.15752816200256</v>
       </c>
       <c r="H584" t="n">
         <v>580443</v>
@@ -17334,7 +17334,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G585" t="n">
-        <v>2.1965856552124</v>
+        <v>2.19658541679382</v>
       </c>
       <c r="H585" t="n">
         <v>1518765</v>
@@ -17363,7 +17363,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G586" t="n">
-        <v>2.25751495361328</v>
+        <v>2.25751519203186</v>
       </c>
       <c r="H586" t="n">
         <v>1032388</v>
@@ -17421,7 +17421,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G588" t="n">
-        <v>2.31219506263733</v>
+        <v>2.31219530105591</v>
       </c>
       <c r="H588" t="n">
         <v>1282951</v>
@@ -17537,7 +17537,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G592" t="n">
-        <v>2.43874073028564</v>
+        <v>2.4387412071228</v>
       </c>
       <c r="H592" t="n">
         <v>965545</v>
@@ -17624,7 +17624,7 @@
         <v>3.11400008201599</v>
       </c>
       <c r="G595" t="n">
-        <v>2.43249201774597</v>
+        <v>2.43249177932739</v>
       </c>
       <c r="H595" t="n">
         <v>1799003</v>
@@ -17653,7 +17653,7 @@
         <v>3.00399994850159</v>
       </c>
       <c r="G596" t="n">
-        <v>2.34656572341919</v>
+        <v>2.34656548500061</v>
       </c>
       <c r="H596" t="n">
         <v>921949</v>
@@ -17682,7 +17682,7 @@
         <v>3</v>
       </c>
       <c r="G597" t="n">
-        <v>2.34344100952148</v>
+        <v>2.34344124794006</v>
       </c>
       <c r="H597" t="n">
         <v>1851145</v>
@@ -17740,7 +17740,7 @@
         <v>3.10800004005432</v>
       </c>
       <c r="G599" t="n">
-        <v>2.42780518531799</v>
+        <v>2.42780494689941</v>
       </c>
       <c r="H599" t="n">
         <v>1169838</v>
@@ -17798,7 +17798,7 @@
         <v>3.05200004577637</v>
       </c>
       <c r="G601" t="n">
-        <v>2.3840606212616</v>
+        <v>2.38406085968018</v>
       </c>
       <c r="H601" t="n">
         <v>913843</v>
@@ -17856,7 +17856,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G603" t="n">
-        <v>2.46529984474182</v>
+        <v>2.4653000831604</v>
       </c>
       <c r="H603" t="n">
         <v>1511750</v>
@@ -17885,7 +17885,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G604" t="n">
-        <v>2.46529984474182</v>
+        <v>2.4653000831604</v>
       </c>
       <c r="H604" t="n">
         <v>2000044</v>
@@ -17914,7 +17914,7 @@
         <v>3.17400002479553</v>
       </c>
       <c r="G605" t="n">
-        <v>2.47936058044434</v>
+        <v>2.47936081886292</v>
       </c>
       <c r="H605" t="n">
         <v>2744827</v>
@@ -17943,7 +17943,7 @@
         <v>3.30399990081787</v>
       </c>
       <c r="G606" t="n">
-        <v>2.58090972900391</v>
+        <v>2.58090949058533</v>
       </c>
       <c r="H606" t="n">
         <v>2221014</v>
@@ -18001,7 +18001,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G608" t="n">
-        <v>2.5465395450592</v>
+        <v>2.54653930664062</v>
       </c>
       <c r="H608" t="n">
         <v>795781</v>
@@ -18030,7 +18030,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G609" t="n">
-        <v>2.54810166358948</v>
+        <v>2.54810190200806</v>
       </c>
       <c r="H609" t="n">
         <v>548275</v>
@@ -18175,7 +18175,7 @@
         <v>3.09599995613098</v>
       </c>
       <c r="G614" t="n">
-        <v>2.41843128204346</v>
+        <v>2.41843104362488</v>
       </c>
       <c r="H614" t="n">
         <v>539410</v>
@@ -18378,7 +18378,7 @@
         <v>3.18799996376038</v>
       </c>
       <c r="G621" t="n">
-        <v>2.49029660224915</v>
+        <v>2.49029684066772</v>
       </c>
       <c r="H621" t="n">
         <v>691299</v>
@@ -18407,7 +18407,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G622" t="n">
-        <v>2.52310490608215</v>
+        <v>2.52310514450073</v>
       </c>
       <c r="H622" t="n">
         <v>1734037</v>
@@ -18494,7 +18494,7 @@
         <v>3.24799990653992</v>
       </c>
       <c r="G625" t="n">
-        <v>2.53716540336609</v>
+        <v>2.53716564178467</v>
       </c>
       <c r="H625" t="n">
         <v>505088</v>
@@ -18552,7 +18552,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G627" t="n">
-        <v>2.52310490608215</v>
+        <v>2.52310514450073</v>
       </c>
       <c r="H627" t="n">
         <v>1052134</v>
@@ -18610,7 +18610,7 @@
         <v>3.26399993896484</v>
       </c>
       <c r="G629" t="n">
-        <v>2.54966378211975</v>
+        <v>2.54966402053833</v>
       </c>
       <c r="H629" t="n">
         <v>1449732</v>
@@ -18784,7 +18784,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G635" t="n">
-        <v>2.71058011054993</v>
+        <v>2.71058034896851</v>
       </c>
       <c r="H635" t="n">
         <v>867265</v>
@@ -18929,7 +18929,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G640" t="n">
-        <v>2.66151165962219</v>
+        <v>2.66151189804077</v>
       </c>
       <c r="H640" t="n">
         <v>1142550</v>
@@ -19074,7 +19074,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G645" t="n">
-        <v>2.65814256668091</v>
+        <v>2.65814280509949</v>
       </c>
       <c r="H645" t="n">
         <v>687583</v>
@@ -19132,7 +19132,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G647" t="n">
-        <v>2.59413170814514</v>
+        <v>2.59413146972656</v>
       </c>
       <c r="H647" t="n">
         <v>573464</v>
@@ -19161,7 +19161,7 @@
         <v>3.01399993896484</v>
       </c>
       <c r="G648" t="n">
-        <v>2.53854322433472</v>
+        <v>2.53854298591614</v>
       </c>
       <c r="H648" t="n">
         <v>931043</v>
@@ -19248,7 +19248,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G651" t="n">
-        <v>2.44926452636719</v>
+        <v>2.44926476478577</v>
       </c>
       <c r="H651" t="n">
         <v>488032</v>
@@ -19422,7 +19422,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G657" t="n">
-        <v>2.45600271224976</v>
+        <v>2.45600247383118</v>
       </c>
       <c r="H657" t="n">
         <v>344477</v>
@@ -19567,7 +19567,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G662" t="n">
-        <v>2.47116303443909</v>
+        <v>2.47116327285767</v>
       </c>
       <c r="H662" t="n">
         <v>401363</v>
@@ -19683,7 +19683,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G666" t="n">
-        <v>2.48800826072693</v>
+        <v>2.48800802230835</v>
       </c>
       <c r="H666" t="n">
         <v>259923</v>
@@ -19741,7 +19741,7 @@
         <v>2.89800000190735</v>
       </c>
       <c r="G668" t="n">
-        <v>2.44084215164185</v>
+        <v>2.44084191322327</v>
       </c>
       <c r="H668" t="n">
         <v>360472</v>
@@ -20031,7 +20031,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G678" t="n">
-        <v>2.35661721229553</v>
+        <v>2.35661697387695</v>
       </c>
       <c r="H678" t="n">
         <v>240265</v>
@@ -20118,7 +20118,7 @@
         <v>3.22399997711182</v>
       </c>
       <c r="G681" t="n">
-        <v>2.71541595458984</v>
+        <v>2.71541571617126</v>
       </c>
       <c r="H681" t="n">
         <v>4686248</v>
@@ -20147,7 +20147,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G682" t="n">
-        <v>2.57223320007324</v>
+        <v>2.57223296165466</v>
       </c>
       <c r="H682" t="n">
         <v>2047557</v>
@@ -20321,7 +20321,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G688" t="n">
-        <v>2.61097645759583</v>
+        <v>2.6109766960144</v>
       </c>
       <c r="H688" t="n">
         <v>540996</v>
@@ -20350,7 +20350,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G689" t="n">
-        <v>2.5857093334198</v>
+        <v>2.58570909500122</v>
       </c>
       <c r="H689" t="n">
         <v>835995</v>
@@ -20379,7 +20379,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G690" t="n">
-        <v>2.57560205459595</v>
+        <v>2.57560229301453</v>
       </c>
       <c r="H690" t="n">
         <v>1181402</v>
@@ -20408,7 +20408,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G691" t="n">
-        <v>2.49306154251099</v>
+        <v>2.49306178092957</v>
       </c>
       <c r="H691" t="n">
         <v>554383</v>
@@ -20524,7 +20524,7 @@
         <v>3.03200006484985</v>
       </c>
       <c r="G695" t="n">
-        <v>2.55370354652405</v>
+        <v>2.55370378494263</v>
       </c>
       <c r="H695" t="n">
         <v>176181</v>
@@ -20640,7 +20640,7 @@
         <v>3.06800007820129</v>
       </c>
       <c r="G699" t="n">
-        <v>2.58402490615845</v>
+        <v>2.58402466773987</v>
       </c>
       <c r="H699" t="n">
         <v>565902</v>
@@ -20872,7 +20872,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G707" t="n">
-        <v>2.5857093334198</v>
+        <v>2.58570909500122</v>
       </c>
       <c r="H707" t="n">
         <v>503676</v>
@@ -20959,7 +20959,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G710" t="n">
-        <v>2.50990676879883</v>
+        <v>2.50990653038025</v>
       </c>
       <c r="H710" t="n">
         <v>1933202</v>
@@ -20988,7 +20988,7 @@
         <v>3.01399993896484</v>
       </c>
       <c r="G711" t="n">
-        <v>2.53854322433472</v>
+        <v>2.53854298591614</v>
       </c>
       <c r="H711" t="n">
         <v>357710</v>
@@ -21017,7 +21017,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G712" t="n">
-        <v>2.50990676879883</v>
+        <v>2.50990653038025</v>
       </c>
       <c r="H712" t="n">
         <v>660930</v>
@@ -21075,7 +21075,7 @@
         <v>2.91400003433228</v>
       </c>
       <c r="G714" t="n">
-        <v>2.4543182849884</v>
+        <v>2.45431804656982</v>
       </c>
       <c r="H714" t="n">
         <v>482372</v>
@@ -21162,7 +21162,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G717" t="n">
-        <v>2.45600271224976</v>
+        <v>2.45600247383118</v>
       </c>
       <c r="H717" t="n">
         <v>519899</v>
@@ -21423,7 +21423,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G726" t="n">
-        <v>2.44926452636719</v>
+        <v>2.44926476478577</v>
       </c>
       <c r="H726" t="n">
         <v>2315220</v>
@@ -21655,7 +21655,7 @@
         <v>2.79200005531311</v>
       </c>
       <c r="G734" t="n">
-        <v>2.35156345367432</v>
+        <v>2.3515636920929</v>
       </c>
       <c r="H734" t="n">
         <v>407635</v>
@@ -21684,7 +21684,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G735" t="n">
-        <v>2.41388988494873</v>
+        <v>2.41389012336731</v>
       </c>
       <c r="H735" t="n">
         <v>672584</v>
@@ -21887,7 +21887,7 @@
         <v>3.04200005531311</v>
       </c>
       <c r="G742" t="n">
-        <v>2.56212639808655</v>
+        <v>2.56212615966797</v>
       </c>
       <c r="H742" t="n">
         <v>920296</v>
@@ -22003,7 +22003,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G746" t="n">
-        <v>2.48295450210571</v>
+        <v>2.48295474052429</v>
       </c>
       <c r="H746" t="n">
         <v>959673</v>
@@ -22177,7 +22177,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>2.49306154251099</v>
+        <v>2.49306178092957</v>
       </c>
       <c r="H752" t="n">
         <v>229054</v>
@@ -22293,7 +22293,7 @@
         <v>3.01399993896484</v>
       </c>
       <c r="G756" t="n">
-        <v>2.53854322433472</v>
+        <v>2.53854298591614</v>
       </c>
       <c r="H756" t="n">
         <v>339559</v>
@@ -22380,7 +22380,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G759" t="n">
-        <v>2.48295450210571</v>
+        <v>2.48295474052429</v>
       </c>
       <c r="H759" t="n">
         <v>299028</v>
@@ -22467,7 +22467,7 @@
         <v>3.03399991989136</v>
       </c>
       <c r="G762" t="n">
-        <v>2.5553879737854</v>
+        <v>2.55538821220398</v>
       </c>
       <c r="H762" t="n">
         <v>577970</v>
@@ -22583,7 +22583,7 @@
         <v>3.09599995613098</v>
       </c>
       <c r="G766" t="n">
-        <v>2.6076078414917</v>
+        <v>2.60760760307312</v>
       </c>
       <c r="H766" t="n">
         <v>954705</v>
@@ -22612,7 +22612,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G767" t="n">
-        <v>2.5772864818573</v>
+        <v>2.57728672027588</v>
       </c>
       <c r="H767" t="n">
         <v>598686</v>
@@ -22670,7 +22670,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G769" t="n">
-        <v>2.57560205459595</v>
+        <v>2.57560229301453</v>
       </c>
       <c r="H769" t="n">
         <v>237570</v>
@@ -22699,7 +22699,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G770" t="n">
-        <v>2.57223320007324</v>
+        <v>2.57223296165466</v>
       </c>
       <c r="H770" t="n">
         <v>235087</v>
@@ -22728,7 +22728,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G771" t="n">
-        <v>2.58907794952393</v>
+        <v>2.5890781879425</v>
       </c>
       <c r="H771" t="n">
         <v>233031</v>
@@ -22815,7 +22815,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G774" t="n">
-        <v>2.67835688591003</v>
+        <v>2.67835664749146</v>
       </c>
       <c r="H774" t="n">
         <v>844822</v>
@@ -22844,7 +22844,7 @@
         <v>3.14199995994568</v>
       </c>
       <c r="G775" t="n">
-        <v>2.64635109901428</v>
+        <v>2.64635133743286</v>
       </c>
       <c r="H775" t="n">
         <v>1054352</v>
@@ -22931,7 +22931,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G778" t="n">
-        <v>2.71710014343262</v>
+        <v>2.7171003818512</v>
       </c>
       <c r="H778" t="n">
         <v>964874</v>
@@ -22960,7 +22960,7 @@
         <v>3.20600008964539</v>
       </c>
       <c r="G779" t="n">
-        <v>2.70025539398193</v>
+        <v>2.70025515556335</v>
       </c>
       <c r="H779" t="n">
         <v>409180</v>
@@ -23076,7 +23076,7 @@
         <v>3.20600008964539</v>
       </c>
       <c r="G783" t="n">
-        <v>2.70025539398193</v>
+        <v>2.70025515556335</v>
       </c>
       <c r="H783" t="n">
         <v>938332</v>
@@ -23105,7 +23105,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G784" t="n">
-        <v>2.71710014343262</v>
+        <v>2.7171003818512</v>
       </c>
       <c r="H784" t="n">
         <v>578855</v>
@@ -23250,7 +23250,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G789" t="n">
-        <v>2.84680700302124</v>
+        <v>2.84680676460266</v>
       </c>
       <c r="H789" t="n">
         <v>815915</v>
@@ -23395,7 +23395,7 @@
         <v>3.14199995994568</v>
       </c>
       <c r="G794" t="n">
-        <v>2.64635109901428</v>
+        <v>2.64635133743286</v>
       </c>
       <c r="H794" t="n">
         <v>768072</v>
@@ -23627,7 +23627,7 @@
         <v>3.36800003051758</v>
       </c>
       <c r="G802" t="n">
-        <v>2.83669972419739</v>
+        <v>2.83669996261597</v>
       </c>
       <c r="H802" t="n">
         <v>706988</v>
@@ -23714,7 +23714,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G805" t="n">
-        <v>2.93776988983154</v>
+        <v>2.93776965141296</v>
       </c>
       <c r="H805" t="n">
         <v>557350</v>
@@ -23975,7 +23975,7 @@
         <v>3.38800001144409</v>
       </c>
       <c r="G814" t="n">
-        <v>2.85354495048523</v>
+        <v>2.85354471206665</v>
       </c>
       <c r="H814" t="n">
         <v>347337</v>
@@ -24091,7 +24091,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G818" t="n">
-        <v>2.45600271224976</v>
+        <v>2.45600247383118</v>
       </c>
       <c r="H818" t="n">
         <v>1497205</v>
@@ -24120,7 +24120,7 @@
         <v>3.00600004196167</v>
       </c>
       <c r="G819" t="n">
-        <v>2.53180527687073</v>
+        <v>2.53180503845215</v>
       </c>
       <c r="H819" t="n">
         <v>790572</v>
@@ -24526,7 +24526,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G833" t="n">
-        <v>2.69183301925659</v>
+        <v>2.69183278083801</v>
       </c>
       <c r="H833" t="n">
         <v>488767</v>
@@ -24555,7 +24555,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G834" t="n">
-        <v>2.67835688591003</v>
+        <v>2.67835664749146</v>
       </c>
       <c r="H834" t="n">
         <v>708286</v>
@@ -24584,7 +24584,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G835" t="n">
-        <v>2.65814256668091</v>
+        <v>2.65814280509949</v>
       </c>
       <c r="H835" t="n">
         <v>524048</v>
@@ -24642,7 +24642,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G837" t="n">
-        <v>2.67835688591003</v>
+        <v>2.67835664749146</v>
       </c>
       <c r="H837" t="n">
         <v>361053</v>
@@ -24700,7 +24700,7 @@
         <v>3.25</v>
       </c>
       <c r="G839" t="n">
-        <v>2.73731446266174</v>
+        <v>2.73731422424316</v>
       </c>
       <c r="H839" t="n">
         <v>461413</v>
@@ -24816,7 +24816,7 @@
         <v>3.25</v>
       </c>
       <c r="G843" t="n">
-        <v>2.73731446266174</v>
+        <v>2.73731422424316</v>
       </c>
       <c r="H843" t="n">
         <v>565490</v>
@@ -24961,7 +24961,7 @@
         <v>3.33599996566772</v>
       </c>
       <c r="G848" t="n">
-        <v>2.80974793434143</v>
+        <v>2.80974769592285</v>
       </c>
       <c r="H848" t="n">
         <v>1117559</v>
@@ -25251,7 +25251,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G858" t="n">
-        <v>2.7979564666748</v>
+        <v>2.79795622825623</v>
       </c>
       <c r="H858" t="n">
         <v>402306</v>
@@ -25338,7 +25338,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G861" t="n">
-        <v>2.78784942626953</v>
+        <v>2.78784918785095</v>
       </c>
       <c r="H861" t="n">
         <v>436318</v>
@@ -25483,7 +25483,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G866" t="n">
-        <v>2.68677926063538</v>
+        <v>2.68677949905396</v>
       </c>
       <c r="H866" t="n">
         <v>1350411</v>
@@ -25541,7 +25541,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G868" t="n">
-        <v>2.65814256668091</v>
+        <v>2.65814280509949</v>
       </c>
       <c r="H868" t="n">
         <v>1567922</v>
@@ -35494,6 +35494,35 @@
         <v>1362738</v>
       </c>
       <c r="I1211" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1212" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1212" t="n">
+        <v>2.08200001716614</v>
+      </c>
+      <c r="D1212" t="n">
+        <v>2.11800003051758</v>
+      </c>
+      <c r="E1212" t="n">
+        <v>2.07399988174438</v>
+      </c>
+      <c r="F1212" t="n">
+        <v>2.10800004005432</v>
+      </c>
+      <c r="G1212" t="n">
+        <v>2.10800004005432</v>
+      </c>
+      <c r="H1212" t="n">
+        <v>1353239</v>
+      </c>
+      <c r="I1212" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MFEA.MI.xlsx
+++ b/data/MFEA.MI.xlsx
@@ -543,7 +543,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G6" t="n">
-        <v>2.28727078437805</v>
+        <v>2.28727102279663</v>
       </c>
       <c r="H6" t="n">
         <v>214912</v>
@@ -572,7 +572,7 @@
         <v>3.70749998092651</v>
       </c>
       <c r="G7" t="n">
-        <v>2.28572964668274</v>
+        <v>2.28572940826416</v>
       </c>
       <c r="H7" t="n">
         <v>170939</v>
@@ -659,7 +659,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>2.33659219741821</v>
+        <v>2.33659195899963</v>
       </c>
       <c r="H10" t="n">
         <v>166086</v>
@@ -891,7 +891,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G18" t="n">
-        <v>2.66951036453247</v>
+        <v>2.66951012611389</v>
       </c>
       <c r="H18" t="n">
         <v>629452</v>
@@ -1036,7 +1036,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G23" t="n">
-        <v>2.49688601493835</v>
+        <v>2.49688625335693</v>
       </c>
       <c r="H23" t="n">
         <v>230967</v>
@@ -1065,7 +1065,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G24" t="n">
-        <v>2.42598652839661</v>
+        <v>2.42598676681519</v>
       </c>
       <c r="H24" t="n">
         <v>208426</v>
@@ -1268,7 +1268,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G31" t="n">
-        <v>2.4044086933136</v>
+        <v>2.40440893173218</v>
       </c>
       <c r="H31" t="n">
         <v>128224</v>
@@ -1442,7 +1442,7 @@
         <v>4.14249992370605</v>
       </c>
       <c r="G37" t="n">
-        <v>2.55391383171082</v>
+        <v>2.55391359329224</v>
       </c>
       <c r="H37" t="n">
         <v>310291</v>
@@ -1616,7 +1616,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G43" t="n">
-        <v>2.03449964523315</v>
+        <v>2.03449988365173</v>
       </c>
       <c r="H43" t="n">
         <v>404535</v>
@@ -1877,7 +1877,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G52" t="n">
-        <v>1.99442625045776</v>
+        <v>1.99442613124847</v>
       </c>
       <c r="H52" t="n">
         <v>186459</v>
@@ -1964,7 +1964,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G55" t="n">
-        <v>1.82796716690063</v>
+        <v>1.82796704769135</v>
       </c>
       <c r="H55" t="n">
         <v>452826</v>
@@ -2109,7 +2109,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G60" t="n">
-        <v>1.79714143276215</v>
+        <v>1.79714119434357</v>
       </c>
       <c r="H60" t="n">
         <v>140935</v>
@@ -2138,7 +2138,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G61" t="n">
-        <v>1.80638933181763</v>
+        <v>1.80638909339905</v>
       </c>
       <c r="H61" t="n">
         <v>175025</v>
@@ -2196,7 +2196,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G63" t="n">
-        <v>1.81255447864532</v>
+        <v>1.81255424022675</v>
       </c>
       <c r="H63" t="n">
         <v>134826</v>
@@ -2283,7 +2283,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G66" t="n">
-        <v>1.71391177177429</v>
+        <v>1.713911652565</v>
       </c>
       <c r="H66" t="n">
         <v>344735</v>
@@ -2341,7 +2341,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G68" t="n">
-        <v>1.6615082025528</v>
+        <v>1.66150796413422</v>
       </c>
       <c r="H68" t="n">
         <v>213075</v>
@@ -2370,7 +2370,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G69" t="n">
-        <v>1.65226054191589</v>
+        <v>1.65226030349731</v>
       </c>
       <c r="H69" t="n">
         <v>531234</v>
@@ -2486,7 +2486,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G73" t="n">
-        <v>1.74165511131287</v>
+        <v>1.74165487289429</v>
       </c>
       <c r="H73" t="n">
         <v>228203</v>
@@ -2544,7 +2544,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G75" t="n">
-        <v>1.6615082025528</v>
+        <v>1.66150796413422</v>
       </c>
       <c r="H75" t="n">
         <v>331684</v>
@@ -2573,7 +2573,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G76" t="n">
-        <v>1.6337651014328</v>
+        <v>1.63376486301422</v>
       </c>
       <c r="H76" t="n">
         <v>246997</v>
@@ -3095,7 +3095,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G94" t="n">
-        <v>1.6399302482605</v>
+        <v>1.63993012905121</v>
       </c>
       <c r="H94" t="n">
         <v>124415</v>
@@ -3182,7 +3182,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G97" t="n">
-        <v>1.57827854156494</v>
+        <v>1.57827877998352</v>
       </c>
       <c r="H97" t="n">
         <v>975446</v>
@@ -3211,7 +3211,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G98" t="n">
-        <v>1.664590716362</v>
+        <v>1.66459059715271</v>
       </c>
       <c r="H98" t="n">
         <v>547180</v>
@@ -3240,7 +3240,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>1.60602176189423</v>
+        <v>1.60602188110352</v>
       </c>
       <c r="H99" t="n">
         <v>524697</v>
@@ -3269,7 +3269,7 @@
         <v>2.45300006866455</v>
       </c>
       <c r="G100" t="n">
-        <v>1.51231157779694</v>
+        <v>1.51231169700623</v>
       </c>
       <c r="H100" t="n">
         <v>588672</v>
@@ -3298,7 +3298,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G101" t="n">
-        <v>1.45497560501099</v>
+        <v>1.4549754858017</v>
       </c>
       <c r="H101" t="n">
         <v>241430</v>
@@ -3414,7 +3414,7 @@
         <v>2.25699996948242</v>
       </c>
       <c r="G105" t="n">
-        <v>1.39147460460663</v>
+        <v>1.39147448539734</v>
       </c>
       <c r="H105" t="n">
         <v>153134</v>
@@ -3472,7 +3472,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>1.33475518226624</v>
+        <v>1.33475506305695</v>
       </c>
       <c r="H107" t="n">
         <v>364496</v>
@@ -3588,7 +3588,7 @@
         <v>2.18899989128113</v>
       </c>
       <c r="G111" t="n">
-        <v>1.34955132007599</v>
+        <v>1.34955155849457</v>
       </c>
       <c r="H111" t="n">
         <v>386160</v>
@@ -3907,7 +3907,7 @@
         <v>2.22099995613098</v>
       </c>
       <c r="G122" t="n">
-        <v>1.3692798614502</v>
+        <v>1.36927998065948</v>
       </c>
       <c r="H122" t="n">
         <v>2110801</v>
@@ -4023,7 +4023,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G126" t="n">
-        <v>1.29344868659973</v>
+        <v>1.29344880580902</v>
       </c>
       <c r="H126" t="n">
         <v>553530</v>
@@ -4226,7 +4226,7 @@
         <v>2.02699995040894</v>
       </c>
       <c r="G133" t="n">
-        <v>1.24967610836029</v>
+        <v>1.249675989151</v>
       </c>
       <c r="H133" t="n">
         <v>1799201</v>
@@ -4255,7 +4255,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>1.28543388843536</v>
+        <v>1.28543400764465</v>
       </c>
       <c r="H134" t="n">
         <v>1315577</v>
@@ -4371,7 +4371,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G138" t="n">
-        <v>1.32304131984711</v>
+        <v>1.3230414390564</v>
       </c>
       <c r="H138" t="n">
         <v>662539</v>
@@ -4400,7 +4400,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G139" t="n">
-        <v>1.27002108097076</v>
+        <v>1.27002096176147</v>
       </c>
       <c r="H139" t="n">
         <v>1000781</v>
@@ -4429,7 +4429,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G140" t="n">
-        <v>1.27926874160767</v>
+        <v>1.27926886081696</v>
       </c>
       <c r="H140" t="n">
         <v>489036</v>
@@ -4458,7 +4458,7 @@
         <v>2.08400011062622</v>
       </c>
       <c r="G141" t="n">
-        <v>1.28481733798981</v>
+        <v>1.2848174571991</v>
       </c>
       <c r="H141" t="n">
         <v>2061793</v>
@@ -4487,7 +4487,7 @@
         <v>2.125</v>
       </c>
       <c r="G142" t="n">
-        <v>1.31009447574615</v>
+        <v>1.31009459495544</v>
       </c>
       <c r="H142" t="n">
         <v>1089881</v>
@@ -4516,7 +4516,7 @@
         <v>2.19099998474121</v>
       </c>
       <c r="G143" t="n">
-        <v>1.3507844209671</v>
+        <v>1.35078454017639</v>
       </c>
       <c r="H143" t="n">
         <v>662529</v>
@@ -4574,7 +4574,7 @@
         <v>2.30900001525879</v>
       </c>
       <c r="G145" t="n">
-        <v>1.42353343963623</v>
+        <v>1.42353332042694</v>
       </c>
       <c r="H145" t="n">
         <v>1061376</v>
@@ -4661,7 +4661,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G148" t="n">
-        <v>1.35633325576782</v>
+        <v>1.35633313655853</v>
       </c>
       <c r="H148" t="n">
         <v>470520</v>
@@ -4806,7 +4806,7 @@
         <v>2.02099990844727</v>
       </c>
       <c r="G153" t="n">
-        <v>1.24597680568695</v>
+        <v>1.24597692489624</v>
       </c>
       <c r="H153" t="n">
         <v>550560</v>
@@ -4922,7 +4922,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G157" t="n">
-        <v>1.30392932891846</v>
+        <v>1.30392944812775</v>
       </c>
       <c r="H157" t="n">
         <v>621284</v>
@@ -4951,7 +4951,7 @@
         <v>2.05100011825562</v>
       </c>
       <c r="G158" t="n">
-        <v>1.26447248458862</v>
+        <v>1.26447260379791</v>
       </c>
       <c r="H158" t="n">
         <v>1072201</v>
@@ -5038,7 +5038,7 @@
         <v>2.08899998664856</v>
       </c>
       <c r="G161" t="n">
-        <v>1.2878999710083</v>
+        <v>1.28790009021759</v>
       </c>
       <c r="H161" t="n">
         <v>544349</v>
@@ -5154,7 +5154,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G165" t="n">
-        <v>1.30701184272766</v>
+        <v>1.30701196193695</v>
       </c>
       <c r="H165" t="n">
         <v>871972</v>
@@ -5183,7 +5183,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G166" t="n">
-        <v>1.28543388843536</v>
+        <v>1.28543400764465</v>
       </c>
       <c r="H166" t="n">
         <v>925875</v>
@@ -5357,7 +5357,7 @@
         <v>1.68299996852875</v>
       </c>
       <c r="G172" t="n">
-        <v>1.1859073638916</v>
+        <v>1.18590748310089</v>
       </c>
       <c r="H172" t="n">
         <v>1157709</v>
@@ -5502,7 +5502,7 @@
         <v>1.4889999628067</v>
       </c>
       <c r="G177" t="n">
-        <v>1.04920744895935</v>
+        <v>1.04920732975006</v>
       </c>
       <c r="H177" t="n">
         <v>2864868</v>
@@ -5531,7 +5531,7 @@
         <v>1.43900001049042</v>
       </c>
       <c r="G178" t="n">
-        <v>1.01397562026978</v>
+        <v>1.01397550106049</v>
       </c>
       <c r="H178" t="n">
         <v>1366037</v>
@@ -5937,7 +5937,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G192" t="n">
-        <v>1.14715242385864</v>
+        <v>1.14715230464935</v>
       </c>
       <c r="H192" t="n">
         <v>1257403</v>
@@ -5966,7 +5966,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>1.15913116931915</v>
+        <v>1.15913105010986</v>
       </c>
       <c r="H193" t="n">
         <v>574328</v>
@@ -6024,7 +6024,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G195" t="n">
-        <v>1.16265428066254</v>
+        <v>1.16265439987183</v>
       </c>
       <c r="H195" t="n">
         <v>1118932</v>
@@ -6227,7 +6227,7 @@
         <v>1.78199994564056</v>
       </c>
       <c r="G202" t="n">
-        <v>1.2556666135788</v>
+        <v>1.25566673278809</v>
       </c>
       <c r="H202" t="n">
         <v>682872</v>
@@ -6517,7 +6517,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G212" t="n">
-        <v>1.29371726512909</v>
+        <v>1.2937171459198</v>
       </c>
       <c r="H212" t="n">
         <v>773982</v>
@@ -6691,7 +6691,7 @@
         <v>2.01900005340576</v>
       </c>
       <c r="G218" t="n">
-        <v>1.42266607284546</v>
+        <v>1.42266619205475</v>
       </c>
       <c r="H218" t="n">
         <v>2210201</v>
@@ -6749,7 +6749,7 @@
         <v>2.01900005340576</v>
       </c>
       <c r="G220" t="n">
-        <v>1.42266607284546</v>
+        <v>1.42266619205475</v>
       </c>
       <c r="H220" t="n">
         <v>731881</v>
@@ -6807,7 +6807,7 @@
         <v>2.0090000629425</v>
       </c>
       <c r="G222" t="n">
-        <v>1.4156197309494</v>
+        <v>1.41561985015869</v>
       </c>
       <c r="H222" t="n">
         <v>1297053</v>
@@ -6894,7 +6894,7 @@
         <v>1.98300004005432</v>
       </c>
       <c r="G225" t="n">
-        <v>1.39729917049408</v>
+        <v>1.39729928970337</v>
       </c>
       <c r="H225" t="n">
         <v>1086938</v>
@@ -6952,7 +6952,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G227" t="n">
-        <v>1.33035838603973</v>
+        <v>1.33035850524902</v>
       </c>
       <c r="H227" t="n">
         <v>521176</v>
@@ -7329,7 +7329,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G240" t="n">
-        <v>1.27891981601715</v>
+        <v>1.27891993522644</v>
       </c>
       <c r="H240" t="n">
         <v>206556</v>
@@ -7822,7 +7822,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G257" t="n">
-        <v>1.37052285671234</v>
+        <v>1.37052297592163</v>
       </c>
       <c r="H257" t="n">
         <v>453008</v>
@@ -7880,7 +7880,7 @@
         <v>1.98800003528595</v>
       </c>
       <c r="G259" t="n">
-        <v>1.40082228183746</v>
+        <v>1.40082240104675</v>
       </c>
       <c r="H259" t="n">
         <v>688541</v>
@@ -7909,7 +7909,7 @@
         <v>1.96099996566772</v>
       </c>
       <c r="G260" t="n">
-        <v>1.3817971944809</v>
+        <v>1.38179707527161</v>
       </c>
       <c r="H260" t="n">
         <v>487506</v>
@@ -7967,7 +7967,7 @@
         <v>2.00600004196167</v>
       </c>
       <c r="G262" t="n">
-        <v>1.4135057926178</v>
+        <v>1.41350591182709</v>
       </c>
       <c r="H262" t="n">
         <v>717038</v>
@@ -8054,7 +8054,7 @@
         <v>2.01300001144409</v>
       </c>
       <c r="G265" t="n">
-        <v>1.41843831539154</v>
+        <v>1.41843843460083</v>
       </c>
       <c r="H265" t="n">
         <v>1394290</v>
@@ -8199,7 +8199,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G270" t="n">
-        <v>1.55161499977112</v>
+        <v>1.55161511898041</v>
       </c>
       <c r="H270" t="n">
         <v>421095</v>
@@ -8315,7 +8315,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G274" t="n">
-        <v>1.48678815364838</v>
+        <v>1.48678827285767</v>
       </c>
       <c r="H274" t="n">
         <v>214455</v>
@@ -8808,7 +8808,7 @@
         <v>2.14100003242493</v>
       </c>
       <c r="G291" t="n">
-        <v>1.50863206386566</v>
+        <v>1.50863218307495</v>
       </c>
       <c r="H291" t="n">
         <v>308198</v>
@@ -8837,7 +8837,7 @@
         <v>2.12400007247925</v>
       </c>
       <c r="G292" t="n">
-        <v>1.49665331840515</v>
+        <v>1.49665343761444</v>
       </c>
       <c r="H292" t="n">
         <v>280648</v>
@@ -8895,7 +8895,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G294" t="n">
-        <v>1.46705842018127</v>
+        <v>1.46705853939056</v>
       </c>
       <c r="H294" t="n">
         <v>796702</v>
@@ -9011,7 +9011,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G298" t="n">
-        <v>1.4755140542984</v>
+        <v>1.47551417350769</v>
       </c>
       <c r="H298" t="n">
         <v>739456</v>
@@ -9040,7 +9040,7 @@
         <v>2.11299991607666</v>
       </c>
       <c r="G299" t="n">
-        <v>1.48890209197998</v>
+        <v>1.48890221118927</v>
       </c>
       <c r="H299" t="n">
         <v>234428</v>
@@ -9069,7 +9069,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G300" t="n">
-        <v>1.51215517520905</v>
+        <v>1.51215529441833</v>
       </c>
       <c r="H300" t="n">
         <v>616627</v>
@@ -9533,7 +9533,7 @@
         <v>2.27300000190735</v>
       </c>
       <c r="G316" t="n">
-        <v>1.60164451599121</v>
+        <v>1.60164439678192</v>
       </c>
       <c r="H316" t="n">
         <v>370098</v>
@@ -9562,7 +9562,7 @@
         <v>2.27300000190735</v>
       </c>
       <c r="G317" t="n">
-        <v>1.60164451599121</v>
+        <v>1.60164439678192</v>
       </c>
       <c r="H317" t="n">
         <v>460584</v>
@@ -9707,7 +9707,7 @@
         <v>2.27699995040894</v>
       </c>
       <c r="G322" t="n">
-        <v>1.60446286201477</v>
+        <v>1.60446298122406</v>
       </c>
       <c r="H322" t="n">
         <v>327351</v>
@@ -9765,7 +9765,7 @@
         <v>2.2590000629425</v>
       </c>
       <c r="G324" t="n">
-        <v>1.59177947044373</v>
+        <v>1.59177935123444</v>
       </c>
       <c r="H324" t="n">
         <v>573058</v>
@@ -9881,7 +9881,7 @@
         <v>2.12400007247925</v>
       </c>
       <c r="G328" t="n">
-        <v>1.49665331840515</v>
+        <v>1.49665343761444</v>
       </c>
       <c r="H328" t="n">
         <v>467462</v>
@@ -9939,7 +9939,7 @@
         <v>2.19899988174438</v>
       </c>
       <c r="G330" t="n">
-        <v>1.54950106143951</v>
+        <v>1.5495011806488</v>
       </c>
       <c r="H330" t="n">
         <v>398017</v>
@@ -10026,7 +10026,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G333" t="n">
-        <v>1.54456865787506</v>
+        <v>1.54456877708435</v>
       </c>
       <c r="H333" t="n">
         <v>544104</v>
@@ -10084,7 +10084,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G335" t="n">
-        <v>1.57698214054108</v>
+        <v>1.57698202133179</v>
       </c>
       <c r="H335" t="n">
         <v>717837</v>
@@ -10142,7 +10142,7 @@
         <v>2.28299999237061</v>
       </c>
       <c r="G337" t="n">
-        <v>1.60869085788727</v>
+        <v>1.60869073867798</v>
       </c>
       <c r="H337" t="n">
         <v>602165</v>
@@ -10171,7 +10171,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G338" t="n">
-        <v>1.59671199321747</v>
+        <v>1.59671187400818</v>
       </c>
       <c r="H338" t="n">
         <v>425896</v>
@@ -10229,7 +10229,7 @@
         <v>2.40300011634827</v>
       </c>
       <c r="G340" t="n">
-        <v>1.6932475566864</v>
+        <v>1.69324779510498</v>
       </c>
       <c r="H340" t="n">
         <v>735566</v>
@@ -10345,7 +10345,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G344" t="n">
-        <v>1.66294801235199</v>
+        <v>1.6629478931427</v>
       </c>
       <c r="H344" t="n">
         <v>625059</v>
@@ -10519,7 +10519,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G350" t="n">
-        <v>1.55161499977112</v>
+        <v>1.55161511898041</v>
       </c>
       <c r="H350" t="n">
         <v>673952</v>
@@ -10577,7 +10577,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G352" t="n">
-        <v>1.56429851055145</v>
+        <v>1.56429862976074</v>
       </c>
       <c r="H352" t="n">
         <v>413799</v>
@@ -10606,7 +10606,7 @@
         <v>2.27099990844727</v>
       </c>
       <c r="G353" t="n">
-        <v>1.60023510456085</v>
+        <v>1.60023522377014</v>
       </c>
       <c r="H353" t="n">
         <v>454310</v>
@@ -10751,7 +10751,7 @@
         <v>2.7574999332428</v>
       </c>
       <c r="G358" t="n">
-        <v>1.94304192066193</v>
+        <v>1.94304215908051</v>
       </c>
       <c r="H358" t="n">
         <v>5360863</v>
@@ -10780,7 +10780,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G359" t="n">
-        <v>1.8672935962677</v>
+        <v>1.86729347705841</v>
       </c>
       <c r="H359" t="n">
         <v>1790824</v>
@@ -10809,7 +10809,7 @@
         <v>2.69749999046326</v>
       </c>
       <c r="G360" t="n">
-        <v>1.90076386928558</v>
+        <v>1.900763630867</v>
       </c>
       <c r="H360" t="n">
         <v>2325561</v>
@@ -10925,7 +10925,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G364" t="n">
-        <v>1.7968293428421</v>
+        <v>1.79682958126068</v>
       </c>
       <c r="H364" t="n">
         <v>380123</v>
@@ -10954,7 +10954,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G365" t="n">
-        <v>1.79330611228943</v>
+        <v>1.79330635070801</v>
       </c>
       <c r="H365" t="n">
         <v>341518</v>
@@ -11012,7 +11012,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G367" t="n">
-        <v>1.75736963748932</v>
+        <v>1.75736975669861</v>
       </c>
       <c r="H367" t="n">
         <v>543237</v>
@@ -11041,7 +11041,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G368" t="n">
-        <v>1.78625988960266</v>
+        <v>1.78626012802124</v>
       </c>
       <c r="H368" t="n">
         <v>410264</v>
@@ -35523,6 +35523,35 @@
         <v>1353239</v>
       </c>
       <c r="I1212" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1213" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1213" t="n">
+        <v>2.09800004959106</v>
+      </c>
+      <c r="D1213" t="n">
+        <v>2.12400007247925</v>
+      </c>
+      <c r="E1213" t="n">
+        <v>2.09200000762939</v>
+      </c>
+      <c r="F1213" t="n">
+        <v>2.09800004959106</v>
+      </c>
+      <c r="G1213" t="n">
+        <v>2.09800004959106</v>
+      </c>
+      <c r="H1213" t="n">
+        <v>1337072</v>
+      </c>
+      <c r="I1213" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MFEA.MI.xlsx
+++ b/data/MFEA.MI.xlsx
@@ -456,7 +456,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G3" t="n">
-        <v>2.25028014183044</v>
+        <v>2.25028038024902</v>
       </c>
       <c r="H3" t="n">
         <v>367297</v>
@@ -543,7 +543,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G6" t="n">
-        <v>2.28727102279663</v>
+        <v>2.28727078437805</v>
       </c>
       <c r="H6" t="n">
         <v>214912</v>
@@ -659,7 +659,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>2.33659195899963</v>
+        <v>2.33659219741821</v>
       </c>
       <c r="H10" t="n">
         <v>166086</v>
@@ -688,7 +688,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G11" t="n">
-        <v>2.31501436233521</v>
+        <v>2.31501412391663</v>
       </c>
       <c r="H11" t="n">
         <v>127118</v>
@@ -862,7 +862,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G17" t="n">
-        <v>2.69417095184326</v>
+        <v>2.69417071342468</v>
       </c>
       <c r="H17" t="n">
         <v>431766</v>
@@ -949,7 +949,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G20" t="n">
-        <v>2.61710619926453</v>
+        <v>2.61710667610168</v>
       </c>
       <c r="H20" t="n">
         <v>162925</v>
@@ -1007,7 +1007,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G22" t="n">
-        <v>2.5955286026001</v>
+        <v>2.59552812576294</v>
       </c>
       <c r="H22" t="n">
         <v>210917</v>
@@ -1036,7 +1036,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G23" t="n">
-        <v>2.49688625335693</v>
+        <v>2.49688601493835</v>
       </c>
       <c r="H23" t="n">
         <v>230967</v>
@@ -1123,7 +1123,7 @@
         <v>3.94250011444092</v>
       </c>
       <c r="G26" t="n">
-        <v>2.43061089515686</v>
+        <v>2.43061065673828</v>
       </c>
       <c r="H26" t="n">
         <v>264886</v>
@@ -1152,7 +1152,7 @@
         <v>3.98250007629395</v>
       </c>
       <c r="G27" t="n">
-        <v>2.45527124404907</v>
+        <v>2.45527148246765</v>
       </c>
       <c r="H27" t="n">
         <v>73167</v>
@@ -1268,7 +1268,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G31" t="n">
-        <v>2.40440893173218</v>
+        <v>2.4044086933136</v>
       </c>
       <c r="H31" t="n">
         <v>128224</v>
@@ -1384,7 +1384,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G35" t="n">
-        <v>2.48455572128296</v>
+        <v>2.48455595970154</v>
       </c>
       <c r="H35" t="n">
         <v>267519</v>
@@ -1645,7 +1645,7 @@
         <v>3.3675000667572</v>
       </c>
       <c r="G44" t="n">
-        <v>2.07611465454102</v>
+        <v>2.07611441612244</v>
       </c>
       <c r="H44" t="n">
         <v>214683</v>
@@ -1703,7 +1703,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G46" t="n">
-        <v>2.02525210380554</v>
+        <v>2.02525186538696</v>
       </c>
       <c r="H46" t="n">
         <v>426915</v>
@@ -1732,7 +1732,7 @@
         <v>3.26749992370605</v>
       </c>
       <c r="G47" t="n">
-        <v>2.01446318626404</v>
+        <v>2.01446294784546</v>
       </c>
       <c r="H47" t="n">
         <v>127552</v>
@@ -1761,7 +1761,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G48" t="n">
-        <v>2.03141713142395</v>
+        <v>2.03141736984253</v>
       </c>
       <c r="H48" t="n">
         <v>198901</v>
@@ -1819,7 +1819,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G50" t="n">
-        <v>2.02525210380554</v>
+        <v>2.02525186538696</v>
       </c>
       <c r="H50" t="n">
         <v>165272</v>
@@ -1848,7 +1848,7 @@
         <v>3.17750000953674</v>
       </c>
       <c r="G51" t="n">
-        <v>1.95897674560547</v>
+        <v>1.95897686481476</v>
       </c>
       <c r="H51" t="n">
         <v>400267</v>
@@ -1877,7 +1877,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G52" t="n">
-        <v>1.99442613124847</v>
+        <v>1.99442601203918</v>
       </c>
       <c r="H52" t="n">
         <v>186459</v>
@@ -1906,7 +1906,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G53" t="n">
-        <v>1.97593080997467</v>
+        <v>1.97593069076538</v>
       </c>
       <c r="H53" t="n">
         <v>157204</v>
@@ -1935,7 +1935,7 @@
         <v>3.1175000667572</v>
       </c>
       <c r="G54" t="n">
-        <v>1.92198586463928</v>
+        <v>1.92198574542999</v>
       </c>
       <c r="H54" t="n">
         <v>195501</v>
@@ -1964,7 +1964,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G55" t="n">
-        <v>1.82796704769135</v>
+        <v>1.82796716690063</v>
       </c>
       <c r="H55" t="n">
         <v>452826</v>
@@ -2080,7 +2080,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G59" t="n">
-        <v>1.79405879974365</v>
+        <v>1.79405891895294</v>
       </c>
       <c r="H59" t="n">
         <v>174796</v>
@@ -2109,7 +2109,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G60" t="n">
-        <v>1.79714119434357</v>
+        <v>1.79714143276215</v>
       </c>
       <c r="H60" t="n">
         <v>140935</v>
@@ -2138,7 +2138,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G61" t="n">
-        <v>1.80638909339905</v>
+        <v>1.80638921260834</v>
       </c>
       <c r="H61" t="n">
         <v>175025</v>
@@ -2167,7 +2167,7 @@
         <v>2.96250009536743</v>
       </c>
       <c r="G62" t="n">
-        <v>1.82642614841461</v>
+        <v>1.82642602920532</v>
       </c>
       <c r="H62" t="n">
         <v>167649</v>
@@ -2196,7 +2196,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G63" t="n">
-        <v>1.81255424022675</v>
+        <v>1.81255435943604</v>
       </c>
       <c r="H63" t="n">
         <v>134826</v>
@@ -2225,7 +2225,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G64" t="n">
-        <v>1.87728846073151</v>
+        <v>1.87728810310364</v>
       </c>
       <c r="H64" t="n">
         <v>324711</v>
@@ -2254,7 +2254,7 @@
         <v>2.89249992370605</v>
       </c>
       <c r="G65" t="n">
-        <v>1.78326976299286</v>
+        <v>1.78326964378357</v>
       </c>
       <c r="H65" t="n">
         <v>336035</v>
@@ -2283,7 +2283,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G66" t="n">
-        <v>1.713911652565</v>
+        <v>1.71391189098358</v>
       </c>
       <c r="H66" t="n">
         <v>344735</v>
@@ -2341,7 +2341,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G68" t="n">
-        <v>1.66150796413422</v>
+        <v>1.66150808334351</v>
       </c>
       <c r="H68" t="n">
         <v>213075</v>
@@ -2457,7 +2457,7 @@
         <v>2.88750004768372</v>
       </c>
       <c r="G72" t="n">
-        <v>1.78018724918365</v>
+        <v>1.78018736839294</v>
       </c>
       <c r="H72" t="n">
         <v>202748</v>
@@ -2486,7 +2486,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G73" t="n">
-        <v>1.74165487289429</v>
+        <v>1.74165523052216</v>
       </c>
       <c r="H73" t="n">
         <v>228203</v>
@@ -2515,7 +2515,7 @@
         <v>2.75</v>
       </c>
       <c r="G74" t="n">
-        <v>1.69541645050049</v>
+        <v>1.69541656970978</v>
       </c>
       <c r="H74" t="n">
         <v>168732</v>
@@ -2544,7 +2544,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G75" t="n">
-        <v>1.66150796413422</v>
+        <v>1.66150808334351</v>
       </c>
       <c r="H75" t="n">
         <v>331684</v>
@@ -2573,7 +2573,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G76" t="n">
-        <v>1.63376486301422</v>
+        <v>1.63376498222351</v>
       </c>
       <c r="H76" t="n">
         <v>246997</v>
@@ -2631,7 +2631,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G78" t="n">
-        <v>1.74782037734985</v>
+        <v>1.74782025814056</v>
       </c>
       <c r="H78" t="n">
         <v>522442</v>
@@ -2660,7 +2660,7 @@
         <v>2.66750001907349</v>
       </c>
       <c r="G79" t="n">
-        <v>1.6445540189743</v>
+        <v>1.64455413818359</v>
       </c>
       <c r="H79" t="n">
         <v>468659</v>
@@ -2689,7 +2689,7 @@
         <v>2.68249988555908</v>
       </c>
       <c r="G80" t="n">
-        <v>1.65380156040192</v>
+        <v>1.65380144119263</v>
       </c>
       <c r="H80" t="n">
         <v>289746</v>
@@ -2718,7 +2718,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G81" t="n">
-        <v>1.62143468856812</v>
+        <v>1.6214348077774</v>
       </c>
       <c r="H81" t="n">
         <v>237552</v>
@@ -2747,7 +2747,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G82" t="n">
-        <v>1.63068234920502</v>
+        <v>1.63068246841431</v>
       </c>
       <c r="H82" t="n">
         <v>172630</v>
@@ -2805,7 +2805,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G84" t="n">
-        <v>1.56594836711884</v>
+        <v>1.56594812870026</v>
       </c>
       <c r="H84" t="n">
         <v>392657</v>
@@ -2834,7 +2834,7 @@
         <v>2.58750009536743</v>
       </c>
       <c r="G85" t="n">
-        <v>1.59523272514343</v>
+        <v>1.59523260593414</v>
       </c>
       <c r="H85" t="n">
         <v>241301</v>
@@ -2921,7 +2921,7 @@
         <v>2.64750003814697</v>
       </c>
       <c r="G88" t="n">
-        <v>1.6322238445282</v>
+        <v>1.63222360610962</v>
       </c>
       <c r="H88" t="n">
         <v>842562</v>
@@ -2979,7 +2979,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G90" t="n">
-        <v>1.62143468856812</v>
+        <v>1.6214348077774</v>
       </c>
       <c r="H90" t="n">
         <v>381738</v>
@@ -3037,7 +3037,7 @@
         <v>2.66750001907349</v>
       </c>
       <c r="G92" t="n">
-        <v>1.6445540189743</v>
+        <v>1.64455413818359</v>
       </c>
       <c r="H92" t="n">
         <v>384701</v>
@@ -3066,7 +3066,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G93" t="n">
-        <v>1.63068234920502</v>
+        <v>1.63068246841431</v>
       </c>
       <c r="H93" t="n">
         <v>293851</v>
@@ -3095,7 +3095,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G94" t="n">
-        <v>1.63993012905121</v>
+        <v>1.63993000984192</v>
       </c>
       <c r="H94" t="n">
         <v>124415</v>
@@ -3153,7 +3153,7 @@
         <v>2.6324999332428</v>
       </c>
       <c r="G96" t="n">
-        <v>1.62297582626343</v>
+        <v>1.62297594547272</v>
       </c>
       <c r="H96" t="n">
         <v>316690</v>
@@ -3182,7 +3182,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G97" t="n">
-        <v>1.57827877998352</v>
+        <v>1.57827842235565</v>
       </c>
       <c r="H97" t="n">
         <v>975446</v>
@@ -3211,7 +3211,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G98" t="n">
-        <v>1.66459059715271</v>
+        <v>1.664590716362</v>
       </c>
       <c r="H98" t="n">
         <v>547180</v>
@@ -3269,7 +3269,7 @@
         <v>2.45300006866455</v>
       </c>
       <c r="G100" t="n">
-        <v>1.51231169700623</v>
+        <v>1.51231145858765</v>
       </c>
       <c r="H100" t="n">
         <v>588672</v>
@@ -3356,7 +3356,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G103" t="n">
-        <v>1.45867466926575</v>
+        <v>1.45867455005646</v>
       </c>
       <c r="H103" t="n">
         <v>277983</v>
@@ -3414,7 +3414,7 @@
         <v>2.25699996948242</v>
       </c>
       <c r="G105" t="n">
-        <v>1.39147448539734</v>
+        <v>1.39147436618805</v>
       </c>
       <c r="H105" t="n">
         <v>153134</v>
@@ -3443,7 +3443,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G106" t="n">
-        <v>1.39085781574249</v>
+        <v>1.39085805416107</v>
       </c>
       <c r="H106" t="n">
         <v>262719</v>
@@ -3588,7 +3588,7 @@
         <v>2.18899989128113</v>
       </c>
       <c r="G111" t="n">
-        <v>1.34955155849457</v>
+        <v>1.34955143928528</v>
       </c>
       <c r="H111" t="n">
         <v>386160</v>
@@ -3617,7 +3617,7 @@
         <v>2.24900007247925</v>
       </c>
       <c r="G112" t="n">
-        <v>1.38654232025146</v>
+        <v>1.38654255867004</v>
       </c>
       <c r="H112" t="n">
         <v>617377</v>
@@ -3733,7 +3733,7 @@
         <v>2.28900003433228</v>
       </c>
       <c r="G116" t="n">
-        <v>1.41120302677155</v>
+        <v>1.41120278835297</v>
       </c>
       <c r="H116" t="n">
         <v>1034023</v>
@@ -3791,7 +3791,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G118" t="n">
-        <v>1.34708547592163</v>
+        <v>1.34708535671234</v>
       </c>
       <c r="H118" t="n">
         <v>844960</v>
@@ -3820,7 +3820,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G119" t="n">
-        <v>1.38099372386932</v>
+        <v>1.38099384307861</v>
       </c>
       <c r="H119" t="n">
         <v>296846</v>
@@ -3849,7 +3849,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G120" t="n">
-        <v>1.37236249446869</v>
+        <v>1.37236261367798</v>
       </c>
       <c r="H120" t="n">
         <v>898674</v>
@@ -3965,7 +3965,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G124" t="n">
-        <v>1.27125418186188</v>
+        <v>1.27125406265259</v>
       </c>
       <c r="H124" t="n">
         <v>589312</v>
@@ -3994,7 +3994,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G125" t="n">
-        <v>1.23919534683228</v>
+        <v>1.23919522762299</v>
       </c>
       <c r="H125" t="n">
         <v>572938</v>
@@ -4023,7 +4023,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G126" t="n">
-        <v>1.29344880580902</v>
+        <v>1.29344856739044</v>
       </c>
       <c r="H126" t="n">
         <v>553530</v>
@@ -4110,7 +4110,7 @@
         <v>2.13700008392334</v>
       </c>
       <c r="G129" t="n">
-        <v>1.31749284267426</v>
+        <v>1.31749272346497</v>
       </c>
       <c r="H129" t="n">
         <v>756330</v>
@@ -4139,7 +4139,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G130" t="n">
-        <v>1.37791109085083</v>
+        <v>1.37791097164154</v>
       </c>
       <c r="H130" t="n">
         <v>658168</v>
@@ -4168,7 +4168,7 @@
         <v>2.21399998664856</v>
       </c>
       <c r="G131" t="n">
-        <v>1.36496424674988</v>
+        <v>1.36496436595917</v>
       </c>
       <c r="H131" t="n">
         <v>425795</v>
@@ -4226,7 +4226,7 @@
         <v>2.02699995040894</v>
       </c>
       <c r="G133" t="n">
-        <v>1.249675989151</v>
+        <v>1.24967586994171</v>
       </c>
       <c r="H133" t="n">
         <v>1799201</v>
@@ -4313,7 +4313,7 @@
         <v>2.20099997520447</v>
       </c>
       <c r="G136" t="n">
-        <v>1.35694968700409</v>
+        <v>1.3569495677948</v>
       </c>
       <c r="H136" t="n">
         <v>597261</v>
@@ -4371,7 +4371,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G138" t="n">
-        <v>1.3230414390564</v>
+        <v>1.32304120063782</v>
       </c>
       <c r="H138" t="n">
         <v>662539</v>
@@ -4458,7 +4458,7 @@
         <v>2.08400011062622</v>
       </c>
       <c r="G141" t="n">
-        <v>1.2848174571991</v>
+        <v>1.28481733798981</v>
       </c>
       <c r="H141" t="n">
         <v>2061793</v>
@@ -4487,7 +4487,7 @@
         <v>2.125</v>
       </c>
       <c r="G142" t="n">
-        <v>1.31009459495544</v>
+        <v>1.31009435653687</v>
       </c>
       <c r="H142" t="n">
         <v>1089881</v>
@@ -4545,7 +4545,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G144" t="n">
-        <v>1.35386729240417</v>
+        <v>1.35386717319489</v>
       </c>
       <c r="H144" t="n">
         <v>698399</v>
@@ -4574,7 +4574,7 @@
         <v>2.30900001525879</v>
       </c>
       <c r="G145" t="n">
-        <v>1.42353332042694</v>
+        <v>1.42353320121765</v>
       </c>
       <c r="H145" t="n">
         <v>1061376</v>
@@ -4719,7 +4719,7 @@
         <v>2.04699993133545</v>
       </c>
       <c r="G150" t="n">
-        <v>1.26200640201569</v>
+        <v>1.26200616359711</v>
       </c>
       <c r="H150" t="n">
         <v>1302379</v>
@@ -4748,7 +4748,7 @@
         <v>2.07100009918213</v>
       </c>
       <c r="G151" t="n">
-        <v>1.27680277824402</v>
+        <v>1.27680265903473</v>
       </c>
       <c r="H151" t="n">
         <v>802560</v>
@@ -4777,7 +4777,7 @@
         <v>2.05299997329712</v>
       </c>
       <c r="G152" t="n">
-        <v>1.26570534706116</v>
+        <v>1.26570546627045</v>
       </c>
       <c r="H152" t="n">
         <v>460461</v>
@@ -4922,7 +4922,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G157" t="n">
-        <v>1.30392944812775</v>
+        <v>1.30392920970917</v>
       </c>
       <c r="H157" t="n">
         <v>621284</v>
@@ -4951,7 +4951,7 @@
         <v>2.05100011825562</v>
       </c>
       <c r="G158" t="n">
-        <v>1.26447260379791</v>
+        <v>1.26447248458862</v>
       </c>
       <c r="H158" t="n">
         <v>1072201</v>
@@ -5038,7 +5038,7 @@
         <v>2.08899998664856</v>
       </c>
       <c r="G161" t="n">
-        <v>1.28790009021759</v>
+        <v>1.2878999710083</v>
       </c>
       <c r="H161" t="n">
         <v>544349</v>
@@ -5125,7 +5125,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G164" t="n">
-        <v>1.31625974178314</v>
+        <v>1.31625962257385</v>
       </c>
       <c r="H164" t="n">
         <v>1321946</v>
@@ -5328,7 +5328,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G171" t="n">
-        <v>1.20140957832336</v>
+        <v>1.20140945911407</v>
       </c>
       <c r="H171" t="n">
         <v>1719560</v>
@@ -5357,7 +5357,7 @@
         <v>1.68299996852875</v>
       </c>
       <c r="G172" t="n">
-        <v>1.18590748310089</v>
+        <v>1.18590724468231</v>
       </c>
       <c r="H172" t="n">
         <v>1157709</v>
@@ -5415,7 +5415,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G174" t="n">
-        <v>1.14151525497437</v>
+        <v>1.14151513576508</v>
       </c>
       <c r="H174" t="n">
         <v>1315279</v>
@@ -5531,7 +5531,7 @@
         <v>1.43900001049042</v>
       </c>
       <c r="G178" t="n">
-        <v>1.01397550106049</v>
+        <v>1.01397562026978</v>
       </c>
       <c r="H178" t="n">
         <v>1366037</v>
@@ -5589,7 +5589,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G180" t="n">
-        <v>1.08514404296875</v>
+        <v>1.08514416217804</v>
       </c>
       <c r="H180" t="n">
         <v>1913773</v>
@@ -5705,7 +5705,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G184" t="n">
-        <v>1.08796262741089</v>
+        <v>1.08796274662018</v>
       </c>
       <c r="H184" t="n">
         <v>1603167</v>
@@ -5734,7 +5734,7 @@
         <v>1.50899994373322</v>
       </c>
       <c r="G185" t="n">
-        <v>1.06330013275146</v>
+        <v>1.06330037117004</v>
       </c>
       <c r="H185" t="n">
         <v>762123</v>
@@ -5763,7 +5763,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G186" t="n">
-        <v>1.06752800941467</v>
+        <v>1.06752812862396</v>
       </c>
       <c r="H186" t="n">
         <v>688465</v>
@@ -5792,7 +5792,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G187" t="n">
-        <v>1.04850292205811</v>
+        <v>1.04850280284882</v>
       </c>
       <c r="H187" t="n">
         <v>343484</v>
@@ -5850,7 +5850,7 @@
         <v>1.5110000371933</v>
       </c>
       <c r="G189" t="n">
-        <v>1.06470954418182</v>
+        <v>1.06470942497253</v>
       </c>
       <c r="H189" t="n">
         <v>1590572</v>
@@ -5879,7 +5879,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G190" t="n">
-        <v>1.11473894119263</v>
+        <v>1.11473882198334</v>
       </c>
       <c r="H190" t="n">
         <v>1164166</v>
@@ -5966,7 +5966,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>1.15913105010986</v>
+        <v>1.15913116931915</v>
       </c>
       <c r="H193" t="n">
         <v>574328</v>
@@ -5995,7 +5995,7 @@
         <v>1.62300002574921</v>
       </c>
       <c r="G194" t="n">
-        <v>1.14362907409668</v>
+        <v>1.14362919330597</v>
       </c>
       <c r="H194" t="n">
         <v>1339210</v>
@@ -6053,7 +6053,7 @@
         <v>1.68900001049042</v>
       </c>
       <c r="G196" t="n">
-        <v>1.19013524055481</v>
+        <v>1.1901353597641</v>
       </c>
       <c r="H196" t="n">
         <v>693474</v>
@@ -6111,7 +6111,7 @@
         <v>1.78699994087219</v>
       </c>
       <c r="G198" t="n">
-        <v>1.25918984413147</v>
+        <v>1.25918972492218</v>
       </c>
       <c r="H198" t="n">
         <v>1728258</v>
@@ -6198,7 +6198,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G201" t="n">
-        <v>1.25778067111969</v>
+        <v>1.2577805519104</v>
       </c>
       <c r="H201" t="n">
         <v>515449</v>
@@ -6227,7 +6227,7 @@
         <v>1.78199994564056</v>
       </c>
       <c r="G202" t="n">
-        <v>1.25566673278809</v>
+        <v>1.2556666135788</v>
       </c>
       <c r="H202" t="n">
         <v>682872</v>
@@ -6256,7 +6256,7 @@
         <v>1.74600005149841</v>
       </c>
       <c r="G203" t="n">
-        <v>1.23029971122742</v>
+        <v>1.23029983043671</v>
       </c>
       <c r="H203" t="n">
         <v>753784</v>
@@ -6314,7 +6314,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G205" t="n">
-        <v>1.30499136447906</v>
+        <v>1.30499148368835</v>
       </c>
       <c r="H205" t="n">
         <v>1053905</v>
@@ -6343,7 +6343,7 @@
         <v>1.84399998188019</v>
       </c>
       <c r="G206" t="n">
-        <v>1.29935431480408</v>
+        <v>1.29935419559479</v>
       </c>
       <c r="H206" t="n">
         <v>1182791</v>
@@ -6372,7 +6372,7 @@
         <v>1.83899998664856</v>
       </c>
       <c r="G207" t="n">
-        <v>1.2958310842514</v>
+        <v>1.29583120346069</v>
       </c>
       <c r="H207" t="n">
         <v>359958</v>
@@ -6517,7 +6517,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G212" t="n">
-        <v>1.2937171459198</v>
+        <v>1.29371726512909</v>
       </c>
       <c r="H212" t="n">
         <v>773982</v>
@@ -6546,7 +6546,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G213" t="n">
-        <v>1.28737556934357</v>
+        <v>1.28737545013428</v>
       </c>
       <c r="H213" t="n">
         <v>677501</v>
@@ -6633,7 +6633,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G216" t="n">
-        <v>1.28596615791321</v>
+        <v>1.2859662771225</v>
       </c>
       <c r="H216" t="n">
         <v>274038</v>
@@ -6720,7 +6720,7 @@
         <v>2.04699993133545</v>
       </c>
       <c r="G219" t="n">
-        <v>1.44239604473114</v>
+        <v>1.44239592552185</v>
       </c>
       <c r="H219" t="n">
         <v>1110213</v>
@@ -6952,7 +6952,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G227" t="n">
-        <v>1.33035850524902</v>
+        <v>1.33035838603973</v>
       </c>
       <c r="H227" t="n">
         <v>521176</v>
@@ -7039,7 +7039,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G230" t="n">
-        <v>1.29442191123962</v>
+        <v>1.29442179203033</v>
       </c>
       <c r="H230" t="n">
         <v>689236</v>
@@ -7184,7 +7184,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G235" t="n">
-        <v>1.25778067111969</v>
+        <v>1.2577805519104</v>
       </c>
       <c r="H235" t="n">
         <v>235737</v>
@@ -7329,7 +7329,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G240" t="n">
-        <v>1.27891993522644</v>
+        <v>1.27891981601715</v>
       </c>
       <c r="H240" t="n">
         <v>206556</v>
@@ -7358,7 +7358,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G241" t="n">
-        <v>1.26482689380646</v>
+        <v>1.26482701301575</v>
       </c>
       <c r="H241" t="n">
         <v>338837</v>
@@ -7416,7 +7416,7 @@
         <v>1.807000041008</v>
       </c>
       <c r="G243" t="n">
-        <v>1.27328276634216</v>
+        <v>1.27328264713287</v>
       </c>
       <c r="H243" t="n">
         <v>162393</v>
@@ -7503,7 +7503,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G246" t="n">
-        <v>1.36277186870575</v>
+        <v>1.36277174949646</v>
       </c>
       <c r="H246" t="n">
         <v>570217</v>
@@ -7532,7 +7532,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G247" t="n">
-        <v>1.38109242916107</v>
+        <v>1.38109254837036</v>
       </c>
       <c r="H247" t="n">
         <v>439371</v>
@@ -7561,7 +7561,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G248" t="n">
-        <v>1.37263679504395</v>
+        <v>1.37263667583466</v>
       </c>
       <c r="H248" t="n">
         <v>452614</v>
@@ -7590,7 +7590,7 @@
         <v>1.94099998474121</v>
       </c>
       <c r="G249" t="n">
-        <v>1.36770439147949</v>
+        <v>1.3677042722702</v>
       </c>
       <c r="H249" t="n">
         <v>394746</v>
@@ -7648,7 +7648,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G251" t="n">
-        <v>1.38602495193481</v>
+        <v>1.38602483272552</v>
       </c>
       <c r="H251" t="n">
         <v>191879</v>
@@ -7677,7 +7677,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G252" t="n">
-        <v>1.35713481903076</v>
+        <v>1.35713469982147</v>
       </c>
       <c r="H252" t="n">
         <v>504498</v>
@@ -7706,7 +7706,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G253" t="n">
-        <v>1.32824444770813</v>
+        <v>1.32824456691742</v>
       </c>
       <c r="H253" t="n">
         <v>496653</v>
@@ -7735,7 +7735,7 @@
         <v>1.95099997520447</v>
       </c>
       <c r="G254" t="n">
-        <v>1.37475061416626</v>
+        <v>1.37475073337555</v>
       </c>
       <c r="H254" t="n">
         <v>410471</v>
@@ -7764,7 +7764,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G255" t="n">
-        <v>1.41984760761261</v>
+        <v>1.4198477268219</v>
       </c>
       <c r="H255" t="n">
         <v>809777</v>
@@ -7793,7 +7793,7 @@
         <v>1.98699998855591</v>
       </c>
       <c r="G256" t="n">
-        <v>1.40011763572693</v>
+        <v>1.40011775493622</v>
       </c>
       <c r="H256" t="n">
         <v>400869</v>
@@ -7822,7 +7822,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G257" t="n">
-        <v>1.37052297592163</v>
+        <v>1.37052285671234</v>
       </c>
       <c r="H257" t="n">
         <v>453008</v>
@@ -7938,7 +7938,7 @@
         <v>1.942999958992</v>
       </c>
       <c r="G261" t="n">
-        <v>1.36911356449127</v>
+        <v>1.36911368370056</v>
       </c>
       <c r="H261" t="n">
         <v>657682</v>
@@ -7996,7 +7996,7 @@
         <v>1.97200000286102</v>
       </c>
       <c r="G263" t="n">
-        <v>1.38954818248749</v>
+        <v>1.3895480632782</v>
       </c>
       <c r="H263" t="n">
         <v>310392</v>
@@ -8054,7 +8054,7 @@
         <v>2.01300001144409</v>
       </c>
       <c r="G265" t="n">
-        <v>1.41843843460083</v>
+        <v>1.41843819618225</v>
       </c>
       <c r="H265" t="n">
         <v>1394290</v>
@@ -8141,7 +8141,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G268" t="n">
-        <v>1.56077527999878</v>
+        <v>1.56077539920807</v>
       </c>
       <c r="H268" t="n">
         <v>856015</v>
@@ -8199,7 +8199,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G270" t="n">
-        <v>1.55161511898041</v>
+        <v>1.55161499977112</v>
       </c>
       <c r="H270" t="n">
         <v>421095</v>
@@ -8228,7 +8228,7 @@
         <v>2.18300008773804</v>
       </c>
       <c r="G271" t="n">
-        <v>1.53822708129883</v>
+        <v>1.53822696208954</v>
       </c>
       <c r="H271" t="n">
         <v>558105</v>
@@ -8257,7 +8257,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G272" t="n">
-        <v>1.53329455852509</v>
+        <v>1.5332944393158</v>
       </c>
       <c r="H272" t="n">
         <v>539558</v>
@@ -8286,7 +8286,7 @@
         <v>2.125</v>
       </c>
       <c r="G273" t="n">
-        <v>1.4973578453064</v>
+        <v>1.49735796451569</v>
       </c>
       <c r="H273" t="n">
         <v>544273</v>
@@ -8373,7 +8373,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G276" t="n">
-        <v>1.48819756507874</v>
+        <v>1.48819768428802</v>
       </c>
       <c r="H276" t="n">
         <v>185994</v>
@@ -8431,7 +8431,7 @@
         <v>2.06699991226196</v>
       </c>
       <c r="G278" t="n">
-        <v>1.45648872852325</v>
+        <v>1.45648884773254</v>
       </c>
       <c r="H278" t="n">
         <v>289759</v>
@@ -8489,7 +8489,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G280" t="n">
-        <v>1.44450986385345</v>
+        <v>1.44450998306274</v>
       </c>
       <c r="H280" t="n">
         <v>636661</v>
@@ -8547,7 +8547,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G282" t="n">
-        <v>1.44450986385345</v>
+        <v>1.44450998306274</v>
       </c>
       <c r="H282" t="n">
         <v>502402</v>
@@ -8663,7 +8663,7 @@
         <v>2.05299997329712</v>
       </c>
       <c r="G286" t="n">
-        <v>1.44662380218506</v>
+        <v>1.44662392139435</v>
       </c>
       <c r="H286" t="n">
         <v>680373</v>
@@ -8721,7 +8721,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G288" t="n">
-        <v>1.4318265914917</v>
+        <v>1.43182647228241</v>
       </c>
       <c r="H288" t="n">
         <v>514101</v>
@@ -8895,7 +8895,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G294" t="n">
-        <v>1.46705853939056</v>
+        <v>1.46705842018127</v>
       </c>
       <c r="H294" t="n">
         <v>796702</v>
@@ -8953,7 +8953,7 @@
         <v>2.125</v>
       </c>
       <c r="G296" t="n">
-        <v>1.4973578453064</v>
+        <v>1.49735796451569</v>
       </c>
       <c r="H296" t="n">
         <v>636274</v>
@@ -9011,7 +9011,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G298" t="n">
-        <v>1.47551417350769</v>
+        <v>1.4755140542984</v>
       </c>
       <c r="H298" t="n">
         <v>739456</v>
@@ -9127,7 +9127,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G302" t="n">
-        <v>1.52202022075653</v>
+        <v>1.52202033996582</v>
       </c>
       <c r="H302" t="n">
         <v>208214</v>
@@ -9185,7 +9185,7 @@
         <v>2.06699991226196</v>
       </c>
       <c r="G304" t="n">
-        <v>1.45648872852325</v>
+        <v>1.45648884773254</v>
       </c>
       <c r="H304" t="n">
         <v>302700</v>
@@ -9214,7 +9214,7 @@
         <v>2.05599999427795</v>
       </c>
       <c r="G305" t="n">
-        <v>1.44873774051666</v>
+        <v>1.44873785972595</v>
       </c>
       <c r="H305" t="n">
         <v>446308</v>
@@ -9301,7 +9301,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G308" t="n">
-        <v>1.49383461475372</v>
+        <v>1.49383449554443</v>
       </c>
       <c r="H308" t="n">
         <v>190816</v>
@@ -9330,7 +9330,7 @@
         <v>2.1029999256134</v>
       </c>
       <c r="G309" t="n">
-        <v>1.48185586929321</v>
+        <v>1.48185575008392</v>
       </c>
       <c r="H309" t="n">
         <v>262297</v>
@@ -9388,7 +9388,7 @@
         <v>2.18300008773804</v>
       </c>
       <c r="G311" t="n">
-        <v>1.53822708129883</v>
+        <v>1.53822696208954</v>
       </c>
       <c r="H311" t="n">
         <v>1223387</v>
@@ -9417,7 +9417,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G312" t="n">
-        <v>1.58261919021606</v>
+        <v>1.58261930942535</v>
       </c>
       <c r="H312" t="n">
         <v>1349589</v>
@@ -9475,7 +9475,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G314" t="n">
-        <v>1.59600734710693</v>
+        <v>1.59600746631622</v>
       </c>
       <c r="H314" t="n">
         <v>377668</v>
@@ -9533,7 +9533,7 @@
         <v>2.27300000190735</v>
       </c>
       <c r="G316" t="n">
-        <v>1.60164439678192</v>
+        <v>1.60164451599121</v>
       </c>
       <c r="H316" t="n">
         <v>370098</v>
@@ -9562,7 +9562,7 @@
         <v>2.27300000190735</v>
       </c>
       <c r="G317" t="n">
-        <v>1.60164439678192</v>
+        <v>1.60164451599121</v>
       </c>
       <c r="H317" t="n">
         <v>460584</v>
@@ -9591,7 +9591,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G318" t="n">
-        <v>1.60305380821228</v>
+        <v>1.60305368900299</v>
       </c>
       <c r="H318" t="n">
         <v>434199</v>
@@ -9765,7 +9765,7 @@
         <v>2.2590000629425</v>
       </c>
       <c r="G324" t="n">
-        <v>1.59177935123444</v>
+        <v>1.59177958965302</v>
       </c>
       <c r="H324" t="n">
         <v>573058</v>
@@ -9939,7 +9939,7 @@
         <v>2.19899988174438</v>
       </c>
       <c r="G330" t="n">
-        <v>1.5495011806488</v>
+        <v>1.54950106143951</v>
       </c>
       <c r="H330" t="n">
         <v>398017</v>
@@ -9968,7 +9968,7 @@
         <v>2.25</v>
       </c>
       <c r="G331" t="n">
-        <v>1.58543765544891</v>
+        <v>1.58543789386749</v>
       </c>
       <c r="H331" t="n">
         <v>523276</v>
@@ -9997,7 +9997,7 @@
         <v>2.22099995613098</v>
       </c>
       <c r="G332" t="n">
-        <v>1.56500315666199</v>
+        <v>1.5650030374527</v>
       </c>
       <c r="H332" t="n">
         <v>221480</v>
@@ -10026,7 +10026,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G333" t="n">
-        <v>1.54456877708435</v>
+        <v>1.54456865787506</v>
       </c>
       <c r="H333" t="n">
         <v>544104</v>
@@ -10055,7 +10055,7 @@
         <v>2.25</v>
       </c>
       <c r="G334" t="n">
-        <v>1.58543765544891</v>
+        <v>1.58543789386749</v>
       </c>
       <c r="H334" t="n">
         <v>841797</v>
@@ -10084,7 +10084,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G335" t="n">
-        <v>1.57698202133179</v>
+        <v>1.5769819021225</v>
       </c>
       <c r="H335" t="n">
         <v>717837</v>
@@ -10200,7 +10200,7 @@
         <v>2.43099999427795</v>
       </c>
       <c r="G339" t="n">
-        <v>1.71297752857208</v>
+        <v>1.71297740936279</v>
       </c>
       <c r="H339" t="n">
         <v>1632236</v>
@@ -10229,7 +10229,7 @@
         <v>2.40300011634827</v>
       </c>
       <c r="G340" t="n">
-        <v>1.69324779510498</v>
+        <v>1.6932475566864</v>
       </c>
       <c r="H340" t="n">
         <v>735566</v>
@@ -10287,7 +10287,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>1.64533221721649</v>
+        <v>1.6453320980072</v>
       </c>
       <c r="H342" t="n">
         <v>505221</v>
@@ -10345,7 +10345,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G344" t="n">
-        <v>1.6629478931427</v>
+        <v>1.66294801235199</v>
       </c>
       <c r="H344" t="n">
         <v>625059</v>
@@ -10374,7 +10374,7 @@
         <v>2.33699989318848</v>
       </c>
       <c r="G345" t="n">
-        <v>1.64674127101898</v>
+        <v>1.64674115180969</v>
       </c>
       <c r="H345" t="n">
         <v>1238842</v>
@@ -10403,7 +10403,7 @@
         <v>2.33699989318848</v>
       </c>
       <c r="G346" t="n">
-        <v>1.64674127101898</v>
+        <v>1.64674115180969</v>
       </c>
       <c r="H346" t="n">
         <v>580707</v>
@@ -10461,7 +10461,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G348" t="n">
-        <v>1.56148016452789</v>
+        <v>1.5614800453186</v>
       </c>
       <c r="H348" t="n">
         <v>2800039</v>
@@ -10490,7 +10490,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G349" t="n">
-        <v>1.5572521686554</v>
+        <v>1.55725228786469</v>
       </c>
       <c r="H349" t="n">
         <v>599427</v>
@@ -10519,7 +10519,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G350" t="n">
-        <v>1.55161511898041</v>
+        <v>1.55161499977112</v>
       </c>
       <c r="H350" t="n">
         <v>673952</v>
@@ -10548,7 +10548,7 @@
         <v>2.19400000572205</v>
       </c>
       <c r="G351" t="n">
-        <v>1.54597806930542</v>
+        <v>1.54597795009613</v>
       </c>
       <c r="H351" t="n">
         <v>432046</v>
@@ -10606,7 +10606,7 @@
         <v>2.27099990844727</v>
       </c>
       <c r="G353" t="n">
-        <v>1.60023522377014</v>
+        <v>1.60023498535156</v>
       </c>
       <c r="H353" t="n">
         <v>454310</v>
@@ -10635,7 +10635,7 @@
         <v>2.26900005340576</v>
       </c>
       <c r="G354" t="n">
-        <v>1.59882605075836</v>
+        <v>1.59882581233978</v>
       </c>
       <c r="H354" t="n">
         <v>579865</v>
@@ -10664,7 +10664,7 @@
         <v>2.36400008201599</v>
       </c>
       <c r="G355" t="n">
-        <v>1.66576659679413</v>
+        <v>1.66576671600342</v>
       </c>
       <c r="H355" t="n">
         <v>862677</v>
@@ -10780,7 +10780,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G359" t="n">
-        <v>1.86729347705841</v>
+        <v>1.86729335784912</v>
       </c>
       <c r="H359" t="n">
         <v>1790824</v>
@@ -10809,7 +10809,7 @@
         <v>2.69749999046326</v>
       </c>
       <c r="G360" t="n">
-        <v>1.900763630867</v>
+        <v>1.90076351165771</v>
       </c>
       <c r="H360" t="n">
         <v>2325561</v>
@@ -10896,7 +10896,7 @@
         <v>2.54250001907349</v>
       </c>
       <c r="G363" t="n">
-        <v>1.79154467582703</v>
+        <v>1.79154455661774</v>
       </c>
       <c r="H363" t="n">
         <v>394519</v>
@@ -10925,7 +10925,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G364" t="n">
-        <v>1.79682958126068</v>
+        <v>1.7968293428421</v>
       </c>
       <c r="H364" t="n">
         <v>380123</v>
@@ -11012,7 +11012,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G367" t="n">
-        <v>1.75736975669861</v>
+        <v>1.75736951828003</v>
       </c>
       <c r="H367" t="n">
         <v>543237</v>
@@ -11041,7 +11041,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G368" t="n">
-        <v>1.78626012802124</v>
+        <v>1.78626000881195</v>
       </c>
       <c r="H368" t="n">
         <v>410264</v>
@@ -11070,7 +11070,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G369" t="n">
-        <v>1.80739915370941</v>
+        <v>1.80739891529083</v>
       </c>
       <c r="H369" t="n">
         <v>372165</v>
@@ -11099,7 +11099,7 @@
         <v>2.5550000667572</v>
       </c>
       <c r="G370" t="n">
-        <v>1.80035281181335</v>
+        <v>1.80035269260406</v>
       </c>
       <c r="H370" t="n">
         <v>510079</v>
@@ -11128,7 +11128,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G371" t="n">
-        <v>1.83206129074097</v>
+        <v>1.83206140995026</v>
       </c>
       <c r="H371" t="n">
         <v>521311</v>
@@ -11186,7 +11186,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G373" t="n">
-        <v>1.8849093914032</v>
+        <v>1.88490927219391</v>
       </c>
       <c r="H373" t="n">
         <v>569369</v>
@@ -11215,7 +11215,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G374" t="n">
-        <v>1.83910775184631</v>
+        <v>1.83910763263702</v>
       </c>
       <c r="H374" t="n">
         <v>564472</v>
@@ -11244,7 +11244,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G375" t="n">
-        <v>1.83910775184631</v>
+        <v>1.83910763263702</v>
       </c>
       <c r="H375" t="n">
         <v>442703</v>
@@ -11273,7 +11273,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G376" t="n">
-        <v>1.86377012729645</v>
+        <v>1.86377000808716</v>
       </c>
       <c r="H376" t="n">
         <v>303450</v>
@@ -11302,7 +11302,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G377" t="n">
-        <v>1.86377012729645</v>
+        <v>1.86377000808716</v>
       </c>
       <c r="H377" t="n">
         <v>377689</v>
@@ -11331,7 +11331,7 @@
         <v>2.6324999332428</v>
       </c>
       <c r="G378" t="n">
-        <v>1.8549622297287</v>
+        <v>1.85496211051941</v>
       </c>
       <c r="H378" t="n">
         <v>460839</v>
@@ -11389,7 +11389,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>1.86377012729645</v>
+        <v>1.86377000808716</v>
       </c>
       <c r="H380" t="n">
         <v>668827</v>
@@ -11447,7 +11447,7 @@
         <v>2.6324999332428</v>
       </c>
       <c r="G382" t="n">
-        <v>1.8549622297287</v>
+        <v>1.85496211051941</v>
       </c>
       <c r="H382" t="n">
         <v>848076</v>
@@ -11476,7 +11476,7 @@
         <v>2.61249995231628</v>
       </c>
       <c r="G383" t="n">
-        <v>1.84086942672729</v>
+        <v>1.84086918830872</v>
       </c>
       <c r="H383" t="n">
         <v>982705</v>
@@ -11505,7 +11505,7 @@
         <v>2.55749988555908</v>
       </c>
       <c r="G384" t="n">
-        <v>1.80211400985718</v>
+        <v>1.80211424827576</v>
       </c>
       <c r="H384" t="n">
         <v>1307235</v>
@@ -11534,7 +11534,7 @@
         <v>2.55250000953674</v>
       </c>
       <c r="G385" t="n">
-        <v>1.79859101772308</v>
+        <v>1.79859113693237</v>
       </c>
       <c r="H385" t="n">
         <v>1784366</v>
@@ -11563,7 +11563,7 @@
         <v>2.35700011253357</v>
       </c>
       <c r="G386" t="n">
-        <v>1.84116351604462</v>
+        <v>1.8411637544632</v>
       </c>
       <c r="H386" t="n">
         <v>1675723</v>
@@ -11592,7 +11592,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G387" t="n">
-        <v>1.80601191520691</v>
+        <v>1.8060120344162</v>
       </c>
       <c r="H387" t="n">
         <v>2221253</v>
@@ -11679,7 +11679,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G390" t="n">
-        <v>1.85131824016571</v>
+        <v>1.851318359375</v>
       </c>
       <c r="H390" t="n">
         <v>717045</v>
@@ -11737,7 +11737,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G392" t="n">
-        <v>1.84741282463074</v>
+        <v>1.84741270542145</v>
       </c>
       <c r="H392" t="n">
         <v>573846</v>
@@ -11795,7 +11795,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G394" t="n">
-        <v>1.81694793701172</v>
+        <v>1.81694805622101</v>
       </c>
       <c r="H394" t="n">
         <v>634308</v>
@@ -11824,7 +11824,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G395" t="n">
-        <v>1.84506940841675</v>
+        <v>1.84506928920746</v>
       </c>
       <c r="H395" t="n">
         <v>768257</v>
@@ -11853,7 +11853,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G396" t="n">
-        <v>1.81694793701172</v>
+        <v>1.81694805622101</v>
       </c>
       <c r="H396" t="n">
         <v>564016</v>
@@ -11940,7 +11940,7 @@
         <v>2.3289999961853</v>
       </c>
       <c r="G399" t="n">
-        <v>1.81929135322571</v>
+        <v>1.819291472435</v>
       </c>
       <c r="H399" t="n">
         <v>717310</v>
@@ -11969,7 +11969,7 @@
         <v>2.29900002479553</v>
       </c>
       <c r="G400" t="n">
-        <v>1.79585707187653</v>
+        <v>1.79585695266724</v>
       </c>
       <c r="H400" t="n">
         <v>435929</v>
@@ -11998,7 +11998,7 @@
         <v>2.30800008773804</v>
       </c>
       <c r="G401" t="n">
-        <v>1.80288732051849</v>
+        <v>1.80288743972778</v>
       </c>
       <c r="H401" t="n">
         <v>290608</v>
@@ -12056,7 +12056,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G403" t="n">
-        <v>1.84350693225861</v>
+        <v>1.84350681304932</v>
       </c>
       <c r="H403" t="n">
         <v>508765</v>
@@ -12085,7 +12085,7 @@
         <v>2.34299993515015</v>
       </c>
       <c r="G404" t="n">
-        <v>1.83022737503052</v>
+        <v>1.83022749423981</v>
       </c>
       <c r="H404" t="n">
         <v>400051</v>
@@ -12114,7 +12114,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G405" t="n">
-        <v>1.85913002490997</v>
+        <v>1.85912990570068</v>
       </c>
       <c r="H405" t="n">
         <v>572167</v>
@@ -12143,7 +12143,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G406" t="n">
-        <v>1.82944655418396</v>
+        <v>1.82944619655609</v>
       </c>
       <c r="H406" t="n">
         <v>327031</v>
@@ -12201,7 +12201,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G408" t="n">
-        <v>1.78257763385773</v>
+        <v>1.78257751464844</v>
       </c>
       <c r="H408" t="n">
         <v>720575</v>
@@ -12259,7 +12259,7 @@
         <v>2.29900002479553</v>
       </c>
       <c r="G410" t="n">
-        <v>1.79585707187653</v>
+        <v>1.79585695266724</v>
       </c>
       <c r="H410" t="n">
         <v>244821</v>
@@ -12288,7 +12288,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G411" t="n">
-        <v>1.80601191520691</v>
+        <v>1.8060120344162</v>
       </c>
       <c r="H411" t="n">
         <v>489918</v>
@@ -12317,7 +12317,7 @@
         <v>2.3289999961853</v>
       </c>
       <c r="G412" t="n">
-        <v>1.81929135322571</v>
+        <v>1.819291472435</v>
       </c>
       <c r="H412" t="n">
         <v>1092003</v>
@@ -12346,7 +12346,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G413" t="n">
-        <v>1.82397842407227</v>
+        <v>1.82397830486298</v>
       </c>
       <c r="H413" t="n">
         <v>525566</v>
@@ -12491,7 +12491,7 @@
         <v>2.26099991798401</v>
       </c>
       <c r="G418" t="n">
-        <v>1.76617348194122</v>
+        <v>1.76617336273193</v>
       </c>
       <c r="H418" t="n">
         <v>422740</v>
@@ -12607,7 +12607,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G422" t="n">
-        <v>1.7302405834198</v>
+        <v>1.73024070262909</v>
       </c>
       <c r="H422" t="n">
         <v>493842</v>
@@ -12665,7 +12665,7 @@
         <v>2.14100003242493</v>
       </c>
       <c r="G424" t="n">
-        <v>1.67243587970734</v>
+        <v>1.67243576049805</v>
       </c>
       <c r="H424" t="n">
         <v>2417146</v>
@@ -12752,7 +12752,7 @@
         <v>2.11299991607666</v>
       </c>
       <c r="G427" t="n">
-        <v>1.65056359767914</v>
+        <v>1.65056347846985</v>
       </c>
       <c r="H427" t="n">
         <v>344744</v>
@@ -12810,7 +12810,7 @@
         <v>2.0789999961853</v>
       </c>
       <c r="G429" t="n">
-        <v>1.62400460243225</v>
+        <v>1.62400472164154</v>
       </c>
       <c r="H429" t="n">
         <v>242331</v>
@@ -12839,7 +12839,7 @@
         <v>2.05299997329712</v>
       </c>
       <c r="G430" t="n">
-        <v>1.60369479656219</v>
+        <v>1.60369491577148</v>
       </c>
       <c r="H430" t="n">
         <v>355572</v>
@@ -12926,7 +12926,7 @@
         <v>1.97699999809265</v>
       </c>
       <c r="G433" t="n">
-        <v>1.54432773590088</v>
+        <v>1.54432761669159</v>
       </c>
       <c r="H433" t="n">
         <v>335769</v>
@@ -12955,7 +12955,7 @@
         <v>1.99899995326996</v>
       </c>
       <c r="G434" t="n">
-        <v>1.56151294708252</v>
+        <v>1.56151282787323</v>
       </c>
       <c r="H434" t="n">
         <v>852921</v>
@@ -13042,7 +13042,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G437" t="n">
-        <v>1.44121634960175</v>
+        <v>1.44121623039246</v>
       </c>
       <c r="H437" t="n">
         <v>430171</v>
@@ -13071,7 +13071,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G438" t="n">
-        <v>1.43887281417847</v>
+        <v>1.43887293338776</v>
       </c>
       <c r="H438" t="n">
         <v>297282</v>
@@ -13274,7 +13274,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G445" t="n">
-        <v>1.48886632919312</v>
+        <v>1.48886620998383</v>
       </c>
       <c r="H445" t="n">
         <v>825110</v>
@@ -13332,7 +13332,7 @@
         <v>1.85300004482269</v>
       </c>
       <c r="G447" t="n">
-        <v>1.44746553897858</v>
+        <v>1.44746541976929</v>
       </c>
       <c r="H447" t="n">
         <v>756122</v>
@@ -13390,7 +13390,7 @@
         <v>1.8309999704361</v>
       </c>
       <c r="G449" t="n">
-        <v>1.43028008937836</v>
+        <v>1.43028020858765</v>
       </c>
       <c r="H449" t="n">
         <v>475160</v>
@@ -13477,7 +13477,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G452" t="n">
-        <v>1.31232690811157</v>
+        <v>1.31232702732086</v>
       </c>
       <c r="H452" t="n">
         <v>1384290</v>
@@ -13535,7 +13535,7 @@
         <v>1.66719996929169</v>
       </c>
       <c r="G454" t="n">
-        <v>1.30232834815979</v>
+        <v>1.3023282289505</v>
       </c>
       <c r="H454" t="n">
         <v>438827</v>
@@ -13564,7 +13564,7 @@
         <v>1.69219994544983</v>
       </c>
       <c r="G455" t="n">
-        <v>1.32185697555542</v>
+        <v>1.32185685634613</v>
       </c>
       <c r="H455" t="n">
         <v>907774</v>
@@ -13622,7 +13622,7 @@
         <v>1.69159996509552</v>
       </c>
       <c r="G457" t="n">
-        <v>1.3213883638382</v>
+        <v>1.32138824462891</v>
       </c>
       <c r="H457" t="n">
         <v>232730</v>
@@ -13651,7 +13651,7 @@
         <v>1.74259996414185</v>
       </c>
       <c r="G458" t="n">
-        <v>1.36122679710388</v>
+        <v>1.36122667789459</v>
       </c>
       <c r="H458" t="n">
         <v>372410</v>
@@ -13680,7 +13680,7 @@
         <v>1.84239995479584</v>
       </c>
       <c r="G459" t="n">
-        <v>1.43918526172638</v>
+        <v>1.43918514251709</v>
       </c>
       <c r="H459" t="n">
         <v>501526</v>
@@ -13709,7 +13709,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G460" t="n">
-        <v>1.42715573310852</v>
+        <v>1.42715561389923</v>
       </c>
       <c r="H460" t="n">
         <v>222767</v>
@@ -13825,7 +13825,7 @@
         <v>1.93680000305176</v>
       </c>
       <c r="G464" t="n">
-        <v>1.51292562484741</v>
+        <v>1.51292550563812</v>
       </c>
       <c r="H464" t="n">
         <v>268931</v>
@@ -13854,7 +13854,7 @@
         <v>1.92239999771118</v>
       </c>
       <c r="G465" t="n">
-        <v>1.50167691707611</v>
+        <v>1.5016770362854</v>
       </c>
       <c r="H465" t="n">
         <v>353065</v>
@@ -13883,7 +13883,7 @@
         <v>2.02950000762939</v>
       </c>
       <c r="G466" t="n">
-        <v>1.58533787727356</v>
+        <v>1.58533799648285</v>
       </c>
       <c r="H466" t="n">
         <v>617753</v>
@@ -13941,7 +13941,7 @@
         <v>1.97259998321533</v>
       </c>
       <c r="G468" t="n">
-        <v>1.54089069366455</v>
+        <v>1.54089057445526</v>
       </c>
       <c r="H468" t="n">
         <v>448541</v>
@@ -13970,7 +13970,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G469" t="n">
-        <v>1.58729088306427</v>
+        <v>1.58729076385498</v>
       </c>
       <c r="H469" t="n">
         <v>310094</v>
@@ -14057,7 +14057,7 @@
         <v>2.00850009918213</v>
       </c>
       <c r="G472" t="n">
-        <v>1.56893396377563</v>
+        <v>1.56893384456635</v>
       </c>
       <c r="H472" t="n">
         <v>366405</v>
@@ -14086,7 +14086,7 @@
         <v>2.15249991416931</v>
       </c>
       <c r="G473" t="n">
-        <v>1.68141889572144</v>
+        <v>1.68141901493073</v>
       </c>
       <c r="H473" t="n">
         <v>1172106</v>
@@ -14173,7 +14173,7 @@
         <v>2.25650000572205</v>
       </c>
       <c r="G476" t="n">
-        <v>1.76265835762024</v>
+        <v>1.76265823841095</v>
       </c>
       <c r="H476" t="n">
         <v>463148</v>
@@ -14289,7 +14289,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G480" t="n">
-        <v>1.7466447353363</v>
+        <v>1.74664485454559</v>
       </c>
       <c r="H480" t="n">
         <v>1270704</v>
@@ -14318,7 +14318,7 @@
         <v>2.22300004959106</v>
       </c>
       <c r="G481" t="n">
-        <v>1.73649001121521</v>
+        <v>1.73648989200592</v>
       </c>
       <c r="H481" t="n">
         <v>624711</v>
@@ -14347,7 +14347,7 @@
         <v>2.31900000572205</v>
       </c>
       <c r="G482" t="n">
-        <v>1.81147992610931</v>
+        <v>1.8114800453186</v>
       </c>
       <c r="H482" t="n">
         <v>1426253</v>
@@ -14376,7 +14376,7 @@
         <v>2.29749989509583</v>
       </c>
       <c r="G483" t="n">
-        <v>1.79468512535095</v>
+        <v>1.79468524456024</v>
       </c>
       <c r="H483" t="n">
         <v>1095196</v>
@@ -14405,7 +14405,7 @@
         <v>2.33599996566772</v>
       </c>
       <c r="G484" t="n">
-        <v>1.82475936412811</v>
+        <v>1.8247594833374</v>
       </c>
       <c r="H484" t="n">
         <v>451325</v>
@@ -14434,7 +14434,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G485" t="n">
-        <v>1.86850368976593</v>
+        <v>1.86850345134735</v>
       </c>
       <c r="H485" t="n">
         <v>792725</v>
@@ -14492,7 +14492,7 @@
         <v>2.25</v>
       </c>
       <c r="G487" t="n">
-        <v>1.7575808763504</v>
+        <v>1.75758099555969</v>
       </c>
       <c r="H487" t="n">
         <v>1370262</v>
@@ -14550,7 +14550,7 @@
         <v>2.34949994087219</v>
       </c>
       <c r="G489" t="n">
-        <v>1.83530497550964</v>
+        <v>1.83530509471893</v>
       </c>
       <c r="H489" t="n">
         <v>626584</v>
@@ -14608,7 +14608,7 @@
         <v>2.39750003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>1.87280023097992</v>
+        <v>1.87280011177063</v>
       </c>
       <c r="H491" t="n">
         <v>839004</v>
@@ -14637,7 +14637,7 @@
         <v>2.3989999294281</v>
       </c>
       <c r="G492" t="n">
-        <v>1.87397170066833</v>
+        <v>1.87397158145905</v>
       </c>
       <c r="H492" t="n">
         <v>458199</v>
@@ -14666,7 +14666,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G493" t="n">
-        <v>1.86225438117981</v>
+        <v>1.86225461959839</v>
       </c>
       <c r="H493" t="n">
         <v>271589</v>
@@ -14695,7 +14695,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G494" t="n">
-        <v>1.85913002490997</v>
+        <v>1.85912990570068</v>
       </c>
       <c r="H494" t="n">
         <v>254944</v>
@@ -14724,7 +14724,7 @@
         <v>2.38100004196167</v>
       </c>
       <c r="G495" t="n">
-        <v>1.85991108417511</v>
+        <v>1.8599112033844</v>
       </c>
       <c r="H495" t="n">
         <v>360476</v>
@@ -14753,7 +14753,7 @@
         <v>2.375</v>
       </c>
       <c r="G496" t="n">
-        <v>1.85522413253784</v>
+        <v>1.85522401332855</v>
       </c>
       <c r="H496" t="n">
         <v>380134</v>
@@ -14840,7 +14840,7 @@
         <v>2.3289999961853</v>
       </c>
       <c r="G499" t="n">
-        <v>1.81929135322571</v>
+        <v>1.819291472435</v>
       </c>
       <c r="H499" t="n">
         <v>426104</v>
@@ -14927,7 +14927,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G502" t="n">
-        <v>1.89662504196167</v>
+        <v>1.89662492275238</v>
       </c>
       <c r="H502" t="n">
         <v>886759</v>
@@ -14956,7 +14956,7 @@
         <v>2.4210000038147</v>
       </c>
       <c r="G503" t="n">
-        <v>1.89115703105927</v>
+        <v>1.89115715026855</v>
       </c>
       <c r="H503" t="n">
         <v>400870</v>
@@ -14985,7 +14985,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G504" t="n">
-        <v>1.90443634986877</v>
+        <v>1.90443646907806</v>
       </c>
       <c r="H504" t="n">
         <v>376866</v>
@@ -15014,7 +15014,7 @@
         <v>2.40199995040894</v>
       </c>
       <c r="G505" t="n">
-        <v>1.87631499767303</v>
+        <v>1.87631523609161</v>
       </c>
       <c r="H505" t="n">
         <v>719122</v>
@@ -15072,7 +15072,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G507" t="n">
-        <v>1.85131824016571</v>
+        <v>1.851318359375</v>
       </c>
       <c r="H507" t="n">
         <v>420850</v>
@@ -15101,7 +15101,7 @@
         <v>2.38750004768372</v>
       </c>
       <c r="G508" t="n">
-        <v>1.86498844623566</v>
+        <v>1.86498880386353</v>
       </c>
       <c r="H508" t="n">
         <v>279164</v>
@@ -15130,7 +15130,7 @@
         <v>2.37949991226196</v>
       </c>
       <c r="G509" t="n">
-        <v>1.85873937606812</v>
+        <v>1.85873925685883</v>
       </c>
       <c r="H509" t="n">
         <v>517495</v>
@@ -15159,7 +15159,7 @@
         <v>2.33949995040894</v>
       </c>
       <c r="G510" t="n">
-        <v>1.82749330997467</v>
+        <v>1.82749342918396</v>
       </c>
       <c r="H510" t="n">
         <v>387078</v>
@@ -15188,7 +15188,7 @@
         <v>2.30800008773804</v>
       </c>
       <c r="G511" t="n">
-        <v>1.80288732051849</v>
+        <v>1.80288743972778</v>
       </c>
       <c r="H511" t="n">
         <v>471638</v>
@@ -15275,7 +15275,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G514" t="n">
-        <v>1.84819388389587</v>
+        <v>1.84819376468658</v>
       </c>
       <c r="H514" t="n">
         <v>499423</v>
@@ -15304,7 +15304,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G515" t="n">
-        <v>1.88256442546844</v>
+        <v>1.88256430625916</v>
       </c>
       <c r="H515" t="n">
         <v>456876</v>
@@ -15333,7 +15333,7 @@
         <v>2.38700008392334</v>
       </c>
       <c r="G516" t="n">
-        <v>1.86459815502167</v>
+        <v>1.86459803581238</v>
       </c>
       <c r="H516" t="n">
         <v>378435</v>
@@ -15391,7 +15391,7 @@
         <v>2.35949993133545</v>
       </c>
       <c r="G518" t="n">
-        <v>1.84311628341675</v>
+        <v>1.84311640262604</v>
       </c>
       <c r="H518" t="n">
         <v>314732</v>
@@ -15420,7 +15420,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G519" t="n">
-        <v>1.84506940841675</v>
+        <v>1.84506928920746</v>
       </c>
       <c r="H519" t="n">
         <v>346938</v>
@@ -15536,7 +15536,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G523" t="n">
-        <v>1.74352025985718</v>
+        <v>1.74352037906647</v>
       </c>
       <c r="H523" t="n">
         <v>587511</v>
@@ -15594,7 +15594,7 @@
         <v>2.18650007247925</v>
       </c>
       <c r="G525" t="n">
-        <v>1.70797789096832</v>
+        <v>1.70797801017761</v>
       </c>
       <c r="H525" t="n">
         <v>339135</v>
@@ -15739,7 +15739,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G530" t="n">
-        <v>1.65603172779083</v>
+        <v>1.65603160858154</v>
       </c>
       <c r="H530" t="n">
         <v>1091564</v>
@@ -15855,7 +15855,7 @@
         <v>2.1029999256134</v>
       </c>
       <c r="G534" t="n">
-        <v>1.64275217056274</v>
+        <v>1.64275205135345</v>
       </c>
       <c r="H534" t="n">
         <v>489001</v>
@@ -15971,7 +15971,7 @@
         <v>2.11150002479553</v>
       </c>
       <c r="G538" t="n">
-        <v>1.64939200878143</v>
+        <v>1.64939188957214</v>
       </c>
       <c r="H538" t="n">
         <v>386864</v>
@@ -16058,7 +16058,7 @@
         <v>2.10949993133545</v>
       </c>
       <c r="G541" t="n">
-        <v>1.64782953262329</v>
+        <v>1.64782965183258</v>
       </c>
       <c r="H541" t="n">
         <v>509259</v>
@@ -16174,7 +16174,7 @@
         <v>2.12750005722046</v>
       </c>
       <c r="G545" t="n">
-        <v>1.6618903875351</v>
+        <v>1.66189050674438</v>
       </c>
       <c r="H545" t="n">
         <v>1419921</v>
@@ -16232,7 +16232,7 @@
         <v>2.10949993133545</v>
       </c>
       <c r="G547" t="n">
-        <v>1.64782953262329</v>
+        <v>1.64782965183258</v>
       </c>
       <c r="H547" t="n">
         <v>489388</v>
@@ -16348,7 +16348,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G551" t="n">
-        <v>1.67009234428406</v>
+        <v>1.67009222507477</v>
       </c>
       <c r="H551" t="n">
         <v>1192328</v>
@@ -16406,7 +16406,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G553" t="n">
-        <v>1.74976944923401</v>
+        <v>1.74976933002472</v>
       </c>
       <c r="H553" t="n">
         <v>1944729</v>
@@ -16464,7 +16464,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G555" t="n">
-        <v>1.74352025985718</v>
+        <v>1.74352037906647</v>
       </c>
       <c r="H555" t="n">
         <v>532106</v>
@@ -16493,7 +16493,7 @@
         <v>2.24449992179871</v>
       </c>
       <c r="G556" t="n">
-        <v>1.75328457355499</v>
+        <v>1.75328433513641</v>
       </c>
       <c r="H556" t="n">
         <v>397911</v>
@@ -16580,7 +16580,7 @@
         <v>2.42149996757507</v>
       </c>
       <c r="G559" t="n">
-        <v>1.89154744148254</v>
+        <v>1.89154756069183</v>
       </c>
       <c r="H559" t="n">
         <v>1056336</v>
@@ -16609,7 +16609,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G560" t="n">
-        <v>1.87865853309631</v>
+        <v>1.8786586523056</v>
       </c>
       <c r="H560" t="n">
         <v>518625</v>
@@ -16638,7 +16638,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G561" t="n">
-        <v>1.92630875110626</v>
+        <v>1.92630863189697</v>
       </c>
       <c r="H561" t="n">
         <v>1119220</v>
@@ -16667,7 +16667,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G562" t="n">
-        <v>1.95130527019501</v>
+        <v>1.95130503177643</v>
       </c>
       <c r="H562" t="n">
         <v>455972</v>
@@ -16754,7 +16754,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G565" t="n">
-        <v>1.97473978996277</v>
+        <v>1.97473990917206</v>
       </c>
       <c r="H565" t="n">
         <v>742112</v>
@@ -16812,7 +16812,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G567" t="n">
-        <v>1.97473978996277</v>
+        <v>1.97473990917206</v>
       </c>
       <c r="H567" t="n">
         <v>1363010</v>
@@ -16841,7 +16841,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G568" t="n">
-        <v>1.99661195278168</v>
+        <v>1.99661183357239</v>
       </c>
       <c r="H568" t="n">
         <v>1003381</v>
@@ -16899,7 +16899,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G570" t="n">
-        <v>1.92943322658539</v>
+        <v>1.9294331073761</v>
       </c>
       <c r="H570" t="n">
         <v>765788</v>
@@ -16928,7 +16928,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G571" t="n">
-        <v>1.93099522590637</v>
+        <v>1.93099534511566</v>
       </c>
       <c r="H571" t="n">
         <v>439198</v>
@@ -17015,7 +17015,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G574" t="n">
-        <v>2.02785754203796</v>
+        <v>2.02785778045654</v>
       </c>
       <c r="H574" t="n">
         <v>1096883</v>
@@ -17044,7 +17044,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G575" t="n">
-        <v>2.04660511016846</v>
+        <v>2.04660534858704</v>
       </c>
       <c r="H575" t="n">
         <v>671436</v>
@@ -17102,7 +17102,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G577" t="n">
-        <v>2.12784433364868</v>
+        <v>2.12784457206726</v>
       </c>
       <c r="H577" t="n">
         <v>1427518</v>
@@ -17160,7 +17160,7 @@
         <v>2.71799993515015</v>
       </c>
       <c r="G579" t="n">
-        <v>2.12315773963928</v>
+        <v>2.1231575012207</v>
       </c>
       <c r="H579" t="n">
         <v>1054021</v>
@@ -17247,7 +17247,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>2.1793999671936</v>
+        <v>2.17940020561218</v>
       </c>
       <c r="H582" t="n">
         <v>543959</v>
@@ -17305,7 +17305,7 @@
         <v>2.76200008392334</v>
       </c>
       <c r="G584" t="n">
-        <v>2.15752816200256</v>
+        <v>2.15752840042114</v>
       </c>
       <c r="H584" t="n">
         <v>580443</v>
@@ -17334,7 +17334,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G585" t="n">
-        <v>2.19658541679382</v>
+        <v>2.1965856552124</v>
       </c>
       <c r="H585" t="n">
         <v>1518765</v>
@@ -17363,7 +17363,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G586" t="n">
-        <v>2.25751519203186</v>
+        <v>2.25751495361328</v>
       </c>
       <c r="H586" t="n">
         <v>1032388</v>
@@ -17421,7 +17421,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G588" t="n">
-        <v>2.31219530105591</v>
+        <v>2.31219506263733</v>
       </c>
       <c r="H588" t="n">
         <v>1282951</v>
@@ -17537,7 +17537,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G592" t="n">
-        <v>2.4387412071228</v>
+        <v>2.43874073028564</v>
       </c>
       <c r="H592" t="n">
         <v>965545</v>
@@ -17624,7 +17624,7 @@
         <v>3.11400008201599</v>
       </c>
       <c r="G595" t="n">
-        <v>2.43249177932739</v>
+        <v>2.43249201774597</v>
       </c>
       <c r="H595" t="n">
         <v>1799003</v>
@@ -17653,7 +17653,7 @@
         <v>3.00399994850159</v>
       </c>
       <c r="G596" t="n">
-        <v>2.34656548500061</v>
+        <v>2.34656572341919</v>
       </c>
       <c r="H596" t="n">
         <v>921949</v>
@@ -17682,7 +17682,7 @@
         <v>3</v>
       </c>
       <c r="G597" t="n">
-        <v>2.34344124794006</v>
+        <v>2.34344100952148</v>
       </c>
       <c r="H597" t="n">
         <v>1851145</v>
@@ -17740,7 +17740,7 @@
         <v>3.10800004005432</v>
       </c>
       <c r="G599" t="n">
-        <v>2.42780494689941</v>
+        <v>2.42780518531799</v>
       </c>
       <c r="H599" t="n">
         <v>1169838</v>
@@ -17798,7 +17798,7 @@
         <v>3.05200004577637</v>
       </c>
       <c r="G601" t="n">
-        <v>2.38406085968018</v>
+        <v>2.3840606212616</v>
       </c>
       <c r="H601" t="n">
         <v>913843</v>
@@ -17856,7 +17856,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G603" t="n">
-        <v>2.4653000831604</v>
+        <v>2.46529984474182</v>
       </c>
       <c r="H603" t="n">
         <v>1511750</v>
@@ -17885,7 +17885,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G604" t="n">
-        <v>2.4653000831604</v>
+        <v>2.46529984474182</v>
       </c>
       <c r="H604" t="n">
         <v>2000044</v>
@@ -17914,7 +17914,7 @@
         <v>3.17400002479553</v>
       </c>
       <c r="G605" t="n">
-        <v>2.47936081886292</v>
+        <v>2.47936058044434</v>
       </c>
       <c r="H605" t="n">
         <v>2744827</v>
@@ -17943,7 +17943,7 @@
         <v>3.30399990081787</v>
       </c>
       <c r="G606" t="n">
-        <v>2.58090949058533</v>
+        <v>2.58090972900391</v>
       </c>
       <c r="H606" t="n">
         <v>2221014</v>
@@ -18001,7 +18001,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G608" t="n">
-        <v>2.54653930664062</v>
+        <v>2.5465395450592</v>
       </c>
       <c r="H608" t="n">
         <v>795781</v>
@@ -18030,7 +18030,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G609" t="n">
-        <v>2.54810190200806</v>
+        <v>2.54810166358948</v>
       </c>
       <c r="H609" t="n">
         <v>548275</v>
@@ -18175,7 +18175,7 @@
         <v>3.09599995613098</v>
       </c>
       <c r="G614" t="n">
-        <v>2.41843104362488</v>
+        <v>2.41843128204346</v>
       </c>
       <c r="H614" t="n">
         <v>539410</v>
@@ -18378,7 +18378,7 @@
         <v>3.18799996376038</v>
       </c>
       <c r="G621" t="n">
-        <v>2.49029684066772</v>
+        <v>2.49029660224915</v>
       </c>
       <c r="H621" t="n">
         <v>691299</v>
@@ -18407,7 +18407,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G622" t="n">
-        <v>2.52310514450073</v>
+        <v>2.52310490608215</v>
       </c>
       <c r="H622" t="n">
         <v>1734037</v>
@@ -18494,7 +18494,7 @@
         <v>3.24799990653992</v>
       </c>
       <c r="G625" t="n">
-        <v>2.53716564178467</v>
+        <v>2.53716540336609</v>
       </c>
       <c r="H625" t="n">
         <v>505088</v>
@@ -18552,7 +18552,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G627" t="n">
-        <v>2.52310514450073</v>
+        <v>2.52310490608215</v>
       </c>
       <c r="H627" t="n">
         <v>1052134</v>
@@ -18610,7 +18610,7 @@
         <v>3.26399993896484</v>
       </c>
       <c r="G629" t="n">
-        <v>2.54966402053833</v>
+        <v>2.54966378211975</v>
       </c>
       <c r="H629" t="n">
         <v>1449732</v>
@@ -18784,7 +18784,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G635" t="n">
-        <v>2.71058034896851</v>
+        <v>2.71058011054993</v>
       </c>
       <c r="H635" t="n">
         <v>867265</v>
@@ -18929,7 +18929,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G640" t="n">
-        <v>2.66151189804077</v>
+        <v>2.66151165962219</v>
       </c>
       <c r="H640" t="n">
         <v>1142550</v>
@@ -19074,7 +19074,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G645" t="n">
-        <v>2.65814280509949</v>
+        <v>2.65814256668091</v>
       </c>
       <c r="H645" t="n">
         <v>687583</v>
@@ -19132,7 +19132,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G647" t="n">
-        <v>2.59413146972656</v>
+        <v>2.59413170814514</v>
       </c>
       <c r="H647" t="n">
         <v>573464</v>
@@ -19161,7 +19161,7 @@
         <v>3.01399993896484</v>
       </c>
       <c r="G648" t="n">
-        <v>2.53854298591614</v>
+        <v>2.53854322433472</v>
       </c>
       <c r="H648" t="n">
         <v>931043</v>
@@ -19248,7 +19248,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G651" t="n">
-        <v>2.44926476478577</v>
+        <v>2.44926452636719</v>
       </c>
       <c r="H651" t="n">
         <v>488032</v>
@@ -19422,7 +19422,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G657" t="n">
-        <v>2.45600247383118</v>
+        <v>2.45600271224976</v>
       </c>
       <c r="H657" t="n">
         <v>344477</v>
@@ -19567,7 +19567,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G662" t="n">
-        <v>2.47116327285767</v>
+        <v>2.47116303443909</v>
       </c>
       <c r="H662" t="n">
         <v>401363</v>
@@ -19683,7 +19683,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G666" t="n">
-        <v>2.48800802230835</v>
+        <v>2.48800826072693</v>
       </c>
       <c r="H666" t="n">
         <v>259923</v>
@@ -19741,7 +19741,7 @@
         <v>2.89800000190735</v>
       </c>
       <c r="G668" t="n">
-        <v>2.44084191322327</v>
+        <v>2.44084215164185</v>
       </c>
       <c r="H668" t="n">
         <v>360472</v>
@@ -20031,7 +20031,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G678" t="n">
-        <v>2.35661697387695</v>
+        <v>2.35661721229553</v>
       </c>
       <c r="H678" t="n">
         <v>240265</v>
@@ -20118,7 +20118,7 @@
         <v>3.22399997711182</v>
       </c>
       <c r="G681" t="n">
-        <v>2.71541571617126</v>
+        <v>2.71541595458984</v>
       </c>
       <c r="H681" t="n">
         <v>4686248</v>
@@ -20147,7 +20147,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G682" t="n">
-        <v>2.57223296165466</v>
+        <v>2.57223320007324</v>
       </c>
       <c r="H682" t="n">
         <v>2047557</v>
@@ -20321,7 +20321,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G688" t="n">
-        <v>2.6109766960144</v>
+        <v>2.61097645759583</v>
       </c>
       <c r="H688" t="n">
         <v>540996</v>
@@ -20350,7 +20350,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G689" t="n">
-        <v>2.58570909500122</v>
+        <v>2.5857093334198</v>
       </c>
       <c r="H689" t="n">
         <v>835995</v>
@@ -20379,7 +20379,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G690" t="n">
-        <v>2.57560229301453</v>
+        <v>2.57560205459595</v>
       </c>
       <c r="H690" t="n">
         <v>1181402</v>
@@ -20408,7 +20408,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G691" t="n">
-        <v>2.49306178092957</v>
+        <v>2.49306154251099</v>
       </c>
       <c r="H691" t="n">
         <v>554383</v>
@@ -20524,7 +20524,7 @@
         <v>3.03200006484985</v>
       </c>
       <c r="G695" t="n">
-        <v>2.55370378494263</v>
+        <v>2.55370354652405</v>
       </c>
       <c r="H695" t="n">
         <v>176181</v>
@@ -20640,7 +20640,7 @@
         <v>3.06800007820129</v>
       </c>
       <c r="G699" t="n">
-        <v>2.58402466773987</v>
+        <v>2.58402490615845</v>
       </c>
       <c r="H699" t="n">
         <v>565902</v>
@@ -20872,7 +20872,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G707" t="n">
-        <v>2.58570909500122</v>
+        <v>2.5857093334198</v>
       </c>
       <c r="H707" t="n">
         <v>503676</v>
@@ -20959,7 +20959,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G710" t="n">
-        <v>2.50990653038025</v>
+        <v>2.50990676879883</v>
       </c>
       <c r="H710" t="n">
         <v>1933202</v>
@@ -20988,7 +20988,7 @@
         <v>3.01399993896484</v>
       </c>
       <c r="G711" t="n">
-        <v>2.53854298591614</v>
+        <v>2.53854322433472</v>
       </c>
       <c r="H711" t="n">
         <v>357710</v>
@@ -21017,7 +21017,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G712" t="n">
-        <v>2.50990653038025</v>
+        <v>2.50990676879883</v>
       </c>
       <c r="H712" t="n">
         <v>660930</v>
@@ -21075,7 +21075,7 @@
         <v>2.91400003433228</v>
       </c>
       <c r="G714" t="n">
-        <v>2.45431804656982</v>
+        <v>2.4543182849884</v>
       </c>
       <c r="H714" t="n">
         <v>482372</v>
@@ -21162,7 +21162,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G717" t="n">
-        <v>2.45600247383118</v>
+        <v>2.45600271224976</v>
       </c>
       <c r="H717" t="n">
         <v>519899</v>
@@ -21423,7 +21423,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G726" t="n">
-        <v>2.44926476478577</v>
+        <v>2.44926452636719</v>
       </c>
       <c r="H726" t="n">
         <v>2315220</v>
@@ -21655,7 +21655,7 @@
         <v>2.79200005531311</v>
       </c>
       <c r="G734" t="n">
-        <v>2.3515636920929</v>
+        <v>2.35156345367432</v>
       </c>
       <c r="H734" t="n">
         <v>407635</v>
@@ -21684,7 +21684,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G735" t="n">
-        <v>2.41389012336731</v>
+        <v>2.41388988494873</v>
       </c>
       <c r="H735" t="n">
         <v>672584</v>
@@ -21887,7 +21887,7 @@
         <v>3.04200005531311</v>
       </c>
       <c r="G742" t="n">
-        <v>2.56212615966797</v>
+        <v>2.56212639808655</v>
       </c>
       <c r="H742" t="n">
         <v>920296</v>
@@ -22003,7 +22003,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G746" t="n">
-        <v>2.48295474052429</v>
+        <v>2.48295450210571</v>
       </c>
       <c r="H746" t="n">
         <v>959673</v>
@@ -22177,7 +22177,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>2.49306178092957</v>
+        <v>2.49306154251099</v>
       </c>
       <c r="H752" t="n">
         <v>229054</v>
@@ -22293,7 +22293,7 @@
         <v>3.01399993896484</v>
       </c>
       <c r="G756" t="n">
-        <v>2.53854298591614</v>
+        <v>2.53854322433472</v>
       </c>
       <c r="H756" t="n">
         <v>339559</v>
@@ -22380,7 +22380,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G759" t="n">
-        <v>2.48295474052429</v>
+        <v>2.48295450210571</v>
       </c>
       <c r="H759" t="n">
         <v>299028</v>
@@ -22467,7 +22467,7 @@
         <v>3.03399991989136</v>
       </c>
       <c r="G762" t="n">
-        <v>2.55538821220398</v>
+        <v>2.5553879737854</v>
       </c>
       <c r="H762" t="n">
         <v>577970</v>
@@ -22583,7 +22583,7 @@
         <v>3.09599995613098</v>
       </c>
       <c r="G766" t="n">
-        <v>2.60760760307312</v>
+        <v>2.6076078414917</v>
       </c>
       <c r="H766" t="n">
         <v>954705</v>
@@ -22612,7 +22612,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G767" t="n">
-        <v>2.57728672027588</v>
+        <v>2.5772864818573</v>
       </c>
       <c r="H767" t="n">
         <v>598686</v>
@@ -22670,7 +22670,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G769" t="n">
-        <v>2.57560229301453</v>
+        <v>2.57560205459595</v>
       </c>
       <c r="H769" t="n">
         <v>237570</v>
@@ -22699,7 +22699,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G770" t="n">
-        <v>2.57223296165466</v>
+        <v>2.57223320007324</v>
       </c>
       <c r="H770" t="n">
         <v>235087</v>
@@ -22728,7 +22728,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G771" t="n">
-        <v>2.5890781879425</v>
+        <v>2.58907794952393</v>
       </c>
       <c r="H771" t="n">
         <v>233031</v>
@@ -22815,7 +22815,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G774" t="n">
-        <v>2.67835664749146</v>
+        <v>2.67835688591003</v>
       </c>
       <c r="H774" t="n">
         <v>844822</v>
@@ -22844,7 +22844,7 @@
         <v>3.14199995994568</v>
       </c>
       <c r="G775" t="n">
-        <v>2.64635133743286</v>
+        <v>2.64635109901428</v>
       </c>
       <c r="H775" t="n">
         <v>1054352</v>
@@ -22931,7 +22931,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G778" t="n">
-        <v>2.7171003818512</v>
+        <v>2.71710014343262</v>
       </c>
       <c r="H778" t="n">
         <v>964874</v>
@@ -22960,7 +22960,7 @@
         <v>3.20600008964539</v>
       </c>
       <c r="G779" t="n">
-        <v>2.70025515556335</v>
+        <v>2.70025539398193</v>
       </c>
       <c r="H779" t="n">
         <v>409180</v>
@@ -23076,7 +23076,7 @@
         <v>3.20600008964539</v>
       </c>
       <c r="G783" t="n">
-        <v>2.70025515556335</v>
+        <v>2.70025539398193</v>
       </c>
       <c r="H783" t="n">
         <v>938332</v>
@@ -23105,7 +23105,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G784" t="n">
-        <v>2.7171003818512</v>
+        <v>2.71710014343262</v>
       </c>
       <c r="H784" t="n">
         <v>578855</v>
@@ -23250,7 +23250,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G789" t="n">
-        <v>2.84680676460266</v>
+        <v>2.84680700302124</v>
       </c>
       <c r="H789" t="n">
         <v>815915</v>
@@ -23395,7 +23395,7 @@
         <v>3.14199995994568</v>
       </c>
       <c r="G794" t="n">
-        <v>2.64635133743286</v>
+        <v>2.64635109901428</v>
       </c>
       <c r="H794" t="n">
         <v>768072</v>
@@ -23627,7 +23627,7 @@
         <v>3.36800003051758</v>
       </c>
       <c r="G802" t="n">
-        <v>2.83669996261597</v>
+        <v>2.83669972419739</v>
       </c>
       <c r="H802" t="n">
         <v>706988</v>
@@ -23714,7 +23714,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G805" t="n">
-        <v>2.93776965141296</v>
+        <v>2.93776988983154</v>
       </c>
       <c r="H805" t="n">
         <v>557350</v>
@@ -23975,7 +23975,7 @@
         <v>3.38800001144409</v>
       </c>
       <c r="G814" t="n">
-        <v>2.85354471206665</v>
+        <v>2.85354495048523</v>
       </c>
       <c r="H814" t="n">
         <v>347337</v>
@@ -24091,7 +24091,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G818" t="n">
-        <v>2.45600247383118</v>
+        <v>2.45600271224976</v>
       </c>
       <c r="H818" t="n">
         <v>1497205</v>
@@ -24120,7 +24120,7 @@
         <v>3.00600004196167</v>
       </c>
       <c r="G819" t="n">
-        <v>2.53180503845215</v>
+        <v>2.53180527687073</v>
       </c>
       <c r="H819" t="n">
         <v>790572</v>
@@ -24526,7 +24526,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G833" t="n">
-        <v>2.69183278083801</v>
+        <v>2.69183301925659</v>
       </c>
       <c r="H833" t="n">
         <v>488767</v>
@@ -24555,7 +24555,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G834" t="n">
-        <v>2.67835664749146</v>
+        <v>2.67835688591003</v>
       </c>
       <c r="H834" t="n">
         <v>708286</v>
@@ -24584,7 +24584,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G835" t="n">
-        <v>2.65814280509949</v>
+        <v>2.65814256668091</v>
       </c>
       <c r="H835" t="n">
         <v>524048</v>
@@ -24642,7 +24642,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G837" t="n">
-        <v>2.67835664749146</v>
+        <v>2.67835688591003</v>
       </c>
       <c r="H837" t="n">
         <v>361053</v>
@@ -24700,7 +24700,7 @@
         <v>3.25</v>
       </c>
       <c r="G839" t="n">
-        <v>2.73731422424316</v>
+        <v>2.73731446266174</v>
       </c>
       <c r="H839" t="n">
         <v>461413</v>
@@ -24816,7 +24816,7 @@
         <v>3.25</v>
       </c>
       <c r="G843" t="n">
-        <v>2.73731422424316</v>
+        <v>2.73731446266174</v>
       </c>
       <c r="H843" t="n">
         <v>565490</v>
@@ -24961,7 +24961,7 @@
         <v>3.33599996566772</v>
       </c>
       <c r="G848" t="n">
-        <v>2.80974769592285</v>
+        <v>2.80974793434143</v>
       </c>
       <c r="H848" t="n">
         <v>1117559</v>
@@ -25251,7 +25251,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G858" t="n">
-        <v>2.79795622825623</v>
+        <v>2.7979564666748</v>
       </c>
       <c r="H858" t="n">
         <v>402306</v>
@@ -25338,7 +25338,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G861" t="n">
-        <v>2.78784918785095</v>
+        <v>2.78784942626953</v>
       </c>
       <c r="H861" t="n">
         <v>436318</v>
@@ -25483,7 +25483,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G866" t="n">
-        <v>2.68677949905396</v>
+        <v>2.68677926063538</v>
       </c>
       <c r="H866" t="n">
         <v>1350411</v>
@@ -25541,7 +25541,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G868" t="n">
-        <v>2.65814280509949</v>
+        <v>2.65814256668091</v>
       </c>
       <c r="H868" t="n">
         <v>1567922</v>
@@ -35552,6 +35552,35 @@
         <v>1337072</v>
       </c>
       <c r="I1213" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1214" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1214" t="n">
+        <v>2.10999989509583</v>
+      </c>
+      <c r="D1214" t="n">
+        <v>2.1340000629425</v>
+      </c>
+      <c r="E1214" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="F1214" t="n">
+        <v>2.12400007247925</v>
+      </c>
+      <c r="G1214" t="n">
+        <v>2.12400007247925</v>
+      </c>
+      <c r="H1214" t="n">
+        <v>1691456</v>
+      </c>
+      <c r="I1214" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MFEA.MI.xlsx
+++ b/data/MFEA.MI.xlsx
@@ -456,7 +456,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G3" t="n">
-        <v>2.25028038024902</v>
+        <v>2.25027990341187</v>
       </c>
       <c r="H3" t="n">
         <v>367297</v>
@@ -485,7 +485,7 @@
         <v>3.71250009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>2.28881216049194</v>
+        <v>2.28881239891052</v>
       </c>
       <c r="H4" t="n">
         <v>267411</v>
@@ -514,7 +514,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G5" t="n">
-        <v>2.30884885787964</v>
+        <v>2.30884909629822</v>
       </c>
       <c r="H5" t="n">
         <v>278466</v>
@@ -543,7 +543,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G6" t="n">
-        <v>2.28727078437805</v>
+        <v>2.28727102279663</v>
       </c>
       <c r="H6" t="n">
         <v>214912</v>
@@ -572,7 +572,7 @@
         <v>3.70749998092651</v>
       </c>
       <c r="G7" t="n">
-        <v>2.28572940826416</v>
+        <v>2.28572964668274</v>
       </c>
       <c r="H7" t="n">
         <v>170939</v>
@@ -746,7 +746,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G13" t="n">
-        <v>2.29343628883362</v>
+        <v>2.29343605041504</v>
       </c>
       <c r="H13" t="n">
         <v>85603</v>
@@ -891,7 +891,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G18" t="n">
-        <v>2.66951012611389</v>
+        <v>2.66951036453247</v>
       </c>
       <c r="H18" t="n">
         <v>629452</v>
@@ -949,7 +949,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G20" t="n">
-        <v>2.61710667610168</v>
+        <v>2.61710643768311</v>
       </c>
       <c r="H20" t="n">
         <v>162925</v>
@@ -1007,7 +1007,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G22" t="n">
-        <v>2.59552812576294</v>
+        <v>2.59552836418152</v>
       </c>
       <c r="H22" t="n">
         <v>210917</v>
@@ -1036,7 +1036,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G23" t="n">
-        <v>2.49688601493835</v>
+        <v>2.49688625335693</v>
       </c>
       <c r="H23" t="n">
         <v>230967</v>
@@ -1065,7 +1065,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G24" t="n">
-        <v>2.42598676681519</v>
+        <v>2.42598652839661</v>
       </c>
       <c r="H24" t="n">
         <v>208426</v>
@@ -1094,7 +1094,7 @@
         <v>3.99499988555908</v>
       </c>
       <c r="G25" t="n">
-        <v>2.46297764778137</v>
+        <v>2.46297740936279</v>
       </c>
       <c r="H25" t="n">
         <v>109853</v>
@@ -1152,7 +1152,7 @@
         <v>3.98250007629395</v>
       </c>
       <c r="G27" t="n">
-        <v>2.45527148246765</v>
+        <v>2.45527124404907</v>
       </c>
       <c r="H27" t="n">
         <v>73167</v>
@@ -1181,7 +1181,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G28" t="n">
-        <v>2.47222566604614</v>
+        <v>2.47222542762756</v>
       </c>
       <c r="H28" t="n">
         <v>194221</v>
@@ -1210,7 +1210,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G29" t="n">
-        <v>2.47530794143677</v>
+        <v>2.47530770301819</v>
       </c>
       <c r="H29" t="n">
         <v>272151</v>
@@ -1268,7 +1268,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G31" t="n">
-        <v>2.4044086933136</v>
+        <v>2.40440893173218</v>
       </c>
       <c r="H31" t="n">
         <v>128224</v>
@@ -1326,7 +1326,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G33" t="n">
-        <v>2.21945405006409</v>
+        <v>2.21945428848267</v>
       </c>
       <c r="H33" t="n">
         <v>419876</v>
@@ -1355,7 +1355,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G34" t="n">
-        <v>2.29343628883362</v>
+        <v>2.29343605041504</v>
       </c>
       <c r="H34" t="n">
         <v>612514</v>
@@ -1471,7 +1471,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G38" t="n">
-        <v>2.58936333656311</v>
+        <v>2.58936309814453</v>
       </c>
       <c r="H38" t="n">
         <v>208860</v>
@@ -1500,7 +1500,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G39" t="n">
-        <v>2.58936333656311</v>
+        <v>2.58936309814453</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -1558,7 +1558,7 @@
         <v>3.5</v>
       </c>
       <c r="G41" t="n">
-        <v>2.15780282020569</v>
+        <v>2.15780258178711</v>
       </c>
       <c r="H41" t="n">
         <v>1105386</v>
@@ -1616,7 +1616,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G43" t="n">
-        <v>2.03449988365173</v>
+        <v>2.03449964523315</v>
       </c>
       <c r="H43" t="n">
         <v>404535</v>
@@ -1645,7 +1645,7 @@
         <v>3.3675000667572</v>
       </c>
       <c r="G44" t="n">
-        <v>2.07611441612244</v>
+        <v>2.07611465454102</v>
       </c>
       <c r="H44" t="n">
         <v>214683</v>
@@ -1674,7 +1674,7 @@
         <v>3.375</v>
       </c>
       <c r="G45" t="n">
-        <v>2.08073830604553</v>
+        <v>2.08073854446411</v>
       </c>
       <c r="H45" t="n">
         <v>332316</v>
@@ -1848,7 +1848,7 @@
         <v>3.17750000953674</v>
       </c>
       <c r="G51" t="n">
-        <v>1.95897686481476</v>
+        <v>1.95897650718689</v>
       </c>
       <c r="H51" t="n">
         <v>400267</v>
@@ -1877,7 +1877,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G52" t="n">
-        <v>1.99442601203918</v>
+        <v>1.99442625045776</v>
       </c>
       <c r="H52" t="n">
         <v>186459</v>
@@ -1935,7 +1935,7 @@
         <v>3.1175000667572</v>
       </c>
       <c r="G54" t="n">
-        <v>1.92198574542999</v>
+        <v>1.92198586463928</v>
       </c>
       <c r="H54" t="n">
         <v>195501</v>
@@ -2051,7 +2051,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G58" t="n">
-        <v>1.82488465309143</v>
+        <v>1.82488453388214</v>
       </c>
       <c r="H58" t="n">
         <v>168347</v>
@@ -2080,7 +2080,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G59" t="n">
-        <v>1.79405891895294</v>
+        <v>1.79405903816223</v>
       </c>
       <c r="H59" t="n">
         <v>174796</v>
@@ -2109,7 +2109,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G60" t="n">
-        <v>1.79714143276215</v>
+        <v>1.79714131355286</v>
       </c>
       <c r="H60" t="n">
         <v>140935</v>
@@ -2138,7 +2138,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G61" t="n">
-        <v>1.80638921260834</v>
+        <v>1.80638909339905</v>
       </c>
       <c r="H61" t="n">
         <v>175025</v>
@@ -2225,7 +2225,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G64" t="n">
-        <v>1.87728810310364</v>
+        <v>1.87728846073151</v>
       </c>
       <c r="H64" t="n">
         <v>324711</v>
@@ -2254,7 +2254,7 @@
         <v>2.89249992370605</v>
       </c>
       <c r="G65" t="n">
-        <v>1.78326964378357</v>
+        <v>1.78326988220215</v>
       </c>
       <c r="H65" t="n">
         <v>336035</v>
@@ -2283,7 +2283,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G66" t="n">
-        <v>1.71391189098358</v>
+        <v>1.71391177177429</v>
       </c>
       <c r="H66" t="n">
         <v>344735</v>
@@ -2341,7 +2341,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G68" t="n">
-        <v>1.66150808334351</v>
+        <v>1.66150832176208</v>
       </c>
       <c r="H68" t="n">
         <v>213075</v>
@@ -2370,7 +2370,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G69" t="n">
-        <v>1.65226030349731</v>
+        <v>1.6522604227066</v>
       </c>
       <c r="H69" t="n">
         <v>531234</v>
@@ -2399,7 +2399,7 @@
         <v>2.92750000953674</v>
       </c>
       <c r="G70" t="n">
-        <v>1.80484795570374</v>
+        <v>1.80484783649445</v>
       </c>
       <c r="H70" t="n">
         <v>1271038</v>
@@ -2457,7 +2457,7 @@
         <v>2.88750004768372</v>
       </c>
       <c r="G72" t="n">
-        <v>1.78018736839294</v>
+        <v>1.78018724918365</v>
       </c>
       <c r="H72" t="n">
         <v>202748</v>
@@ -2486,7 +2486,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G73" t="n">
-        <v>1.74165523052216</v>
+        <v>1.74165511131287</v>
       </c>
       <c r="H73" t="n">
         <v>228203</v>
@@ -2544,7 +2544,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G75" t="n">
-        <v>1.66150808334351</v>
+        <v>1.66150832176208</v>
       </c>
       <c r="H75" t="n">
         <v>331684</v>
@@ -2602,7 +2602,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>1.64917778968811</v>
+        <v>1.6491779088974</v>
       </c>
       <c r="H77" t="n">
         <v>209971</v>
@@ -2631,7 +2631,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G78" t="n">
-        <v>1.74782025814056</v>
+        <v>1.74782013893127</v>
       </c>
       <c r="H78" t="n">
         <v>522442</v>
@@ -2660,7 +2660,7 @@
         <v>2.66750001907349</v>
       </c>
       <c r="G79" t="n">
-        <v>1.64455413818359</v>
+        <v>1.64455389976501</v>
       </c>
       <c r="H79" t="n">
         <v>468659</v>
@@ -2805,7 +2805,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G84" t="n">
-        <v>1.56594812870026</v>
+        <v>1.56594836711884</v>
       </c>
       <c r="H84" t="n">
         <v>392657</v>
@@ -2892,7 +2892,7 @@
         <v>2.50250005722046</v>
       </c>
       <c r="G87" t="n">
-        <v>1.54282891750336</v>
+        <v>1.54282903671265</v>
       </c>
       <c r="H87" t="n">
         <v>224920</v>
@@ -2921,7 +2921,7 @@
         <v>2.64750003814697</v>
       </c>
       <c r="G88" t="n">
-        <v>1.63222360610962</v>
+        <v>1.63222372531891</v>
       </c>
       <c r="H88" t="n">
         <v>842562</v>
@@ -3037,7 +3037,7 @@
         <v>2.66750001907349</v>
       </c>
       <c r="G92" t="n">
-        <v>1.64455413818359</v>
+        <v>1.64455389976501</v>
       </c>
       <c r="H92" t="n">
         <v>384701</v>
@@ -3095,7 +3095,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G94" t="n">
-        <v>1.63993000984192</v>
+        <v>1.6399302482605</v>
       </c>
       <c r="H94" t="n">
         <v>124415</v>
@@ -3124,7 +3124,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G95" t="n">
-        <v>1.59985661506653</v>
+        <v>1.59985673427582</v>
       </c>
       <c r="H95" t="n">
         <v>255560</v>
@@ -3182,7 +3182,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G97" t="n">
-        <v>1.57827842235565</v>
+        <v>1.57827854156494</v>
       </c>
       <c r="H97" t="n">
         <v>975446</v>
@@ -3240,7 +3240,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>1.60602188110352</v>
+        <v>1.60602176189423</v>
       </c>
       <c r="H99" t="n">
         <v>524697</v>
@@ -3356,7 +3356,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G103" t="n">
-        <v>1.45867455005646</v>
+        <v>1.45867466926575</v>
       </c>
       <c r="H103" t="n">
         <v>277983</v>
@@ -3385,7 +3385,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G104" t="n">
-        <v>1.37482857704163</v>
+        <v>1.37482845783234</v>
       </c>
       <c r="H104" t="n">
         <v>330336</v>
@@ -3414,7 +3414,7 @@
         <v>2.25699996948242</v>
       </c>
       <c r="G105" t="n">
-        <v>1.39147436618805</v>
+        <v>1.39147448539734</v>
       </c>
       <c r="H105" t="n">
         <v>153134</v>
@@ -3443,7 +3443,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G106" t="n">
-        <v>1.39085805416107</v>
+        <v>1.39085793495178</v>
       </c>
       <c r="H106" t="n">
         <v>262719</v>
@@ -3472,7 +3472,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>1.33475506305695</v>
+        <v>1.33475518226624</v>
       </c>
       <c r="H107" t="n">
         <v>364496</v>
@@ -3617,7 +3617,7 @@
         <v>2.24900007247925</v>
       </c>
       <c r="G112" t="n">
-        <v>1.38654255867004</v>
+        <v>1.38654243946075</v>
       </c>
       <c r="H112" t="n">
         <v>617377</v>
@@ -3704,7 +3704,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G115" t="n">
-        <v>1.36558091640472</v>
+        <v>1.36558079719543</v>
       </c>
       <c r="H115" t="n">
         <v>684447</v>
@@ -3733,7 +3733,7 @@
         <v>2.28900003433228</v>
       </c>
       <c r="G116" t="n">
-        <v>1.41120278835297</v>
+        <v>1.41120302677155</v>
       </c>
       <c r="H116" t="n">
         <v>1034023</v>
@@ -3820,7 +3820,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G119" t="n">
-        <v>1.38099384307861</v>
+        <v>1.38099372386932</v>
       </c>
       <c r="H119" t="n">
         <v>296846</v>
@@ -3878,7 +3878,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G121" t="n">
-        <v>1.4056544303894</v>
+        <v>1.40565431118011</v>
       </c>
       <c r="H121" t="n">
         <v>1163100</v>
@@ -3907,7 +3907,7 @@
         <v>2.22099995613098</v>
       </c>
       <c r="G122" t="n">
-        <v>1.36927998065948</v>
+        <v>1.36928009986877</v>
       </c>
       <c r="H122" t="n">
         <v>2110801</v>
@@ -4052,7 +4052,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G127" t="n">
-        <v>1.33043944835663</v>
+        <v>1.33043956756592</v>
       </c>
       <c r="H127" t="n">
         <v>576146</v>
@@ -4081,7 +4081,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G128" t="n">
-        <v>1.35325062274933</v>
+        <v>1.35325050354004</v>
       </c>
       <c r="H128" t="n">
         <v>1234804</v>
@@ -4110,7 +4110,7 @@
         <v>2.13700008392334</v>
       </c>
       <c r="G129" t="n">
-        <v>1.31749272346497</v>
+        <v>1.31749284267426</v>
       </c>
       <c r="H129" t="n">
         <v>756330</v>
@@ -4139,7 +4139,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G130" t="n">
-        <v>1.37791097164154</v>
+        <v>1.37791121006012</v>
       </c>
       <c r="H130" t="n">
         <v>658168</v>
@@ -4168,7 +4168,7 @@
         <v>2.21399998664856</v>
       </c>
       <c r="G131" t="n">
-        <v>1.36496436595917</v>
+        <v>1.36496424674988</v>
       </c>
       <c r="H131" t="n">
         <v>425795</v>
@@ -4197,7 +4197,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G132" t="n">
-        <v>1.29468166828156</v>
+        <v>1.29468154907227</v>
       </c>
       <c r="H132" t="n">
         <v>903030</v>
@@ -4226,7 +4226,7 @@
         <v>2.02699995040894</v>
       </c>
       <c r="G133" t="n">
-        <v>1.24967586994171</v>
+        <v>1.249675989151</v>
       </c>
       <c r="H133" t="n">
         <v>1799201</v>
@@ -4255,7 +4255,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>1.28543400764465</v>
+        <v>1.28543388843536</v>
       </c>
       <c r="H134" t="n">
         <v>1315577</v>
@@ -4313,7 +4313,7 @@
         <v>2.20099997520447</v>
       </c>
       <c r="G136" t="n">
-        <v>1.3569495677948</v>
+        <v>1.35694968700409</v>
       </c>
       <c r="H136" t="n">
         <v>597261</v>
@@ -4458,7 +4458,7 @@
         <v>2.08400011062622</v>
       </c>
       <c r="G141" t="n">
-        <v>1.28481733798981</v>
+        <v>1.2848174571991</v>
       </c>
       <c r="H141" t="n">
         <v>2061793</v>
@@ -4487,7 +4487,7 @@
         <v>2.125</v>
       </c>
       <c r="G142" t="n">
-        <v>1.31009435653687</v>
+        <v>1.31009459495544</v>
       </c>
       <c r="H142" t="n">
         <v>1089881</v>
@@ -4632,7 +4632,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G147" t="n">
-        <v>1.35325062274933</v>
+        <v>1.35325050354004</v>
       </c>
       <c r="H147" t="n">
         <v>729575</v>
@@ -4661,7 +4661,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G148" t="n">
-        <v>1.35633313655853</v>
+        <v>1.35633325576782</v>
       </c>
       <c r="H148" t="n">
         <v>470520</v>
@@ -4719,7 +4719,7 @@
         <v>2.04699993133545</v>
       </c>
       <c r="G150" t="n">
-        <v>1.26200616359711</v>
+        <v>1.2620062828064</v>
       </c>
       <c r="H150" t="n">
         <v>1302379</v>
@@ -4748,7 +4748,7 @@
         <v>2.07100009918213</v>
       </c>
       <c r="G151" t="n">
-        <v>1.27680265903473</v>
+        <v>1.27680277824402</v>
       </c>
       <c r="H151" t="n">
         <v>802560</v>
@@ -4835,7 +4835,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G154" t="n">
-        <v>1.23611283302307</v>
+        <v>1.23611271381378</v>
       </c>
       <c r="H154" t="n">
         <v>622012</v>
@@ -4893,7 +4893,7 @@
         <v>2.10899996757507</v>
       </c>
       <c r="G156" t="n">
-        <v>1.3002302646637</v>
+        <v>1.30023038387299</v>
       </c>
       <c r="H156" t="n">
         <v>825405</v>
@@ -4922,7 +4922,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G157" t="n">
-        <v>1.30392920970917</v>
+        <v>1.30392932891846</v>
       </c>
       <c r="H157" t="n">
         <v>621284</v>
@@ -5038,7 +5038,7 @@
         <v>2.08899998664856</v>
       </c>
       <c r="G161" t="n">
-        <v>1.2878999710083</v>
+        <v>1.28789985179901</v>
       </c>
       <c r="H161" t="n">
         <v>544349</v>
@@ -5125,7 +5125,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G164" t="n">
-        <v>1.31625962257385</v>
+        <v>1.31625974178314</v>
       </c>
       <c r="H164" t="n">
         <v>1321946</v>
@@ -5183,7 +5183,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G166" t="n">
-        <v>1.28543400764465</v>
+        <v>1.28543388843536</v>
       </c>
       <c r="H166" t="n">
         <v>925875</v>
@@ -5212,7 +5212,7 @@
         <v>2.06900000572205</v>
       </c>
       <c r="G167" t="n">
-        <v>1.27556967735291</v>
+        <v>1.27556979656219</v>
       </c>
       <c r="H167" t="n">
         <v>928824</v>
@@ -5299,7 +5299,7 @@
         <v>1.84899997711182</v>
       </c>
       <c r="G170" t="n">
-        <v>1.30287754535675</v>
+        <v>1.30287742614746</v>
       </c>
       <c r="H170" t="n">
         <v>1744533</v>
@@ -5357,7 +5357,7 @@
         <v>1.68299996852875</v>
       </c>
       <c r="G172" t="n">
-        <v>1.18590724468231</v>
+        <v>1.18590748310089</v>
       </c>
       <c r="H172" t="n">
         <v>1157709</v>
@@ -5386,7 +5386,7 @@
         <v>1.65199995040894</v>
       </c>
       <c r="G173" t="n">
-        <v>1.16406345367432</v>
+        <v>1.16406357288361</v>
       </c>
       <c r="H173" t="n">
         <v>1205156</v>
@@ -5415,7 +5415,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G174" t="n">
-        <v>1.14151513576508</v>
+        <v>1.14151525497437</v>
       </c>
       <c r="H174" t="n">
         <v>1315279</v>
@@ -5473,7 +5473,7 @@
         <v>1.53900003433228</v>
       </c>
       <c r="G176" t="n">
-        <v>1.08443939685822</v>
+        <v>1.0844395160675</v>
       </c>
       <c r="H176" t="n">
         <v>1625041</v>
@@ -5502,7 +5502,7 @@
         <v>1.4889999628067</v>
       </c>
       <c r="G177" t="n">
-        <v>1.04920732975006</v>
+        <v>1.04920744895935</v>
       </c>
       <c r="H177" t="n">
         <v>2864868</v>
@@ -5531,7 +5531,7 @@
         <v>1.43900001049042</v>
       </c>
       <c r="G178" t="n">
-        <v>1.01397562026978</v>
+        <v>1.01397550106049</v>
       </c>
       <c r="H178" t="n">
         <v>1366037</v>
@@ -5589,7 +5589,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G180" t="n">
-        <v>1.08514416217804</v>
+        <v>1.08514404296875</v>
       </c>
       <c r="H180" t="n">
         <v>1913773</v>
@@ -5705,7 +5705,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G184" t="n">
-        <v>1.08796274662018</v>
+        <v>1.08796262741089</v>
       </c>
       <c r="H184" t="n">
         <v>1603167</v>
@@ -5734,7 +5734,7 @@
         <v>1.50899994373322</v>
       </c>
       <c r="G185" t="n">
-        <v>1.06330037117004</v>
+        <v>1.06330013275146</v>
       </c>
       <c r="H185" t="n">
         <v>762123</v>
@@ -5763,7 +5763,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G186" t="n">
-        <v>1.06752812862396</v>
+        <v>1.06752800941467</v>
       </c>
       <c r="H186" t="n">
         <v>688465</v>
@@ -5792,7 +5792,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G187" t="n">
-        <v>1.04850280284882</v>
+        <v>1.04850292205811</v>
       </c>
       <c r="H187" t="n">
         <v>343484</v>
@@ -5821,7 +5821,7 @@
         <v>1.54200005531311</v>
       </c>
       <c r="G188" t="n">
-        <v>1.08655333518982</v>
+        <v>1.08655345439911</v>
       </c>
       <c r="H188" t="n">
         <v>1596742</v>
@@ -5850,7 +5850,7 @@
         <v>1.5110000371933</v>
       </c>
       <c r="G189" t="n">
-        <v>1.06470942497253</v>
+        <v>1.06470954418182</v>
       </c>
       <c r="H189" t="n">
         <v>1590572</v>
@@ -5879,7 +5879,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G190" t="n">
-        <v>1.11473882198334</v>
+        <v>1.11473894119263</v>
       </c>
       <c r="H190" t="n">
         <v>1164166</v>
@@ -5995,7 +5995,7 @@
         <v>1.62300002574921</v>
       </c>
       <c r="G194" t="n">
-        <v>1.14362919330597</v>
+        <v>1.14362895488739</v>
       </c>
       <c r="H194" t="n">
         <v>1339210</v>
@@ -6024,7 +6024,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G195" t="n">
-        <v>1.16265439987183</v>
+        <v>1.16265428066254</v>
       </c>
       <c r="H195" t="n">
         <v>1118932</v>
@@ -6053,7 +6053,7 @@
         <v>1.68900001049042</v>
       </c>
       <c r="G196" t="n">
-        <v>1.1901353597641</v>
+        <v>1.19013524055481</v>
       </c>
       <c r="H196" t="n">
         <v>693474</v>
@@ -6082,7 +6082,7 @@
         <v>1.64100003242493</v>
       </c>
       <c r="G197" t="n">
-        <v>1.15631258487701</v>
+        <v>1.1563127040863</v>
       </c>
       <c r="H197" t="n">
         <v>2056453</v>
@@ -6111,7 +6111,7 @@
         <v>1.78699994087219</v>
       </c>
       <c r="G198" t="n">
-        <v>1.25918972492218</v>
+        <v>1.25918984413147</v>
       </c>
       <c r="H198" t="n">
         <v>1728258</v>
@@ -6227,7 +6227,7 @@
         <v>1.78199994564056</v>
       </c>
       <c r="G202" t="n">
-        <v>1.2556666135788</v>
+        <v>1.25566673278809</v>
       </c>
       <c r="H202" t="n">
         <v>682872</v>
@@ -6256,7 +6256,7 @@
         <v>1.74600005149841</v>
       </c>
       <c r="G203" t="n">
-        <v>1.23029983043671</v>
+        <v>1.23029971122742</v>
       </c>
       <c r="H203" t="n">
         <v>753784</v>
@@ -6314,7 +6314,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G205" t="n">
-        <v>1.30499148368835</v>
+        <v>1.30499136447906</v>
       </c>
       <c r="H205" t="n">
         <v>1053905</v>
@@ -6372,7 +6372,7 @@
         <v>1.83899998664856</v>
       </c>
       <c r="G207" t="n">
-        <v>1.29583120346069</v>
+        <v>1.2958310842514</v>
       </c>
       <c r="H207" t="n">
         <v>359958</v>
@@ -6459,7 +6459,7 @@
         <v>1.91100001335144</v>
       </c>
       <c r="G210" t="n">
-        <v>1.34656512737274</v>
+        <v>1.34656524658203</v>
       </c>
       <c r="H210" t="n">
         <v>522665</v>
@@ -6517,7 +6517,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G212" t="n">
-        <v>1.29371726512909</v>
+        <v>1.2937171459198</v>
       </c>
       <c r="H212" t="n">
         <v>773982</v>
@@ -6575,7 +6575,7 @@
         <v>1.81099998950958</v>
       </c>
       <c r="G214" t="n">
-        <v>1.27610123157501</v>
+        <v>1.2761013507843</v>
       </c>
       <c r="H214" t="n">
         <v>308754</v>
@@ -6865,7 +6865,7 @@
         <v>2.02099990844727</v>
       </c>
       <c r="G224" t="n">
-        <v>1.42407536506653</v>
+        <v>1.42407548427582</v>
       </c>
       <c r="H224" t="n">
         <v>728660</v>
@@ -6894,7 +6894,7 @@
         <v>1.98300004005432</v>
       </c>
       <c r="G225" t="n">
-        <v>1.39729928970337</v>
+        <v>1.39729917049408</v>
       </c>
       <c r="H225" t="n">
         <v>1086938</v>
@@ -6923,7 +6923,7 @@
         <v>1.93099999427795</v>
       </c>
       <c r="G226" t="n">
-        <v>1.36065793037415</v>
+        <v>1.36065781116486</v>
       </c>
       <c r="H226" t="n">
         <v>764236</v>
@@ -7039,7 +7039,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G230" t="n">
-        <v>1.29442179203033</v>
+        <v>1.29442191123962</v>
       </c>
       <c r="H230" t="n">
         <v>689236</v>
@@ -7097,7 +7097,7 @@
         <v>1.86300003528595</v>
       </c>
       <c r="G232" t="n">
-        <v>1.31274247169495</v>
+        <v>1.31274235248566</v>
       </c>
       <c r="H232" t="n">
         <v>190892</v>
@@ -7126,7 +7126,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G233" t="n">
-        <v>1.27539646625519</v>
+        <v>1.27539658546448</v>
       </c>
       <c r="H233" t="n">
         <v>331881</v>
@@ -7416,7 +7416,7 @@
         <v>1.807000041008</v>
       </c>
       <c r="G243" t="n">
-        <v>1.27328264713287</v>
+        <v>1.27328276634216</v>
       </c>
       <c r="H243" t="n">
         <v>162393</v>
@@ -7503,7 +7503,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G246" t="n">
-        <v>1.36277174949646</v>
+        <v>1.36277186870575</v>
       </c>
       <c r="H246" t="n">
         <v>570217</v>
@@ -7532,7 +7532,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G247" t="n">
-        <v>1.38109254837036</v>
+        <v>1.38109242916107</v>
       </c>
       <c r="H247" t="n">
         <v>439371</v>
@@ -7561,7 +7561,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G248" t="n">
-        <v>1.37263667583466</v>
+        <v>1.37263679504395</v>
       </c>
       <c r="H248" t="n">
         <v>452614</v>
@@ -7619,7 +7619,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G250" t="n">
-        <v>1.36981821060181</v>
+        <v>1.3698183298111</v>
       </c>
       <c r="H250" t="n">
         <v>296376</v>
@@ -7648,7 +7648,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G251" t="n">
-        <v>1.38602483272552</v>
+        <v>1.38602495193481</v>
       </c>
       <c r="H251" t="n">
         <v>191879</v>
@@ -7706,7 +7706,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G253" t="n">
-        <v>1.32824456691742</v>
+        <v>1.32824444770813</v>
       </c>
       <c r="H253" t="n">
         <v>496653</v>
@@ -7735,7 +7735,7 @@
         <v>1.95099997520447</v>
       </c>
       <c r="G254" t="n">
-        <v>1.37475073337555</v>
+        <v>1.37475061416626</v>
       </c>
       <c r="H254" t="n">
         <v>410471</v>
@@ -7851,7 +7851,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G258" t="n">
-        <v>1.39236664772034</v>
+        <v>1.39236652851105</v>
       </c>
       <c r="H258" t="n">
         <v>262724</v>
@@ -7938,7 +7938,7 @@
         <v>1.942999958992</v>
       </c>
       <c r="G261" t="n">
-        <v>1.36911368370056</v>
+        <v>1.36911356449127</v>
       </c>
       <c r="H261" t="n">
         <v>657682</v>
@@ -7967,7 +7967,7 @@
         <v>2.00600004196167</v>
       </c>
       <c r="G262" t="n">
-        <v>1.41350591182709</v>
+        <v>1.4135057926178</v>
       </c>
       <c r="H262" t="n">
         <v>717038</v>
@@ -7996,7 +7996,7 @@
         <v>1.97200000286102</v>
       </c>
       <c r="G263" t="n">
-        <v>1.3895480632782</v>
+        <v>1.38954818248749</v>
       </c>
       <c r="H263" t="n">
         <v>310392</v>
@@ -8054,7 +8054,7 @@
         <v>2.01300001144409</v>
       </c>
       <c r="G265" t="n">
-        <v>1.41843819618225</v>
+        <v>1.41843831539154</v>
       </c>
       <c r="H265" t="n">
         <v>1394290</v>
@@ -8141,7 +8141,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G268" t="n">
-        <v>1.56077539920807</v>
+        <v>1.56077527999878</v>
       </c>
       <c r="H268" t="n">
         <v>856015</v>
@@ -8199,7 +8199,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G270" t="n">
-        <v>1.55161499977112</v>
+        <v>1.55161511898041</v>
       </c>
       <c r="H270" t="n">
         <v>421095</v>
@@ -8228,7 +8228,7 @@
         <v>2.18300008773804</v>
       </c>
       <c r="G271" t="n">
-        <v>1.53822696208954</v>
+        <v>1.53822708129883</v>
       </c>
       <c r="H271" t="n">
         <v>558105</v>
@@ -8257,7 +8257,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G272" t="n">
-        <v>1.5332944393158</v>
+        <v>1.53329455852509</v>
       </c>
       <c r="H272" t="n">
         <v>539558</v>
@@ -8373,7 +8373,7 @@
         <v>2.11199998855591</v>
       </c>
       <c r="G276" t="n">
-        <v>1.48819768428802</v>
+        <v>1.48819756507874</v>
       </c>
       <c r="H276" t="n">
         <v>185994</v>
@@ -8431,7 +8431,7 @@
         <v>2.06699991226196</v>
       </c>
       <c r="G278" t="n">
-        <v>1.45648884773254</v>
+        <v>1.45648872852325</v>
       </c>
       <c r="H278" t="n">
         <v>289759</v>
@@ -8489,7 +8489,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G280" t="n">
-        <v>1.44450998306274</v>
+        <v>1.44450986385345</v>
       </c>
       <c r="H280" t="n">
         <v>636661</v>
@@ -8518,7 +8518,7 @@
         <v>2.03699994087219</v>
       </c>
       <c r="G281" t="n">
-        <v>1.43534958362579</v>
+        <v>1.43534970283508</v>
       </c>
       <c r="H281" t="n">
         <v>774489</v>
@@ -8547,7 +8547,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G282" t="n">
-        <v>1.44450998306274</v>
+        <v>1.44450986385345</v>
       </c>
       <c r="H282" t="n">
         <v>502402</v>
@@ -8692,7 +8692,7 @@
         <v>2.02099990844727</v>
       </c>
       <c r="G287" t="n">
-        <v>1.42407536506653</v>
+        <v>1.42407548427582</v>
       </c>
       <c r="H287" t="n">
         <v>575103</v>
@@ -8721,7 +8721,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G288" t="n">
-        <v>1.43182647228241</v>
+        <v>1.4318265914917</v>
       </c>
       <c r="H288" t="n">
         <v>514101</v>
@@ -8837,7 +8837,7 @@
         <v>2.12400007247925</v>
       </c>
       <c r="G292" t="n">
-        <v>1.49665343761444</v>
+        <v>1.49665331840515</v>
       </c>
       <c r="H292" t="n">
         <v>280648</v>
@@ -8924,7 +8924,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G295" t="n">
-        <v>1.51074600219727</v>
+        <v>1.51074612140656</v>
       </c>
       <c r="H295" t="n">
         <v>440171</v>
@@ -9011,7 +9011,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G298" t="n">
-        <v>1.4755140542984</v>
+        <v>1.47551417350769</v>
       </c>
       <c r="H298" t="n">
         <v>739456</v>
@@ -9040,7 +9040,7 @@
         <v>2.11299991607666</v>
       </c>
       <c r="G299" t="n">
-        <v>1.48890221118927</v>
+        <v>1.48890209197998</v>
       </c>
       <c r="H299" t="n">
         <v>234428</v>
@@ -9069,7 +9069,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G300" t="n">
-        <v>1.51215529441833</v>
+        <v>1.51215517520905</v>
       </c>
       <c r="H300" t="n">
         <v>616627</v>
@@ -9127,7 +9127,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G302" t="n">
-        <v>1.52202033996582</v>
+        <v>1.52202022075653</v>
       </c>
       <c r="H302" t="n">
         <v>208214</v>
@@ -9185,7 +9185,7 @@
         <v>2.06699991226196</v>
       </c>
       <c r="G304" t="n">
-        <v>1.45648884773254</v>
+        <v>1.45648872852325</v>
       </c>
       <c r="H304" t="n">
         <v>302700</v>
@@ -9214,7 +9214,7 @@
         <v>2.05599999427795</v>
       </c>
       <c r="G305" t="n">
-        <v>1.44873785972595</v>
+        <v>1.44873774051666</v>
       </c>
       <c r="H305" t="n">
         <v>446308</v>
@@ -9301,7 +9301,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G308" t="n">
-        <v>1.49383449554443</v>
+        <v>1.49383473396301</v>
       </c>
       <c r="H308" t="n">
         <v>190816</v>
@@ -9388,7 +9388,7 @@
         <v>2.18300008773804</v>
       </c>
       <c r="G311" t="n">
-        <v>1.53822696208954</v>
+        <v>1.53822708129883</v>
       </c>
       <c r="H311" t="n">
         <v>1223387</v>
@@ -9417,7 +9417,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G312" t="n">
-        <v>1.58261930942535</v>
+        <v>1.58261919021606</v>
       </c>
       <c r="H312" t="n">
         <v>1349589</v>
@@ -9446,7 +9446,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G313" t="n">
-        <v>1.61855566501617</v>
+        <v>1.61855578422546</v>
       </c>
       <c r="H313" t="n">
         <v>610651</v>
@@ -9504,7 +9504,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G315" t="n">
-        <v>1.61855566501617</v>
+        <v>1.61855578422546</v>
       </c>
       <c r="H315" t="n">
         <v>297781</v>
@@ -9620,7 +9620,7 @@
         <v>2.29299998283386</v>
       </c>
       <c r="G319" t="n">
-        <v>1.61573731899261</v>
+        <v>1.61573719978333</v>
       </c>
       <c r="H319" t="n">
         <v>855625</v>
@@ -9649,7 +9649,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G320" t="n">
-        <v>1.62489748001099</v>
+        <v>1.62489759922028</v>
       </c>
       <c r="H320" t="n">
         <v>946396</v>
@@ -9678,7 +9678,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G321" t="n">
-        <v>1.63758099079132</v>
+        <v>1.63758087158203</v>
       </c>
       <c r="H321" t="n">
         <v>897308</v>
@@ -9736,7 +9736,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G323" t="n">
-        <v>1.60234904289246</v>
+        <v>1.60234880447388</v>
       </c>
       <c r="H323" t="n">
         <v>324411</v>
@@ -9765,7 +9765,7 @@
         <v>2.2590000629425</v>
       </c>
       <c r="G324" t="n">
-        <v>1.59177958965302</v>
+        <v>1.59177947044373</v>
       </c>
       <c r="H324" t="n">
         <v>573058</v>
@@ -9794,7 +9794,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G325" t="n">
-        <v>1.57416355609894</v>
+        <v>1.57416367530823</v>
       </c>
       <c r="H325" t="n">
         <v>449454</v>
@@ -9823,7 +9823,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G326" t="n">
-        <v>1.51074600219727</v>
+        <v>1.51074612140656</v>
       </c>
       <c r="H326" t="n">
         <v>964268</v>
@@ -9852,7 +9852,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G327" t="n">
-        <v>1.47128629684448</v>
+        <v>1.47128617763519</v>
       </c>
       <c r="H327" t="n">
         <v>1679948</v>
@@ -9881,7 +9881,7 @@
         <v>2.12400007247925</v>
       </c>
       <c r="G328" t="n">
-        <v>1.49665343761444</v>
+        <v>1.49665331840515</v>
       </c>
       <c r="H328" t="n">
         <v>467462</v>
@@ -9997,7 +9997,7 @@
         <v>2.22099995613098</v>
       </c>
       <c r="G332" t="n">
-        <v>1.5650030374527</v>
+        <v>1.56500327587128</v>
       </c>
       <c r="H332" t="n">
         <v>221480</v>
@@ -10084,7 +10084,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G335" t="n">
-        <v>1.5769819021225</v>
+        <v>1.57698202133179</v>
       </c>
       <c r="H335" t="n">
         <v>717837</v>
@@ -10113,7 +10113,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G336" t="n">
-        <v>1.61855566501617</v>
+        <v>1.61855578422546</v>
       </c>
       <c r="H336" t="n">
         <v>709843</v>
@@ -10142,7 +10142,7 @@
         <v>2.28299999237061</v>
       </c>
       <c r="G337" t="n">
-        <v>1.60869073867798</v>
+        <v>1.60869085788727</v>
       </c>
       <c r="H337" t="n">
         <v>602165</v>
@@ -10171,7 +10171,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G338" t="n">
-        <v>1.59671187400818</v>
+        <v>1.59671199321747</v>
       </c>
       <c r="H338" t="n">
         <v>425896</v>
@@ -10258,7 +10258,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G341" t="n">
-        <v>1.65942490100861</v>
+        <v>1.6594250202179</v>
       </c>
       <c r="H341" t="n">
         <v>442544</v>
@@ -10316,7 +10316,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G343" t="n">
-        <v>1.61010015010834</v>
+        <v>1.61010003089905</v>
       </c>
       <c r="H343" t="n">
         <v>391481</v>
@@ -10374,7 +10374,7 @@
         <v>2.33699989318848</v>
       </c>
       <c r="G345" t="n">
-        <v>1.64674115180969</v>
+        <v>1.64674139022827</v>
       </c>
       <c r="H345" t="n">
         <v>1238842</v>
@@ -10403,7 +10403,7 @@
         <v>2.33699989318848</v>
       </c>
       <c r="G346" t="n">
-        <v>1.64674115180969</v>
+        <v>1.64674139022827</v>
       </c>
       <c r="H346" t="n">
         <v>580707</v>
@@ -10461,7 +10461,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G348" t="n">
-        <v>1.5614800453186</v>
+        <v>1.56147992610931</v>
       </c>
       <c r="H348" t="n">
         <v>2800039</v>
@@ -10519,7 +10519,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G350" t="n">
-        <v>1.55161499977112</v>
+        <v>1.55161511898041</v>
       </c>
       <c r="H350" t="n">
         <v>673952</v>
@@ -10548,7 +10548,7 @@
         <v>2.19400000572205</v>
       </c>
       <c r="G351" t="n">
-        <v>1.54597795009613</v>
+        <v>1.54597806930542</v>
       </c>
       <c r="H351" t="n">
         <v>432046</v>
@@ -10606,7 +10606,7 @@
         <v>2.27099990844727</v>
       </c>
       <c r="G353" t="n">
-        <v>1.60023498535156</v>
+        <v>1.60023522377014</v>
       </c>
       <c r="H353" t="n">
         <v>454310</v>
@@ -10664,7 +10664,7 @@
         <v>2.36400008201599</v>
       </c>
       <c r="G355" t="n">
-        <v>1.66576671600342</v>
+        <v>1.66576659679413</v>
       </c>
       <c r="H355" t="n">
         <v>862677</v>
@@ -10693,7 +10693,7 @@
         <v>2.50250005722046</v>
       </c>
       <c r="G356" t="n">
-        <v>1.76335906982422</v>
+        <v>1.76335918903351</v>
       </c>
       <c r="H356" t="n">
         <v>4862397</v>
@@ -10722,7 +10722,7 @@
         <v>2.83750009536743</v>
       </c>
       <c r="G357" t="n">
-        <v>1.99941325187683</v>
+        <v>1.99941301345825</v>
       </c>
       <c r="H357" t="n">
         <v>4829114</v>
@@ -10751,7 +10751,7 @@
         <v>2.7574999332428</v>
       </c>
       <c r="G358" t="n">
-        <v>1.94304215908051</v>
+        <v>1.94304203987122</v>
       </c>
       <c r="H358" t="n">
         <v>5360863</v>
@@ -10780,7 +10780,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G359" t="n">
-        <v>1.86729335784912</v>
+        <v>1.86729347705841</v>
       </c>
       <c r="H359" t="n">
         <v>1790824</v>
@@ -10809,7 +10809,7 @@
         <v>2.69749999046326</v>
       </c>
       <c r="G360" t="n">
-        <v>1.90076351165771</v>
+        <v>1.90076375007629</v>
       </c>
       <c r="H360" t="n">
         <v>2325561</v>
@@ -10838,7 +10838,7 @@
         <v>2.65750002861023</v>
       </c>
       <c r="G361" t="n">
-        <v>1.87257814407349</v>
+        <v>1.87257826328278</v>
       </c>
       <c r="H361" t="n">
         <v>670603</v>
@@ -10896,7 +10896,7 @@
         <v>2.54250001907349</v>
       </c>
       <c r="G363" t="n">
-        <v>1.79154455661774</v>
+        <v>1.79154443740845</v>
       </c>
       <c r="H363" t="n">
         <v>394519</v>
@@ -10925,7 +10925,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G364" t="n">
-        <v>1.7968293428421</v>
+        <v>1.79682946205139</v>
       </c>
       <c r="H364" t="n">
         <v>380123</v>
@@ -10983,7 +10983,7 @@
         <v>2.50250005722046</v>
       </c>
       <c r="G366" t="n">
-        <v>1.76335906982422</v>
+        <v>1.76335918903351</v>
       </c>
       <c r="H366" t="n">
         <v>920397</v>
@@ -11012,7 +11012,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G367" t="n">
-        <v>1.75736951828003</v>
+        <v>1.75736963748932</v>
       </c>
       <c r="H367" t="n">
         <v>543237</v>
@@ -11041,7 +11041,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G368" t="n">
-        <v>1.78626000881195</v>
+        <v>1.78625988960266</v>
       </c>
       <c r="H368" t="n">
         <v>410264</v>
@@ -11070,7 +11070,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G369" t="n">
-        <v>1.80739891529083</v>
+        <v>1.80739915370941</v>
       </c>
       <c r="H369" t="n">
         <v>372165</v>
@@ -11099,7 +11099,7 @@
         <v>2.5550000667572</v>
       </c>
       <c r="G370" t="n">
-        <v>1.80035269260406</v>
+        <v>1.80035281181335</v>
       </c>
       <c r="H370" t="n">
         <v>510079</v>
@@ -11157,7 +11157,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G372" t="n">
-        <v>1.87786293029785</v>
+        <v>1.87786269187927</v>
       </c>
       <c r="H372" t="n">
         <v>730632</v>
@@ -11186,7 +11186,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G373" t="n">
-        <v>1.88490927219391</v>
+        <v>1.8849093914032</v>
       </c>
       <c r="H373" t="n">
         <v>569369</v>
@@ -11273,7 +11273,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G376" t="n">
-        <v>1.86377000808716</v>
+        <v>1.86377024650574</v>
       </c>
       <c r="H376" t="n">
         <v>303450</v>
@@ -11302,7 +11302,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G377" t="n">
-        <v>1.86377000808716</v>
+        <v>1.86377024650574</v>
       </c>
       <c r="H377" t="n">
         <v>377689</v>
@@ -11360,7 +11360,7 @@
         <v>2.64249992370605</v>
       </c>
       <c r="G379" t="n">
-        <v>1.86200845241547</v>
+        <v>1.86200857162476</v>
       </c>
       <c r="H379" t="n">
         <v>662990</v>
@@ -11389,7 +11389,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>1.86377000808716</v>
+        <v>1.86377024650574</v>
       </c>
       <c r="H380" t="n">
         <v>668827</v>
@@ -11418,7 +11418,7 @@
         <v>2.59750008583069</v>
       </c>
       <c r="G381" t="n">
-        <v>1.83029985427856</v>
+        <v>1.83029997348785</v>
       </c>
       <c r="H381" t="n">
         <v>623499</v>
@@ -11476,7 +11476,7 @@
         <v>2.61249995231628</v>
       </c>
       <c r="G383" t="n">
-        <v>1.84086918830872</v>
+        <v>1.84086942672729</v>
       </c>
       <c r="H383" t="n">
         <v>982705</v>
@@ -11505,7 +11505,7 @@
         <v>2.55749988555908</v>
       </c>
       <c r="G384" t="n">
-        <v>1.80211424827576</v>
+        <v>1.80211412906647</v>
       </c>
       <c r="H384" t="n">
         <v>1307235</v>
@@ -11592,7 +11592,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G387" t="n">
-        <v>1.8060120344162</v>
+        <v>1.80601191520691</v>
       </c>
       <c r="H387" t="n">
         <v>2221253</v>
@@ -11679,7 +11679,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G390" t="n">
-        <v>1.851318359375</v>
+        <v>1.85131847858429</v>
       </c>
       <c r="H390" t="n">
         <v>717045</v>
@@ -11708,7 +11708,7 @@
         <v>2.40700006484985</v>
       </c>
       <c r="G391" t="n">
-        <v>1.88022112846375</v>
+        <v>1.88022089004517</v>
       </c>
       <c r="H391" t="n">
         <v>1427819</v>
@@ -11737,7 +11737,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G392" t="n">
-        <v>1.84741270542145</v>
+        <v>1.84741282463074</v>
       </c>
       <c r="H392" t="n">
         <v>573846</v>
@@ -11824,7 +11824,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G395" t="n">
-        <v>1.84506928920746</v>
+        <v>1.84506916999817</v>
       </c>
       <c r="H395" t="n">
         <v>768257</v>
@@ -11882,7 +11882,7 @@
         <v>2.29699993133545</v>
       </c>
       <c r="G397" t="n">
-        <v>1.79429459571838</v>
+        <v>1.79429471492767</v>
       </c>
       <c r="H397" t="n">
         <v>625118</v>
@@ -11969,7 +11969,7 @@
         <v>2.29900002479553</v>
       </c>
       <c r="G400" t="n">
-        <v>1.79585695266724</v>
+        <v>1.79585707187653</v>
       </c>
       <c r="H400" t="n">
         <v>435929</v>
@@ -11998,7 +11998,7 @@
         <v>2.30800008773804</v>
       </c>
       <c r="G401" t="n">
-        <v>1.80288743972778</v>
+        <v>1.80288755893707</v>
       </c>
       <c r="H401" t="n">
         <v>290608</v>
@@ -12056,7 +12056,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G403" t="n">
-        <v>1.84350681304932</v>
+        <v>1.84350693225861</v>
       </c>
       <c r="H403" t="n">
         <v>508765</v>
@@ -12085,7 +12085,7 @@
         <v>2.34299993515015</v>
       </c>
       <c r="G404" t="n">
-        <v>1.83022749423981</v>
+        <v>1.83022737503052</v>
       </c>
       <c r="H404" t="n">
         <v>400051</v>
@@ -12114,7 +12114,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G405" t="n">
-        <v>1.85912990570068</v>
+        <v>1.85913002490997</v>
       </c>
       <c r="H405" t="n">
         <v>572167</v>
@@ -12143,7 +12143,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G406" t="n">
-        <v>1.82944619655609</v>
+        <v>1.82944655418396</v>
       </c>
       <c r="H406" t="n">
         <v>327031</v>
@@ -12259,7 +12259,7 @@
         <v>2.29900002479553</v>
       </c>
       <c r="G410" t="n">
-        <v>1.79585695266724</v>
+        <v>1.79585707187653</v>
       </c>
       <c r="H410" t="n">
         <v>244821</v>
@@ -12288,7 +12288,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G411" t="n">
-        <v>1.8060120344162</v>
+        <v>1.80601191520691</v>
       </c>
       <c r="H411" t="n">
         <v>489918</v>
@@ -12404,7 +12404,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G415" t="n">
-        <v>1.79351365566254</v>
+        <v>1.79351353645325</v>
       </c>
       <c r="H415" t="n">
         <v>274714</v>
@@ -12520,7 +12520,7 @@
         <v>2.23699998855591</v>
       </c>
       <c r="G419" t="n">
-        <v>1.74742591381073</v>
+        <v>1.74742603302002</v>
       </c>
       <c r="H419" t="n">
         <v>1089414</v>
@@ -12607,7 +12607,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G422" t="n">
-        <v>1.73024070262909</v>
+        <v>1.7302405834198</v>
       </c>
       <c r="H422" t="n">
         <v>493842</v>
@@ -12665,7 +12665,7 @@
         <v>2.14100003242493</v>
       </c>
       <c r="G424" t="n">
-        <v>1.67243576049805</v>
+        <v>1.67243587970734</v>
       </c>
       <c r="H424" t="n">
         <v>2417146</v>
@@ -12723,7 +12723,7 @@
         <v>2.11700010299683</v>
       </c>
       <c r="G426" t="n">
-        <v>1.65368843078613</v>
+        <v>1.65368831157684</v>
       </c>
       <c r="H426" t="n">
         <v>542238</v>
@@ -12752,7 +12752,7 @@
         <v>2.11299991607666</v>
       </c>
       <c r="G427" t="n">
-        <v>1.65056347846985</v>
+        <v>1.65056359767914</v>
       </c>
       <c r="H427" t="n">
         <v>344744</v>
@@ -12781,7 +12781,7 @@
         <v>2.1010000705719</v>
       </c>
       <c r="G428" t="n">
-        <v>1.64119005203247</v>
+        <v>1.64118993282318</v>
       </c>
       <c r="H428" t="n">
         <v>384515</v>
@@ -12955,7 +12955,7 @@
         <v>1.99899995326996</v>
       </c>
       <c r="G434" t="n">
-        <v>1.56151282787323</v>
+        <v>1.56151294708252</v>
       </c>
       <c r="H434" t="n">
         <v>852921</v>
@@ -13013,7 +13013,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G436" t="n">
-        <v>1.45762038230896</v>
+        <v>1.45762050151825</v>
       </c>
       <c r="H436" t="n">
         <v>630873</v>
@@ -13042,7 +13042,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G437" t="n">
-        <v>1.44121623039246</v>
+        <v>1.44121634960175</v>
       </c>
       <c r="H437" t="n">
         <v>430171</v>
@@ -13071,7 +13071,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G438" t="n">
-        <v>1.43887293338776</v>
+        <v>1.43887281417847</v>
       </c>
       <c r="H438" t="n">
         <v>297282</v>
@@ -13332,7 +13332,7 @@
         <v>1.85300004482269</v>
       </c>
       <c r="G447" t="n">
-        <v>1.44746541976929</v>
+        <v>1.44746553897858</v>
       </c>
       <c r="H447" t="n">
         <v>756122</v>
@@ -13361,7 +13361,7 @@
         <v>1.84399998188019</v>
       </c>
       <c r="G448" t="n">
-        <v>1.44043517112732</v>
+        <v>1.44043505191803</v>
       </c>
       <c r="H448" t="n">
         <v>564069</v>
@@ -13390,7 +13390,7 @@
         <v>1.8309999704361</v>
       </c>
       <c r="G449" t="n">
-        <v>1.43028020858765</v>
+        <v>1.43028008937836</v>
       </c>
       <c r="H449" t="n">
         <v>475160</v>
@@ -13506,7 +13506,7 @@
         <v>1.67340004444122</v>
       </c>
       <c r="G453" t="n">
-        <v>1.30717146396637</v>
+        <v>1.30717158317566</v>
       </c>
       <c r="H453" t="n">
         <v>770495</v>
@@ -13535,7 +13535,7 @@
         <v>1.66719996929169</v>
       </c>
       <c r="G454" t="n">
-        <v>1.3023282289505</v>
+        <v>1.30232834815979</v>
       </c>
       <c r="H454" t="n">
         <v>438827</v>
@@ -13564,7 +13564,7 @@
         <v>1.69219994544983</v>
       </c>
       <c r="G455" t="n">
-        <v>1.32185685634613</v>
+        <v>1.32185697555542</v>
       </c>
       <c r="H455" t="n">
         <v>907774</v>
@@ -13622,7 +13622,7 @@
         <v>1.69159996509552</v>
       </c>
       <c r="G457" t="n">
-        <v>1.32138824462891</v>
+        <v>1.3213883638382</v>
       </c>
       <c r="H457" t="n">
         <v>232730</v>
@@ -13651,7 +13651,7 @@
         <v>1.74259996414185</v>
       </c>
       <c r="G458" t="n">
-        <v>1.36122667789459</v>
+        <v>1.36122679710388</v>
       </c>
       <c r="H458" t="n">
         <v>372410</v>
@@ -13680,7 +13680,7 @@
         <v>1.84239995479584</v>
       </c>
       <c r="G459" t="n">
-        <v>1.43918514251709</v>
+        <v>1.43918526172638</v>
       </c>
       <c r="H459" t="n">
         <v>501526</v>
@@ -13767,7 +13767,7 @@
         <v>1.80599999427795</v>
       </c>
       <c r="G462" t="n">
-        <v>1.41075158119202</v>
+        <v>1.41075146198273</v>
       </c>
       <c r="H462" t="n">
         <v>246924</v>
@@ -13825,7 +13825,7 @@
         <v>1.93680000305176</v>
       </c>
       <c r="G464" t="n">
-        <v>1.51292550563812</v>
+        <v>1.51292562484741</v>
       </c>
       <c r="H464" t="n">
         <v>268931</v>
@@ -13941,7 +13941,7 @@
         <v>1.97259998321533</v>
       </c>
       <c r="G468" t="n">
-        <v>1.54089057445526</v>
+        <v>1.54089069366455</v>
       </c>
       <c r="H468" t="n">
         <v>448541</v>
@@ -13970,7 +13970,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G469" t="n">
-        <v>1.58729076385498</v>
+        <v>1.58729088306427</v>
       </c>
       <c r="H469" t="n">
         <v>310094</v>
@@ -14086,7 +14086,7 @@
         <v>2.15249991416931</v>
       </c>
       <c r="G473" t="n">
-        <v>1.68141901493073</v>
+        <v>1.68141889572144</v>
       </c>
       <c r="H473" t="n">
         <v>1172106</v>
@@ -14144,7 +14144,7 @@
         <v>2.25950002670288</v>
       </c>
       <c r="G475" t="n">
-        <v>1.76500165462494</v>
+        <v>1.76500177383423</v>
       </c>
       <c r="H475" t="n">
         <v>775246</v>
@@ -14173,7 +14173,7 @@
         <v>2.25650000572205</v>
       </c>
       <c r="G476" t="n">
-        <v>1.76265823841095</v>
+        <v>1.76265835762024</v>
       </c>
       <c r="H476" t="n">
         <v>463148</v>
@@ -14202,7 +14202,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G477" t="n">
-        <v>1.75601851940155</v>
+        <v>1.75601840019226</v>
       </c>
       <c r="H477" t="n">
         <v>381912</v>
@@ -14231,7 +14231,7 @@
         <v>2.22699999809265</v>
       </c>
       <c r="G478" t="n">
-        <v>1.73961448669434</v>
+        <v>1.73961436748505</v>
       </c>
       <c r="H478" t="n">
         <v>1434510</v>
@@ -14318,7 +14318,7 @@
         <v>2.22300004959106</v>
       </c>
       <c r="G481" t="n">
-        <v>1.73648989200592</v>
+        <v>1.73649001121521</v>
       </c>
       <c r="H481" t="n">
         <v>624711</v>
@@ -14347,7 +14347,7 @@
         <v>2.31900000572205</v>
       </c>
       <c r="G482" t="n">
-        <v>1.8114800453186</v>
+        <v>1.81147992610931</v>
       </c>
       <c r="H482" t="n">
         <v>1426253</v>
@@ -14376,7 +14376,7 @@
         <v>2.29749989509583</v>
       </c>
       <c r="G483" t="n">
-        <v>1.79468524456024</v>
+        <v>1.79468536376953</v>
       </c>
       <c r="H483" t="n">
         <v>1095196</v>
@@ -14434,7 +14434,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G485" t="n">
-        <v>1.86850345134735</v>
+        <v>1.86850368976593</v>
       </c>
       <c r="H485" t="n">
         <v>792725</v>
@@ -14463,7 +14463,7 @@
         <v>2.32649993896484</v>
       </c>
       <c r="G486" t="n">
-        <v>1.81733858585358</v>
+        <v>1.81733870506287</v>
       </c>
       <c r="H486" t="n">
         <v>753540</v>
@@ -14550,7 +14550,7 @@
         <v>2.34949994087219</v>
       </c>
       <c r="G489" t="n">
-        <v>1.83530509471893</v>
+        <v>1.83530497550964</v>
       </c>
       <c r="H489" t="n">
         <v>626584</v>
@@ -14579,7 +14579,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G490" t="n">
-        <v>1.82007253170013</v>
+        <v>1.82007241249084</v>
       </c>
       <c r="H490" t="n">
         <v>579196</v>
@@ -14608,7 +14608,7 @@
         <v>2.39750003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>1.87280011177063</v>
+        <v>1.87280023097992</v>
       </c>
       <c r="H491" t="n">
         <v>839004</v>
@@ -14637,7 +14637,7 @@
         <v>2.3989999294281</v>
       </c>
       <c r="G492" t="n">
-        <v>1.87397158145905</v>
+        <v>1.87397170066833</v>
       </c>
       <c r="H492" t="n">
         <v>458199</v>
@@ -14695,7 +14695,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G494" t="n">
-        <v>1.85912990570068</v>
+        <v>1.85913002490997</v>
       </c>
       <c r="H494" t="n">
         <v>254944</v>
@@ -14724,7 +14724,7 @@
         <v>2.38100004196167</v>
       </c>
       <c r="G495" t="n">
-        <v>1.8599112033844</v>
+        <v>1.85991108417511</v>
       </c>
       <c r="H495" t="n">
         <v>360476</v>
@@ -14753,7 +14753,7 @@
         <v>2.375</v>
       </c>
       <c r="G496" t="n">
-        <v>1.85522401332855</v>
+        <v>1.85522413253784</v>
       </c>
       <c r="H496" t="n">
         <v>380134</v>
@@ -14927,7 +14927,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G502" t="n">
-        <v>1.89662492275238</v>
+        <v>1.89662504196167</v>
       </c>
       <c r="H502" t="n">
         <v>886759</v>
@@ -14956,7 +14956,7 @@
         <v>2.4210000038147</v>
       </c>
       <c r="G503" t="n">
-        <v>1.89115715026855</v>
+        <v>1.89115703105927</v>
       </c>
       <c r="H503" t="n">
         <v>400870</v>
@@ -14985,7 +14985,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G504" t="n">
-        <v>1.90443646907806</v>
+        <v>1.90443634986877</v>
       </c>
       <c r="H504" t="n">
         <v>376866</v>
@@ -15072,7 +15072,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G507" t="n">
-        <v>1.851318359375</v>
+        <v>1.85131847858429</v>
       </c>
       <c r="H507" t="n">
         <v>420850</v>
@@ -15101,7 +15101,7 @@
         <v>2.38750004768372</v>
       </c>
       <c r="G508" t="n">
-        <v>1.86498880386353</v>
+        <v>1.86498844623566</v>
       </c>
       <c r="H508" t="n">
         <v>279164</v>
@@ -15130,7 +15130,7 @@
         <v>2.37949991226196</v>
       </c>
       <c r="G509" t="n">
-        <v>1.85873925685883</v>
+        <v>1.85873913764954</v>
       </c>
       <c r="H509" t="n">
         <v>517495</v>
@@ -15188,7 +15188,7 @@
         <v>2.30800008773804</v>
       </c>
       <c r="G511" t="n">
-        <v>1.80288743972778</v>
+        <v>1.80288755893707</v>
       </c>
       <c r="H511" t="n">
         <v>471638</v>
@@ -15275,7 +15275,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G514" t="n">
-        <v>1.84819376468658</v>
+        <v>1.84819388389587</v>
       </c>
       <c r="H514" t="n">
         <v>499423</v>
@@ -15304,7 +15304,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G515" t="n">
-        <v>1.88256430625916</v>
+        <v>1.88256442546844</v>
       </c>
       <c r="H515" t="n">
         <v>456876</v>
@@ -15333,7 +15333,7 @@
         <v>2.38700008392334</v>
       </c>
       <c r="G516" t="n">
-        <v>1.86459803581238</v>
+        <v>1.86459815502167</v>
       </c>
       <c r="H516" t="n">
         <v>378435</v>
@@ -15391,7 +15391,7 @@
         <v>2.35949993133545</v>
       </c>
       <c r="G518" t="n">
-        <v>1.84311640262604</v>
+        <v>1.84311628341675</v>
       </c>
       <c r="H518" t="n">
         <v>314732</v>
@@ -15420,7 +15420,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G519" t="n">
-        <v>1.84506928920746</v>
+        <v>1.84506916999817</v>
       </c>
       <c r="H519" t="n">
         <v>346938</v>
@@ -15478,7 +15478,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G521" t="n">
-        <v>1.83960127830505</v>
+        <v>1.83960139751434</v>
       </c>
       <c r="H521" t="n">
         <v>400601</v>
@@ -15536,7 +15536,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G523" t="n">
-        <v>1.74352037906647</v>
+        <v>1.74352014064789</v>
       </c>
       <c r="H523" t="n">
         <v>587511</v>
@@ -15594,7 +15594,7 @@
         <v>2.18650007247925</v>
       </c>
       <c r="G525" t="n">
-        <v>1.70797801017761</v>
+        <v>1.7079781293869</v>
       </c>
       <c r="H525" t="n">
         <v>339135</v>
@@ -15710,7 +15710,7 @@
         <v>2.1324999332428</v>
       </c>
       <c r="G529" t="n">
-        <v>1.66579604148865</v>
+        <v>1.66579592227936</v>
       </c>
       <c r="H529" t="n">
         <v>1224677</v>
@@ -15739,7 +15739,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G530" t="n">
-        <v>1.65603160858154</v>
+        <v>1.65603172779083</v>
       </c>
       <c r="H530" t="n">
         <v>1091564</v>
@@ -15855,7 +15855,7 @@
         <v>2.1029999256134</v>
       </c>
       <c r="G534" t="n">
-        <v>1.64275205135345</v>
+        <v>1.64275217056274</v>
       </c>
       <c r="H534" t="n">
         <v>489001</v>
@@ -16000,7 +16000,7 @@
         <v>2.1010000705719</v>
       </c>
       <c r="G539" t="n">
-        <v>1.64119005203247</v>
+        <v>1.64118993282318</v>
       </c>
       <c r="H539" t="n">
         <v>348613</v>
@@ -16058,7 +16058,7 @@
         <v>2.10949993133545</v>
       </c>
       <c r="G541" t="n">
-        <v>1.64782965183258</v>
+        <v>1.64782953262329</v>
       </c>
       <c r="H541" t="n">
         <v>509259</v>
@@ -16174,7 +16174,7 @@
         <v>2.12750005722046</v>
       </c>
       <c r="G545" t="n">
-        <v>1.66189050674438</v>
+        <v>1.6618903875351</v>
       </c>
       <c r="H545" t="n">
         <v>1419921</v>
@@ -16203,7 +16203,7 @@
         <v>2.14299988746643</v>
       </c>
       <c r="G546" t="n">
-        <v>1.67399799823761</v>
+        <v>1.67399787902832</v>
       </c>
       <c r="H546" t="n">
         <v>1450618</v>
@@ -16232,7 +16232,7 @@
         <v>2.10949993133545</v>
       </c>
       <c r="G547" t="n">
-        <v>1.64782965183258</v>
+        <v>1.64782953262329</v>
       </c>
       <c r="H547" t="n">
         <v>489388</v>
@@ -16290,7 +16290,7 @@
         <v>2.12949991226196</v>
       </c>
       <c r="G549" t="n">
-        <v>1.66345250606537</v>
+        <v>1.66345262527466</v>
       </c>
       <c r="H549" t="n">
         <v>838112</v>
@@ -16348,7 +16348,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G551" t="n">
-        <v>1.67009222507477</v>
+        <v>1.67009234428406</v>
       </c>
       <c r="H551" t="n">
         <v>1192328</v>
@@ -16435,7 +16435,7 @@
         <v>2.24300003051758</v>
       </c>
       <c r="G554" t="n">
-        <v>1.752112865448</v>
+        <v>1.75211274623871</v>
       </c>
       <c r="H554" t="n">
         <v>387019</v>
@@ -16464,7 +16464,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G555" t="n">
-        <v>1.74352037906647</v>
+        <v>1.74352014064789</v>
       </c>
       <c r="H555" t="n">
         <v>532106</v>
@@ -16493,7 +16493,7 @@
         <v>2.24449992179871</v>
       </c>
       <c r="G556" t="n">
-        <v>1.75328433513641</v>
+        <v>1.75328457355499</v>
       </c>
       <c r="H556" t="n">
         <v>397911</v>
@@ -16522,7 +16522,7 @@
         <v>2.30550003051758</v>
       </c>
       <c r="G557" t="n">
-        <v>1.80093455314636</v>
+        <v>1.80093443393707</v>
       </c>
       <c r="H557" t="n">
         <v>567946</v>
@@ -16580,7 +16580,7 @@
         <v>2.42149996757507</v>
       </c>
       <c r="G559" t="n">
-        <v>1.89154756069183</v>
+        <v>1.89154744148254</v>
       </c>
       <c r="H559" t="n">
         <v>1056336</v>
@@ -16609,7 +16609,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G560" t="n">
-        <v>1.8786586523056</v>
+        <v>1.87865853309631</v>
       </c>
       <c r="H560" t="n">
         <v>518625</v>
@@ -16638,7 +16638,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G561" t="n">
-        <v>1.92630863189697</v>
+        <v>1.92630875110626</v>
       </c>
       <c r="H561" t="n">
         <v>1119220</v>
@@ -16667,7 +16667,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G562" t="n">
-        <v>1.95130503177643</v>
+        <v>1.95130515098572</v>
       </c>
       <c r="H562" t="n">
         <v>455972</v>
@@ -16696,7 +16696,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G563" t="n">
-        <v>1.96536588668823</v>
+        <v>1.96536612510681</v>
       </c>
       <c r="H563" t="n">
         <v>1160065</v>
@@ -16754,7 +16754,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G565" t="n">
-        <v>1.97473990917206</v>
+        <v>1.97473978996277</v>
       </c>
       <c r="H565" t="n">
         <v>742112</v>
@@ -16812,7 +16812,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G567" t="n">
-        <v>1.97473990917206</v>
+        <v>1.97473978996277</v>
       </c>
       <c r="H567" t="n">
         <v>1363010</v>
@@ -16841,7 +16841,7 @@
         <v>2.55599999427795</v>
       </c>
       <c r="G568" t="n">
-        <v>1.99661183357239</v>
+        <v>1.9966117143631</v>
       </c>
       <c r="H568" t="n">
         <v>1003381</v>
@@ -16870,7 +16870,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G569" t="n">
-        <v>1.92005932331085</v>
+        <v>1.92005956172943</v>
       </c>
       <c r="H569" t="n">
         <v>1136036</v>
@@ -16899,7 +16899,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G570" t="n">
-        <v>1.9294331073761</v>
+        <v>1.92943322658539</v>
       </c>
       <c r="H570" t="n">
         <v>765788</v>
@@ -16928,7 +16928,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G571" t="n">
-        <v>1.93099534511566</v>
+        <v>1.93099522590637</v>
       </c>
       <c r="H571" t="n">
         <v>439198</v>
@@ -16986,7 +16986,7 @@
         <v>2.56800007820129</v>
       </c>
       <c r="G573" t="n">
-        <v>2.00598549842834</v>
+        <v>2.00598573684692</v>
       </c>
       <c r="H573" t="n">
         <v>4035540</v>
@@ -17044,7 +17044,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G575" t="n">
-        <v>2.04660534858704</v>
+        <v>2.04660511016846</v>
       </c>
       <c r="H575" t="n">
         <v>671436</v>
@@ -17073,7 +17073,7 @@
         <v>2.70600008964539</v>
       </c>
       <c r="G576" t="n">
-        <v>2.11378407478333</v>
+        <v>2.11378383636475</v>
       </c>
       <c r="H576" t="n">
         <v>1342948</v>
@@ -17160,7 +17160,7 @@
         <v>2.71799993515015</v>
       </c>
       <c r="G579" t="n">
-        <v>2.1231575012207</v>
+        <v>2.12315773963928</v>
       </c>
       <c r="H579" t="n">
         <v>1054021</v>
@@ -17305,7 +17305,7 @@
         <v>2.76200008392334</v>
       </c>
       <c r="G584" t="n">
-        <v>2.15752840042114</v>
+        <v>2.15752816200256</v>
       </c>
       <c r="H584" t="n">
         <v>580443</v>
@@ -17334,7 +17334,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G585" t="n">
-        <v>2.1965856552124</v>
+        <v>2.19658541679382</v>
       </c>
       <c r="H585" t="n">
         <v>1518765</v>
@@ -17537,7 +17537,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G592" t="n">
-        <v>2.43874073028564</v>
+        <v>2.43874096870422</v>
       </c>
       <c r="H592" t="n">
         <v>965545</v>
@@ -17624,7 +17624,7 @@
         <v>3.11400008201599</v>
       </c>
       <c r="G595" t="n">
-        <v>2.43249201774597</v>
+        <v>2.43249177932739</v>
       </c>
       <c r="H595" t="n">
         <v>1799003</v>
@@ -17653,7 +17653,7 @@
         <v>3.00399994850159</v>
       </c>
       <c r="G596" t="n">
-        <v>2.34656572341919</v>
+        <v>2.34656548500061</v>
       </c>
       <c r="H596" t="n">
         <v>921949</v>
@@ -17682,7 +17682,7 @@
         <v>3</v>
       </c>
       <c r="G597" t="n">
-        <v>2.34344100952148</v>
+        <v>2.34344124794006</v>
       </c>
       <c r="H597" t="n">
         <v>1851145</v>
@@ -17798,7 +17798,7 @@
         <v>3.05200004577637</v>
       </c>
       <c r="G601" t="n">
-        <v>2.3840606212616</v>
+        <v>2.38406085968018</v>
       </c>
       <c r="H601" t="n">
         <v>913843</v>
@@ -17856,7 +17856,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G603" t="n">
-        <v>2.46529984474182</v>
+        <v>2.4653000831604</v>
       </c>
       <c r="H603" t="n">
         <v>1511750</v>
@@ -17885,7 +17885,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G604" t="n">
-        <v>2.46529984474182</v>
+        <v>2.4653000831604</v>
       </c>
       <c r="H604" t="n">
         <v>2000044</v>
@@ -17914,7 +17914,7 @@
         <v>3.17400002479553</v>
       </c>
       <c r="G605" t="n">
-        <v>2.47936058044434</v>
+        <v>2.47936081886292</v>
       </c>
       <c r="H605" t="n">
         <v>2744827</v>
@@ -18001,7 +18001,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G608" t="n">
-        <v>2.5465395450592</v>
+        <v>2.54653930664062</v>
       </c>
       <c r="H608" t="n">
         <v>795781</v>
@@ -18059,7 +18059,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G610" t="n">
-        <v>2.46373796463013</v>
+        <v>2.46373772621155</v>
       </c>
       <c r="H610" t="n">
         <v>1532299</v>
@@ -18088,7 +18088,7 @@
         <v>3.24600005149841</v>
       </c>
       <c r="G611" t="n">
-        <v>2.53560328483582</v>
+        <v>2.53560304641724</v>
       </c>
       <c r="H611" t="n">
         <v>978496</v>
@@ -18117,7 +18117,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G612" t="n">
-        <v>2.4137442111969</v>
+        <v>2.41374444961548</v>
       </c>
       <c r="H612" t="n">
         <v>1036670</v>
@@ -18175,7 +18175,7 @@
         <v>3.09599995613098</v>
       </c>
       <c r="G614" t="n">
-        <v>2.41843128204346</v>
+        <v>2.41843104362488</v>
       </c>
       <c r="H614" t="n">
         <v>539410</v>
@@ -18233,7 +18233,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G616" t="n">
-        <v>2.39343452453613</v>
+        <v>2.39343428611755</v>
       </c>
       <c r="H616" t="n">
         <v>397137</v>
@@ -18436,7 +18436,7 @@
         <v>3.21799993515015</v>
       </c>
       <c r="G623" t="n">
-        <v>2.51373100280762</v>
+        <v>2.5137312412262</v>
       </c>
       <c r="H623" t="n">
         <v>829894</v>
@@ -18494,7 +18494,7 @@
         <v>3.24799990653992</v>
       </c>
       <c r="G625" t="n">
-        <v>2.53716540336609</v>
+        <v>2.53716564178467</v>
       </c>
       <c r="H625" t="n">
         <v>505088</v>
@@ -18523,7 +18523,7 @@
         <v>3.2720000743866</v>
       </c>
       <c r="G626" t="n">
-        <v>2.55591320991516</v>
+        <v>2.55591297149658</v>
       </c>
       <c r="H626" t="n">
         <v>682877</v>
@@ -18610,7 +18610,7 @@
         <v>3.26399993896484</v>
       </c>
       <c r="G629" t="n">
-        <v>2.54966378211975</v>
+        <v>2.54966402053833</v>
       </c>
       <c r="H629" t="n">
         <v>1449732</v>
@@ -18668,7 +18668,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G631" t="n">
-        <v>2.57778525352478</v>
+        <v>2.5777850151062</v>
       </c>
       <c r="H631" t="n">
         <v>943074</v>
@@ -18726,7 +18726,7 @@
         <v>3.42199993133545</v>
       </c>
       <c r="G633" t="n">
-        <v>2.67308497428894</v>
+        <v>2.67308521270752</v>
       </c>
       <c r="H633" t="n">
         <v>1448985</v>
@@ -18842,7 +18842,7 @@
         <v>3.53200006484985</v>
       </c>
       <c r="G637" t="n">
-        <v>2.75901126861572</v>
+        <v>2.7590115070343</v>
       </c>
       <c r="H637" t="n">
         <v>1376981</v>
@@ -18929,7 +18929,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G640" t="n">
-        <v>2.66151165962219</v>
+        <v>2.66151189804077</v>
       </c>
       <c r="H640" t="n">
         <v>1142550</v>
@@ -19074,7 +19074,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G645" t="n">
-        <v>2.65814256668091</v>
+        <v>2.65814280509949</v>
       </c>
       <c r="H645" t="n">
         <v>687583</v>
@@ -19132,7 +19132,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G647" t="n">
-        <v>2.59413170814514</v>
+        <v>2.59413146972656</v>
       </c>
       <c r="H647" t="n">
         <v>573464</v>
@@ -19161,7 +19161,7 @@
         <v>3.01399993896484</v>
       </c>
       <c r="G648" t="n">
-        <v>2.53854322433472</v>
+        <v>2.53854298591614</v>
       </c>
       <c r="H648" t="n">
         <v>931043</v>
@@ -19248,7 +19248,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G651" t="n">
-        <v>2.44926452636719</v>
+        <v>2.44926476478577</v>
       </c>
       <c r="H651" t="n">
         <v>488032</v>
@@ -19422,7 +19422,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G657" t="n">
-        <v>2.45600271224976</v>
+        <v>2.45600247383118</v>
       </c>
       <c r="H657" t="n">
         <v>344477</v>
@@ -19567,7 +19567,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G662" t="n">
-        <v>2.47116303443909</v>
+        <v>2.47116327285767</v>
       </c>
       <c r="H662" t="n">
         <v>401363</v>
@@ -19683,7 +19683,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G666" t="n">
-        <v>2.48800826072693</v>
+        <v>2.48800802230835</v>
       </c>
       <c r="H666" t="n">
         <v>259923</v>
@@ -19741,7 +19741,7 @@
         <v>2.89800000190735</v>
       </c>
       <c r="G668" t="n">
-        <v>2.44084215164185</v>
+        <v>2.44084191322327</v>
       </c>
       <c r="H668" t="n">
         <v>360472</v>
@@ -20031,7 +20031,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G678" t="n">
-        <v>2.35661721229553</v>
+        <v>2.35661697387695</v>
       </c>
       <c r="H678" t="n">
         <v>240265</v>
@@ -20118,7 +20118,7 @@
         <v>3.22399997711182</v>
       </c>
       <c r="G681" t="n">
-        <v>2.71541595458984</v>
+        <v>2.71541571617126</v>
       </c>
       <c r="H681" t="n">
         <v>4686248</v>
@@ -20147,7 +20147,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G682" t="n">
-        <v>2.57223320007324</v>
+        <v>2.57223296165466</v>
       </c>
       <c r="H682" t="n">
         <v>2047557</v>
@@ -20321,7 +20321,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G688" t="n">
-        <v>2.61097645759583</v>
+        <v>2.6109766960144</v>
       </c>
       <c r="H688" t="n">
         <v>540996</v>
@@ -20350,7 +20350,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G689" t="n">
-        <v>2.5857093334198</v>
+        <v>2.58570909500122</v>
       </c>
       <c r="H689" t="n">
         <v>835995</v>
@@ -20379,7 +20379,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G690" t="n">
-        <v>2.57560205459595</v>
+        <v>2.57560229301453</v>
       </c>
       <c r="H690" t="n">
         <v>1181402</v>
@@ -20408,7 +20408,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G691" t="n">
-        <v>2.49306154251099</v>
+        <v>2.49306178092957</v>
       </c>
       <c r="H691" t="n">
         <v>554383</v>
@@ -20524,7 +20524,7 @@
         <v>3.03200006484985</v>
       </c>
       <c r="G695" t="n">
-        <v>2.55370354652405</v>
+        <v>2.55370378494263</v>
       </c>
       <c r="H695" t="n">
         <v>176181</v>
@@ -20640,7 +20640,7 @@
         <v>3.06800007820129</v>
       </c>
       <c r="G699" t="n">
-        <v>2.58402490615845</v>
+        <v>2.58402466773987</v>
       </c>
       <c r="H699" t="n">
         <v>565902</v>
@@ -20872,7 +20872,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G707" t="n">
-        <v>2.5857093334198</v>
+        <v>2.58570909500122</v>
       </c>
       <c r="H707" t="n">
         <v>503676</v>
@@ -20959,7 +20959,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G710" t="n">
-        <v>2.50990676879883</v>
+        <v>2.50990653038025</v>
       </c>
       <c r="H710" t="n">
         <v>1933202</v>
@@ -20988,7 +20988,7 @@
         <v>3.01399993896484</v>
       </c>
       <c r="G711" t="n">
-        <v>2.53854322433472</v>
+        <v>2.53854298591614</v>
       </c>
       <c r="H711" t="n">
         <v>357710</v>
@@ -21017,7 +21017,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G712" t="n">
-        <v>2.50990676879883</v>
+        <v>2.50990653038025</v>
       </c>
       <c r="H712" t="n">
         <v>660930</v>
@@ -21075,7 +21075,7 @@
         <v>2.91400003433228</v>
       </c>
       <c r="G714" t="n">
-        <v>2.4543182849884</v>
+        <v>2.45431804656982</v>
       </c>
       <c r="H714" t="n">
         <v>482372</v>
@@ -21162,7 +21162,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G717" t="n">
-        <v>2.45600271224976</v>
+        <v>2.45600247383118</v>
       </c>
       <c r="H717" t="n">
         <v>519899</v>
@@ -21423,7 +21423,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G726" t="n">
-        <v>2.44926452636719</v>
+        <v>2.44926476478577</v>
       </c>
       <c r="H726" t="n">
         <v>2315220</v>
@@ -21655,7 +21655,7 @@
         <v>2.79200005531311</v>
       </c>
       <c r="G734" t="n">
-        <v>2.35156345367432</v>
+        <v>2.3515636920929</v>
       </c>
       <c r="H734" t="n">
         <v>407635</v>
@@ -21684,7 +21684,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G735" t="n">
-        <v>2.41388988494873</v>
+        <v>2.41389012336731</v>
       </c>
       <c r="H735" t="n">
         <v>672584</v>
@@ -21887,7 +21887,7 @@
         <v>3.04200005531311</v>
       </c>
       <c r="G742" t="n">
-        <v>2.56212639808655</v>
+        <v>2.56212615966797</v>
       </c>
       <c r="H742" t="n">
         <v>920296</v>
@@ -22003,7 +22003,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G746" t="n">
-        <v>2.48295450210571</v>
+        <v>2.48295474052429</v>
       </c>
       <c r="H746" t="n">
         <v>959673</v>
@@ -22177,7 +22177,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>2.49306154251099</v>
+        <v>2.49306178092957</v>
       </c>
       <c r="H752" t="n">
         <v>229054</v>
@@ -22293,7 +22293,7 @@
         <v>3.01399993896484</v>
       </c>
       <c r="G756" t="n">
-        <v>2.53854322433472</v>
+        <v>2.53854298591614</v>
       </c>
       <c r="H756" t="n">
         <v>339559</v>
@@ -22380,7 +22380,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G759" t="n">
-        <v>2.48295450210571</v>
+        <v>2.48295474052429</v>
       </c>
       <c r="H759" t="n">
         <v>299028</v>
@@ -22467,7 +22467,7 @@
         <v>3.03399991989136</v>
       </c>
       <c r="G762" t="n">
-        <v>2.5553879737854</v>
+        <v>2.55538821220398</v>
       </c>
       <c r="H762" t="n">
         <v>577970</v>
@@ -22583,7 +22583,7 @@
         <v>3.09599995613098</v>
       </c>
       <c r="G766" t="n">
-        <v>2.6076078414917</v>
+        <v>2.60760760307312</v>
       </c>
       <c r="H766" t="n">
         <v>954705</v>
@@ -22612,7 +22612,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G767" t="n">
-        <v>2.5772864818573</v>
+        <v>2.57728672027588</v>
       </c>
       <c r="H767" t="n">
         <v>598686</v>
@@ -22670,7 +22670,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G769" t="n">
-        <v>2.57560205459595</v>
+        <v>2.57560229301453</v>
       </c>
       <c r="H769" t="n">
         <v>237570</v>
@@ -22699,7 +22699,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G770" t="n">
-        <v>2.57223320007324</v>
+        <v>2.57223296165466</v>
       </c>
       <c r="H770" t="n">
         <v>235087</v>
@@ -22728,7 +22728,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G771" t="n">
-        <v>2.58907794952393</v>
+        <v>2.5890781879425</v>
       </c>
       <c r="H771" t="n">
         <v>233031</v>
@@ -22815,7 +22815,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G774" t="n">
-        <v>2.67835688591003</v>
+        <v>2.67835664749146</v>
       </c>
       <c r="H774" t="n">
         <v>844822</v>
@@ -22844,7 +22844,7 @@
         <v>3.14199995994568</v>
       </c>
       <c r="G775" t="n">
-        <v>2.64635109901428</v>
+        <v>2.64635133743286</v>
       </c>
       <c r="H775" t="n">
         <v>1054352</v>
@@ -22931,7 +22931,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G778" t="n">
-        <v>2.71710014343262</v>
+        <v>2.7171003818512</v>
       </c>
       <c r="H778" t="n">
         <v>964874</v>
@@ -22960,7 +22960,7 @@
         <v>3.20600008964539</v>
       </c>
       <c r="G779" t="n">
-        <v>2.70025539398193</v>
+        <v>2.70025515556335</v>
       </c>
       <c r="H779" t="n">
         <v>409180</v>
@@ -23076,7 +23076,7 @@
         <v>3.20600008964539</v>
       </c>
       <c r="G783" t="n">
-        <v>2.70025539398193</v>
+        <v>2.70025515556335</v>
       </c>
       <c r="H783" t="n">
         <v>938332</v>
@@ -23105,7 +23105,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G784" t="n">
-        <v>2.71710014343262</v>
+        <v>2.7171003818512</v>
       </c>
       <c r="H784" t="n">
         <v>578855</v>
@@ -23250,7 +23250,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G789" t="n">
-        <v>2.84680700302124</v>
+        <v>2.84680676460266</v>
       </c>
       <c r="H789" t="n">
         <v>815915</v>
@@ -23395,7 +23395,7 @@
         <v>3.14199995994568</v>
       </c>
       <c r="G794" t="n">
-        <v>2.64635109901428</v>
+        <v>2.64635133743286</v>
       </c>
       <c r="H794" t="n">
         <v>768072</v>
@@ -23627,7 +23627,7 @@
         <v>3.36800003051758</v>
       </c>
       <c r="G802" t="n">
-        <v>2.83669972419739</v>
+        <v>2.83669996261597</v>
       </c>
       <c r="H802" t="n">
         <v>706988</v>
@@ -23714,7 +23714,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G805" t="n">
-        <v>2.93776988983154</v>
+        <v>2.93776965141296</v>
       </c>
       <c r="H805" t="n">
         <v>557350</v>
@@ -23975,7 +23975,7 @@
         <v>3.38800001144409</v>
       </c>
       <c r="G814" t="n">
-        <v>2.85354495048523</v>
+        <v>2.85354471206665</v>
       </c>
       <c r="H814" t="n">
         <v>347337</v>
@@ -24091,7 +24091,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G818" t="n">
-        <v>2.45600271224976</v>
+        <v>2.45600247383118</v>
       </c>
       <c r="H818" t="n">
         <v>1497205</v>
@@ -24120,7 +24120,7 @@
         <v>3.00600004196167</v>
       </c>
       <c r="G819" t="n">
-        <v>2.53180527687073</v>
+        <v>2.53180503845215</v>
       </c>
       <c r="H819" t="n">
         <v>790572</v>
@@ -24526,7 +24526,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G833" t="n">
-        <v>2.69183301925659</v>
+        <v>2.69183278083801</v>
       </c>
       <c r="H833" t="n">
         <v>488767</v>
@@ -24555,7 +24555,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G834" t="n">
-        <v>2.67835688591003</v>
+        <v>2.67835664749146</v>
       </c>
       <c r="H834" t="n">
         <v>708286</v>
@@ -24584,7 +24584,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G835" t="n">
-        <v>2.65814256668091</v>
+        <v>2.65814280509949</v>
       </c>
       <c r="H835" t="n">
         <v>524048</v>
@@ -24642,7 +24642,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G837" t="n">
-        <v>2.67835688591003</v>
+        <v>2.67835664749146</v>
       </c>
       <c r="H837" t="n">
         <v>361053</v>
@@ -24700,7 +24700,7 @@
         <v>3.25</v>
       </c>
       <c r="G839" t="n">
-        <v>2.73731446266174</v>
+        <v>2.73731422424316</v>
       </c>
       <c r="H839" t="n">
         <v>461413</v>
@@ -24816,7 +24816,7 @@
         <v>3.25</v>
       </c>
       <c r="G843" t="n">
-        <v>2.73731446266174</v>
+        <v>2.73731422424316</v>
       </c>
       <c r="H843" t="n">
         <v>565490</v>
@@ -24961,7 +24961,7 @@
         <v>3.33599996566772</v>
       </c>
       <c r="G848" t="n">
-        <v>2.80974793434143</v>
+        <v>2.80974769592285</v>
       </c>
       <c r="H848" t="n">
         <v>1117559</v>
@@ -25251,7 +25251,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G858" t="n">
-        <v>2.7979564666748</v>
+        <v>2.79795622825623</v>
       </c>
       <c r="H858" t="n">
         <v>402306</v>
@@ -25338,7 +25338,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G861" t="n">
-        <v>2.78784942626953</v>
+        <v>2.78784918785095</v>
       </c>
       <c r="H861" t="n">
         <v>436318</v>
@@ -25483,7 +25483,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G866" t="n">
-        <v>2.68677926063538</v>
+        <v>2.68677949905396</v>
       </c>
       <c r="H866" t="n">
         <v>1350411</v>
@@ -25541,7 +25541,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G868" t="n">
-        <v>2.65814256668091</v>
+        <v>2.65814280509949</v>
       </c>
       <c r="H868" t="n">
         <v>1567922</v>
@@ -35581,6 +35581,35 @@
         <v>1691456</v>
       </c>
       <c r="I1214" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1215" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1215" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="D1215" t="n">
+        <v>2.13599991798401</v>
+      </c>
+      <c r="E1215" t="n">
+        <v>2.07599997520447</v>
+      </c>
+      <c r="F1215" t="n">
+        <v>2.09200000762939</v>
+      </c>
+      <c r="G1215" t="n">
+        <v>2.09200000762939</v>
+      </c>
+      <c r="H1215" t="n">
+        <v>1845214</v>
+      </c>
+      <c r="I1215" t="s">
         <v>9</v>
       </c>
     </row>
